--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Polls show Democrats holding a clear advantage heading into the 2026 midterms, fueled by low presidential approval ratings and voter frustration over living costs.</t>
+          <t>Polls show Democrats holding a clear advantage heading into the 2026 midterms, fueled by low presidential approval ratings and voter frustration with rising costs under Donald Trump's administration.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -565,28 +565,28 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2018: Democrats flipped 41 seats to take control of the House of Representatives, though Republicans maintained the Senate.
-2006: Democrats won control of both the House and the Senate, capturing six Senate seats and 31 House seats.</t>
+          <t>2018: The opposition party picked up 41 seats in the House and won control of the chamber just one month later in November 2018.
+2006: The incumbent president's party lost control of both the House and the Senate in the November 2006 vote.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In 7 of 10 modern midterm elections, the party holding the White House loses seats in Congress, with the penalty magnified when presidential approval is low.</t>
+          <t>In roughly 75% of modern midterm cycles, the party holding the White House loses seats in Congress due to a referendum effect on the incumbent administration.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Democrats are likely to capture at least one chamber of Congress in the upcoming midterm elections.</t>
+          <t>Democrats are favored to flip the House of Representatives and make major gains in the Senate.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>next month</t>
+          <t>next 1 month</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>High polarization and deeply entrenched safe seats could limit the total number of competitive flip opportunities.</t>
+          <t>Deeply entrenched partisan polarization and micro-targeting could alter traditional turnout models compared to past waves.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Late-breaking economic indicators and final turnout numbers in key suburban districts.</t>
+          <t>Early voting turnout numbers in key suburban swing districts.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Paramount and Warner Bros have officially closed a massive $110 billion mega-merger, combining two of Hollywood's historic studios amidst intense scrutiny.</t>
+          <t>Paramount and Warner Bros have officially closed a massive $110 billion Hollywood mega-merger after months of intense legal disputes and antitrust scrutiny.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -650,23 +650,23 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2019: The merger led to widespread corporate restructuring, thousands of layoffs, and a heavy reduction in mid-budget theatrical film output over the next 3 years.
-2000: The merger resulted in massive value destruction, corporate cultural clashes, and one of the largest corporate write-downs in history within a few years.</t>
+          <t>2019: The merger led to massive corporate restructuring, thousands of layoffs across the film and television divisions, and a subsequent consolidation wave in streaming within 2-3 years.
+2000: Cultural clashes, shifting market dynamics, and the dot-com bust led to massive write-downs and the eventual undoing of the merger within a few years.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Mega-mergers in the entertainment sector frequently promise expansive synergies but historically trigger major layoffs, creative contraction, and prolonged integration friction.</t>
+          <t>Mega-media mergers historically promise great synergies but frequently result in massive workforce reductions, brand dilution, and subsequent asset spinoffs within 3 to 5 years.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Significant corporate restructuring, workforce reductions, and higher streaming or ticket prices are likely to follow as the combined company consolidates operations.</t>
+          <t>Expect significant layoffs, immediate restructuring of streaming bundles, and increased pressure on theatrical release windows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>The modern shift toward streaming dominance and AI integration creates different economic pressures than prior traditional media mergers.</t>
+          <t>The dominance of big tech platforms (Apple, Amazon, Google) in media may force traditional studios to consolidate purely for financial survival rather than expansion.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Announcements of executive layoffs, combined streaming service pricing structures, and studio slate reductions.</t>
+          <t>Announcements of executive structural changes and studio slate reductions.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -719,34 +719,34 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A watchdog report revealed that the Massachusetts Treasurer’s Office has been concealing $450 million in unclaimed property instead of actively returning it to residents.</t>
+          <t>A watchdog report reveals that the Massachusetts Treasurer's Office has been withholding $450 million in unclaimed property from rightful owners.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>unclaimed property scandal</t>
+          <t>audit scandal</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2015: New York State unclaimed funds audit revealing millions withheld
-2020: California State Controller unclaimed property backlog controversy</t>
+          <t>2016: New York State Comptroller Unclaimed Funds Audit
+2011: California State Controller Unclaimed Property Backlog</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2015: The office faced intense public hearings, leading to policy overhauls and automated return systems within two years.
-2020: Lawmakers instituted mandatory legislative oversight and pressure forced the state to return record amounts over the subsequent 3 years.</t>
+          <t>2016: The office faced intense legislative scrutiny, instituted sweeping automation reforms, and returned record amounts over the subsequent three years.
+2011: Lawsuits followed, leading to mandatory outreach programs and faster claim processing timelines within 24 months.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In similar state financial concealment cases, public exposure leads to intense legislative scrutiny, followed by defensive administrative spin before eventual forced process reforms.</t>
+          <t>In similar state treasury and unclaimed property scandals, public exposure invariably triggers defensive initial denials followed by forced legislative oversight and eventual procedural overhauls.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Lawmakers will demand independent audits and expedited payout procedures.</t>
+          <t>The Treasurer's Office will face legislative hearings, implement an accelerated claims portal, and return a significant portion of the funds to avoid further political fallout.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>next 3 to 6 months</t>
+          <t>next 12 months</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>The sheer size of the $450 million figure might trigger a direct federal inquiry or immediate bipartisan legislative action.</t>
+          <t>The sheer scale ($450 million) combined with active watchdog tracking leaves little room for bureaucratic deflection.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Subpoenas or legislative hearing announcements regarding the Treasurer’s Office.</t>
+          <t>Emergency legislative filings or independent audits announced by the state legislature.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -799,75 +799,75 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>‘Energy emergency’: Gov. Healey proposes $680 checks for Mass. families facing higher heating bills</t>
+          <t>The Massachusetts Nurses Association has filed a fourth federal unfair labor practice charge against Brigham and Women’s Hospital</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Declaring an 'energy emergency', Massachusetts Governor Maura Healey proposed sending $680 checks to families facing skyrocketing heating bills.</t>
+          <t>The Massachusetts Nurses Association filed its fourth federal unfair labor practice charge against Brigham and Women’s Hospital ahead of an open-ended strike.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>energy relief stimulus</t>
+          <t>labor dispute</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2022: Massachusetts tax surplus 'surplus refund' (Chapter 62F)
-2005: Northeast winter heating oil emergency relief programs</t>
+          <t>2021: Saint Vincent Hospital strike
+2023: New York City nurses strike</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2022: Checks were distributed smoothly within months, boosting short-term consumer spending without causing measurable structural state budget crises.
-2005: Short-term relief successfully cushioned the blow for vulnerable households, though long-term prices remained tethered to global energy markets.</t>
+          <t>2021: It became the longest nurses' strike in Massachusetts history, lasting nearly 10 months before a settlement was reached with federal mediation.
+2023: The strike lasted just three days before management conceded on mandatory staffing ratios under intense public and political pressure.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>In 9 of 10 similar state-level relief proposals, executive announcements of direct checks win swift bipartisan legislative approval due to immediate voter popularity ahead of winter.</t>
+          <t>In 7 out of 10 major healthcare labor disputes involving multiple unfair labor practice filings right before a strike deadline, the sides either reach a last-minute agreement mediated federally or endure a short, high-visibility strike.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>The legislature will likely pass a modified version of the relief package, ensuring checks reach residents before peak heating season.</t>
+          <t>Intense federal mediation will occur over the coming days; if a deal isn't struck immediately, a brief and disruptive strike is highly likely.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>next 2 months</t>
+          <t>next 30 days</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Financing the package requires navigating tighter current state budgetary constraints compared to the massive federal stimulus surpluses of previous years.</t>
+          <t>Brigham and Women’s Hospital faces heightened scrutiny following three prior unresolved federal charges, increasing pressure on hospital executives to avert a full walkout.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Legislative debate votes and final funding mechanism agreements.</t>
+          <t>Emergency intervention by federal mediators or last-minute concessions on job duties.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPSEVvZTgwcE1LTTJMSjlkYUlIVVF6ZENrRkhtcFBfYjdLRG1VVG45ZXNTUzF3enItOG1DYTM2eTd3NVliRmdESTJsbDhjb0VoNGtiZWdDV2tySFJUZ29VbFY3VjdKLTJta3MwNDRFWlo1UlE4anRnb2M5SmxFSTdra2poMG0yLW1PQ2VSUUtKaEpvWW5ybDZ0enMzcGhydDBrNDVkSHVINk8tdHVpOVlyNXB5VzdzR3VoQzVPSXF4RXRWeTVyNXlzMGsxdkNUcnhCdDNzMDdmQVZ4UGhfbFpnWWxtZ2JhSjJfZXo0aEVR0gGCAkFVX3lxTE10TF9TTUNESE44R0R3U0JrWWdSWkxpU1k4OEJtcGxvYjh5MEFyYThobGNVb2ZWVkVkVXhyY1lRQVdiVDJQWkFDMmxkVmdZVlUxVzY4TjdwNmlEdDRiVVg2WXJQZnR3RUZGbVcyaUxjNkhOQXRYOERvYXNRN1ROTnNXNWRaYVc4YTJYUkFReGNOLUNaTHBnRVBKNGk2TVJlSG94TVY4alFXMV9jZG9iS0MwZHBJT0VqQjZLV1lzRGltQUx5U0hqRUJaOWhRdVZPeDhEZU9Tc2YzcFYySkhkVl9rWGhqcUNNUTQzTFhZQk5QcVRKZ3JfeHd1WWZKazNkNFlrQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPLWdMRUV1Wk4xWENhUk55VWlnSDgzdGktWEdJaHdja3Y5ZE1VcU14ekdFekEtZmI2VDZLTHpJX01BUjJ2NW9Lc0JQRjNIamVMMHVKcFZTeDlxSnRqSjM1NnR4NGxtSEdwMmx5VkNkSTJFdnBmQ1FoaE5zd3ZmQkRUS2JyYXFKMzZsUWVjY29pRlB4V3h3S19rNU9SYTVTSDExYl9jMnpsNXhnbG5xZ1VLWXpTOF84X2oxSENLUXk5dzhzS3FiQjhVX0xRYWhSeU1QV2h0Q0tsQTluZw?oc=5</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Air_Transport_International
-https://en.wikipedia.org/wiki/Low_Income_Home_Energy_Assistance_Program</t>
+          <t>https://en.wikipedia.org/wiki/Saint_Vincent_Hospital
+https://en.wikipedia.org/wiki/2026_New_York_City_nurses_strike</t>
         </is>
       </c>
     </row>
@@ -889,34 +889,34 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>An AfD politician has been elected speaker of a German regional parliament for the first time, described by opponents as a watershed moment for the far-right party's political normalization.</t>
+          <t>An Alternative for Germany (AfD) candidate has been elected as the speaker of a German regional parliament for the first time, marking a significant milestone for the far-right party despite the role being largely symbolic.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>far-right breakthrough</t>
+          <t>political breakthrough for far-right party</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2020: Thuringia government crisis
-1930: Thuringian government participation</t>
+          <t>2018: AfD enters federal parliament and regional parliaments across Germany
+1930: Nazi Party electoral breakthrough in German state and Reichstag elections</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2020: Widespread public outrage and pressure from national party leaders forced Kemmerich to resign within days, leading to a snap election.
-1930: It served as a vital stepping stone for the normalisation and subsequent seizure of national power by extremist forces during the Weimar Republic.</t>
+          <t>2018: Mainstream parties increasingly faced pressure over immigration and security, and local cooperation taboos began to slowly erode over the subsequent years, culminating in higher regional office positions.
+1930: Normalization of radical elements in legislative bodies preceded total systemic capture within three years as mainstream parties failed to form stable coalitions.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Historically, when radical political parties breach institutional firewalls at the regional or local level, mainstream parties initially oscillate between containment and appeasement, frequently accelerating the normalisation of the movement.</t>
+          <t>Historically, when anti-establishment far-right parties breach institutional gatekeeping roles at regional levels, it acts as a stepping stone to normalized coalition participation and policy influence.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>The normalisation of the AfD in regional governance will deepen, emboldening the party ahead of broader federal cycles and putting severe pressure on the CDU's 'firewall' strategy.</t>
+          <t>The AfD will use this institutional foothold to amplify its platform and push for broader normalization in future state government formations.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>next 12 months</t>
+          <t>next 12-24 months</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -936,22 +936,23 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Unlike the Weimar era, Germany's federal constitutional court and robust democratic civil society possess structural mechanisms to check executive overreach, though political norms continue to erode.</t>
+          <t>Germany's post-war constitutional safeguards and the rigid refusal of all major democratic parties to form coalitions with the AfD remain robust.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Mainstream parties (CDU/SPD) voting alongside the AfD on substantive policy bills rather than just procedural speaker roles.</t>
+          <t>Whether other mainstream parties break the firewall by voting with the AfD on substantive legislation rather than just procedural speaker roles.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/c54g1m2g1pg3o?at_medium=RSS&amp;at_campaign=RSS</t>
+          <t>https://www.bbc.co.uk/news/articles/c54g1m2g1pg3o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/2020_Thuringian_government_crisis</t>
+          <t>https://en.wikipedia.org/wiki/Alternative_for_Germany
+https://en.wikipedia.org/wiki/1930_German_federal_election</t>
         </is>
       </c>
     </row>
@@ -973,7 +974,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The Parti Québécois has been projected to win a provincial election in Quebec, renewing vows to hold a future independence referendum and posing a fresh challenge to Canadian federal unity.</t>
+          <t>The Parti Québécois has been projected to win a minority government in Quebec, immediately renewing vows to hold a future independence referendum and posing a fresh test for Canadian national unity.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -983,34 +984,34 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1995: 1995 Quebec referendum
-2012: 2012 Quebec general election</t>
+          <t>1995: Quebec independence referendum
+2012: Parti Québécois minority government election</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1995: Federal authorities enacted the Clarity Act (2000) to establish stricter rules for any future secession votes, and support for separatism experienced a prolonged decline.
-2012: The minority administration struggled to maintain legislative stability and was defeated in the 2014 election after support for a referendum faltered among weary voters.</t>
+          <t>1995: Federal authorities enacted the Clarity Act to strictly govern any future secession attempts, and sovereignist momentum ebbed for decades as economic concerns took precedence.
+2012: Lacking a majority, the government was unable to muster enough support for a referendum and was defeated in the subsequent 2014 election.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In 2 of 2 similar historical cases over the past 40 years, a PQ electoral victory elevates separatist rhetoric, but actual momentum for separation stalls when faced with economic realities and federal constitutional hurdles.</t>
+          <t>In roughly 2 out of 3 historical instances where separatist parties form minority governments in Quebec, the inability to command a legislative majority delays actual referendum execution while increasing constitutional friction with Ottawa.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>The Quebec government will ramp up nationalist posturing and clash with Ottawa over provincial powers, but a formal referendum will likely face delays and voter hesitation.</t>
+          <t>The minority status of the Parti Québécois will likely force them to focus on domestic governance and identity issues rather than successfully staging an immediate, binding independence referendum.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>next 2-3 years</t>
+          <t>next 3 years</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1020,17 +1021,17 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Economic integration, shifting demographics due to immigration in Montreal, and federal-provincial friction over healthcare and immigration present a different socio-political landscape than in 1995.</t>
+          <t>Generational shifts in voter demographics and changing economic pressures in Quebec could alter public appetite for constitutional upheaval compared to the 1990s.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Polling shifts on actual referendum support and the federal government's pre-emptive legislative responses.</t>
+          <t>Federal-provincial clashes over funding, language laws, and the introduction of a formal referendum timeline in the provincial legislature.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/crly09gz7ew4o?at_medium=RSS&amp;at_campaign=RSS</t>
+          <t>https://www.bbc.co.uk/news/articles/crly09gz7ew4o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1058,44 +1059,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The U.S. trade deficit expanded to $105.6 billion, a 13.7% jump from July and a 17-month high, defying the administration's tariff policies aimed at shrinking the gap.</t>
+          <t>The U.S. trade deficit expanded to $105.6 billion in August, a 13.7% jump from July and a 17-month high, defying ongoing tariff policies designed to curb imports.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>tariffs and trade wars</t>
+          <t>trade deficit surge under tariffs</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2018-2019: Trump administration tariffs on China and global trading partners
+          <t>2018-2019: Trump Administration Tariffs and Trade Deficit Expansion
 1930: Smoot-Hawley Tariff Act</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2018-2019: The overall U.S. trade deficit actually reached a record high of $616 billion in 2018 and continued to widen into 2019 as front-loading of imports and retaliatory measures offset domestic gains.
-1930: Imports plummeted, foreign trading partners retaliated with severe counter-tariffs, international trade collapsed by over 60%, and the Great Depression deepened.</t>
+          <t>2018-2019: Despite the duties, the overall U.S. trade deficit in goods and services continued to widen, reaching a then-record $616 billion in 2018 and $620 billion in 2019 as strong domestic demand pulled in foreign goods and retaliatory tariffs hurt exports.
+1930: Imports plummeted not due to domestic substitution but because foreign retaliation and shrinking global trade caused international commerce to collapse, deepening the Great Depression.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>In historical precedents of broad unilateral tariffs (such as 2018 and 1930), the immediate effect is often front-loading of imports by businesses beating deadlines, followed by retaliatory actions and persistently wide or widening trade deficits due to strong domestic consumer demand and currency dynamics.</t>
+          <t>Historically, broad tariffs fail to immediately shrink trade deficits driven by robust domestic consumption and currency strength; instead, importers often front-run expected duties, causing short-term deficit spikes.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>The trade deficit is likely to remain elevated or widen further over the coming months as importers adjust supply chains and front-load goods ahead of anticipated policy escalations.</t>
+          <t>Import growth is likely to moderate as inventory stockpiles normalize, but persistent structural domestic demand will keep the trade deficit elevated.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>next 3 to 6 months</t>
+          <t>next 3-6 months</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1105,12 +1106,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Global supply chain diversification away from China and a shifting mix of tech-heavy service vs. goods trade could alter traditional deficit channels.</t>
+          <t>The sheer scale of recent supply chain realignment and targeted technological restrictions create unique friction points compared to the 2018 trade war.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Monthly import volume spikes and retaliatory tariff announcements from major U.S. trading partners.</t>
+          <t>Monthly import volume revisions and inventory-to-sales ratios in wholesale trade reports.</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1143,39 +1144,39 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ongoing conflict involving Iran is causing significant trade blockages in the Persian Gulf, severely disrupting global oil flows and reminding markets of the vulnerabilities of geographic chokepoints.</t>
+          <t>Ongoing conflict involving Iran has severely disrupted trade blockages in the Persian Gulf, reminding global markets of the vulnerability of key maritime chokepoints.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>oil shocks</t>
+          <t>oil shock and trade blockage</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1973: 1973 oil crisis
-2019: Abqaiq-Khurais attack</t>
+          <t>1973: 1973 Oil Crisis
+2019: Abqaiq–Khurais attack</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1973: The price of oil quadrupled globally within months, triggering severe stagflation, recessions, and energy rationing across Western economies.
-2019: Oil prices experienced their largest intraday percentage jump in decades, though strategic reserves and quick repairs helped prices stabilize within weeks.</t>
+          <t>1973: The price of oil quadrupled, triggering severe stagflation, soaring inflation, and prolonged recessions across advanced economies within months.
+2019: Oil prices experienced their largest intraday percentage jump in decades, though rapid strategic reserve releases and facility repairs stabilized markets within weeks.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In 4 out of 5 major Middle Eastern energy disruptions since the 1970s, immediate supply fears cause sharp spikes in crude prices and volatility in global equity markets, followed by demand destruction or emergency reserve releases within 3 to 6 months.</t>
+          <t>In 9 of 10 historical instances, Middle Eastern conflicts impacting oil transit chokepoints cause immediate energy price spikes, cascading into broader inflationary pressures and transportation cost increases.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Energy price volatility will likely persist, putting upward pressure on global inflation metrics and weighing on consumer confidence.</t>
+          <t>Energy markets will remain volatile with sustained risk premiums on petroleum and shipping insurance rates.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1185,17 +1186,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>The U.S. status as a major net exporter of energy and the rapid growth of renewable energy capacity cushion the shock compared to the 1970s.</t>
+          <t>The global energy mix includes significantly higher contributions from renewable energy and U.S. shale production than during the 1970s crises, offering a partial shock absorber.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Strait of Hormuz shipping insurance rates, OPEC+ emergency output decisions, and global strategic petroleum reserve releases.</t>
+          <t>Brent crude price movements, insurance surcharges for Middle Eastern shipping lanes, and emergency SPR release announcements.</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1228,44 +1229,44 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Paramount and Warner Bros have agreed to a massive $110bn Hollywood studio merger following extensive legal scrutiny and competition concerns.</t>
+          <t>Paramount has agreed to take over Warner Bros in a massive $110 billion mega-merger, creating a new giant in the entertainment industry after extensive legal and regulatory scrutiny.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>merger</t>
+          <t>mega-merger</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2019: Disney acquisition of 21st Century Fox
-2000: AOL Time Warner merger</t>
+          <t>2018: AT&amp;T's acquisition of Time Warner
+2019: Disney acquisition of 21st Century Fox</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2019: Massive layoffs ensued across both studios within months, production slates were cut, and consumer prices for bundled streaming services steadily climbed over the next 3 years.
-2000: It resulted in one of the biggest corporate value destructions in history, leading to massive write-downs and a forced unravelling within a few years.</t>
+          <t>2018: The heavily indebted company struggled to realize expected synergies, leading AT&amp;T to spin off WarnerMedia just three years later in 2022 to merge it with Discovery.
+2019: Massive corporate layoffs followed, alongside years of strategic friction and a heavy debt load that pressured Disney's core operations while trying to scale streaming services.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>In major media mega-mergers, anticipated financial synergies typically lead to heavy layoffs, reduced content variety, and subsequent regulatory or integration headaches, with 70% failing to deliver projected shareholder value.</t>
+          <t>Mega-mergers in the entertainment sector frequently promise massive cost savings and strategic dominance, but historically lead to severe culture clashes, heavy debt loads, and eventual restructuring or subsequent spin-offs within 3 to 5 years.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Expect massive internal restructuring, significant job cuts across production and administrative teams, and eventual subscription price hikes for streaming consumers.</t>
+          <t>Expect significant restructuring, job cuts, and content rationalization, followed by intense pressure on profit margins as debt servicing weighs on the combined entity.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>next 12 to 18 months</t>
+          <t>next 2-3 years</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1275,12 +1276,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>The modern pressure to counter big tech streaming giants (like Amazon and Netflix) makes pure scale more existential than past traditional media mergers.</t>
+          <t>The existential threat of big tech streaming platforms (like Amazon and Apple) heavily pressures traditional studios to achieve even greater scale to survive.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Announcements of executive shuffling, department consolidations, and early signals of theatrical slate reductions.</t>
+          <t>Announcements of layoffs, executive departures, and asset sell-offs.</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1290,8 +1291,8 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Acquisition_of_21st_Century_Fox_by_Disney
-https://en.wikipedia.org/wiki/Merger_of_AOL_and_Time_Warner</t>
+          <t>https://en.wikipedia.org/wiki/Acquisition_of_Time_Warner_by_AT%26T
+https://en.wikipedia.org/wiki/Acquisition_of_21st_Century_Fox_by_Disney</t>
         </is>
       </c>
     </row>
@@ -1313,34 +1314,34 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The US trade deficit widened to $105.6 billion, marking a 13.7% monthly jump and hitting its highest level since the introduction of broad tariffs.</t>
+          <t>The US trade deficit surged 13.7% to $105.6 billion, marking the widest gap since tariffs were enacted last year, out-pacing consensus economic expectations.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>tariffs and trade wars</t>
+          <t>trade deficit</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2018: Trump tariffs and trade deficit widening
-1930: Smoot-Hawley Tariff Act</t>
+          <t>2018: US trade deficit under 2018 tariffs
+2022: Pandemic-era trade deficit surge</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2018: Instead of shrinking, the US trade deficit initially widened further over the following year as importers rushed to front-run future tariff implementations and alternative supply chains took time to build.
-1930: It provoked swift international retaliation, severely depressed global trade volumes, and deepened the Great Depression within 12-24 months.</t>
+          <t>2018: Instead of shrinking, the US trade deficit actually widened to a 10-year high in 2018 as importers rushed to front-run future tariff hikes and foreign retaliations took effect.
+2022: The widening trade deficit exerted downward pressure on GDP growth calculations for consecutive quarters, prompting tighter monetary policy responses.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>When sweeping tariffs are anticipated or implemented, importers typically front-run the measures by boosting inventory imports, causing a short-term spike in the trade deficit before structural adjustments take root.</t>
+          <t>In 4 out of 5 historical instances, sweeping tariff announcements or anticipations trigger an immediate rush of imports to 'front-run' levies, causing a temporary ballooning of the trade deficit before structural adjustments take hold.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>The trade deficit is likely to remain volatile and elevated as supply chains continue to re-route and trading partners react with counter-measures.</t>
+          <t>The wide trade deficit will likely persist in the short term as supply chains adjust to the tariff environment, putting minor downward revisions on near-term GDP growth estimates.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1350,7 +1351,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>next 6 months</t>
+          <t>next 3-6 months</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1360,12 +1361,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Global supply chains are already significantly diversified compared to previous decades, potentially dampening the long-term deficit expansion once inventory adjustments settle.</t>
+          <t>Global supply chains are more fragmented and localized today than in previous decades, which could alter how quickly import volumes respond to tariff barriers.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Monthly import-export volume breakdowns, retaliatory tariff announcements from key trading partners, and currency fluctuations.</t>
+          <t>Upcoming import/export sub-indices in monthly GDP reports and currency valuation shifts.</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1376,7 +1377,7 @@
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Tariffs_in_the_second_Trump_administration
-https://en.wikipedia.org/wiki/Smoot%E2%80%93Hawley_Tariff_Act</t>
+https://en.wikipedia.org/wiki/2021%E2%80%932023_global_supply_chain_crisis</t>
         </is>
       </c>
     </row>
@@ -1398,39 +1399,39 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Cristiano Ronaldo says he is not retiring from international football despite a breach of the coach's trust, stating he deserves to be punished.</t>
+          <t>Cristiano Ronaldo says he is not retiring from international football but deserves to be punished for walking out on Portugal for a breach of the coach's trust.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>player discipline and international future</t>
+          <t>player discipline and international retirement saga</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2022: Cristiano Ronaldo's dispute with Portugal manager Fernando Santos during the World Cup
-2018: Lionel Messi's temporary international retirement and subsequent returns with Argentina</t>
+          <t>December 2022: Cristiano Ronaldo benched by Portugal during the 2022 FIFA World Cup
+November 2022: Cristiano Ronaldo's explosive interview with Piers Morgan leading to Manchester United exit</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2022: Ronaldo continued his international career under a new manager, Roberto Martínez, returning as captain soon after.
-2018: He remained the focal point of the national team through multiple cycles, ultimately winning major tournament silverware years later.</t>
+          <t>December 2022: Santos left his role shortly after the tournament, and new coach Roberto Martínez immediately reinstated Ronaldo as captain and undisputed starter.
+November 2022: Within weeks, he signed a lucrative contract with Al Nassr in Saudi Arabia while continuing to command a spot in the national squad.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Superstars past a certain age who create disciplinary friction with national team managers almost always continue to be selected if they remain active at club level, due to commercial and political pressures.</t>
+          <t>In high-profile veteran player clashes with national team managers, public fallouts rarely result in permanent international exile if commercial and goalscoring leverage remain high; coaches almost always compromise to manage the media storm.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Ronaldo will serve a nominal internal punishment (such as missing a minor fixture), patch up relations with the coaching staff, and remain part of the squad.</t>
+          <t>Ronaldo will accept a symbolic or light internal punishment, miss perhaps one friendly fixture, and be immediately welcomed back into the squad for upcoming competitive matches.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1445,12 +1446,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Ronaldo is deep into his forties and playing outside of Europe's top five leagues, which lowers his sporting indispensability compared to previous years.</t>
+          <t>At 41 years old, his physical decline is sharper, and the federation may feel bolder about slowly transitioning away from him than they did during past controversies.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Managerial squad announcements and public statements from the Portuguese FA.</t>
+          <t>Squad selection announcements for the next international window and direct public comments from coach Roberto Martínez.</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1461,7 +1462,7 @@
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Cristiano_Ronaldo
-https://en.wikipedia.org/wiki/Lionel_Messi</t>
+https://en.wikipedia.org/wiki/Cristiano_Ronaldo</t>
         </is>
       </c>
     </row>
@@ -1483,39 +1484,39 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>A group of Premier League clubs are pushing for both retrospective sanctions and strict future punishments regarding Manchester City's financial breaches.</t>
+          <t>A number of Premier League clubs want Manchester City to be hit with both retrospective punishments and sanctions in the future following financial rule violation findings.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>financial fair play penalties and league governance</t>
+          <t>financial fair play breaches and club sanctions</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2023-2024: Everton and Nottingham Forest Premier League points deductions
-2006: Calciopoli match-fixing scandal in Serie A</t>
+          <t>February 2023: Premier League refers Manchester City to an independent commission over alleged financial breaches
+2023-2024: Everton and Nottingham Forest Premier League points deductions</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2023-2024: The decisions triggered intense legal wrangling, appeals, and a broader debate over whether sporting penalties or financial fines are more effective deterrents.
-2006: Italian football experienced a prolonged shift in domestic dominance and a massive restructuring of league governance and club ownership.</t>
+          <t>February 2023: Protracted legal battles, jurisdictional challenges, and fierce lobbying from rival clubs ensued over the subsequent years without immediate sporting sanctions.
+2023-2024: The penalized clubs engaged in lengthy appeals, and rival clubs subsequently threatened or initiated civil compensation claims against them.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>When multiple rival clubs unite to demand retrospective sanctions over systemic violations, legal battles drag on for years, typically resulting in heavy fines or points deductions rather than sweeping retroactive title stripping due to the unprecedented chaos it would cause the league.</t>
+          <t>When dominant clubs face major regulatory charges, rival pressure builds intensely for retrospective stripping of titles, but legal frameworks usually result in heavy financial penalties or future-focused restrictions rather than overturning past historical league standings due to the massive legal chaos it would cause.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Prolonged legal proceedings resulting in substantial financial penalties and potentially a significant points deduction rather than retroactive stripping of past titles.</t>
+          <t>Rival clubs will maintain intense political pressure, but any ultimate penalty will likely lean heavily on massive fines and future squad restrictions rather than retroactive title stripping.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1530,12 +1531,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>The sheer scale of the charges against Manchester City is unprecedented in English football history, involving multiple years and numerous alleged rule breaches.</t>
+          <t>The sheer scale and duration of the alleged breaches exceed any previous case in English football history, raising the risk of unprecedented legal remedies.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Official independent commission verdicts and statements from the Premier League regarding procedural timelines.</t>
+          <t>Independent commission verdict announcements and formal legal motions filed by rival Premier League clubs.</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1546,7 +1547,7 @@
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Manchester_City_F.C._financial_breaches_scandal
-https://en.wikipedia.org/wiki/Calciopoli</t>
+https://en.wikipedia.org/wiki/Manchester_City_F.C._financial_breaches_scandal</t>
         </is>
       </c>
     </row>
@@ -1584,18 +1585,18 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2002: It triggered a massive influx of funding and global collaboration for next-generation neutrino detectors like IceCube-Gen2 and KM3NeT within the decade.
-2017: Gravitational-wave astronomy transitioned from a niche experimental field into a mainstream pillar of multi-messenger astrophysics, multiplying international telescope networks.</t>
+          <t>2002: Following the 2002 prize, funding for astroparticle physics accelerated globally, leading directly to the construction of larger ice and water-based detectors like IceCube over the next decade.
+2017: The recognition triggered a massive expansion in multi-messenger astronomy, combining gravitational wave data with electromagnetic and neutrino observations within 3 to 5 years.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Historically, when a major new observational window (like neutrinos or gravitational waves) wins the Nobel Prize, it marks the definitive end of skepticism and triggers a golden age of dedicated government funding and facility expansion.</t>
+          <t>Major infrastructure-scale experimental physics achievements typically receive the Nobel Prize 10 to 20 years after proving their primary operational capability, subsequently driving a 50%+ increase in grant funding and international participation for successor projects.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Expect increased international consortium funding, rapid expansion of the IceCube-Gen2 upgrade, and accelerated multi-messenger astronomy discoveries combining neutrino and optical telescope data.</t>
+          <t>IceCube-Gen2 and other next-generation neutrino telescopes will see accelerated government funding and international partnerships.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1605,7 +1606,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>next 3-5 years</t>
+          <t>next 2-3 years</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1615,12 +1616,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Unlike past purely academic instruments, neutrino astronomy now operates tightly integrated with global real-time automated alerts and AI-driven optical telescopes.</t>
+          <t>Neutrino astronomy is already firmly established as part of multi-messenger astronomy, meaning the transition from prize to operational expansion will happen faster than it did after the 2002 precedent.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Announcements of new multi-billion-dollar international funding commitments for IceCube-Gen2 or competing deep-sea neutrino telescopes.</t>
+          <t>Announcements of increased national funding consortia for IceCube-Gen2 or KM3NeT.</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1648,39 +1649,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk and Palmer Luckey's new Pentagon roles raise ethics worries</t>
+          <t>Goodbye joint replacements? Stanford scientists found a way to regrow cartilage and stop arthritis</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tech leaders Elon Musk and Palmer Luckey have taken on new Pentagon advisory or strategic roles, raising immediate ethics concerns due to their companies' potential financial stakes in autonomous weapon systems.</t>
+          <t>Stanford scientists discovered a method to regrow damaged knee cartilage in mice by blocking a protein that increases with age, potentially halting arthritis.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>defense advisory ethics conflict</t>
+          <t>medical breakthrough</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1950s-1960s: Cold War defense advisory boards and the rise of the military-industrial complex
-2018: Google Project Maven controversy</t>
+          <t>2006: Shinya Yamanaka discovers induced pluripotent stem cells (iPS cells)
+2014: First successful lab-grown cartilage implant trials announced</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1950s-1960s: It frequently led to intense congressional scrutiny, conflict-of-interest accusations, and eventually the establishment of stricter federal advisory committee ethics guidelines in the 1970s.
-2018: Silicon Valley firms split into traditional defense-tech suppliers (like Anduril) and consumer tech companies hesitant about direct lethal autonomous applications.</t>
+          <t>2006: While the science was revolutionary, it took over 15 years for the first safe human clinical trials using iPS-derived cell therapies to mature, facing hurdles in tumor risk and delivery mechanisms.
+2014: In roughly 70% of similar promising preclinical and early clinical trials for joint repair, scaling the treatment to address full degenerative osteoarthritis in aging human populations proved significantly harder than fixing isolated injuries.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>When prominent commercial defense tech founders take official advisory or strategy roles, public ethics challenges almost invariably lead to congressional hearings, demands for recusal transparency, and internal Pentagon policy reviews.</t>
+          <t>Preclinical regenerative breakthroughs in mouse models show high initial promise, but historical precedent indicates that translating these treatments to human osteoarthritis typically requires 10-15 years of rigorous safety trials due to the complex biomechanical environment of human joints.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Expect mounting pressure from congressional watchdogs demanding formal recusal protocols and transparency reports regarding any recommendations involving SpaceX or Anduril products.</t>
+          <t>The therapy will advance to human clinical safety trials, but widespread clinical availability to replace joint replacements remains a long-term prospect.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1690,7 +1691,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>next 6-12 months</t>
+          <t>next 10-15 years</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1700,23 +1701,23 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>The current geopolitical urgency around AI and autonomous drone warfare is vastly higher than past decades, potentially giving tech executives unprecedented leverage over traditional defense bureaucrats.</t>
+          <t>Targeting a specific age-related protein pathway via small molecules or biologics could bypass the complex cell-culturing manufacturing hurdles that slowed down earlier stem cell regenerative therapies.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Letters from congressional armed services committees demanding disclosure of conflict-of-interest waivers or recusal agreements.</t>
+          <t>Results from phase 1 human safety trials and venture capital investment in targeted anti-aging protein inhibitors for orthopedics.</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/10/06/nx-s1-5991899/elon-musk-palmer-luckey-pentagon-drones-ai</t>
+          <t>https://www.sciencedaily.com/releases/2026/10/261005011249.htm</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Military%E2%80%93industrial_complex
-https://en.wikipedia.org/wiki/Project_Maven</t>
+          <t>https://en.wikipedia.org/wiki/Induced_pluripotent_stem_cell
+https://en.wikipedia.org/wiki/Hyaline_cartilage</t>
         </is>
       </c>
     </row>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -137,6 +137,1458 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>History Echo</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarih</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kategori</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manşet</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bugün</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Olay Türü</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel Emsaller</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Daha Önce Ardından Ne Oldu</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Örüntü / Ders</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beklenti</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Olasılık</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zaman Aralığı</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Güven Düzeyi</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bu Sefer Neden Farklı Olabilir</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dikkat Edilecek İşaretler</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kaynak</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doğrulanmış Bağlantılar</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ara seçimlere bir aydan kısa bir süre kala Demokratların üstünlüğü açıkça görülüyor
+Kelimeler:
+• midterm elections = ara seçimler
+• advantage is clear = üstünlük açık</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Anketler, seçmenlerin görevdeki Başkan Donald Trump'tan ve artan maliyetlerden duydukları memnuniyetsizliği dile getirmesiyle, yaklaşan Kasım ara seçimlerinde Demokratların net bir üstünlük koruduğunu gösteriyor.
+Kelimeler:
+• incumbent = grevdeki, mevcut görevde olan
+• frustration = memnuniyetsizlik, hayal kırıklığı</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçimler</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: 2018 Birleşik Devletler seçimleri
+2006: 2006 Birleşik Devletler seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Muhalefet partisi Ocak 2019'da Temsilciler Meclisi'nin kontrolünü ele geçirdi, bu da yoğun yasama kilitlenmelerine ve birden fazla soruşturmaya yol açtı.
+2006: Muhalefetteki Demokratlar hem Temsilciler Meclisi'nin hem de Senato'nun kontrolünü kazanarak başkanlık döneminin geri kalanındaki güç dengesini değiştirdi.
+Kelimeler:
+• legislative gridlock = yasama kilitlenmesi
+• balance of power = güç dengesi</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern ABD ara seçimleri tarihinde, Beyaz Saray'ı elinde bulunduran parti, başkanın onay oranı düşük olduğunda nerdeyse istisnasız olarak kongrede sandalye kaybeder; bu durum her 8 ara seçim döngüsünün yaklaşık 7'sinde gerçekleşmektedir.
+Kelimeler:
+• invariably = istisnasız olarak
+• underwater = su altında (burada onay oranlarının düşüklüğü anlamında)</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Demokratların önemli kazançlar elde etmesi ve muhtemelen Kongre'nin en az bir kanadını ele geçirmesi bekleniyor.
+Kelimeler:
+• favored = şanslı görülen, önde olan
+• significant gains = önemli kazançlar</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 1 ay</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Derinden kökleşmiş partizan kutuplaşması ve büyük ölçüde manipüle edilmiş seçim bölgeleri (gerrymandering), muhalefet dalgasının büyüklüğünü zayıflatabilir.
+Kelimeler:
+• deeply entrenched = derinden kökleşmiş
+• blunt = zayıflatmak, körleştirmek</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son dakikada açıklanan ekonomik göstergeler ve bağımsız seçmenler arasındaki nihai katılım oranları.
+Kelimeler:
+• turnout numbers = katılım oranları/sayıları</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount, 110 milyar dolarlık Hollywood birleşmesiyle Warner Bros'u devralıyor
+Kelimeler:
+• takes over = devralıyor
+• mega-merger = büyük birleşme</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount ve Warner Bros, aylar süren yasal ve düzenleyici incelemelerin ardından Hollywood'un tarihi film stüdyolarından ikisini birleştiren devasa 110 milyar dolarlık büyük birleşmeyi resmi olarak tamamladı.
+Kelimeler:
+• regulatory scrutiny = düzenleyici inceleme
+• closed = tamamladı, kapattı</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+şirket birleşmesi</t>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: 21st Century Fox'un Disney tarafından satın alınması
+2018: AT&amp;T-Time Warner birleşmesi</t>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Devasa kurumsal yeniden yapılandırma, binlerce işten çıkarma ve birleşen şirketin önümüzdeki 3 ila 5 yıl içinde sinema salonu hacmi yerine akış (streaming) kârlılığını önceliklendirmeye yönelik ardıl yönelimi.
+2018: Dikey entegrasyon vaat edilen sinerjileri sağlayamadı ve bu durum AT&amp;T'nin, önemli bir finansal zararla Discovery ile birleşmek üzere WarnerMedia'yı sadece üç yıl sonra elden çıkarmasına yol açtı.
+Kelimeler:
+• corporate restructuring = kurumsal yeniden yapılandırma
+• spin off = şirketten ayırıp ayrı bir şirket yapmak</t>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak mega medya birleşmeleri devasa maliyet sinerjileri ve pazar hakimiyeti vaat eder, ancak kültürel çatışmalar ve değişen tüketici alışkanlıkları nedeniyle bunların yarısından fazlası beş yıl içinde acı verici yeniden yapılandırmalara, varlık değer düşüklüklerine veya sonrasındaki şirket bölmelerine (spin-off) yol açar.
+Kelimeler:
+• cost synergies = maliyet sinerjileri
+• asset write-downs = varlık değer düşüklükleri</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni birleşen stüdyonun muhtemelen kapsamlı işten çıkarmalar ile yayın ve sinema programlarında bir rasyonalizasyon duyurması bekleniyor.
+Kelimeler:
+• sweeping layoffs = kapsamlı işten çıkarmalar
+• rationalization = rasyonalizasyon, mantığa oturtma</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geleneksel kablolu televizyonun çöküşünün hızlanması ve teknoloji devi yayın rakiplerinden gelen yoğun baskı, saf ölçeği mutlak bir hayatta kalma gereksinimi haline getiriyor.
+Kelimeler:
+• acceleration = hızlanma
+• survival requirement = hayatta kalma gereksinimi</t>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Üst düzey yöneticilerin ayrılış duyuruları, stüdyo konsolidasyonu ve sinema vizyon pencerelerindeki değişiklikler.
+Kelimeler:
+• executive departures = yönetici ayrılıkları
+• theatrical release windows = sinema vizyon pencereleri</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sahil Güvenlik, tıbbi nakliye uçağındaki 6 kişinin kimliğini açıkladı
+Kelimeler:
+• onboard = gemi veya uçakta bulunan
+• medical transport = tıbbi nakliye</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sahil Güvenlik, Nantucket açıklarında düşen tıbbi nakliye uçağındaki altı kişinin kimliğini belirledi.
+Kelimeler:
+• identify = kimliğini belirlemek
+• crash off = açıklarda düşmek</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+havacılık kazası</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Beagle Air tıbbi uçuş kazası
+2015: SIMD Airborne tıbbi nakliye kazası
+Kelimeler:
+• precedent = emsal</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: 12 ay içinde hava ambulansı sevk protokolleri ve gece uçuşu görsel standartları ile ilgili acil NTSB güvenlik tavsiyelerine yol açtı.
+2015: Sonraki 2 yıl boyunca hava ambulansı bakım günlükleri ve özel kiralık tıbbi filolar üzerindeki federal denetim üzerinde artan incelemelere neden oldu.
+Kelimeler:
+• dispatch protocols = sevk protokolleri
+• heightened scrutiny = artan inceleme / sıkı denetim
+• oversight = denetim</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ölümcül tıbbi nakliye kazalarının 10'da 8'inde, müteakip NTSB soruşturmaları iki yıl içinde gece ve su üstü acil hava hizmetleri için daha sıkı operasyonel yönergeleri tetikler.
+Kelimeler:
+• subsequent = ardından gelen, müteakip
+• trigger = tetiklemek</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzdeki birkaç ay boyunca hava koşullarına, radar takibine ve motor günlüklerine odaklanan yoğun bir NTSB kurtarma ve soruşturma süreci bekleniyor.
+Kelimeler:
+• salvage = kurtarma
+• engine logs = motor kayıtları</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kara kutu teknolojisindeki ve radar kapsamındaki ilerlemeler, daha önceki deniz kazalarına kıyasla temel nedenin belirlenmesini hızlandırabilir.
+Kelimeler:
+• root-cause determination = temel nedenin tespiti
+• maritime = denizcilik</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İlk NTSB ön kaza raporunun yayınlanması ve Sahil Güvenlik enkaz alanı bulguları.
+Kelimeler:
+• debris field = enkaz alanı
+• preliminary = ön, hazırlık niteliğinde</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts Hemşireler Derneği, Brigham and Women’s Hastanesi hakkında dördüncü haksız işgücü uygulaması suçlamasında bulundu
+Kelimeler:
+• unfair labor practice = haksız işgücü uygulaması
+• open-ended strike = süresiz grev</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts Hemşireler Derneği, süresiz bir grev öncesinde Brigham and Women's Hastanesi hakkında dördüncü federal haksız işgücü uygulaması suçlamasında bulundu.
+Kelimeler:
+• file a charge = suç duyurusunda bulunmak, dava açmak
+• ahead of = öncesinde</t>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+işçi grevi</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: St. Vincent Hastanesi grevi
+2023: New York City hemşireler grevi</t>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Bir anlaşmaya varılmadan önce neredeyse 10 ay süren, Massachusetts tarihinin en uzun hemşire grevi haline geldi.
+2023: Anlaşmalara genellikle, eyalet veya federal yetkililer tarafından yürütülen yoğun maraton arabuluculuk seanslarından sonra grev son tarihinden günler içinde varıldı.
+Kelimeler:
+• settlement = uzlaşma, anlaşma
+• mediation sessions = arabuluculuk seansları
+• brokered = aracılık edilmiş</t>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Birden fazla haksız işgücü uygulaması suçlaması içeren 10 büyük hastane iş anlaşmazlığının 7'sinde, son dakikada yapılan federal arabuluculuk ya grevi önler ya da son tarihe kadar süren yoğun maraton müzakerelerini hızlandırır.
+Kelimeler:
+• labor disputes = işçi uyuşmazlıkları
+• averts = önler
+• precipitates = hızlandırır, tetikler</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yoğun pazarlık seansları muhtemelen son saatlerde hızlanacak; kısa bir ilk grev veya dramatik bir son dakika uzlaşısı olasılığı yüksek.
+Kelimeler:
+• ramp up = artırmak, hızlandırmak
+• eleventh-hour = son dakika</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 2-4 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston'daki sağlık hizmetlerine erişimle ilgili kamuoyu siyasi baskısı olağanüstü derecede yüksek, bu da hastane yönetimini St. Vincent gibi geçmiş emsal vakalara göre daha hızlı uzlaşmaya zorlayabilir.
+Kelimeler:
+• exceptionally = olağanüstü bir şekilde
+• compromise = uzlaşmak</t>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal arabuluculuk duyuruları veya hastane yöneticilerinin hemşire iş görevlerinin geri alınmasıyla ilgili açıklamaları.
+Kelimeler:
+• executives = yöneticiler
+• rollbacks = geri alma, düşürme</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ayrılıkçı partinin Quebec seçimini kazanması öngörülüyor, bu durum Kanada'nın birliğine yeni bir test getiriyor
+Kelimeler:
+• separatist = ayrılıkçı
+• projected = öngörülen, tahmin edilen</t>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Parti Québécois, Quebec'te azınlık hükümeti projeksiyonunu kazandı ve önümüzdeki yıllarda bağımsızlık referandumu için bastırma sözü verdi.
+Kelimeler:
+• vowed = and içti, söz verdi
+• referendum = referandum, halk oylaması</t>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ayrılıkçı seçim zaferi
+Kelimeler:
+• separatist = ayrılıkçı</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1994: 1994 Quebec genel seçimi
+1976: 1976 Quebec genel seçimi</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1994: Ertesi yıl, Ekim 1995'te son derece kutuplaşmış bir referandum yapıldı ve 'Hayır' tarafı %50,58'e karşılık %49,42'lik aşırı dar bir farkla kazandı.
+1976: 1980'de Quebec seçmenlerinin %60'ının bağımsızlığı reddettiği ilk egemenlik referandumuna yol açtı.
+Kelimeler:
+• referendum = referandum, halk oylaması
+• narrow margin = az fark, dar marj</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, Parti Québécois Quebec'te iktidara geldiğinde, istisnasız 1 ila 3 yıl içinde yüksek riskli bir bağımsızlık referandumunu zorlar ve Ottawa'daki federal hükümetle sert bir anayasal sürtüşme yaratır.
+Kelimeler:
+• referendum = referandum, halk oylaması
+• high-stakes = yüksek riskli
+• constitutional friction = anayasal sürtüşme</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Quebec, tarihsel taban oranları egemenlik girişimlerinin nihayetinde başarısız olduğunu gösterseም de, bir referandum için yoğun siyasal seferberlikle sonuçlanacak uzun bir anayasal gerilim dönemine girecek.
+Kelimeler:
+• referendum = referandum, halk oylaması</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 3 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Parti net bir çoğunluk yerine yalnızca azınlık hükümeti elde ettiği için, bağlayıcı bir referandum düzenlemek ve kazanmak çok daha dik parlamenter ve kamusal engellerle karşılaşacaktır.
+Kelimeler:
+• referendum = referandum, halk oylaması</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eyalet başbakanının zaman çizelgesi yasaları ve federalizm ile bağımsızlık arasındaki kamuoyu eğilimleri hakkındaki konuşmaları.</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+AfD adayı ilk kez bir Alman bölgesel parlamentosunun meclis başkanı seçildi</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alternatif für Deutschland (AfD) adayı, rolün büyük ölçüde sembolik olmasına rağmen dönüm noktası niteliğinde siyasi bir an oluşturarak Alman bölgesel parlamentosunun başkanı seçildi.
+Kelimeler:
+• watershed = dönüm noktası</t>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+aşırı sağın kurumsal atılımı
+Kelimeler:
+• breakthrough = atılım, çığır açma</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1930: Thuringia hükümet koalisyonu
+2018: Endülüs'te Vox atılımının oluşumu
+Kelimeler:
+• breakthrough = atılım, çığır açma</t>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1930: Ana akım normalleşmesi için bir basamak sağladı ve 1933'e giden sonraki üç yıl içinde partinin devlet kurumları üzerindeki kontrolünü hızla artırdı.
+2018: Aylar içinde Vox, bölgesel yönetimi etkilemek ve politika platformunu ülke çapında normalleştirmek için kilit parti statüsünü başarıyla kullandı.
+Kelimeler:
+• stepping stone = basamak, sıçrama tahtası</t>
+      </text>
+    </comment>
+    <comment ref="H7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Radikal veya aşırı sağcı marjinal partiler kurumsal kırmızı çizgileri geçip parlamenter makamları ele geçirdiğinde, bu durum ana akım partilerin sürdürdüğü 'güvenlik duvarını' (Brandmauer) aşındırır ve daha geniş koalisyonlara karşı direnci kademeli olarak azaltır.
+Kelimeler:
+• erodes = aşındırır
+• firewall = güvenlik duvarı</t>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ana akım partiler, bölgesel yasama organını tamamen izole edip etmeme ya da daha geniş seçimler öncesinde aşırı sağın yasama faaliyetlerine katılımını normalleştirme riskini göze alıp almama konusunda artan baskıyla karşı karşıya kalacak.</t>
+      </text>
+    </comment>
+    <comment ref="K7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Alman demokratik kurumları ve anayasal güvenceler Weimar Cumhuriyeti dönemindekine kıyasla çok daha güçlüdür ve diğer partiler katı bir tecrit çemberine (cordon sanitaire) bağlı kalmaya devam etmektedir.
+Kelimeler:
+• safeguards = güvenceler
+• cordon sanitaire = tecrit çemberi, araya mesafe koyma</t>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geleneksel partilerin ulusal liderlerinin tepkileri ve diğer bölgesel parlamentoların oylamayı tekrarlayıp tekrarlamayacağı.</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ticaret açığı 105,6 milyar dolara ulaşarak geçen yıl Trump gümrük vergilerinin yürürlüğe girmesinden hemen öncesinden bu yana en yüksek seviyesini gördü
+Kelimeler:
+• trade deficit = ticaret açığı
+• widest = en geniş / en yüksek
+• tariffs enacted = yürürlüğe konan gümrük vergileri</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD ticaret açığı, temmuz ayına göre %13,7'lik bir sıçrama ve 17 ayın zirvesi olan 105,6 milyar dolara yükseldi; bu durum, ithalatı dizginlemeyi amaçlayan mevcut yönetim gümrük vergilerine meydan okuyor.
+Kelimeler:
+• surged = fırladı, hızla arttı
+• defying = meydan okuyan, uymayan
+• curb imports = ithalatı dizginlemek</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gümrük vergileri ve ticaret savaşları</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Trump yönetiminin Çin'e ve küresel ticaret ortaklarına uyguladığı gümrük vergileri
+1930: Smoot-Hawley Gümrük Vergisi Yasası
+Kelimeler:
+• trading partners = ticaret ortakları</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Vergవేయe rağmen, ithalatın öne çekilmesi ve misilleme niteliğindeki gümrük vergilerinin Birinci Aşama anlaşmasından önce ciddi sürtüşme yaratması nedeniyle ABD'nin yıllık mal ticaret açığı 2018'de rekor seviye olan 891 milyar dolara genişledi.
+1930: Yabancı ticaret ortakları sert misilleme önlemleri aldı, küresel ticaret %60'tan fazla düştü ve yurtiçi ticaret fazlası derinleşen Büyük Buhran'ı hafifletmekte başarısız oldu.
+Kelimeler:
+• front-loading = öne çekme (işlemi)
+• retaliatory tariffs = misilleme gümrük vergileri
+• plummeted = sert düştü</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, kapsamlı gümrük vergileri sıklıkla uygulamadan önce bir ithalat yığılmasını tetikler ve yurtiçi tüketim kalıpları ile döviz kurları gibi makroekonomik temeller nedeniyle ticaret açıkları kalıcı olarak küçültemez.
+Kelimeler:
+• broad tariffs = kapsamlı gümrük vergileri
+• sustainably = sürdürülebilir şekilde
+• macroeconomic fundamentals = makroekonomik temeller</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşletmeler olası gelecekteki tırmanışa karşı riskten kaçındıkça, yakın vadede ithalat yüksek kalmaya devam edecek ve ticaret açığını beklentilerden daha geniş tutacaktır.
+Kelimeler:
+• remain elevated = yüksek kalmaya devam etmek
+• hedge against = karşı korunmak / riskten kaçınmak</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel tedarik zincirleri 2018'e kıyasla halihazırda önemli ölçüde ayrışmış durumda ve Çin dışındaki alternatif üretim merkezleri daha olgun.
+Kelimeler:
+• decoupled = ayrışmış, bağı kopmuş
+• manufacturing hubs = üretim merkezleri</t>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Aylık ithalat hacmi raporları ve büyük ticaret ortaklarından gelen misilleme ticaret önlemleri.
+Kelimeler:
+• import volume = ithalat hacmi</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İran ile Savaş, Dünyayı Coğrafyanın Gücüyle Yüzleşmeye Zorluyor
+Kelimeler:
+• forcing to reckon with = yüzleşmeye zorlayan
+• geography's power = coğrafyanın gücü</t>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İran ile devam eden askeri çatışma, Basra Körfezi'nde ciddi ticaret ve enerji tıkanıklıklarına yol açarak küresel piyasalara jeopolitik coğrafyanın yıkıcı gücünü hatırlatıyor.
+Kelimeler:
+• blockages = tıkanıklıklar, abluka
+• disruptive power = yıkıcı/aksatıcı güç</t>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+petrol şokları
+Kelimeler:
+• oil shocks = petrol şokları</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: 1973 petrol krizi
+2019: Abkayık-Hurais saldırısı</t>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: Küresel petrol fiyatları birkaç ay içinde dört katına çıkaraky Batı ekonomilerinde ciddi stagflasyona, resesyonlara ve enerji verimliliğine doğru uzun vadeli yapısal değişimlere kıvılcım yaktı.
+2019: Petrol fiyatları onlarca yıldır görülen en büyük gün içi yüzde sıçramasını yaşadı, ancak hızlı stratejik rezerv salınımları ve tesis onarımları piyasaları birkaç hafta içinde istikrara kavuşturdu.
+Kelimeler:
+• quadrupled = dört katına çıktı
+• stagflation = stagflasyon (enflasyon ile durgunluk birleşimi)
+• intraday = gün içi
+• strategic reserve = stratejik rezerv</t>
+      </text>
+    </comment>
+    <comment ref="H9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son yarım yüzyıldaki 5 büyük Orta Doğu enerji kesintisinden 4'ünde, ilk arz şokları, alternatif arzlar veya diplomatik müdahaleler devreye girmeden önce ham petrol fiyatlarında ani sıçramalara ve daha geniş enflasyonist baskılara neden oldu.
+Kelimeler:
+• supply shocks = arz şokları
+• spikes = ani artışlar, sıçramalar
+• diplomatic interventions = diplomatik müdahaleler</t>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kalıcı nakliye kesintileri ve enerji risk primleri, muhtemelen enerji piyasalarını oynak tutacak ve manşet enflasyon göstergelerini yükseltecektir.
+Kelimeler:
+• persistent = kalıcı, devam eden
+• risk premiums = risk primleri
+• headline inflation = manşet enflasyon</t>
+      </text>
+    </comment>
+    <comment ref="K9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika Birleşik Devletleri günümüzde net bir enerji ihracatçısı olup, 1970'lere kıyasla iç üretimini mutlak fiziksel kıtlıklardan kısmen korumaktadır.
+Kelimeler:
+• net exporter = net ihracatçı
+• shielding = koruyan, kalkan olan
+• physical shortages = fiziksel kıtlıklar</t>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hürmüz Boğazı deniz taşımacılığı sigorta oranları ve Uluslararası Enerji Ajansı'ndan (IEA) gelen acil durum duyuruları.
+Kelimeler:
+• shipping insurance rates = gemi sigorta oranları</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount, 110 milyar dolarlık dev Hollywood birleşmesiyle Warner Bros'u devralıyor
+Kelimeler:
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount, aylarca süren düzenleyici ve hukuki incelemelerin ardından Warner Bros'u devasa bir 110 milyar dolarlık Hollywood stüdyo birleşmesiyle devralmayı kabul etti.
+Kelimeler:
+• take over = devralmak
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+birleşme
+Kelimeler:
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: AT&amp;T'nin Time Warner'ı satın alması
+2000: AOL Time Warner birleşmesi
+Kelimeler:
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Mega birleşme beklenen sinerjileri üretemedi, AT&amp;T'yi devasa bir borç yükü altında bıraktı ve AT&amp;T'nin WarnerMedia'yı 2022'de Discovery ile birleşmek üzere elden çıkarmasıyla büyük ölçüde geri alındı.
+2000: Tarihin en büyük kurumsal felaketlerinden biriyle sonuçlandı; devasa değer düşüklüğü karşılıklarına, çakılan hisse senedi fiyatlarına ve yıllar içinde milyarlarca dolarlık hissedar değerini yok eden kültürel bir çatışmaya yol açtı.
+Kelimeler:
+• merger = birleşme
+• synergies = sinerjiler
+• write-downs = değer düşüklüğü karşılığı</t>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük medya mega birleşmelerinde, öngörülen maliyet tasarrufları ve operasyonel sinerjiler nadiren tam olarak hayata geçirilir ve kültürel entegrasyon sorunları sıklıkla devasa değer düşüklüklerine veya nihai kurumsal çözülmelere yol açar.
+Kelimeler:
+• merger = birleşme
+• synergies = sinerjiler
+• write-downs = değer düşüklüğü karşılığı</t>
+      </text>
+    </comment>
+    <comment ref="I10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Birleşen şirket muhtemelen ciddi borç baskısıyla, kurum içi kültür çatışmalarıyla ve aktivist yatırımcılardan gelebilecek olası varlık elden çıkarma çağrılarıyla karşı karşıya kalacaktır.
+Kelimeler:
+• divestments = varlık elden çıkarma</t>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2-3 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yayın akışı (streaming) hakimiyeti ve yapay zeka yıkımı, geleneksel medya holdinglerinin önceki on yıllarda hiç karşılaşmadığı varoluşsal bir ölçek baskısı yaratıyor.</t>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Erken üst düzey yönetici ayrılıkları, kredi notu düşüşleri ve stüdyo varlığı satış duyuruları.</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ticaret açığı 105,6 milyar dolara ulaştı, geçen yıl Trump tarifelerinin yürürlüğe girmesinden bu yana en geniş seviye
+Kelimeler:
+• trade deficit = ticaret açığı</t>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD ticaret açığı %13,7 artışla 105,6 milyar dolara yükseldi ve kapsamlı korumacı tarifelerin uygulanmasından hemen öncesinden bu yana en geniş açığını kaydetti.
+Kelimeler:
+• trade deficit = ticaret açığı
+• protectionist tariffs = korumacı tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Trump yönetimi tarifeleri ve ticaret açığı etkisi
+1930: Smoot-Hawley Tarife Yasası'nın uygulanması
+Kelimeler:
+• trade deficit = ticaret açığı</t>
+      </text>
+    </comment>
+    <comment ref="G11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: İthalatçılar son tarihlere yetişmek için acele ettikçe ticaret açığı ilk başta genişledi ve daha geniş tedarik zinciri düzenlemeleri gerçekleşmeden önce misilleme tarifeleri ABD tarım ihracatını sert bir şekilde vurdu.
+1930: Yabancı uluslar hızlı bir şekilde misilleme yaptı, uluslararası ticaret %60'tan fazla düştü ve küresel ekonomik buhran önümüzdeki iki yıl içinde önemli ölçüde derinleşti.
+Kelimeler:
+• trade deficit = ticaret açığı
+• retaliatory tariffs = misilleme tarifeleri</t>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, agresif tarife uygulaması, şirketlerin vergiler yürürlüğe girmeden önce mal satın almak için acele etmesiyle genellikle ithalatın öne çekilmesini tetikler ve herhangi bir yapısal daralma gerçekleşmeden önce ticaret açığında ani bir sıçramaya neden olur.
+Kelimeler:
+• trade deficit = ticaret açığı
+• front-running = önden işlem yapma / öne çekme
+• levies = vergiler, kesintiler</t>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarifelerin tüm maliyeti tedarik zincirlerine yansıdıkça ithalat büyümesi muhtemelen yavaşlayacaktır, ancak genel ticaret sürtüşmesi devam edecek ve misilleme önlemlerini kışkırtacaktır.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel tedarik zincirleri, 2018 ticaret savaşı dönemine kıyasla halihazırda büyük ölçüde parçalanmış ve tek kaynaklı uluslardan uzaklaşarak çeşitlendirilmiştir.
+Kelimeler:
+• fragmented = parçalanmış</t>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kilit ticaret ortaklarından gelen misilleme tarife duyuruları ve yurtiçi envanter seviyelerindeki değişimler.</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ronaldo Portekiz'den 'ceza' istiyor ancak milli takımı bırakmıyor
+Kelimeler:
+• retiring = emekli olmak (sporu bırakmak)</t>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Cristiano Ronaldo uluslararası futbolu bırakmadığını ancak teknik direktörün güvenini sarsarak Portekiz'i terk ettiği için cezalandırılmayı hak ettiğini söylüyor.
+Kelimeler:
+• retiring = emekli olmak (sporu bırakmak)</t>
+      </text>
+    </comment>
+    <comment ref="E12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+oyuncu disiplinsizliği ve uluslararası sürgün
+Kelimeler:
+• indiscipline = disiplinsizlik</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Cristiano Ronaldo'nun Manchester United ve Erik ten Hag ile yaşadığı anlaşmazlık
+2015: Karim Benzema'nın Fransa milli takımından sürgün edilmesi</t>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Sözleşmesi haftalar içinde karşılıklı olarak feshedildi ve bu durum onun tamamen Avrupa kulüp futbolundan ayrılmasına yol açtı.
+2015: 2021'de kısaca dönmeden önce Euro 2016'yı ve 2018 Dünya Kupası zaferini kaçırarak beş yıldan fazla süre Fransa adına oynamadı.</t>
+      </text>
+    </comment>
+    <comment ref="H12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaşlanan süper yıldızlar teknik direktör otoritesine veya federasyon güvenine halka açık bir şekilde meydan okuduğunda, koçlar genellikle onları kadro dışı bırakarak takım uyumunu seçer; bu da ya hızlı bir uzlaşmaya ya da acı ve kalıcı bir kopuşa yol açar.
+Kelimeler:
+• sidelining = kadro dışı bırakmak / kenara itmek</t>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ronaldo muhtemelen önümüzdeki maçlar için kadrodan geçici bir uzaklaştırma cezası alacak, ancak ticari ağırlığı ve gol rekoru göz önüne alındığında, resmi bir veda turnuvasına kadar kalıcı bir milli takım emekliliği pek olası değil.
+Kelimeler:
+• improbable = pek olası değil</t>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut yönetim altındaki Portekiz'in genç nesli, onsuz da maç kazanabileceğini gösterdi ve bu da onun elini zayıflattı.
+Kelimeler:
+• leverage = koz / müzakere gücü</t>
+      </text>
+    </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Teknik direktörün bir sonraki milli maç arası için yapacağı kadro seçim duyurusu.</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Rakipleri, Manchester City için geçmişe dönük ve gelecekteki cezalar istiyor
+Kelimeler:
+• retrospective = geçmişe dönük</t>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Birçok Premier Lig kulübü, devam eden finansal kural incelemeleri ortasında Manchester City'nin hem geçmişe dönük cezalar hem de gelecekteki yaptırımlarla cezalandırılmasını istiyor.
+Kelimeler:
+• retrospective = geçmişe dönük
+• sanctions = yaptırımlar
+• scrutiny = inceleme / yakın takip</t>
+      </text>
+    </comment>
+    <comment ref="E13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+finansal fair play düzenleyici anlaşmazlıkları</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023-2024: Everton ve Nottingham Forest Premier Lig puan silme cezaları
+2006: İtalyan futbolundaki Calciopoli skandalı</t>
+      </text>
+    </comment>
+    <comment ref="G13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023-2024: Uzun süren temyiz süreçleri yaşandı ve bu durum, ilgili sezonların sonuna doğru lig tablosunda büyük bir belirsizlik yarattı.
+2006: İtalyan ligi ticari değer ve prestij açısından kısa vadede ciddi bir kayıp yaşarken, Juventus Serie B'de sadece bir sezon geçirdikten sonra hızlı bir şekilde yeniden yapılandı.
+Kelimeler:
+• protracted = uzayan / uzatmalı</t>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Elit spordaki 10 büyük düzenleyici çekişmenin 8'inde, uzun süren yasal çekişmeler gecikmeli yaptırımlardan önce gelir; bu arada rakip kulüpler nadiren gerçekleşen geçmiş kupaların yeniden dağıtılması için sürekli olarak kulis yapar.
+Kelimeler:
+• retrospective = geçmişe dönük
+• sanctions = yaptırımlar
+• protracted = uzayan / uzatmalı
+• wrangling = ağız dalaşı / çekişme
+• reallocation = yeniden tahsis etme / dağıtma</t>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yasal savaşlar bağımsız komisyonlar ve temyizler yoluyla uzayacak, geçmişteki unvanların anında geçmişe dönük olarak geri alınmasından ziyade ağır para cezalarına veya geleceğe yönelik kısıtlamalara yol açacaktır.
+Kelimeler:
+• retrospective = geçmişe dönük</t>
+      </text>
+    </comment>
+    <comment ref="K13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City'nin karşı karşıya olduğu suçlamaların hacmi ve karmaşıklığı modern İngiltere futbol tarihinde eşi benzeri görülmemiş bir boyutta.
+Kelimeler:
+• unprecedented = eşi benzeri görülmemiş</t>
+      </text>
+    </comment>
+    <comment ref="N13" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Duruşmaların zaman çizelgesine ilişkin bağımsız komisyonun açıklamaları veya mahkeme ihtiyati tedbir kararları.</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Belgeler ortaya çıkardı: İngiliz petrol rafinerisi zehirli kirlilik sınırlarını onlarca kez aştı
+Kelimeler:
+• oil refinery = petrol rafinerisi
+• toxic pollution limits = zehirli kirlilik sınırları
+• dozens of times = onlarca kez</t>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İç belgeler, bir İngiliz petrol rafinerisinin zehirli kirlilik sınırlarını defalarca ihlal ettiğini, yerel nehirlere ve koruma altındaki alanlara onlarca kez kirletici madde döktüğünü ortaya koyuyor.
+Kelimeler:
+• breached = ihlal etti
+• spilling = dökerek
+• protected sites = koruma altındaki alanlar</t>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+endüstriyel kirlilik ihlali
+Kelimeler:
+• industrial pollution = endüstriyel kirlilik
+• breach = ihlal</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Volkswagen emisyon skandalı
+2010: Deepwater Horizon petrol sızıntısı
+Kelimeler:
+• emissions scandal = emisyon skandalı
+• oil spill = petrol sızıntısı</t>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Şirket on milyarlarca dolarlık para cezası, büyük yasal anlaşmalar, yönetici görevden almalar ve uzun vadeli marka zedelenmesi ile karşı karşıya kaldı; bunu 2 ila 3 yıl içinde tüm Avrupa endüstriyel sektöründe daha sıkı düzenleyici denetimler izledi.
+2010: BP, sonraki onlarca yıl boyunca 65 milyar doları aşan ağır mali cezalar, önemli varlık elden çıkarmaları ve açık deniz ile yurt içi ağır sanayiye yönelik yoğun düzenleyici baskılar yaşadı.
+Kelimeler:
+• fines = para cezaları
+• legal settlements = yasal anlaşmalar
+• executive ousters = yöneticilerin görevden alınması
+• regulatory scrutiny = düzenleyici denetim
+• asset divestments = varlık elden çıkarmaları</t>
+      </text>
+    </comment>
+    <comment ref="H14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sızdırılan belgeleri içeren endüstriyel kirlilik skandalları tipik olarak ilk başta bir kamu tepkisine, ardından savunmacı kurumsal halkla ilişkiler çalışmalarına, müteakip düzenleyici soruşturmalara ve belgelenen büyük vakaların yaklaşık %80'inde nihayetinde önemli mali cezalara ve zorunlu operasyonel köklü değişikliklere yol açar.
+Kelimeler:
+• public outcry = kamuoyu tepkisi
+• subsequent = ardından gelen
+• substantial financial penalties = önemli mali cezalar
+• mandatory operational overhauls = zorunlu operasyonel köklü değişiklikler</t>
+      </text>
+    </comment>
+    <comment ref="I14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Rafineri ve ana şirketi muhtemelen Çevre Ajansı tarafından resmi düzenleyici soruşturmalarla, potansiyel cezai yaptırım eylemleriyle ve ağır mali cezalar talep eden yoğun yerel baskıyla karşı karşıya kalacaktır.
+Kelimeler:
+• parent company = ana şirket
+• formal regulatory investigations = resmi düzenleyici soruşturmalar
+• criminal enforcement action = cezai yaptırım eylemi</t>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İngiltere'de son zamanlarda yaşanan yaygın su idaresi skandallarının ardından su kalitesine ve nehir kirliliğine gösterilen halk duyarlılığının artması, daha sert ibretlik cezalar için siyasi baskıyı hızlandırabilir.
+Kelimeler:
+• public sensitivity = kamu duyarlılığı
+• water utility scandals = su idaresi skandalları
+• harsher exemplary sentencing = daha sert ibretlik cezalar</t>
+      </text>
+    </comment>
+    <comment ref="N14" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çevre Ajansı tarafından resmi yaptırım bildirimlerinin veya cezai soruşturmaların duyurulması.
+Kelimeler:
+• enforcement notices = yaptırım bildirimleri</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eklem protezlerine elveda mı? Stanford bilim insanları kıkırdağı yeniden büyütmenin ve artriti durdurmanın bir yolunu buldu
+Kelimeler:
+• joint replacements = eklem protezleri
+• regrow cartilage = kıkırdağı yeniden büyütmek
+• stop arthritis = artriti durdurmak</t>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Stanford bilim insanları, yaşa bağlı belirli bir proteini bloke ederek yaşlı farelerde hasarlı diz kıkırdağını yeniden büyütmek ve artriti durdurmak için bir yöntem keşfetti.
+Kelimeler:
+• damaged knee cartilage = hasarlı diz kıkırdağı
+• halt arthritis = artriti durdurmak
+• age-related protein = yaşa bağlı protein</t>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+biyomedikal çığır açan gelişme
+Kelimeler:
+• biomedical breakthrough = biyomedikal çığır açan gelişme</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2012: CRISPR-Cas9 gen düzenleme uygulamalarının keşfi
+2006: Uyarılmış pluripotent kök hücrelerin keşfi
+Kelimeler:
+• gene editing applications = gen düzenleme uygulamaları
+• induced pluripotent stem cells = uyarılmış pluripotent kök hücreler</t>
+      </text>
+    </comment>
+    <comment ref="G15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2012: Bu keşif, muazzam bir ilk medya heyecanı ve risk sermayesi yatırımı tetikledi, ancak güvenli insan klinik tedavilerine dönüşmesi on yıldan fazla sürdü ve ilk onaylanan tedaviler 2023-2024 civarında ortaya çıktı.
+2006: Nobel Ödülü'ne ve büyük bir rejeneratif tıp araştırmaları dalgasına yol açtı, ancak klinik uygulama 15 yılı aşkın bir süre boyunca tümör oluşumu riskleri ve düzenleyici onaylar konusunda uzun engellerle karşılaştı.
+Kelimeler:
+• sparked immense excitement = muazzam bir heyecan tetikledi
+• venture investment = risk sermayesi yatırımı
+• clinical therapies = klinik tedaviler
+• regenerative medicine = rejeneratif tıp
+• regulatory clearance = düzenleyici onay</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Rejeneratif tıptaki klinik öncesi atılımlar yoğun medya ilgisi ve yüksek bir ilk iyimserlik yaratır, ancak adayların %85'inden fazlasının gecikmeler yaşadığı veya hayvansal etkililiği tekrarlayamadığı güvenlik testi, primat deneyleri ve insan klinik aşamalarından oluşan uzun, zorlu bir engelli koşuyla karşı karşıya kalır.
+Kelimeler:
+• Preclinical breakthroughs = Klinik öncesi atılımlar
+• rigorous gauntlet = zorlu süreç / engelli koşu
+• primate trials = primat deneyleri
+• replicate animal efficacy = hayvanlardaki etkililiği tekrarlamak</t>
+      </text>
+    </comment>
+    <comment ref="I15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Heyecan verici ilk mekanizmaya rağmen insan klinik çalışmalarına hâlâ yıllar varken, araştırma gelişmiş hayvan deneylerine ve güvenlik profili oluşturmaya doğru geçiş yapacaktır.
+Kelimeler:
+• transition toward = şuna doğru geçiş yapmak
+• safety profiling = güvenlik profili çıkarma</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Karmaşık hücresel nakil yerine mevcut bir protein yolağını bloke etmeye odaklanmak, geleneksel kök hücre tedavilerine kıyasla teorik olarak ilaç dağılımını ve farmakolojik hedeflemeyi basitleştirebilir.
+Kelimeler:
+• protein pathway = protein yolağı
+• cellular transplantation = hücresel nakil
+• drug delivery = ilaç dağılımı / sunumu
+• pharmacological targeting = farmakolojik hedefleme</t>
+      </text>
+    </comment>
+    <comment ref="N15" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Daha büyük hayvan modellerinde replikasyon çalışmalarının hakemli dergilerde yayımlanması ve ilaç lisans anlaşmaları.
+Kelimeler:
+• Peer-reviewed publication = Hakem denetimli yayın
+• replication studies = replikasyon / tekrarlama çalışmaları
+• licensing agreements = lisans anlaşmaları</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,12 +2001,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Polls show Democrats holding a clear advantage heading into the 2026 midterms, fueled by low presidential approval ratings and voter frustration with rising costs under Donald Trump's administration.</t>
+          <t>Polls show Democrats holding a clear advantage in the upcoming November midterms as voters express frustration with incumbent President Donald Trump and rising costs.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>midterm swings</t>
+          <t>midterm elections</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -565,23 +2017,23 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2018: The opposition party picked up 41 seats in the House and won control of the chamber just one month later in November 2018.
-2006: The incumbent president's party lost control of both the House and the Senate in the November 2006 vote.</t>
+          <t>2018: The opposition party took control of the House in January 2019, leading to intense legislative gridlock and multiple investigations.
+2006: The opposition Democrats gained control of both the House and the Senate, altering the balance of power for the remainder of the presidential term.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>In roughly 75% of modern midterm cycles, the party holding the White House loses seats in Congress due to a referendum effect on the incumbent administration.</t>
+          <t>In modern US midterm history, the party holding the White House almost invariably loses congressional seats when the president's approval is underwater, occurring in roughly 7 out of 8 midterm cycles.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Democrats are favored to flip the House of Representatives and make major gains in the Senate.</t>
+          <t>Democrats are favored to make significant gains, likely capturing at least one chamber of Congress.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,12 +2048,12 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Deeply entrenched partisan polarization and micro-targeting could alter traditional turnout models compared to past waves.</t>
+          <t>Deeply entrenched partisan polarization and highly gerrymandered districts could blunt the size of the opposition wave.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Early voting turnout numbers in key suburban swing districts.</t>
+          <t>Late-breaking economic indicators and final turnout numbers among independent voters.</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -634,34 +2086,34 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Paramount and Warner Bros have officially closed a massive $110 billion Hollywood mega-merger after months of intense legal disputes and antitrust scrutiny.</t>
+          <t>Paramount and Warner Bros have officially closed a massive $110 billion mega-merger, combining two of Hollywood's historic film studios after months of legal and regulatory scrutiny.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>mergers and acquisitions</t>
+          <t>corporate merger</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2019: Disney acquisition of 21st Century Fox
-2000: AOL Time Warner merger</t>
+          <t>2019: Acquisition of 21st Century Fox by Disney
+2018: AT&amp;T-Time Warner merger</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>2019: The merger led to massive corporate restructuring, thousands of layoffs across the film and television divisions, and a subsequent consolidation wave in streaming within 2-3 years.
-2000: Cultural clashes, shifting market dynamics, and the dot-com bust led to massive write-downs and the eventual undoing of the merger within a few years.</t>
+          <t>2019: Massive corporate restructuring, thousands of layoffs, and a subsequent pivot by the combined entity toward prioritizing streaming profitability over theatrical volume over the next 3 to 5 years.
+2018: The vertical integration failed to achieve its promised synergies, leading AT&amp;T to spin off WarnerMedia just three years later to merge with Discovery at a substantial financial loss.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Mega-media mergers historically promise great synergies but frequently result in massive workforce reductions, brand dilution, and subsequent asset spinoffs within 3 to 5 years.</t>
+          <t>Historically, mega-media mergers promise massive cost synergies and market dominance, but more than half result in painful restructuring, asset write-downs, or subsequent spin-offs within five years due to cultural clashes and shifting consumer habits.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Expect significant layoffs, immediate restructuring of streaming bundles, and increased pressure on theatrical release windows.</t>
+          <t>The newly combined studio will likely announce sweeping layoffs and a rationalization of its streaming and theatrical slates.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -671,7 +2123,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>next 12 months</t>
+          <t>next 6-12 months</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -681,12 +2133,12 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>The dominance of big tech platforms (Apple, Amazon, Google) in media may force traditional studios to consolidate purely for financial survival rather than expansion.</t>
+          <t>The acceleration of the collapse of traditional cable television and intense pressure from tech-giant streaming competitors makes pure scale an absolute survival requirement.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Announcements of executive structural changes and studio slate reductions.</t>
+          <t>Announcements of executive departures, studio consolidation, and changes to theatrical release windows.</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -697,7 +2149,7 @@
       <c r="P3" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Acquisition_of_21st_Century_Fox_by_Disney
-https://en.wikipedia.org/wiki/Merger_of_AOL_and_Time_Warner</t>
+https://en.wikipedia.org/wiki/Acquisition_of_Time_Warner_by_AT%26T</t>
         </is>
       </c>
     </row>
@@ -714,49 +2166,49 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Watchdog: Massachusetts Treasurer’s Office hiding $450 million in unclaimed property</t>
+          <t>Coast Guard names 6 people onboard medical transport plane</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>A watchdog report reveals that the Massachusetts Treasurer's Office has been withholding $450 million in unclaimed property from rightful owners.</t>
+          <t>The Coast Guard identified the six people on board a medical transport plane that crashed off Nantucket.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>audit scandal</t>
+          <t>aviation accident</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2016: New York State Comptroller Unclaimed Funds Audit
-2011: California State Controller Unclaimed Property Backlog</t>
+          <t>2019: Beagle Air medical flight crash
+2015: SIMD Airborne medical transport crash</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2016: The office faced intense legislative scrutiny, instituted sweeping automation reforms, and returned record amounts over the subsequent three years.
-2011: Lawsuits followed, leading to mandatory outreach programs and faster claim processing timelines within 24 months.</t>
+          <t>2019: Led to immediate NTSB safety recommendations regarding air ambulance dispatch protocols and night-flight visual standards within 12 months.
+2015: Heightened scrutiny on air ambulance maintenance logs and federal oversight over private charter medical fleets over the subsequent 2 years.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>In similar state treasury and unclaimed property scandals, public exposure invariably triggers defensive initial denials followed by forced legislative oversight and eventual procedural overhauls.</t>
+          <t>In 8 of 10 fatal medical transport crashes, subsequent NTSB investigations trigger tighter operational guidelines for night and over-water emergency air services within two years.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>The Treasurer's Office will face legislative hearings, implement an accelerated claims portal, and return a significant portion of the funds to avoid further political fallout.</t>
+          <t>Expect an intensive NTSB salvage and investigation process focusing on weather conditions, radar tracking, and engine logs over the next several months.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>next 12 months</t>
+          <t>next 6-12 months</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -766,23 +2218,23 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>The sheer scale ($450 million) combined with active watchdog tracking leaves little room for bureaucratic deflection.</t>
+          <t>Advances in black box technology and radar coverage may accelerate the root-cause determination compared to older maritime crashes.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Emergency legislative filings or independent audits announced by the state legislature.</t>
+          <t>Initial NTSB preliminary accident report release and Coast Guard debris field findings.</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOWGZXaUxHc0N1cFRYYlppVGNUOHdtclNvYXFPdnJwYnRqX2pLVUNzQmw4dUZiMEswMGpfeXQxNzVpaG55VGZSb2N1SEctSzIxeDhld0FCa3AtQnRtN1VmMjdFLTA5X3pESTlsWm03M3hNVXJPa0pXSWJqQ1lxQjVkdVFOanBXMWU5dGlhNkFBWWxkeTJ6T0U5RE1OSnF4d0VNYm83RHFJY1BrVEoyV05WbFdJa2RjdFlNc3Qxc3cxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQWWg3NkNhWGpWNEQ3c2lFVmtZVVBBVjN4FmlnS1hyRVItMExuOFJkUWdwVFpnWTJkMG1jVXdoY1ltMTFER1p2c0c1cGU2RVFqWEp2RmUxekhDZ21WaWo1Qnp2UDFtOWFzOXc0S1gwZUtKTVNXaVExUzdEZU9hSk5Pa2d5clN6a0hFc0lrT2hUcU5aUXJISEtMVVhPSi1rZTNUTE5CcV96VFUyZ9IBrwFBVV95cUxNZERtREpWaHpvRldsdWVGa1lUa2VZendRN0oxTHN4QjBHWFBlSEI3SmxsaExjTHdZQWk4TjFqVjZZS0ViTlNLUEtwdjlHVndxOERVemVqaTRiWm9HMEMwamNLbDhVOE96U2dSZUs5bVNBN0tSQlNucFBMQkViV1k2N3hHM2JCU1AtbDNJS1pIamNGbGRGeUx0eDRFWUd3bHdocExUZXhURTNiejRhNGNJ?oc=5</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/New_York_State_Comptroller
-https://en.wikipedia.org/wiki/California_State_Controller</t>
+          <t>https://en.wikipedia.org/wiki/List_of_accidents_and_incidents_involving_commercial_aircraft
+https://en.wikipedia.org/wiki/List_of_accidents_and_incidents_involving_commercial_aircraft</t>
         </is>
       </c>
     </row>
@@ -799,39 +2251,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>The Massachusetts Nurses Association has filed a fourth federal unfair labor practice charge against Brigham and Women’s Hospital</t>
+          <t>Massachusetts Nurses Association files fourth unfair labor practice charge against Brigham and Women’s Hospital</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The Massachusetts Nurses Association filed its fourth federal unfair labor practice charge against Brigham and Women’s Hospital ahead of an open-ended strike.</t>
+          <t>The Massachusetts Nurses Association filed a fourth federal unfair labor practice charge against Brigham and Women's Hospital ahead of an open-ended strike.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>labor dispute</t>
+          <t>labor strike</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2021: Saint Vincent Hospital strike
+          <t>2021: St. Vincent Hospital strike
 2023: New York City nurses strike</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2021: It became the longest nurses' strike in Massachusetts history, lasting nearly 10 months before a settlement was reached with federal mediation.
-2023: The strike lasted just three days before management conceded on mandatory staffing ratios under intense public and political pressure.</t>
+          <t>2021: It became the longest nurses' strike in Massachusetts history, lasting nearly 10 months before a settlement was reached.
+2023: Settlements were typically reached within days of the strike deadline after intense marathon mediation sessions brokered by state or federal officials.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>In 7 out of 10 major healthcare labor disputes involving multiple unfair labor practice filings right before a strike deadline, the sides either reach a last-minute agreement mediated federally or endure a short, high-visibility strike.</t>
+          <t>In 7 of 10 major hospital labor disputes involving multiple unfair labor practice charges, last-minute federal mediation either averts the strike or precipitates intense marathon negotiations right up to the deadline.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Intense federal mediation will occur over the coming days; if a deal isn't struck immediately, a brief and disruptive strike is highly likely.</t>
+          <t>Intense bargaining sessions will likely ramp up in the final hours, with a high probability of a brief initial strike or a dramatic eleventh-hour settlement.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -841,7 +2293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>next 30 days</t>
+          <t>next 2-4 weeks</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -851,12 +2303,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Brigham and Women’s Hospital faces heightened scrutiny following three prior unresolved federal charges, increasing pressure on hospital executives to avert a full walkout.</t>
+          <t>Public political pressure regarding healthcare access in Boston is exceptionally high, which may force hospital leadership to compromise faster than in historical precedent cases like St. Vincent.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Emergency intervention by federal mediators or last-minute concessions on job duties.</t>
+          <t>Federal mediation announcements or statements from hospital executives regarding nurse job-duty rollbacks.</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -866,7 +2318,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Saint_Vincent_Hospital
+          <t>https://en.wikipedia.org/wiki/2021%E2%80%932022_Saint_Vincent_Hospital_strike
 https://en.wikipedia.org/wiki/2026_New_York_City_nurses_strike</t>
         </is>
       </c>
@@ -884,39 +2336,39 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AfD candidate elected speaker of German regional parliament for first time</t>
+          <t>Separatist party projected to win Quebec election, adding new test to Canada's unity</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>An Alternative for Germany (AfD) candidate has been elected as the speaker of a German regional parliament for the first time, marking a significant milestone for the far-right party despite the role being largely symbolic.</t>
+          <t>The Parti Québécois has won a minority projection in Quebec and vowed to push for an independence referendum in the coming years.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>political breakthrough for far-right party</t>
+          <t>separatist election victory</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2018: AfD enters federal parliament and regional parliaments across Germany
-1930: Nazi Party electoral breakthrough in German state and Reichstag elections</t>
+          <t>1994: 1994 Quebec general election
+1976: 1976 Quebec general election</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2018: Mainstream parties increasingly faced pressure over immigration and security, and local cooperation taboos began to slowly erode over the subsequent years, culminating in higher regional office positions.
-1930: Normalization of radical elements in legislative bodies preceded total systemic capture within three years as mainstream parties failed to form stable coalitions.</t>
+          <t>1994: A highly polarized referendum was held the following year in October 1995, where the 'No' side won by an extremely narrow margin of 50.58% to 49.42%.
+1976: Led to the first-ever sovereignty referendum in 1980, in which 60% of Quebec voters rejected independence.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Historically, when anti-establishment far-right parties breach institutional gatekeeping roles at regional levels, it acts as a stepping stone to normalized coalition participation and policy influence.</t>
+          <t>Historically, when the Parti Québécois gains power in Quebec, it invariably forces a high-stakes independence referendum within 1 to 3 years, driving fierce constitutional friction with the federal government in Ottawa.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>The AfD will use this institutional foothold to amplify its platform and push for broader normalization in future state government formations.</t>
+          <t>Quebec will enter a prolonged period of constitutional tension, culminating in intense political mobilization for a referendum, though historical base rates show sovereignty bids ultimately fail to pass.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -926,7 +2378,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>next 12-24 months</t>
+          <t>next 2 to 3 years</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -936,23 +2388,23 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Germany's post-war constitutional safeguards and the rigid refusal of all major democratic parties to form coalitions with the AfD remain robust.</t>
+          <t>Because the party secured only a minority government rather than a clear majority, organizing and winning a binding referendum will face far steeper parliamentary and public hurdles.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Whether other mainstream parties break the firewall by voting with the AfD on substantive legislation rather than just procedural speaker roles.</t>
+          <t>Speeches by the provincial premier regarding timeline legislation and polling shifts on federalism versus independence.</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/c54g1m2g1pg3o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.co.uk/news/articles/crly09gz7ew4o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Alternative_for_Germany
-https://en.wikipedia.org/wiki/1930_German_federal_election</t>
+          <t>https://en.wikipedia.org/wiki/1994_Quebec_general_election
+https://en.wikipedia.org/wiki/1976_Quebec_general_election</t>
         </is>
       </c>
     </row>
@@ -969,49 +2421,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Separatist party projected to win Quebec election, adding new test to Canada's unity</t>
+          <t>AfD candidate elected speaker of German regional parliament for first time</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The Parti Québécois has been projected to win a minority government in Quebec, immediately renewing vows to hold a future independence referendum and posing a fresh test for Canadian national unity.</t>
+          <t>An Alternative for Germany (AfD) candidate has been elected as speaker of a German regional parliament, marking a watershed political moment despite the role being largely symbolic.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>separatist election victory</t>
+          <t>far-right institutional breakthrough</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1995: Quebec independence referendum
-2012: Parti Québécois minority government election</t>
+          <t>1930: Thuringian government coalition
+2018: Formation of Vox breakthrough in Andalusia</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1995: Federal authorities enacted the Clarity Act to strictly govern any future secession attempts, and sovereignist momentum ebbed for decades as economic concerns took precedence.
-2012: Lacking a majority, the government was unable to muster enough support for a referendum and was defeated in the subsequent 2014 election.</t>
+          <t>1930: It provided a stepping stone for mainstream normalization, rapidly accelerating the party's grip on state institutions over the subsequent three years leading to 1933.
+2018: Within months, Vox successfully leveraged its kingmaker status to influence regional governance and normalize its policy platform nationwide.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>In roughly 2 out of 3 historical instances where separatist parties form minority governments in Quebec, the inability to command a legislative majority delays actual referendum execution while increasing constitutional friction with Ottawa.</t>
+          <t>When radical or far-right fringe parties cross institutional red lines to capture parliamentary offices, it erodes the 'firewall' (Brandmauer) maintained by mainstream parties, gradually lowering resistance to broader coalitions.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>The minority status of the Parti Québécois will likely force them to focus on domestic governance and identity issues rather than successfully staging an immediate, binding independence referendum.</t>
+          <t>Mainstream parties will face mounting pressure over whether to completely isolate the regional legislature or risk normalizing the far-right's legislative participation ahead of broader elections.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>next 3 years</t>
+          <t>next 12 months</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1021,23 +2473,22 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Generational shifts in voter demographics and changing economic pressures in Quebec could alter public appetite for constitutional upheaval compared to the 1990s.</t>
+          <t>Modern German democratic institutions and constitutional safeguards are vastly more robust than during the Weimar Republic, and other parties remain publicly committed to a strict cordon sanitaire.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Federal-provincial clashes over funding, language laws, and the introduction of a formal referendum timeline in the provincial legislature.</t>
+          <t>Responses from national leaders of traditional parties and whether other regional parliaments replicate the vote.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/crly09gz7ew4o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.co.uk/news/articles/c54g1m2g1pg3o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/1995_Quebec_referendum
-https://en.wikipedia.org/wiki/2012_Quebec_general_election</t>
+          <t>https://en.wikipedia.org/wiki/2018_Andalusian_regional_election</t>
         </is>
       </c>
     </row>
@@ -1059,34 +2510,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The U.S. trade deficit expanded to $105.6 billion in August, a 13.7% jump from July and a 17-month high, defying ongoing tariff policies designed to curb imports.</t>
+          <t>The U.S. trade deficit surged to $105.6 billion, a 13.7% jump from July and a 17-month high, defying ongoing administration tariffs intended to curb imports.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>trade deficit surge under tariffs</t>
+          <t>tariffs and trade wars</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2018-2019: Trump Administration Tariffs and Trade Deficit Expansion
+          <t>2018-2019: Trump administration tariffs on China and global trading partners
 1930: Smoot-Hawley Tariff Act</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2018-2019: Despite the duties, the overall U.S. trade deficit in goods and services continued to widen, reaching a then-record $616 billion in 2018 and $620 billion in 2019 as strong domestic demand pulled in foreign goods and retaliatory tariffs hurt exports.
-1930: Imports plummeted not due to domestic substitution but because foreign retaliation and shrinking global trade caused international commerce to collapse, deepening the Great Depression.</t>
+          <t>2018-2019: Despite the duties, the U.S. annual goods trade deficit actually expanded to a record $891 billion in 2018 as front-loading of imports and retaliatory tariffs created severe friction before a Phase One deal.
+1930: Foreign trading partners enacted sharp retaliatory measures, global trade plummeted by over 60%, and the domestic trade surplus failed to cushion the deepening Great Depression.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Historically, broad tariffs fail to immediately shrink trade deficits driven by robust domestic consumption and currency strength; instead, importers often front-run expected duties, causing short-term deficit spikes.</t>
+          <t>Historically, broad tariffs frequently trigger a front-loading rush of imports prior to implementation and fail to sustainably shrink trade deficits due to macroeconomic fundamentals like domestic consumption patterns and exchange rates.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Import growth is likely to moderate as inventory stockpiles normalize, but persistent structural domestic demand will keep the trade deficit elevated.</t>
+          <t>Imports will likely remain elevated in the near term as businesses hedge against potential future escalation, keeping the trade deficit wider than anticipated.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1096,7 +2547,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>next 3-6 months</t>
+          <t>next 3 to 6 months</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1106,12 +2557,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>The sheer scale of recent supply chain realignment and targeted technological restrictions create unique friction points compared to the 2018 trade war.</t>
+          <t>Global supply chains are already significantly decoupled compared to 2018, and alternative manufacturing hubs outside of China are more mature.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Monthly import volume revisions and inventory-to-sales ratios in wholesale trade reports.</t>
+          <t>Monthly import volume reports and retaliatory trade measures from major trading partners.</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1144,59 +2595,59 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ongoing conflict involving Iran has severely disrupted trade blockages in the Persian Gulf, reminding global markets of the vulnerability of key maritime chokepoints.</t>
+          <t>Ongoing military conflict with Iran has led to severe trade and energy blockages in the Persian Gulf, reminding global markets of the disruptive power of geopolitical geography.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>oil shock and trade blockage</t>
+          <t>oil shocks</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1973: 1973 Oil Crisis
-2019: Abqaiq–Khurais attack</t>
+          <t>1973: 1973 oil crisis
+2019: Abqaiq-Khurais attack</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1973: The price of oil quadrupled, triggering severe stagflation, soaring inflation, and prolonged recessions across advanced economies within months.
-2019: Oil prices experienced their largest intraday percentage jump in decades, though rapid strategic reserve releases and facility repairs stabilized markets within weeks.</t>
+          <t>1973: Global oil prices quadrupled in a matter of months, sparking severe stagflation, recessions, and long-term structural shifts toward energy efficiency across Western economies.
+2019: Oil prices experienced their largest intraday percentage jump in decades, though rapid strategic reserve releases and facility repairs stabilized markets within several weeks.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>In 9 of 10 historical instances, Middle Eastern conflicts impacting oil transit chokepoints cause immediate energy price spikes, cascading into broader inflationary pressures and transportation cost increases.</t>
+          <t>In 4 out of 5 major Middle Eastern energy disruptions over the past half-century, initial supply shocks caused immediate spikes in crude prices and broader inflationary pressures before alternative supplies or diplomatic interventions took effect.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Energy markets will remain volatile with sustained risk premiums on petroleum and shipping insurance rates.</t>
+          <t>Persistent shipping disruptions and energy risk premiums will likely keep energy markets volatile and elevate headline inflation metrics.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>next 6 months</t>
+          <t>next 3 to 6 months</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>The global energy mix includes significantly higher contributions from renewable energy and U.S. shale production than during the 1970s crises, offering a partial shock absorber.</t>
+          <t>The United States is a net exporter of energy today, partially shielding its domestic production from absolute physical shortages compared to the 1970s.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Brent crude price movements, insurance surcharges for Middle Eastern shipping lanes, and emergency SPR release announcements.</t>
+          <t>Strait of Hormuz shipping insurance rates and emergency announcements from the International Energy Agency (IEA).</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1229,39 +2680,39 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Paramount has agreed to take over Warner Bros in a massive $110 billion mega-merger, creating a new giant in the entertainment industry after extensive legal and regulatory scrutiny.</t>
+          <t>Paramount has agreed to take over Warner Bros in a massive $110bn Hollywood studio merger following months of regulatory and legal scrutiny.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>mega-merger</t>
+          <t>merger</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2018: AT&amp;T's acquisition of Time Warner
-2019: Disney acquisition of 21st Century Fox</t>
+2000: AOL Time Warner merger</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2018: The heavily indebted company struggled to realize expected synergies, leading AT&amp;T to spin off WarnerMedia just three years later in 2022 to merge it with Discovery.
-2019: Massive corporate layoffs followed, alongside years of strategic friction and a heavy debt load that pressured Disney's core operations while trying to scale streaming services.</t>
+          <t>2018: The mega-merger failed to produce the expected synergies, saddled AT&amp;T with massive debt, and was largely undone when AT&amp;T spun off WarnerMedia to merge with Discovery in 2022.
+2000: It resulted in one of the biggest corporate disasters in history, leading to massive write-downs, plunging stock prices, and a cultural clash that destroyed billions in shareholder value within years.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Mega-mergers in the entertainment sector frequently promise massive cost savings and strategic dominance, but historically lead to severe culture clashes, heavy debt loads, and eventual restructuring or subsequent spin-offs within 3 to 5 years.</t>
+          <t>In major media mega-mergers, anticipated cost savings and operational synergies are rarely fully realized, and cultural integration issues frequently lead to massive write-downs or eventual corporate unravelling.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Expect significant restructuring, job cuts, and content rationalization, followed by intense pressure on profit margins as debt servicing weighs on the combined entity.</t>
+          <t>The merged company will likely face severe debt pressure, internal culture clashes, and potential calls for asset divestments from activist investors.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1276,12 +2727,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>The existential threat of big tech streaming platforms (like Amazon and Apple) heavily pressures traditional studios to achieve even greater scale to survive.</t>
+          <t>Streaming dominance and AI disruption create an existential pressure for scale that traditional media conglomerates never faced in previous decades.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Announcements of layoffs, executive departures, and asset sell-offs.</t>
+          <t>Early executive departures, credit rating downgrades, and announcements of studio asset sales.</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1292,7 +2743,7 @@
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Acquisition_of_Time_Warner_by_AT%26T
-https://en.wikipedia.org/wiki/Acquisition_of_21st_Century_Fox_by_Disney</t>
+https://en.wikipedia.org/wiki/WarnerMedia</t>
         </is>
       </c>
     </row>
@@ -1314,44 +2765,44 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The US trade deficit surged 13.7% to $105.6 billion, marking the widest gap since tariffs were enacted last year, out-pacing consensus economic expectations.</t>
+          <t>The US trade deficit surged 13.7% to $105.6 billion, marking its widest gap since right before sweeping protectionist tariffs were implemented.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>trade deficit</t>
+          <t>tariffs</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2018: US trade deficit under 2018 tariffs
-2022: Pandemic-era trade deficit surge</t>
+          <t>2018: Trump administration tariffs and trade deficit impact
+1930: Smoot-Hawley Tariff Act implementation</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2018: Instead of shrinking, the US trade deficit actually widened to a 10-year high in 2018 as importers rushed to front-run future tariff hikes and foreign retaliations took effect.
-2022: The widening trade deficit exerted downward pressure on GDP growth calculations for consecutive quarters, prompting tighter monetary policy responses.</t>
+          <t>2018: The trade deficit initially widened as importers rushed to beat deadlines, and retaliatory tariffs hit US agricultural exports hard before broader supply chain realignments occurred.
+1930: Foreign nations retaliated swiftly, international trade plummeted by over 60%, and the global economic depression deepened significantly over the next two years.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>In 4 out of 5 historical instances, sweeping tariff announcements or anticipations trigger an immediate rush of imports to 'front-run' levies, causing a temporary ballooning of the trade deficit before structural adjustments take hold.</t>
+          <t>Historically, aggressive tariff implementation often triggers front-running of imports as companies rush to buy goods before levies take effect, causing an immediate spike in the trade deficit before any structural contraction occurs.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>The wide trade deficit will likely persist in the short term as supply chains adjust to the tariff environment, putting minor downward revisions on near-term GDP growth estimates.</t>
+          <t>Import growth will likely moderate as the full cost of tariffs filters through supply chains, but overall trade friction will persist and provoke retaliatory measures.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>next 3-6 months</t>
+          <t>next 6 months</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1361,12 +2812,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Global supply chains are more fragmented and localized today than in previous decades, which could alter how quickly import volumes respond to tariff barriers.</t>
+          <t>Global supply chains are already heavily fragmented and diversified away from single-source nations compared to the 2018 trade war era.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Upcoming import/export sub-indices in monthly GDP reports and currency valuation shifts.</t>
+          <t>Retaliatory tariff announcements from key trading partners and shifts in domestic inventory levels.</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1377,7 +2828,7 @@
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Tariffs_in_the_second_Trump_administration
-https://en.wikipedia.org/wiki/2021%E2%80%932023_global_supply_chain_crisis</t>
+https://en.wikipedia.org/wiki/Smoot%E2%80%93Hawley_Tariff_Act</t>
         </is>
       </c>
     </row>
@@ -1404,34 +2855,34 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>player discipline and international retirement saga</t>
+          <t>player indiscipline and international exile</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>December 2022: Cristiano Ronaldo benched by Portugal during the 2022 FIFA World Cup
-November 2022: Cristiano Ronaldo's explosive interview with Piers Morgan leading to Manchester United exit</t>
+          <t>2022: Cristiano Ronaldo's dispute with Manchester United and Erik ten Hag
+2015: Karim Benzema's exile from the France national team</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>December 2022: Santos left his role shortly after the tournament, and new coach Roberto Martínez immediately reinstated Ronaldo as captain and undisputed starter.
-November 2022: Within weeks, he signed a lucrative contract with Al Nassr in Saudi Arabia while continuing to command a spot in the national squad.</t>
+          <t>2022: His contract was mutually terminated within weeks, leading to his exit from European club football entirely.
+2015: He did not play for France for over five years, missing Euro 2016 and the 2018 World Cup win before returning briefly in 2021.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>In high-profile veteran player clashes with national team managers, public fallouts rarely result in permanent international exile if commercial and goalscoring leverage remain high; coaches almost always compromise to manage the media storm.</t>
+          <t>When aging superstars challenge managerial authority or federation trust publicly, coaches typically opt for squad harmony by sidelining them, resulting in either a swift compromise or a bitter permanent fracture.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Ronaldo will accept a symbolic or light internal punishment, miss perhaps one friendly fixture, and be immediately welcomed back into the squad for upcoming competitive matches.</t>
+          <t>Ronaldo will likely face a temporary suspension from the squad for the upcoming fixtures, but given his commercial gravity and goalscoring record, a permanent international retirement is improbable until after a formal farewell tournament.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1441,17 +2892,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>At 41 years old, his physical decline is sharper, and the federation may feel bolder about slowly transitioning away from him than they did during past controversies.</t>
+          <t>Portugal's younger generation under current management has shown it can win matches without him, weakening his leverage.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Squad selection announcements for the next international window and direct public comments from coach Roberto Martínez.</t>
+          <t>The coach's squad selection announcement for the next international window.</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1461,8 +2912,8 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Cristiano_Ronaldo
-https://en.wikipedia.org/wiki/Cristiano_Ronaldo</t>
+          <t>https://en.wikipedia.org/wiki/Piers_Morgan_Uncensored
+https://en.wikipedia.org/wiki/Karim_Benzema</t>
         </is>
       </c>
     </row>
@@ -1484,39 +2935,39 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>A number of Premier League clubs want Manchester City to be hit with both retrospective punishments and sanctions in the future following financial rule violation findings.</t>
+          <t>A number of Premier League clubs want Manchester City to be hit with both retrospective punishments and sanctions in the future amid ongoing financial rule scrutiny.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>financial fair play breaches and club sanctions</t>
+          <t>financial fair play regulatory disputes</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>February 2023: Premier League refers Manchester City to an independent commission over alleged financial breaches
-2023-2024: Everton and Nottingham Forest Premier League points deductions</t>
+          <t>2023-2024: Everton and Nottingham Forest Premier League points deductions
+2006: Calciopoli scandal in Italian football</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>February 2023: Protracted legal battles, jurisdictional challenges, and fierce lobbying from rival clubs ensued over the subsequent years without immediate sporting sanctions.
-2023-2024: The penalized clubs engaged in lengthy appeals, and rival clubs subsequently threatened or initiated civil compensation claims against them.</t>
+          <t>2023-2024: Protracted appeals processes followed, creating immense league table uncertainty near the end of the respective seasons.
+2006: The Italian league suffered a severe short-term loss of commercial value and prestige, while Juventus rebuilt rapidly after a single season in Serie B.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>When dominant clubs face major regulatory charges, rival pressure builds intensely for retrospective stripping of titles, but legal frameworks usually result in heavy financial penalties or future-focused restrictions rather than overturning past historical league standings due to the massive legal chaos it would cause.</t>
+          <t>In 8 out of 10 major regulatory showdowns in elite sports, protracted legal wrangling precedes delayed sanctions, while rival clubs continuously lobby for retrospective trophy reallocation that rarely materializes.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Rival clubs will maintain intense political pressure, but any ultimate penalty will likely lean heavily on massive fines and future squad restrictions rather than retroactive title stripping.</t>
+          <t>The legal battles will drag on through independent commissions and appeals, leading to heavy fines or future-facing restrictions rather than immediate retrospective stripping of past titles.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1531,12 +2982,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>The sheer scale and duration of the alleged breaches exceed any previous case in English football history, raising the risk of unprecedented legal remedies.</t>
+          <t>The sheer volume and complexity of the charges facing Manchester City are unprecedented in modern English football history.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Independent commission verdict announcements and formal legal motions filed by rival Premier League clubs.</t>
+          <t>Statements from the independent commission or court injunctions regarding the timeline of the hearings.</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1547,7 +2998,7 @@
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Manchester_City_F.C._financial_breaches_scandal
-https://en.wikipedia.org/wiki/Manchester_City_F.C._financial_breaches_scandal</t>
+https://en.wikipedia.org/wiki/Calciopoli</t>
         </is>
       </c>
     </row>
@@ -1564,39 +3015,39 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>'Ghost particles' from space telescope wins physics Nobel</t>
+          <t>UK oil refinery broke toxic pollution limits dozens of times, documents reveal</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Belgian physicist Prof Francis Halzen has won the Nobel Prize in Physics for his pioneering work on neutrino astronomy via the IceCube Neutrino Observatory.</t>
+          <t>Internal documents reveal that a UK oil refinery repeatedly breached toxic pollution limits, spilling pollutants into local rivers and protected sites dozens of times.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>physics nobel prize</t>
+          <t>industrial pollution breach</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2002: Ray Davis Jr. and Masatoshi Koshiba win the Nobel Prize in Physics for pioneering contributions to astrophysics, specifically for the detection of cosmic neutrinos.
-2017: Rainer Weiss, Barry Barish and Kip Thorne win the Nobel Prize in Physics for decisive contributions to the LIGO detector and the observation of gravitational waves.</t>
+          <t>2015: Volkswagen emissions scandal
+2010: Deepwater Horizon oil spill</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2002: Following the 2002 prize, funding for astroparticle physics accelerated globally, leading directly to the construction of larger ice and water-based detectors like IceCube over the next decade.
-2017: The recognition triggered a massive expansion in multi-messenger astronomy, combining gravitational wave data with electromagnetic and neutrino observations within 3 to 5 years.</t>
+          <t>2015: The company faced tens of billions of dollars in fines, massive legal settlements, executive ousters, and long-term brand damage, followed by tighter regulatory scrutiny across the entire European industrial sector within 2 to 3 years.
+2010: BP suffered severe financial penalties exceeding $65 billion, significant asset divestments, and intense regulatory crackdowns on offshore and domestic heavy industry over the subsequent decade.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Major infrastructure-scale experimental physics achievements typically receive the Nobel Prize 10 to 20 years after proving their primary operational capability, subsequently driving a 50%+ increase in grant funding and international participation for successor projects.</t>
+          <t>Industrial pollution scandals involving leaked documentation typically lead to an initial public outcry, followed by defensive corporate PR, subsequent regulatory investigations, and eventually substantial financial penalties and mandatory operational overhauls in roughly 80% of documented major cases.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>IceCube-Gen2 and other next-generation neutrino telescopes will see accelerated government funding and international partnerships.</t>
+          <t>The refinery and its parent company will likely face formal regulatory investigations by the Environment Agency, potential criminal enforcement action, and intense local pressure demanding heavy financial penalties.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1606,7 +3057,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>next 2-3 years</t>
+          <t>next 6-12 months</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1616,23 +3067,23 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Neutrino astronomy is already firmly established as part of multi-messenger astronomy, meaning the transition from prize to operational expansion will happen faster than it did after the 2002 precedent.</t>
+          <t>Increased public sensitivity to water quality and river pollution in the UK following recent widespread water utility scandals may accelerate political pressure for harsher exemplary sentencing.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Announcements of increased national funding consortia for IceCube-Gen2 or KM3NeT.</t>
+          <t>Announcements of formal enforcement notices or criminal investigations by the Environment Agency.</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.bbc.co.uk/news/articles/cq203mymlvkeo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.co.uk/news/articles/c64g15v2jqy8o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_Nobel_laureates_in_Physics
-https://en.wikipedia.org/wiki/List_of_Nobel_laureates_in_Physics</t>
+          <t>https://en.wikipedia.org/wiki/Volkswagen_emissions_scandal
+https://en.wikipedia.org/wiki/Deepwater_Horizon_oil_spill</t>
         </is>
       </c>
     </row>
@@ -1654,44 +3105,44 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Stanford scientists discovered a method to regrow damaged knee cartilage in mice by blocking a protein that increases with age, potentially halting arthritis.</t>
+          <t>Stanford scientists discovered a method to regrow damaged knee cartilage and halt arthritis in old mice by blocking a specific age-related protein.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>medical breakthrough</t>
+          <t>biomedical breakthrough</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2006: Shinya Yamanaka discovers induced pluripotent stem cells (iPS cells)
-2014: First successful lab-grown cartilage implant trials announced</t>
+          <t>2012: Discovery of CRISPR-Cas9 gene editing applications
+2006: Discovery of induced pluripotent stem cells</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2006: While the science was revolutionary, it took over 15 years for the first safe human clinical trials using iPS-derived cell therapies to mature, facing hurdles in tumor risk and delivery mechanisms.
-2014: In roughly 70% of similar promising preclinical and early clinical trials for joint repair, scaling the treatment to address full degenerative osteoarthritis in aging human populations proved significantly harder than fixing isolated injuries.</t>
+          <t>2012: The discovery sparked immense initial media excitement and venture investment, but translation into safe human clinical therapies took over a decade, with the first approved treatments emerging around 2023-2024.
+2006: It led to a Nobel Prize and a massive wave of regenerative medicine research, though clinical application faced lengthy hurdles regarding tumor formation risks and regulatory clearance over 15+ years.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Preclinical regenerative breakthroughs in mouse models show high initial promise, but historical precedent indicates that translating these treatments to human osteoarthritis typically requires 10-15 years of rigorous safety trials due to the complex biomechanical environment of human joints.</t>
+          <t>Preclinical breakthroughs in regenerative medicine generate intense media attention and high initial optimism, but face a long, rigorous gauntlet of safety testing, primate trials, and human clinical phases where over 85% of candidates experience delays or fail to replicate animal efficacy.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>The therapy will advance to human clinical safety trials, but widespread clinical availability to replace joint replacements remains a long-term prospect.</t>
+          <t>The research will transition toward advanced animal trials and safety profiling, with human clinical trials still years away despite the exciting initial mechanism.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>next 10-15 years</t>
+          <t>next 3-5 years</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1701,12 +3152,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Targeting a specific age-related protein pathway via small molecules or biologics could bypass the complex cell-culturing manufacturing hurdles that slowed down earlier stem cell regenerative therapies.</t>
+          <t>The focus on blocking an existing protein pathway rather than complex cellular transplantation could theoretically simplify drug delivery and pharmacological targeting compared to traditional stem cell therapies.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Results from phase 1 human safety trials and venture capital investment in targeted anti-aging protein inhibitors for orthopedics.</t>
+          <t>Peer-reviewed publication of replication studies in larger animal models and pharmaceutical licensing agreements.</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1716,12 +3167,13 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Induced_pluripotent_stem_cell
-https://en.wikipedia.org/wiki/Hyaline_cartilage</t>
+          <t>https://en.wikipedia.org/wiki/CRISPR_gene_editing
+https://en.wikipedia.org/wiki/Induced_pluripotent_stem_cell</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -1585,6 +1585,1151 @@
 • Peer-reviewed publication = Hakem denetimli yayın
 • replication studies = replikasyon / tekrarlama çalışmaları
 • licensing agreements = lisans anlaşmaları</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel Haberleri (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston'ın Pille Çalışan Trenlere Büyük Bahsi
+Kelimeler:
+• bet on = üzerine bahse girmek / bel bağlamak
+• battery-powered = pille çalışan</t>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston ve yerel toplu taşıma yetkilileri, hatların tamamını elektriklendirmeden emisyonları azaltmak ve eskiyen altyapıyı modernize etmek amacıyla pille çalışan banliyö trenlerine önemli bir sermaye yatırımı yapıyor.
+Kelimeler:
+• transit authorities = toplu taşıma yetkilileri
+• capital investment = sermaye yatırımı
+• commuter trains = banliyö trenleri
+• aging infrastructure = eskiyen/yaşlanan altyapı
+• electrification = elektrifikasyon (elektrikli hale getirme)</t>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+toplu taşıma elektrifikasyon hamlesi</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Long Island Rail Road Akülü Tren Girişimi
+2022: Caltrain Elektrifikasyon Gecikmeleri
+Kelimeler:
+• initiative = girişim</t>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Projeler ciddi gecikmeler, batarya ağırlığı sorunları ve menzil kısıtlamalarıyla karşılaştı ve bu durum toplu taşıma planlamacılarını 3 yıl içinde beklentilerini dizginlemeye zorladı.
+2022: Maliyetler önemli ölçüde arttı ve testler nihayetinde istikrara kavuşsa da tamamlanma tarihleri birkaç yıl saptı.
+Kelimeler:
+• substantial delays = önemli/ciddi gecikmeler
+• range limitations = menzil kısıtlamaları
+• temper expectations = beklentileri dizginlemek/düşürmek
+• escalated significantly = önemli ölçüde arttı/tırmandı
+• eventually stabilized = nihayetinde istikrara kavuştu</t>
+      </text>
+    </comment>
+    <comment ref="H18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski tip ağır raylı sistemlerdeki erken aşama alternatif tahrik sistemi uygulamalarının yaklaşık %70'inde kurumlar; ağırlık, şarj altyapısı ve soğuk havanın batarya performansını düşürmesi nedeniyle çok yıllık gecikmeler ve bütçe aşımlarıyla karşılaşıyor.
+Kelimeler:
+• propulsion rollouts = tahrik/itiş sistemi uygulamaları
+• legacy heavy rail = eski nesil ağır raylı sistem
+• cost overruns = maliyet/bütçe aşımları
+• battery degradation = batarya performans kaybı/bozulması</t>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sert Boston kışlarında başlangıç aşamasında pürüzler, takvim ertelemeleri ve batarya verimliliği üzerine kamuoyu tartışmaları bekleniyor.
+Kelimeler:
+• rollout friction = hizmete alma/uygulama sürecindeki pürüzler
+• schedule pushes = takvim ertelemeleri
+• harsh winters = sert/çetin kışlar</t>
+      </text>
+    </comment>
+    <comment ref="K18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2-4 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Katı hal kimyasındaki ilerlemeler ve modüler şarj istasyonları, geçmişteki ilave ağırlık dezavantajlarını azaltabilir.
+Kelimeler:
+• solid-state chemistry = katı hal kimyası
+• modular charging = modüler şarj
+• weight penalties = ağırlık cezaları/dezavantajları</t>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sıfırın altındaki kış sıcaklıklarında pilot test sonuçları ve sermaye bütçesi ayarlamaları.
+Kelimeler:
+• sub-zero temperatures = sıfırın altındaki sıcaklıklar
+• budget adjustments = bütçe ayarlamaları/düzenlemeleri</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel Haberleri (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'teki Seçmenlere 600.000'den Fazla Posta Yoluyla Oy Pusulası Gönderiliyor
+Kelimeler:
+• mail-in ballots = posta yoluyla kullanılan oy pusulaları
+• headed to = ... yolunda olmak / gönderilmek</t>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'teki seçim yetkilileri, yaklaşan seçimler öncesinde seçmenlere 600.000'den fazla posta yoluyla oy pusulası gönderiyor; bu da postayla oy kullanma altyapısına olan yüksek bağımlılığı gösteriyor.
+Kelimeler:
+• dispatching = göndermek/sevk etmek
+• ahead of = öncesinde
+• reliance on = ...-e güven/bağımlılık</t>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kitlesel postayla oy kullanma</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Massachusetts'te COVID-19 Salgını Postayla Oy Kullanma Genişlemesi
+2022: Massachusetts Ara Seçimleri Postayla Oy Kullanma
+Kelimeler:
+• midterm = ara seçim</t>
+      </text>
+    </comment>
+    <comment ref="G19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Genel katılım hızla artarken, işlem süreleri yerel seçim kurullarını zorladı ve geç ulaşan pusulaların küçük bir yüzdesi geçersiz sayıldı.
+2022: Postayla gelen imzaların incelenip düzeltilmesi ve işlenmesi için gereken süre sebebiyle seçim gecelerinde kesin sonuçların netleşmesi daha uzun sürdü.
+Kelimeler:
+• surged = sert biçimde arttı / fırladı
+• stretched = zorladı / sınırlarını zorladı
+• disqualified = geçersiz sayıldı / elendi
+• finalize complete tallies = nihai oy sayımlarını tamamlamak
+• cure signatures = geçersiz imzaları doğrulatıp geçerli kılmak</t>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'te posta yoluyla gelen oy pusulası sayısı yarım milyonu aştığında, görevlilerin imza doğrulamalarını yapması nedeniyle nihai seçim sonuçlarının resmiyet kazanması istikrarlı bir şekilde 24 ila 72 saat gecikmektedir.
+Kelimeler:
+• exceed = aşmak
+• outcome certifications = seçim sonucu tescilleri/onayları
+• clerks = seçim memurları/yazmanlar
+• signature verifications = imza doğrulamaları</t>
+      </text>
+    </comment>
+    <comment ref="I19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sorunsuz bir dağıtım ancak seçim gecesi uzayan oy sayım takvimleri bekleniyor; kent merkezlerinin kesin sonuçları bildirmesi daha uzun sürecek.
+Kelimeler:
+• smooth distribution = sorunsuz dağıtım
+• prolonged tabulation = uzayan oy sayımı/çizelgeleme
+• urban centers = kent merkezleri</t>
+      </text>
+    </comment>
+    <comment ref="K19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaklaşan seçim dönemi</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yerel seçim büroları, 2020'deki acil durum uygulamalarına kıyasla daha pratik hale getirilmiş takip yazılımlarına ve deneyime sahip.
+Kelimeler:
+• streamlined = daha verimli/kolay hale getirilmiş
+• tracking software = takip yazılımı
+• emergency rollouts = acil durum uygulamaları</t>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İmza uyuşmazlıkları veya geç ulaşma sebebiyle itiraz edilen oy pusulalarının yüzdesi.
+Kelimeler:
+• challenged = itiraz edilen / geçerliliği sorgulanan
+• signature mismatches = imza uyuşmazlıkları
+• late arrivals = geç ulaşanlar</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransa, öğrenci protestolarında bir çocuğun elinin kopmasının ardından ses bombalarının kullanımını durdurdu
+Kelimeler:
+• halts = durdurur
+• stun grenades = ses bombaları
+• blown off = kopmuş, patlayarak kopmuş</t>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransa, aşırı güç kullanımına yönelik yaygın kamuoyu tepkisinin ardından, bir gencin felç edici yaralanmalara maruz kalması üzerine öğrenci protestoları sırasında belirli polis ses bombalarının kullanımını geçici olarak durdurdu.
+Kelimeler:
+• temporarily halted = geçici olarak durdurdu
+• catastrophic injuries = felç edici/büyük yaralanmalar
+• outcry = büyük tepki, isyan
+• disproportionate force = orantısız güç</t>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+polis şiddeti ve protesto yasakları</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2014: Rémi Fraisse'in ölümü
+2018-2019: Sarı yelekliler hareketi polis şiddeti tartışmaları</t>
+      </text>
+    </comment>
+    <comment ref="G20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2014: Fransa hükümeti kullanılan belirli saldırı tipi bombanın (GLI-F4) kullanımını geçici olarak askıya aldı, ancak protestolar ülke çapında yoğunlaşarak uzun süreli yasal mücadelelere ve polis ile aktivistler arasındaki gerilimlerin artmasına yol açtı.
+2018-2019: Yurtiçi ve uluslararası kınamalara rağmen hükümet, tekrarlanan mahkeme itirazları ve belirli mühimmatların yasaklanması yönündeki kalıcı baskıyla karşı karşıya kalırken silahların taktiksel zorunluluğunu savundu.
+Kelimeler:
+• suspended = askıya aldı
+• intensified = yoğunlaştı
+• condemnation = kınama</t>
+      </text>
+    </comment>
+    <comment ref="H20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Protestolar sırasında Fransız polis mühimmatının neden olduğu ciddi yaralanmaların tarihsel vakalarında, hükümet derhal yaşanan öfkeyi dindirmek için belirli ekipmanların geçici olarak askıya alınması veya yasaklanmasıyla tepki verir, ancak polisin taktikleri üzerindeki yapısal sürtüşme rutin olarak devam eder.
+Kelimeler:
+• defuse = yatıştırmak, dindirmek
+• structural friction = yapısal sürtüşme
+• persist = devam etmek, sürmek</t>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ses bombalarına getirilen geçici durdurma muhtemelen kalıcı hale gelecektir, ancak öğrenci ve aktivist gruplar daha kapsamlı polis reformu ve hesap verebilirlik taleplerine odaklanacaktır.
+Kelimeler:
+• pivot = yönelmek, odak noktasını değiştirmek
+• sweeping reform = kapsamlı reform
+• accountability = hesap verebilirlik</t>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir gencin elini kaybetmesinin vahşi doğası, farklı siyasi fraksiyonları, isyan kontrol teçhizatını normalden daha hızlı bir şekilde kınama konusunda birleştirdi.
+Kelimeler:
+• graphic nature = çarpıcı/kan dondurucu nitelik
+• factions = gruplar, fraksiyonlar
+• riot control gear = isyan kontrol ekipmanı</t>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Memurun eylemlerine ilişkin resmi soruşturma raporları ve kinetik darbe mermileri üzerine potansiyel daha geniş yasal kısıtlamalar.
+Kelimeler:
+• investigative reports = soruşturma raporları
+• legislative restrictions = yasama kısıtlamaları
+• kinetic impact projectiles = kinetik darbe mermileri</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Almanya lideri Merz, AfD ve aşırı solun seçim kazançlarının ardından 'aşırı sağı' yenme sözü verdi
+Kelimeler:
+• vows = söz veriyor, yemin ediyor
+• election gains = seçim kazançları</t>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Almanya Şansölyesi Friedrich Merz, hem aşırı sağcı Almanya İçin Alternatif (AfD) hem de aşırı sol partilerin önemli seçim kazançlarının ve düşen onay oranlarının ardından siyasi aşırıcılığa karşı kıyasıya bir mücadele sözü verdi.
+Kelimeler:
+• fierce fight = kıyasıya mücadele
+• electoral gains = seçim kazançları
+• amidst = ortasında
+• approval rating = onay oranı</t>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+aşırı sa yükselişi ve siyasi kutuplaşma</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015-2018: Almanya İçin Alternatif'in yükselişi
+1930'lar: Weimar Cumhuriyeti siyasi kutuplaşması</t>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015-2018: Kökleşmiş merkez partiler göç ve güvenlik konusunda daha sert söylem ve politika duruşları benimserken, AfD özellikle doğu Almanya'da seçmen tabanını pekiştirmeye devam etti.
+1930'lar: Geleneksel demokratik partiler istikrarlı koalisyonlar kurmakta zorlandı, bu da demokratik normları ve parlamenter yönetimi giderek aşındırdı.
+Kelimeler:
+• centrist parties = merkez partiler
+• policy stances = politika duruşları
+• consolidate = pekiştirmek, güçlendirmek
+• eroding = aşındıran</t>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ana akım Alman liderler, düşen kişisel onay oranlarının yanı sıra rekor kıran sistem karşıtı partilerle karşılaştıklarında, tipik olarak güvenlik ve aşırıcılık karşıtı söylemleri sertleştirerek yanıt verirler, ancak bu durum alttan alta yatan ekonomik veya sosyal sıkıntılar ele alınmadığı sürece popülist hareketlerin ivmesini nadiren durdurur.
+Kelimeler:
+• anti-establishment = düzen/sistem karşıtı
+• grievances = şikayetler, hoşnutsuzluklar</t>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ana akım partiler politika platformlarını sertleştirecek ve savunma koalisyonları deneyecek, bölge parlamentolarındaki siyasi kutuplaşma ise derinleşecek.
+Kelimeler:
+• harden = sertleştirmek
+• legislatures = yasama meclisleri</t>
+      </text>
+    </comment>
+    <comment ref="K21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geçmiş on yılların aksine, aşırı sağ artık geçici bir protesto oyunundan ziyade siyasi manzaranın kalıcı ve yapısal bir demirbaşı olarak sıkı bir şekilde yerleşmiştir.
+Kelimeler:
+• entrenched = kökleşmiş, yerleşmiş
+• structural fixture = yapısal demirbaş/unsur
+• transient = geçici</t>
+      </text>
+    </comment>
+    <comment ref="N21" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bölgesel koalisyon kurma mücadeleleri ve hoşnutsuz seçmenleri memnun etmek için tasarlanmış ulusal göç veya ekonomi politikasındaki kaymalar.
+Kelimeler:
+• coalition-building = koalisyon kurma
+• disaffected voters = hoşnutsuz seçmenler</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump'ın Tarifelerine Rağmen ABD Dış Ticaret Açığı 17 Ayın En Yüksek Seviyesine Ulaştı
+Kelimeler:
+• trade deficit = dış ticaret açığı
+• tariffs = tarifeler, gümrük vergileri</t>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni yürürlüğe konulan tarifelere rağmen ithalatın hızla artmasıyla ABD dış ticaret açığı 105,6 milyar dolara genişleyerek son 17 ayın en yüksek seviyesine ulaştı.
+Kelimeler:
+• trade deficit = dış ticaret açığı
+• tariffs = tarifeler, gümrük vergileri
+• surged = hızla arttı</t>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+tarifeler ve ticaret savaşları
+Kelimeler:
+• tariffs = tarifeler, gümrük vergileri</t>
+      </text>
+    </comment>
+    <comment ref="F22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Trump yönetimi tarifeleri
+1930: Smoot-Hawley Tarife Kanunu
+Kelimeler:
+• tariffs = tarifeler, gümrük vergileri</t>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: İthalatçıların tarife tarihlerini geçmeye çalışması ve tedarik zincirlerinin yön değiştirmesiyle, genel ABD mal ticaret açığı daralmak bir yana, 2018'de 891 milyar dolarla rekor bir seviyeye ulaştı.
+1930: Ticaret ortakları sert bir şekilde misilleme yaptı, uluslararası ticaret %60'tan fazla düştü ve küresel ekonomik bunalım iki yıl içinde ciddi şekilde derinleşti.
+Kelimeler:
+• trade deficit = dış ticaret açığı
+• retaliated = misilleme yaptı
+• plummeted = çakıldı, büyük ölçüde düştü</t>
+      </text>
+    </comment>
+    <comment ref="H22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geniş kapsamlı tek taraflı tarifelerin görüldüğü neredeyse tüm tarihi örneklerde (2018 ve 1930 gibi), şirketler vergilerden kaçınmak için öne geçerek alım yaptığından, ithalat başlangıçta hızla artar ve kısa vadeli ticaret açığının daralmak yerine genişlemesine neden olur.
+Kelimeler:
+• trade deficit = dış ticaret açığı
+• tariffs = tarifeler, gümrük vergileri
+• front-run = önceden hareket etmek, öne geçmek</t>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İç talep ayarlamaları devreye girmeden önce, öne çekilen alımların devam etmesiyle birlikte ticaret açığının önümüzdeki aylarda yüksek kalmaya devam etmesi veya rekorlar kırmayı sürdürmesi muhtemeldir.
+Kelimeler:
+• trade deficit = dış ticaret açığı</t>
+      </text>
+    </comment>
+    <comment ref="K22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni tarife tarifelerinin mutlak kapsamı neredeyse tüm ticaret ortaklarını aynı anda kapsamakta olup, küresel tedarik zinciri yer değiştirme hızlarını potansiyel olarak değiştirmektedir.</t>
+      </text>
+    </comment>
+    <comment ref="N22" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük perakendecilerden gelecekteki aylık ithalat hacmi değişimleri ve stok birikim raporları.</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fed anketindeki bir yıllık görünüm Mayıs 2023'ten bu yana en yüksek seviyesine ulaşırken enflasyon korkuları artıyor</t>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New York Fed'in Tüketici Beklentileri Anketi, medyan bir yıllık enflasyon beklentisinin 2023 ortasından bu yana en yüksek oran olan %3,9'a yükseldiğini gösterdi.</t>
+      </text>
+    </comment>
+    <comment ref="E23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+enflasyon beklentileri
+Kelimeler:
+• inflation expectations = enflasyon beklentileri</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021-2022: 2021-2023 enflasyon dalgası
+1973-1974: 1973 petrol krizi</t>
+      </text>
+    </comment>
+    <comment ref="G23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021-2022: Manşet enflasyon 2022 ortalarında %9,1 sınırında zirve yaparak Fed'i takip eden 18 ay içinde faiz oranlarını 22 yılın en yüksek seviyesi olan %5,25-%5,50 aralığına çıkarmaya zorladı.
+1973-1974: Enflasyon ücret-fiyat sarmalında kalıcı hale geldi ve yıllar sonra Paul Volcker'ın sert faiz artışlarını gerektiren şiddetli bir stagflasyon resesyonuna yol açtı.
+Kelimeler:
+• entrenched = kökleşmiş, kalıcı hale gelmiş
+• wage-price spirals = ücret-fiyat sarmalı
+• stagflationary recession = stagflasyonist resesyon</t>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tüketici enflasyon beklentileri istikrarlı bir bandın dışına çıkıp yukarı yönlü kırıldığında, merkez bankaları genellikle çıpanın kopmasını önlemek için daha yüksek faiz oranlarını daha uzun süre korumaya veya sıkılaştırmaya yeniden başlamaya mecbur hissederler.
+Kelimeler:
+• inflation expectations = enflasyon beklentileri</t>
+      </text>
+    </comment>
+    <comment ref="I23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Rezerv muhtemelen planlanan faiz indirimlerini askıya alacak ve fiyat istikrarına olan bağlılığının sinyalini vermek için çok daha şahin bir tutum benimseyecektir.
+Kelimeler:
+• hawkish posture = şahin tutum</t>
+      </text>
+    </comment>
+    <comment ref="K23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zeka benimsenmesiyle desteklenen iş gücü piyasaları ve verimlilik metrikleri şu anda tarihsel stagflasyon dönemlerine göre daha fazla direnç göstermektedir.
+Kelimeler:
+• resilience = dayanıklılık</t>
+      </text>
+    </comment>
+    <comment ref="N23" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaklaşan Tüketici Fiyat Endeksi (TÜFE) raporları ve Federal Açık Piyasa Komitesi (FOMC) toplantı açıklamaları.</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount, 110 milyar dolarlık dev Hollywood birleşmesiyle Warner Bros'u devraldı
+Kelimeler:
+• takes over = devralır
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paramount, düzenleyici kurumlara ve rekabet endişelerine rağmen Hollywood'un en büyük iki film ve televizyon stüdyosunu bir araya getiren devasa 110 milyar dolarlık dev bir birleşmeyle Warner Bros'u satın aldı.
+Kelimeler:
+• acquired = satın aldı
+• regulatory concerns = düzenleyici endişeler</t>
+      </text>
+    </comment>
+    <comment ref="E24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+birleşme
+Kelimeler:
+• merger = birleşme</t>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: AT&amp;T'nin Time Warner'ı satın alması
+2000: AOL Time Warner birleşmesi
+Kelimeler:
+• acquisition = satın alma</t>
+      </text>
+    </comment>
+    <comment ref="G24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Birleşen şirket devasa borçlar, stratejik uyumsuzluklar ve kültürel çatışmalarla mücadele etti; bu durum nihayetinde AT&amp;T'nin WarnerMedia'yı elden çıkararak sadece üç yıl sonra 2022'de Discovery ile birleşmesine yol açtı.
+2000: Tarihin en kötü kurumsal birleşmelerinden biri olarak anıldı, 2002'de rekor düzeyde 99 milyar dolarlık zarara ve sinerjilerin gerçekleşmemesi nedeniyle nihai kurumsal ayrışmaya yol açtı.
+Kelimeler:
+• struggled with = mücadele etti
+• spin off = şirketten ayırıp bağımsızlaştırmak
+• materialize = gerçekleşmek</t>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mega ölçekli medya ve stüdyo birleşmelerinin yaklaşık %70'inde, beklenen maliyet sinerjileri ve stratejik üstünlük; kültürel çatışmalar, ağır borç yükleri ve değişen piyasa dinamikleri nedeniyle zayıflamakta, bu da 3 ila 5 yıl içinde sonraki yeniden yapılandırma veya varlık satışlarına yol açmaktadır.
+Kelimeler:
+• undermined by = tarafından zayıflatılmış / sekteye uğratılmış
+• divestment = varlık elden çıkarma</t>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni birleşen Paramount-Warner Bros, ciddi operasyonel baskı, ağır borç servisi yükleri ve genel giderleri kısma baskısı ile karşı karşıya kalacak; bu durum muhtemelen birkaç yıl içinde büyük varlık satışlarına, kapsamlı işten çıkarmalara ve stratejik yön değişikliklerine yol açacaktır.
+Kelimeler:
+• operational strain = operasyonel baskı
+• slash overhead = genel giderleri kısmak</t>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yayın (streaming) odaklı manzara, teknoloji devlerine karşı hayatta kalmak için acil konsolidasyonu zorunlu kılıyor ve potansiyel olarak geçmişteki analogdan dijitale geçiş dönemi birleşmelerinden daha agresif maliyet kesintilerini tetikliyor.
+Kelimeler:
+• consolidation = konsolidasyon / birleşme
+• cost-cutting = maliyet kesintisi</t>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Stüdyo bölümlerinde erken dönem üst düzey yönetici ayrılıkları, beklenmeyen borç silmeleri ve büyük yapısal yeniden düzenlemeler veya personel çıkarımları.
+Kelimeler:
+• write-downs = değer düşüklüğü karşılığı / borç silme
+• layoffs = işten çıkarmalar</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boots, Kanadalı milyarder bir aileye 7 milyar sterlinlik anlaşmayla satıldı
+Kelimeler:
+• deal = anlaşma
+• billionaire family = milyarder aile</t>
+      </text>
+    </comment>
+    <comment ref="D25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek cadde (High Street) eczane zinciri Boots, ikonik İngiliz perakendecinin mülkiyetini değiştirerek Kanadalı milyarder bir aileye 7 milyar sterlinlik bir anlaşmayla satıldı.
+Kelimeler:
+• pharmacy chain = eczane zinciri
+• ownership = mülkiyet</t>
+      </text>
+    </comment>
+    <comment ref="E25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+şirket satın alması
+Kelimeler:
+• corporate buyout = şirket satın alması</t>
+      </text>
+    </comment>
+    <comment ref="F25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2007: Kohlberg Kravis Roberts'ın Alliance Boots'u satın alması
+2021: Clayton, Dubilier &amp; Rice tarafından Morrisons'ın özel sermaye fonuyla devralınması
+Kelimeler:
+• private equity takeover = özel sermaye şirketi devralması</t>
+      </text>
+    </comment>
+    <comment ref="G25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2007: Özel sermaye mülkiyet yapısı, önemli finansal yeniden yapılandırmaya, genel merkezlerin yurt dışına taşındığı kurumsal vergi düzenlemelerine ve önümüzdeki on yılda Walgreens ile nihai entegrasyona yol açtı.
+2021: Yeni sahipler, yükselen faiz oranları ortasında yüksek borç yüklerinin baskısıyla karşı karşıya kaldı; bu durum varlık satışlarına, daha sıkı operasyonel maliyet kontrollerine ve indirimli rakiplere karşı pazar payını koruma konusunda zorluklara yol açtı.
+Kelimeler:
+• restructuring = yeniden yapılandırma
+• debt burdens = borç yükleri</t>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geleneksel perakende cadde zincirlerinin özel sermaye veya varlıklı aile ofisleri tarafından büyük ölçekli satın alımları, satın alma primlerini telafi etmek için genellikle agresif borçlanma (kaldıraç) veya hızlı maliyet kesintisi girişimlerini tetikler.
+Kelimeler:
+• debt-leveraging = borç kaldıracı kullanma
+• recoup = telafi etmek / geri kazanmak</t>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni mülkiyetin, 7 milyar sterlinlik yatırımdan elde edilen getiriyi maksimize etmek için kapsamlı tedarik zinciri optimizasyonları, dijital yatırımlar ve potansiyel mağaza/mülk rasyonelleştirmeleri başlatması muhtemeldir.
+Kelimeler:
+• supply chain optimizations = tedarik zinciri optimizasyonları
+• rationalizations = rasyonelleştirmeler / akılcılaştırma</t>
+      </text>
+    </comment>
+    <comment ref="K25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 18 ay</t>
+      </text>
+    </comment>
+    <comment ref="L25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Katı bir şekilde borç ağırlıklı kaldıraçlı satın alma (LBO) modellerine güvenen geleneksel özel sermaye şirketlerinin aksine, bir milyarder aile ofisinin desteği daha uzun vadeli bir yatırım ufkuna ve daha sabırlı bir sermayeye imkan tanıyabilir.
+Kelimeler:
+• debt-laden = borç yükü altında
+• investment horizon = yatırım ufk / vadesi</t>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mağaza ayak izi optimizasyonu, kurumsal yeniden yapılandırma veya tedarik zinciri ve dijital stratejilerdeki değişikliklerle ilgili duyurular.
+Kelimeler:
+• store footprint = mağaza ağı / alanı</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Üst düzey yetkililer, Man City'nin önümüzdeki sezon Şampiyonlar Ligi'nde yer almasından endişe ediyor
+Kelimeler:
+• senior figures = üst düzey yetkililer</t>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İngiliz futbolunun içindeki üst düzey yetkililer, finansal düzenlemeleri ihlal ettikleri gerekçesiyle küme düşseler bile Manchester City'nin önümüzdeki sezon Şampiyonlar Ligi'nde oynayabileceğinden endişe ediyor.
+Kelimeler:
+• senior figures = üst düzey yetkililer
+• relegated = küme düşmüş
+• breaching = ihlal eden</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+finansal düzenleme ve küme düşme açığı
+Kelimeler:
+• loophole = yasal boşluk / açık</t>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: Calciopoli skandalı
+2023: Everton'ın finansal ihlaller nedeniyle puan silme cezası</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: Juventus, Serie A'ya hemen geri dönmeden önce Serie B'de yalnızca bir sezon geçirdi ve iki yıl içinde derhal Avrupa kupalarına katılmaya hak kazandı.
+2023: Ağır sportif yaptırıma rağmen Everton, Sean Dyche yönetimindeki iyi bir form grafiğiyle sahada küme düşmekten başarıyla kurtuldu ve küme düşmekten tamamen kaçındı.
+Kelimeler:
+• sanction = yaptırım</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Elit kulüpler ağır düzenleyici veya sportif yaptırımlarla karşılaştığında, karmaşık yasal çerçeveler ve devasa ticari nüfuz tipik olarak felaket niteliğindeki yapısal dışlanmayı önler; ancak ara sıra sportif küme düşme gerçekleşmiştir.
+Kelimeler:
+• sanction = yaptırım
+• leverage = nüfuz / güç</t>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, her türlü ağır sportif yaptırıma karşı muhtemelen uzun süren yasal mücadelelerle direnecek ve hukuki süreçler uzarken onları acil bir Avrupa dışı kalma durumundan uzak tutacaktır.
+Kelimeler:
+• sanction = yaptırım</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+115 suçlamanın boyutu ve yerel ile UEFA kural kitapları arasındaki doğrudan koordinasyon, hukuki olarak keşfedilmemiş bir alan yaratıyor.</t>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+UEFA hukuk ekiplerinden yerel ligden küme düşme geçiş kurallarına ilişkin açıklamalar.</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ronaldo Portekiz'den 'ceza' istiyor ancak milli takımı bırakmıyor
+Kelimeler:
+• retiring = emekli olmak / bırakmak</t>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Cristiano Ronaldo, uluslararası futbolu bırakmadığını ancak teknik direktör Jorge Jesus'un kendisine verdiği sözü tutmamasının ardından Portekiz kampını terk ettiği için cezalandırılmayı hak ettiğini söylüyor.
+Kelimeler:
+• retiring = emekli olmak / bırakmak
+• walking out = terkedip gitmek
+• broke his word = sözünü tutmadı</t>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+futbolcu teknik direktör anlaşmazlığı
+Kelimeler:
+• fallout = anlaşmazlık / kavga</t>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Fransa millî takımının 2010 Dünya Kupası boykotu
+2022: Cristiano Ronaldo'nun Manchester United'dan ayrılışı</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Fransa turnuvadan grup aşamasında elendi ve hemen ardından teknik heyette ve yaşlı oyuncularda büyük bir tasfiye yaşandı.
+2022: Ardından gelen patlayıcı nitelikteki izinsiz röportajın ardından sözleşmesi haftalar içinde karşılıklı olarak feshedildi ve Suudi Arabistan'a transferine yol açtı.</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaşlanan megastarları içeren halka açık futbolcu-teknik direktör anlaşmazlıkları nadiren iç uzlaşmayla çözülür; tipik olarak teknik direktörün takım uyumunu korumak için geri adım atmasıyla ya da oyuncunun kadrodan tamamen çıkarılmasıyla sonuçlanır.
+Kelimeler:
+• fallout = anlaşmazlık / kavga
+• phased out = aşama aşama kadrodan çıkarılmak</t>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Jorge Jesus ve Portekiz federasyonu, büyük turnuvalar öncesinde onu sessizce yeniden kadroya dahil etmeden veya kadrodan aşamalı olarak çıkarmadan önce muhtemelen geçici bir disiplin cezası süreci yürütecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ronaldo'nun dokunulmaz bir ulusal ikon olarak tarihi statüsü, sıradan kadro üyelerine kıyasla ona benzersiz bir nüfuz kazandırıyor.
+Kelimeler:
+• untouchable = dokunulmaz</t>
+      </text>
+    </comment>
+    <comment ref="N27" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Portekiz'in önümüzdeki maçları için kadro seçim duyuruları.</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tropikal Fırtına Isaias'ın 2026'nın ilk Atlantik kasırgası olması bekleniyor
+Kelimeler:
+• forecast = tahmin etmek / tahmin</t>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+El Niño koşullarının tetiklediği Atlantik kasırga sezonunun olağandışı sakin başlangıcı, Tropikal Fırtına Isaias'ın güney ABD'yi etkilemek üzere kasırga statüsüne doğru güçlenmesiyle sona eriyor.
+Kelimeler:
+• strengthens = güçleniyor</t>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kasırga oluşumu</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1992: Andrew Kasırgası
+2005: Katrina Kasırgası</t>
+      </text>
+    </comment>
+    <comment ref="G28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1992: ABD genelinde aylar içinde 27 milyar dolarlık hasara yol açtı ve bina yönetmelikleri ile acil durum yönetiminde kapsamlı köklü değişiklikleri tetikledi.
+2005: New Orleans'ta yaygın sedye (set) arızaları, felaket niteliğinde su baskınlarına, uzun süreli yerinden edilmelere ve sonraki yıllarda devasa federal afet müdahale reformuna yol açtı.
+Kelimeler:
+• sweeping overhauls = kapsamlı köklü değişiklikler</t>
+      </text>
+    </comment>
+    <comment ref="H28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+El Niño nedeniyle baskılanan tarihsel sezonlarda, elverişli tropikal dalgaların nihai ortaya çıkışı, biriken okyanus ısısı boşaldıkça genellikle yoğun ve ani başlayan kasırgalara yol açar.
+Kelimeler:
+• rapid-onset = ani başlayan</t>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ilık kıyı sularına ulaşıldığında hızlı şiddetlenme, güney ABD kıyı şeridi için şiddetli rüzgar ve sel hasarı tehlikesi oluşturmaktadır.
+Kelimeler:
+• intensification = şiddetlenme</t>
+      </text>
+    </comment>
+    <comment ref="K28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 1-2 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gelişmiş uydu izleme ve sayısal hava tahmin modelleri, geçmiş on yıllara göre çok daha erken tahliye uyarılarına imkan tanımaktadır.</t>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fırtına ılık Körfez veya Atlantik akıntilerine yaklaşırken hızlı basınç düşüşleri ve rüzgar kesmesi (shear) azalmaları.
+Kelimeler:
+• wind shear = rüzgar kesmesi</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaşamın asimetrisi gizemini çözenlere Kimya Nobel Ödülü verildi
+Kelimeler:
+• asymmetry = asimetri</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 Nobel Kimya Ödülü, biyolojik homokiral asimetri gizemini başarıyla çözen Fransız ve Japon bilim insanlarına verildi.
+Kelimeler:
+• asymmetry = asimetri</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nobel Ödülü duyurusu</t>
+      </text>
+    </comment>
+    <comment ref="F29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1953: DNA yapısının keşfi
+1996: Katalitik RNA'nın keşfi</t>
+      </text>
+    </comment>
+    <comment ref="G29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1953: Bir onlar yıl içinde biyoteknoloji endüstrisini, modern eczacılığı ve genetik mühendisliğini tetikleyerek biyolojik bilimi kökten değiştirdi.
+1996: Sonraki 10 ila 20 yıl içinde RNA bazlı tedaviler ve sentetik biyoloji araştırmalarını hızlandırdı.</t>
+      </text>
+    </comment>
+    <comment ref="H29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Temel moleküler kökenlerdeki büyük Nobel ödüllü çığırlar, tipik olarak hedefe yönelik ilaç geliştirmede, sentetik biyoloji uygulamalarında ve biyomoleküllerin yapay sentezinde 5 ila 10 yıllık bir artışı tetikler.
+Kelimeler:
+• breakthroughs = çığır açan gelişmeler
+• surge = ani artış</t>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hedefe yönelik ilaç dağıtımı ve farmakoloji için kiral molekülleri manipüle etmeyi amaçlayan hibe fonlarında ve ticari biyoteknoloji yatırımlarında belirgin bir artış.
+Kelimeler:
+• grant funding = hibe finansmanı
+• manipulating = manipüle etme, yönlendirerek işleme</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern yapay zeka destekli protein ve moleküler katlanma modelleri (gelişmiş AlphaFold varyantları gibi), bu bulguları tarihsel emsallerine göre çok daha hızlı bir şekilde ticarileştirecek ve uygulayacaktır.
+Kelimeler:
+• variants = varyantlar, türler</t>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İlaç yan etkilerini azaltmak için kiral asimetriden yararlanan yeni eczacılık patentleri.
+Kelimeler:
+• asymmetry = asimetri</t>
       </text>
     </comment>
   </commentList>
@@ -1880,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3172,6 +4317,1196 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>She got Trump's $500 check for health insurance. To her, it's a 'political stunt'</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>As direct health cost subsidy checks from President Trump hit millions of mailboxes four weeks before the midterms, polls show voters view them as political maneuvers rather than trust-builders on healthcare.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>stimulus checks</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2020: Trump administration sending coronavirus stimulus checks with the president's name printed on them
+2006: Bush administration sending out tax relief checks ahead of midterm elections</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2020: Despite the direct cash injection, it did not prevent his defeat in November 2020, though it briefly boosted economic sentiment.
+2006: The incumbent party suffered a 'thumping' in the midterms anyway, losing control of both the House and Senate due to broader discontent over the Iraq War and the economy.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Last-minute financial distributions from the executive branch rarely override overarching voter dissatisfaction with national direction or specific policy distrust (like healthcare). In nearly all midterms featuring an unpopular incumbent, financial stunts fail to shift the structural legislative outcome.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>The checks will provide a temporary headline distraction, but will fail to alter the broader anti-administration wave heading into the November midterms.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Next 4 weeks</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Targeting specific health insurance costs directly touches an acute household pain point compared to broader macroeconomic checks.</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Movement in late-deciding voter polling regarding trust in healthcare management.</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/07/nx-s1-5991687/trump-medicare-aca-payments-midterms</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/CARES_Act
+https://en.wikipedia.org/wiki/Economic_Growth_and_Tax_Relief_Reconciliation_Act_of_2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>The Republican candidates walking a Trump tightrope</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Republican candidates running in the November midterms are struggling to navigate an unpopular president who continues to dominate their party's base.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>midterm elections</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2018: Republican midterm elections under President Donald Trump
+2006: Republican midterms under President George W. Bush</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2018: Democrats won a 'blue wave' pickup of 41 seats in the House of Representatives.
+2006: Democrats retook both chambers of Congress in a decisive wave election.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>When the sitting president's party faces a midterm headwind, candidates who try to balance the base and swing voters typically suffer from suppressed enthusiasm on one side and alienation on the other. Base-rate history shows the out-party almost always makes significant gains.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>A substantial portion of these tightrope-walking candidates will lose tight races as moderate voters break toward the opposition.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Next 4 weeks</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Deeply entrenched partisan polarization means fewer true swing voters exist, making district-level candidate quality and local issues more decisive than past wave years.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Late campaign spending shifts and presidential rally schedules in competitive districts.</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cm93z74e0n9zo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_United_States_elections
+https://en.wikipedia.org/wiki/2006_United_States_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Boston’s Big Bet On Battery-Powered Trains</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Boston and local transit authorities are making a significant capital investment into battery-powered commuter trains to reduce emissions and upgrade aging infrastructure without complete electrification.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>transit electrification bet</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2019: Long Island Rail Road Battery Train Initiative
+2022: Caltrain Electrification Delays</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2019: Projects faced substantial delays, battery weight issues, and range limitations, forcing transit planners to temper expectations within 3 years.
+2022: Costs escalated significantly and completion dates slipped by multiple years, though testing eventually stabilized.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 70% of early-stage alternative propulsion rollouts on legacy heavy rail, agencies encounter multi-year delays and cost overruns due to weight, charging infrastructure, and cold-weather battery degradation.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Expect initial rollout friction, schedule pushes, and public debate over battery efficiency during harsh Boston winters.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>next 2-4 years</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Advances in solid-state chemistry and modular charging stations could reduce historical weight penalties.</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Pilot test results during sub-zero winter temperatures and capital budget adjustments.</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQUGhCRGx0SWlHOEhtbzFWc2ZpSmQ5Zm5CQ3Zmc2xoaXF1OE92Q01ya3ZnYTE2aE9NYngxM3Y5ZlZmSGZpdUZHRUxzRWlmbi1uaGRDMDROX3NTajJxQWs2SnUyNGNYeWo2ZjVCUlR2Y1BVX05VQXRqcUM1NDBfenFac3dVekJyRzZx?oc=5</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Long_Island_Rail_Road
+https://en.wikipedia.org/wiki/Caltrain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>More than 600,000 mail-in ballots headed to Massachusetts voters</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Election authorities in Massachusetts are dispatching over 600,000 mail-in ballots to voters ahead of upcoming elections, signaling high reliance on vote-by-mail infrastructure.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>mass mail-in voting</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2020: COVID-19 Pandemic Mail-In Voting Expansion in Massachusetts
+2022: Massachusetts Midterm Mail-In Voting</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2020: While overall participation surged, processing times stretched local election boards, and a small percentage of late-arriving ballots were disqualified.
+2022: Election nights took longer to finalize complete tallies due to the time required to cure and process mail-in signatures.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>When mail-in ballot volumes exceed half a million in Massachusetts, final election outcome certifications are consistently delayed by 24 to 72 hours as clerks process signature verifications.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Expect smooth distribution but prolonged tabulation timelines on election night, with urban centers taking longer to report final totals.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>upcoming election cycle</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Local election offices have streamlined tracking software and experience compared to the emergency rollouts of 2020.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Percentage of ballots challenged for signature mismatches or late arrivals.</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNalMwSnprWERCaGt6NzkzMEFkaV9ZMXBrQjB2clRlZHhWQ3BzWTVRVjdTVS1WNkNNMjVaODJCbENCNkVaR3MwMmhyamRfdGV1d2tpMEJWMUZfa0pZd2QwU0EzWFZadmJJWDdUZThWSnZUYzBOV2JvaUVQZ2lrdXM3Yno1RjBKSGxESHFIMDZqU1Z4SkxrRWV2TzRDRTZ3bTdmWUxvVzdwSWJfR0FIaXN0czFXVlBTMHNnMXlhcm5fNVl4X0pzR3RDcE1LbFc?oc=5</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2020_United_States_presidential_election_in_Massachusetts
+https://en.wikipedia.org/wiki/2022_Massachusetts_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>France halts use of stun grenades after boy's hand blown off in student protests</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>France has temporarily halted the use of specific police stun grenades during student protests after a teenager suffered catastrophic injuries, following widespread public outcry over disproportionate force.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>police brutality and protest bans</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2014: Death of Rémi Fraisse
+2018-2019: Yellow vests movement police violence controversies</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2014: The French government temporarily suspended the specific type of offensive grenade used (GLI-F4), but protests intensified nationwide, leading to long-term legal battles and heightened tensions between police and activists.
+2018-2019: Despite domestic and international condemnation, the government defended the tactical necessity of the weapons while facing repeated court challenges and permanent pressure to ban specific munitions.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>In historical cases of severe injury caused by French police munitions during protests, the government reacts with temporary suspensions or bans of specific equipment to defuse immediate outrage, but structural friction over policing tactics routinely persists.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>The temporary halt on stun grenades will likely become permanent, but student and activist groups will pivot to broader demands for sweeping police reform and accountability.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>The graphic nature of a teenager losing a hand has united diverse political factions in condemning specific riot control gear faster than usual.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Official investigative reports into the officer's actions and potential broader legislative restrictions on kinetic impact projectiles.</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cqzjx7z2r4gko?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Killing_of_R%C3%A9mi_Fraisse
+https://en.wikipedia.org/wiki/Yellow_vests_protests</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Germany’s Merz vows to fight ‘extremism’ after AfD, far-left election gains</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>German Chancellor Friedrich Merz has vowed a fierce fight against political extremism following significant electoral gains by both the far-right Alternative for Germany (AfD) and far-left parties, amidst a sinking approval rating.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>rise of far-right and political polarization</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2015-2018: Rise of the Alternative for Germany
+1930s: Weimar Republic political polarization</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2015-2018: Established centrist parties adopted tougher rhetoric and policy stances on immigration and security, yet the AfD continued to consolidate its electorate base, particularly in eastern Germany.
+1930s: Traditional democratic parties struggled to form stable coalitions, progressively eroding democratic norms and parliamentary governance.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>When mainstream German leaders face surging anti-establishment parties alongside declining personal approval, they typically respond by tightening security and anti-extremism rhetoric, but this rarely halts the momentum of populist movements without addressing underlying economic or social grievances.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Mainstream parties will harden their policy platforms and attempt defensive coalitions, while political polarization in regional legislatures deepens.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Unlike past decades, the far-right is now firmly entrenched as a permanent structural fixture of the political landscape rather than a transient protest vote.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Regional coalition-building struggles and shifts in national immigration or economic policy designed to appease disaffected voters.</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aljazeera.com/news/2026/10/7/germanys-merz-vows-to-fight-extremism-after-afd-far-left-election-gains?traffic_source=rss</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Alternative_for_Germany
+https://en.wikipedia.org/wiki/Weimar_Republic</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Trade Deficit Hits 17-Month High Despite Trump’s Tariffs</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. trade deficit expanded to $105.6 billion, its widest level in 17 months, as imports surged despite newly enacted tariffs.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>tariffs and trade wars</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2018-2019: Trump administration tariffs
+1930: Smoot-Hawley Tariff Act</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2018-2019: Rather than shrinking, the overall U.S. goods trade deficit hit a record high of $891 billion in 2018 as importers rushed to beat tariff deadlines and supply chains rerouted.
+1930: Trading partners retaliated sharply, international trade plummeted by over 60%, and the global economic depression deepened severely within two years.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>In nearly all historical instances of broad unilateral tariffs (such as 2018 and 1930), imports initially surge as companies front-run duties, causing the short-term trade deficit to widen rather than narrow.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>The trade deficit is likely to remain elevated or continue hitting highs in the coming months as front-loading persists, before domestic demand adjustments take over.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>next 3-6 months</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>The sheer breadth of the new tariff schedules covers virtually all trading partners simultaneously, potentially altering global supply chain relocation speeds.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Monthly import volume changes and inventory accumulation reports from major retailers.</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/06/business/economy/us-trade-deficit.html</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tariffs_in_the_Trump_administration
+https://en.wikipedia.org/wiki/Smoot%E2%80%93Hawley_Tariff_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Inflation fears on the rise as one-year outlook in Fed survey hits highest level since May 2023</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>The New York Fed's Survey of Consumer Expectations showed the median one-year inflation outlook rising to 3.9%, the highest mark since mid-2023.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>inflation expectations</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2021-2022: Inflation surge of 2021–2023
+1973-1974: 1973 oil crisis</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2021-2022: Headline inflation peaked near 9.1% in mid-2022, forcing the Fed to raise interest rates to a 22-year high of 5.25%-5.50% over the subsequent 18 months.
+1973-1974: Inflation became entrenched in wage-price spirals, leading to a severe stagflationary recession that required Paul Volcker's drastic rate hikes years later.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>When consumer inflation expectations break upward out of a stable band, central banks typically feel compelled to maintain higher interest rates longer or resume tightening to prevent unanchoring.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve will likely pause any planned rate cuts and adopt a much more hawkish posture to signal commitment to price stability.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets and productivity metrics driven by AI adoption currently show more resilience than during historical stagflation periods.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Upcoming Consumer Price Index (CPI) reports and upcoming Federal Open Market Committee (FOMC) meeting statements.</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/07/inflation-fears-on-the-rise-as-one-year-outlook-in-fed-survey-hits-highest-since-may-2023.html</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge
+https://en.wikipedia.org/wiki/1973_oil_crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Paramount takes over Warner Bros in $110bn Hollywood merger</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Paramount has acquired Warner Bros in a massive $110bn mega-merger, combining two of Hollywood's biggest film and television studios despite regulatory and competition concerns.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>merger</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2018: AT&amp;T's acquisition of Time Warner
+2000: AOL Time Warner merger</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2018: The combined entity struggled with massive debt, strategic misalignments, and cultural clashes, ultimately leading AT&amp;T to spin off WarnerMedia to merge with Discovery just three years later in 2022.
+2000: It became known as one of the worst corporate mergers in history, resulting in a record $99 billion loss in 2002 and eventual corporate decoupling as synergies failed to materialize.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>In approximately 70% of mega-scale media and studio mergers, anticipated cost synergies and strategic dominance are undermined by culture clashes, heavy debt loads, and shifting market dynamics, leading to subsequent restructuring or divestment within 3 to 5 years.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>The newly merged Paramount-Warner Bros will face severe operational strain, heavy debt servicing burdens, and pressure to slash overhead, likely resulting in major asset sell-offs, extensive layoffs, and strategic pivoting within a few years.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>next 3 years</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>The streaming-dominated landscape forces immediate consolidation for survival against tech giants, potentially driving more aggressive cost-cutting than past analog-to-digital era mergers.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Early executive departures, unexpected debt write-downs, and major structural reorganizations or staff layoffs within the studio divisions.</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cxj0604d33qzo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Acquisition_of_Time_Warner_by_AT%26T
+https://en.wikipedia.org/wiki/WarnerMedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Boots sold in £7bn deal to Canadian billionaire family</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>High Street pharmacy chain Boots has been sold in a £7 billion deal to a Canadian billionaire family, shifting ownership of the iconic British retailer.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>corporate buyout</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2007: Kohlberg Kravis Roberts buyout of Alliance Boots
+2021: Morrisons private equity takeover by Clayton, Dubilier &amp; Rice</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2007: The private equity ownership structure led to significant financial restructuring, corporate tax re-arrangements moving headquarters abroad, and eventual integration into Walgreens over the following decade.
+2021: The new owners faced pressure from high debt burdens amid rising interest rates, leading to asset sales, tighter operational cost controls, and challenges in maintaining market share against discount competitors.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Large-scale acquisitions of traditional retail high-street chains by private capital or wealthy family offices frequently trigger aggressive debt-leveraging or rapid cost-cutting initiatives to recoup purchase premiums.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>The new ownership is likely to launch comprehensive supply chain optimizations, digital investments, and potential estate rationalizations to maximize the return on the £7 billion investment.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>next 18 months</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Unlike traditional private equity firms relying strictly on debt-laden LBO models, backing from a billionaire family office may afford a longer-term investment horizon and more patient capital.</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Announcements regarding store footprint optimization, corporate restructuring, or changes in supply chain and digital strategies.</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cwly0jyk2vl5o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Alliance_Boots
+https://en.wikipedia.org/wiki/Morrisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Senior figures worried about Man City being in next season's Champions League</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Senior figures within the English game are concerned that Manchester City could play in the Champions League next season even if they are relegated for breaching financial regulations.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>financial regulation and relegation loophole</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2006: Calciopoli scandal
+2023: Everton points deduction for financial breaches</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2006: Juventus spent only one season in Serie B before bouncing straight back to Serie A, immediately securing European qualification within two years.
+2023: Despite the severe sporting sanction, Everton successfully fought off relegation on the pitch through a strong run of form under Sean Dyche, avoiding the drop entirely.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>When elite clubs face severe regulatory or sporting sanctions, complex legal frameworks and massive commercial leverage typically prevent catastrophic structural exclusion, though sporting relegation has occasionally occurred.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City will likely fight any severe sporting sanction through prolonged legal challenges, keeping them clear of immediate European exclusion while legal battles drag on.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>The sheer scale of the 115 charges and direct coordination between domestic and UEFA rulebooks creates a legally uncharted territory.</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Statements from UEFA legal teams regarding domestic relegation crossover rules.</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c9p8gxgm71zzo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Calciopoli
+https://en.wikipedia.org/wiki/2023%E2%80%9324_Everton_F.C._season</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldo wants Portugal 'punishment' but not retiring</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo says he is not retiring from international football but deserves to be punished for walking out on Portugal after head coach Jorge Jesus broke his word to him.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>player manager fallout</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2010: France national team 2010 World Cup strike
+2022: Cristiano Ronaldo Manchester United exit</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2010: France crashed out of the tournament in the group stage, and a massive clear-out of the coaching staff and senior players followed immediately afterwards.
+2022: After a subsequent explosive unauthorized interview, his contract was mutually terminated within weeks, leading to his move to Saudi Arabia.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Public player-manager fallouts involving aging megastars rarely resolve through internal compromise; they typically result in either the manager backing down to protect team harmony or the player being phased out of the squad entirely.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Jesus and the Portuguese federation will likely navigate a temporary disciplinary suspension before quietly reintegrating or phasing him out ahead of major tournaments.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Ronaldo's historical status as an untouchable national icon gives him unique leverage compared to standard squad members.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Squad selection announcements for Portugal's upcoming fixtures.</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cmd7qn48q13lo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2010_FIFA_World_Cup_Group_A
+https://en.wikipedia.org/wiki/Cristiano_Ronaldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Tropical Storm Isaias forecast to become first Atlantic hurricane of 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>An unusually quiet start to the Atlantic hurricane season, driven by El Niño conditions, is coming to an end as Tropical Storm Isaias strengthens toward hurricane status to impact the southern USA.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>hurricane formation</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1992: Hurricane Andrew
+2005: Hurricane Katrina</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1992: It caused $27 billion in damage and prompted sweeping overhauls of building codes and emergency management across the United States within months.
+2005: Widespread levee failures in New Orleans led to catastrophic flooding, prolonged displacement, and massive federal disaster response reform over the subsequent years.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>In historical seasons suppressed by El Niño, the eventual emergence of favorable tropical waves often leads to intense, rapid-onset hurricanes as stored ocean heat discharges.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Rapid intensification upon reaching warm coastal waters, posing a severe threat of wind and flood damage to the southern US coastline.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>next 1-2 weeks</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Advanced satellite monitoring and numerical weather prediction models allow for much earlier evacuation warnings than in past decades.</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Rapid pressure drops and wind shear reductions as the storm approaches warm Gulf or Atlantic currents.</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/weather/articles/cw146l6pnvx0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hurricane_Andrew
+https://en.wikipedia.org/wiki/Hurricane_Katrina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Chemistry Nobel awarded for solving mystery of life's asymmetry</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>The 2026 Nobel Prize in Chemistry has been awarded to French and Japanese scientists for successfully solving the mystery of biological homochiral asymmetry.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Nobel Prize announcement</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1953: Discovery of the structure of DNA
+1996: Discovery of catalytic RNA</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1953: Within a decade, it sparked the biotechnology industry, modern pharmaceuticals, and genetic engineering, fundamentally altering biological science.
+1996: Accelerated research into RNA-based therapies and synthetic biology over the following 10 to 20 years.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Major Nobel-winning breakthroughs in fundamental molecular origins typically trigger a 5-to-10-year surge in targeted pharmaceutical development, synthetic biology applications, and artificial synthesis of biomolecules.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>A significant increase in grant funding and commercial biotech investment aimed at manipulating chiral molecules for targeted drug delivery and pharmacology.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Modern AI-driven protein and molecular folding models (such as advanced AlphaFold variants) will commercialize and apply these findings much faster than historical precedents.</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>New pharmaceutical patents utilizing chiral asymmetry to reduce drug side effects.</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c6ly038jg0d4o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Molecular_Structure_of_Nucleic_Acids%3A_A_Structure_for_Deoxyribose_Nucleic_Acid
+https://en.wikipedia.org/wiki/Nobel_Prize_in_Chemistry</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -2730,6 +2730,1101 @@
 İlaç yan etkilerini azaltmak için kiral asimetriden yararlanan yeni eczacılık patentleri.
 Kelimeler:
 • asymmetry = asimetri</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, İkinci Dünya Savaşı'ndan bu yana ordunun ilk idam mangasıyla infazını onayladı. Neden şimdi?
+Kelimeler:
+• firing squad = idam mangası</t>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pentagon, Tennessee'de başarısızlıkla sonuçlanan ve idam cezası yöntemine ilişkin tartışmaları yeniden alevlendiren zehirli iğne uygulamasının ardından Nidal Hasan'ın Aralık ayında askeri idam mangası tarafından idam edileceğini açıkladı.
+Kelimeler:
+• firing squad = idam mangası
+• botched = yüzüne gözüne bulaşmış, başarısız
+• lethal injection = zehirli iğne
+• capital punishment = idam cezası</t>
+      </text>
+    </comment>
+    <comment ref="E30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+infaz yöntemi değişikliği</t>
+      </text>
+    </comment>
+    <comment ref="F30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Ronnie Lee Gardner'ın idamı
+1945: Eddie Slovik'in idamı</t>
+      </text>
+    </comment>
+    <comment ref="G30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: İnfaz, yasal bir aksama olmaksızın sorunsuz bir şekilde gerçekleşti, ancak Sekizinci Değişiklik'in zalimane ve alışılmadık ceza iddiaları üzerindeki yoğun medya incelemesi ve yasal itirazlar nedeniyle idam mangalarına yönelik daha geniş ulusal bir geri dönüşü tetiklemekte başarısız oldu.
+1945: Sıkı uygulamanın caydırıcı savaş zamanı amacı geçici olarak hizmet gördü, ancak komutanları neredeyse bir yüzyıl boyunca idam mangalarına tekrar yetki vermekten alıkoyan kalıcı bir damgalanma yarattı.
+Kelimeler:
+• firing squad = idam mangası
+• cruel and unusual punishment = zalimane ve alışılmadık ceza</t>
+      </text>
+    </comment>
+    <comment ref="H30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geleneksel infaz yöntemleri başarısız olduğunda veya yasal çıkmaza girdiğinde, hükümetler ara sıra idam mangası gibi alternatif, oldukça görünür yöntemlere yönelmektedir; ancak 3 modern örnekten 2'sinde bu durum, uygulamayı geciktiren ani ve uzun süren anayasal davaları tetiklemektedir.
+Kelimeler:
+• firing squad = idam mangası</t>
+      </text>
+    </comment>
+    <comment ref="I30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Planlanan idam mangası infazı, zalimane ve alışılmadık cezalara ilişkin kapsamlı yasal itirazlarla karşı karşıya kalacak ve bu durum muhtemelen nihai bir çözümden önce geçici bir yargı durdurma kararıyla sonuçlanacaktır.
+Kelimeler:
+• firing squad = idam mangası
+• cruel and unusual punishment = zalimane ve alışılmadık ceza
+• judicial stay = yargısal durdurma kararı</t>
+      </text>
+    </comment>
+    <comment ref="K30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ay</t>
+      </text>
+    </comment>
+    <comment ref="L30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bu durum, sivil bir eyalet mahkemesinden ziyade, tarihi olarak federal yetkililere daha fazla saygı gösteren farklı Askeri Adalet Tekdüzen Kanunu kuralları altında faaliyet gösteren askeri bir mahkemeyi içermektedir.</t>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal bölge mahkemesinde veya Silahlı Kuvvetler Temyiz Mahkemesinde acil savunma dilekçelerinin verilmesi.</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kripto ve tahmin piyasaları genişledikçe düzenleyicileri küçülüyor</t>
+      </text>
+    </comment>
+    <comment ref="D31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Emtia Vadeli İşlemler Ticaret Komisyonu (CFTC), kripto ve tahmin piyasaları üzerindeki düzenleyici yetki alanında devasa bir genişlemeyle karşı karşıya kalmasına rağmen, ikinci Trump yönetimi sırasında personel sayısı ve yaptırım eylemleri keskin bir şekilde düştü.
+Kelimeler:
+• regulatory remit = düzenleyici yetki alanı
+• precipitously = sarp bir şekilde, keskin bir şekilde</t>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+düzenleyici gerileme</t>
+      </text>
+    </comment>
+    <comment ref="F31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017-2018: İlk Trump yönetimi altında kuralsızlaştırma ve personel kesintileri
+2000: 2000 Tarihli Emtika Vadeli İşlemler Modernizasyon Yasası
+Kelimeler:
+• deregulation = kuralsızlaştırma, denetimleri kaldırma</t>
+      </text>
+    </comment>
+    <comment ref="G31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017-2018: Düzenlemeye tabi kuruluşlar uyum maliyetlerinden hemen kurtulurken, birkaç sektör nihayetinde 24 ay içinde acil geriye dönük müdahaleler gerektiren piyasa manipülasyonu skandalları ve sistemik şoklar yaşadı.
+2000: Denetim eksikliği, sekiz yıl sonra 2008 küresel finans krizini körükleyen karmaşık finansal enstrümanların şeffaf olmamasına doğrudan katkıda bulundu.
+Kelimeler:
+• compliance costs = uyum maliyetleri
+• opacity = şeffaf olmama, karanlıkta kalma</t>
+      </text>
+    </comment>
+    <comment ref="H31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Finansal düzenleyicilerin hızlı varlık inovasyonu dönemlerinde kasıtlı küçülmeyle karşılaştığı 5 tarihi vakanın 4'ünde, piyasa manipülasyonu önemli ölçüde arttı ve sonunda agresif yaptırıma gecikmiş bir dönüşü zorladı.</t>
+      </text>
+    </comment>
+    <comment ref="I31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tahmin piyasaları ve kripto platformları, dikkat çekici yüksek profilli dolandırıcılık vakalarının eşlik ettiği spekülatif bir hacim artışı yaşayacak, bu da sonunda kamuoyunun tepkisini ve acil Kongre müdahalesi çağrılarını tetikleyecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Merkeziyetsiz uygulamalar ve modern tahmin platformları aracılığıyla perakende katılımının saf hızı, tarihi türev piyasalarını geride bırakmakta ve kuralsızlaştırmadan piyasa çöküşüne giden zaman çizelgesini potansiyel olarak hızlandırmaktadır.
+Kelimeler:
+• deregulation = kuralsızlaştırma, denetimleri kaldırma</t>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Düzenlenmemiş tahmin piyasalarında büyük likidite krizleri veya içeriden öğrenenlerin ticareti skandalları.
+Kelimeler:
+• liquidity crunch = likidite krizi</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Süresiz grev yaklaşırken Brigham hemşireleri ve hastane yönetimi bir araya geliyor
+Kelimeler:
+• open-ended strike = süresiz grev
+• looms = kapıda, yaklaşmakta</t>
+      </text>
+    </comment>
+    <comment ref="D32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham and Women's Hospital yönetimi ve binlerce hemşireyi temsil eden sendika müzakerecileri, süresiz grev tehdidi yaklaşırken son çare olarak sözleşme pazarlığı için toplanıyor. Anlaşmazlık personel oranları, ücretler ve iş yeri güvenliği etrafında dönüyor.
+Kelimeler:
+• last-ditch = son çare, son an
+• staffing ratios = personel oranları</t>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+grev tehdidi
+Kelimeler:
+• labor strike threat = işçi grevi tehdidi</t>
+      </text>
+    </comment>
+    <comment ref="F32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2016: Brigham and Women's Hospital Grev Bildirimi
+Temmuz 2017: Tufts Medical Center Hemşireler Grevi
+Mart 2021 – Ocak 2022: Saint Vincent Hastanesi Hemşireler Grevi</t>
+      </text>
+    </comment>
+    <comment ref="G32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2016: Eylemin başlamasına yaklaşık 16 saat kala 22 saatlik maraton federal arabuluculuk oturumunda geçici bir anlaşmaya varılmasının ardından grev önlendi.
+Temmuz 2017: Hastane operasyonları yedek personel nedeniyle ciddi şekilde aksadı ve beş süren çekişmeli geçici görüşmelerin ardından Aralık 2017'de bir anlaşma onaylandı.
+Mart 2021 – Ocak 2022: Grev 301 gün sürdü — Massachusetts tarihindeki en uzun hemşireler grevi — federal yetkililerin aracılık ettiği arabuluculuk yoluyla varılan uzlaşmayla sona ermeden önce onlarca milyon dolara mal oldu.
+Kelimeler:
+• averted = önlenen, atlatılan
+• contentious = çekişmeli, tartışmalı
+• ratified = onaylanan, yürürlüğe konan
+• brokered = aracılık edilen</t>
+      </text>
+    </comment>
+    <comment ref="H32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'teki sağlık sendikalarının grev yetkilendirmeleri ağırlıklı olarak son dakikada pazarlık kozu olarak işlev görür; tarihsel olarak, büyük Boston akademik tıp merkezlerindeki MNA grev bildirilerinin %80 ila %85'i uzun süreli grevler yerine uçurumun kenarından dönüş uzlaşmalarıyla sonuçlanır.
+Kelimeler:
+• eleventh-hour = son dakika
+• bargaining leverage = pazarlık kozu / gücü</t>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İki tarafın son dakikada anlaşmaya varması veya son tarihten sonraki 24 ila 48 saat içinde kesintisiz arabuluculuk konusunda anlaşarak uzun süreli ve süresiz bir iş bırakma eylemini kıl payı önlemesi muhtemeldir.
+Kelimeler:
+• narrowly averting = kıl payı önlemek
+• walkout = iş bırakma eylemi, grev</t>
+      </text>
+    </comment>
+    <comment ref="K32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 7 gün</t>
+      </text>
+    </comment>
+    <comment ref="L32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pandemi sonrası hemşire tükenmişliği ve ülke çapındaki hastane kâr marjı sıkışmaları her iki taraftaki tutumları sertleştirdi ve Mass General Brigham, 2016'ya kıyasla esnekliği azaltan sistem çapında personel maliyeti baskılarıyla karşı karşıya.
+Kelimeler:
+• burnout = tükenmişlik
+• margin compressions = kâr marjı daralmaları/sıkışmaları</t>
+      </text>
+    </comment>
+    <comment ref="N32" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal arabulucuların görüşmelere katılması, Brigham'ın elektif ameliyatları iptal etmeye başlayıp başlamadığı ve seyahat eden yedek hemşire sözleşmeleriyle ilgili kesin lojistik duyuruları.
+Kelimeler:
+• elective surgeries = isteğe bağlı / planlı ameliyatlar</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Biyoteknik sektöründeki gerilemeyle birlikte Boston'un yaşam bilimleri laboratuvar alanının üçte biri boş duruyor
+Kelimeler:
+• sits vacant = boş duruyor
+• pullback = geri çekilme, yavaşlama</t>
+      </text>
+    </comment>
+    <comment ref="D33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük Boston bölgesindeki yaşam bilimleri ticari laboratuvar boşluk oranı, agresif spekülatif geliştirme ve biyoteknoloji risk sermayesi finansmanındaki düşüşün ardından neredeyse %30'a tırmandı. Geliştiriciler ve mülk sahipleri artık boş durumdaki son teknoloji tesisler üzerinde borç yapılandırmalarıyla karşı karşıya.
+Kelimeler:
+• speculative development = spekülatif yapılaşma/geliştirme
+• state-of-the-art = son teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ticari gayrimenkul çöküşü
+Kelimeler:
+• commercial real estate bust = ticari gayrimenkul çöküşü</t>
+      </text>
+    </comment>
+    <comment ref="F33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2001-2004: Silikon Vadisi Dot-Com Gayrimenkul Kongresi
+1989-1993: Yeni İngiltere Gayrimenkul ve Bankacılık Çöküşü</t>
+      </text>
+    </comment>
+    <comment ref="G33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2001-2004: Ticari kiralar %40-50 oranında çöktü, mülk sahipleri büyük kiracı iyileştirme sübvansiyonları sundu ve fazla metrekareleri tarihsel taban seviyelerine geri emmek 5 ila 7 yıl sürdü.
+1989-1993: Yüksek boşluk oranı, Bank of New England dahil olmak üzere bölgesel banka iflaslarını tetikledi; bunu, temizlenmesi beş yıldan uzun süren ciddi borç silmeleri, icralar ve kredi yeniden yapılandırmaları izledi.
+Kelimeler:
+• tenant-improvement subsidies = kiracı iyileştirme sübvansiyonları
+• insolvencies = iflaslar, aciz durumlar
+• writedowns = değer düşüklüğü karşılığı, borç silme
+• foreclosures = icra yoluyla satış, haciz</t>
+      </text>
+    </comment>
+    <comment ref="H33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Risk sermayesi rüzgarlarıyla yönlendirilen gayrimenkul döngülerinde, ticari arz teslimleri tipik olarak talebin 2 ila 3 yıl gerisinden gelir; spekülatif boşluklar %25'i aştığında, tarihsel emilim taban oranları, yüksek kira imtiyazları ve varlık yeniden kullanımın öne çıktığı en az 4 ila 6 yıllık uzun bir toparlanmayı dikte eder.
+Kelimeler:
+• windfalls = beklenmedik büyük kazançlar
+• lag demand = talebin gerisinde kalmak
+• lease concessions = kira imtiyazları / tavizleri
+• asset repurposing = varlıkların kullanım amacını değiştirme</t>
+      </text>
+    </comment>
+    <comment ref="I33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük Boston'daki laboratuvar alanı boşluğunun 2028 yılına kadar %20'nin üzerinde yüksek kalması muhtemeldir; sorunlu varlık satışları, kredi verenlerin iyileştirme çalışmaları ve geleneksel sağlık veya eğitim alanına dönüştürmeler önümüzdeki iki yıl içinde önemli ölçüde hızlanacaktır.
+Kelimeler:
+• elevated = yüksek seviyede kalmış
+• distressed asset sales = sorunlu varlık satışları
+• lender workouts = kredi verenlerin yapılandırma/uzlaşma çalışmaları</t>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 4 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Standart ofis binalarının aksine, ıslak laboratuvarların inşası metrekare başına 1.000+ dolara mal oluyor; bu da laboratuvar dışı kullanımlara dönüşümü ekonomik olarak cezalandırıcı hale getiriyor ve kurumsal sahipleri hızlı bir şekilde yeniden amaca uygun hale getirmek yerine derin zararlarla elde tutmaya zorluyor.
+Kelimeler:
+• wet labs = ıslak laboratuvarlar (biyoloji/kimya laboratuvarları)
+• economically punitive = ekonomik açıdan cezalandırıcı/çok maliyetli</t>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bölgesel bankaların tahsili gecikmiş kredi açıklamaları, Watertown, Waltham ve Somerville gibi banliyölerdeki sorunlu varlık müzayedeleri ve federal faiz indirimi hamlelerinin biyoteknoloji halka arzlarını (IPO) yeniden alevlendirip alevlendirmeyeceği.
+Kelimeler:
+• non-performing loan disclosures = tahsili gecikmiş kredi açıklamaları
+• initial public offerings = halka arzlar</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eritre birlikleri Etiyopya'nın Tigray bölgesinin içlerine ilerliyor, sakinler BBC'ye söylüyor</t>
+      </text>
+    </comment>
+    <comment ref="D34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tigray'deki sakinler, Eritre birliklerinin bölgenin derinliklerine yeniden ilerlediğini bildiriyor; bu durum, önceki barış anlaşmalarına rağmen yeniden büyük çaplı çatışma korkularını artırıyor.
+Kelimeler:
+• renewed large-scale conflict = yeniden başlayan büyük çaplı çatışma</t>
+      </text>
+    </comment>
+    <comment ref="E34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ateşkes ihlali
+Kelimeler:
+• ceasefire violation = ateşkes ihlali</t>
+      </text>
+    </comment>
+    <comment ref="F34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Tigray Savaşı
+2018: Eritre-Etiyopya zirvesi</t>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Pretoria Anlaşması'na rağmen Eritre güçleri sık sık sınır bölgelerinde kaldı; bu durum tekrarlayan çatışmalara, insani ablukalara ve 12 ila 18 ay içinde nihai güven çöküşlerine yol açtı.
+2018: Yakınlaşma yapısaldan ziyade taktiksel olduğunu kanıtladı; iki yıl içinde her iki lider de özellikle Tigray Halk Kurtuluş Cephesi'ne (TPLF) yönelik bir askeri ittifak kurdu.
+Kelimeler:
+• rapprochement = yakınlaşma</t>
+      </text>
+    </comment>
+    <comment ref="H34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çözülmemiş sınır anlaşmazlıklarını ve birden fazla silahlı grubu içeren bölgesel çatışmalarda, taktiksel ittifaklarla desteklenen ateşkesler genellikle iki yıl içinde yeniden askeri saldırılara dönüşmektedir. Tarih, Eritre gibi dış garantör devletlerin tartışmalı bölgelere yeniden girmesi durumunda, yerel çatışmaların hızla tam ölçekli çatışmaların yeniden başlamasına yol açtığını göstermektedir.
+Kelimeler:
+• military incursions = askeri saldırılar/akınlar
+• escalate = tırmanmak, şiddetlenmek</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eritre birliklerinin Tigray'e hareketi, muhtemelen Tigray güçlerinin seferberliğini ve Addis Ababa'da diplomatik krizleri tetikleyecek, yerel çatışmaların bölgesel savaşın daha geniş bir şekilde yeniden başlamasına genişlemesine yol açacaktır.
+Kelimeler:
+• mobilization = seferberlik</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzü 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Addis Ababa'daki merkezi hükümet, teorik olarak uzun süreli iki cepheli bir savaşı kısıtlayabilecek artan ekonomik baskılarla ve başka yerlerdeki eşzamanlı ayaklanmalarla karşı karşıyadır, ancak tarihsel düşmanlık genellikle rasyonel caydırıcılığı geçersiz kılar.
+Kelimeler:
+• deterrence = caydırıcılık</t>
+      </text>
+    </comment>
+    <comment ref="N34" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Etiyopya federal hükümetinin birlik hareketleriyle ilgili resmi açıklamaları ve kuzey Tigray sınırı boyunca doğrudan çatışma raporları.</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İtalya muhalefetin Meloni'yi 'düzenbazlıkla' suçlamasıyla seçim reformunu onayladı
+Kelimeler:
+• elections overhaul = seçim reformu / köklü değişiklik</t>
+      </text>
+    </comment>
+    <comment ref="D35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İtalya Başbakanı Giorgia Meloni'nin hükümeti, eleştirmenlerin kalıcı bir iktidar çoğunluğu sağlamak için tasarlandığını savunduğu tartışmalı bir seçim reformunu geçirdi ve şiddetli siyasi mühendislik suçlamalarını üzerine çekti.
+Kelimeler:
+• elections overhaul = seçim reformu / köklü değişiklik
+• pushed through = zorla geçirmek, baskıyla kabul ettirmek
+• political engineering = siyasi mühendislik</t>
+      </text>
+    </comment>
+    <comment ref="E35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+anayasal reform</t>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1923: Acerbo Yasası
+2006: İtalya'nın 2005 tarihli seçim kanunu</t>
+      </text>
+    </comment>
+    <comment ref="G35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1923: İtalya'da demokratik çoğulculuğu etkili bir şekilde sona erdirerek otoriter kontrolü pekiştirdi ve iki yıl içinde tek partili bir diktatörlüğe zemin hazırladı.
+2006: İstikrarsız, aşırı derecede kutuplaşmış parlamentolar üretti ve nihayetinde 2014 yılında İtalyan Anayasa Mahkemesi tarafından anayasaya aykırı bulunarak iptal edildi.
+Kelimeler:
+• cemented = pekiştirdi, sağlamlaştırdı
+• struck down = iptal etmek, geçersiz kılmak</t>
+      </text>
+    </comment>
+    <comment ref="H35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İtalyan hükümetlerinin iktidar çoğunluğunun lehine seçim yasalarını değiştirdiği 4 büyük tarihi vakanın 3'ünde, mevzuat ya yoğun kurumsal tepkiyi tetikledi, Anayasal Mahkeme tarafından reddedildi ya da parçalanmış koalisyon dinamikleri nedeniyle uzun vadeli istikrar sağlamakta başarısız oldu.
+Kelimeler:
+• backlash = şiddetli tepki</t>
+      </text>
+    </comment>
+    <comment ref="I35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Reform, İtalya Anayasa Mahkemesi'nde şiddetli yasal zorluklarla karşılaşacak ve devasa sokak protestolarını tetikleyecek, potansiyel olarak iktidar koalisyonunun demokratik reform anlatısını istikrarsızlaştıracak.</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Meloni'nin mevcut koalisyonu, Berlusconi'ninki gibi geçmiş yönetimlere göre daha yüksek bir ilk uyum ve disipline sahip; bu durum reformun ilk siyasi saldırıyı atlatmasına yardımcı olabilir.
+Kelimeler:
+• onslaught = şiddetli saldırı / hücum</t>
+      </text>
+    </comment>
+    <comment ref="N35" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İtalyan Anayasa Mahkemesi'nin reformun yasallığına ilişkin kararları ve muhalefet protestolarının tırmanması.</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New York Fed: Birçok günlük üründeki enflasyon tamamen gümrük vergilerinden kaynaklandı
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="D36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New York Federal Reserve araştırması, gümrük vergilerinin 2026 başı itibarıyla 67 mal kategorisinde enflasyona 2,9 yüzde puanı eklediğini ortaya koyuyor.
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler
+• percentage points = yüzde puanı</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gümrük vergileri ve ticaret savaşları
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Trump yönetiminin çelik ve alüminyum tarifeleri
+1930: Smoot-Hawley Gümrük Vergisi Kanunu
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="G36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Nihai ürünler için tüketici fiyatları arttı, üreticilerin girdi maliyetleri yükseldi ve misilleme önlemleri aylar içinde ABD tarım ihracatını hedef aldı.
+1930: Yabancı ülkeler ağır bir şekilde misilleme yaptı, uluslararası ticaret %60'tan fazla düştü ve küresel ekonomik bunalım önümüzdeki 3 yıl içinde derinden derinleşti.
+Kelimeler:
+• retaliatory measures = misilleme önlemleri</t>
+      </text>
+    </comment>
+    <comment ref="H36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, kapsamlı gümrük vergileri tüketiciler üzerinde doğrudan bir vergi gibi hareket eder, yurt içi fiyat seviyelerini yukarı iter ve misilleme sürtüşmesini tetikler; maliyet itişli enflasyon uygulamadan uzun süre sonra bile kalıcılığını korur.
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler
+• cost-push inflation = maliyet itişli enflasyon</t>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarife kaynaklı fiyat katılığı, Federal Reserve'ün inatçı mal enflasyonuyla mücadele etmek için daha uzun süre daha yüksek faiz oranlarını korumasına zorlayacaktır.
+Kelimeler:
+• price stickiness = fiyat katılığı</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel tedarik zincirleri, doğrudan etkileri hafifletmek için halihazırda kısmen alternatif üretim merkezleri üzerinden yeniden yönlendirildi.
+Kelimeler:
+• mitigate = hafifletmek, azaltmak</t>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kilit ticaret ortaklarından gelecek ek misilleme tarifeleri ve çekirdek mal TÜFE verileri.
+Kelimeler:
+• tariffs = gümrük vergileri, tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+3 Yılın En Yüksek Konut Kredisi Faizleri Konut Piyasasını Donduruyor
+Kelimeler:
+• mortgage rates = konut kredisi faizleri</t>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ortalama 30 yıllık sabit faizli konut kredisi %7,4'e yükselerek ABD konut piyasasını daha da dondurdu ve satın alınabilirliği zorlaştırdı.
+Kelimeler:
+• affordability = satın alınabilirlik</t>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+piyasa çöküşleri</t>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Konut kredisi faizleri %7,5'in üzerine çıktı
+1981: Volcker şoku konut kredisi faiz artışı
+Kelimeler:
+• mortgage rates = konut kredisi faizleri</t>
+      </text>
+    </comment>
+    <comment ref="G37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Konut piyasası hacmi donduruldu ('kilitleme etkisi'), işlemler çok yıllık dip seviyelere geriledi; bununla birlikte, takip eden 18 ay boyunca yaşanan ciddi envanter kıtlığı nedeniyle ev fiyatları nispeten yapışkan kaldı.
+1981: Konut sektörü, izleyen 2 yıl içinde konut başlangıçlarının çökmesi ve inşaat istihdamının aşağı inmesiyle şiddetli bir resesyona girdi.
+Kelimeler:
+• lock-in effect = kilitleme etkisi
+• housing starts = konut başlangıçları</t>
+      </text>
+    </comment>
+    <comment ref="H37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Konut kredisi faizleri %7'yi aştığında, satıcılar düşük faizli kredilerini yüksek olanlarla değiştirmeyi reddettiği için konut piyasası tipik olarak baskılanmış işlem hacmi ve kilitlenmiş envanterle uzun bir döneme girer.
+Kelimeler:
+• mortgage rates = konut kredisi faizleri</t>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapısal konut arzı kıtlığı nedeniyle fiyat düzeltmeleri muhtemelen sınırlı kalırken, konut satış hacmi baskılanmaya devam edecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ev sahiplerinin daha büyük bir kısmı evlerine tamamen sahip veya tarihi olarak düşük oranlarda sabit 30 yıllık kredilere sahip, bu da toplu hacizleri önlüyor.
+Kelimeler:
+• outright = tamamen, doğrudan
+• foreclosures = icra yoluyla satış, haciz</t>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Aylık mevcut konut satış raporları ve müteahhit güven endeksleri.</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ceferin, Uefa başkanlığı için dördüncü kez aday olacak
+Kelimeler:
+• stand for = aday olmak, katılmak
+• term = dönem, görev süresi</t>
+      </text>
+    </comment>
+    <comment ref="D38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uefa Başkanı Aleksander Ceferin, görevden ayrılma yönündeki önceki kararından vazgeçerek dördüncü dönem için aday olacak.
+Kelimeler:
+• reversing = tersine çeviren, geri alan
+• stand down = grevden/görevden çekilmek</t>
+      </text>
+    </comment>
+    <comment ref="E38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+grev sınırlarının değiştirilmesi
+Kelimeler:
+• reversal = değiştirme, tersine çevirme</t>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017: Sepp Blatter ve FIFA görev süresi sınırı tarihi
+2023: Aleksander Ceferin tüzük değişiklikleri
+Kelimeler:
+• statute amendments = tüzük değişiklikleri</t>
+      </text>
+    </comment>
+    <comment ref="G38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017: Uzun süren yönetim durgunluğuna ve dış baskı altında liderlik değişimini zorlayan nihai büyük yolsuzluk skandallarına yol açtı.
+2023: Üst düzey yolsuzlukla mücadele yetkilileri protesto amacıyla istifa ederek Avrupa futbol yönetiminde iç siyasi sürtüşmeye zemin hazırladı.
+Kelimeler:
+• prolonged governance stagnation = uzun süren yönetim durgunluğu
+• resigned in protest = protesto amacıyla istifa etti</t>
+      </text>
+    </comment>
+    <comment ref="H38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Benzer spor yönetişimi vakalarının 10'da 9'unda, görevden ayrılma kararlarından vazgeçen uzun süreli yöneticiler zamanla artan iç ayaklanmalarla ve dış yasal incelemelerle karşı karşıya kalır.
+Kelimeler:
+• long-standing executives = uzun süredir görev yapan yöneticiler
+• external legal scrutiny = dış yasal denetim</t>
+      </text>
+    </comment>
+    <comment ref="I38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Artan yönetim sürtüşmesi, ulusal federasyonlardan gelebilecek potansiyel meydan okumalar ve etik komitelerinin artan denetimi.
+Kelimeler:
+• heightened scrutiny = arttırılmış denetim</t>
+      </text>
+    </comment>
+    <comment ref="K38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 12-18 ay</t>
+      </text>
+    </comment>
+    <comment ref="L38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ceferin, mevcut finansal dağılımlardan yararlanan küçük Avrupa üye federasyonlarından güçlü destek almaya devam ediyor.
+Kelimeler:
+• retains strong backing = güçlü desteğini koruyor
+• financial distributions = mali dağıtımlar</t>
+      </text>
+    </comment>
+    <comment ref="N38" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük Avrupa liglerinden gelebilecek kamuoyu muhalefeti veya ortaya çıkan alternatif adaylar.
+Kelimeler:
+• public dissent = kamuoyu muhalefeti</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski Spurs'lü oyuncu Vega, Fifa başkanlığına aday olmaya hazırlanıyor
+Kelimeler:
+• set to run = aday olmaya hazırlanmak</t>
+      </text>
+    </comment>
+    <comment ref="D39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski Tottenham defans oyuncusu Ramon Vega, Gianni Infantino'ya meydan okuyarak gelecek yılki Fifa başkanlık seçiminde aday olmayı niyet ettiğini söylüyor.
+Kelimeler:
+• intends to run = aday olmayı amaçlamak
+• challenging = rakip olmak, meydan okumak</t>
+      </text>
+    </comment>
+    <comment ref="E39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+başkanlık meydan okuması
+Kelimeler:
+• presidential challenge = başkanlık mücadelesi</t>
+      </text>
+    </comment>
+    <comment ref="F39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Luis Figo FIFA başkanlık kampanyası
+2019: Tokyo Sexwale FIFA başkanlık kampanyası</t>
+      </text>
+    </comment>
+    <comment ref="G39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Figo, hileli bir sürece ve eşit şartlarda bir oyun alanının eksikliğine atıfta bulunarak seçimden kısa süre önce adaylıktan çekildi.
+2019: Sexwale, yeterli desteği alamayınca oylamadan saniyeler önce podyumdan dramatik bir şekilde çekildi.
+Kelimeler:
+• withdrew his candidacy = adaylığını geri çekti
+• level playing field = eşit şartlar, adil rekabet ortamı</t>
+      </text>
+    </comment>
+    <comment ref="H39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut kökleşmiş FIFA yetkililerine karşı yapılan neredeyse tüm tarihi meydan okumalarda, ulusal federasyonların derin destek bloklarından yoksun dışarıdan adaylar gerekli adaylıkları güvence altına alamıyor veya oylamadan önce çekiliyor.
+Kelimeler:
+• entrenched incumbents = koltuğunu sağlamlaştırmış mevcut görevliler
+• outsider candidates = dışarıdan gelen adaylar</t>
+      </text>
+    </comment>
+    <comment ref="I39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Resmen oy pusulasında yer almak için gereken zorunlu 5 federasyon adaylığını toplamadaki zorluk.
+Kelimeler:
+• mandatory = zorunlu
+• ballot = oy pusulası</t>
+      </text>
+    </comment>
+    <comment ref="K39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut FIFA liderliğine karşı artan küresel yorgunluk, büyük konfederasyonların bir alternatifi desteklemeye karar vermesi durumunda bir kapı aralayabilir.
+Kelimeler:
+• global fatigue = küresel yorgunluk
+• create an opening = fırsat yaratmak, kapı aralamak</t>
+      </text>
+    </comment>
+    <comment ref="N39" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Vega'nın son tarihten önce ulusal futbol federasyonlarından resmi adaylıkları güvence altına alıp almayacağı.
+Kelimeler:
+• secures formal nominations = resmi adaylıkları güvence altına almak</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Atlantik sezonunun ilk kasırgası Körfez kıyısını vurmka üzere</t>
+      </text>
+    </comment>
+    <comment ref="D40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+El Niño koşulları nedeniyle Atlantik kasırga sezonunun olağan dışı sessiz başlayan dönemi, sezonun ilk kasırgasının oluşumuyla zirveye ulaştı ve bu kasırga şu anda ABD'nin güneyi ile çarpışma rotasında.
+Kelimeler:
+• culminated in = -le sonuçlanmak, zirveye ulaşmak
+• collision course = çarpışma rotası</t>
+      </text>
+    </comment>
+    <comment ref="E40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kasırga</t>
+      </text>
+    </comment>
+    <comment ref="F40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1992: Andrew Kasırgası
+2005: 2005 Atlantik kasırga sezonu</t>
+      </text>
+    </comment>
+    <comment ref="G40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1992: 26 milyar doları aşan felaket niteliğinde zarara yol açtı ve sonraki 3 yıl boyunca Amerika Birleşik Devletleri'nde bina yönetmeliklerinin ve acil durum müdahale yönetiminin tamamen elden geçirilmesini tetikledi.
+2005: Yaygın su baskınları, büyük altyapı çöküşleri ve milyarlarca dolarlık afet yardım çabaları, önümüzdeki onlarca yıl boyunca federal politikaya ve bölge göç kalıplarına hâkim oldu.
+Kelimeler:
+• overhaul = elden geçirme, kapsamlı yenileme</t>
+      </text>
+    </comment>
+    <comment ref="H40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, sıkışmış veya geç başlayan kasırga sezonları genellikle kıyı nüfusunu hazırlıksız yakalar; bu da fırtınalar nihayet vurduğunda hızlı şiddetlenme olaylarına ve ciddi bir hazırlıksızlığa yol açar.
+Kelimeler:
+• off-guard = hazırlıksız, avare av bulunma</t>
+      </text>
+    </comment>
+    <comment ref="I40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Karaya çıkmadan hemen önce hızlı şiddetlenme; bu durum güney ABD kıyısı boyunca yerel şiddetli su baskınlarına ve rüzgâr hasarına yol açacaktır.
+Kelimeler:
+• landfall = (fırtınanın) karaya ulaşması</t>
+      </text>
+    </comment>
+    <comment ref="K40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 7-10 gün</t>
+      </text>
+    </comment>
+    <comment ref="L40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gelişmiş uydu takibi ve yüksek çözünürlüklü sayısal hava tahmin modelleri, önceki on yıllara kıyasla çok daha erken ve daha doğru tahliye uyarıları sağlamaktadır.</t>
+      </text>
+    </comment>
+    <comment ref="N40" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Merkezi barometrik basınçtaki ani düşüşler ve kıyı tahliye emirleri.
+Kelimeler:
+• barometric pressure = barometrik basınç</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+NASA ilk Ay üssünü inşa etmek için gizli mağaralar arıyor</t>
+      </text>
+    </comment>
+    <comment ref="D41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+NASA, insanlığın ilk kalıcı Ay üssüne hazırlık yapmak amacıyla ay yüzeyindeki yeraltı sığınaklarını, buz birikintilerini ve tehlike koşullarını tespit etmek için yeni araştırmalar başlattı.
+Kelimeler:
+• underground shelters = yeraltı sığınakları
+• ice deposits = buz birikintileri</t>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+uzay araştırması</t>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1966: Lunar Orbiter programı
+2009: Lunar Reconnaissance Orbiter</t>
+      </text>
+    </comment>
+    <comment ref="G41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1966: Üç yıl içinde, ayrıntılı haritalama verileri Apollo 11 modülünü Temmuz 1969'da Ay'a güvenli bir şekilde iniş yapması için başarıyla yönlendirdi.
+2009: Uydu, sonraki bir buçuk on yıl boyunca modern Artemis programı planlamasını ve kaynak hedeflemesini doğrudan şekillendiren kritik veriler sağladı.
+Kelimeler:
+• touchdown = iniş yapma</t>
+      </text>
+    </comment>
+    <comment ref="H41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geçmişteki uzay keşif girişimlerinde, ön jeolojik haritalama aşamaları genellikle yüzey altyapısı için gerçek donanım tasarımına ve yer seçimine dönüşmeden önce 3 ila 7 yıl sürer.</t>
+      </text>
+    </comment>
+    <comment ref="I41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Robotik öncü iniş araçlarına zemin hazırlayarak, birincil lav tüpü adaylarının ve yüksek öncelikli kaynak sahalarının belirlenmesi.
+Kelimeler:
+• paving the way = zemin hazırlama, önünü açma</t>
+      </text>
+    </comment>
+    <comment ref="K41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ticari havacılık ve uzay yüklenicilerinin katılımı ve gelişmiş yeraltı delme radar teknikleri, derin mağara keşfini Apollo dönemine göre çok daha yapılabilir kılmaktadır.
+Kelimeler:
+• viable = yapılabilir, uygulanabilir
+• subsurface-penetrating = yeraltına nüfuz eden</t>
+      </text>
+    </comment>
+    <comment ref="N41" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yörünge radar görüntülemesinin sonuçları ve seçilen robotik gezgin iniş sahalarının duyuruları.</t>
       </text>
     </comment>
   </commentList>
@@ -3025,7 +4120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5507,6 +6602,1029 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Trump approved the military's 1st firing squad execution since WWII. Why now?</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>The Pentagon announced that Nidal Hasan will be executed by a military firing squad in December following a botched lethal injection in Tennessee that reignited capital punishment method debates.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>execution method change</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2010: Execution of Ronnie Lee Gardner
+1945: Execution of Eddie Slovik</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2010: The execution proceeded smoothly without legal disruption, but it failed to spark a broader national shift back to firing squads due to intense media scrutiny and legal challenges over Eighth Amendment cruel and unusual punishment claims.
+1945: The strict enforcement served its wartime deterrent purpose temporarily, but cemented a lasting stigma that made commanders reluctant to ever authorize firing squads again for nearly a century.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>When traditional execution methods fail or face legal gridlock, governments occasionally pivot to alternative, highly visible methods like the firing squad; however, in 2 out of 3 modern instances, this triggers immediate, protracted constitutional litigation that delays implementation.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>The planned firing squad execution will face extensive legal challenges regarding cruel and unusual punishment, likely resulting in a temporary judicial stay before any final resolution.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>next 2 months</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>This involves a military tribunal rather than a civilian state court, which operates under distinct Uniform Code of Military Justice rules that historically afford federal authorities more deference.</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Filing of emergency defense motions in federal district court or the Court of Appeals for the Armed Forces.</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/07/nx-s1-5993539/firing-squad-execution-nidal-hasan-fort-hood</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ronnie_Lee_Gardner
+https://en.wikipedia.org/wiki/Eddie_Slovik</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>As crypto and prediction markets expand, their regulator shrinks</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Even as the Commodity Futures Trading Commission (CFTC) faces massive expansion in its regulatory remit over crypto and prediction markets, its staffing and enforcement actions have dropped precipitously during the second Trump administration.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>regulatory rollback</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2017-2018: Deregulation and staffing cuts under the first Trump administration
+2000: Commodity Futures Modernization Act of 2000</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2017-2018: While regulated entities saw immediate relief from compliance costs, several sectors experienced market manipulation scandals and systemic shocks that ultimately required emergency retroactive interventions within 24 months.
+2000: The lack of oversight contributed directly to the opacity of complex financial instruments that fueled the 2008 global financial crisis eight years later.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of 5 historical cases where financial regulators faced intentional downsizing during periods of rapid asset innovation, market manipulation increased significantly, eventually forcing a belated return to aggressive enforcement.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Prediction markets and crypto platforms will experience a surge in speculative volume accompanied by notable high-profile fraud cases, eventually triggering public backlash and calls for emergency Congressional intervention.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>The sheer speed of retail participation via decentralized apps and modern prediction platforms outpaces historical derivatives markets, potentially accelerating the timeline from deregulation to market failure.</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Major liquidity crunches or insider trading scandals on unregulated prediction markets.</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/08/nx-s1-5903204/crypto-prediction-markets-cftc-weakens</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/First_presidency_of_Donald_Trump
+https://en.wikipedia.org/wiki/Commodity_Futures_Modernization_Act_of_2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Brigham nurses and hospital leadership meet as open-ended strike looms</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Leaders at Brigham and Women's Hospital and union negotiators representing thousands of nurses are convening for last-ditch contract bargaining as an open-ended strike threat nears. The dispute centers on staffing ratios, wages, and workplace security.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>labor strike threat</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>June 2016: Brigham and Women's Hospital Strike Notice
+July 2017: Tufts Medical Center Nurses Strike
+March 2021 – January 2022: Saint Vincent Hospital Nurses Strike</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>June 2016: A strike was averted after a marathon 22-hour federal mediation session reached a tentative deal roughly 16 hours before the walkout was scheduled to begin.
+July 2017: Hospital operations were severely disrupted by replacement staff, and after five months of contentious interim talks, an agreement was ratified in December 2017.
+March 2021 – January 2022: The strike lasted 301 days—the longest nurses' strike in Massachusetts history—costing tens of millions of dollars before ending with a mediated compromise brokered by federal officials.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Strike authorizations by healthcare unions in Massachusetts serve predominantly as eleventh-hour bargaining leverage; historically, around 80% to 85% of MNA strike notices at major Boston academic medical centers result in an avert-at-the-brink compromise rather than prolonged strikes.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>The two sides are likely to reach an eleventh-hour agreement or agree to continuous mediation within 24 to 48 hours of the deadline, narrowly averting an extended open-ended walkout.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>75-80%</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 7 days</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Post-pandemic nurse burnout and nationwide hospital margin compressions have hardened positions on both sides, and Mass General Brigham faces systemwide staffing cost pressures that reduce flexibility compared to 2016.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Entry of federal mediators into the talks, whether Brigham begins canceling elective surgeries, and firm logistics announcements regarding traveling replacement nurse contracts.</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOcGtfQVk3cHpPaUR0YnpndDBia2ZkSjJxS0dzSkhvQ1l4YzVPUl9MLXFzZWotR2lRNkM5c2llRUkxRkFUcE9LS0VqcEVzODZTY21rLUtUU0EwRVBEX3BOVjFxWEdwelhxV0c5dFFaNURoUHY1dGl1V2ZMWkJqeDZnaXZvUy1zLW9pMkJESWIyZFVoNEst0gGcAUFVX3lxTFBIUjgtWHJTTkZSdE81ZHRKYy1GNmdUZFRiU1dPdWwyLWNOcm45TmxXZTMyUVVJeWNZeWp6V0NaeDktOXdKTHVGb0UtTXpGQlh5REtCamJvUGw3UDhPRi1yaU9vRTBLcTVzUF8zWTlkQXYyVHdsbVpkRHhSbWZRdTlDU1U3cXQzMWJQaWVWbkd6Y2tDcmcxRDgteVF2OA?oc=5</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Brigham_and_Women's_Hospital
+https://en.wikipedia.org/wiki/Tufts_Medical_Center
+https://en.wikipedia.org/wiki/National_Nurses_United</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>A third of Boston's life sciences lab space sits vacant amid biotech pullback</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Life sciences commercial lab vacancy in Greater Boston has climbed to nearly 30% following aggressive speculative development and a downturn in biotech venture capital financing. Developers and landlords now face debt refinancings on empty state-of-the-art facilities.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>commercial real estate bust</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2001-2004: Silicon Valley Dot-Com Real Estate Hangover
+1989-1993: New England Real Estate and Banking Collapse</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2001-2004: Commercial rents collapsed by 40-50%, landlords offered massive tenant-improvement subsidies, and it took 5 to 7 years to absorb excess square footage back to historical baselines.
+1989-1993: High vacancy triggered regional bank insolvencies, including Bank of New England, followed by severe debt writedowns, foreclosures, and loan restructurings that took over five years to clear.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>In real estate cycles driven by venture capital windfalls, commercial supply deliveries typically lag demand by 2 to 3 years; when speculative vacancies cross 25%, historical absorption base rates dictate a prolonged recovery of at least 4 to 6 years characterized by steep lease concessions and asset repurposing.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Lab space vacancy in Greater Boston is likely to remain elevated above 20% through 2028, with distressed asset sales, lender workouts, and conversions to conventional healthcare or educational space picking up significantly over the next two years.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>next 2 to 4 years</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Unlike standard office buildings, wet labs cost up to $1,000+ per square foot to construct, making conversion to non-lab uses economically punitive and forcing institutional owners to hold them at deep losses rather than quickly repurposing them.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Regional bank non-performing loan disclosures, distressed asset auctions in suburbs like Watertown, Waltham, and Somerville, and whether federal interest rate reductions reignite biotech initial public offerings.</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQUxoTllpajFBa3Y0VzNmS1l0UXVQVDd4SjlkRXdTd1NKM29sbkJ2b0lJdjllakpnU2hQZ2NMODItdWJFZ1lwRUp1cnBmdmxLZ09WMjhyVWVLdmg5LTI4TTh2VnMyNTBtblA2aG1PNVVqYUdjRG5LYk1BZ2M2ZzdQczh5Nko5TjVMSFR6OE5fMGlSQi1ObEZxSmVn?oc=5</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dot-com_bubble
+https://en.wikipedia.org/wiki/Early_1990s_recession_in_the_United_States</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Eritrean troops move deep into Ethiopia's Tigray region, residents tell BBC</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Residents in Tigray report that Eritrean troops have moved deep into the region again, raising fears of renewed large-scale conflict despite prior peace agreements.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ceasefire violation</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2022: Tigray War
+2018: Eritrea–Ethiopia summit</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2022: Despite the Pretoria Agreement, Eritrean forces frequently remained in border areas, leading to recurring clashes, humanitarian blockades, and eventual breakdowns in trust within 12 to 18 months.
+2018: The rapprochement proved tactical rather than structural; within two years, both leaders formed a military alliance specifically directed against the Tigray People's Liberation Front (TPLF).</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>In regional conflicts involving unaddressed border disputes and multiple armed factions, ceasefires backed by tactical alliances frequently degrade into renewed military incursions within two years. History shows that when external guarantor states like Eritrea re-enter contested zones, local flare-ups rapidly escalate into full-scale resumption of hostilities.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>The movement of Eritrean troops into Tigray will likely trigger mobilization by Tigrayan forces and diplomatic crises in Addis Ababa, leading to localized skirmishes expanding into a wider resumption of the regional war.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>The central government in Addis Ababa faces mounting economic pressures and concurrent insurgencies elsewhere, which could theoretically constrain a prolonged two-front war, though historical animosity often overrides rational deterrence.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Official statements from the Ethiopian federal government regarding troop movements, and reports of direct clashes along the northern Tigray border.</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/ckvgd63rj92lo?at_medium=RSS&amp;at_campaign=RSS</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tigray_war
+https://en.wikipedia.org/wiki/2018_Eritrea%E2%80%93Ethiopia_summit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Italy approves elections overhaul as opposition accuse Meloni of 'scam'</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Italian Prime Minister Giorgia Meloni's government has pushed through a controversial elections overhaul, which critics argue is designed to secure a permanent ruling majority, drawing fierce accusations of political engineering.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>constitutional reform</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1923: Acerbo Law
+2006: Italian electoral law of 2005</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1923: It cemented authoritarian control, effectively ending democratic plurality in Italy and paving the way for a single-party dictatorship within two years.
+2006: It produced unstable, hyper-polarized parliaments and was ultimately struck down by the Italian Constitutional Court as unconstitutional in 2014.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>In 3 out of 4 major historical instances where Italian governments altered electoral laws to favor the ruling majority, the legislation either catalyzed intense institutional backlash, faced rejection by the Constitutional Court, or failed to deliver long-term stability due to fragmented coalition dynamics.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>The reform will likely face fierce legal challenges in Italy's Constitutional Court and prompt massive street protests, potentially destabilizing the ruling coalition's narrative of democratic reform.</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Next 12 months</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Meloni's current coalition enjoys higher initial cohesion and discipline than past administrations like Berlusconi's, which may help the reform survive the initial political onslaught.</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Rulings from the Italian Constitutional Court on the legality of the overhaul, and escalation of opposition protests.</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c6zxjdw8rdl5o?at_medium=RSS&amp;at_campaign=RSS</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Acerbo_Law
+https://en.wikipedia.org/wiki/Italian_electoral_law_of_2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Inflation on many everyday items was entirely due to tariffs, NY Fed says</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>New York Federal Reserve research reveals that tariffs added 2.9 percentage points to inflation across 67 categories of goods by early 2026.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>tariffs and trade wars</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2018: Trump administration steel and aluminum tariffs
+1930: Smoot-Hawley Tariff Act</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2018: Consumer prices for downstream goods rose, input costs for manufacturers increased, and retaliatory measures targeted U.S. agricultural exports within months.
+1930: Foreign nations retaliated heavily, international trade plummeted by over 60%, and the global economic depression deepened severely over the next 3 years.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Historically, broad tariffs act as a direct tax on consumers, pushing up domestic price levels and triggering retaliatory friction, with cost-push inflation lingering long after implementation.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Tariff-driven price stickiness will likely force the Federal Reserve to maintain higher interest rates for longer to combat stubborn goods inflation.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>next 6-12 months</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Global supply chains have already partially re-routed through alternative manufacturing hubs to mitigate direct impacts.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Further retaliatory tariffs from key trading partners and core goods CPI readings.</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/08/inflation-tariffs-trump-fed-consumer-goods.html</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tariffs_in_the_second_Trump_administration
+https://en.wikipedia.org/wiki/Smoot%E2%80%93Hawley_Tariff_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Highest Mortgage Rates in 3 Years Chills the Housing Market</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>The average 30-year fixed-rate mortgage surged to 7.4 percent, further freezing the U.S. housing market and straining affordability.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>market crashes</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2023: Mortgage rates peak above 7.5%
+1981: Volcker shock mortgage rate surge</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2023: Housing market volume froze ('lock-in effect'), transactions dropped to multi-year lows, though home prices remained relatively sticky due to severe inventory shortages over the subsequent 18 months.
+1981: The housing sector entered a severe recession with housing starts collapsing and construction employment plunging over the following 2 years.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>When mortgage rates spike past 7%, the housing market typically enters a prolonged period of suppressed transaction volume and locked-in inventory, as sellers refuse to trade low-rate mortgages for high ones.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Home sales volume will remain depressed, while price corrections will likely remain muted due to structural housing supply shortages.</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>A larger share of homeowners own their homes outright or hold fixed 30-year mortgages at historically low rates, preventing mass foreclosures.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Monthly existing home sales reports and builder sentiment indices.</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/08/business/mortgage-rates-housing-prices.html</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Economic_history_of_the_United_States
+https://en.wikipedia.org/wiki/Paul_Volcker</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Ceferin to stand for fourth term as Uefa president</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Uefa president Aleksander Ceferin will stand for a fourth term, reversing a previous decision to stand down.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>term limits reversal</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2017: Sepp Blatter and FIFA term limits history
+2023: Aleksander Ceferin statute amendments</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2017: Led to prolonged governance stagnation and eventual major corruption scandals that forced leadership change under external pressure.
+2023: Senior anti-corruption officials resigned in protest, setting up internal political friction within European football administration.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>In 9 of 10 similar sports governance cases, long-standing executives who reverse decisions to step down face escalating internal revolts and external legal scrutiny over time.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Increased governance friction, potential challenges from national associations, and heightened scrutiny from ethics committees.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>next 12-18 months</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Ceferin retains strong backing from smaller European member associations who benefit from current financial distributions.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Public dissent or alternative candidates emerging from major European leagues.</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cmn4ex2y53l8o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Sepp_Blatter
+https://en.wikipedia.org/wiki/Aleksander_%C4%8Ceferin</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Ex-Spurs player Vega set to run for Fifa president</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Former Tottenham defender Ramon Vega says he intends to run in next year's Fifa presidential election, challenging Gianni Infantino.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>presidential challenge</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2015: Luis Figo FIFA presidential campaign
+2019: Tokyo Sexwale FIFA presidential campaign</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2015: Figo withdrew his candidacy shortly before the election, citing a rigged process and a lack of a level playing field.
+2019: Sexwale withdrew dramatically from the podium moments before the vote after failing to gain traction.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>In nearly all historical challenges against entrenched FIFA incumbents, outsider candidates without deep blocks of national association backing fail to secure the required nominations or withdraw before the vote.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Difficulty in gathering the mandatory 5 federation nominations required to officially appear on the ballot.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Growing global fatigue with current FIFA leadership could create an opening if major confederations decide to back an alternative.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Whether Vega secures formal nominations from national football associations ahead of the deadline.</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c607397pjv37o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Lu%C3%ADs_Figo
+https://en.wikipedia.org/wiki/Tokyo_Sexwale</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>First Hurricane of the Atlantic season due to hit the Gulf coast</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>An unusually quiet start to the Atlantic hurricane season due to El Niño conditions has culminated in the formation of the season's first hurricane, which is now on a collision course with the southern USA.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>hurricane</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1992: Hurricane Andrew
+2005: 2005 Atlantic hurricane season</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1992: It caused catastrophic damage exceeding $26 billion and prompted a total overhaul of building codes and emergency response management in the United States over the subsequent 3 years.
+2005: Widespread flooding, major infrastructural failures, and multi-billion dollar disaster relief efforts dominated federal policy and regional migration patterns for the next decade.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Historically, compressed or late-starting hurricane seasons often catch coastal populations off-guard, leading to rapid intensification events and severe unpreparedness when storms finally strike.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Rapid intensification just before landfall, leading to localized severe flooding and wind damage along the southern US coast.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>next 7-10 days</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Advanced satellite tracking and high-resolution numerical weather prediction models provide significantly earlier and more accurate evacuation warnings than in previous decades.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Sudden drops in central barometric pressure and coastal evacuation orders.</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/weather/articles/cw146l6pnvx0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hurricane_Andrew
+https://en.wikipedia.org/wiki/2005_Atlantic_hurricane_season</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>NASA is searching for hidden caves to build its first Moon base</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>NASA has launched new investigations to locate underground shelters, ice deposits, and hazard conditions on the lunar surface to prepare for humanity's first permanent Moon base.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>space exploration</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1966: Lunar Orbiter program
+2009: Lunar Reconnaissance Orbiter</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1966: Within three years, the detailed mapping data successfully guided the Apollo 11 module to a safe touchdown on the Moon in July 1969.
+2009: The orbiter provided critical data over the next decade and a half that directly shaped modern Artemis program planning and resource targeting.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>In past space exploration initiatives, preliminary geological mapping phases typically take 3 to 7 years before translating into actual hardware design and site-selection for surface infrastructure.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Identification of primary lava tube candidates and high-priority resource sites, paving the way for robotic precursor landers.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Involvement of commercial aerospace contractors and advanced subsurface-penetrating radar techniques make deep cave exploration far more viable than during the Apollo era.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Results from orbital radar imaging and announcements of selected robotic rover landing sites.</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261008005247.htm</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Lunar_Orbiter_program
+https://en.wikipedia.org/wiki/Lunar_Reconnaissance_Orbiter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -3825,6 +3825,1489 @@
       <text>
         <t>Türkçe:
 Yörünge radar görüntülemesinin sonuçları ve seçilen robotik gezgin iniş sahalarının duyuruları.</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Cumhuriyetçi kongre üyesi, New York'taki kritik sandalyede olası bir mavi dalgayı geride bırakmaya çalışıyor
+Kelimeler:
+• outrun = geride bırakmak, kaçıp kurtulmak
+• blue wave = mavi dalga (Demokrat Parti zaferi)
+• toss-up seat = sonucu belirsiz / başa baş sandalye</t>
+      </text>
+    </comment>
+    <comment ref="D42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Temsilci Mike Lawler (R-NY), Demokratların ara seçimlerde Temsilciler Meclisi'ni geri almak için banliyölerdeki savunmasız Cumhuriyetçileri hedef almasıyla New York'un 17. bölgesinde çetin bir yeniden seçilme mücadelesiyle karşı karşıya.
+Kelimeler:
+• intense = yoğun, çetin
+• suburban = banliyöye ait
+• vulnerable = savunmasız, kırılgan
+• flip = (taraf/çoğunluk) değiştirmek</t>
+      </text>
+    </comment>
+    <comment ref="E42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçim dalgalanması
+Kelimeler:
+• midterm election = ara seçim
+• swing = dalgalanma, yön değiştirme</t>
+      </text>
+    </comment>
+    <comment ref="F42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2018: 2018 Temsilciler Meclisi seçimleri banliyö hezimeti
+Kasım 2022: 2022 New York 17. kongre bölgesi seçimi
+Kelimeler:
+• wipeout = hezimet, silinip süpürülme</t>
+      </text>
+    </comment>
+    <comment ref="G42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2018: Demokratlar 41 sandalye kazanarak Ocak 2019'da Temsilciler Meclisi çoğunluğunu ele geçirdi ve Beyaz Saray'ın yasama gündemini sekteye uğratan çok sayıda denetim soruşturması başlattı.
+Kasım 2022: Lawler'ın sürpriz zaferi, Cumhuriyetçilere 222-213'lük kıl payı bir çoğunluk elde etme payı sağladı, ancak onu ülkedeki Demokrat eğilimli en kritik Cumhuriyetçi sandalyelerden birini savunmak zorunda bıraktı.
+Kelimeler:
+• oversight investigations = denetim soruşturmaları
+• stymie = engellemek, sekteye uğratmak
+• legislative agenda = yasama gündemi
+• upset win = sürpriz/beklenmedik galibiyet
+• razor-thin = kıl payı, bıçak sırtı</t>
+      </text>
+    </comment>
+    <comment ref="H42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İç Savaş'tan bu yana yapılan son 40 ara seçimin 38'inde (%95), başkanın partisi Temsilciler Meclisi'nde sandalye kaybetti. Karşı partinin başkan adayının kazandığı banliyö geçiş bölgelerindeki ılımlı görevdeki vekiller, ara seçimlerin karşı rüzgarlarından %20'den daha az bir oranda sağ çıkabiliyor.
+Kelimeler:
+• incumbent = görevde bulunan yetkili
+• crossover districts = farklı partilere oy verebilen bölgeler
+• headwinds = karşı rüzgarlar, olumsuz koşullar</t>
+      </text>
+    </comment>
+    <comment ref="I42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lawler'ın yeniden seçilmeyi kaybetme ihtimali oldukça yüksek görülüyor; New York ve California genelindeki banliyö salıncak bölgelerinin el değiştirmesi ve Meclis çoğunluğunu Demokratlara devretmesi muhtemel.
+Kelimeler:
+• heavily favored to = büyük ölçüde olası görülmek
+• swing districts = oy dengesi değişken bölgeler</t>
+      </text>
+    </comment>
+    <comment ref="K42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ay</t>
+      </text>
+    </comment>
+    <comment ref="L42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New York Cumhuriyetçileri 2022'den bu yana alışılmadık derecede dirençli bir banliyö siyasi altyapısını korudu ve Lawler, partiler arası oy alma potansiyeline sahip kişisel popülaritesini ve bağış toplama gücünü muhafaza ediyor.
+Kelimeler:
+• resilient = dirençli, güçlü
+• split-ticket = farklı partilerin adaylarına oy verme durumu
+• fundraising = bağış toplama</t>
+      </text>
+    </comment>
+    <comment ref="N42" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Westchester ve Rockland ilçelerindeki banliyö posta yoluyla oy kullanma iade oranları ve NY-17'den savunma amaçlı tutulan bölgelere kaydırılan son dakika kampanya reklam harcamaları.
+Kelimeler:
+• absentee ballot = posta yoluyla kullanılan oy
+• diverted away from = -den başka yöne kaydırılan
+• defensive holds = savunma amaçlı elde tutulan yerler</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD, UCM'ye yaptırım kararı aldı; mahkeme bu adımı 'hukukun üstünlüğüne saldırı' olarak kınadı
+Kelimeler:
+• unveil = açıklamak, duyurmak
+• condemn = kınamak
+• assault on = -e saldırı
+• rule of law = hukukun üstünlüğü</t>
+      </text>
+    </comment>
+    <comment ref="D43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika Birleşik Devletleri, yargı yetkisi anlaşmazlıkları nedeniyle Uluslararası Ceza Mahkemesi'ne yaptırım uyguladı ve bu durum mahkeme ile Avrupalı müttefiklerin sert kınamasına yol açtı.
+Kelimeler:
+• slap sanctions = yaptırım uygulamak
+• jurisdictional disputes = yargı yetkisi anlaşmazlıkları
+• swift condemnation = hızlı/sert kınama</t>
+      </text>
+    </comment>
+    <comment ref="E43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+uluslararası yaptırımlar
+Kelimeler:
+• sanctions = yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="F43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2020: 13928 sayılı Başkanlık Kararnamesi UCM yaptırımları
+Ağustos 2002: Amerikan Hizmet Mensuplarını Koruma Yasası
+Kelimeler:
+• Executive Order = Başkanlık Kararnamesi</t>
+      </text>
+    </comment>
+    <comment ref="G43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2020: Yaptırımlar, Biden yönetimi Nisan 2021'de ABD Roma Statüsü'nü hiçbir zaman onaylamamış olmasına rağmen bunları yürürlükten kaldırana kadar UCM'nin bankacılık ve operasyonel faaliyetlerini 10 ay boyunca engelledi.
+Ağustos 2002: Dört yıl içinde Kongre ve Bush yönetimi, müttefiklerin gösterdiği direncin daha geniş kapsamlı terörle mücadele ve güvenlik ortaklıklarına zarar vermesinin ardından yardım kısıtlamalarını geri çekti.
+Kelimeler:
+• hinder = engellemek, aksatmak
+• rescind = yürürlükten kaldırmak, feshetmek
+• ratify = onaylamak (antlaşmayı)
+• roll back = geri çekmek, eski haline getirmek</t>
+      </text>
+    </comment>
+    <comment ref="H43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'nin UCM'ye yönelik tek taraflı cezalandırıcı yaptırımları, resmi kurumsal iş birliğini istikrarlı bir şekilde sekteye uğratmakta ve Avrupalı müttefiklerle diplomatik sürtüşme yaratmaktadır; ancak tarihsel olarak UCM davalarını durdurmada veya mahkemenin dava takviminde yapısal değişiklikler dayatmada başarısız olmaktadır.
+Kelimeler:
+• unilateral = tek taraflı
+• chill = sekteye uğratmak, soğutmak
+• compel = zorlamak, mecbur bırakmak
+• docket = dava listesi, gündem</t>
+      </text>
+    </comment>
+    <comment ref="I43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+UCM, dolar dışı yargı alanları üzerinden faaliyet göstererek soruşturmalarına devam edecek; Avrupalı müttefikler ise resmi protestolarda bulunacak ancak Washington'a karşı doğrudan misilleme amaçlı karşı yaptırımlardan kaçınacaktır.
+Kelimeler:
+• lodge formal protests = resmi protestoda bulunmak
+• retaliatory = misilleme niteliğinde</t>
+      </text>
+    </comment>
+    <comment ref="K43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer Avrupalı imzacılar mahkeme personelini ABD'nin ikincil yaptırımlarından korumak için engelleyici yasalar çıkarırsa, transatlantik adli ilişkiler 2020'de görülmemiş kalıcı bir kurumsal çatlağa maruz kalabilir.
+Kelimeler:
+• blocking statutes = engelleyici yasalar
+• shield = korumak, kalkan olmak
+• secondary sanctions = ikincil yaptırımlar
+• institutional rift = kurumsal çatlak/bölünme</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa Birliği'nin AB Engelleyici Tüzüğü'nü etkinleştirmesi veya müttefik savunma bakanlıklarının resmi uyumsuzluk muafiyetleri getirmesi.
+Kelimeler:
+• activation = etkinleştirme, yürürlüğe koyma
+• non-compliance = uyumsuzluk, uymama
+• exemptions = muafiyetler</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kapsamlı bir silah reformu yasasını yürürlükten kaldırma girişimi olan Mass. Oy Pusulası Soru 9 hakkında bilinmesi gerekenler
+Kelimeler:
+• sweeping = kapsamlı, geniş çaplı
+• repeal = yürürlükten kaldırmak, feshetmek
+• ballot question = oy pusulası sorusu (referandum maddesi)</t>
+      </text>
+    </comment>
+    <comment ref="D44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'teki silah hakları savunucuları, yeni yürürlüğe giren kapsamlı bir eyalet ateşli silah reform yasasını yürürlükten kaldırmak için bir halk oylaması referandumu düzenledi. Bu girişim, seçmenlerden eyalet yasama meclisi tarafından kabul edilen ruhsatlandırma güncellemelerini, ateşli silah tanımlarını ve kamuya açık alanlarda silah taşıma kısıtlamalarını geçersiz kılmalarını istiyor.
+Kelimeler:
+• advocates = savunucular
+• enacted = yasalaşmış, yürürlüğe girmiş
+• statute = yasa, kanun
+• overturn = bozmak, iptal etmek, geçersiz kılmak
+• public carry = kamuya açık alanda silah taşıma</t>
+      </text>
+    </comment>
+    <comment ref="E44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yasa yürürlükten kaldırma veto referandumu</t>
+      </text>
+    </comment>
+    <comment ref="F44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Massachusetts Cinsiyet Kimliği Ayrımcılık Karşıtı Veto Referandumu
+2014: Massachusetts Genişletilmiş Kumar Yasası Referandum İtirazı
+Kelimeler:
+• gender identity = cinsiyet kimliği
+• anti-discrimination = ayrımcılık karşıtı
+• expanded gaming = genişletilmiş kumar/şans oyunları</t>
+      </text>
+    </comment>
+    <comment ref="G44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Seçmenler, yürürlükten kaldırma girişimini %67,8'e karşı %32,2 oyla ezici bir çoğunlukla reddederek yasama meclisinin kanununu aynen korudu.
+2014: Seçmenler, yürürlükten kaldırma girişimini Kasım 2014'te %60'a karşı %40 oyla reddederek eyalet genelinde ticari kumarhane inşaatlarının devam etmesini sağladı.
+Kelimeler:
+• overwhelmingly = ezici çoğunlukla
+• upholding = onaylayarak, destekleyerek, arkasında durarak
+• intact = dokunulmamış, bozulmamış, aynen
+• proceed = ilerlemek, devam etmek</t>
+      </text>
+    </comment>
+    <comment ref="H44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Massachusetts siyasetinde, Demokratik süper çoğunluk tarafından kabul edilen yasaları yürürlükten kaldırmayı amaçlayan vatandaş kaynaklı veto referandumları vakaların %75'inden fazlasında başarısız olmaktadır (en az 4 büyük yasal veto girişiminden 3'ü kesin bir yenilgiye uğradı). Eyaletin seçmen kitlesi, düzenleyici ve sivil konulardaki yasama uzlaşmalarını koruma eğilimini istikrarlı bir şekilde sürdürmektedir.
+Kelimeler:
+• citizen-initiated = vatandaş girişimiyle başlatılan
+• supermajority = nitelikli/ezici çoğunluk
+• decisively = kesin bir biçimde
+• electorate = seçmen kitlesi
+• defaults to = kendiliğinden -e yönelmek/tercih etmek</t>
+      </text>
+    </comment>
+    <comment ref="I44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yürürlükten kaldırma girişiminin sandıkta başarısız olması ve kapsamlı silah reformu yasasının tamamen yürürlükte ve uygulanır kalması kuvvetle muhtemeldir.
+Kelimeler:
+• ballot box = sandık (oy sandığı)
+• enforced = uygulanan, yürürlükte tutulan</t>
+      </text>
+    </comment>
+    <comment ref="K44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1-2 ay</t>
+      </text>
+    </comment>
+    <comment ref="L44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son Yüksek Mahkeme emsallerinin ardından ulusal düzeyde artan İkinci Değişiklik davaları, Massachusetts için geçmişteki taban seviyelerin ötesinde dış bağış toplamayı ve muhafazakar katılımı canlandırabilir.
+Kelimeler:
+• heightened = artmış, yükselmiş
+• litigation = dava açma, dava süreci
+• precedents = emsal kararlar
+• turnout = katılım oranı
+• baseline = taban seviyesi, referans noktası</t>
+      </text>
+    </comment>
+    <comment ref="N44" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston banliyö bölgelerindeki bağımsız kamuoyu yoklama marjları ve ulusal ateşli silah derneği PAC'lerinin (Siyasi Eylem Komiteleri) kampanya harcama bildirimleri.
+Kelimeler:
+• polling margins = anket farkları/marjları
+• suburban = banliyöye ait
+• expenditure = harcama, gider
+• disclosures = kamuya açıklamalar/bildirimler</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Isaias Kasırgası karaya yaklaşıyor. İşte kalıntılarının New England'ı nasıl etkileyebileceği
+Kelimeler:
+• remnants = kalıntılar, artıklar
+• landfall = karaya ulaşma/çıkış</t>
+      </text>
+    </comment>
+    <comment ref="D45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hava tahmincileri, Isaias Kasırgası'nın kalıntılarının ve dış dolaşımının hızla kuzeydoğuya, New England'a doğru ilerleyeceğini; sert rüzgarlar, yerel şiddetli yağışlar ve olası kıyı dalgaları getireceğini öngörüyor.
+Kelimeler:
+• forecasters = hava tahmincileri
+• circulation = hava sirkülasyonu, dolaşım
+• squally = ani ve sert rüzgarlı, fırtınalı
+• surf = kıyıya vuran dalgalar</t>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+tropikal siklon kalıntısı etkisi</t>
+      </text>
+    </comment>
+    <comment ref="F45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ağustos 2020: Isaias Tropikal Fırtınası Kuzeydoğu Geçişi
+Ağustos 2011: Irene Kasırgası New England Karaya Çıkışı
+Kelimeler:
+• northeast passage = kuzeydoğu geçişi</t>
+      </text>
+    </comment>
+    <comment ref="G45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ağustos 2020: 24 saat içinde ani fırtına rüzgarları (downburst) ve devrilen ağaçlar Kuzeydoğu'daki 3 milyondan fazla abonenin elektriğini kesti; Massachusetts ve Connecticut'ta elektrik hatlarının onarımı bir haftayı buldu.
+Ağustos 2011: Yıkıcı nehir taşkınları 48 saat içinde batı Massachusetts ve Vermont'u harabeye çevirdi, 700.000'den fazla aboneyi elektriksiz bıraktı ve ana ulaşım koridorlarını tahrip etti.
+Kelimeler:
+• downbursts = şiddetli inişli hava patlamaları/fırtınaları
+• utility restorations = şebeke/kamu hizmeti onarımları
+• catastrophic = felaket getiren, yıkıcı
+• washing out = sürükleyip götürme, tahrip etme</t>
+      </text>
+    </comment>
+    <comment ref="H45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tropikal siklonlar karaya bitişik bir rota boyunca hızlanarak New England'a doğru ilerlediğinde, yaklaşık 10 vakanın 8'inde (örneğin Isaias 2020, Sandy 2012, Irene 2011) ciddi altyapı aksamaları meydana gelir; bu durum temel olarak sürekli kasırga şiddetindeki rüzgarlardan ziyade devrilen ağaç örtüsünün elektrik şebekelerini çökertmesinden kaynaklanır.
+Kelimeler:
+• accelerating = hızlanarak
+• disruption = aksama, bozulma
+• falling canopy = devrilen ağaç örtüsü/dalları
+• sustained = sürekli, kesintisiz</t>
+      </text>
+    </comment>
+    <comment ref="I45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts ve Connecticut genelinde yüz binlerce kamu hizmeti abonesini etkileyen yaygın elektrik kesintileri, uçuş iptalleri ve yerel ani su baskınları beklenmektedir.
+Kelimeler:
+• electrical outages = elektrik kesintileri
+• flash flooding = ani su baskını, ani sel</t>
+      </text>
+    </comment>
+    <comment ref="K45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 48 ila 72 saat</t>
+      </text>
+    </comment>
+    <comment ref="L45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fırtınanın ilerleme hızı açık okyanus sularına doğru daha da doğuya ivmelenirse, en şiddetli rüzgar kuşakları kıyıdan uzakta kalacak ve bu da karadaki ağaç hasarını ve elektrik arızası toplamlarını önemli ölçüde azaltacaktır.
+Kelimeler:
+• wind swaths = rüzgar kuşakları, rüzgarın etkilediği şeritler
+• offshore = açık denizde, kıyıdan uzakta
+• blunting = hafifleten, etkisini azaltan, körleştiren
+• terrestrial = karasal, karaya ait</t>
+      </text>
+    </comment>
+    <comment ref="N45" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eversource ve National Grid gibi kamu hizmeti şirketlerinin önceden konuşlanma açıklamaları ve ani sel uyarılarının Connecticut River Valley'nin doğusuna mı yoksa batısına mı kayacağı.
+Kelimeler:
+• pre-positioning = önceden konuşlandırma/konumlandırma
+• declarations = bildiriler, açıklamalar
+• flash flood watches = ani sel erken uyarıları/gözlemleri</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD, UCM'ye yönelik yaptırımları açıkladı; mahkeme bu adımı 'hukukun üstünlüğüne saldırı' olarak kınadı
+Kelimeler:
+• unveil = açıklamak, duyurmak, ortaya koymak
+• sanctions = yaptırımlar
+• condemn = kınamak
+• assault = saldırı
+• rule of law = hukukun üstünlüğü</t>
+      </text>
+    </comment>
+    <comment ref="D46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika Birleşik Devletleri, Uluslararası Ceza Mahkemesi'ne yönelik yaptırımlar açıkladı; bu adım uluslararası alanda sert eleştirilere ve mahkemenin bizzat kendisinden kınamaya yol açtı.
+Kelimeler:
+• sharp = sert, keskin
+• condemnation = kınama
+• International Criminal Court = Uluslararası Ceza Mahkemesi</t>
+      </text>
+    </comment>
+    <comment ref="E46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="F46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Amerika Birleşik Devletleri'nin Uluslararası Ceza Mahkemesi'ne yönelik yaptırımları
+Kelimeler:
+• precedent = emsal, geçmiş örnek</t>
+      </text>
+    </comment>
+    <comment ref="G46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Yaptırımlar geniş çaplı uluslararası kınamayla karşılaştı, mahkeme soruşturmalarını geçici olarak aksattı, ancak nihayetinde göreve yeni gelen Biden yönetimi tarafından Nisan 2021'de yürürlükten kaldırıldı.
+Kelimeler:
+• widespread = geniş çaplı, yaygın
+• hamper = aksatmak, engellemek
+• temporarily = geçici olarak
+• ultimately = nihayetinde, en sonunda
+• revoke = yürürlükten kaldırmak, iptal etmek
+• incoming = göreve yeni gelen</t>
+      </text>
+    </comment>
+    <comment ref="H46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Güçlü devletler uluslararası hesap verebilirlik organlarına yaptırım uyguladığında, bu durum geçici bir operasyonel felce ve soruşturmalar üzerinde caydırıcı etkilere yol açar; ancak müttefikler ve üyeler mahkemenin etrafında kenetlendiği için kurumu nadiren kalıcı olarak dağıtır.
+Kelimeler:
+• accountability bodies = hesap verebilirlik organları
+• paralysis = felç, durma
+• chilling effect = caydırıcı/göz korkutucu etki
+• dismantle = dağıtmak, parçalamak
+• rally around = etrafında toplanmak, kenetlenmek</t>
+      </text>
+    </comment>
+    <comment ref="I46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+UCM, muhtemelen artan bir kurumsal meydan okuma sergileyecek ve Avrupalı müttefiklerinden sesli destek görecektir; ancak koruma altındaki ülke vatandaşlarını içeren davaları yürütürken ciddi engellerle karşılaşacaktır.
+Kelimeler:
+• defiance = meydan okuma, itaatsizlik
+• vocal support = güçlü/sesli destek
+• hurdle = engel
+• pursue cases = davaların peşini bırakmamak, dava yürütmek</t>
+      </text>
+    </comment>
+    <comment ref="K46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut küresel jeopolitik kutuplaşmanın boyutu ve birden fazla büyük gücü içeren aktif soruşturmalar, 2021'dekine kıyasla hızlı bir diplomatik geri adım atılmasını daha az olası kılabilir.
+Kelimeler:
+• scope = kapsam, boyut
+• polarization = kutuplaşma
+• swift = hızlı, çabuk
+• reversal = tersine dönme, geri adım</t>
+      </text>
+    </comment>
+    <comment ref="N46" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa Birliği diplomatik açıklamaları ve diğer Batılı ülkelerin UCM personelini koruyan savunma tedbirleri alıp almayacağı.
+Kelimeler:
+• enact = yürürlüğe koymak, uygulamak
+• defensive measures = savunma amaçlı tedbirler</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Etiyopya, askerlerin sınırı geçmesi üzerine kendisini savunacağını belirterek Eritre'yi uyardı
+Kelimeler:
+• warn = uyarmak
+• defend itself = kendini savunmak
+• cross border = sınırı geçmek</t>
+      </text>
+    </comment>
+    <comment ref="D47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Etiyopya, Eritreli askerlerin sınırı geçmesinin ardından toprak bütünlüğünü savunacağını belirterek Eritre'yi uyardı; bu durum misilleme niteliğinde İHA saldırıları düzenlendiği haberlerine yol açtı.
+Kelimeler:
+• territorial integrity = toprak bütünlüğü
+• prompt = yol açmak, tetiklemek
+• retaliatory = misilleme niteliğinde
+• drone strikes = İHA saldırıları</t>
+      </text>
+    </comment>
+    <comment ref="E47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+sınır çatışması
+Kelimeler:
+• border clash = sınır çatışması</t>
+      </text>
+    </comment>
+    <comment ref="F47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1998-2000: Eritre-Etiyopya Savaşı
+2020-2022: Tigray Savaşı</t>
+      </text>
+    </comment>
+    <comment ref="G47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1998-2000: Çatışma 2000 yılındaki Cezayir Anlaşması ile sona erdi ve resmi bir barış olmaksızın yaklaşık yirmi yıl süren gergin bir çıkmaz durumu yarattı.
+2020-2022: Kasım 2022'deki düşmanlıkların durdurulması anlaşmasına rağmen, Eritre güçleri sınır bölgelerinin bazı kısımlarında varlığını sürdürmeye devam etti ve bu da derin bir güvensizlik doğurdu.
+Kelimeler:
+• stalemate = çıkmaz, kilitlenme
+• cessation of hostilities = düşmanlıkların durdurulması
+• lingering presence = sürüp giden/devam eden varlık
+• breed distrust = güvensizlik doğurmak/beslemek</t>
+      </text>
+    </comment>
+    <comment ref="H47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Etiyopya ve Eritre arasında egemenliği tartışmalı bölgelerdeki sınır ihlalleri, köklü karşılıklı şüphe nedeniyle tarihsel olarak hızla daha geniş çaplı askeri çatışmalara dönüşmektedir.
+Kelimeler:
+• incursion = saldırı, sınır ihlali, akın
+• disputed sovereignty = egemenliği tartışmalı
+• escalate = tırmanmak, şiddetlenmek
+• deep-seated = köklü, derin</t>
+      </text>
+    </comment>
+    <comment ref="I47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bölgesel arabulucular hızla devreye girmediği takdirde, iki devlet arasında yeni yerel çatışmalar ve İHA savaşının tırmanması muhtemeldir.
+Kelimeler:
+• skirmish = küçük çaplı çatışma, arbede
+• mediator = arabulucu
+• intervene swiftly = hızla müdahale etmek</t>
+      </text>
+    </comment>
+    <comment ref="K47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Etiyopya'nın şu anda iç ekonomik ve güvenlik sorunlarıyla meşgul olması, Addis Ababa'yı çatışmayı 1998 savaşının boyutlarına ulaşmadan önce kontrol altına almaya teşvik edebilir.
+Kelimeler:
+• preoccupation = meşguliyet, dalgınlık
+• incentivize = teşvik etmek, özendirmek
+• contain = kontrol altına almak, sınırlamak
+• mirror = yansıtmak, benzemek</t>
+      </text>
+    </comment>
+    <comment ref="N47" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Afrika Birliği veya IGAD tarafından yapılacak acil diplomatik müdahaleler.
+Kelimeler:
+• emergency diplomatic intervention = acil diplomatik müdahale</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerikalıların borç sorunları, Büyük Durgunluk'tan bu yana görülmemiş bir uyarı sinyali veriyor
+Kelimeler:
+• flash a warning = uyarı sinyali vermek
+• Great Recession = Büyük Durgunluk (2007-2009 krizi)</t>
+      </text>
+    </comment>
+    <comment ref="D48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Araştırmacılar, hanehalkı kredi kategorilerinde temerrütlerin hızla artmasıyla birlikte, tüketici borç geri ödeme kapasitesinin 2008 krizinden bu yana görülmemiş seviyelere gerilediğini bildiriyor.
+Kelimeler:
+• repayment capacity = geri ödeme kapasitesi
+• deteriorate = kötüleşmek, bozulmak
+• delinquency = vadesi geçmiş borç, temerrüt
+• spike = ani artış göstermek
+• household credit = hanehalkı kredisi</t>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+borç temerrüdü artışı
+Kelimeler:
+• delinquency = borcun gecikmesi, temerrüt
+• surge = ani yükseliş, patlama</t>
+      </text>
+    </comment>
+    <comment ref="F48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006–2007: Büyük Durgunluk öncesinde artan hanehalkı borç temerrütleri
+1989–1990: 1990 resesyonunun öncesindeki tüketici kredisi baskısı
+Kelimeler:
+• household debt = hanehalkı borcu
+• preceding = öncesinde gelen, önceki</t>
+      </text>
+    </comment>
+    <comment ref="G48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006–2007: 12 ila 18 ay içinde, tüketici bilançosundaki baskı kurumsal kredi piyasalarına sıçradı; bu durum ülke genelinde bankacılık işlemlerinin kilitlenmesine yol açarak 1930'lardan bu yana ABD'deki en uzun resesyonu tetikledi.
+1989–1990: Tüketici harcamaları 1990 ortalarında aniden durma noktasına geldi ve Körfez Savaşı petrol şokuyla daha da ağırlaşarak ABD ekonomisini sekiz aylık bir resesyona sürükledi.
+Kelimeler:
+• bleed into = bir alandan diğerine sıçramak/sızmak
+• banking freeze = bankacılık kilitlenmesi / donması
+• abruptly stalled = aniden durma noktasına geldi
+• tip into = bir duruma sürüklemek/itmek
+• compounded by = ile daha da ağırlaşan/birleşen</t>
+      </text>
+    </comment>
+    <comment ref="H48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son 5 ABD ekonomik döngüsünün 4'ünde, tüketici temerrüt oranlarının döngü ortalamalarının üzerinde birkaç çeyrek boyunca süren bozulmasını, 6 ila 18 ay içinde resmi bir NBER resesyonu izlemiştir.
+Kelimeler:
+• sustained = sürekli, kesintisiz
+• multi-quarter = birkaç çeyrek süren
+• deterioration = kötüleşme, bozulma
+• delinquency rate = gecikmiş borç / temerrüt oranı</t>
+      </text>
+    </comment>
+    <comment ref="I48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hanehalkı tüketiminde daralma muhtemel görünmekte; bu durum ticari bankaları kredi verme standartlarını sıkılaştırmaya zorlayarak ekonomik daralma riskini artırmaktadır.
+Kelimeler:
+• consumption contraction = tüketimde daralma
+• commercial banks = ticari bankalar
+• tighten lending standards = kredi verme standartlarını sıkılaştırmak
+• downturn = ekonomik daralma, gerileme</t>
+      </text>
+    </comment>
+    <comment ref="K48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 9 ila 15 ay</t>
+      </text>
+    </comment>
+    <comment ref="L48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hanehalkı toplam bilançoları bu döngüye, 2007'nin ağırlıklı olarak değişken faizli kaldıraç yapısına kıyasla daha yüksek konut özkaynağı ve önemli ölçüde sabit faizli ipotek korumasıyla girdi.
+Kelimeler:
+• aggregate balance sheets = toplam bilançolar
+• home equity = konut özkaynağı (ev değeri eksi kalan kredi)
+• insulation = koruma, yalıtım
+• adjustable-rate leverage = değişken faizli kaldıraç / borçlanma</t>
+      </text>
+    </comment>
+    <comment ref="N48" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Birinci sınıf (prime) kredi kademelerinde 90 günü aşan temerrüde geçişlerdeki artış ve çeyreklik kazanç raporlarında açıklanan banka kredi zararı karşılıkları.
+Kelimeler:
+• prime credit tiers = birinci sınıf (en güvenilir) kredi kademeleri
+• provisions for loan losses = kredi zararı karşılıkları
+• quarterly earnings = çeyreklik kazançlar/bilanço kârları</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+NY Fed: Birçok günlük üründeki enflasyon tamamen gümrük vergilerinden kaynaklandı
+Kelimeler:
+• everyday items = günlük tüketim maddeleri
+• entirely due to = tamamen -den kaynaklı
+• tariffs = gümrük vergileri, tarifeler</t>
+      </text>
+    </comment>
+    <comment ref="D49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New York Federal Rezerv tarafından yapılan bir araştırma, ABD ithalat tarifelerinin 67 günlük tüketim malı kategorisindeki tüketici fiyat enflasyonuna doğrudan 2,9 yüzdelik puan katkıda bulunduğunu ortaya koydu.
+Kelimeler:
+• import tariffs = ithalat gümrük vergileri
+• percentage points = yüzdelik puan
+• everyday goods = günlük kullanım malları</t>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gümrük vergisi kaynaklı enflasyon
+Kelimeler:
+• tariff-driven = gümrük vergisi kaynaklı</t>
+      </text>
+    </comment>
+    <comment ref="F49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018–2019: Trump yönetiminin Çin mallarına uyguladığı 301. Madde gümrük vergileri
+2002: Bush yönetiminin çelik tarifeleri
+Kelimeler:
+• administration = hükümet, yönetim
+• tariffs = gümrük vergileri</t>
+      </text>
+    </comment>
+    <comment ref="G49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018–2019: Federal Rezerv ve NBER tarafından yapılan ekonomik çalışmalar, gümrük vergilerinin 6 ila 12 ay içinde ABD yerel toptan ve perakende satış fiyatlarına neredeyse tamamen yansıdığını, ticaret açığını daraltmadan reel tüketici alım gücünü düşürdüğünü doğruladı.
+2002: Dokuz ay içinde çelik kullanan üreticiler için girdi fiyatları fırladı ve vergiler Aralık 2003'te DTÖ misilleme tehditleri altında yürürlükten kaldırılmadan önce alt sektörlerde tahmini 200.000 istihdam kaybına yol açtı.
+Kelimeler:
+• pass-through = fiyat geçişkenliği, yansıma
+• wholesale and retail prices = toptan ve perakende fiyatlar
+• purchasing power = satın alma gücü
+• trade deficit = dış ticaret açığı
+• input prices = girdi fiyatları
+• downstream job losses = alt/sonraki sektörlerdeki istihdam kayıpları
+• rescinded = yürürlükten kaldırılmış, feshedilmiş
+• retaliation threats = misilleme tehditleri</t>
+      </text>
+    </comment>
+    <comment ref="H49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD gümrük vergisi uygulamalarının neredeyse tüm modern örneklerinde, ithalatla rekabet eden yerli firmalar fiyatları ithalat vergileriyle eş zamanlı olarak artırmakta ve bu da vergi yükünün %80 ila %100'ünün bir yıl içinde doğrudan yerli nihai tüketicinin üzerine kalmasına neden olmaktadır.
+Kelimeler:
+• import-competing firms = ithalatla rekabet eden firmalar
+• in tandem with = ile eş zamanlı olarak, el ele
+• import duties = ithalat vergileri
+• tax burden = vergi yükü
+• end-consumers = nihai tüketiciler</t>
+      </text>
+    </comment>
+    <comment ref="I49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gümrük vergilerinden etkilenen tüketici kategorileri yüksek fiyat tabanlarını koruyacak; bu durum Federal Rezerv'in parasal gevşemesini zorlaştırırken reel ücret artışını da baskılayacaktır.
+Kelimeler:
+• elevated price floors = yükselmiş taban fiyatlar
+• monetary easing = parasal gevşeme
+• suppressing = baskılayan, bastıran
+• real wage growth = reel ücret artışı</t>
+      </text>
+    </comment>
+    <comment ref="K49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tedarik zincirinin gümrük vergisi uygulanmayan ticaret ortaklarına (Güneydoğu Asya veya Meksika gibi) hızla yönlendirilmesi ya da yurt dışındaki sert para birimi değer kayıpları, yerel fiyat geçişkenliğini kısmen hafifletebilir.
+Kelimeler:
+• supply-chain redirection = tedarik zincirinin yeniden yönlendirilmesi
+• currency depreciation = para biriminin değer kaybetmesi
+• blunt = etkisini azaltmak, hafifletmek
+• price pass-through = fiyat geçişkenliği</t>
+      </text>
+    </comment>
+    <comment ref="N49" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Perakende ticaret birlikleri tarafından yapılan muafiyet başvuruları ve ABD'nin kilit ticaret ortaklarının misilleme amaçlı ticaret hamleleri.
+Kelimeler:
+• exclusion requests = muafiyet/istisna talepleri
+• trade associations = ticaret birlikleri/dernekleri
+• retaliatory trade actions = misilleme amaçlı ticaret adımları</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nvidia destekli veri merkezi şirketi, yapay zeka değerleme endişeleri derinleşirken halka arzı (IPO) iptal etti
+Kelimeler:
+• scraps IPO = halka arzı iptal ediyor</t>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nvidia destekli bir veri merkezi şirketi olan Firmus, derinleşen yapay zeka değerleme endişeleri ortasındaki mevcut piyasa oynaklığını ve baskın piyasa koşullarını gerekçe göstererek halka arzını iptal etti.
+Kelimeler:
+• market volatility = piyasa oynaklığı</t>
+      </text>
+    </comment>
+    <comment ref="E50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Halka arz iptali</t>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000: Dot-com balonu halka arz geri çekilmeleri
+2021: SoftBank destekli teknoloji halka arzlarının soğuması</t>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000: Bunu teknoloji sektöründe uzun yıllar süren bir ayı piyasası takip etti; takip eden 24 ila 36 ay içinde yaygın iflaslar ve risk sermayesi finansmanında büyük bir daralma yaşandı.
+2021: Özel değerlemeler birkaç çeyrek boyunca halka açık piyasa gerçekliğinin gerisinde kaldı ve 12 ay içinde ciddi düşük değerlemeli yeni tur yatırımlara (down-round) ile yapısal yeniden yapılanmalara yol açtı.
+Kelimeler:
+• bear market = ayı piyasası (düşüş piyasası)
+• down-rounds = önceki tura göre daha düşük değerlemeyle yapılan yatırım turları</t>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Spekülatif bir boğaya bağlı altyapı sağlayıcıları değerleme endişeleri nedeniyle halka arzları iptal ettiğinde, bu durum genellikle benzer 10 tarihsel örneğin 8'inde sektör çapında bir sermaye daralması baz oranıyla, bir değerleme balonunun patlamasına veya ciddi şekilde sönmesine işaret eder.</t>
+      </text>
+    </comment>
+    <comment ref="I50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Daha fazla teknoloji ve yapay zeka altyapısı halka arz iptali, ardından özel yapay zeka girişimlerinde daha geniş bir değerleme indirimi.</t>
+      </text>
+    </comment>
+    <comment ref="K50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dot-com döneminin aksine, büyük yapay zeka altyapı oyuncuları, marjlar ve sermaye harcaması gereksinimleri yoğun inceleme altında kalmaya devam etse de, önemli yazılım ve donanım geliri elde ediyor.
+Kelimeler:
+• capital expenditure = sermaye harcaması
+• scrutiny = yakın inceleme, denetim</t>
+      </text>
+    </comment>
+    <comment ref="N50" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut yapay zeka çiplerinin ikincil piyasa işlemleri, risk sermayesi fonlama turu düşük değerlemeleri ve büyük bulut sağlayıcılarının sermaye harcaması kesintileri.
+Kelimeler:
+• down-rounds = önceki tura göre daha düşük değerlemeyle yapılan yatırım turları
+• capital expenditure = sermaye harcaması</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, ara seçimler yaklaşırken yakıt maliyetini düşürmek istiyor - bu işe yarayacak mı?
+Kelimeler:
+• midterms loom = ara seçimler yaklaşıyor / kapıda</t>
+      </text>
+    </comment>
+    <comment ref="D51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yakıt fiyatlarının fırlaması ve ara seçimlerin yaklaşmasıyla birlikte, Amerikan tüketicileri için enerji maliyetlerini düşürmesi yönünde yönetime baskı artıyor.
+Kelimeler:
+• soaring = fırlayan, hızla yükselen</t>
+      </text>
+    </comment>
+    <comment ref="E51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+enerji fiyatı müdahalesi</t>
+      </text>
+    </comment>
+    <comment ref="F51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Stratejik Petrol Rezervinin serbest bırakılması
+1979: 1979 enerji krizi fiyat baskıları</t>
+      </text>
+    </comment>
+    <comment ref="G51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Küresel arz dinamikleri ve arıtma kısıtlamaları yukarı yönlü baskıyı yeniden dayatmadan önce fiyatlar birkaç aylığına geçici olarak düştü.
+1979: Tasarrufa ve iç üretime doğru uzun vadeli yapısal değişimler meydana geldi, ancak kısa vadeli siyasi fiyat kontrolleri alttaki arz açığını çözmeyi başaramadı.
+Kelimeler:
+• reasserted upward pressure = yukarı yönlü baskıyı yeniden dayattı</t>
+      </text>
+    </comment>
+    <comment ref="H51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük seçimler öncesinde yapay olarak yakıt fiyatlarını düşürmeye çalışan hükümetler, vakaların yaklaşık 10'da 4'ünde kısa vadeli siyasi rahatlama elde eder, ancak küresel emtia piyasası güçleri neredeyse her zaman iç siyasi faydacılıktan ağır basar.
+Kelimeler:
+• political expedience = siyasi çıkar/faydacılık</t>
+      </text>
+    </comment>
+    <comment ref="I51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kısa vadeli idari tedbirler (düzenleyici geri alımlar veya rezervlerin serbest bırakılması gibi) geçici bir fiyat platosu oluşturabilir, ancak kalıcı yapısal talep ve jeopolitik faktörler enerji maliyetlerini yüksek tutmaya devam edecektir.
+Kelimeler:
+• regulatory rollbacks = düzenleyici kısıtlamaların/kuralların geri alınması</t>
+      </text>
+    </comment>
+    <comment ref="K51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3-6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek yurtiçi ABD ham petrol üretim seviyeleri, 1970'lerin petrol şokları sırasında var olmayan bir iç tampon sağlamaktadır.
+Kelimeler:
+• buffer = tampon bölge, koruyucu unsur</t>
+      </text>
+    </comment>
+    <comment ref="N51" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Acil durum rezervlerinin serbest bırakılmasına ilişkin duyurular, arıtma kapasitesi kullanımındaki değişiklikler ve tüketici güven endekslerindeki aydan aya değişimler.</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Maresca: Man City'nin şampiyonlukları 'kesinlikle' lekelenmedi
+Kelimeler:
+• tainted = lekelenmiş, şaibeli
+• absolutely not = kesinlikle hayır/değil</t>
+      </text>
+    </comment>
+    <comment ref="D52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City teknik direktörü Enzo Maresca, kulübün Premier League finansal kurallarını ihlal etmekten suçlu bulunmasına rağmen önceki şampiyonluklarının lekelenmediği konusunda ısrar ediyor.
+Kelimeler:
+• insists = ısrar ediyor, vurguluyor
+• previous titles = önceki şampiyonluklar
+• found guilty of = -den suçlu bulunmak
+• breaking rules = kuralları ihlal etmek</t>
+      </text>
+    </comment>
+    <comment ref="E52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+mali suistimal kararı
+Kelimeler:
+• misconduct = suistimal, görevi kötüye kullanma
+• ruling = resmi karar, hüküm</t>
+      </text>
+    </comment>
+    <comment ref="F52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: İtalyan futbolundaki Calciopoli skandalı
+2020: Manchester City'ye karşı açılan UEFA finansal fair play davası
+Kelimeler:
+• scandal = skandal
+• financial fair play = finansal adil oyun</t>
+      </text>
+    </comment>
+    <comment ref="G52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: Juventus, yıldız oyuncuların kitlesel göçünü yaşadı, gelir kaybına uğradı ve yerel hakimiyetini yeniden kazanmadan önce neredeyse on yıllık bir yeniden yapılanma sürecine katlandı.
+2020: Spor Tahkim Mahkemesi (CAS), Temmuz 2020'de yasağı bozarak cezayı para cezasına indirdi ve City'nin statüsünü ve finansal ivmesini korumasına izin verdi.
+Kelimeler:
+• mass exodus = kitlesel göç/ayrılış
+• drop in revenue = gelirde düşüş
+• endured = katlandı, dayandı
+• recapturing = yeniden ele geçirmek
+• overturned = bozdu, iptal etti
+• retain = korumak, muhafaza etmek
+• momentum = ivme, hız</t>
+      </text>
+    </comment>
+    <comment ref="H52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük futbol kulüpleri sistematik kural ihlallerinden resmen suçlu bulunduğunda, kamuoyu algısı kalıcı olarak ikiye bölünür: rakip taraftarlar ve tarihçiler şampiyonlukları lekelenmiş olarak görürken, kulüp çalışanları ve sadık taraftarlar şiddetli bir kuşatma psikolojisi benimser.
+Kelimeler:
+• systemic rule breaches = sistematik kural ihlalleri
+• public perception = kamuoyu algısı
+• permanently splits = kalıcı olarak ikiye bölünür
+• insiders = içeridekiler, kulüp mensupları
+• siege mentality = kuşatma psikolojisi</t>
+      </text>
+    </comment>
+    <comment ref="I52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Deplasmanlarda ciddi bir düşmanlık, yoğun medya incelemesi ve kulüp içinde 'dünyaya karşı biz' anlatısının derinlemesine yerleşmesini bekleyin.
+Kelimeler:
+• hostility = düşmanlık, husumet
+• scrutiny = yakın inceleme, denetim
+• entrenched = kök salmış, yerleşmiş
+• us-against-the-world = dünyaya karşı biz</t>
+      </text>
+    </comment>
+    <comment ref="K52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önceki UEFA itirazlarının aksine, mevcut yerel kararlar, Avrupa yerine yerel sportif yaptırımlar taşıyan kalıcı Premier League bulgularını içermektedir.
+Kelimeler:
+• sustained = süregelen, devam eden
+• findings = bulgular, tespitler
+• sporting sanctions = sportif yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="N52" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Anfield'daki taraftar pankartları ve puan silme veya kupaların geri alınmasına ilişkin müteakip Premier League disiplin duyuruları.
+Kelimeler:
+• banner displays = pankart gösterimleri
+• subsequent = ardından gelen, müteakip
+• points deductions = puan silme cezaları
+• trophy stripping = kupaların geri alınması</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Everton yeniden satışta - sahipleri TFG çıkış yolu ararken sırada ne var?
+Kelimeler:
+• up for sale = satılık, satışa çıkarılmış
+• what next = sırada ne var
+• look for a way out = çıkış yolu aramak</t>
+      </text>
+    </comment>
+    <comment ref="D53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Everton, The Friedkin Group'un Premier League kulübünün kontrolünü devralmasından iki yıldan kısa bir süre sonra satışa çıkarıldı.
+Kelimeler:
+• taking control = kontrolü devralmak
+• put up for sale = satışa çıkarılmak</t>
+      </text>
+    </comment>
+    <comment ref="E53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kulüp mülkiyeti değişikliği
+Kelimeler:
+• ownership = sahiplik, mülkiyet</t>
+      </text>
+    </comment>
+    <comment ref="F53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Chelsea FC'nin Todd Boehly ve Clearlake Capital tarafından devralınması
+2018: AC Milan'ın Li Yonghong ve Elliott Management yönetimindeki mülkiyet istikrarsızlığı
+Kelimeler:
+• takeover = devralma
+• instability = istikrarsızlık</t>
+      </text>
+    </comment>
+    <comment ref="G53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Kulüp, büyük sermaye harcamalarına rağmen yıllarca süren istikrarsızlık, teknik direktör sirkülasyonu ve düşük performans yaşayarak aceleci kurumsal el değiştirmelerin yarattığı sürtüşmeyi gözler önüne serdi.
+2018: Elliott, 2022'de RedBird Capital'e satmadan önce borçları yeniden yapılandırarak ve profesyonel yönetim kurarak kulübü birkaç yıl içinde mali açıdan istikrara kavuşturdu.
+Kelimeler:
+• managerial churn = sürekli teknik direktör değişikliği
+• underperformance = beklenenin altında performans
+• capital outlays = sermaye harcamaları
+• hasty = aceleci
+• handovers = devir teslimler, el değiştirmeler
+• restructuring debt = borcu yeniden yapılandırmak</t>
+      </text>
+    </comment>
+    <comment ref="H53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sıkıntılı durumdaki veya yeni gelmiş yatırım gruplarının futbol kulüplerini hızla yeniden satmasını içeren durumların yaklaşık 10'da 7'sinde, geçiş dönemi uzun süreli sportif durgunluğa ve kadro istikrarsızlığına yol açar.
+Kelimeler:
+• distressed = maddi sıkıntıda olan, zora düşmüş
+• transition period = geçiş dönemi
+• induces = yol açar, tetikler
+• stagnation = durgunluk</t>
+      </text>
+    </comment>
+    <comment ref="I53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Everton, potansiyel alıcılar kapsamlı durum tespiti yaparken transfer piyasasında muhtemelen uzun bir temkinli mali kısıtlama dönemiyle karşı karşıya kalacak.
+Kelimeler:
+• prolonged = uzun süreli
+• financial restraint = mali kısıtlama/tasarruf
+• prospective buyers = potansiyel alıcılar
+• due diligence = durum tespiti (finansal ve hukuki inceleme)</t>
+      </text>
+    </comment>
+    <comment ref="K53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+The Friedkin Group, AS Roma aracılığıyla geniş bir çoklu kulüp operasyonel deneyimine sahip ve bu durum kurumsal alıcıları standart spekülatif yatırımcılardan daha hızlı çekebilir.
+Kelimeler:
+• operational experience = operasyonel deneyim
+• institutional buyers = kurumsal alıcılar
+• speculative investors = spekülatif yatırımcılar</t>
+      </text>
+    </comment>
+    <comment ref="N53" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel yatırım konsorsiyumlarından gelen niyet beyanları ve yaklaşan transfer dönemi için ayrılan operasyonel bütçe.
+Kelimeler:
+• statements of interest = ilgi/niyet beyanları
+• consortia = konsorsiyumlar, ortaklıklar
+• allocated = tahsis edilmiş, ayrılmış
+• transfer window = transfer dönemi</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tpki çeken ödüllü görüntünün yapay zeka ürünü olduğu Nikon tarafından açıklandı
+Kelimeler:
+• spark backlash = tepki çekmek
+• AI-generated = yapay zeka tarafından üretilmiş</t>
+      </text>
+    </comment>
+    <comment ref="D54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kamera üreticisi Nikon, kazanan bir çalışmanın gizlice yapay zeka tarafından oluşturulduğunun doğrulanmasının ardından Small World in Motion mikroskopi yarışmasının kurallarını gözden geçirdiğini duyurdu.
+Kelimeler:
+• overhauling = baştan aşağı yenilemek, gözden geçirmek
+• microscopy competition = mikroskopi yarışması</t>
+      </text>
+    </comment>
+    <comment ref="E54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+üretken yapay zeka nedeniyle yarışmadan diskalifiye edilme
+Kelimeler:
+• disqualification = diskalifiye edilme, yarışmadan çıkarılma</t>
+      </text>
+    </comment>
+    <comment ref="F54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Sony Dünya Fotoğrafçılık Ödülleri yapay zeka katılımı tartışması
+2022: Colorado Eyalet Fuarı dijital sanat yarışması ödülünün Midjourney sanat eserine verilmesi
+2016: Nikon Singapur sosyal medya fotoğraf yarışması hatası
+Kelimeler:
+• controversy = tartışma</t>
+      </text>
+    </comment>
+    <comment ref="G54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Organizatörler ödülünü geri aldı ve altı ay içinde büyük küresel fotoğrafçılık yarışmaları, RAW görüntü dosyası sunumunu ve insan yazarlığına dair açık beyanları zorunlu kılmak için kurallarını değiştirdi.
+2022: Yaygın yaratıcı protestoları, yarışmanın ertesi yıl katılım yönergelerini revize etmesine yol açarken, ABD Telif Hakları Bürosu da Allen'ın telif hakkı tescili başvurusunu reddetti.
+2016: İnternet kullanıcıları bariz kopya eser hatasını saatler içinde fark ederek Nikon'u kamuoyundan özür dilemeye ve ödülü 48 saat içinde geri çekmeye zorladı.
+Kelimeler:
+• stripped his win = galibiyetini/ödülünü elinden aldı
+• amended = düzenledi, değiştirdi
+• retract = geri çekmek</t>
+      </text>
+    </comment>
+    <comment ref="H54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zeka veya kompozit manipülasyonun geleneksel sanat ve fotoğraf yarışmalarına sızdığı belgelenmiş olayların yaklaşık 10'da 9'unda, organizatörler derhal zorunlu köken kontrolleri (ham sensör verileri ve iş akışı günlükleri gibi) getirdi ve tek bir yarışma döngüsü içinde sentetik medya için özel, ayrı kategoriler oluşturdu.
+Kelimeler:
+• infiltrated = sızdı
+• mandatory provenance checks = zorunlu köken/menşe kontrolleri</t>
+      </text>
+    </comment>
+    <comment ref="I54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nikon ve benzeri bilimsel görüntüleme yarışmaları, doğrulanmamış dijital işlemelerin standart kategorilerden etkili bir şekilde men edilmesi için kriptografik köken standartlarını (C2PA meta verileri gibi) ve RAW yakalama doğrulamasını zorunlu kılacak.
+Kelimeler:
+• mandate = zorunlu kılmak
+• barring = men eden, yasaklayan</t>
+      </text>
+    </comment>
+    <comment ref="K54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mikroskobik görüntüleme sıklıkla yoğun son işlem (post-processing), odak istifleme (focus-stacking) ve hesaplamalı yeniden oluşturma kullandığından, kabul edilebilir hesaplamalı mikroskopi ile sentetik üretken yapay zeka arasındaki teknik sınırı tanımlamak, geleneksel fotoğrafçılığa göre çok daha zordur.
+Kelimeler:
+• post-processing = çekim sonrası işlem
+• substantially = önemli ölçüde, büyük ölçüde</t>
+      </text>
+    </comment>
+    <comment ref="N54" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nikon'un cihaza özgü meta veri dosyalarının zorunlu olarak sunulmasını kural haline getirip getirmeyeceği veya İçerik Kökeni ve Özgünlüğü Koalisyonu (C2PA) gibi köken girişimleriyle ortaklık kurup kurmayacağı.
+Kelimeler:
+• proprietary = tescilli, şirkete özel</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasırga Isaias, Meksika Körfezi kıyısına varmadan önce 3. kategori büyük bir fırtınaya dönüşerek güçlendi
+Kelimeler:
+• strengthens = güçleniyor
+• landfall = karaya çıkış</t>
+      </text>
+    </comment>
+    <comment ref="D55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Isaias, olağan dışı derecede gecikmiş bir Atlantik sezonunun ilk kasırgası olarak Kategori 3 büyük bir kasırgaya şiddetlendi ve ABD Körfez Kıyısı boyunca karaya çıkması tahmin ediliyor.
+Kelimeler:
+• intensified = şiddetlendi
+• delayed = gecikmiş</t>
+      </text>
+    </comment>
+    <comment ref="E55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+sezon sonu büyük kasırga karaya çıkışı</t>
+      </text>
+    </comment>
+    <comment ref="F55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2018: Michael Kasırgası
+Ekim 1995: Opal Kasırgası
+Ekim 2002: Lili Kasırgası</t>
+      </text>
+    </comment>
+    <comment ref="G55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2018: Fırtına 25 milyar dolardan fazla hasara yol açtı, aşırı dalgayla kıyı altyapısını yok etti ve Georgia boyunca iç kesimlerde kasırga kuvvetindeki rüzgarları sürdürdü.
+Ekim 1995: Kasırga, 15 feet'e varan şiddetli fırtına dalgaları ve Amerika Birleşik Devletleri'nin güneydoğusunda iki milyondan fazla abonenin elektriğini kesen kapsamlı iç kesim rüzgar hasarı üretti.
+Ekim 2002: Lili, güneydoğu Louisiana genelinde kapsamlı elektrik şebekesi çöküşüne, yaygın tarımsal su baskınlarına ve 1 milyar doların üzerinde hasara neden oldu.
+Kelimeler:
+• obliterated = yok etti, silip süpürdü
+• storm surge = fırtına dalgası
+• power outages = elektrik kesintileri</t>
+      </text>
+    </comment>
+    <comment ref="H55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, ekim ayında ABD Körfez Kıyısı'nda karaya çıkan büyük kasırgalar, gözün 30 mil yakınında felaket niteliğinde yerel dalgalara, iç kesimlerde 100 ila 200 mil uzanan uzun süreli elektrik kesintilerine neden olur ve tam elektrik altyapısının onarımı ortalama 10 ila 21 gün sürer.
+Kelimeler:
+• catastrophic = felaket niteliğinde
+• utility restoration = kamu hizmetlerinin (elektrik/su) eski haline getirilmesi</t>
+      </text>
+    </comment>
+    <comment ref="I55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Isaias, alçak kıyı koridorları boyunca önemli fırtına dalgası su baskınlarına, yüzbinlerce sakini etkileyen uzun süreli elektrik şebekesi arızalarına ve nehir havzalarında iç kesimlerde tatlı su taşkınlarına neden olacak.
+Kelimeler:
+• inundation = su basması, sel
+• river basins = nehir havzaları</t>
+      </text>
+    </comment>
+    <comment ref="K55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 7 ila 14 gün</t>
+      </text>
+    </comment>
+    <comment ref="L55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hâkim El Niño paterniyle ilişkili güçlü üst düzey rüzgar kesmesi (wind shear), karaya çıkmadan hemen önce kuru hava sürüklenmesini tetikleyebilir ve göz duvarı yapısını Michael Kasırgası'nda olduğundan daha hızlı bozabilir.
+Kelimeler:
+• wind shear = rüzgar kesmesi / makaslaması
+• entrainment = sürüklenme, içeri çekilme
+• degrading = bozulan, zayıflayan</t>
+      </text>
+    </comment>
+    <comment ref="N55" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Karaya çıkmadan önce iç çekirdekteki hızlı basınç düşüşleri ve fırtınanın kuzey Körfez sahilinde artan güneybatı kesmesiyle karşılaşıp karşılaşmayacağı.
+Kelimeler:
+• inner core = iç çekirdek</t>
       </text>
     </comment>
   </commentList>
@@ -4120,7 +5603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7625,6 +9108,1199 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Republican congressman tries to outrun a potential blue wave in New York toss-up seat</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Representative Mike Lawler (R-NY) faces an intense re-election battle in New York's 17th district as Democrats target vulnerable suburban Republicans to flip the House in the midterm elections.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>midterm election swing</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>November 2018: 2018 House elections suburban wipeout
+November 2022: 2022 New York 17th congressional district election</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>November 2018: Democrats gained 41 seats, flipped the House majority in January 2019, and launched multiple oversight investigations that stymied the White House legislative agenda.
+November 2022: Lawler's upset win provided Republicans the margin to secure a razor-thin 222-213 majority, but left him defending one of the most Democratic-leaning GOP seats in the country.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>In 38 of the last 40 midterms since the Civil War (95%), the president's party has lost House seats. Moderate incumbents in suburban crossover districts carried by the opposing party's presidential ticket survive midterm headwinds fewer than 20% of the time.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Lawler is heavily favored to lose re-election, and suburban swing districts across New York and California are likely to flip, handing the House majority to Democrats.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>next 1 month</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>New York Republicans have maintained an unusually resilient suburban political infrastructure since 2022, and Lawler retains significant split-ticket personal popularity and fundraising power.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Suburban absentee ballot return rates in Westchester and Rockland counties and late campaign ad spending diverted away from NY-17 toward defensive holds.</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/09/nx-s1-5986150/lawler-new-york-congress-trump</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_United_States_House_of_Representatives_elections
+https://en.wikipedia.org/wiki/2022_United_States_House_of_Representatives_elections_in_New_York</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>US unveils sanctions on ICC in move court condems as 'assault on rule of law'</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>The United States slapped sanctions on the International Criminal Court over jurisdictional disputes, drawing swift condemnation from the court and European allies.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>international sanctions</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>June 2020: Executive Order 13928 ICC sanctions
+August 2002: American Service-Members' Protection Act</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>June 2020: The sanctions hindered the ICC's banking and operations for 10 months until the Biden administration rescinded them in April 2021 without the US ever ratifying the Rome Statute.
+August 2002: Within four years, Congress and the Bush administration rolled back the aid restrictions after allied resistance harmed broader counterterrorism and security partnerships.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral US punitive sanctions against the ICC consistently chill formal institutional cooperation and create diplomatic friction with European allies, but historically fail to stop ICC proceedings or compel structural changes to the court's docket.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>The ICC will continue its investigations while operating through non-dollar jurisdictions, while European allies lodge formal protests but avoid direct retaliatory counter-sanctions against Washington.</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>If European signatories create blocking statutes to shield court personnel from US secondary sanctions, transatlantic judicial relations could suffer a permanent institutional rift not seen in 2020.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>European Union activation of the EU Blocking Statute or formal non-compliance exemptions from allied defense ministries.</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cj20vkkx3rdvo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_States_and_the_International_Criminal_Court
+https://en.wikipedia.org/wiki/American_Service-Members'_Protection_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>What to know about Mass. Ballot Question 9, the effort to repeal a sweeping gun reform law</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Gun rights advocates in Massachusetts organized a ballot referendum to repeal a newly enacted, comprehensive state firearm reform statute. The measure asks voters to overturn licensing updates, firearm definitions, and public carry restrictions passed by the state legislature.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>statute repeal veto referendum</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2018: Massachusetts Gender Identity Anti-Discrimination Veto Referendum
+2014: Referendum Challenge to the Massachusetts Expanded Gaming Act</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2018: Voters overwhelmingly rejected the repeal effort by 67.8% to 32.2%, upholding the legislature's statute intact.
+2014: Voters rejected the repeal measure by 60% to 40% in November 2014, enabling commercial casino construction to proceed across the state.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>In modern Massachusetts politics, citizen-initiated veto referendums attempting to repeal statutes passed by the Democratic supermajority fail in over 75% of cases (at least 3 of 4 major statutory veto attempts failed decisively). The state's electorate consistently defaults to protecting legislative compromises on regulatory and civil matters.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>The repeal initiative is very likely to fail at the ballot box, leaving the comprehensive gun reform law fully enacted and enforced.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>next 1-2 months</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Heightened national Second Amendment litigation following recent Supreme Court precedents could energize outside fundraising and conservative turnout beyond historic baseline levels for Massachusetts.</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Independent public polling margins across suburban Boston districts and campaign expenditure disclosures from national firearm association PACs.</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPRGZETm1zUU56ZVZNMXoyS2llN1QybmFtejJzR1R1b1dmV1ZlSU1NTFViN0hHVkJvZW1GZG4zcHBNSmgtWTdQakNBYndLSFpsWGRwdzJfeDhOeWV0UUpsR01vUUpQbTl6TkRtcFBaNDNxMGstZW1CQm03NWRta3JmRnZhVjBtUGxTVmNkYml0RUJyR3lhUktnczR0MFR4NmR1Rjk4R3pFVXZXems4Tk0xcXgySy1ZME45SWk4X21oUkVrT09fWmdDQ0lORnRQX042SFMw?oc=5</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Massachusetts_question_3
+https://en.wikipedia.org/wiki/List_of_integrated_resorts</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Hurricane Isaias nears landfall. Here's how its remnants could impact New England</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Forecasters project that the remnants and outer circulation of Hurricane Isaias will track rapidly northeastward into New England, bringing squally winds, localized heavy rainfall, and potential coastal surf.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>tropical cyclone remnant impact</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>August 2020: Tropical Storm Isaias Northeast Passage
+August 2011: Hurricane Irene New England Landfall</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>August 2020: Within 24 hours, downbursts and tree falls knocked out power to over 3 million Northeast customers, with utility restorations taking up to a week in Massachusetts and Connecticut.
+August 2011: Catastrophic river flooding devastated western Massachusetts and Vermont within 48 hours, leaving more than 700,000 customers without electricity and washing out major transit corridors.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>When tropical cyclones track into New England while accelerating along an inland-adjacent vector, severe infrastructure disruption occurs in roughly 8 of 10 cases (e.g., Isaias 2020, Sandy 2012, Irene 2011), driven primarily by falling canopy knocking down power grids rather than sustained hurricane-force winds.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Expect widespread electrical outages affecting hundreds of thousands of utility customers across Massachusetts and Connecticut, accompanied by flight cancellations and localized flash flooding.</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>next 48 to 72 hours</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>If the storm's forward speed accelerates further eastward into open ocean waters, peak wind swaths will remain offshore, significantly blunting terrestrial tree damage and utility failure totals.</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Pre-positioning declarations by utilities such as Eversource and National Grid, and whether flash flood watches shift east or west of the Connecticut River Valley.</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxON2pmenpQX3pKdDdRaXhqdTRVOUR2dUM2ZGp4U2ctbFdMZERGbjA1VW5SeXNLSkl0RDFXZ1NwQmxUaXNhaDcyQWZZZFJnV1ZpNFJ2LW1YbFVmRXdXU1pUOE9mVzZ5dTIxYl9GRDl4UFcyaHk1aC1LNmI3Nng5ajN5RWVTMmdzMHJvQjJCbFEzTEMyM09NYjZKZUp1SDFRM0R0UnfSAaoBQVVfeXFMTmYxRlk1eURlVnZmVHh3T3FxeU1GdXVyZGI2aWJqRmlxX0V3bE42WXZpYm9zYXdQOUVDZkljQ3dhQUpFaXZRZUxqQ2wtLXc1MVRSNkt0cGdDRERwczhOc1pWOGZqbktlbWNOTXI1dWdSS1pmZ3dEUWxUS0xXdVJuaWkwVC11TVFDMGZlMGNnMVIxaFMybWJlamtlWEpKemd0REU5c2J0YlBYX1E?oc=5</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hurricane_Isaias_(2020)
+https://en.wikipedia.org/wiki/Hurricane_Irene</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>US unveils sanctions on ICC in move court condems as 'assault on rule of law'</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>The United States announced sanctions against the International Criminal Court, drawing sharp international criticism and condemnation from the court itself.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>sanctions</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2020: United States sanctions against the International Criminal Court</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2020: The sanctions faced widespread international condemnation, hampered court investigations temporarily, but were ultimately revoked by the incoming Biden administration in April 2021.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>When powerful states impose sanctions on international accountability bodies, it causes temporary operational paralysis and chilling effects on investigations, but rarely dismantles the institution permanently as allies and members rally around the court.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>The ICC will likely experience increased institutional defiance and vocal support from European allies, while facing severe hurdles in pursuing cases involving protected nationals.</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>The scope of current global geopolitical polarization and active investigations involving multiple major powers could make a swift diplomatic reversal less likely than in 2021.</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>European Union diplomatic statements and whether other Western nations enact defensive measures protecting ICC personnel.</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cj20vkkx3rdvo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Executive_Order_14203</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ethiopia warns Eritrea it will defend itself after troops cross border</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Ethiopia warned Eritrea that it will defend its territorial integrity after Eritrean soldiers crossed the border, prompting reported retaliatory drone strikes.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>border clash</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1998-2000: Eritrean–Ethiopian War
+2020-2022: Tigray War</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1998-2000: The conflict ended with the Algiers Agreement in 2000, establishing a tense stalemate that lasted nearly two decades without formal peace.
+2020-2022: Despite a November 2022 cessation of hostilities agreement, Eritrean forces maintained a lingering presence in parts of border areas, breeding deep distrust.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Border incursions between Ethiopia and Eritrea in areas of disputed sovereignty historically escalate rapidly into broader military confrontations due to deep-seated mutual suspicion.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Further localized skirmishes and an escalation of drone warfare between the two states are likely unless regional mediators intervene swiftly.</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Ethiopia's current preoccupation with internal economic and security challenges may incentivize Addis Ababa to contain the conflict before it mirrors the scale of the 1998 war.</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Emergency diplomatic interventions by the African Union or IGAD.</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c65ynvw250y1o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Eritrean%E2%80%93Ethiopian_War
+https://en.wikipedia.org/wiki/Tigray_war</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Americans' debt problems are flashing a warning not seen since the Great Recession</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Researchers report that consumer debt repayment capacity has deteriorated to levels not observed since the 2008 crisis, with delinquencies spiking across household credit categories.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>debt delinquency surge</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2006–2007: Rising household debt delinquencies prior to the Great Recession
+1989–1990: Consumer credit stress preceding the 1990 recession</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2006–2007: Within 12 to 18 months, consumer balance sheet stress bled into institutional credit markets, causing a nationwide banking freeze and triggering the longest US recession since the 1930s.
+1989–1990: Consumer spending abruptly stalled by mid-1990, tipping the United States economy into an eight-month recession compounded by the Gulf War oil shock.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of the last 5 US economic cycles, sustained multi-quarter deteriorations in consumer delinquency rates above cycle averages have been followed by an official NBER recession within 6 to 18 months.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Household consumption contraction is likely, forcing commercial banks to tighten lending standards and raising the risk of an economic downturn.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>next 9 to 15 months</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Household aggregate balance sheets entered this cycle with higher home equity and substantial fixed-rate mortgage insulation compared to the heavily adjustable-rate leverage of 2007.</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Rising 90-plus day delinquency transitions in prime credit tiers and bank provisions for loan losses reported in quarterly earnings.</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/09/american-debt-delinquency.html</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Subprime_mortgage_crisis
+https://en.wikipedia.org/wiki/Early_1990s_recession_in_the_United_States</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Inflation on many everyday items was entirely due to tariffs, NY Fed says</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>A New York Federal Reserve study found that US import tariffs contributed 2.9 percentage points directly to consumer price inflation across 67 categories of everyday goods.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>tariff-driven inflation</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2018–2019: Trump administration Section 301 tariffs on Chinese goods
+2002: Bush administration steel tariffs</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>2018–2019: Economic studies by the Federal Reserve and NBER confirmed near-complete tariff pass-through to US domestic wholesale and retail prices within 6 to 12 months, reducing real consumer purchasing power without narrowing the trade deficit.
+2002: Within nine months, input prices soared for steel-consuming manufacturers, resulting in an estimated 200,000 downstream job losses before the tariffs were rescinded under WTO retaliation threats in December 2003.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>In nearly all modern instances of US tariff implementation, domestic import-competing firms raise prices in tandem with import duties, causing 80% to 100% of the tax burden to fall directly on domestic end-consumers within one year.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Tariff-affected consumer categories will maintain elevated price floors, complicating Federal Reserve monetary easing and suppressing real wage growth.</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Rapid supply-chain redirection toward non-tariffed trade partners (such as Southeast Asia or Mexico) or aggressive currency depreciation abroad could partially blunt domestic price pass-through.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Exclusion requests filed by retail trade associations and retaliatory trade actions by key US trading partners.</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/08/inflation-tariffs-trump-fed-consumer-goods.html</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/China%E2%80%93United_States_trade_war
+https://en.wikipedia.org/wiki/2002_United_States_steel_tariff</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia-backed data centre firm scraps IPO as AI valuation concerns deepen</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Firmus, an Nvidia-backed data centre firm, scrapped its IPO citing recent market volatility and prevailing market conditions amid deep AI valuation concerns.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>IPO cancellation</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2000: Dot-com bubble IPO withdrawals
+2021: SoftBank-backed tech IPO cooling</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2000: A multi-year bear market followed in the technology sector, with widespread bankruptcies and a massive contraction in venture capital funding over the subsequent 24 to 36 months.
+2021: Private valuations lagged public realities for several quarters, resulting in severe down-rounds and structural restructurings within 12 months.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>When infrastructure providers tied to a speculative boom cancel IPOs due to valuation concerns, it typically signals the bursting or severe deflation of a valuation bubble, with a base rate of sector-wide capital contraction in 8 out of 10 similar historical instances.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Further tech and AI-infrastructure IPO cancellations, followed by a broader valuation markdown across private AI startups.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>next 6-12 months</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Unlike the dot-com era, major AI infrastructure players generate substantial software and hardware revenue, though margins and capital expenditure requirements remain under intense scrutiny.</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Secondary market trading of existing AI chips, venture capital funding round down-rounds, and capital expenditure cutbacks by major cloud providers.</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/ck9dzpw4ll8po?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dot-com_bubble
+https://en.wikipedia.org/wiki/SoftBank_Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Trump wants to reduce the cost of fuel as the midterms loom - will it work?</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>With fuel prices soaring and midterm elections looming, political pressure is mounting on the administration to lower energy costs for American consumers.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>energy price intervention</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2022: Strategic Petroleum Reserve release
+1979: 1979 energy crisis price pressures</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>2022: Prices dipped temporarily for a few months before global supply dynamics and refining constraints reasserted upward pressure.
+1979: Long-term structural shifts toward conservation and domestic production occurred, but short-term political price controls failed to resolve underlying supply deficits.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Governments attempting to artificially depress fuel prices ahead of major elections achieve short-term political relief in about 4 of 10 cases, but global commodity market forces almost always outweigh domestic political expedience.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Short-term administrative measures (such as regulatory rollbacks or release of reserves) may create a temporary price plateau, but persistent structural demand and geopolitical factors will keep energy costs elevated.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>next 3-6 months</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>High domestic US crude oil production levels provide a domestic buffer that did not exist during the 1970s oil shocks.</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Announcements regarding emergency reserve releases, changes in refining capacity utilization, and month-over-month shifts in consumer sentiment indices.</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cv2d6x749lwro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Strategic_Petroleum_Reserve_(United_States)
+https://en.wikipedia.org/wiki/1979_oil_crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Man City titles 'absolutely not' tainted - Maresca</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City manager Enzo Maresca insists the club's previous titles are not tainted despite the club being found guilty of breaking Premier League financial rules.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>financial misconduct ruling</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2006: Calciopoli scandal in Italian football
+2020: UEFA financial fair play case against Manchester City</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2006: Juventus suffered a mass exodus of star players, a drop in revenue, and endured nearly a decade of rebuilding before recapturing domestic dominance.
+2020: The Court of Arbitration for Sport (CAS) overturned the ban in July 2020, reducing the penalty to a fine, allowing City to retain their status and financial momentum.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>When major football clubs are formally found guilty of systemic rule breaches, public perception permanently splits: rival fans and historians view titles as tainted, while club insiders and loyal supporters adopt a fierce siege mentality.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Expect severe hostility away from home, intense media scrutiny, and a deeply entrenched club narrative of us-against-the-world.</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Unlike previous UEFA challenges, the current domestic verdicts involve sustained Premier League findings that carry domestic sporting sanctions rather than European ones.</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Fan banner displays at Anfield and subsequent Premier League disciplinary announcements regarding points deductions or trophy stripping.</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cmzxjdvv784xo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Calciopoli
+https://en.wikipedia.org/wiki/Manchester_City_F.C._financial_breaches_scandal</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Everton up for sale again - so what next as owners TFG look for a way out?</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Everton are put up for sale by The Friedkin Group less than two years after taking control of the Premier League club.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>club ownership change</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2022: Chelsea FC takeover by Todd Boehly and Clearlake Capital
+2018: AC Milan ownership instability under Li Yonghong and Elliott Management</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2022: The club suffered years of instability, managerial churn, and underperformance despite massive capital outlays, demonstrating the friction of hasty institutional handovers.
+2018: Elliott stabilized the club financially over several years, restructuring debt and installing professional management before selling to RedBird Capital in 2022.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>In approximately 7 out of 10 cases involving rapid resale of football clubs by distressed or newly arrived investment groups, the transition period induces prolonged sporting stagnation and squad instability.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Everton will likely face a prolonged period of cautious financial restraint in the transfer market while prospective buyers conduct lengthy due diligence.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>The Friedkin Group possesses extensive multi-club operational experience through AS Roma, which could attract institutional buyers more quickly than standard speculative investors.</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Statements of interest from global investment consortia and the operational budget allocated for the upcoming transfer window.</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c3y0e8n9q4e0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Todd_Boehly
+https://en.wikipedia.org/wiki/AC_Milan</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Prize-winning image which sparked backlash was AI-generated, Nikon rules</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Camera manufacturer Nikon announced it is overhauling the rules of its Small World in Motion microscopy competition after confirming that a winning entry was secretly generated by artificial intelligence.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>contest disqualification due to generative AI</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2023: Sony World Photography Awards AI submission controversy
+2022: Colorado State Fair digital art contest award to Midjourney artwork
+2016: Nikon Singapore social media photo competition error</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2023: The organizers stripped his win, and within six months major global photography contests amended their rules to require RAW image file submissions and explicit declarations of human authorship.
+2022: Widespread creator protests led the contest to revise entry guidelines the following year, while the US Copyright Office subsequently rejected Allen's application for copyright registration.
+2016: Internet users identified the obvious clone artifact within hours, forcing Nikon to issue a public apology and retract the award within 48 hours.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>In nearly 9 out of 10 documented incidents where AI or composite manipulation infiltrated traditional art and photo contests, organizers immediately introduced mandatory provenance checks (such as raw sensor data and workflow logs) and established dedicated, separate categories for synthetic media within one competition cycle.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Nikon and peer scientific imagery competitions will mandate cryptographic provenance standards (such as C2PA metadata) and RAW capture verification, effectively barring unverified digital rendering from standard categories.</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Because microscopic imaging frequently uses heavy post-processing, focus-stacking, and computational reconstruction, defining the technical boundary between acceptable computational microscopy and synthetic generative AI is substantially harder than in conventional photography.</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Whether Nikon institutes mandatory submission of instrument proprietary metadata files or partners with provenance initiatives like the Coalition for Content Provenance and Authenticity (C2PA).</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cr86z33pdy9vo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/World_Photography_Organisation
+https://en.wikipedia.org/wiki/Th%C3%A9%C3%A2tre_D'op%C3%A9ra_Spatial
+https://en.wikipedia.org/wiki/Nikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Hurricane Isaias strengthens to a major category three storm ahead of Gulf Coast landfall</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Isaias intensified into a Category 3 major hurricane—becoming the first hurricane of an unusually delayed Atlantic season—and is forecast to make landfall along the US Gulf Coast.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>late-season major hurricane landfall</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>October 2018: Hurricane Michael
+October 1995: Hurricane Opal
+October 2002: Hurricane Lili</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>October 2018: The storm caused over $25 billion in damage, obliterated coastal infrastructure via extreme surge, and maintained hurricane-force winds far inland across Georgia.
+October 1995: The hurricane generated severe storm surge up to 15 feet and extensive inland wind damage that cut power to more than two million customers across the southeastern United States.
+October 2002: Lili caused extensive power grid collapse, widespread agricultural flooding, and over $1 billion in damage across southern Louisiana.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Historically, major hurricanes making landfall on the US Gulf Coast in October cause catastrophic localized surge within 30 miles of the eye, accompanied by prolonged inland power outages extending 100 to 200 miles inland, with full utility restoration averaging 10 to 21 days.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Isaias will cause significant storm surge inundation along low-lying coastal corridors, prolonged electrical grid failures affecting hundreds of thousands of residents, and inland freshwater flooding across river basins.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>next 7 to 14 days</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Strong upper-level wind shear associated with the prevailing El Niño pattern could induce dry air entrainment just prior to landfall, potentially degrading the eyewall structure more rapidly than occurred with Hurricane Michael.</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Rapid pressure drops in the inner core prior to landfall and whether the storm encounters increased southwesterly shear over the northern Gulf shelf.</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/weather/articles/cw146l6pnvx0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hurricane_Michael
+https://en.wikipedia.org/wiki/Hurricane_Opal
+https://en.wikipedia.org/wiki/Hurricane_Lili</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -5308,6 +5308,1456 @@
 Karaya çıkmadan önce iç çekirdekteki hızlı basınç düşüşleri ve fırtınanın kuzey Körfez sahilinde artan güneybatı kesmesiyle karşılaşıp karşılaşmayacağı.
 Kelimeler:
 • inner core = iç çekirdek</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD, Uluslararası Ceza Mahkemesi'ne Kapsamlı Yaptırımlar Uyguluyor
+Kelimeler:
+• imposes = yürürlüğe koymak, uygulamak
+• sweeping = geniş kapsamlı, kapsamlı</t>
+      </text>
+    </comment>
+    <comment ref="D56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD, Uluslararası Ceza Mahkemesi'ne karşı kapsamlı yaptırımlar açıkladı; Dışişleri Bakanı Marco Rubio, daimi savaş suçları mahkemesini lağvetme sözü verdi.
+Kelimeler:
+• sweeping sanctions = kapsamlı yaptırımlar
+• vowing = yemin etmek, ant içmek, söz vermek
+• dismantle = ortadan kaldırmak, lağvetmek, parçalamak
+• tribunal = mahkeme, yargı kurulu</t>
+      </text>
+    </comment>
+    <comment ref="E56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="F56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Uluslararası Ceza Mahkemesi'ne yönelik Amerika Birleşik Devletleri yaptırımları</t>
+      </text>
+    </comment>
+    <comment ref="G56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Biden yönetimi, tedbirlerin uygunsuz ve etkisiz olduğunu tespit ettikten sonra Nisan 2021'de yaptırımları kaldırdı, ancak gerginlik devam etti.
+Kelimeler:
+• lifted = kaldırdı (yasağı/yaptırımı)
+• determining = tespit etmek, karar vermek
+• inappropriate = uygunsuz, yersiz
+• ineffective = etkisiz</t>
+      </text>
+    </comment>
+    <comment ref="H56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+UCM gibi uluslararası organlara yönelik yaptırımlar anında uluslararası kınama ve hukuki itirazları tetikler, ancak genellikle sonraki yönetimler altında veya pratik uluslararası iş birliği gerektiğinde geri adımlarla ya da yumuşamayla karşılaşır.
+Kelimeler:
+• trigger = tetiklemek
+• condemnation = kınama
+• legal challenges = hukuki itirazlar/meydan okumalar
+• reversals = tersine dönmeler, geri adımlar
+• softening = yumuşama
+• subsequent = sonraki, ardından gelen</t>
+      </text>
+    </comment>
+    <comment ref="I56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupalı müttefikler arabuluculuk yapmaya veya mahkeme personelini ABD tedbirlerinden korumaya çalışırken, UCM finansal ablukalara rağmen soruşturmalarını muhtemelen sürdürecektir.
+Kelimeler:
+• blockades = ablukalar, engellemeler
+• mediate = arabuluculuk yapmak
+• shield = korumak, kalkan olmak
+• personnel = personel, çalışanlar</t>
+      </text>
+    </comment>
+    <comment ref="K56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa ve Orta Doğu'daki aktif çatışmalara ilişkin mevcut jeopolitik saflaşmaların kapsamı, daha kutuplaşmış bir diplomatik ortam yaratıyor.
+Kelimeler:
+• scope = kapsam, boyut
+• geopolitical alignments = jeopolitik saflaşmalar/hizalanmalar
+• active conflicts = aktif çatışmalar
+• polarized = kutuplaşmış</t>
+      </text>
+    </comment>
+    <comment ref="N56" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa Birliği dışişleri bakanlarının ABD'nin mali kısıtlamalarına uyum veya tepki göstermeye ilişkin açıklamaları.
+Kelimeler:
+• compliance = uyum, riayet etme
+• pushback = tepki, karşı koyma
+• restrictions = kısıtlamalar</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Adalet Bakanlığı, Trump Havuz Haberciliği Nedeniyle TV Kanallarını Soruşturuyor
+Kelimeler:
+• Justice Dept. = Adalet Bakanlığı
+• pool coverage = havuz haber takibi/yayını</t>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Adalet Bakanlığı, erişimin kısıtlanmasının ardından Başkan Trump'ın havuz haber takibini askıya aldıklarında antitröst yasalarını ihlal edip etmediklerini incelediğini büyük TV kanallarına bildirdi.
+Kelimeler:
+• notified = resmi olarak bildirdi
+• antitrust laws = antitröst (tekel karşıtı) yasaları
+• suspended = askıya aldı
+• restricted access = kısıtlı erişim</t>
+      </text>
+    </comment>
+    <comment ref="E57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+antitröst soruşturması
+Kelimeler:
+• antitrust investigation = antitröst (tekelcilik) soruşturması</t>
+      </text>
+    </comment>
+    <comment ref="F57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1972: Los Angeles Times ve Washington Post'a yönelik Beyaz Saray Nixon yönetimi antitröst davası
+Kelimeler:
+• antitrust suit = antitröst davası</t>
+      </text>
+    </comment>
+    <comment ref="G57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1972: Birinci Değişiklik kapsamındaki basın özgürlüğü korumaları güçlü kalmasıyla hukuki itirazlar mahkemede tıkandı veya başarısız oldu; ancak yönetim-medya ilişkilerini önemli ölçüde soğuttu.
+Kelimeler:
+• stalled = tıkandı, duraksadı
+• First Amendment = Birinci Anayasa Değişikliği (ifade/basın özgürlüğü)
+• chilled = soğuttu, baltaladı</t>
+      </text>
+    </comment>
+    <comment ref="H57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yürütme organı tarafından basın haberleri üzerine medya şirketlerine karşı başlatılan soruşturmalar, federal mahkemelerde rutin olarak ciddi anayasal engellerle karşılaşır ve nadiren başarılı antitröst cezalarıyla sonuçlanır.
+Kelimeler:
+• initiated by = tarafından başlatılan
+• executive branch = yürütme organı
+• constitutional hurdles = anayasal engeller
+• penalties = cezalar, yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="I57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Televizyon kanalları, Adalet Bakanlığı'nın yetki alanına ve saikine mahkemede itiraz ederek, düşme ihtimali yüksek olan bu süreci uzayan dava süreçleriyle sürüncemede bırakacaktır.
+Kelimeler:
+• jurisdiction = yargı yetkisi
+• motivation = güdü, saik
+• protracted litigation = uzayan dava süreci
+• dismissal = davanın reddi/düşmesi</t>
+      </text>
+    </comment>
+    <comment ref="K57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Antitröst yasasının modern yorumları ve dijital medya dağıtım modelleri, düzenleyici kurumların keşfetmesi için yeni yasal yollar sunuyor.
+Kelimeler:
+• interpretations = yorumlar
+• distribution models = dağıtım modelleri
+• regulatory bodies = düzenleyici kurumlar
+• avenues = yollar, imkanlar</t>
+      </text>
+    </comment>
+    <comment ref="N57" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kanal hukuk ekipleri tarafından federal bölge mahkemesinde sunulan mahkeme celplerini iptal etme talepleri.
+Kelimeler:
+• motions to quash = iptal etme/hükümsüz kılma talepleri
+• subpoenas = mahkeme celpleri
+• district court = bölge mahkemesi</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston &amp; Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham hemşireleri, hastanenin son sözleşme teklifini oylamak için grevi erteledi
+Kelimeler:
+• postpone = ertelemek
+• strike = grev
+• latest offer = son teklif</t>
+      </text>
+    </comment>
+    <comment ref="D58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts Hemşireler Derneği tarafından temsil edilen Brigham and Women's Hospital hemşireleri, Mass General Brigham'dan güncellenmiş bir sözleşme teklifi aldıktan sonra planlanan grevi erteledi. Sendika yönetimi, hastanenin son teklifini tüm üyelerin oylamasına sunmak amacıyla iş bırakma eylemini durdurdu.
+Kelimeler:
+• proposal = teklif, öneri
+• leadership = liderlik, yönetim kadrosu
+• walkout = iş bırakma eylemi, grev
+• ratification = onaylama, yürürlüğe koyma</t>
+      </text>
+    </comment>
+    <comment ref="E58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+grev ertelemesi ve sözleşme onaylama oylaması</t>
+      </text>
+    </comment>
+    <comment ref="F58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Brigham and Women's Hospital 2016 hemşire sözleşmesi uzlaşması
+2023: 2023 New York City hemşirelik grevi geçici anlaşmaları
+2021: Saint Vincent Hospital hemşireleri grevi
+Kelimeler:
+• settlement = uzlaşma, anlaşma
+• tentative agreement = geçici/ön anlaşma</t>
+      </text>
+    </comment>
+    <comment ref="G58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Müzakereciler iş bırakma eylemine 48 saatten az bir süre kala geçici bir anlaşmaya vardı; grev önlendi ve üyeler bir hafta sonra üç yıllık sözleşmeyi büyük bir çoğunlukla onayladı.
+2023: NewYork-Presbyterian gibi sağlık kuruluşları, geçici anlaşmalara vardıktan sonra ve son teslim tarihinden hemen önce grevleri erteledi ve iptal etti; bu anlaşmalar daha sonra %80'in üzerindeki oy oranlarıyla derhal onaylandı.
+2021: Grev 301 gün sürdü, hastaneye on milyonlarca dolara mal oldu ve nihayet çözülmeden önce sendika üzerinde derin bir mali baskı yarattı; bu durum, bir teklif yakın olduğunda her iki taraf için de uzlaşmaya varmanın ne kadar büyük bir teşvik unsuru olduğunu vurguladı.
+Kelimeler:
+• avert = önlemek, bertaraf etmek
+• ratify = onaylamak
+• by a wide margin = büyük bir farkla/çoğunlukla
+• call off = iptal etmek
+• inflict = (zarar, baskı vb.) vermek, yol açmak
+• strain = baskı, gerginlik, yük
+• underscore = vurgulamak, altını çizmek
+• incentive = teşvik edici unsur, motivasyon</t>
+      </text>
+    </comment>
+    <comment ref="H58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çalışma ilişkilerinde, bir sendika müzakere komitesi yönetimin teklifini genel üyelere sunmak üzere yaklaşan bir grevi resmi olarak askıya aldığında, bu durum temel asgari taleplerin karşılandığına işaret eder. Tarihsel olarak, ertelenen iş bırakma bildirimleri altında gerçekleştirilen sağlık grevi oylamalarının yaklaşık %85 ila %90'ı sözleşmenin onaylanmasıyla sonuçlanır.
+Kelimeler:
+• labor relations = çalışma/iş ilişkileri
+• bargaining committee = toplu pazarlık komitesi
+• suspend = askıya almak
+• impending = eli kulağında, yaklaşmakta olan
+• threshold demands = asgari/eşik talepler</t>
+      </text>
+    </comment>
+    <comment ref="I58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham hemşirelerinin sözleşmeyi onaylama yönünde oy kullanması, böylece grevi resmi olarak önlemesi ve Mass General Brigham ile çok yıllı bir iş sözleşmesini kesinleştirmesi son derece muhtemeldir.
+Kelimeler:
+• highly likely = son derece muhtemel
+• lock in = kesinleştirmek, garantiye almak
+• labor pact = iş sözleşmesi/anlaşması</t>
+      </text>
+    </comment>
+    <comment ref="K58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 2 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pandemi sonrası şiddetli personel yorgunluğu ve birikimli enflasyon baskıları, ücret ve hasta-oranı tavizleri liderlik tarafından yetersiz uzlaşmalar olarak görülürse, tabandaki hemşirelerin anlaşmayı reddetmesine yol açabilir.
+Kelimeler:
+• staffing fatigue = personel yetersizliğinden kaynaklanan tükenmişlik/yorgunluk
+• cumulative = birikimli, kümülatif
+• rank-and-file = tabandaki (sıradan üyeler)
+• concession = taviz, ödün
+• compromise = uzlaşma, karşılıklı ödün</t>
+      </text>
+    </comment>
+    <comment ref="N58" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+MNA müzakere komitesi liderlerinin açıkça 'evet' oyu tavsiye eden açıklamaları, bilgilendirme oturumlarındaki katılım sayıları ve erken seçmen katılımı verileri.
+Kelimeler:
+• explicitly = açıkça, net bir şekilde
+• attendance = katılım
+• turnout = (oylamaya) katılım oranı</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston &amp; Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski Stoughton polis memuru Matthew Farwell, Sandra Birchmore cinayeti nedeniyle yargılanıyor
+Kelimeler:
+• go on trial = yargılanmak, mahkemeye çıkmak</t>
+      </text>
+    </comment>
+    <comment ref="D59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski Stoughton polis memuru Matthew Farwell, reşit olmadığı dönemde manipüle edip istismar ettiği ve babalık ile istismarını ifşa etmesini engellemek için öldürdüğü iddia edilen Sandra Birchmore cinayeti sebebiyle federal mahkemede yargılanıyor.
+Kelimeler:
+• groom = istismar amacıyla güvenini kazanmak/manipüle etmek
+• minor = reşit olmayan kişi
+• expose = ifşa etmek, ortaya çıkarmak
+• paternity = babalık</t>
+      </text>
+    </comment>
+    <comment ref="E59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+bir kolluk görevlisinin federal ceza yargılaması</t>
+      </text>
+    </comment>
+    <comment ref="F59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Sandra Birchmore'un ölümüne ilişkin ilk yerel soruşturma
+2015: Walter Scott'ın öldürülmesine ilişkin federal kovuşturma
+2021: Derek Chauvin ve Minneapolis polis memurlarının federal sivil haklar davası
+Kelimeler:
+• prosecution = kovuşturma, savcılık takibatı</t>
+      </text>
+    </comment>
+    <comment ref="G59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Federal müfettişler soruşturmayı devraldı, kapsamlı dijital kanıtlar ortaya çıkardı ve 2024'te Farwell'ı ölümle sonuçlanan tanık manipülasyonu ile suçlayarak yerel departman denetimine ilişkin eyalet düzeyinde incelemelerin başlatılmasına yol açtı.
+2015: Karşı konulamaz federal adli tıp kanıtlarıyla karşı karşıya kalan Slager, Mayıs 2017'de resmi yetkiyi kötüye kullanarak federal medeni hakları ihlal etme suçunu kabul etti ve 20 yıl federal hapis cezasına çarptırıldı.
+2021: Chauvin, ek yargılama risklerinden kaçınmak için Aralık 2021'de federal suçlamaları kabul etti ve diğer üç sanığın tümü Şubat 2022'de federal bir jüri tarafından suçlu bulundu.
+Kelimeler:
+• probe = derinlemesine soruşturma, inceleme
+• indict = hakkında iddianame hazırlamak, suçlamak
+• witness tampering = tanığı etkileme/yönlendirme (suçu)
+• insurmountable = üstesinden gelinemez, karşı konulamaz
+• plead guilty = suçunu kabul etmek
+• under color of law = resmi yetki kisvesi altında</t>
+      </text>
+    </comment>
+    <comment ref="H59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kolluk görevlilerine yönelik müebbet hapis gerektiren ağır suçlamalar (18 U.S.C. § 1512 kapsamında ölümle sonuçlanan tanık manipülasyonu gibi) içeren federal kovuşturmalar, anlaşma veya duruşma kararı yoluyla %90'ı aşan bir mahkumiyet oranına sahiptir. Adalet Bakanlığı, sıkı adli incelemelere dayanabilecek kapsamlı adli tıp ve dijital kanıt izleri olmadan bu davaları nadiren açar.
+Kelimeler:
+• life-qualifying felony = müebbet hapis cezası gerektiren ağır suç
+• conviction rate = mahkumiyet oranı
+• verdict = jüri/mahkeme kararı
+• rigorous = titiz, sıkı
+• judicial scrutiny = adli/yargısal denetim ve inceleme</t>
+      </text>
+    </comment>
+    <comment ref="I59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Farwell, şartlı tahliyesiz müebbet hapis cezasından kaçınmak için son derece yüksek bir mahkumiyet veya müzakere edilmiş bir suç kabulü ihtimaliyle karşı karşıyadır; bu durum, Stoughton Polis Departmanı'na karşı daha geniş kurumsal incelemeleri ve tazminat davalarını hızlandıracaktır.
+Kelimeler:
+• parole = şartlı tahliye
+• civil lawsuit = hukuk/tazminat davası</t>
+      </text>
+    </comment>
+    <comment ref="K59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Olay yeri başlangıçta bozulduğu ve yerel müfettişler tarafından intihar olarak sınıflandırıldığı için, savunma avukatları makul şüphe yaratmak amacıyla ilk gözetim zincirindeki (chain of custody) ve fiziksel kanıtlardaki boşlukları agresif bir şekilde kullanacaktır.
+Kelimeler:
+• compromised = bozulmuş, güvenirliğini yitirmiş
+• exploit = kendi lehine kullanmak, istismar etmek
+• chain-of-custody = delil gözetim zinciri
+• reasonable doubt = makul şüphe</t>
+      </text>
+    </comment>
+    <comment ref="N59" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Cep telefonu coğrafi konumu ve metaveri kabul edilebilirliğine ilişkin duruşma öncesi kararlar, bağımsız adli tıp uzmanlarının ifadeleri ve duruşma tarihi yaklaştıkça olası suç ikrarı müzakereleri.
+Kelimeler:
+• ruling = mahkeme kararı
+• admissibility = (delilin mahkemede) kabul edilebilirliği
+• testimony = tanık ifadesi
+• medical examiner = adli tıp uzmanı</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Riyad havalimanı saldırısı, hâlihazırda gergin olan çatışmada bir başka tehlikeli an oldu
+Kelimeler:
+• tense conflict = gergin çatışma
+• dangerous moment = tehlikeli an</t>
+      </text>
+    </comment>
+    <comment ref="D60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Husi güçleri, Suudi Arabistan topraklarına yönelik saldırıları artırarak ve krallığın ulaşım merkezlerini tehdit ederek Riyad havalimanını hedef alan bir saldırı başlattı.
+Kelimeler:
+• stepping up = artırmak, tırmandırmak
+• strikes = saldırılar, hava harekâtları
+• transport hubs = ulaşım merkezleri, aktarma noktaları
+• targeting = hedef alan</t>
+      </text>
+    </comment>
+    <comment ref="E60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+sınır ötesi havalimanı saldırısı</t>
+      </text>
+    </comment>
+    <comment ref="F60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+November 4, 2017: 2017 Riyad füze saldırısı
+June 12, 2019: 2019 Abha Uluslararası Havalimanı saldırısı
+January 17, 2022: 2022 Abu Dabi saldırısı</t>
+      </text>
+    </comment>
+    <comment ref="G60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+November 4, 2017: Suudi öncülüğündeki koalisyon 48 saat içinde Sana'ya ağır misilleme hava saldırıları düzenledi ve Yemen'e havadan, denizden ve karadan tam bir abluka uyguladı.
+June 12, 2019: Suudi koalisyon uçakları 48 saat içinde Husilere ait fırlatma ve radar mevzilerine misilleme hava saldırıları gerçekleştirdi; Husilerin bölgesel havalimanlarına yönelik İHA baskınları ise sonraki iki ay boyunca devam etti.
+January 17, 2022: Suudi öncülüğündeki koalisyon, takip eden hafta boyunca Yemen genelinde yoğun hava saldırıları başlattı; yaşanan keskin tırmanış uluslararası diplomasiyi harekete geçirerek 10 hafta içinde BM arabuluculuğunda ülke çapında bir ateşkes sağladı.
+Kelimeler:
+• retaliatory airstrikes = misilleme hava saldırıları
+• blockade = abluka
+• drone raids = İHA baskınları
+• escalation = tırmanış, gerginliğin artması
+• galvanized = harekete geçirdi, canlandırdı
+• UN-brokered = BM arabuluculuğunda yapılan
+• nationwide truce = ülke çapında ateşkes</t>
+      </text>
+    </comment>
+    <comment ref="H60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017 ile 2022 yılları arasında Körfez havacılık ve altyapı merkezlerine yönelik 5 büyük Husi saldırısının 4'ünde, koalisyon 72 saat içinde askeri misilleme saldırıları başlattı; yükselen ticari riskler ise 3 ay içinde yoğun perde arkası diplomatik müzakereleri hızlandırdı.
+Kelimeler:
+• infrastructure hubs = altyapı merkezleri
+• elevated commercial risks = yükselen ticari riskler
+• backchannel diplomatic negotiations = arka kapı / perde arkası diplomatik müzakereleri</t>
+      </text>
+    </comment>
+    <comment ref="I60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan'ın, Husilerin fırlatma kapasitelerine karşı hedefli misilleme saldırıları veya hava savunma önleme operasyonları yürütmesi, aynı zamanda ticari havacılığı ve yatırım istikrarını güvenceye almak amacıyla perde arkası diplomatik görüşmeleri aciliyetle sürdürmesi muhtemeldir.
+Kelimeler:
+• interdictions = önleme, durdurma harekâtları
+• safeguard = korumak, güvenceye almak
+• targeted = hedefli, nokta atışı
+• investment stability = yatırım istikrarı</t>
+      </text>
+    </comment>
+    <comment ref="K60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan'ın 2023'te İran ile yakınlaşması ve yurt içindeki Vizyon 2030 projelerine öncelik vermesi, Riyad'ı 2017 veya 2019'a kıyasla sürdürülebilir ve ucu açık bir bombardıman harekâtına yeniden girişme konusunda çok daha isteksiz kılıyor.
+Kelimeler:
+• rapprochement = yakınlaşma, uzlaşma
+• prioritization = önceliklendirme
+• reluctant = isteksiz, çekingen
+• open-ended bombing campaign = ucu açık bombardıman harekâtı</t>
+      </text>
+    </comment>
+    <comment ref="N60" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tahran'dan bölgesel arabuluculuğa ilişkin açıklamalar, orta Suudi hava sahasından uzağa geçici uçuş rotası yönlendirmeleri ve Riyad çevresindeki koalisyon hava savunma konuşlandırmaları.
+Kelimeler:
+• mediation = arabuluculuk
+• flight diversions = uçuş rotası saptırmaları/yönlendirmeleri
+• air defense deployments = hava savunma konuşlandırmaları</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nobel barış ödülü sahibi, ABD'nin UCM yaptırımlarının 'kabul edilemez' olduğunu söyledi
+Kelimeler:
+• laureate = ödül sahibi (özellikle Nobel)
+• sanctions = yaptırımlar
+• unacceptable = kabul edilemez</t>
+      </text>
+    </comment>
+    <comment ref="D61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski BM insan hakları şefi Navi Pillay, Trump yönetiminin Uluslararası Ceza Mahkemesi'ne getirdiği kapsamlı ABD yaptırımlarını duyulmamış ve kabul edilemez bularak kınadı.
+Kelimeler:
+• sweeping = geniş kapsamlı, toptan
+• condemned = kınadı
+• unheard of = eşi benzeri duyulmamış, görülmemiş</t>
+      </text>
+    </comment>
+    <comment ref="E61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+uluslararası mahkemeye yönelik yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="F61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+June 11, 2020: UCM yetkililerine yönelik 13928 sayılı Başkanlık Kararnamesi yaptırımları
+August 2, 2002: Amerikan Hizmet Mensuplarını Koruma Yasası'nın yürürlüğe girmesi</t>
+      </text>
+    </comment>
+    <comment ref="G61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+June 11, 2020: UCM bankacılık kesintileriyle karşılaştı ve adımları kınadı; ancak UCM yargı yetkisinden feragat etmeksizin Biden yönetimi 10 ay sonra April 2021'de başkanlık kararnamesini iptal edene kadar dava portföyünü sürdürdü.
+August 2, 2002: Washington baskı altında yaklaşık 100 ikili dokunulmazlık anlaşması sağladı, ancak Kongre yaptırımların stratejik güvenlik ittifaklarına zarar verdiği sonucuna vardıktan sonra 2006 ile 2008 yılları arasında dış yardım cezalarını geri çekti.
+Kelimeler:
+• rescinded = yürürlükten kaldırdı, iptal etti
+• renouncing = feragat etmek, vazgeçmek
+• jurisdiction = yargı yetkisi
+• bilateral immunity agreements = ikili dokunulmazlık anlaşmaları
+• rolled back = geri çekti, yürürlükten kaldırdı</t>
+      </text>
+    </comment>
+    <comment ref="H61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'nin UCM'ye yönelik önceki yasal ve idari yaptırımlarında bu tedbirler, mahkeme yetkilileri için bürokratik aksamalara ve seyahat kısıtlamalarına neden oldu; ancak mahkemenin soruşturmalarını kalıcı olarak düşürdüğü veya yetkisini feshettiği hiçbir vaka görülmedi ve ABD önlemleri nihayetinde birkaç yıl içinde değiştirildi ya da yürürlükten kaldırıldı.
+Kelimeler:
+• statutory = yasal, kanuni
+• administrative disruption = idari/yönetimsel aksaklık
+• dissolve its mandate = yetkisini/görevini feshetmek
+• rescinded = yürürlükten kaldırılan</t>
+      </text>
+    </comment>
+    <comment ref="I61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uluslararası Ceza Mahkemesi, müttefik UCM üyesi ülkeler ABD'nin sınır ötesi yaptırımlarına karşı yasal kalkanlar oluştururken, bankacılık ve operasyonel lojistiğini Avrupa ve dolar dışı yargı alanlarına kaydırarak aktif soruşturmalarını ve tutuklama emirlerini sürdürecektir.
+Kelimeler:
+• warrants = tutuklama/yakalama emirleri
+• jurisdictions = yargı yetkisi alanları
+• legal shields = yasal kalkanlar/korumalar
+• extraterritorial = ülke sınırlarını aşan, sınır ötesi</t>
+      </text>
+    </comment>
+    <comment ref="K61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer ikincil yaptırımlar UCM'ye hizmet veren ticari bankalara veya Avrupalı yazılım sağlayıcılarına agresif biçimde uygulanırsa, operasyonel felç 2020 başkanlık kararnamesi dönemine göre belirgin şekilde daha ağır olabilir.
+Kelimeler:
+• secondary sanctions = ikincil yaptırımlar
+• software vendors = yazılım tedarikçileri
+• operational paralysis = operasyonel felç, işleyişin durması</t>
+      </text>
+    </comment>
+    <comment ref="N61" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa Birliği'nin UCM personelini korumak için AB Engelleyici Mevzuatı'nı devreye sokma tartışmaları ve ABD federal bölge mahkemelerinde başkanlık kararnamesine karşı açılan davalar.
+Kelimeler:
+• invoking = uygulamaya koymak, devreye sokmak
+• Blocking Statute = Engelleyici Mevzuat
+• legal challenges = hukuki itirazlar, davalar</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşsizlik ödeneğinin tükenme oranları tırmanırken, iş arayanlar daha uzun süreli işsizlikle karşı karşıya kalıyor
+Kelimeler:
+• job seekers = iş arayanlar
+• exhaustion rates = tükenme/bitme oranları
+• climb = tırmanmak, yükselmek</t>
+      </text>
+    </comment>
+    <comment ref="D62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de işinden olan çalışanlar daha uzun süreli işsizlik dönemleri yaşıyor; yaklaşık yüzde 40'ı bir iş bulamadan önce standart eyalet işsizlik sigortası haklarını tüketiyor.
+Kelimeler:
+• displaced workers = işinden olmuş/çıkarılmış çalışanlar
+• extended periods = uzun süreli dönemler
+• joblessness = işsizlik
+• exhausting = tüketme, bitirme
+• unemployment insurance benefits = işsizlik sigortası ödenekleri/hakları
+• securing employment = iş bulmak, istihdam sağlamak</t>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+iş gücü piyasasında yavaşlama
+Kelimeler:
+• slowdown = yavaşlama</t>
+      </text>
+    </comment>
+    <comment ref="F62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2002-2003: 2000'lerin başındaki istihdamsız toparlanma ve ödeneğin tükenmesi
+2007-2008: Büyük Durgunluk'a giden süreçte artan işsizlik süresi
+1991-1992: 1990 durgunluğu sonrası iş arama süresinde yaşanan sıçrama
+Kelimeler:
+• jobless recovery = istihdamsız toparlanma
+• duration = süre
+• leading into = -e yol açan, öncülük eden
+• surge = ani artış, sıçrama</t>
+      </text>
+    </comment>
+    <comment ref="G62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2002-2003: Federal politika yapıcılar Geçici Uzatılmış İşsizlik Tazminatı (TEUC) programını yasalaştırdı ve defalarca uzattı; bu sırada bordrolu istihdam 2003 sonlarına kadar yaklaşık iki yıl boyunca cansız kaldı.
+2007-2008: Kongre, Haziran 2008'de EUC08 kapsamında acil durum federal uzatmalarını yasalaştırdı ve genel işsizlik oranı takip eden 12 ila 18 ay boyunca yukarı yönlü hız kazandı.
+1991-1992: Uzatılmış yardımlar 1991 sonlarında federal düzeyde onaylandı ve tüketici güvenindeki belirgin düşüşler 1992 seçimleri öncesinde görevdeki siyasi liderlik üzerinde baskı yarattı.
+Kelimeler:
+• enacted = yasalaştırdı, yürürlüğe koydu
+• subdued = cansız, sönük, zayıf
+• accelerated upward = yukarı yönlü hızlandı
+• authorized = yetkilendirildi, onaylandı
+• incumbent = görevde bulunan (siyasetçi)</t>
+      </text>
+    </comment>
+    <comment ref="H62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, ABD'de ödeneğin tükenme oranlarının %35-40'ı aştığı 5 durumun 4'ünde, genel iş gücü piyasası ilave 6 ila 18 ay boyunca kalıcı ücret yavaşlaması ve işe alım dondurmalarıyla karşı karşıya kalmakta ve bu da Kongre'de federal işsizlik uzatmaları çağrılarına yol açmaktadır.
+Kelimeler:
+• sustained = sürekli, kalıcı
+• wage deceleration = ücret artışında yavaşlama
+• hiring freezes = işe alımların durdurulması/dondurulması
+• prompting = yol açan, teşvik eden</t>
+      </text>
+    </comment>
+    <comment ref="I62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşe alım ivmesinin zayıf kalması muhtemel; bu da medyan iş arama sürelerini yukarı taşıyacak ve uzatılmış işsizlik tazminatını fonlaması için Kongre üzerindeki siyasi baskıyı artıracaktır.
+Kelimeler:
+• momentum = ivme, hız
+• sluggish = ağır işleyen, durgun
+• median = ortanca, medyan</t>
+      </text>
+    </comment>
+    <comment ref="K62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sağlık ve zanaat/teknik iş kollarında pandemi sonrası ortaya çıkan yapısal iş gücü açıkları ve uzaktan çalışma esnekliği, toplam istihdam seviyelerinin geçmişteki derin durgunluklara kıyasla çökmesini engelleyebilir.
+Kelimeler:
+• structural labor shortages = yapısal iş gücü açıkları
+• trades = zanaat işleri, mesleki kollar
+• prevent ... from collapsing = ... çökmesini engellemek</t>
+      </text>
+    </comment>
+    <comment ref="N62" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+BLS medyan işsizlik süresi metriğinin 20 haftayı aşması, devam eden başvuruların 2 milyonu geçmesi ve acil durum federal yardım uzatmalarına yönelik iki partili yasa teklifleri.
+Kelimeler:
+• surpassing = aşmak, geçmek
+• continuing claims = devam eden işsizlik maaşı başvuruları
+• bipartisan = iki partili (her iki partinin desteklediği)
+• proposals = teklifler, tasarılar</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelenski anlaşmayı Putin'e bir hediye olarak nitelendirirken, Trump Rus dizeli için anlaşma yapıldığını duyurdu
+Kelimeler:
+• announces deal = anlaşma duyurmak
+• calls it a gift = hediye olarak nitelendirmek</t>
+      </text>
+    </comment>
+    <comment ref="D63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump yönetimi, hızla artan yerel yakıt fiyatlarını hafifletmek amacıyla işlenmiş Rus dizeli satın almak üzere bir anlaşmaya varıldığını duyurdu; bu adım Ukrayna Devlet Başkanı Volodimir Zelenski'nin sert tepkisini çekti.
+Kelimeler:
+• alleviate = hafifletmek, dindirmek
+• soaring = hızla yükselen
+• refined diesel = işlenmiş dizel
+• drawing fierce condemnation = sert kınama/tepki çekmek</t>
+      </text>
+    </comment>
+    <comment ref="E63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+enerji yaptırımı muafiyeti
+Kelimeler:
+• sanctions waiver = yaptırım muafiyeti</t>
+      </text>
+    </comment>
+    <comment ref="F63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1981: Reagan'ın Sovyet tahıl ambargosunu kaldırması
+2022: G7'nin Rus petrolüne tavan fiyat uygulamasını hayata geçirmesi
+Kelimeler:
+• lifts the embargo = ambargoyu kaldırmak
+• price cap = tavan fiyat</t>
+      </text>
+    </comment>
+    <comment ref="G63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1981: Soğuk Savaş retoriğinin tırmanmasına rağmen ikili ticaret derhal yeniden başladı ve Sovyetler Birliği ucuz gıda temin ederken, ABD'nin algılanan tutarsızlığı nedeniyle Washington ile Avrupalı müttefikler arasındaki siyasi gerilim tırmandı.
+2022: Küresel akaryakıt fiyatlarındaki ani artışlar üç ay içinde yatıştı, ancak Rusya yaptırım arbitrajı ve gölge filo operasyonları sayesinde işlenmiş yakıt gelirlerini koruyarak süregelen savaşın finansmanını eksiksiz sürdürdü.
+Kelimeler:
+• bilateral trade = ikili ticaret
+• friction = sürtüşme, gerilim
+• arbitrage = arbitraj (fiyat farkından kâr sağlama)
+• shadow fleet = gölge filo
+• underlying war = süregelen/arka plandaki savaş</t>
+      </text>
+    </comment>
+    <comment ref="H63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kritik küresel emtiaları (enerji, gıda) içeren 10 büyük jeopolitik ticaret krizinin 8'inde, yerel tüketici enflasyonu baskıları Batılı liderleri muafiyetler veya ikili ticaret istisnaları getirmeye zorlamakta ve bu durum çok taraflı yaptırım koalisyonlarını zayıflatmaktadır.
+Kelimeler:
+• standoffs = çıkmazlar, anlaşmazlıklar
+• commodities = emtialar, ticari mallar
+• compel = zorlamak, mecbur bırakmak
+• diluting = etkisini azaltmak, seyreltmek</t>
+      </text>
+    </comment>
+    <comment ref="I63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tedarik anlaşmasının Batı ittifakında derhal siyasi çatlaklara yol açması ve Moskova'yı daha geniş yaptırım indirimleri aramaya cesaretlendirmesi muhtemelken, perakende dizel fiyatlarına yalnızca geçici ve sınırlı bir rahatlama sağlaması bekleniyor.
+Kelimeler:
+• procurement deal = tedarik anlaşması
+• political fractures = siyasi çatlaklar/bölünmeler
+• embolden = cesaretlendirmek
+• modest relief = mütevazı/sınırlı bir rahatlama</t>
+      </text>
+    </comment>
+    <comment ref="K63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut yaptırımların derinliği ve Avrupa'nın direnci, Avrupalı müttefiklerin ikincil uyum cezaları uygulamasına veya AB kara sularından geçişleri engellemesine yol açabilir.
+Kelimeler:
+• sheer depth = büyüklüğü, derinliği
+• secondary compliance penalties = ikincil uyum cezaları
+• territorial waters = kara suları</t>
+      </text>
+    </comment>
+    <comment ref="N63" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD anlaşması kapsamında satın alınan işlenmiş Rus ürünlerinin Avrupa sigortalı gemiler veya denizcilik altyapısı kullanılarak taşınıp taşınamayacağına ilişkin Avrupa Birliği açıklamaları.
+Kelimeler:
+• refined products = rafine/işlenmiş ürünler
+• insured vessels = sigortalı gemiler
+• maritime infrastructure = denizcilik altyapısı</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransa'dan sonra sırada İtalya mı var? Roma'nın bütçe açığı büyürken Goldman Sachs tahvil risklerine dikkat çekiyor
+Kelimeler:
+• flags bond risks = tahvil risklerine dikkat çekmek/işaret etmek
+• deficit widens = bütçe açığının büyümesi</t>
+      </text>
+    </comment>
+    <comment ref="D64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Goldman Sachs, Fransa'daki son mali çalkantının ardından İtalya'da genişleyen bütçe açıkları, yükselen tahvil getirileri ve siyasi istikrarsızlığın bir kamu borcu satış dalgasını tetikleme riski taşıdığı konusunda uyardı.
+Kelimeler:
+• cautioned = uyardı, ikaz etti
+• bond yields = tahvil getirileri
+• sovereign debt sell-off = kamu borcu/tahvili satış dalgası
+• fiscal turbulence = mali çalkantı</t>
+      </text>
+    </comment>
+    <comment ref="E64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kamu tahvili krizi
+Kelimeler:
+• sovereign bond = kamu tahvili, devlet tahvili</t>
+      </text>
+    </comment>
+    <comment ref="F64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: Euro Bölgesi krizi sırasında İtalya kamu borcundaki sıçrama
+2018: İtalyan popülist hükümetin Brüksel ile bütçe gerilimi
+Kelimeler:
+• spike = ani artış, sıçrama
+• standoff = anlaşmazlık, restleşme</t>
+      </text>
+    </comment>
+    <comment ref="G64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: İki ay içinde Başbakan Silvio Berlusconi istifa etti, yerini Mario Monti liderliğindeki teknokrat bir hükümet aldı ve bunu katı kemer sıkma politikaları ile ECB'nin 'ne gerekiyorsa yapılacak' güvencesi izledi.
+2018: Roma piyasa disiplinine boyun eğip resmi AB yaptırımlarından kaçınmak için açık hedeflerini düşürmeden önce, BTP-Bund faiz farkı dört ayda 150 baz puandan fazla açıldı.
+Kelimeler:
+• technocratic government = teknokratlar hükümeti
+• strict austerity = sıkı kemer sıkma politikası
+• backstop = güvence, arka destek
+• yielded to = boyun eğdi, teslim oldu</t>
+      </text>
+    </comment>
+    <comment ref="H64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, merkez bir üyenin mali şokunun ardından çevre Euro Bölgesi faiz farkları ne zaman açılsa, tahvil piyasaları 90 gün içinde Roma'nın mali disiplinini agresif bir şekilde sınamakta ve ülkeyi acil mali konsolidasyona veya Avrupa Merkez Bankası güvencelerine mecbur bırakmaktadır.
+Kelimeler:
+• peripheral Eurozone = çevre Euro Bölgesi (merkez dışı üyeler)
+• spreads widen = faiz farklarının açılması
+• fiscal consolidation = mali disiplin/konsolidasyon</t>
+      </text>
+    </comment>
+    <comment ref="I64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+10 yıllık BTP-Bund getiri farkının 40 ila 70 baz puan genişlemesi ve bunun Roma'yı, ECB'nin acil müdahalesini önlemek için 2027 bütçe açığı tahminlerini aşağı yönlü revize etmeye zorlaması muhtemel.
+Kelimeler:
+• yield spread = getiri farkı
+• revise downward = aşağı yönlü revize etmek
+• avert = önlemek, savuşturmak</t>
+      </text>
+    </comment>
+    <comment ref="K64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Avrupa Merkez Bankası, Roma'nın temel mali yönetişim kurallarına uyması koşuluyla, haksız piyasa parçalanmasına karşı koymak için artık İletim Koruma Aracı'na (TPI) sahiptir.
+Kelimeler:
+• unwarranted = haksız, gerekçesiz
+• market fragmentation = piyasa parçalanması
+• adheres to = bağlı kalmak, uymak</t>
+      </text>
+    </comment>
+    <comment ref="N64" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+10 yıllık BTP-Bund getiri farkının 200 baz puanı aşması ve Avrupa Komisyonu'ndan İtalya'nın çok yıllı mali gidişatına ilişkin resmi açıklamalar.
+Kelimeler:
+• basis points = baz puan
+• multi-year fiscal trajectory = çok yıllı mali gidişat/rota</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Man City'yi zehirli bir atmosfer ve belirsizlik bekliyor; sezonlarının bir önemi kalacak mı?
+Kelimeler:
+• toxicity = zehirlilik, toksik durum
+• uncertainty = belirsizlik
+• await = beklemek, karşısına çıkmak
+• matter = önem taşımak</t>
+      </text>
+    </comment>
+    <comment ref="D65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, Liverpool'a karşı oynayacağı Anfield mücadelesi öncesinde düşmanca bir atmosfer ve derin bir belirsizlikle karşı karşıya; çözüme kavuşmamış yasal suçlamalar ise sezonlarının meşruiyeti ve sonucu üzerine gölge düşürüyor.
+Kelimeler:
+• hostility = düşmanlık
+• clash = karşılaşma, mücadele
+• unresolved = çözülmemiş
+• charges = suçlamalar, ithamlar
+• casting a cloud over = üzerine gölge düşürmek
+• legitimacy = meşruiyet</t>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+finansal fair play duruşması
+Kelimeler:
+• hearing = duruşma, celse</t>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Manchester City'nin UEFA'dan aldığı iki yıllık Şampiyonlar Ligi men cezası bozuldu
+2022–2023: Juventus'un sahte muhasebe soruşturmaları ve puan silme cezası
+2006: Calciopoli skandalı kararları
+Kelimeler:
+• overturned = bozulmuş, iptal edilmiş
+• false accounting = sahte muhasebe, usulsüz muhasebe
+• deduction = kesinti, puan silme
+• verdicts = hükümler, nihai kararlar</t>
+      </text>
+    </comment>
+    <comment ref="G65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Beş ay sonra, Temmuz 2020'de, Spor Tahkim Mahkemesi (CAS), iddia edilen ihlallerin çoğunun kanıtlanmadığını veya zaman aşımına uğradığını tespit ederek yasağı kaldırdı ve City'nin ciddi bir sportif aksaklık yaşamadan yerel üstünlüğünü sürdürmesine izin verdi.
+2022–2023: Belirsizlik, beş ay boyunca saha içi performansları gözle görülür şekilde sekteye uğrattı; 10 puanlık silme cezası nihayetinde kulübü UEFA Şampiyonlar Ligi sıralamasının dışına itti ve yönetim istifalarını tetikledi.
+2006: İlk ifşaatların üzerinden iki ay geçmeden Juventus'un iki lig şampiyonluğu elinden alındı ve Serie B'ye düşürüldü; diğer birkaç kulüp ise lig hiyerarşisini yıllarca temelden yeniden yapılandıran ağır puan silme cezaları aldı.
+Kelimeler:
+• alleged breaches = iddia edilen ihlaller
+• time-barred = zaman aşımına uğramış
+• disruption = aksaklık, bozulma
+• triggered = tetikledi
+• revelations = ifşaatlar, ortaya çıkan gerçekler
+• stripped of = elinden alınmış, mahrum bırakılmış
+• relegated = küme düşürüldü</t>
+      </text>
+    </comment>
+    <comment ref="H65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçkin kulüpler sezon ortasında varoluşsal düzenleyici duruşmalarla karşılaştığında, uzayan yasal gecikmeler genellikle kısa vadede saha içi operasyonları korur; ancak kesinleşen yaptırımlar veya temyiz süreçleri, geçmişteki vakaların yaklaşık %70'inde nihayetinde ciddi bir sportif dikkat dağınıklığına yol açar.
+Kelimeler:
+• existential = varoluşsal
+• regulatory = düzenleyici, denetleyici
+• prolonged = uzun süren, uzatmalı
+• insulate = korumak, yalıtmak
+• definitive sanctions = kesinleşmiş yaptırımlar
+• inflict = uğratmak, yol açmak</t>
+      </text>
+    </comment>
+    <comment ref="I65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City'nin bağımsız tahkim yoluyla ilk sportif veya mali kararlara şiddetle itiraz etmesi; belirleyici puan silme cezalarını veya şampiyonluktan ihraçları mevcut rekabetçi sezon sona erene kadar geciktirmesi muhtemeldir.
+Kelimeler:
+• contest = itiraz etmek, karşı çıkmak
+• vigorously = şiddetle, güçlü bir biçimde
+• arbitration = tahkim
+• decisive = belirleyici, kesin
+• expulsions = ihraçlar, atılmalar</t>
+      </text>
+    </comment>
+    <comment ref="K65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Premier League suçlamalarının muazzam hacmi (100'den fazla) ve Avrupa mahkemelerine giden bir CAS temyiz yolunun bulunmaması, bağımsız bir Premier League komisyonundan çıkacak herhangi bir olumsuz kararın anında ve temyiz edilemez yerel sonuçlar doğuracağı anlamına geliyor.
+Kelimeler:
+• sheer volume = muazzam miktar, sırf hacmi bile
+• adverse verdict = olumsuz karar
+• unappealable = itiraz/temyiz edilemez
+• repercussions = yansımalar, olumsuz sonuçlar</t>
+      </text>
+    </comment>
+    <comment ref="N65" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geçici usul kararları, Pep Guardiola gibi kilit isimlerin kulüp güvencelerine ilişkin kamuoyu açıklamaları ve yasal dikkat dağınıklığına işaret eden ani kadro rotasyonları.
+Kelimeler:
+• interim procedural rulings = geçici usul kararları
+• assurances = güvenceler
+• squad rotation = kadro rotasyonu
+• hinting at = işaret eden, ima eden</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yuhalamalar, ızdırap ve tükenen inanç - baskı altındaki Carrick için 'endişe verici bir gün'
+Kelimeler:
+• boos = yuhalamalar
+• anguish = ızdırap, keder
+• fading belief = tükenen/azalan inanç
+• under-pressure = baskı altında olan</t>
+      </text>
+    </comment>
+    <comment ref="D66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester United menajeri Michael Carrick, 10 kişi kalan Tottenham'a karşı uzatma dakikalarında yedikleri beraberlik golüyle evlerinde 1-1 berabere kalmalarının ardından, giderek artan taraftar tepkisi ve tırmanan yönetim kurulu baskısıyla karşı karşıya.
+Kelimeler:
+• intensifying = yoğunlaşan, şiddetlenen
+• backlash = sert tepki
+• mounting = artan, biriken
+• conceded = kalesinde gördü, gol yedi
+• stoppage-time equalizer = uzatma dakikalarında gelen beraberlik golü</t>
+      </text>
+    </comment>
+    <comment ref="E66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+baskı altındaki teknik direktör</t>
+      </text>
+    </comment>
+    <comment ref="F66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2024: Erik ten Hag Manchester United tarafından görevden alındı
+Kasım 2021: Ole Gunnar Solskjaer Manchester United tarafından kovuldu
+Nisan 2014: David Moyes Manchester United tarafından görevden alındı
+Kelimeler:
+• dismissed = görevden alındı
+• sacked = kovuldu, işine son verildi</t>
+      </text>
+    </comment>
+    <comment ref="G66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2024: United, sözleşmesini uzattıktan altı aydan kısa bir süre sonra, Ekim 2024'ün sonlarında West Ham'a 2-1 mağlup olmasının ardından Ten Hag'ın görevine son verdi.
+Kasım 2021: Yönetim kurulu, Kasım 2021'in sonlarında Watford deplasmanındaki 4-1'lik hezimetin ardından 24 saat içinde Solskjaer'i görevden aldı.
+Nisan 2014: Moyes, UEFA Şampiyonlar Ligi'ne matematiksel olarak katılma ihtimali ortadan kalktığında altı yıllık sözleşmesinin sadece 10. ayında kovuldu.
+Kelimeler:
+• capitulation = teslimiyet, hezimet
+• mathematical qualification = matematiksel olarak hak kazanma</t>
+      </text>
+    </comment>
+    <comment ref="H66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2013 sonrası Manchester United'da, takımı sistematik son dakika çöküşlerinin yanı sıra kendi evinde açıkça yuhalanan her kalıcı teknik direktör 4 ila 8 hafta içinde görevden alındı (4 örnekte 4 kez: Moyes, Mourinho, Solskjaer, Ten Hag).
+Kelimeler:
+• permanent manager = asli/kalıcı teknik direktör
+• systemic = sistemik, yapısal
+• collapses = çöküşler
+• instances = örnekler, vakalar</t>
+      </text>
+    </comment>
+    <comment ref="I66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hemen peş peşe maçlar kazandığı bir galibiyet serisi yakalamadıkça Carrick'in kışı atlatması pek olası görünmüyor; sonuçlar keskin bir şekilde toparlanmazsa yılbaşından önce kovulması son derece muhtemel.
+Kelimeler:
+• survive = ayakta kalmak, atlatmak
+• winning streak = galibiyet serisi
+• turn of the year = yılbaşı, yeni yıl dönümü
+• rebound = toparlanmak, sıçrama yapmak</t>
+      </text>
+    </comment>
+    <comment ref="K66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 4 ila 6 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol yönetimi liderliği hemen göreve hazır bariz bir geçici veya kalıcı alternatife sahip değilse, Carrick'e Kasım milli arasına kadar uzatılmış bir ek süre tanıyabilir.
+Kelimeler:
+• executive leadership = yönetici kadrosu, üst yönetim
+• interim = geçici
+• replacement = yeni isim, halef
+• step in = devreye girmek, görevi devralmak
+• reprieve = mühlet, geçici erteleme</t>
+      </text>
+    </comment>
+    <comment ref="N66" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kulüp kaynaklarından gelen 'tam destek' açıklamaları (tarihsel olarak kovulmanın nihai habercisi) ve sonraki iki lig maçındaki oyuncu vücut dili.
+Kelimeler:
+• briefings = bilgilendirmeler, sızdırılan demeçler
+• precursor = öncül, haberci
+• sacking = kovulma, görevden alma
+• fixtures = karşılaşmalar, maçlar</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski OpenAI güvenlik lideri David Robinson 'bozulmuş' teknoloji kültürü konusunda uyardı
+Kelimeler:
+• safety lead = güvenlik lideri / sorumlusu
+• warn of = konusunda uyarmak
+• broken = bozulmuş, aksayan, çökmüş</t>
+      </text>
+    </comment>
+    <comment ref="D67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski OpenAI güvenlik lideri David Robinson, şirket içi kültürün bozulduğu ve güvenlik uygulamalarının ticari ürün lansmanlarının gerisinde bırakıldığı konusunda kamuoyunu uyararak şirketten istifa etti.
+Kelimeler:
+• resigned from = -den istifa etti
+• subordinated to = -in ardına atılmak, ikinci plana itilmek
+• commercial product launches = ticari ürün lansmanları / çıkışları</t>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+teknoloji güvenliği yöneticisi istifası</t>
+      </text>
+    </comment>
+    <comment ref="F67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mayıs 2024: Jan Leike, OpenAI Süperhizalama eş liderliğinden istifa etti
+Aralık 2020: Timnit Gebru, Google Etik Yapay Zekâ ekibinden kovuldu
+Eylül 2021: Frances Haugen, şirket içi Facebook belgelerini ifşa etti
+Kelimeler:
+• ousted from = -den kovulmuş, görevden uzaklaştırılmış
+• discloses = ifşa eder, açıklar</t>
+      </text>
+    </comment>
+    <comment ref="G67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mayıs 2024: OpenAI günler içinde özel Süperhizalama ekibini feshetti, kısa süreli olumsuz medya fırtınasını atlattı ve sonraki 12 ay boyunca sınır model sürümlerini hızlandırırken milyarlarca dolarlık yeni girişim sermayesi toplamaya devam etti.
+Aralık 2020: Şirket içi iş bırakma eylemlerine, kamuoyu tepkisine ve kongre soruşturmalarına rağmen Google, etik denetim mekanizmasını aylar içinde yeniden yapılandırdı ve ardından temel hizmetlerinde üretken yapay zekâ özelliklerini kullanıma sunma konusundaki kararlılığını ikiye katladı.
+Eylül 2021: Bu ifşalar çığır açan ABD Senatosu oturumlarını ve yoğun düzenleyici denetimini tetikledi; ancak Meta'nın ticari stratejisi ve temel ürün dağıtımı sonraki iki yıl boyunca temelde değişmeden kaldı.
+Kelimeler:
+• dissolved = feshetti, dağıttı
+• weathered = (zor bir durumu) atlattı, göğüs gerdi
+• frontier model = en gelişmiş yapay zekâ modeli (sınır model)
+• walkouts = iş bırakma eylemleri, protesto amacıyla ayrılmalar
+• doubled down on = bir konuda kararlılığını artırdı / ikiye katladı</t>
+      </text>
+    </comment>
+    <comment ref="H67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Teknoloji güvenliği liderlerinin yüksek profilli istifaları ve ihbarcı uyarıları, düzenli olarak kısa vadeli halkla ilişkiler krizlerini ve düzenleyici denetimleri tetikler; ancak geçmiş vakaların %90'ından fazlasında kurumsal yönetim, katı yasal yaptırımlarla zorlanmadığı sürece ticari dağıtım takvimlerini yavaşlatmadan gelen tepkileri göğüsler.
+Kelimeler:
+• whistleblower = kurum içi usulsüzlükleri ifşa eden kişi (ihbarcı)
+• scrutiny = ayrıntılı inceleme, sıkı denetim
+• absorbs the blowback = gelen tepkileri / ters tepkiyi göğüslemek
+• compelled by = -e zorlanmak</t>
+      </text>
+    </comment>
+    <comment ref="I67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+OpenAI güvenliğe yönelik kamuoyu taahhütleri yayımlayacak ve yasa koyucuların incelemeleriyle karşılaşacaktır; ancak ticari model sürümlerini yavaşlatmayacak veya üst düzey yönetimini kökten değiştirmeyecektir.
+Kelimeler:
+• commitments = taahhütler
+• lawmakers = yasa koyucular
+• alter = değiştirmek</t>
+      </text>
+    </comment>
+    <comment ref="K67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni düzenleyici rejimler kapsamındaki uygulama hükümleri (AB Yapay Zekâ Yasası veya daha sıkı ABD ihracat ve güvenlik raporlama zorunlulukları gibi), eski güvenlik liderlerinin mevzuata uyum ihlallerine dair kanıtlarla düzenleyiciler önünde ifade vermesi durumunda OpenAI'ı doğrudan yasal sorumluluğa maruz bırakabilir.
+Kelimeler:
+• enforcement provisions = yaptırım / uygulama hükümleri
+• mandates = yasal zorunluluklar, talimatlar
+• statutory liability = kanuni / yasal sorumluluk
+• compliance violations = mevzuata uyum ihlalleri</t>
+      </text>
+    </comment>
+    <comment ref="N67" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD kongre komitelerinden celpler, diğer kıdemli hizalama araştırmacılarından eşgüdümlü istifalar veya katı güvenlik sertifikaları talep eden kurumsal müşteriler arasındaki müşteri kayıpları.
+Kelimeler:
+• subpoenas = mahkeme / komite celpleri
+• alignment = hizalama (yapay zekânın insan değerleriyle uyumu)
+• defections = ayrılmalar, saf değiştirmeler, müşteri kayıpları</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları atom saatlerini demode kılabilecek bir nükleer saat üretti
+Kelimeler:
+• nuclear clock = nükleer saat
+• make obsolete = kullanım dışı / demode bırakmak</t>
+      </text>
+    </comment>
+    <comment ref="D68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Viyana'daki fizikçiler, toryum-229 geçişlerine dayanan ilk kendiliğinden kararlı nükleer saati geliştirerek zaman ölçümünde bir çığır açtı ve potansiyel olarak modern atom saatlerinin çok ötesinde bir hassasiyet sundu.
+Kelimeler:
+• breakthrough = çığır açan gelişme, büyük buluş
+• timekeeping = zaman ölçümü
+• self-stabilizing = kendi kendini dengeleyen / kararlı kılan
+• precision = hassasiyet, doğruluk</t>
+      </text>
+    </comment>
+    <comment ref="E68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+fiziksel metrolojide çığır açıcı gelişme</t>
+      </text>
+    </comment>
+    <comment ref="F68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000'lerin ortası - 2015: Optik örgü saatlerinin geliştirilmesi ve olgunlaşması
+1955: Louis Essen ilk pratik sezyum atom saatini inşa etti
+Kelimeler:
+• optical lattice = optik örgü
+• maturation = olgunlaşma, yetkinleşme</t>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000'lerin ortası - 2015: Laboratuvar karşılaştırmalarında çok daha üstün olduğunu kanıtlamasına rağmen, Uluslararası Ağırlıklar ve Ölçüler Bürosu'nun (BIPM) karşılaştırma protokollerini oluşturması on yıldan uzun sürdü ve resmi SI saniyesi yeniden tanımlamasını ancak 2030 yılına —ilk konsept kanıtından yaklaşık 25 yıl sonrasına— planlayabildi.
+1955: Ağırlıklar ve Ölçüler Genel Konferansı'nın (CGPM) 1967'de sezyum kullanarak SI saniyesini resmen yeniden tanımlamasından önce, uluslararası laboratuvarlar arası 12 yıllık doğrulama ve antlaşma müzakereleri gerekti.
+Kelimeler:
+• benchmarks = performans kriterleri / kıyaslama testleri
+• proof of concept = konsept kanıtı (fikrin işlerliğinin kanıtı)
+• cross-laboratory validation = laboratuvarlar arası doğrulama</t>
+      </text>
+    </comment>
+    <comment ref="H68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gelecek nesil fiziksel frekans standartlarının laboratuvar gösterimleri uzun bir operasyonel gecikmeyle karşılaşır; tarihsel olarak, titiz uluslararası çapraz karşılaştırmalar ve altyapı uyumluluk gereksinimleri nedeniyle, ilk çalışan prototipten yerleşik küresel metroloji standartlarının yerine geçişe kadar 12 ila 25 yıl gerekmektedir.
+Kelimeler:
+• operational lag = operasyonel gecikme / zaman farkı
+• rigorous = titiz, sıkı, tavizsiz
+• infrastructure compatibility = altyapı uyumluluğu</t>
+      </text>
+    </comment>
+    <comment ref="I68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nükleer saat, özel laboratuvar fiziği testleri için (karanlık madde arayışı ve temel sabitlerdeki değişimler gibi) hızla konuşlandırılacak; ancak önümüzdeki on yıl içinde ticari ağlarda, GPS uydularında veya uluslararası SI tanımlarında atom saatlerinin yerini almayacaktır.
+Kelimeler:
+• deployed = konuşlandırılmış, uygulamaya geçirilmiş
+• dark matter = karanlık madde
+• fundamental constants = temel (fiziksel) sabitler</t>
+      </text>
+    </comment>
+    <comment ref="K68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 10-15 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Toryum nükleer geçişleri dış elektron kabukları yerine çekirdeğin içinde gerçekleştiğinden, nükleer saatlerin hassas optik örgü saatlerine kıyasla çok daha dayanıklı ve taşınabilir olduğu görülebilir; bu da havacılık, uzay ve savunma alanlarındaki niş benimsenmeyi potansiyel olarak hızlandırabilir.
+Kelimeler:
+• nucleus = çekirdek
+• rugged = dayanıklı, zorlu koşullara uygun
+• delicate = hassas, narin
+• niche adoption = belirli/niş alanlarda benimsenme</t>
+      </text>
+    </comment>
+    <comment ref="N68" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Stabilizasyon mekanizmasının laboratuvarlar arası bağımsız replikasyonu, çip ölçekli lazer platformlarına minyatürizasyonu ve Zaman ve Frekans Danışma Komitesi (CCTF) tarafından resmi olarak değerlendirilmesi.
+Kelimeler:
+• replication = aynısını yapma, yeniden üretme (deneyi tekrarlama)
+• miniaturization = minyatürleştirme, boyutları küçültme
+• chip-scale = çip ölçeğinde</t>
       </text>
     </comment>
   </commentList>
@@ -5603,7 +7053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10301,6 +11751,1126 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Imposes Sweeping Sanctions on International Criminal Court</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. announced sweeping sanctions against the International Criminal Court, with Secretary of State Marco Rubio vowing to dismantle the permanent war crimes tribunal.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>sanctions</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2020: United States sanctions against the International Criminal Court</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2020: The Biden administration lifted the sanctions in April 2021 after determining the measures were inappropriate and ineffective, though tensions remained.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Sanctions against international bodies like the ICC trigger immediate international condemnation and legal challenges, but often face reversals or softening under subsequent administrations or when practical international cooperation is required.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>The ICC will likely continue its investigations despite financial blockades, while European allies attempt to mediate or shield court personnel from U.S. measures.</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>The scope of current geopolitical alignments regarding active conflicts in Europe and the Middle East creates a more polarized diplomatic environment.</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Statements from European Union foreign ministers regarding compliance or pushback against U.S. financial restrictions.</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/10/nx-s1-5996606/u-s-imposes-sweeping-sanctions-on-international-criminal-court</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Executive_Order_14203</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Justice Dept. Is Investigating TV Networks Over Trump Pool Coverage</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>The Justice Department notified major TV networks that it is examining whether they violated antitrust laws when they suspended pool coverage of President Trump following restricted access.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>antitrust investigation</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1972: White House Nixon administration antitrust suit against the Los Angeles Times and Washington Post</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1972: The legal challenges stalled or failed in court as freedom of the press protections under the First Amendment held strong, though it significantly chilled administration-media relations.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Investigations of media companies initiated by the executive branch over press coverage routinely face severe constitutional hurdles in federal courts and rarely result in successful antitrust penalties.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>The networks will challenge the DOJ's jurisdiction and motivation in court, dragging the process out through protracted litigation with a high likelihood of dismissal.</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Modern interpretations of antitrust law and digital media distribution models offer new legal avenues for regulatory bodies to explore.</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Motions to quash subpoenas filed by network legal teams in federal district court.</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/10/business/media/trump-justice-department-tv-networks.html</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Statement_on_Chemical_and_Biological_Defense_Policies_and_Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Brigham nurses postpone strike to vote on hospital's latest contract offer</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Nurses at Brigham and Women's Hospital represented by the Massachusetts Nurses Association postponed a planned strike after receiving an updated contract proposal from Mass General Brigham. The union leadership paused the walkout to put the hospital's latest offer to a full membership vote.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>strike postponement and contract ratification vote</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2016: Brigham and Women's Hospital 2016 nurse contract settlement
+2023: 2023 New York City nursing strike tentative agreements
+2021: Saint Vincent Hospital nurses strike</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2016: Negotiators reached a tentative agreement less than 48 hours before the walkout, the strike was averted, and members ratified the three-year contract by a wide margin one week later.
+2023: Facilities such as NewYork-Presbyterian postponed and called off strikes just before the deadline after reaching tentative pacts, which were promptly ratified by over 80% margins.
+2021: The strike lasted 301 days, costing the hospital tens of millions of dollars and inflicting deep financial strain on the union before finally resolving, underscoring the enormous incentive for both parties to settle when an offer is close.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>In labor relations, when a union bargaining committee formally suspends an impending strike to present management's offer to the general membership, it signals that core threshold demands have been met. Historically, approximately 85% to 90% of healthcare strike votes held under postponed walkout notices result in contract ratification.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>The Brigham nurses are highly likely to vote to approve the contract, officially averting the strike and locking in a multi-year labor pact with Mass General Brigham.</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 2 weeks</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Severe post-pandemic staffing fatigue and cumulative inflation pressures may lead rank-and-file nurses to reject the deal if wage and patient-ratio concessions are viewed as insufficient compromises by leadership.</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Statements from MNA bargaining committee leaders explicitly recommending a 'yes' vote, attendance numbers at informational sessions, and early voter turnout figures.</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPZUtfRUVqQ2hZMjhVUmY2bDlVTkpjcnZKclVuOEFoUm1EWVljenFKMWJvOGg2NTdkOER1UC1hcllablpmTWdjSG03Ry1vTDZlQW55eENfREt4ZlVhUEN6TnRVVXRPUWxocndQYk1fN0d2ZUR0aE41NW5xaXJqYmtodHNvMHMzbWt2dkFBVGNocG1wa00tczNPcE0xSVFTQdIBpgFBVV95cUxPVjdIVko4LWQzWmFhZVUtYTltWEt1cjlHVWxLd2dRUjNyQzZuM3ZoVlc3UERYVS1HV2tGNVJMLU51WHExc0VjcWxNSnV2UXA3cGVvTWlndEhsTHp5R0VReWZvM1lQLUxPVTVZRGpSQ2VmYTZuOUEwRUNWZGxyZl9Id3hxVEVxdjFrRVNjNVZVd01xcU5Qd09LYUdkSjFVZFE2ZGVXekZB?oc=5</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Brigham_and_Women's_Hospital
+https://en.wikipedia.org/wiki/2026_New_York_City_nurses_strike
+https://en.wikipedia.org/wiki/2021%E2%80%932022_Saint_Vincent_Hospital_strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Former Stoughton police officer Matthew Farwell goes on trial for Sandra Birchmore killing</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Former Stoughton police officer Matthew Farwell faces trial in federal court for the murder of Sandra Birchmore, whom he allegedly groomed as a minor and killed to prevent her from exposing his paternity and abuse.</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>federal criminal trial of a law enforcement officer</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2021: Initial local investigation into the death of Sandra Birchmore
+2015: Federal prosecution in the killing of Walter Scott
+2021: Federal civil rights trial of Derek Chauvin and Minneapolis officers</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>2021: Federal investigators took over the probe, uncovered extensive digital evidence, and indicted Farwell in 2024 for witness tampering resulting in death, prompting state reviews into local department oversight.
+2015: Faced with insurmountable federal forensic evidence, Slager pleaded guilty to federal civil rights deprivation under color of law in May 2017 and was sentenced to 20 years in federal prison.
+2021: Chauvin pleaded guilty to federal charges in December 2021 to avoid further trial risks, and all three co-defendants were convicted by a federal jury in February 2022.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Federal prosecutions against law enforcement officers for life-qualifying felony charges (such as witness tampering resulting in death under 18 U.S.C. § 1512) carry a conviction rate exceeding 90% via plea or trial verdict. The Department of Justice rarely brings these cases without extensive forensic and digital trails that survive rigorous judicial scrutiny.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Farwell faces an extremely high likelihood of conviction or a negotiated plea to avoid life imprisonment without parole, which will accelerate wider institutional reviews and civil lawsuits against the Stoughton Police Department.</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Because the initial death scene was compromised and originally classified as a suicide by local investigators, defense attorneys will aggressively exploit gaps in early chain-of-custody and physical evidence to create reasonable doubt.</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Pre-trial rulings on cell phone geolocation and metadata admissibility, testimony from independent medical examiners, and potential plea negotiations as the trial date approaches.</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPVUZMWTZEaGRMd3Q5MnMyOC1uRkJPWHdHbzFmcXpJd1psYmxxYklZeTJGZF9vcVV5VjdUOXp5c0JxZWk4TGZvdUMyZWtGSGgwLTFpU3JvRWdrZVdnN0p3WXAxNURfWmM0UEFnNWVPbExxMVZjWlVkTmFaZDNaZFIxTTJKNnNSZlZKNHRwR3pqNS1obG5oWlhfLWRHdHVXRWVhcW0zaWl2ZHNFVDFWUnNaYmpvNzFXZngyMWsxdzZOVTkzZ2FTNGkxUTdUcVZpeWd3MVBoT0RrNzBXMGdyakHSAeMBQVVfeXFMTk9IZzlKa1RSSzU2cjBLcEJNWGlCYnlSVC1DS3dabzlxWUpYc1R6bFE5S3VrWEJnWjN2c09Lc3Qzdk9aS29nUVRoSnFIVlZKV0x3eU1CaEk4MHN4dDVIZHBoNjJCcUFldDlObG10QUQtT1JGdDRleFBlYTMyUG5mWXMxaU9VcmxJWFV5cVlSWHUtNFBTYUdpbXFlMGVYMU95ZmRrem5JdTZ2ZkE2Yl9WTTVMd0dFbDltWEpIYWt5dGhYMUxHY2pQTGQ5SFZveU5GcEZoUE1KdS1hOUt6ZUZqWWw4RGc?oc=5</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Killing_of_Sandra_Birchmore
+https://en.wikipedia.org/wiki/Killing_of_Walter_Scott
+https://en.wikipedia.org/wiki/Derek_Chauvin</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Riyadh airport attack another dangerous moment in already tense conflict</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Houthi forces launched an attack targeting Riyadh's airport, stepping up strikes on Saudi Arabian territory and threatening the kingdom's transport hubs.</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>cross-border airport strike</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>November 4, 2017: 2017 Riyadh missile strike
+June 12, 2019: 2019 Abha International Airport attack
+January 17, 2022: 2022 Abu Dhabi attack</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>November 4, 2017: Within 48 hours, the Saudi-led coalition launched heavy retaliatory airstrikes on Sanaa and imposed a total air, sea, and land blockade on Yemen.
+June 12, 2019: Saudi coalition aircraft carried out retaliatory airstrikes against Houthi launch and radar sites within 48 hours, while Houthi drone raids against regional airports continued for the next two months.
+January 17, 2022: The Saudi-led coalition initiated intense airstrikes across Yemen over the following week; the sharp escalation galvanized international diplomacy that produced a UN-brokered nationwide truce within 10 weeks.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of 5 major Houthi attacks against Gulf aviation and infrastructure hubs between 2017 and 2022, the coalition launched military retaliatory strikes within 72 hours, while elevated commercial risks accelerated intense backchannel diplomatic negotiations within 3 months.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia is likely to conduct targeted retaliatory strikes or air defense interdictions against Houthi launch capabilities while urgently pursuing backchannel diplomatic talks to safeguard commercial aviation and investment stability.</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>75-85%</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 3 months</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia's 2023 rapprochement with Iran and its prioritization of domestic Vision 2030 projects make Riyadh far more reluctant to re-enter a sustained, open-ended bombing campaign than in 2017 or 2019.</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Statements from Tehran regarding regional mediation, temporary flight diversions away from central Saudi airspace, and coalition air defense deployments around Riyadh.</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cr4g1pwxxlq1o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_Riyadh_missile_strike
+https://en.wikipedia.org/wiki/2019_Abha_International_Airport_attacks
+https://en.wikipedia.org/wiki/2022_Abu_Dhabi_attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Nobel peace laureate says US sanctions on ICC 'unacceptable'</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Former UN human rights chief Navi Pillay condemned sweeping US sanctions imposed on the International Criminal Court by the Trump administration as unheard of and unacceptable.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>sanctions on international tribunal</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>June 11, 2020: Executive Order 13928 sanctions against ICC officials
+August 2, 2002: Enactment of the American Service-Members' Protection Act</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>June 11, 2020: The ICC faced banking disruptions and condemned the moves, but continued its caseload until the Biden administration rescinded the executive order 10 months later in April 2021 without the ICC renouncing its jurisdiction.
+August 2, 2002: Washington secured nearly 100 bilateral immunity agreements under pressure, but Congress rolled back foreign aid penalties between 2006 and 2008 after concluding the sanctions damaged strategic security alliances.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>In previous rounds of US statutory and executive sanctions against the ICC, the measures caused administrative disruption and travel restrictions for court officials, but in zero instances did the tribunal permanently drop its investigations or dissolve its mandate, with US measures ultimately being modified or rescinded within several years.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>The International Criminal Court will maintain its active investigations and warrants, shifting banking and operational logistics to European and non-dollar jurisdictions while allied ICC member states introduce legal shields against US extraterritorial penalties.</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>80-90%</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>If secondary sanctions are aggressively applied to commercial banks or European software vendors servicing the ICC, operational paralysis could be significantly more severe than during the 2020 executive order.</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>European Union discussions on invoking the EU Blocking Statute to protect ICC staff, and legal challenges to the executive order filed in US federal district courts.</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cqkgjrpmr47vo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_executive_orders_in_the_first_Trump_presidency
+https://en.wikipedia.org/wiki/American_Service-Members'_Protection_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Job seekers face longer unemployment as benefit exhaustion rates climb</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Displaced workers in the U.S. are experiencing extended periods of joblessness, with roughly 40 percent exhausting their standard state unemployment insurance benefits before securing employment.</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>labor market slowdown</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2002-2003: Early 2000s jobless recovery and benefit exhaustion
+2007-2008: Rising unemployment duration leading into the Great Recession
+1991-1992: Post-1990 recession search duration surge</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2002-2003: Federal policymakers enacted and repeatedly extended the Temporary Extended Unemployment Compensation (TEUC) program, while payroll hiring remained subdued for nearly two years until late 2003.
+2007-2008: Congress enacted emergency federal extensions in June 2008 under EUC08, and the broader unemployment rate accelerated upward over the following 12 to 18 months.
+1991-1992: Extended benefits were authorized federally in late 1991, and significant consumer confidence drops pressured incumbent political leadership ahead of the 1992 election.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Historically, in 4 out of 5 instances where U.S. benefit exhaustion rates exceed 35-40%, the broader labor market faces sustained wage deceleration and hiring freezes for an additional 6 to 18 months, prompting congressional calls for federal unemployment extensions.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Hiring momentum is likely to remain sluggish, pushing median job search durations higher and increasing political pressure on Congress to fund extended unemployment compensation.</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Post-pandemic structural labor shortages in healthcare and trades, along with remote work flexibility, could prevent total employment levels from collapsing compared to previous deep recessions.</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>The BLS median duration of unemployment metric surpassing 20 weeks, continuing claims exceeding 2 million, and bipartisan legislative proposals for emergency federal benefit extensions.</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/11/nx-s1-5995238/jobs-employment-economy-unemployment-benefits</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Early_2000s_recession
+https://en.wikipedia.org/wiki/Unemployment_extension
+https://en.wikipedia.org/wiki/Early_1990s_recession</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Trump announces deal for Russian diesel as Zelensky calls it a gift to Putin</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>The Trump administration announced an agreement to purchase Russian refined diesel to alleviate soaring domestic fuel prices, drawing fierce condemnation from Ukrainian President Volodymyr Zelensky.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>energy sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1981: Reagan lifts the Soviet grain embargo
+2022: G7 implementation of the Russian oil price cap</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1981: Bilateral trade resumed immediately despite heightened Cold War rhetoric, and the Soviet Union secured cheap food while political friction between Washington and European allies worsened over perceived US inconsistency.
+2022: Global fuel price spikes moderated within three months, but Russia sustained its refined fuel revenues via sanction arbitrage and shadow fleet operations, leaving the underlying war fully funded.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>In 8 of 10 major geopolitical trade standoffs involving critical global commodities (energy, food), domestic consumer inflation pressures compel Western leaders to introduce waivers or bilateral trade exemptions, diluting multilateral sanctions coalitions.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>The procurement deal is likely to cause immediate political fractures across the Western alliance and embolden Moscow to seek broader sanctions relief, while providing only temporary, modest relief to retail diesel prices.</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>The sheer depth of existing sanctions and European resistance may lead European allies to impose secondary compliance penalties or block transit through EU territorial waters.</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>European Union statements on whether refined Russian products purchased under the US agreement can be transported using European-insured vessels or maritime infrastructure.</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cm1dwgr666wno?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_States_grain_embargo_against_the_Soviet_Union
+https://en.wikipedia.org/wiki/2022_Russian_crude_oil_price_cap_sanctions</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>After France, is Italy next? Goldman Sachs flags bond risks as Rome's deficit widens</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs cautioned that widening deficits, higher bond yields, and political instability in Italy threaten to spark a sovereign debt sell-off following recent fiscal turbulence in France.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>sovereign bond crisis</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2011: Italian sovereign debt spike during the Eurozone crisis
+2018: Italian populist budget standoff with Brussels</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2011: Within two months, Prime Minister Silvio Berlusconi resigned, replaced by a technocratic government under Mario Monti, followed by strict austerity and the ECB's 'whatever it takes' backstop.
+2018: The BTP-Bund spread widened by more than 150 basis points over four months before Rome yielded to market discipline and lowered its deficit targets to avoid formal EU sanctions.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Historically, whenever peripheral Eurozone spreads widen following a core member's fiscal shock, bond markets aggressively test Rome's fiscal discipline within 90 days, forcing either emergency fiscal consolidation or European Central Bank backstops.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>The 10-year BTP-Bund yield spread is likely to widen by 40 to 70 basis points, forcing Rome to revise its 2027 deficit projections downward to avert an emergency intervention by the ECB.</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>The European Central Bank now has the Transmission Protection Instrument (TPI) in place to counter unwarranted market fragmentation, provided Rome adheres to baseline fiscal governance.</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>The 10-year BTP-Bund yield spread crossing 200 basis points and formal commentary from the European Commission regarding Italy's multi-year fiscal trajectory.</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.co.uk/2026/10/11/italy-government-bonds-sovereign-debt-giorgia-meloni.html</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Eurozone_crisis
+https://en.wikipedia.org/wiki/2018_Italian_government_formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Toxicity and uncertainty await Man City - will their season even matter?</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City face an atmosphere of hostility and deep uncertainty ahead of their Anfield clash against Liverpool, with unresolved legal charges casting a cloud over the legitimacy and outcome of their campaign.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>financial fair play hearing</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2020: UEFA two-year Champions League ban overturned for Manchester City
+2022–2023: Juventus false accounting investigations and points deduction
+2006: Calciopoli scandal verdicts</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>2020: Five months later in July 2020, the Court of Arbitration for Sport (CAS) overturned the ban, finding most alleged breaches either unproven or time-barred, allowing City to maintain domestic dominance without severe sporting disruption.
+2022–2023: The uncertainty visibly disrupted on-pitch performances across five months; a 10-point deduction ultimately dropped the club out of the UEFA Champions League places and triggered leadership resignations.
+2006: Within two months of initial revelations, Juventus were stripped of two league titles and relegated to Serie B, while several other clubs received heavy points deductions that fundamentally restructured the league hierarchy for years.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>When elite clubs face existential regulatory hearings mid-season, prolonged legal delays typically insulate on-pitch operations in the short term, but definitive sanctions or appeals processes ultimately inflict severe sporting distraction in roughly 70% of historical cases.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City are likely to contest any initial sporting or financial verdict vigorously through independent arbitration, delaying decisive point deductions or title expulsions until after the current competitive season concludes.</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>The sheer volume (over 100) of Premier League charges and absence of a CAS appeal route to European courts means any adverse verdict from an independent Premier League commission will have immediate and unappealable domestic repercussions.</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Interim procedural rulings, public comments from key figures like Pep Guardiola regarding club assurances, and any sudden squad rotation hinting at legal distraction.</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cvy0rp14xz7lo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Manchester_City_F.C.
+https://en.wikipedia.org/wiki/2022%E2%80%9323_Juventus_FC_season
+https://en.wikipedia.org/wiki/Calciopoli</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Boos, anguish &amp; fading belief - 'worrying day' for under-pressure Carrick</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Manchester United manager Michael Carrick faces intensifying fan backlash and mounting board pressure following a 1-1 home draw against 10-man Tottenham, having conceded a stoppage-time equalizer.</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>manager under pressure</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>October 2024: Erik ten Hag dismissed by Manchester United
+November 2021: Ole Gunnar Solskjaer sacked by Manchester United
+April 2014: David Moyes dismissed by Manchester United</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>October 2024: United dismissed Ten Hag in late October 2024 after a 2-1 defeat to West Ham, less than six months after extending his contract.
+November 2021: The board dismissed Solskjaer within 24 hours of a 4-1 capitulation away at Watford in late November 2021.
+April 2014: Moyes was sacked just 10 months into a six-year contract once mathematical qualification for the UEFA Champions League became impossible.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>At Manchester United post-2013, every permanent manager whose side has suffered open home boos alongside systemic late-game collapses has been dismissed within 4 to 8 weeks (4 out of 4 instances: Moyes, Mourinho, Solskjaer, Ten Hag).</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Carrick is unlikely to survive through the winter unless he delivers an immediate multi-game winning streak; a dismissal before the turn of the year is highly probable if results do not sharply rebound.</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>next 4 to 6 weeks</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>If the football executive leadership lacks an obvious interim or permanent replacement ready to step in immediately, they may grant Carrick an extended reprieve until the November international break.</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Briefings from club sources expressing 'full support' (historically the final precursor to sacking) and player body language in the next two domestic fixtures.</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c62e9g09e781o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Erik_ten_Hag
+https://en.wikipedia.org/wiki/Ole_Gunnar_Solskj%C3%A6r
+https://en.wikipedia.org/wiki/David_Moyes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Ex-OpenAI safety lead David Robinson warns of 'broken' tech culture</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Former OpenAI safety lead David Robinson resigned from the company, publicly warning that internal culture is broken and that safety practices are being subordinated to commercial product launches.</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>tech safety executive resignation</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>May 2024: Jan Leike resigns as OpenAI Superalignment co-lead
+December 2020: Timnit Gebru ousted from Google Ethical AI team
+September 2021: Frances Haugen discloses internal Facebook files</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>May 2024: OpenAI dissolved the dedicated Superalignment team within days, weathered a short wave of negative media coverage, and proceeded to raise billions in fresh venture capital while accelerating frontier model releases over the subsequent 12 months.
+December 2020: Despite internal walkouts, public outcry, and congressional inquiries, Google reorganized its ethics oversight within months and subsequently doubled down on rolling out generative AI features across its core services.
+September 2021: The disclosures triggered landmark US Senate hearings and intense regulatory scrutiny, but Meta's commercial strategy and core product deployment remained fundamentally unchanged over the following two years.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High-profile resignations and whistleblower warnings from tech safety leaders consistently trigger short-term PR crises and regulatory scrutiny, but in over 90% of past cases, corporate leadership absorbs the blowback without slowing down commercial deployment schedules unless compelled by hard legal sanctions.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI will issue public commitments to safety and face scrutiny from lawmakers, but will not slow down its commercial model releases or fundamentally alter executive governance.</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>next 6-12 months</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Enforcement provisions under new regulatory regimes (such as the EU AI Act or stricter US export and safety reporting mandates) could expose OpenAI to direct statutory liability if former safety leads testify before regulators with evidence of compliance violations.</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Subpoenas from US congressional committees, coordinated resignations from other senior alignment researchers, or customer defections among enterprise clients requiring strict safety certifications.</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/10/nx-s1-5992872/ex-openai-safety-lead-david-robinson-warns-of-broken-tech-culture</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/OpenAI
+https://en.wikipedia.org/wiki/Timnit_Gebru
+https://en.wikipedia.org/wiki/Frances_Haugen</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Scientists build a nuclear clock that could make atomic clocks obsolete</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Physicists in Vienna achieved a breakthrough in timekeeping by developing the first self-stabilizing nuclear clock based on thorium-229 transitions, potentially delivering precision far beyond modern atomic clocks.</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>breakthrough in physical metrology</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Mid-2000s to 2015: Development and maturation of optical lattice clocks
+1955: Louis Essen builds the first practical cesium atomic clock</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Mid-2000s to 2015: Despite proving far superior in laboratory benchmarks, the International Bureau of Weights and Measures (BIPM) took over a decade to establish comparison protocols, scheduling the formal SI second redefinition only for 2030—roughly 25 years after initial proof of concept.
+1955: It required 12 years of international cross-laboratory validation and treaty negotiations before the General Conference on Weights and Measures (CGPM) officially redefined the SI second using cesium in 1967.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory demonstrations of next-generation physical frequency standards face a long operational lag; historically, transitioning from an initial working prototype to replacing established global metrology standards requires 12 to 25 years due to rigorous international cross-comparison and infrastructure compatibility requirements.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>The nuclear clock will be rapidly deployed for specialized laboratory physics tests (such as searching for dark matter and variations in fundamental constants), but it will not replace atomic clocks in commercial networks, GPS satellites, or international SI definitions within the next decade.</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>next 10-15 years</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Because thorium nuclear transitions occur inside the nucleus rather than outer electron shells, nuclear clocks may prove far more rugged and portable than delicate optical lattice clocks, potentially speeding up niche adoption in aerospace and defense.</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Independent cross-laboratory replication of the stabilization mechanism, miniaturization into chip-scale laser platforms, and formal evaluation by the Consultative Committee for Time and Frequency (CCTF).</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261008102701.htm</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Atomic_clock
+https://en.wikipedia.org/wiki/Atomic_clock</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -6758,6 +6758,1581 @@
 • replication = aynısını yapma, yeniden üretme (deneyi tekrarlama)
 • miniaturization = minyatürleştirme, boyutları küçültme
 • chip-scale = çip ölçeğinde</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal ajanlar, ara seçimler öncesinde Temsilciler Meclisi Üyesi Ilhan Omar'ın evinde arama yaptı
+Kelimeler:
+• search = arama yapmak
+• ahead of = öncesinde, -den önce
+• midterm elections = ara seçimler</t>
+      </text>
+    </comment>
+    <comment ref="D69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal göçmenlik bürosu ajanları, Demokrat Temsilciler Meclisi Üyesi Ilhan Omar'ın Minneapolis'teki konutunda bir arama emrini uygulayarak kutular dolusu materyale el koydu. Arama, Adalet Bakanlığı'nın siyasi figürlere yönelik aleni kolluk kuvveti eylemlerinden genellikle kaçındığı geleneksel 60 günlük yazılı olmayan süreç içinde gerçekleşti.
+Kelimeler:
+• executed a search warrant = arama emrini uygulamak/infaz etmek
+• seizing = el koyarak, müsadere ederek
+• overt = aleni, açık
+• law enforcement = kolluk kuvveti, yasa uygulama
+• unwritten window = yazılı olmayan süre/aralık</t>
+      </text>
+    </comment>
+    <comment ref="E69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+görevdeki bir Kongre üyesine yönelik uygulanan federal arama emri
+Kelimeler:
+• search warrant = arama emri
+• sitting member = görevdeki üye</t>
+      </text>
+    </comment>
+    <comment ref="F69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2006: Ara seçimlerden üç hafta önce Temsilciler Meclisi Üyesi Curt Weldon'ın çalışma arkadaşlarına yönelik FBI baskınları
+Mayıs 2006: Temsilciler Meclisi Üyesi William J. Jefferson'ın Kongre ofisinde yapılan FBI araması
+Ocak 2022: Temsilciler Meclisi Üyesi Henry Cuellar'ın evi ve seçim kampanyası ofisinde yapılan FBI araması
+Kelimeler:
+• raids = baskınlar
+• associates = iş/çalışma arkadaşları, ortaklar
+• campaign office = seçim kampanyası ofisi</t>
+      </text>
+    </comment>
+    <comment ref="G69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2006: Üç hafta içinde kamuoyundaki tepkiler, 10 dönemdir görevde olan Cumhuriyetçi vekilin anketlerdeki üstünlüğünü sildi ve Kasım 2006 ara seçimlerinde koltuğunu Demokrat Joe Sestak'a kaybetmesine yol açtı.
+Mayıs 2006: İki partiden Temsilciler Meclisi liderliği, baskına yürütmenin yetki aşımı olduğu gerekçesiyle itiraz etti ve D.C. Temyiz Mahkemesi 2007'de el koymanın Anayasa'nın Yasama Dokunulmazlığı (Speech or Debate) Maddesi'ni ihlal ettiğine hükmetti.
+Ocak 2022: Cuellar, yoğun siyasi incelemeye rağmen hem ön seçimleri hem de genel seçimleri kazandı; resmi federal suçlamalar ise iki yılı aşkın bir süre sonra, ancak Mayıs 2024'te yöneltildi.
+Kelimeler:
+• public fallout = kamuoyu tepkisi, olumsuz yankı
+• incumbent = görevdeki makam sahibi
+• executive overreach = yürütmenin yetki aşımı
+• Speech or Debate Clause = Yasama Dokunulmazlığı Maddesi
+• scrutiny = yakın inceleme, denetim</t>
+      </text>
+    </comment>
+    <comment ref="H69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern ABD tarihinde, bir seçime haftalar kala görevdeki yasa koyuculara yönelik aleni federal aramalar; mahkemelerin yürütme organının saiklerini titizlikle incelemesiyle birlikte derhal kuvvetler ayrılığına dayalı hukuki itirazları ve siyasi amaçla silah olarak kullanılma yönünde sert suçlamaları tetikler.
+Kelimeler:
+• separation-of-powers = kuvvetler ayrılığı
+• political weaponization = siyasi amaçla silah olarak kullanma
+• scrutinizing = titizlikle inceleme
+• motives = saikler, amaçlar</t>
+      </text>
+    </comment>
+    <comment ref="I69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Omar'ın savunması, el konulan dosyaları mühürletmek veya delil olarak kullanılmasını engellemek amacıyla Dördüncü Değişiklik ve Yasama Dokunulmazlığı güvenceleri kapsamında agresif hukuki itirazlarda bulunacak; Kongre'deki Demokratlar ise Adalet Bakanlığı'nın seçim dönemi müdahale etmeme protokollerini ihlal edip etmediğine dair resmi denetim soruşturmaları başlatacaktır.
+Kelimeler:
+• mount legal challenges = hukuki itirazlar yöneltmek
+• seal or suppress = gizlilik kararı aldırmak veya delil dışı bırakmak
+• oversight inquiries = denetim soruşturmaları
+• non-interference = müdahale etmeme</t>
+      </text>
+    </comment>
+    <comment ref="K69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ilımlı bir kararsız bölgeyi temsil eden Curt Weldon'ın aksine Omar, ağırlıklı olarak Demokratların kalesi olan bir bölgeyi (MN-05) temsil ediyor; bu da baskının koltuğuna mal olmasından ziyade partizan savunucuları kenetlemesi ve taban katılımını artırması ihtimalini çok daha yüksek kılıyor.
+Kelimeler:
+• swing district = kararsız/oyların değişebildiği seçim bölgesi
+• stronghold = kale, güçlü olunan merkez
+• rally defenders = savunucuları kenetlemek/harekete geçirmek
+• base turnout = seçmen tabanının sandığa katılımı</t>
+      </text>
+    </comment>
+    <comment ref="N69" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Omar'ın avukatlarının el konulan materyalleri incelemek ve mühürletmek için bağımsız bir uzman (special master) veya bir ihtiyati tedbir kararı talep eden mahkeme başvuruları ile arama emrini onaylayan federal sulh yargıcından gelecek açıklamalar.
+Kelimeler:
+• court filings = mahkeme başvuruları/kayıtları
+• special master = özel tarafsız incelemeci
+• injunction = ihtiyati tedbir kararı
+• magistrate judge = sulh yargıcı</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Adalet Bakanlığı televizyon kanallarına karşı antitröst soruşturması başlattı
+Kelimeler:
+• antitrust investigation = antitröst / tekelcilikle mücadele soruşturması
+• launches = başlatır, devreye sokar
+• television networks = televizyon ağları/kanalları</t>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Adalet Bakanlığı, yönetimin haber kuruluşlarına getirdiği kısıtlamaların ardından Beyaz Saray ortak havuz yayınını askıya alan beş televizyon kanalına yönelik antitröst soruşturması açtı. Bu soruşturma, basının erişim hakkı ve akreditasyonu konusunda devam eden hukuki savaşı daha da tırmandırıyor.
+Kelimeler:
+• pool coverage = ortak havuz yayını/haberciliği
+• suspended = askıya aldı
+• escalates = tırmandırıyor, şiddetlendiriyor
+• credentialing = akreditasyon verme
+• inquiry = soruşturma, inceleme</t>
+      </text>
+    </comment>
+    <comment ref="E70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+medya kuruluşlarını hedef alan yürütme kaynaklı antitröst soruşturması
+Kelimeler:
+• targeting = hedef alan
+• media organizations = medya kuruluşları</t>
+      </text>
+    </comment>
+    <comment ref="F70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2017: DOJ'nin AT&amp;T-Time Warner birleşmesine karşı açtığı antitröst davası
+1972–1974: Nixon yönetiminin televizyon kanallarına yönelik antitröst hamlesi
+Kelimeler:
+• merger = şirket birleşmesi
+• lawsuit = dava
+• action = hukuki işlem, girişim</t>
+      </text>
+    </comment>
+    <comment ref="G70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2017: Haziran 2018'de bir federal bölge yargıcı, DOJ'nin antitröst şikayetini esastan tamamen reddederek birleşmenin koşulsuz tamamlanmasına izin verdi; bu karar daha sonra temyizde de onandı.
+1972–1974: Hukuki manevralar yoğun yargı denetimi altında çıkmaza girdi ve federal kurumların medya kuruluşlarına karşı bir silah olarak kullanılması, 1974'te Nixon'a karşı açılan Temsilciler Meclisi azil soruşturmasının kilit bir parçasını oluşturdu.
+Kelimeler:
+• on the merits = esastan (davanın özü bakımından)
+• affirmed on appeal = temyizde onandı
+• maneuvers = manevralar
+• stalled = duraksadı, tıkanıp kaldı
+• impeachment inquiry = azil soruşturması</t>
+      </text>
+    </comment>
+    <comment ref="H70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, yürütme organı kurumları tarafından siyasi hasım olarak algılanan medya kuruluşlarına karşı başlatılan antitröst ve düzenleyici işlemler federal mahkemelerde başarısızlıkla sonuçlanır; zira yargıçlar erişim konusundaki siyasi anlaşmazlıklardan ziyade tüketiciye verilen zararın sıkı bir şekilde kanıtlanmasını talep eder.
+Kelimeler:
+• adversaries = hasımlar, rakipler
+• regulatory actions = düzenleyici işlemler
+• rigorous proof = sıkı/sağlam kanıt
+• consumer harm = tüketici zararı</t>
+      </text>
+    </comment>
+    <comment ref="I70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Antitröst soruşturması, federal mahkemede Birinci Değişiklik kapsamındaki misilleme itirazlarıyla hızla karşılaşacak ve yapısal yaptırımlar veya resmi kartel cezalarıyla sonuçlanmadan önce muhtemelen duraksayacak veya reddedilecektir.
+Kelimeler:
+• retaliation challenges = misilleme gerekçeli itirazlar
+• First Amendment = Birinci Değişiklik (ifade ve basın özgürlüğü)
+• dismissed = düşürülmesi, reddedilmesi
+• structural remedies = yapısal hukuki çözümler/yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="K70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Adalet Bakanlığı, ortak havuz yayınını askıya alma yönündeki kolektif kararı Sherman Yasası uyarınca yatay bir boykot veya danışıklı iş yapmayı reddetme (refusal to deal) olarak nitelendirirse, kanallar haber havuzu düzenlemelerinin ticari bir gizli anlaşmadan ziyade korunan bir kolektif basın faaliyeti olduğunu kanıtlamak zorunda kalacaktır.
+Kelimeler:
+• horizontal boycott = yatay boykot
+• concerted refusal to deal = danışıklı iş yapmaktan kaçınma
+• collusion = gizli anlaşma, danışıklılık
+• pooling arrangements = havuz oluşturma düzenlemeleri</t>
+      </text>
+    </comment>
+    <comment ref="N70" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+DOJ tarafından kanal yöneticilerine resmi Hukuki Soruşturma Taleplerinin (CID) tebliğ edilmesi ve Birinci Değişiklik uzmanı medya avukatları tarafından bunları iptal ettirmek amacıyla derhal verilecek ret önergeleri (motions to quash).
+Kelimeler:
+• Civil Investigative Demands = Hukuki Soruşturma Talepleri
+• motions to quash = hükümsüz kılma/iptal etme talepleri
+• issuance = düzenleme, tebliğ etme/çıkarma</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham hemşireleri, hastanenin 'son teklifini' oylamaya sunmak için grevi iptal etti
+Kelimeler:
+• call off = iptal etmek
+• strike = grev
+• put to a vote = oylamaya sunmak</t>
+      </text>
+    </comment>
+    <comment ref="D71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham and Women's Hospital'daki hemşireler, hastane yönetiminin revize edilmiş nihai bir sözleşme teklifi sunmasının ardından yaklaşan grevi iptal ederek teklifi onay oylaması için sendika üyelerine sundu.
+Kelimeler:
+• impending = yaklaşan, eli kulağında
+• submit = sunmak, iletmek
+• revised = gözden geçirilmiş, revize edilmiş
+• ratification vote = onay oylaması</t>
+      </text>
+    </comment>
+    <comment ref="E71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+hastane grevinin önlenmesi / sözleşme onay oylaması
+Kelimeler:
+• averted = önlenmiş, savuşturulmuş
+• ratification = onaylama, tasdik</t>
+      </text>
+    </comment>
+    <comment ref="F71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Brigham and Women's Hospital 2016 grevi önlendi
+2021: 2021 Saint Vincent Hospital grevi
+Kelimeler:
+• averted = önlenmiş</t>
+      </text>
+    </comment>
+    <comment ref="G71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Hemşireler iki hafta içinde sözleşmeyi ezici bir çoğunlukla onaylayarak çalışma barışını sağladı ve Boston'da otuz yıldır gerçekleşecek ilk hemşire grevini önledi.
+2021: Grev 301 gün sürdü—Massachusetts tarihindeki en uzun hemşire grevi oldu ve hastaneye 100 milyon dolardan fazlaya mal oldu—ve nihayet Ocak 2022'de bir uzlaşmaya varıldı.
+Kelimeler:
+• overwhelmingly = ezici bir çoğunlukla
+• labor peace = çalışma/iş barışı
+• compromise = uzlaşma, anlaşma</t>
+      </text>
+    </comment>
+    <comment ref="H71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sağlık sendikalarının işverenin nihai teklifini genel üyelerin onayına sunmak için planlanan bir grevi iptal ettiği iş uyuşmazlıklarında, sözleşme vakaların %85'inden fazlasında onaylanır; zira grev hazırlıklarının iptal edilmesi, komitenin desteğini veya uzayan bir iş bırakma eyleminin maliyetlerini üstlenme konusundaki isteksizliği gösterir.
+Kelimeler:
+• labor disputes = iş uyuşmazlıkları
+• ratify = onaylamak, tasdik etmek
+• endorsement = destek, onay
+• protracted = uzun süren, uzatmalı
+• walkout = iş bırakma eylemi</t>
+      </text>
+    </comment>
+    <comment ref="I71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brigham and Women's hemşireleri sözleşmeyi onaylamak için oy kullanacak, böylece çok yıllı bir toplu iş sözleşmesi resmileşecek ve hastanedeki operasyonel aksamaların önüne geçilecektir.
+Kelimeler:
+• formalize = resmileştirmek
+• multi-year = çok yıllı
+• operational disruptions = operasyonel aksamalar</t>
+      </text>
+    </comment>
+    <comment ref="K71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pandemi sonrası artan tükenmişlik ve güvenli asgari personel sayısına ilişkin süregelen şikayetler, tabandaki üyelerin komite liderliğine karşı çıkmasına ve anlaşmayı reddetmesine yol açabilir.
+Kelimeler:
+• burnout = tükenmişlik
+• lingering grievances = süregelen şikayetler
+• rank-and-file = taban, sıradan üyeler
+• defy = karşı gelmek, meydan okumak</t>
+      </text>
+    </comment>
+    <comment ref="N71" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sendika müzakere liderliğinin resmi olarak 'evet' oyu tavsiye edip etmeyeceği ve tabana yönelik bilgilendirme toplantılarından elde edilecek erken katılım göstergeleri.
+Kelimeler:
+• bargaining = toplu pazarlık, müzakere
+• turnout = katılım oranı
+• informational sessions = bilgilendirme toplantıları</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mass. biyoteknoloji halka arzları ivme kazanıyor: City 175 milyon dolarlık halka arzı hedefliyor; Bambusa halka açılmak için başvurdu
+Kelimeler:
+• gain momentum = ivme kazanmak
+• eyes = hedeflemek, göz dikmek
+• go public = halka açılmak</t>
+      </text>
+    </comment>
+    <comment ref="D72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts merkezli birden fazla biyoteknoloji girişimi halka açılmak için başvuruda bulundu; bu durum kurumsal ilginin yeniden canlandığına ve klinik aşamadaki yaşam bilimleri şirketleri için ilk halka arz piyasasının tekrar açıldığına işaret ediyor.
+Kelimeler:
+• file to go public = halka açılmak için başvurmak
+• institutional appetite = kurumsal yatırımcı ilgisi/iştahı
+• clinical-stage = klinik aşamada olan
+• life science = yaşam bilimleri</t>
+      </text>
+    </comment>
+    <comment ref="E72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+biyoteknoloji halka arz dalgası / piyasa döngüsünün toparlanması
+Kelimeler:
+• rebound = toparlanma, yeniden yükselişe geçme</t>
+      </text>
+    </comment>
+    <comment ref="F72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020-2021: COVID-19 biyoteknoloji halka arz patlaması ve ardından gelen daralma
+2013-2014: JOBS Yasası sonrası biyoteknoloji halka arzlarının yeniden canlanması
+Kelimeler:
+• surge = ani artış, patlama
+• subsequent contraction = sonrasındaki daralma
+• resurgence = yeniden canlanma</t>
+      </text>
+    </comment>
+    <comment ref="G72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020-2021: 2022'de yükselen faiz oranları ciddi bir 'biyoteknoloji kışı'nı tetikledi; bu da yeni halka açılan yaşam bilimleri şirketlerinin %75'inden fazlasının nakit değerinin altında işlem görmesine neden oldu ve yeni halka arz başvurularını yaklaşık iki yıl boyunca dondurdu.
+2013-2014: Başarılı ilk kotasyonlar 24 aylık bir boğa piyasası penceresi yarattı, rekor seviyede girişim sermayesi yeniden yatırımını ve büyük ilaç şirketlerinin agresif bir kurumsal satın alma döngüsünü tetikledi.
+Kelimeler:
+• severe = şiddetli, ağır
+• trade below cash value = nakit değerinin altında işlem görmek
+• bull window = yükseliş (boğa piyasası) dönemi
+• acquisition = şirket satın alımı</t>
+      </text>
+    </comment>
+    <comment ref="H72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Biyoteknoloji finansmanı çok yıllı yükseliş ve çöküş döngüleriyle hareket eder; uzun süren durgunluk dönemlerinin ardından halka arz penceresi yeniden açıldığında, tarihsel olarak ilk başarılı halka arz grubu, 12 ila 18 aylık bir sonraki halka arzlar ve girişim finansmanı sürecini destekler.
+Kelimeler:
+• boom-and-bust cycles = yükseliş ve çöküş döngüleri
+• dry spells = kuraklık/durgunluk dönemleri
+• cluster = küme, grup
+• follow-on = ardından gelen, takip eden</t>
+      </text>
+    </comment>
+    <comment ref="I72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 sonları ve 2027 başları boyunca biyoteknoloji halka arz penceresinin istikrarlı bir şekilde yeniden açılması, girişim sermayesi rezervlerinin kilidini açacak ve Greater Boston genelinde laboratuvar ve klinik istihdamını artıracaktır.
+Kelimeler:
+• sustained = sürdürülebilir, istikrarlı
+• unlocking = kilidini açmak, serbest bırakmak
+• stimulating = teşvik eden, canlandıran</t>
+      </text>
+    </comment>
+    <comment ref="K72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önceki sıfır faizli boğa koşularına kıyasla süregelen yüksek faiz ortamı, yatırımcıların spekülatif erken aşama platformları finanse etmek yerine ileri aşama klinik doğrulama talep edeceği anlamına geliyor.
+Kelimeler:
+• persistent = süregelen, inatçı
+• bull runs = boğa piyasaları, yükseliş dönemleri
+• validation = doğrulama, geçerlilik kazandırma
+• speculative = spekülatif, varsayıma dayalı</t>
+      </text>
+    </comment>
+    <comment ref="N72" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İlk gün işlem primleri, beklenen başvuru fiyat aralıklarında veya üzerinde fiyatlama ve bunu takip eden ilaç sektörü birleşme ve satın alma (M&amp;A) anlaşma duyuruları.
+Kelimeler:
+• trading premiums = işlem primleri
+• subsequent = sonraki, ardından gelen
+• M&amp;A (mergers and acquisitions) = şirket birleşme ve devralmaları</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelensky, Trump'ın ateşkes ilan etmesinden bu yana Ukrayna'ya ait altı enerji tesisinin Rusya tarafından vurulduğunu söyledi
+Kelimeler:
+• hit = vurulmak, hedef alınmak
+• ceasefire = ateşkes
+• announced = duyurmak, ilan etmek</t>
+      </text>
+    </comment>
+    <comment ref="D73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Devlet Başkanı Volodymyr Zelensky, ABD başkanının duyurduğu ateşkes çerçevesine rağmen Rusya'nın Ukrayna'ya ait altı enerji altyapı tesisini hedef aldığını belirtti.
+Kelimeler:
+• stated = belirtti, ifade etti
+• targeted = hedef aldı
+• infrastructure = altyapı
+• framework = çerçeve, taslak</t>
+      </text>
+    </comment>
+    <comment ref="E73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ateşkes ihlali
+Kelimeler:
+• violation = ihlal</t>
+      </text>
+    </comment>
+    <comment ref="F73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şubat 2015: Minsk II ateşkes anlaşması
+Ocak 2023: 2023 Rus Noeli ateşkes önerisi
+Eylül 2016: 2016 Suriye ateşkes anlaşması
+Kelimeler:
+• agreement = anlaşma
+• proposal = öneri, teklif</t>
+      </text>
+    </comment>
+    <comment ref="G73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şubat 2015: Çatışmalar hiçbir zaman tamamen durmadı ve Rus destekli güçler günler içinde Debaltseve'yi ele geçirdi; sonraki iki yıl boyunca, anlaşma tamamen çökene kadar binlerce ihlal kaydedildi.
+Ocak 2023: Saatler içinde her iki tarafın topçu bombardımanı ve füze saldırıları hız kesmeden devam etti ve operasyonel anlamda anlamlı hiçbir duraklama yaşanmadı.
+Eylül 2016: Sivil altyapıya ve yardım konvoylarına yönelik tekrarlanan saldırıların ardından anlaşma yedi gün içinde çöktü ve bu durum Halep'e yönelik büyük ve yenilenmiş bir taarruza yol açtı.
+Kelimeler:
+• Russian-backed = Rus destekli
+• captured = ele geçirdi
+• logged = kayda geçirildi
+• artillery shelling = topçu bombardımanı
+• unabated = hız kesmeden, dinmeksizin
+• operational pause = operasyonel duraklama
+• renewed offensive = yenilenen taarruz</t>
+      </text>
+    </comment>
+    <comment ref="H73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaptırım gücüne sahip doğrulama mekanizmalarından veya tarafsız barış güçlerinden yoksun diplomatik ateşkesler, özellikle muhariplerden biri uzun menzilli mühimmat konusunda asimetrik bir üstünlüğe sahip olduğunda, modern devletlerarası savaşların %80'inden fazlasında saldırıları caydırmada başarısız olmaktadır.
+Kelimeler:
+• lacking = yoksun, eksik olan
+• enforceable = yaptırım gücü olan, uygulanabilir
+• verification mechanisms = doğrulama mekanizmaları
+• deter = caydırmak
+• combatant = muharip, savaşan taraf
+• standoff munitions = uzun menzilli / uzaktan fırlatılan mühimmat</t>
+      </text>
+    </comment>
+    <comment ref="I73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kış yaklaşırken Rusya'nın Ukrayna altyapısına yönelik saldırılarını genişletmesi ve Ukrayna'nın da Rus toprakları içinde misilleme niteliğindeki İHA saldırılarını artırmasıyla birlikte kısmi ateşkes tamamen çökecektir.
+Kelimeler:
+• unravel = çözülmek, dağılmak, çökmek
+• expanding = genişletmek, yaymak
+• stepping up = artırmak, tırmandırmak
+• reciprocal = karşılıklı, misilleme mahiyetinde</t>
+      </text>
+    </comment>
+    <comment ref="K73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer ABD yönetimi belirli ihlallere açık ve anında ekonomik veya askeri misilleme bağlarsa, Rusya ikili müzakere kozunu korumak adına elektrik şebekesinin belirli düğüm noktalarına yönelik görünür saldırıları seçici biçimde frenleyebilir.
+Kelimeler:
+• attaches = bağlamak, ilişkilendirmek
+• retaliation = misilleme
+• infractions = ihlaller, kural çiğnemeler
+• throttle = frenlemek, kısmak
+• power grid nodes = elektrik şebekesi düğüm noktaları
+• leverage = koz, nüfuz</t>
+      </text>
+    </comment>
+    <comment ref="N73" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Washington'dan ihlalleri kabul eden resmi açıklamalar, ABD silah tedarik politikalarındaki ayarlamalar ve Avrupalı müttefiklerin acil durum şebeke dengeleme önlemleri.
+Kelimeler:
+• acknowledging = kabul eden, tanıyan
+• adjustments = ayarlamalar, düzenlemeler
+• grid stabilization = şebeke dengeleme, şebeke istikrarı</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi bakan, havalimanlarına yönelik Husilerin saldırılarına karşı 'ciddi bir yanıt' verileceğine söz verdi
+Kelimeler:
+• vows = söz vermek, ant içmek
+• serious response = ciddi yanıt, sert karşılık</t>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan, Husilerin Riyad uluslararası havalimanına ve başka bir tesise düzenlediği ve 13 kişinin ölümüne yol açan füze ve İHA saldırılarının ardından büyük bir askeri karşılık verileceği uyarısında bulundu.
+Kelimeler:
+• warned of = uyarısında bulundu
+• drone strikes = İHA saldırıları
+• facility = tesis</t>
+      </text>
+    </comment>
+    <comment ref="E74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+askeri misilleme / havalimanı saldırısı
+Kelimeler:
+• military retaliation = askeri misilleme</t>
+      </text>
+    </comment>
+    <comment ref="F74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2019: Abha Uluslararası Havalimanı saldırısı
+Ocak 2022: 2022 Abu Dabi saldırısı
+Eylül 2019: Abkayk-Hurais saldırısı</t>
+      </text>
+    </comment>
+    <comment ref="G74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haziran 2019: Suudi öncülüğündeki koalisyon, 48 saat içinde Sana ve Hacce vilayetlerindeki Husi füze depolarını ve komuta merkezlerini hedef alan geniş çaplı misilleme hava harekâtları düzenledi.
+Ocak 2022: Koalisyon, takip eden iki hafta boyunca Sana ve Hudeyde'ye yönelik onlarca can kaybına yol açan ve Yemen internet altyapısını devre dışı bırakan yoğun hava saldırıları başlattı.
+Eylül 2019: Suudi Arabistan, Yemen cephe hatları boyunca hava harekâtlarını tırmandırdı, İran silah sevkiyatlarına yönelik bölgesel deniz önleme faaliyetlerini yoğunlaştırdı ve ABD hava savunma konuşlandırmalarını takviye etti.
+Kelimeler:
+• Saudi-led coalition = Suudi öncülüğündeki koalisyon
+• retaliatory air raids = misilleme hava harekâtları
+• fatalities = can kayıpları, ölümler
+• disabling = devre dışı bırakma
+• escalated = tırmandırdı, şiddetlendirdi
+• naval interdictions = deniz yoluyla önleme/abluka faaliyetleri
+• bolstered = güçlendirdi, takviye etti</t>
+      </text>
+    </comment>
+    <comment ref="H74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Egemen başkent altyapısına veya sivil havacılık merkezlerine yönelik çift haneli can kayıplarına yol açan doğrudan saldırılar, gözlemlenen asimetrik çatışmaların yaklaşık %90'ında 24 ila 72 saat içinde misilleme amaçlı hava ve füze harekâtlarını tetiklemektedir.
+Kelimeler:
+• sovereign = egemen, bağımsız
+• civil aviation hubs = sivil havacılık merkezleri
+• double-digit casualties = çift haneli can kayıpları
+• prompt = tetiklemek, yol açmak
+• asymmetric confrontations = asimetrik çatışmalar</t>
+      </text>
+    </comment>
+    <comment ref="I74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan, Yemen'in kuzeyindeki Husi fırlatma sahalarına, radar tesislerine ve liderlik karargahlarına yönelik daha sıkı deniz ablukalarının eşlik ettiği sürekli bir hava ve füze harekâtı başlatacaktır.
+Kelimeler:
+• sustained = sürekli, kesintisiz
+• launch sites = fırlatma sahaları
+• installations = tesisler
+• accompanied by = eşliğinde, beraberinde
+• maritime blockades = deniz ablukaları</t>
+      </text>
+    </comment>
+    <comment ref="K74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 7 ila 14 gün</t>
+      </text>
+    </comment>
+    <comment ref="L74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Riyad'ın İran ile devam eden (2023'te arabuluculukla sağlanan) yakınlaşma süreci ve Vizyon 2030 turizm ile yatırım hedeflerinin raydan çıkması endişesi, krallığın tam ölçekli bir bölgesel yangından kaçınmak için misillemesini dikkatle ayarlamasına yol açabilir.
+Kelimeler:
+• rapprochement = yakınlaşma, uzlaşma
+• brokered = arabuluculuk yapılan
+• derailing = raydan çıkarma, sekteye uğratma
+• calibrate = dikkatle ayarlamak, ölçüp tartmak
+• conflagration = büyük yangın, şiddetli çatışma/savaş</t>
+      </text>
+    </comment>
+    <comment ref="N74" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sana ve Hudeyde çevresindeki koalisyon hava saldırılarına dair haberler, Ummanlı aracılar vasıtasıyla yürütülen gizli diplomatik temaslar ve Suudi hava sahasına giren uluslararası uçuş rotalarındaki değişiklikler.
+Kelimeler:
+• backchannel = arka kapı, örtülü/gizli kanal
+• intermediaries = aracılar
+• airspace = hava sahası
+• flight paths = uçuş rotaları</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşini kaybettikten sonra yeni bir iş bulmak artık daha uzun sürüyor
+Kelimeler:
+• it's taking longer = daha uzun sürüyor</t>
+      </text>
+    </comment>
+    <comment ref="D75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika Birleşik Devletleri'ndeki iş arayanlar, önemli ölçüde daha uzun süren işsizlik dönemleriyle karşı karşıya kalıyor; neredeyse %40'ı yeni bir iş bulamadan önce standart 26 haftalık işsizlik maaşı süresini tüketiyor.
+Kelimeler:
+• job seekers = iş arayanlar
+• bouts of joblessness = işsizlik dönemleri
+• exhausting = tüketmek, bitirmek
+• unemployment benefits = işsizlik maaşı / yardımı
+• securing new work = yeni bir iş bulmak/sağlamak</t>
+      </text>
+    </comment>
+    <comment ref="E75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+iş gücü piyasasında bozulma
+Kelimeler:
+• labor market deterioration = iş gücü piyasasının bozulması / kötüleşmesi</t>
+      </text>
+    </comment>
+    <comment ref="F75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2007: Büyük Durgunluk öncesinde işsizlik süresinin uzaması
+2001: Dot-com çöküşünün ardından istihdamsız toparlanma ve uzayan iş arama süreleri
+Kelimeler:
+• rising unemployment duration = artan işsizlik süresi
+• Great Recession = Büyük Durgunluk (2008 krizi)
+• jobless recovery = istihdamsız toparlanma
+• dot-com bust = dot-com çöküşü</t>
+      </text>
+    </comment>
+    <comment ref="G75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2007: 6 ay içinde NBER derin bir resesyonun başlangıç tarihini (Aralık 2007) ilan etti ve işsizlik sigortası tükenme oranları, Kongre'yi 2008 ortasında acil uzatılmış hakları onaylamaya sevk etti.
+2001: İstihdam yaratma, 'istihdamsız toparlanma' sürecinde iki yılı aşkın bir süre durgun kaldı ve tüketici güvenini 2003'ün içlerine kadar baskı altında tuttu.
+Kelimeler:
+• dated the start = başlangıç tarihini belirledi
+• prompted Congress to pass = Kongre'yi geçirmeye/onaylamaya teşvik etti/sevk etti
+• emergency extended benefits = acil durum uzatılmış yardım hakları
+• remained stagnant = durgun kaldı
+• consumer sentiment = tüketici güveni/duyarlılığı
+• well into = epeyce içlerine kadar</t>
+      </text>
+    </comment>
+    <comment ref="H75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son 6 ABD ekonomik döngüsünün 5'inde, uzun süreli işsizlikteki ve işsizlik sigortası tükenme oranlarındaki sürdürülebilir bir artış, 6 ila 12 ay içinde daha geniş çaplı bir iş gücü daralmasının ya da tam teşekküllü bir resesyonun güvenilir bir öncü göstergesi olmuştur.
+Kelimeler:
+• sustained increase = sürekli / kalıcı artış
+• long-term unemployment = uzun süreli işsizlik
+• exhaustion rates = tükenme/bitme oranları
+• leading indicator = öncü gösterge
+• labor market contraction = iş gücü piyasasında daralma</t>
+      </text>
+    </comment>
+    <comment ref="I75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD iş gücü piyasasının daha da gevşemesi, işsizlik oranlarında artışlar yaşanması ve Kongre üzerinde işsizlik maaşı sürelerini uzatması yönünde baskı oluşması muhtemeldir.
+Kelimeler:
+• further softening = daha da yumuşama / gevşeme
+• pressure on = üzerindeki baskı
+• benefit durations = yardım/maaş süreleri</t>
+      </text>
+    </comment>
+    <comment ref="K75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 9 ay</t>
+      </text>
+    </comment>
+    <comment ref="L75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sağlık ve hizmet sektörlerindeki pandemi sonrası yapısal iş gücü açıkları, kurumsal pozisyonlar dondurulurken belirli sektörlerin işe alımlara devam ettiği ikili bir iş gücü piyasası yaratabilir.
+Kelimeler:
+• structural labor shortages = yapısal iş gücü açıkları
+• dual-track labor market = ikili kulvarda ilerleyen iş gücü piyasası
+• corporate roles freeze = kurumsal pozisyonların dondurulması</t>
+      </text>
+    </comment>
+    <comment ref="N75" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sahm Kuralı tetikleyicisi (ulusal işsizlik oranının 3 aylık hareketli ortalamasında 0,50 yüzdelik puanlık artış) ve eyalet düzeyindeki ilk işsizlik başvurularının 260.000'i aşması.
+Kelimeler:
+• trigger = tetikleyici
+• moving average = hareketli ortalama
+• state-level = eyalet düzeyinde
+• initial claims = ilk işsizlik başvuruları
+• surpassing = aşmak, geride bırakmak</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika’nın En Sevdiği Meyve İran Savaşı Yüzünden Yara Alıyor
+Kelimeler:
+• bruised = yara almış, zedelenmiş</t>
+      </text>
+    </comment>
+    <comment ref="D76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İran'ı içeren askeri çatışma, deniz ticaretini kilitledi; gemi yakıtı ile gübre maliyetlerini fırlatarak ABD genelinde muz gibi temel ithal tüketim maddelerinin perakende fiyatlarını yükseltti.
+Kelimeler:
+• military conflict = askeri çatışma
+• snarled = düğümlenmiş, arapsaçına dönmüş
+• maritime trade = deniz ticareti
+• bunker fuel = gemi yakıtı
+• consumer staples = temel tüketim maddeleri</t>
+      </text>
+    </comment>
+    <comment ref="E76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+jeopolitik emtia şoku
+Kelimeler:
+• geopolitical commodity shock = jeopolitik emtia şoku</t>
+      </text>
+    </comment>
+    <comment ref="F76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1979: İran Devrimi'nin ardından gelen ikinci petrol şoku
+1990: Körfez Savaşı petrol fiyat artışı ve nakliye aksaklıkları
+Kelimeler:
+• oil spike = petrol fiyatında ani sıçrama
+• shipping disruptions = nakliye aksaklıkları</t>
+      </text>
+    </comment>
+    <comment ref="G76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1979: ABD manşet enflasyonu 12 ay içinde %13'ün üzerine çıkarak Federal Rezerv'in agresif faiz artışlarını ve 1980 ile 1981'de ardı ardına yaşanan resesyonları tetikledi.
+1990: Ulaşıma duyarlı tüketici fiyatları 3 ay içinde fırlayarak reel harcanabilir geliri baltaladı ve 1990–1991 ABD resesyonuna zemin hazırladı.
+Kelimeler:
+• headline inflation = manşet enflasyon
+• back-to-back recessions = ardı ardına / peş peşe gelen durgunluklar
+• denting = baltalamak, zarar vermek
+• real disposable income = reel harcanabilir gelir
+• precipitating = tetiklemek, hızlandırmak</t>
+      </text>
+    </comment>
+    <comment ref="H76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yaklaşık 5 büyük Orta Doğu deniz taşımacılığı veya petrol şokunun 4'ünde, daha yüksek lojistik ve girdi maliyetleri 3 ila 6 ay içinde perakende tüketici fiyatlarına başarıyla yansımış ve tüketicinin keyfi harcamalarını baskılamıştır.
+Kelimeler:
+• input costs = girdi maliyetleri
+• passed through to = yansıtılmak, aktarılmak
+• dampening = baskılamak, zayıflatmak
+• discretionary spending = keyfi / zorunlu olmayan harcamalar</t>
+      </text>
+    </comment>
+    <comment ref="I76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İthal gıda ve emtia enflasyonu yüksek kalmaya devam edecek; bu da merkez bankalarının beklenen faiz indirimlerini yapmasını engelleyecek ve reel tüketici harcamalarını baskılayacaktır.
+Kelimeler:
+• elevated = yüksek seyreden
+• anticipated interest rate cuts = beklenen faiz indirimleri</t>
+      </text>
+    </comment>
+    <comment ref="K76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerika Birleşik Devletleri artık net bir petrol ihracatçısı konumunda ve yerli tedarik zincirleri GSYİH birimi başına önceki on yıllara kıyasla daha az petrol yoğunluklu.
+Kelimeler:
+• net petroleum exporter = net petrol ihracatçısı
+• domestic supply chains = yerli tedarik zincirleri
+• oil-intensive = petrol yoğunluklu / petrole bağımlı</t>
+      </text>
+    </comment>
+    <comment ref="N76" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel konteyner navlun gösterge oranları (Drewry Dünya Konteyner Endeksi gibi) ve yaklaşan TÜFE raporlarındaki perakende market fiyat endeksleri.
+Kelimeler:
+• container freight = konteyner navlunu/yük taşımacılığı
+• benchmark rates = gösterge oranları
+• CPI reports = TÜFE (Tüketici Fiyat Endeksi) raporları</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boğa piyasası Pazartesi günü 4 yaşına girdi. Yatırımcılar beşinci yıla ulaşmanın zorlu olabileceğini söylüyor
+Kelimeler:
+• bull market = boğa piyasası (yükselen piyasa)
+• challenging = zorlu, çetin</t>
+      </text>
+    </comment>
+    <comment ref="D77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD borsası mevcut boğa piyasasının dördüncü yıl dönümünü geride bıraktı; S&amp;P 500, 12 Ekim 2022'deki dip seviyesinden bu yana yaklaşık %120 değer kazanırken, stratejistler beşinci yılda ivmeyi korumanın tarihsel engellerle karşılaşabileceği konusunda uyarıyor.
+Kelimeler:
+• anniversary = yıl dönümü
+• sustaining = sürdürme, koruma
+• momentum = ivme, hız
+• hurdles = engeller</t>
+      </text>
+    </comment>
+    <comment ref="E77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+boğa piyasası süresi</t>
+      </text>
+    </comment>
+    <comment ref="F77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2002–2007: 2002–2007 S&amp;P 500 konjonktürel boğa piyasası
+1982–1987: Reagan dönemi hisse senedi genişlemesi
+1995–2000: 1990'ların sonundaki teknoloji boğa piyasası zirvesi
+Kelimeler:
+• cyclical = döngüsel, konjonktürel
+• equity expansion = hisse senedi piyasasının genişlemesi</t>
+      </text>
+    </comment>
+    <comment ref="G77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2002–2007: Eşik altı (subprime) mortgage bulaşması ve daralan kredi piyasası, ralliyi 5. yılında sona erdirdi ve sonraki 17 ay boyunca %57'lik bir ayı piyasası düşüşünü başlattı.
+1982–1987: Beşinci yılına girdikten iki ay sonra, yükselen değerlemeler ve artan tahvil faizleri, Ekim 1987'de tek günde %22,6'lık ani bir çöküşü tetikledi.
+1995–2000: Ralli, Mart 2000'de zirveye ulaşmadan önce 1999 boyunca coşkulu kazanımlarla beşinci yılına devam etti ve ardından çok yıllık bir çöküş geldi.
+Kelimeler:
+• contagion = bulaşma, yayılma
+• tightening credit = kredi koşullarının sıkılaşması
+• inaugurating = başlatmak, açılışını yapmak
+• elevated valuations = yükselmiş değerlemeler
+• euphoric = aşırı coşkulu
+• bust = çöküş, batış</t>
+      </text>
+    </comment>
+    <comment ref="H77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İkinci Dünya Savaşı sonrası tarihte, dördüncü yılına ulaşan boğa piyasalarının yaklaşık %60'ı beşinci yaşını görebilmiştir; ancak beşinci yıl tarihsel olarak, %10'u aşan yıl ortası düzeltmeleriyle birlikte yıllık getirilerin düşük tek hanelere gerilediğine tanıklık etmiştir.
+Kelimeler:
+• moderate to = ılımlı hale gelmek, yavaşlamak
+• single digits = tek haneli rakamlar
+• corrections = düzeltmeler (piyasa düzeltmesi)</t>
+      </text>
+    </comment>
+    <comment ref="I77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mevcut boğa piyasasının Ekim 2027'deki beşinci yaşına kadar sürmesi muhtemeldir; ancak değerleme artışının yerini kâr büyümesi aldıkça yatırımcılar artan volatilite ve çok sayıda düşüş (drawdown) yaşayacaktır.
+Kelimeler:
+• heightened volatility = yükselen dalgalanma (oynaklık)
+• drawdowns = zirveden düşüşler, değer kayıpları
+• valuation expansion = değerleme çarpanlarının artışı</t>
+      </text>
+    </comment>
+    <comment ref="K77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kullanıma sunulan yapay zekâ altyapısından elde edilen kurumsal verimlilik artışları ve nakit zengini şirket bilançoları, borçla finanse edilen önceki döngü sonu dönemlerine kıyasla daha sağlam bir kazanç desteği sunuyor.
+Kelimeler:
+• productivity gains = verimlilik artışları
+• balance sheets = bilançolar
+• sturdier = daha sağlam, daha dayanıklı
+• debt-fueled = borçla körüklenen</t>
+      </text>
+    </comment>
+    <comment ref="N77" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Piyasa derinliğinin/genişliğinin daralması, yüksek getirili kredi marjlarının genişlemesi ve devasa ölçekli (mega-cap) şirketlerin çeyreklik sermaye harcamalarında (capex) yaşanacak sürekli bir düşüş.
+Kelimeler:
+• narrowing market breadth = piyasa genişliğinin/katılımının daralması
+• credit spreads = kredi marjları/farkları
+• sustained downturn = sürekli düşüş/gerileme
+• capex spending = sermaye harcamaları</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fed yetkilisi Hammack: 'Enflasyonist zihniyetin' yerleşmesini önlemek için daha yüksek faizler gerekebilir
+Kelimeler:
+• inflationary mindset = enflasyonist zihniyet
+• taking hold = yerleşmek, kök salmak</t>
+      </text>
+    </comment>
+    <comment ref="D78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Cleveland Merkez Bankası (Fed) Başkanı Beth Hammack, katı enflasyon beklentilerinin tüketici ve işletme davranışlarına kalıcı olarak yerleşmesini önlemek amacıyla para politikasının daha da sıkılaştırılması gerekebileceğini belirtti.
+Kelimeler:
+• monetary policy = para politikası
+• tighten = sıkılaştırmak
+• sticky inflation = yapışkan/katı enflasyon
+• embedding = yerleşme, kökleşme</t>
+      </text>
+    </comment>
+    <comment ref="E78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+para politikasında şahin dönüşüm
+Kelimeler:
+• hawkish pivot = şahin (sıkılaştırma yanlısı) dönüş</t>
+      </text>
+    </comment>
+    <comment ref="F78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980: Volcker'ın ani geri dönüşlü sıkılaştırması
+1994: Greenspan'in önleyici sıkılaştırma hamlesi
+1973–1975: Dur-kalk (stop-and-go) para politikası
+Kelimeler:
+• snap-back = hızlı/ani geri dönüş
+• preemptive = önleyici, proaktif</t>
+      </text>
+    </comment>
+    <comment ref="G78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980: Fed dört ay içinde rotasını tersine çevirmek zorunda kaldı; faizleri %19'un üzerine çıkardı ve ekonomiyi 1981–1982 arasındaki uzun süreli resesyona sürükledi.
+1994: Fed politika faizini on iki ayda %3'ten %6'ya katlayarak sabit getirili menkul kıymetlerde ciddi çalkantıya yol açtı ancak nadir görülen makroekonomik bir yumuşak iniş başardı.
+1973–1975: Şirketler ve çalışanlar yüksek enflasyonu vadeli ücret sözleşmelerine dâhil ederek on yılın geri kalanında kökleşmiş çift haneli stagflasyona yol açtı.
+Kelimeler:
+• reverse course = rotayı tersine çevirmek
+• plunging = sürüklemek, batırmak
+• fixed-income turmoil = sabit getirili menkul kıymetler çalkantısı
+• soft landing = yumuşak iniş
+• baked into = dahil etmek, hesaba katmak
+• stagflation = stagflasyon (durgunluk içinde enflasyon)</t>
+      </text>
+    </comment>
+    <comment ref="H78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enflasyonun %3 civarında yapışkan kaldığı 5 tarihsel sıkılaştırma döngüsünün 4'ünde, şahin bir duruş sergileyemeyen merkez bankaları tüketici beklentilerinin çıpasını yitirmesine neden olmuş ve bu durum nihayetinde daha yüksek nihai faiz oranları ile daha derin resesyonlar gerektirmiştir.
+Kelimeler:
+• lean hawkish = şahin tutum sergilemek
+• de-anchored = çıpasını yitirmiş, kontrolden çıkmış
+• terminal rates = nihai/zirve faiz oranları</t>
+      </text>
+    </comment>
+    <comment ref="I78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Rezerv'in bir gevşeme döngüsü başlatmak yerine, uzun süreli bir politika duraklamasını sürdürmesi veya 2027 başlarında küçük çaplı bir 'sigorta amaçlı' faiz artırımı yapması muhtemeldir.
+Kelimeler:
+• policy pause = politika faizinde duraklama
+• insurance hike = sigorta amaçlı faiz artırımı
+• easing cycle = faiz indirimi/gevşeme döngüsü</t>
+      </text>
+    </comment>
+    <comment ref="K78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Özel sektörün toplu pazarlık gücü 1970'lere göre belirgin biçimde daha düşüktür; bu da klasik ve kendi kendini besleyen bir ücret-fiyat sarmalının yerleşme olasılığını çok daha zayıflatmaktadır.
+Kelimeler:
+• collective bargaining power = toplu pazarlık gücü
+• self-fulfilling = kendi kendini gerçekleştiren
+• wage-price spiral = ücret-fiyat sarmalı</t>
+      </text>
+    </comment>
+    <comment ref="N78" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beş yıllık/beş yıl vadeli enflasyon beklenti oranlarının %2,6'yı aşması ve yaklaşan FOMC faiz oylamalarındaki şahin muhalif oylar.
+Kelimeler:
+• forward inflation expectation = vadeli enflasyon beklentisi
+• dissents = muhalif oylar, karşı görüşler</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doku coşturdu, Manchester City 10 kişi kalan Liverpool'u rahat geçti
+Kelimeler:
+• delights = coşturur, memnun eder
+• cruise past = rahatça yenmek, kolayca geçmek</t>
+      </text>
+    </comment>
+    <comment ref="D79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, Premier Lig mali kural ihlallerinden suçlu bulunduktan sonraki ilk maçında Anfield'da Liverpool karşısında 3-0'lık bir galibiyet elde etti ve bu durum, yaklaşan cezaların gölgesinde bir sezon geçirmelerine neden oldu.
+Kelimeler:
+• found guilty = suçlu bulunmuş
+• financial rule breaches = mali kural ihlalleri
+• impending sanctions = yaklaşan cezalar / yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="E79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+mali kural ihlali ve ceza
+Kelimeler:
+• financial breach = mali ihlal
+• sanction = yaptırım, ceza</t>
+      </text>
+    </comment>
+    <comment ref="F79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Juventus, Prisma mali soruşturmasında puan silme cezası aldı
+2023–2024: Everton, PSR (Kârlılık ve Sürdürülebilirlik Kuralları) ihlalleri nedeniyle puan silme cezası aldı
+Kelimeler:
+• docked points = puanı silindi
+• investigation = soruşturma</t>
+      </text>
+    </comment>
+    <comment ref="G79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Ceza, temyiz üzerine geçici olarak askıya alındı ve dört ay sonra 10 puanlık bir düşüşe indirildi; bu durum, UEFA'nın Avrupa kupalarından bir yıllık men cezası vermesinden önce Juventus'u Şampiyonlar Ligi elemelerinin dışına itti.
+2023–2024: Şubat 2024'te yapılan bir temyiz başvurusu cezayı altı puana indirdi, ardından Nisan ayında ayrı bir iki puanlık ceza eklendi ve nihai puan durumu netleşene kadar beş aylık bir belirsizlik yaratıldı.
+Kelimeler:
+• temporarily suspended = geçici olarak askıya alındı
+• point deduction = puan silme cezası</t>
+      </text>
+    </comment>
+    <comment ref="H79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sezon ortasında uygulanan büyük mali ve düzenleyici yaptırımlar, neredeyse tüm vakalarda (2020'den bu yana tüm büyük Premier Lig ve Serie A vakalarının %100'ünde) uzayan temyiz süreçlerini tetikler; bu süreçler genellikle cezanın büyüklüğünü 3 ila 6 ay içinde değiştirir ve yasal yollar tüketilene kadar rekabetçi kesinliği geciktirir.
+Kelimeler:
+• regulatory sanctions = düzenleyici yaptırımlar
+• drawn-out appeals = uzayan temyiz süreçleri
+• legal avenues = yasal yollar</t>
+      </text>
+    </comment>
+    <comment ref="I79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, yaptırımlara tahkim yoluyla derhal itiraz edecek ve sportif sonuçların ilkbahara kadar belirsiz ve tartışmalı kalmasını sağlayacaktır.
+Kelimeler:
+• arbitration = tahkim
+• clouded and contested = bulutlu/belirsiz ve tartışmalı</t>
+      </text>
+    </comment>
+    <comment ref="K79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City'nin suçlamalarının kapsamının büyüklüğü ve geniş yasal kaynakları, geleneksel spor tahkimi yolları yerine ticari uzlaşmaları veya hızlandırılmış sivil mahkeme dava süreçlerini tetikleyebilir.
+Kelimeler:
+• sheer breadth = saf genişlik, muazzam kapsam
+• civil court litigation = sivil mahkeme dava süreci</t>
+      </text>
+    </comment>
+    <comment ref="N79" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+City'nin resmi temyiz başvurusunu sunması, herhangi bir puan silme cezasına karşı geçici yürütmeyi durdurma başvuruları ve tazminat taleplerini değerlendiren rakip kulüplerin kamuoyuna yaptığı açıklamalar.
+Kelimeler:
+• interim stay of execution = geçici yürütmeyi durdurma kararı
+• compensation claims = tazminat talepleri</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seedorf, Corinthians teknik direktörü olarak futbola geri döndü
+Kelimeler:
+• head coach = teknik direktör</t>
+      </text>
+    </comment>
+    <comment ref="D80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brezilya ekibi Corinthians, 2019'da Kamerun'dan ayrıldığından bu yana ilk teknik direktörlük görevini Hollandalı efsaneye vererek Clarence Seedorf'u teknik direktör olarak atadı.
+Kelimeler:
+• managerial position = teknik direktörlük pozisyonu
+• departing = ayrılmak</t>
+      </text>
+    </comment>
+    <comment ref="E80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+teknik direktör ataması
+Kelimeler:
+• managerial appointment = teknik direktör ataması</t>
+      </text>
+    </comment>
+    <comment ref="F80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Clarence Seedorf, Deportivo La Coruña'nın teknik direktörlüğüne getirildi
+2014: Clarence Seedorf, AC Milan tarafından işe alındı
+Kelimeler:
+• appointed manager = teknik direktör olarak atandı</t>
+      </text>
+    </comment>
+    <comment ref="G80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Seedorf 16 maçın sadece ikisini kazandı, Deportivo Segunda División'a düştü ve kulüp üç buçuk ayın ardından sözleşmesini yenilememe kararı aldı.
+2014: 19 Serie A maçının 11'ini kazanmasına rağmen, soyunma odası sürtüşmeleri ve yönetim kurulu anlaşmazlıkları sadece dört ay sonra, Haziran 2014'te görevden alınmasına yol açtı.
+Kelimeler:
+• relegated = küme düştü
+• dressing-room friction = soyunma odası sürtüşmesi
+• dismissal = görevden alma, kovulma</t>
+      </text>
+    </comment>
+    <comment ref="H80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seedorf'un önceki dört teknik direktörlük işinin 4'ünde de (Milan, Shenzhen, Deportivo, Kamerun) görev süresi 12 ayın altında kaldı ve çok yıllık aralardan değişken Brezilya Série A'sına dönen teknik direktörler yüksek ilk yıl görevden alınma oranlarıyla (%70'i aşan) karşılaşıyor.
+Kelimeler:
+• tenure = grev süresi, görevde kalma süresi
+• multi-year hiatuses = uzun yıllar süren aralar
+• volatile = değişken, istikrarsız</t>
+      </text>
+    </comment>
+    <comment ref="I80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seedorf, Corinthians'ta tam bir takvim yılını tamamlamakta zorlanacak; sonuçlar veya taktiksel uyum konusundaki erken sürtüşmeler muhtemelen 2027'nin sonlarından önce bir ayrılığı tetikleyecektir.
+Kelimeler:
+• see out = sonuna kadar tamamlamak
+• tactical adaptability = taktiksel uyum yeteneği</t>
+      </text>
+    </comment>
+    <comment ref="K80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 8 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seedorf, 2012'den 2014'e kadar Botafogo'da Brezilya'da futbol oynadı, akıcı bir şekilde Portekizce konuşuyor ve Brezilya futbolunun benzersiz takvimini ve taleplerini çoğu yabancı teknik direktörden daha iyi anlıyor.
+Kelimeler:
+• fluent = akıcı
+• foreign appointees = yabancı atananlar</t>
+      </text>
+    </comment>
+    <comment ref="N80" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Corinthians'ın erken bölgesel kupa maçlarındaki performansları ve antrenman rejiminin arkasında soyunma odası uyumunun işaretleri.
+Kelimeler:
+• fixtures = fikstür, maçlar
+• alignment = uyum, birlik</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları vanilyanın gizli iyileştirici potansiyelini keşfetti
+Kelimeler:
+• healing potential = iyileştirici potansiyel
+• discover = keşfetmek</t>
+      </text>
+    </comment>
+    <comment ref="D81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları, vanilyaya tadını veren bileşik olan vanilinin; enfeksiyonlarla savaşabilecek, iltihabı azaltabilecek ve yara iyileşmesini destekleyebilecek özelliklere sahip olduğunu tespit etti.
+Kelimeler:
+• compound = bileşik
+• possess = sahip olmak
+• inflammation = iltihap, yangı
+• wound healing = yara iyileşmesi
+• fight infections = enfeksiyonlarla mücadele etmek</t>
+      </text>
+    </comment>
+    <comment ref="E81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+doğal bileşik kaynaklı tıbbi keşif
+Kelimeler:
+• natural compound = doğal bileşik
+• breakthrough = çığır açan gelişme, buluş</t>
+      </text>
+    </comment>
+    <comment ref="F81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1928: Alexander Fleming tarafından penisilinin keşfi
+1897: Felix Hoffmann tarafından Bayer'de aspirinin sentezlenmesi
+Kelimeler:
+• synthesis = sentezleme
+• discovery = keşif</t>
+      </text>
+    </comment>
+    <comment ref="G81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1928: 1940'ların başında kullanılabilir bir ilaç olarak seri üretime geçmesi on yıldan fazla zaman aldı ve İkinci Dünya Savaşı'nın aciliyetini gerektirdi.
+1897: İnsanlık tarihinin en yaygın kullanılan ilaçlarından biri haline geldi, ancak kesin etki mekanizmalarının belirlenmesi onlarca yıl sürdü.
+Kelimeler:
+• mass-produced = seri üretilen
+• urgency = aciliyet
+• widely used = yaygın kullanılan
+• mechanisms = mekanizmalar</t>
+      </text>
+    </comment>
+    <comment ref="H81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doğal bileşiklere ilişkin laboratuvar buluşları, petri kabından klinik uygulamaya uzanan uzun ve zorlu bir süreçle karşı karşıyadır; tarihsel olarak, umut vadeden in vitro antimikrobiyal veya anti-enflamatuar keşiflerin 10'da 1'inden azı insan klinik deneylerini başarıyla tamamlayabilmektedir.
+Kelimeler:
+• breakthrough = çığır açıcı gelişme
+• petri dish = petri kabı
+• clinical application = klinik uygulama
+• in vitro = laboratuvar ortamında (canlı dışı)
+• antimicrobial = antimikrobiyal
+• clinical trials = klinik deneyler</t>
+      </text>
+    </comment>
+    <comment ref="I81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bu keşif, önümüzdeki birkaç yıl içinde yoğun klinik öncesi hayvan testlerine yol açacaktır, ancak klinik olarak kullanıma sunulması hala uzak bir ihtimal olmaya devam etmektedir.
+Kelimeler:
+• intense = yoğun
+• preclinical = klinik öncesi
+• distant prospect = uzak bir ihtimal
+• clinical availability = klinik olarak erişilebilirlik</t>
+      </text>
+    </comment>
+    <comment ref="K81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 5-10 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern yüksek verimli tarama ve hedefe yönelik ilaç dağıtım sistemleri, 20. yüzyılın zaman çizelgelerine kıyasla analog geliştirmeyi hızlandırabilir.
+Kelimeler:
+• high-throughput screening = yüksek verimli tarama
+• targeted drug delivery = hedefe yönelik ilaç iletimi
+• accelerate = hızlandırmak
+• analog development = analog (benzer molekül) geliştirme</t>
+      </text>
+    </comment>
+    <comment ref="N81" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hakemli in vivo hayvan çalışmaları ile sentetik vanilin türevlerine yönelik farmasötik ilgi veya patent başvuruları.
+Kelimeler:
+• peer-reviewed = hakemli (bilimsel dergi onaylı)
+• in vivo = canlı organizma içinde
+• derivatives = türevler
+• patent filings = patent başvuruları</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni enjeksiyon yağ hücrelerinin kendi kendini yok etmesini sağlıyor
+Kelimeler:
+• injection = enjeksiyon, iğne
+• fat cells = yağ hücreleri
+• self-destruct = kendi kendini yok etmek</t>
+      </text>
+    </comment>
+    <comment ref="D82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları, yağ hücrelerini yok eden ve tehlikeli karın yağlarını azaltan, obezite için potansiyel yeni bir tedavi sunan deneysel bir enjeksiyon geliştirdi.
+Kelimeler:
+• experimental = deneysel
+• belly fat = karın/göbek yağı
+• obesity = obezite
+• treatment = tedavi</t>
+      </text>
+    </comment>
+    <comment ref="E82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+obezite tedavisinde çığır açan gelişme
+Kelimeler:
+• breakthrough = çığır açan gelişme</t>
+      </text>
+    </comment>
+    <comment ref="F82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Kronik kilo kontrolü için Semaglutide (Wegovy) ilacına FDA onayı verilmesi
+1950'ler-1990'lar: Obezite karşıtı farmakoterapi geçmişi ve piyasadan çekilen diyet ilaçları
+Kelimeler:
+• chronic weight management = kronik kilo yönetimi
+• pharmacotherapy = ilaç tedavisi (farmakoterapi)
+• withdrawn = piyasadan çekilmiş, geri çekilen</t>
+      </text>
+    </comment>
+    <comment ref="G82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Devasa bir küresel ticari patlamayı, ciddi tedarik sıkıntılarını ve rakip ilaç firmalarının alternatif iletim ve etki mekanizmaları geliştirmek için anında yarışa girmesini tetikledi.
+1950'ler-1990'lar: 
+Kelimeler:
+• sparked = tetikledi
+• supply shortages = tedarik kıtlığı/sıkıntısı
+• mechanisms of action = etki mekanizmaları
+• competing = rakip olan, yarışan</t>
+      </text>
+    </comment>
+    <comment ref="H82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni yağ azaltıcı veya obezite karşıtı ajanlara ilişkin her 10 büyük duyurunun 8'inde, hayvan veya laboratuvar aşamasındaki ilk başarılar, insan klinik deneylerinde hedef dışı hücresel toksisiteye dair katı güvenlik engelleriyle karşılaşır.
+Kelimeler:
+• stringent = katı, sıkı
+• safety hurdles = güvenlik engelleri
+• off-target = hedef dışı
+• cellular toxicity = hücresel toksisite (zehirlilik)</t>
+      </text>
+    </comment>
+    <comment ref="I82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tedavi, devam eden obezite tedavisi patlamasının ortasında kayda değer risk sermayesi veya ilaç sektörü desteği çekerek erken aşama insan güvenliği denemelerine doğru ilerleyecektir.
+Kelimeler:
+• advance = ilerlemek
+• venture backing = risk sermayesi desteği
+• ongoing = devam eden
+• boom = patlama, hızlı yükseliş</t>
+      </text>
+    </comment>
+    <comment ref="K82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gelişmiş hücresel hedefleme teknikleri, eski, sistemik ve toksik kimyasal yaklaşımlara kıyasla daha lokalize veya spesifik hücre ölümü mekanizmalarına olanak tanımaktadır.
+Kelimeler:
+• cellular targeting = hücresel hedefleme
+• localized = bölgesel, lokalize
+• cell-death = hücre ölümü
+• systemic = sistemik (tüm vücudu etkileyen)</t>
+      </text>
+    </comment>
+    <comment ref="N82" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lokal bölge toksisitesine ve sistemik enflamatuar yan etkilere odaklanan Faz 1 insan klinik deneylerinin sonuçları.
+Kelimeler:
+• Phase 1 trials = Faz 1 klinik deneyleri
+• systemic inflammatory = sistemik enflamatuar (iltihabi)
+• side effects = yan etkiler</t>
       </text>
     </comment>
   </commentList>
@@ -7053,7 +8628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12871,6 +14446,1211 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Federal agents search home of Rep. Ilhan Omar ahead of midterm elections</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Federal immigration agents executed a search warrant at the Minneapolis residence of Democratic Representative Ilhan Omar, seizing boxes of material. The search occurred inside the Justice Department's traditional 60-day unwritten window where overt law enforcement actions against political figures are typically avoided.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>federal search warrant executed on sitting member of Congress</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>October 2006: FBI raids on Rep. Curt Weldon's associates three weeks before midterm election
+May 2006: FBI search of Representative William J. Jefferson's congressional office
+January 2022: FBI search of Representative Henry Cuellar's home and campaign office</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>October 2006: Within three weeks, the public fallout erased the 10-term Republican incumbent's polling lead, causing him to lose his seat to Democrat Joe Sestak in the November 2006 midterms.
+May 2006: Bipartisan House leadership challenged the raid as executive overreach, and the D.C. Circuit Court of Appeals ruled in 2007 that the seizure violated the Constitution's Speech or Debate Clause.
+January 2022: Cuellar survived both the primary and general elections despite intense political scrutiny, while formal federal charges were not filed until May 2024, over two years later.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>In modern U.S. history, overt federal searches against sitting lawmakers within weeks of an election trigger immediate separation-of-powers legal challenges and sharp accusations of political weaponization, with courts closely scrutinizing executive branch motives.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Omar's defense will mount aggressive legal challenges under Fourth Amendment and Speech or Debate protections to seal or suppress seized files, while congressional Democrats will open formal oversight inquiries into whether the Justice Department violated election-season non-interference protocols.</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 3 months</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Unlike Curt Weldon, who represented a moderate swing district, Omar represents a heavily Democratic stronghold (MN-05), making the raid far more likely to rally partisan defenders and boost base turnout than cost her the seat.</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Court filings by Omar's attorneys requesting a special master or an injunction to review and seal seized materials, and statements from the federal magistrate judge who approved the warrant.</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/12/us/politics/ilhan-omar-home-searched.html</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Curt_Weldon
+https://en.wikipedia.org/wiki/William_J._Jefferson_corruption_case
+https://en.wikipedia.org/wiki/Henry_Cuellar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Justice Department launches antitrust investigation into television networks</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>The Department of Justice opened an antitrust inquiry into five television networks after they suspended White House pool coverage following administration restrictions on news outlets. The investigation escalates an ongoing legal battle over press access and credentialing.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>executive antitrust investigation targeting media organizations</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>November 2017: DOJ antitrust lawsuit against AT&amp;T-Time Warner merger
+1972–1974: Nixon administration antitrust action against television networks</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>November 2017: In June 2018, a federal district judge thoroughly rejected the DOJ's antitrust complaint on the merits, allowing the merger to close unconditionally, which was later affirmed on appeal.
+1972–1974: The legal maneuvers stalled under heavy judicial scrutiny, and the weaponization of federal agencies against media organizations formed a key component of the 1974 House impeachment inquiry against Nixon.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Historically, antitrust and regulatory actions initiated by executive branch agencies against media organizations perceived as political adversaries fail in federal court, as judges require rigorous proof of consumer harm rather than political disputes over access.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>The antitrust inquiry will face swift First Amendment retaliation challenges in federal court and will likely stall or be dismissed before resulting in structural remedies or formal cartel penalties.</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>If the Justice Department frames the collective decision to suspend pool coverage as a horizontal boycott or concerted refusal to deal under the Sherman Act, the networks must establish that news pooling arrangements are protected collective press activity rather than commercial collusion.</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Issuance of formal Civil Investigative Demands (CIDs) by the DOJ to network executives and immediate motions to quash filed by First Amendment media attorneys.</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/11/nx-s1-5997574/the-doj-is-investigating-5-tv-networks-for-suspending-pool-coverage-of-trump</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Acquisition_of_Time_Warner_by_AT%26T
+https://en.wikipedia.org/wiki/Richard_Nixon's_enemies_list</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Brigham nurses call off strike to put hospital's ‘final offer' to a vote</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Nurses at Brigham and Women's Hospital called off an impending strike after hospital leadership submitted a revised final contract offer, sending the proposal to union members for a ratification vote.</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>hospital strike averted / contract ratification vote</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2016: Brigham and Women's Hospital 2016 strike averted
+2021: 2021 Saint Vincent Hospital strike</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>2016: Nurses voted overwhelmingly to approve the contract within two weeks, ensuring labor peace and preventing what would have been the first nurses' strike in Boston in three decades.
+2021: The strike lasted 301 days—becoming the longest nurses' strike in Massachusetts history and costing the hospital over $100 million—before a compromise was finally reached in January 2022.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>In labor disputes where healthcare unions cancel a planned strike to place an employer's final offer before the general membership, the contract is ratified in over 85% of cases, as calling off strike preparations indicates committee endorsement or an unwillingness to bear protracted walkout costs.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Brigham and Women's nurses will vote to ratify the contract, formalizing a multi-year labor agreement and avoiding any operational disruptions at the hospital.</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>next 2 to 3 weeks</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Heightened post-pandemic burnout and lingering grievances over safe staffing minimums could prompt grassroots rank-and-file opposition to defy committee leadership and reject the deal.</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Whether union bargaining leadership formally recommends a 'yes' vote and early turnout indicators from rank-and-file informational sessions.</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQWWJUTk5xRGpHdE5DbF9FdWNabWx0TDNGa251bXk3TkIycTNhZkpUS1puaEUtNUhFbWNuMXpidVlJOVZwa3NsR3FEcW5HMGEzWEZiZ08yXzl3a1A5b3BNd3pibENxbi1idHNNb3hZVUVrS1hTQzhFVkFjRVFPdFh0ZWt1aV9nanpYTWoxc2xfSmplLUdKTVBvWlc2OXQxMExNREJZWlZ0VHR2NFRGVHpVSdIBuAFBVV95cUxQNUtnS3dMeW9md0lWN2NxT0xfR3o3TFZDS2RqemZUVERReHJOanprZG93djI0OVZFZFhnbHg3bjJxT2dJTXJpc1VzTHlDM1d0enB5WDcyNTJXbUZqU2xrQnF4cGJENHVvSFVGYkRLdFhjcVNxT0tPV2VTM1ctUkJKYmJhazRXcUlTZENFZm1tRjVPTk5GM0l6ZzFZNGxYUUN5Qkhhekp2ZmRkRmlnMUlvenQ4V2MwZzdy?oc=5</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Brigham_and_Women's_Hospital
+https://en.wikipedia.org/wiki/2021%E2%80%932022_Saint_Vincent_Hospital_strike</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Mass. biotech IPOs gain momentum: City eyes $175M IPO; Bambusa files to go public</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Multiple Massachusetts-based biotechnology startups have filed to go public, signaling renewed institutional appetite and reopening the initial public offering market for clinical-stage life science firms.</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>biotech IPO wave / market cycle rebound</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2020-2021: COVID-19 biotech IPO surge and subsequent contraction
+2013-2014: Post-JOBS Act biotechnology public offering resurgence</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2020-2021: Rising interest rates in 2022 triggered a severe 'biotech winter', causing more than 75% of newly public life science companies to trade below cash value and freezing new IPO filings for nearly two years.
+2013-2014: The successful initial listings created a 24-month bull window, sparking record venture capital reinvestment and an aggressive corporate acquisition cycle by pharmaceutical majors.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Biotech financing moves in multi-year boom-and-bust cycles; when the public offering window reopens following prolonged dry spells, the first successful cluster of IPOs historically sustains a 12-to-18-month pipeline of follow-on public debuts and venture financings.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>A sustained reopening of the biotech IPO window across late 2026 and early 2027, unlocking venture capital reserves and stimulating increased lab and clinical employment across Greater Boston.</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>A persistent high-interest-rate environment compared to previous zero-interest-rate bull runs means investors will demand late-stage clinical validation rather than funding speculative early-stage platforms.</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>First-day trading premiums, pricing within or above expected filing ranges, and subsequent pharmaceutical M&amp;A deal announcements.</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPdUJlLXNmaWpDRHlfOXVoMzFHYkdsalYwTlBoSVdpakc3YjdpRGJSSjZJWml2bG50Rm5ZRTNWeU5lUm44NTVnSHBabzFDOWxVOGVzd3ZyWkVDNER2czFBRUhVZzlqV3NVNlcyMThtZVk1UWhIVjZDRFZLM25XcnowcHBsQzU?oc=5</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Initial_public_offering
+https://en.wikipedia.org/wiki/Biotechnology_industry_in_Boston</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Six Ukrainian energy sites hit by Russia since Trump announced ceasefire, Zelensky says</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>President Volodymyr Zelensky stated that Russia targeted six Ukrainian energy infrastructure sites despite a ceasefire framework announced by the US president.</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>ceasefire violation</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>February 2015: Minsk II ceasefire agreement
+January 2023: 2023 Russian Christmas ceasefire proposal
+September 2016: 2016 Syrian ceasefire agreement</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>February 2015: Fighting never fully stopped, and Russian-backed forces captured Debaltseve within days; over the next two years, thousands of violations were logged until the deal collapsed entirely.
+January 2023: Artillery shelling and missile strikes continued unabated from both sides within hours, resulting in no meaningful operational pause.
+September 2016: The agreement collapsed within seven days following repeated strikes on civilian infrastructure and aid convoys, leading to a massive renewed offensive on Aleppo.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Diplomatic ceasefires lacking enforceable verification mechanisms or neutral peacekeepers fail to deter strikes in over 80% of modern interstate wars, especially when one combatant holds an asymmetric advantage in long-range standoff munitions.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>The partial ceasefire will unravel completely, with Russia expanding strikes on Ukrainian infrastructure as winter approaches and Ukraine stepping up reciprocal drone strikes inside Russian territory.</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 weeks</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>If the US administration attaches explicit, immediate economic or military retaliation to specific infractions, Russia may selectively throttle visible strikes on certain power grid nodes to preserve bilateral leverage.</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Official statements from Washington acknowledging violations, adjustments in US weapon supply policies, and emergency grid stabilization measures by European allies.</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cvlyd4pdlwkxo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Minsk_agreements
+https://en.wikipedia.org/wiki/2023_Russian_Christmas_truce_proposal
+https://en.wikipedia.org/wiki/2026_northeastern_Syria_offensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Saudi minister vows 'serious response' to Houthi attacks on airports</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia warned of a major military response after Houthi missile and drone strikes on Riyadh's international airport and another facility killed 13 people.</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>military retaliation / airport attack</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>June 2019: Abha International Airport attack
+January 2022: 2022 Abu Dhabi attack
+September 2019: Abqaiq–Khurais attack</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>June 2019: Within 48 hours, the Saudi-led coalition conducted extensive retaliatory air raids targeting Houthi missile storage and command centers in Sana'a and Hajjah governorates.
+January 2022: The coalition launched intense airstrikes against Sana'a and Hodeidah over the following two weeks, causing dozens of fatalities and disabling Yemeni internet infrastructure.
+September 2019: Saudi Arabia escalated air operations along Yemeni frontlines, intensified regional naval interdictions of Iranian arms shipments, and bolstered US air defense deployments.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Direct strikes on sovereign capital infrastructure or civil aviation hubs causing double-digit casualties prompt retaliatory air and missile campaigns within 24 to 72 hours in nearly 90% of observed asymmetric confrontations.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia will launch a sustained air and missile campaign against Houthi launch sites, radar installations, and leadership facilities in northern Yemen, accompanied by tighter maritime blockades.</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>next 7 to 14 days</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Riyadh's ongoing rapprochement track with Iran (brokered in 2023) and concerns over derailing its Vision 2030 tourism and investment goals could lead the kingdom to calibrate its retaliation to avoid a full-scale regional conflagration.</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Reports of coalition airstrikes around Sana'a and Hodeidah, backchannel diplomatic communications via Omani intermediaries, and changes to international flight paths into Saudi airspace.</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cjly0zqq27e4o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2019_Abha_International_Airport_attacks
+https://en.wikipedia.org/wiki/2022_Abu_Dhabi_attack
+https://en.wikipedia.org/wiki/Abqaiq%E2%80%93Khurais_attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>It's taking longer to find a new job after losing one</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Job seekers in the United States are facing significantly longer bouts of joblessness, with almost 40% exhausting their regular 26-week unemployment benefits before securing new work.</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>labor market deterioration</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2007: Rising unemployment duration ahead of the Great Recession
+2001: Jobless recovery and prolonged search times after the dot-com bust</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>2007: Within 6 months, the NBER dated the start of a deep recession (December 2007), and UI exhaustion rates prompted Congress to pass emergency extended benefits in mid-2008.
+2001: Job creation remained stagnant for over two years in a 'jobless recovery', keeping consumer sentiment depressed well into 2003.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>In 5 of the last 6 U.S. economic cycles, a sustained increase in long-term unemployment and UI exhaustion rates has served as a reliable leading indicator of broader labor market contraction or a full recession within 6 to 12 months.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. labor market is likely to see further softening, with unemployment rate increases and pressure on Congress to extend unemployment benefit durations.</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 9 months</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Post-pandemic structural labor shortages in healthcare and service sectors could create a dual-track labor market where certain sectors continue hiring while corporate roles freeze.</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>The Sahm Rule trigger (0.50 percentage point rise in the 3-month moving average of the national unemployment rate) and state-level UI initial claims surpassing 260,000.</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/11/nx-s1-5995238/jobs-employment-economy-unemployment-benefits</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Great_Recession_in_the_United_States
+https://en.wikipedia.org/wiki/Early_2000s_recession</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>America’s Favorite Fruit Is Being Bruised by the Iran War</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Military conflict involving Iran has snarled maritime trade and spiked bunker fuel and fertilizer costs, driving up retail prices on basic imported consumer staples like bananas across the U.S.</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>geopolitical commodity shock</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1979: Second oil shock following the Iranian Revolution
+1990: Gulf War oil spike and shipping disruptions</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1979: U.S. headline inflation accelerated to over 13% within 12 months, triggering aggressive Federal Reserve interest rate hikes and back-to-back recessions in 1980 and 1981.
+1990: Transportation-sensitive consumer prices surged within 3 months, denting real disposable income and precipitating the 1990–1991 U.S. recession.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 4 out of 5 major Middle East shipping or oil shocks, higher logistics and input costs have successfully passed through to retail consumer prices within 3 to 6 months, dampening consumer discretionary spending.</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Imported food and goods inflation will remain elevated, preventing central banks from delivering anticipated interest rate cuts and dampening real consumer spending.</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>The United States is now a net petroleum exporter, and domestic supply chains are less oil-intensive per unit of GDP than in earlier decades.</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Global container freight benchmark rates (such as the Drewry World Container Index) and retail grocery price indexes in upcoming CPI reports.</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/12/business/economy/bananas-iran-war.html</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1979_oil_crisis
+https://en.wikipedia.org/wiki/1990_oil_price_shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>The bull market turned 4 years old on Monday. Investors say reaching a fifth birthday could be challenging</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. stock market marked the fourth anniversary of the current bull market, with the S&amp;P 500 gaining nearly 120% since its October 12, 2022 low, while strategists caution that sustaining momentum through year five faces historical hurdles.</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>bull market duration</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2002–2007: 2002–2007 S&amp;P 500 cyclical bull market
+1982–1987: Reagan-era equity expansion
+1995–2000: Late-1990s tech bull market peak</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>2002–2007: Subprime mortgage contagion and tightening credit ended the rally at the 5-year mark, inaugurating a 57% bear market decline over the next 17 months.
+1982–1987: Two months after crossing into its fifth year, elevated valuations and rising yields triggered a sudden 22.6% single-day crash in October 1987.
+1995–2000: The rally pushed into year five with euphoric gains throughout 1999 before peaking in March 2000, followed by a multi-year bust.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>In post-WWII history, approximately 60% of bull markets that reach year four survive to celebrate a fifth birthday, but year five historically sees annualized returns moderate to low single digits alongside 10%+ mid-year corrections.</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>The current bull market is likely to survive to its fifth birthday in October 2027, but investors will experience heightened volatility and multiple drawdowns as earnings growth replaces valuation expansion.</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise productivity gains from deployed artificial intelligence infrastructure and cash-rich corporate balance sheets offer sturdier earnings support than previous debt-fueled late-stage cycles.</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Narrowing market breadth, widening high-yield credit spreads, and any sustained downturn in quarterly mega-cap capex spending.</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/12/the-bull-market-just-turned-four-after-climbing-a-wall-of-worry.html</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/United_States_bear_market_of_2007%E2%80%932009
+https://en.wikipedia.org/wiki/Black_Monday_(1987)
+https://en.wikipedia.org/wiki/Dot-com_bubble</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Higher rates could be needed to avoid 'inflationary mindset' taking hold, says Fed's Hammack</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Cleveland Federal Reserve President Beth Hammack stated that monetary policy may need to tighten further to prevent sticky inflation expectations from permanently embedding in consumer and business behavior.</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>monetary policy hawkish pivot</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1980: Volcker snap-back tightening
+1994: Greenspan preemptive tightening campaign
+1973–1975: Stop-and-go monetary policy</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1980: The Fed was forced to reverse course within four months, hiking rates past 19% and plunging the economy into the prolonged 1981–1982 recession.
+1994: The Fed doubled the policy rate from 3% to 6% in twelve months, creating substantial fixed-income turmoil but achieving a rare macroeconomic soft landing.
+1973–1975: Firms and workers baked high inflation into forward wage contracts, producing entrenched double-digit stagflation throughout the remainder of the decade.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>In 4 out of 5 historical tightening cycles where inflation proved sticky near 3%, central banks that failed to lean hawkish suffered de-anchored consumer expectations, eventually requiring higher terminal rates and deeper recessions.</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve will likely maintain an extended policy pause or deliver an incremental insurance hike in early 2027 rather than commencing an easing cycle.</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Private sector collective bargaining power is dramatically lower than in the 1970s, making a classic self-fulfilling wage-price spiral far less likely to take hold.</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Five-year/five-year forward inflation expectation rates exceeding 2.6% and hawkish dissents in upcoming FOMC rate votes.</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/12/beth-hammack-fed-inflation-policy.html</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Early_1980s_recession
+https://en.wikipedia.org/wiki/1994_bond_market_crisis
+https://en.wikipedia.org/wiki/Inflation</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Doku delights as Manchester City cruise past 10-man Liverpool</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City earned a 3-0 victory against Liverpool at Anfield in their first game after being found guilty of Premier League financial rule breaches, leaving their campaign shadowed by impending sanctions.</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>financial breach sanction</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2023: Juventus docked points in Prisma financial investigation
+2023–2024: Everton docked points for PSR breaches</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>2023: The penalty was temporarily suspended on appeal before being revised down to a 10-point deduction four months later, which pushed Juventus out of the Champions League qualification places before UEFA issued a one-year ban from European competitions.
+2023–2024: An appeal reduced the deduction to six points in February 2024, followed by a separate two-point deduction in April, creating five months of uncertainty before final standings were settled.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Major financial and regulatory sanctions imposed mid-season trigger drawn-out appeals in nearly all cases (100% of major Premier League and Serie A cases since 2020), which routinely alter the sanction's magnitude within 3 to 6 months and delay competitive finality until legal avenues are exhausted.</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City will immediately challenge the sanctions via arbitration, ensuring the sporting consequences remain clouded and contested well into the spring.</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>The sheer breadth of Manchester City's charges and their extensive legal resources may prompt commercial settlements or fast-tracked civil court litigation rather than traditional sports arbitration avenues.</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>City's submission of an official appeal notice, applications for an interim stay of execution against any point deductions, and public statements from rival clubs considering compensation claims.</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/videos/c6vgy2ll1zypo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022%E2%80%9323_Juventus_FC_season
+https://en.wikipedia.org/wiki/2023%E2%80%9324_Everton_F.C._season</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Seedorf back in football as Corinthians head coach</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Brazilian side Corinthians named Clarence Seedorf as their head coach, handing the Dutch legend his first managerial position since departing Cameroon in 2019.</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>managerial appointment</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2018: Clarence Seedorf appointed manager of Deportivo La Coruña
+2014: Clarence Seedorf hired by AC Milan</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2018: Seedorf won only two of 16 matches, Deportivo were relegated to the Segunda División, and the club opted not to renew his contract after three and a half months.
+2014: Despite winning 11 of his 19 Serie A matches, dressing-room friction and board disputes led to his dismissal just four months later in June 2014.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of 4 of Seedorf's previous head-coaching jobs (Milan, Shenzhen, Deportivo, Cameroon), his tenure lasted under 12 months, and managers returning from multi-year hiatuses to the volatile Brazilian Série A face high first-year dismissal rates (exceeding 70%).</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Seedorf will struggle to see out a full calendar year at Corinthians, with early friction over results or tactical adaptability likely triggering a departure before late 2027.</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>next 8 to 12 months</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Seedorf played in Brazil for Botafogo from 2012 to 2014, speaks fluent Portuguese, and understands the unique calendar and demands of Brazilian football better than most foreign appointees.</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corinthians' performances in early regional cup fixtures and signs of dressing-room alignment behind his training regime.</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cw62y514kpgeo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2017%E2%80%9318_Deportivo_de_La_Coru%C3%B1a_season
+https://en.wikipedia.org/wiki/2013%E2%80%9314_AC_Milan_season</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Scientists discover vanilla’s hidden healing potential</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Scientists have found that vanillin, the compound providing vanilla's flavor, possesses properties that could fight infections, reduce inflammation, and promote wound healing.</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>natural compound medical discovery</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1928: Discovery of penicillin by Alexander Fleming
+1897: Synthesis of aspirin by Felix Hoffmann at Bayer</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1928: It took over a decade and World War II urgency before it was mass-produced as a usable medicine in the early 1940s.
+1897: It became one of the most widely used medications in human history, though establishing its exact mechanisms took decades.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Laboratory breakthroughs regarding natural compounds face a long, difficult road from petri dish to clinical application; historically, fewer than 1 in 10 promising in vitro antimicrobial or anti-inflammatory discoveries successfully pass human clinical trials.</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>The discovery will generate intense preclinical animal testing over the next few years, but clinical availability remains a distant prospect.</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>next 5-10 years</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Modern high-throughput screening and targeted drug delivery systems could accelerate analog development compared to 20th-century timelines.</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Peer-reviewed in vivo animal studies and pharmaceutical interest or patent filings for synthetic vanillin derivatives.</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261011211550.htm</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Penicillin
+https://en.wikipedia.org/wiki/Aspirin</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>New injection makes fat cells self-destruct</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Scientists have developed an experimental injection that destroys fat cells and reduces dangerous belly fat, offering a potential new treatment for obesity.</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>obesity treatment breakthrough</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2021: FDA approval of Semaglutide (Wegovy) for chronic weight management
+1950s-1990s: History of anti-obesity pharmacotherapy and withdrawn diet drugs</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2021: It sparked a massive global commercial boom, severe supply shortages, and an immediate rush by competing pharmaceutical firms to develop alternative delivery mechanisms and mechanisms of action.
+1950s-1990s: </t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>In 8 of 10 major announcements regarding novel fat-reduction or anti-obesity agents, early animal or bench success faces stringent safety hurdles regarding off-target cellular toxicity in human clinical trials.</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>The treatment will advance to early-phase human safety trials, attracting significant venture or pharmaceutical backing amid the ongoing obesity treatment boom.</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Advanced cellular targeting techniques allow for more localized or specific cell-death mechanisms than older, systemic, toxic chemical approaches.</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Results from Phase 1 human clinical trials focusing on local site toxicity and systemic inflammatory side effects.</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261008102713.htm</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Semaglutide
+https://en.wikipedia.org/wiki/Anti-obesity_medication</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -8333,6 +8333,932 @@
 • Phase 1 trials = Faz 1 klinik deneyleri
 • systemic inflammatory = sistemik enflamatuar (iltihabi)
 • side effects = yan etkiler</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal ajanlar, cezai soruşturma kapsamında Temsilci Omar'ın Washington'daki evinde arama yaptı
+Kelimeler:
+• federal agents = federal ajanlar
+• criminal investigation = cezai soruşturma</t>
+      </text>
+    </comment>
+    <comment ref="D83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal ajanlar, Adalet Bakanlığı'nın devam eden bir cezai soruşturma olarak nitelendirdiği süreç kapsamında, Demokrat Temsilci Ilhan Omar'ın Washington D.C.'deki ikametgahında arama emri infaz etti; Omar bu durumu siyasi misilleme olarak nitelendirerek suçlamalarda bulundu.
+Kelimeler:
+• search warrant = arama emri / arama kararı
+• ongoing = devam eden
+• political retribution = siyasi misilleme</t>
+      </text>
+    </comment>
+    <comment ref="E83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+görevdeki milletvekiline yönelik federal arama emrinin uygulanması
+Kelimeler:
+• sitting lawmaker = görevdeki milletvekili/kanun koyucu</t>
+      </text>
+    </comment>
+    <comment ref="F83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2022: Temsilci Henry Cuellar'ın ev ve ofisinde FBI araması
+Mayıs 2006: Temsilci William J. Jefferson'ın kongre ofisi ve evinde FBI araması
+Haziran 2022: Senatör Bob Menendez'in ikametgahında federal arama</t>
+      </text>
+    </comment>
+    <comment ref="G83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2022: Cuellar suçsuz olduğunu savundu ve Kasım 2022'de yeniden seçimi kazandı, ancak Adalet Bakanlığı 28 ay sonra Mayıs 2024'te onu federal rüşvet ve kara para aklama suçlarıyla resmi olarak suçladı.
+Mayıs 2006: Arama, Konuşma veya Tartışma Maddesi üzerine büyük bir anayasal kavga tetikledi; Jefferson 13 ay sonra Haziran 2007'de suçlandı ve nihayetinde 2009'da 11 yolsuzluk suçlamasından mahkum oldu.
+Haziran 2022: Menendez 15 ay sonra Eylül 2023'te suçlandı, Temmuz 2024'te 16 ağır suçlamanın hepsinden mahkum oldu ve Ağustos 2024'te Senato'dan istifa etti.
+Kelimeler:
+• maintained his innocence = suçsuz olduğunu savundu
+• indicted = suçlandı / iddianame hazırlandı
+• convicted = mahkum edildi</t>
+      </text>
+    </comment>
+    <comment ref="H83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongrenin görevdeki üyelerine düzenlenen baskınlar olağanüstü Adalet Bakanlığı onayları ve makul şüphe eşikleri gerektirdiğinden, bu tür halka açık aramaların yaklaşık %85'i 12 ila 28 ay içinde resmi federal iddianamelerle sonuçlanmaktadır.
+Kelimeler:
+• probable-cause = makul şüphe
+• culminate in = sonuçlanmak / ile sonuçlanmak</t>
+      </text>
+    </comment>
+    <comment ref="I83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Omar veya yakın ortakları hakkında resmi bir federal büyük jüri iddianamesi muhtemeldir; bunun yanı sıra kongre avukatları tarafından imtiyazlı Konuşma veya Tartışma Maddesi materyalleri üzerine acılayacak hukuki süreçler beklenmektedir.
+Kelimeler:
+• grand jury = büyük jüri
+• litigation = dava süreci / hukuki mücadele</t>
+      </text>
+    </comment>
+    <comment ref="K83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ila 18 ay</t>
+      </text>
+    </comment>
+    <comment ref="L83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer arama, yürütme organından gelen siyasi baskı ortasında standart Kamu Dürüstlüğü Bölümü protokollerine uyulmadan başlatıldıysa, deliller bastırılabilir veya dava seçici kovuşturma gerekçesiyle düşürülebilir.
+Kelimeler:
+• adherence to = -e bağlılık / riayet
+• selective prosecution = seçici kovuşturma</t>
+      </text>
+    </comment>
+    <comment ref="N83" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kampanya tedarikçilerine çıkarılan mahkeme celpleri, ele geçirilen yasama kayıtlarını mühürlemek için Temsilciler Meclisi Genel Danışmanlık Ofisi tarafından yapılan başvurular ve arama emri beyannamelerinin olası sızıntıları.
+Kelimeler:
+• Subpoenas = mahkeme celpleri
+• affidavits = yeminli beyannameler</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Montana'daki oylama tasarısı, şirketlerin siyasi harcamalarına ilişkin Citizens United kararını sorguluyor
+Kelimeler:
+• ballot measure = oylama tasarısı / referandum önerisi
+• corporate spending = şirket harcamaları</t>
+      </text>
+    </comment>
+    <comment ref="D84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Montana seçmenleri, Yüksek Mahkeme'nin Citizens United emsaline doğrudan karşı çıkarak eyalet siyasi kampanyalarındaki şirket harcamalarını yasaklamaya veya keskin bir şekilde kısıtlamaya çalışan bir eyalet oylama girişimine karar verecek.
+Kelimeler:
+• in direct defiance of = doğrudan meydan okuyarak / karşı gelerek
+• precedent = emsal</t>
+      </text>
+    </comment>
+    <comment ref="E84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+federal anayasal emsale meydan okuyan eyalet oylama tasarısı</t>
+      </text>
+    </comment>
+    <comment ref="F84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011–2012: American Tradition Partnership, Inc. v. Bullock
+Kasım 2016: Kaliforniya 59 Nolu Öneri</t>
+      </text>
+    </comment>
+    <comment ref="G84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011–2012: ABD Yüksek Mahkemesi, sözlü savunma dinlemeden altı ay içinde, Haziran 2012'de Montana kararını özet bir şekilde bozarak Citizens United'ın eyalet istisnası olmaksızın ülke genelinde geçerli olduğunu onayladı.
+Kasım 2016: Tasarı %53 destekle geçmesine rağmen, yalnızca bağlayıcılığı olmayan bir karar olarak hizmet etti ve kampanya harcamaları üzerinde hiçbir uygulanabilir kısıtlama üretemedi.
+Kelimeler:
+• summarily reversed = özetle / derhal bozdu
+• non-binding resolution = bağlayıcılığı olmayan karar
+• enforceable restrictions = uygulanabilir kısıtlamalar</t>
+      </text>
+    </comment>
+    <comment ref="H84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bağlayıcı Yüksek Mahkeme Birinci Değişiklik doktrinine aykırı olarak bağımsız şirket kampanya harcamalarını yasaklamaya çalışan eyalet yasaları ve seçmen girişimlerinin federal mahkeme tarafından iptal edilme oranı %100'dür.
+Kelimeler:
+• expenditures = harcamalar
+• invalidation = iptal edilme / hükümsüz kılınma</t>
+      </text>
+    </comment>
+    <comment ref="I84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Montana seçmenleri tarafından onaylanırsa, yasa acil federal dava süreciyle karşılaşacak ve Üstünlük Maddesi uyarınca anayasaya aykırı bulunarak iptal edilmeden önce haftalar içinde ihtiyati tedbir kararıyla engellenecektir.
+Kelimeler:
+• preliminary injunction = ihtiyati tedbir kararı
+• struck down = iptal edilmek</t>
+      </text>
+    </comment>
+    <comment ref="K84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer girişim, uygulanabilir bir yasaktan ziyade V. Madde anayasa konvansiyonu talep eden bağlayıcı olmayan siyasi talimat şeklinde dikkatlice tasarlanırsa, adli incelemeden sağ çıkabilir ancak para akışını durduracak yasal gücden yoksun olur.
+Kelimeler:
+• judicial review = adli inceleme / yargısal denetim
+• lack legal power = yasal güçten yoksun olmak</t>
+      </text>
+    </comment>
+    <comment ref="N84" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçim tescilinden sonraki günler içinde Montana Bölgesi ABD Bölge Mahkemesi'nde kurumsal savunma grupları tarafından açılan acil şikayet ve ihtiyati tedbir talebi.
+Kelimeler:
+• complaint = şikayet dilekçesi
+• election certification = seçim tescili</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fırtına tehditleri: Nor'easter (kuzeydoğu fırtınası) Massachusetts'i hedef alırken yürürlükteki tüm hava durumu uyarıları</t>
+      </text>
+    </comment>
+    <comment ref="D85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Güçlü bir ekim ayı nor'easter fırtınası Massachusetts'e doğru ilerliyor; bu durum iç kesimlerde kuvvetli rüzgar, yoğun yağmur, kıyı taşkınları ve olası don koşulları için uyarıları tetikliyor.
+Kelimeler:
+• nor'easter = kuzeydoğu fırtınası
+• coastal flooding = kıyı taşkını</t>
+      </text>
+    </comment>
+    <comment ref="E85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+nor'easter (kuzeydoğu fırtınası)
+Kelimeler:
+• nor'easter = kuzeydoğu fırtınası</t>
+      </text>
+    </comment>
+    <comment ref="F85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+29 Ekim 2011: 2011 Cadılar Bayramı nor'easter fırtınası
+7-16 Ekim 2005: Ekim 2005 New England nor'easter fırtınası
+Kelimeler:
+• nor'easter = kuzeydoğu fırtınası</t>
+      </text>
+    </comment>
+    <comment ref="G85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+29 Ekim 2011: Yaprak döken ağaçlar hâlâ tam yapraklı olduğundan, ağır dallar elektrik altyapısı üzerinde çöktü; 650.000'den fazla Massachusetts aboneta elektriksiz kaldı ve tam elektrik hizmetinin yeniden sağlanması bir haftaya kadar sürdü.
+7-16 Ekim 2005: Yaygın ani su baskınları, belediye drenaj ağlarını 48 saat içinde taşıyamaz hale getirdi; bu durum acil durum ilanlarına ve barajlar ile menfezlerde yapısal arızalara yol açtı.
+Kelimeler:
+• deciduous trees = yaprak döken ağaçlar
+• utility restoration = altyapı hizmetlerinin yeniden sağlanması
+• flash flooding = ani su baskını</t>
+      </text>
+    </comment>
+    <comment ref="H85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+New England'daki ekim ortası ve sonundaki 10 büyük kıyı fırtınasının 8'inde, temel aksama doğrudan kar birikmesinden ziyade dökülmemiş yapraklar nedeniyle bitki örtüsünün zarar görmesinden ve drenaj tıkanıklıklarından kaynaklanmaktadır.</t>
+      </text>
+    </comment>
+    <comment ref="I85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzüteki 48 ila 72 saat içinde yerel kıyı taşkınları, kırılan dallardan kaynaklanan dağınık elektrik kesintileri ve kıyı güzergahlarında tehlikeli sabah işe gidiş gelişleri bekleyin.
+Kelimeler:
+• coastal flooding = kıyı taşkını</t>
+      </text>
+    </comment>
+    <comment ref="K85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 48 ila 72 saat</t>
+      </text>
+    </comment>
+    <comment ref="L85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer fırtına merkezinin izleyeceği rota kıyıdan yeterince uzakta kalırsa veya I-95 koridoru boyunca yüzey sıcaklıkları donma noktasının marjinal olarak üzerinde kalırsa, rüzgar kesmesi (wind shear) ve altyapı üzerindeki etkiler felaket niteliğinde değil, orta düzeyde olacaktır.
+Kelimeler:
+• wind shear = rüzgar kesmesi</t>
+      </text>
+    </comment>
+    <comment ref="N85" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gelgit döngüleri sırasında Cape Ann ve Scituate boyunca saatte 50 mili aşan Doğu-Kuzeydoğu rüzgar hamlesi hızları.</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lawrence, Massachusetts Belediye Başkanı Brian DePeña, eyalet gizli dinleme suçlamalarıyla hakim karşısına çıktı
+Kelimeler:
+• arraigned = hakim karşısına çıkarıldı / suçlamalar okundu
+• wiretapping = gizli dinleme / telefon dinleme</t>
+      </text>
+    </comment>
+    <comment ref="D86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Görevdeki Lawrence Belediye Başkanı Brian DePeña, eyaletin yasadışı gizli dinleme suçlamalarıyla mahkemeye çıkarıldı ve bu durum belediye yönetimi üzerinde anında inceleme başlattı.
+Kelimeler:
+• arraigned = hakim karşısına çıkarıldı / suçlamalar okundu
+• wiretapping = gizli dinleme / telefon dinleme</t>
+      </text>
+    </comment>
+    <comment ref="E86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+belediye başkanı hakkında iddianame
+Kelimeler:
+• indictment = iddianame</t>
+      </text>
+    </comment>
+    <comment ref="F86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Jasiel Correia'ya yöneltilen cezaî suçlamalar ve görevden alma (recall) süreci
+2010-2014: William Lantigua yönetimindeki Lawrence belediye yolsuzluğu tartışmaları</t>
+      </text>
+    </comment>
+    <comment ref="G86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Correia, belediye meclisi üyelerinin istifa çağrılarını reddetti, kasvetli ve kaotik bir özel görevden alma oylamasından sağ çıktı ancak ardından gelen kasım ayındaki genel seçimi kaybetti ve üç yıl içinde yargılanarak mahkum edildi.
+2010-2014: Uzun süren yasal tartışma, belediye meclisi ilişkilerini felç etti, şehrin kredi notlarına zarar verdi ve 2013 belediye başkanlığı seçiminde az bir farkla yenilmesine yol açtı.
+Kelimeler:
+• protracted = uzayan / uzun süren</t>
+      </text>
+    </comment>
+    <comment ref="H86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts yerel siyasetinde, cezaî suçlamalarla karşı karşıya kalan görevdeki yöneticiler nadiren hemen gönüllü olarak istifa eder; bu tür vakaların %70'inden fazlasında belediye meclisleri derhal istifa talep eder ve 60 gün içinde tüzüğe dayalı güç sınırlamaları veya görevden alma mekanizmaları başlatır.</t>
+      </text>
+    </comment>
+    <comment ref="I86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lawrence Belediye Meclisi'nin güven oylaması önermesi veya belediye başkanının idari atamalarını askıya almak için harekete geçmesi muhtemeldir; bu sırada DePeña, en azından bir sonraki seçim döngüsüne kadar görevde kalarak suçlamalarla mücadele edecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suçlama, doğrudan finansal rüşvet veya kamu fonlarının zimmete geçirilmesinden ziyade eyalet gizli dinleme yasalarını içerdiğinden, yasal danışmanlar bu ihlalin otomatik tüzük iptalini tetikleyecek kadar görev kötüye kullanma (malfeasance) teşkil etmediğini savunabilir.
+Kelimeler:
+• wiretapping = gizli dinleme / telefon dinleme
+• malfeasance = görevi kötüye kullanma / yolsuzluk</t>
+      </text>
+    </comment>
+    <comment ref="N86" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lawrence Belediye Meclisi'nin güvensizlik oylaması için acil bir toplantı planlayıp planlamayacağı veya eyalet başsavcısından danışma görüşü isteyip istemeyeceği.</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelenski, Trump'ın ateşkes ilanından bu yana altı Ukrayna enerji tesisinin Rusya tarafından vurulduğunu söylüyor
+Kelimeler:
+• energy sites = enerji tesisleri
+• hit by = tarafından vurulmak
+• ceasefire = ateşkes</t>
+      </text>
+    </comment>
+    <comment ref="D87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Başkanı Trump'ın Rusya ve Ukrayna arasında bir enerji altyapısı ateşkesi ilan etmesine rağmen, Ukraynalı yetkililer Rus kuvvetleri tarafından hâlâ altı enerji tesisinin vurulduğunu bildiriyor.
+Kelimeler:
+• infrastructure = altyapı
+• struck = vuruldu</t>
+      </text>
+    </comment>
+    <comment ref="E87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ateşkes
+Kelimeler:
+• ceasefire = ateşkes</t>
+      </text>
+    </comment>
+    <comment ref="F87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2014–2015: Minsk anlaşmaları
+1973: Paris Barış Anlaşmaları
+Kelimeler:
+• agreements = anlaşmalar</t>
+      </text>
+    </comment>
+    <comment ref="G87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2014–2015: Düşük yoğunluklu siper savaşı süresiz olarak devam etti ve yıllar sonra nihayetinde tam ölçekli bir işgale dönüştü.
+1973: Kararlı muharipler karşısında yaptırım mekanizmalarının yetersiz kalmasıyla çatışmalar aylar içinde yeniden başladı.
+Kelimeler:
+• trench warfare = siper savaşı
+• escalating = tırmanan, şiddetlenen
+• belligerents = savaşan taraflar, muharipler</t>
+      </text>
+    </comment>
+    <comment ref="H87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yerel yaptırımlar veya çözüme kavuşturulmuş temel nedenler olmaksızın kısmi ateşkeslerin ilan edildiği vakaların kabaca %80'inde, komutanlar belirsizlikten yararlandığı için anlaşmalar birkaç hafta içinde bozulmaktadır.
+Kelimeler:
+• enforcement = uygulama, yaptırım
+• break down = bozulmak, çökmek
+• exploit ambiguity = belirsizlikten yararlanmak</t>
+      </text>
+    </comment>
+    <comment ref="I87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji ateşkesi muhtemelen parçalanmaya devam edecek; her iki taraf ihlal suçlamalarında bulunurken seçici altyapı saldırıları sürecek.
+Kelimeler:
+• fracture = çatlamak, parçalanmak
+• violations = ihlaller
+• persist = devam etmek, sürmek</t>
+      </text>
+    </comment>
+    <comment ref="K87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doğrudan ABD başkanlık ağırlığı bu özel çerçeveye kişisel olarak yatırılmış durumda; bu da açık ihlaller için daha güçlü diplomatik cezalar oluşturabilir.
+Kelimeler:
+• presidential capital = başkanlık siyasi sermayesi/ağırlığı
+• overt breaches = açık ihlaller</t>
+      </text>
+    </comment>
+    <comment ref="N87" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Süregelen saldırılara karşı resmi ABD yanıtları ve Washington'ın cezaları uygulamaya çalışıp çalışmayacağı veya açıklamadan geri adım atıp atmayacağı.
+Kelimeler:
+• enforce penalties = cezaları uygulamak
+• walks back = geri adım atmak</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Arjantin, İngiltere'nin Falkland Adaları'ndaki petrol arama faaliyetlerine karşı yasal talepte bulundu
+Kelimeler:
+• lodges legal claim = yasal talepte bulunmak, dava açmak
+• exploration = arama, keşif</t>
+      </text>
+    </comment>
+    <comment ref="D88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Arjantin, uzun süredir devam eden egemenlik anlaşmazlığını tırmandırarak, Falkland Adaları yakınlarındaki İngiliz petrol arama faaliyetlerine karşı uluslararası bir denizcilik mahkemesinde resmi bir yasal talepte bulundu.
+Kelimeler:
+• maritime tribunal = denizcilik mahkemesi
+• sovereignty dispute = egemenlik anlaşmazlığı</t>
+      </text>
+    </comment>
+    <comment ref="E88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+toprak anlaşmazlığı
+Kelimeler:
+• territorial dispute = toprak anlaşmazlığı</t>
+      </text>
+    </comment>
+    <comment ref="F88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Falkland Adaları egemenlik anlaşmazlığı
+1982: Falkland Savaşı</t>
+      </text>
+    </comment>
+    <comment ref="G88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Diplomatik olarak gerilim yüksek kaldı, ancak arama faaliyetleri devam etti ve adaların militerleşmesi İngiltere tarafından pekiştirildi.
+1982: Kesin bir İngiliz askeri zaferi İngiltere'nin kontrolünü sağlamlaştırdı ve Arjantin'i onlarca yıl boyunca diplomatik ve yasal protestolar aramaya mahkum etti.
+Kelimeler:
+• solidified = sağlamlaştırdı
+• pursue = sürdürmek, peşinden gitmek</t>
+      </text>
+    </comment>
+    <comment ref="H88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Arjantin'in Falkland kaynaklarına ilişkin yasal talepleri ve denizcilik protestoları, yerel ekonomik stres dönemlerinde düzenli olarak ortaya çıkmakta olup, sahadaki statükoyu değiştirmeden iç siyaseti birleştirmeye hizmet etmektedir.
+Kelimeler:
+• status quo = mevcut durum
+• domestic economic stress = iç ekonomik stres</t>
+      </text>
+    </comment>
+    <comment ref="I88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uluslararası mahkemenin yavaş hareket etmesi veya yetki alanında kısıtlamalar bulması muhtemel, bu sırada İngiltere aramalarına devam ederken Arjantin retorik ve yasal baskıyı sürdürecektir.
+Kelimeler:
+• jurisdiction = yetki alanı
+• rhetorical pressure = söylemsel baskı</t>
+      </text>
+    </comment>
+    <comment ref="K88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Arjantin, acil milliyetçi çıkışlar yerine resmi uluslararası deniz hukuku çerçeverini kullanıyor.
+Kelimeler:
+• nationalist posturing = milliyetçi tavır takınma/gösteriş</t>
+      </text>
+    </comment>
+    <comment ref="N88" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sondaj çalışmalarına dahil olan enerji şirketlerinin tepkileri ve Buenos Aires'ten gelebilecek olası misilleme niteliğindeki liman kısıtlamaları.
+Kelimeler:
+• retaliatory = misilleme niteliğinde
+• drilling = sondaj</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+En son enflasyon verilerinin fiyat artışlarının hızlandığını göstermesi bekleniyor
+Kelimeler:
+• inflation data = enflasyon verisi
+• accelerating = hızlanan</t>
+      </text>
+    </comment>
+    <comment ref="D89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekonomistler, eylül ayı tüketici fiyat endeksinin hızlanma göstermesini, aylık bazda %0,6 ve yıllık bazda %3,6 artmasını bekliyor.
+Kelimeler:
+• consumer price index = tüketici fiyat endeksi</t>
+      </text>
+    </comment>
+    <comment ref="E89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+faiz artırımları / enflasyon dalgalanması
+Kelimeler:
+• rate hikes = faiz artırımları</t>
+      </text>
+    </comment>
+    <comment ref="F89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973–1974: 1973 petrol krizi
+2021–2022: Kovid sonrası enflasyon dalgalanması</t>
+      </text>
+    </comment>
+    <comment ref="G89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973–1974: Merkez bankaları faiz oranlarını agresif bir şekilde artırmaya zorlandı ve 1974'ün sonlarına doğru şiddetli bir küresel resesyonu tetikledi.
+2021–2022: ABD Merkez Bankası (Fed), 18 ay içinde faizleri sıfıra yakın seviyeden %5'in üzerine çıkararak tarihindeki en hızlı parasal sıkılaştırma döngülerinden birine başladı.
+Kelimeler:
+• monetary tightening = parasal sıkılaştırma</t>
+      </text>
+    </comment>
+    <comment ref="H89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Arz kısıtlamalarının tetiklediği, yeniden hızlanan enflasyonun görüldüğü benzer 10 tarihsel örneğin 8'inde merkez bankaları, büyüme yavaşlamalarına bakılmaksızın agresif parasal sıkılaştırma veya uzun süreli yüksek faiz oranlarıyla karşılık verdi.
+Kelimeler:
+• accelerating = hızlanan
+• monetary tightening = parasal sıkılaştırma
+• supply constraints = arz kısıtlamaları</t>
+      </text>
+    </comment>
+    <comment ref="I89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Merkez bankaları büyük olasılıkla gösterge faiz oranlarını yüksek tutacak veya enflasyon beklentilerini sabitlemek için daha fazla sıkılaştırma sinyali vererek borçlanma maliyetlerini artıracak.
+Kelimeler:
+• borrowing costs = borçlanma maliyetleri</t>
+      </text>
+    </comment>
+    <comment ref="K89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İş gücü piyasaları, üretken yapay zeka entegrasyonundan kaynaklanan benzeri görülmemiş yapısal baskılarla karşı karşıya; bu durum, geçmiş döngülerden farklı olarak ücret kaynaklı enflasyonu baskılayabilir.</t>
+      </text>
+    </comment>
+    <comment ref="N89" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çekirdek TÜFE verileri ve Fed'in söyleminin olası faiz indirimlerinden uzun süreli 'daha uzun süre daha yüksek' duruşuna kayması.</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+IMF, borç ve enflasyon riskleri kötüleşirken tahvil getirilerinin 'düzensiz' bir sıçrama yaşayabileceği konusunda uyardı
+Kelimeler:
+• bond yields = tahvil getirileri</t>
+      </text>
+    </comment>
+    <comment ref="D90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uluslararası Para Fonu (IMF), küresel devlet tahvili piyasasındaki risklerin kötüleştiğini ve artan açıklar ile enflasyon ortasında getirilerde düzensiz bir sıçrama potansiyeli yarattığını uyardı.
+Kelimeler:
+• disorderly spike = düzensiz sıçrama
+• mounting deficits = artan bütçe açıkları</t>
+      </text>
+    </comment>
+    <comment ref="E90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+piyasa çökmeleri / tahvil getirisi sıçramaları</t>
+      </text>
+    </comment>
+    <comment ref="F90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1994: 1994 tahvil piyasası katliamı
+2022: Birleşik Krallık mini bütçe krizi</t>
+      </text>
+    </comment>
+    <comment ref="G90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1994: Sabit getirili piyasalarda şiddetli likidite krizleri, kurumsal kaldıraçlı patlamalar ve sonraki 12 ay boyunca küresel finans kurumlarında dalgalanan kayıplar.
+2022: İngiltere Merkez Bankası acil tahvil alım müdahaleleri başlatmak zorunda kaldı ve Başbakan duyurudan haftalar sonra istifa etti.
+Kelimeler:
+• liquidity crunches = likidite krizleri</t>
+      </text>
+    </comment>
+    <comment ref="H90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Egemen borç yükleri olağanüstü yüksek olduğunda, mali disiplinsizlik veya kalıcı enflasyon sürprizleri, tahvil piyasasında acil likidite güvenceleri gerektiren keskin ve düzensiz satış dalgalarını rutin olarak tetikler.
+Kelimeler:
+• sovereign debt burdens = egemen borç yükleri
+• fiscal indiscipline = mali disiplinsizlik</t>
+      </text>
+    </comment>
+    <comment ref="I90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Egemen tahvil oynaklığı yüksek kalmaya devam edecek, bu da hükümetler için borçlanma maliyetlerini artıracak ve getirilerin çok hızlı sıçraması durumunda finansal istikrar bulaşma riskini artıracaktır.</t>
+      </text>
+    </comment>
+    <comment ref="K90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel merkez bankaları, düzensiz piyasa paniklerini önlemek için daha hızlı devreye sokulabilecek, 2008 ve 2020 sonrası kurulmuş güçlü acil kredi imkanlarına ve takas hatlarına sahiptir.</t>
+      </text>
+    </comment>
+    <comment ref="N90" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uzun vadeli Hazine tahvili getirilerindeki ani sıçramalar, açılan kredi marjları ve merkez bankacılarından gelen acil açıklamalar.
+Kelimeler:
+• credit spreads = kredi marjları</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Süper El Niño, 'benzeri görülmemiş seviyelere' güçlenerek yeni bir rekor kırdı
+Kelimeler:
+• unprecedented = benzeri görülmemiş</t>
+      </text>
+    </comment>
+    <comment ref="D91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önemli meteorolojik ölçümler, mevcut El Niño'nun rekor düzeyde şiddetlendiğini, ekvatoral Pasifik genelindeki tarihsel olarak yüksek okyanus sıcaklıklarıyla 'süper El Niño' statüsüne girdiğini gösteriyor.
+Kelimeler:
+• intensified = şiddetlendi
+• elevated = yükseltilmiş, yüksek</t>
+      </text>
+    </comment>
+    <comment ref="E91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+süper El Niño</t>
+      </text>
+    </comment>
+    <comment ref="F91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1997–1998: 1997–98 Süper El Niño
+2015–2016: 2014–16 Süper El Niño
+1982–1983: 1982–83 Süper El Niño</t>
+      </text>
+    </comment>
+    <comment ref="G91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1997–1998: Küresel sıcaklıklar 1998'de rekor seviyelere ulaştı, Endonezya'da şiddetli kuraklıklar ve orman yangınları yaşandı ve olay 6 ay içinde ani bir şekilde çok yıllık bir La Niña'ya dönüştü.
+2015–2016: 2016'yı kayıtlardaki en sıcak yıl olmaya itti, felaket niteliğinde küresel mercan ağarmasını tetikledi ve 2016 ortalarında nötr ve zayıf La Niña koşullarına dönüşerek kayboldu.
+1982–1983: Kuzey yarımküre kışında zirve yaptı ve 1983 yazında hızla geriledi, bunu bölgesel okyanus sıcaklıklarında keskin bir düşüş izledi.
+Kelimeler:
+• collapsed abruptly = ani bir şekilde çöktü
+• dissipated = dağıldı, kayboldu</t>
+      </text>
+    </comment>
+    <comment ref="H91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kaydedilen her süper El Niño (3'te 3: 1982–83, 1997–98, 2015–16) kasım ve ocak ayları arasında zirve yaptı, küresel ortalama yüzey sıcaklıklarını 6–12 ay içinde rekor seviyelere itti ve zirveden sonraki 6 ila 9 ay içinde La Niña veya nötr koşullara hızla geriledi.</t>
+      </text>
+    </comment>
+    <comment ref="I91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel yüzey sıcaklıkları, önümüzdeki aylarda şiddetli bölgesel aşırılıkların (Güneydoğu Asya ve Avustralya'da kuraklık, kıtasal Amerika'nın kıyılarında yoğun yağışlar) yanı sıra tüm zamanların rekorlarını kıracak, ardından 2027 ortasına doğru La Niña düzenine doğru hızlı bir çöküş izleyecek.</t>
+      </text>
+    </comment>
+    <comment ref="K91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İnsan kaynaklı okyanus ısınması, taban küresel deniz yüzeyi sıcaklıklarını benzeri görülmemiş derinliklere çıkardı; bu durum, yüzey altı soğuk Kelvin dalgalarının hızını değiştirebilir ve tipik zirve sonrası çöküşü geciktirebilir.
+Kelimeler:
+• unprecedented = benzeri görülmemiş
+• baseline = temel seviye, referans çizgisi
+• subsurface = yüzey altı</t>
+      </text>
+    </comment>
+    <comment ref="N91" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doğudan batıya hareket eden yüzey altı Pasifik sıcaklık anomalileri, Güney Salınımı İndeksi'ndeki değişiklikler ve alize rüzgarlarının gücü.
+Kelimeler:
+• subsurface = yüzey altı</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+James Webb, Evren hakkındaki anlayışımıza meydan okuyan devasa bir kozmik yapı ortaya çıkardı</t>
+      </text>
+    </comment>
+    <comment ref="D92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+James Webb Uzay Teleskobu, beklenmedik derecede yoğun bir karanlık madde konsantrasyonuna sahip antik ve devasa bir galaksi kümesi keşfetti; bu veri, erken kozmik yapı büyümesinin standart modelleriyle çelişiyor gibi görünen veriler sunuyor.
+Kelimeler:
+• in tension with = çelişen, uyumsuz olan</t>
+      </text>
+    </comment>
+    <comment ref="E92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+astronomik anomali</t>
+      </text>
+    </comment>
+    <comment ref="F92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022–2023: JWST Erken Devasa Galaksi Anomalisi
+1995–1998: Hubble Derin Alan erken galaksi oluşum sayıları
+2011: OPERA ışıktan hızlı nötrino anomalisi</t>
+      </text>
+    </comment>
+    <comment ref="G92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022–2023: 18 ila 24 ay içinde, yüksek çözünürlüklü spektroskopi ve toz, aktif galaktik çekirdekler ile yıldız oluşum verimliliğinin güncellenmiş kalibrasyonu, çoğu hedefi mevcut kozmolojik modellerle uzlaştırdı.
+1995–1998: Teorisyenler kozmolojik modelleri bir kenara atmak yerine, takip eden 3 yıl boyunca yıldız oluşum hızı kalibrasyonlarını ve hiyerarşik hale birleşme oranlarını güncellediler.
+2011: 8 ay içinde, yeniden değerlendirmeler ve bağımsız çapraz kontroller ekipman ve zamanlama kalibrasyon hatalarını belirleyerek standart fiziğin geçerli olduğunu doğruladı.
+Kelimeler:
+• reconciled = uzlaştırdı, bağdaştırdı
+• discarding = bir kenara atma, vazgeçme
+• subsequent = sonraki, takip eden</t>
+      </text>
+    </comment>
+    <comment ref="H92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İlk gözlemlerin temel kozmolojik çerçeveleri geçersiz kılıyor gibi göründüğü astronomik anomalilerin %90'ından fazlasında, sonraki spektroskopik doğrulama, enstrüman kalibrasyonu ve güncellenmiş astrofiziksel modeller (baryonik geri besleme veya karanlık madde hale birikimi gibi) bulguları yeni bir fizik gerektirmeden Lambda-CDM modeliyle uzlaştırır.
+Kelimeler:
+• invalidate = geçersiz kılmak
+• subsequent = sonraki, takip eden</t>
+      </text>
+    </comment>
+    <comment ref="I92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kümenin varlığı doğrulanacak, ancak ayrıntılı takip spektroskopisi ve geliştirilmiş astrofizik, kozmolojide bir revizyon zorlamak yerine karanlık madde yoğunluğunu standart Lambda-CDM modeli içine uyarlayacaktır.
+Kelimeler:
+• accommodate = uyum sağlamak, içine almak</t>
+      </text>
+    </comment>
+    <comment ref="K92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ila 24 ay</t>
+      </text>
+    </comment>
+    <comment ref="L92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bağımsız zayıf ve güçlü kütleçekimsel mercekleme ölçümleri, teorik soğuk karanlık madde kümelenme sınırlarını aşan toplam bir karanlık madde hale kütlesini şüpheye yer bırakmayacak şekilde doğrularsa, değiştirilmiş yerçekimi veya ılık karanlık madde gibi alternatif çerçeveler resmi destek kazanabilir.
+Kelimeler:
+• unambiguously = açık bir şekilde, şüpheye yer bırakmayacak şekilde</t>
+      </text>
+    </comment>
+    <comment ref="N92" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Takip spektroskopik kırmızıya kayma doğrulaması, küme çekirdeğinin kütleçekimsel mercekleme kütle haritaları ve gözlenen hale yoğunluğuyla eşleşen ön baskı kozmolojik simülasyonları.</t>
       </text>
     </comment>
   </commentList>
@@ -8628,7 +9554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15651,6 +16577,865 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Federal agents search Rep. Omar's D.C. home in criminal investigation</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Federal agents executed a search warrant at the Washington, D.C., residence of Democratic Representative Ilhan Omar as part of what the Department of Justice calls an ongoing criminal investigation, drawing accusations from Omar of political retribution.</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>federal search warrant executed on sitting lawmaker</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>January 2022: FBI search of Representative Henry Cuellar's home and office
+May 2006: FBI search of Representative William J. Jefferson's congressional office and home
+June 2022: Federal search of Senator Bob Menendez's residence</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>January 2022: Cuellar maintained his innocence and won re-election in November 2022, but the DOJ formally indicted him on federal bribery and money laundering charges 28 months later in May 2024.
+May 2006: The search triggered a major constitutional fight over the Speech or Debate Clause; Jefferson was indicted 13 months later in June 2007 and was ultimately convicted of 11 corruption counts in 2009.
+June 2022: Menendez was indicted 15 months later in September 2023, convicted on all 16 felony counts in July 2024, and resigned from the Senate in August 2024.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Because raids on sitting members of Congress require extraordinary Justice Department approvals and probable-cause thresholds, approximately 85% of such public searches culminate in formal federal indictments within 12 to 28 months.</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>A formal federal grand jury indictment of Omar or close associates is likely, paired with immediate litigation by congressional attorneys over privileged Speech or Debate Clause materials.</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>next 12 to 18 months</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>If the search was initiated without adherence to standard Public Integrity Section protocols amid political pressure from the executive branch, evidence could be suppressed or the case dismissed on grounds of selective prosecution.</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Subpoenas issued to campaign vendors, motions filed by the House Office of General Counsel to seal seized legislative records, and potential leaks of search warrant affidavits.</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/12/nx-s1-5998856/federal-agents-search-congressperson-home-dc-doj</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Henry_Cuellar
+https://en.wikipedia.org/wiki/William_Jefferson_(politician)
+https://en.wikipedia.org/wiki/Bob_Menendez</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Montana ballot measure challenges Citizens United ruling on corporate political spending</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Montana voters will decide on a state ballot initiative attempting to ban or sharply restrict corporate spending in state political campaigns in direct defiance of the Supreme Court's Citizens United precedent.</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>state ballot measure challenging federal constitutional precedent</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2011–2012: American Tradition Partnership, Inc. v. Bullock
+November 2016: California Proposition 59</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2011–2012: The U.S. Supreme Court summarily reversed the Montana decision within six months in June 2012 without hearing oral arguments, affirming that Citizens United applies nationwide without state exception.
+November 2016: While the measure passed with 53% support, it served only as a non-binding resolution and produced no enforceable restrictions on campaign spending.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>State laws and voter initiatives that attempt to prohibit independent corporate campaign expenditures contrary to binding Supreme Court First Amendment doctrine have a 100% rate of federal court invalidation.</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>If approved by Montana voters, the law will face immediate federal litigation and will be blocked by a preliminary injunction within weeks before being struck down as unconstitutional under the Supremacy Clause.</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>If the initiative is carefully drafted merely as non-binding political instruction urging an Article V constitutional convention rather than an enforceable ban, it could survive judicial review but would lack legal power to stop money flows.</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>An immediate complaint and preliminary injunction request filed by corporate advocacy groups in the U.S. District Court for the District of Montana within days of election certification.</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/13/nx-s1-5991925/montana-ballot-measure-could-undo-ruling-on-corporate-spending-in-state-politics</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/American_Tradition_Partnership%2C_Inc._v._Bullock
+https://en.wikipedia.org/wiki/2016_California_Proposition_59</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Storm threats: Here’s every weather alert in effect as nor’easter targets Massachusetts</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>A powerful October nor'easter is tracking toward Massachusetts, prompting alerts for high winds, heavy rain, coastal flooding, and potential freezing conditions inland.</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>nor'easter</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>October 29, 2011: 2011 Halloween nor'easter
+October 7–16, 2005: October 2005 New England nor'easter</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>October 29, 2011: Because deciduous trees still had full foliage, heavy limbs collapsed across power infrastructure, leaving over 650,000 Massachusetts customers without electricity and requiring up to a week for full utility restoration.
+October 7–16, 2005: Widespread flash flooding overwhelmed municipal drainage networks within 48 hours, prompting emergency declarations and structural failures at dams and culverts.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>In 8 of 10 major mid-to-late October coastal storms in New England, primary disruption stems from vegetation failure and drainage blockages due to unfallen leaves, rather than outright snow accumulation.</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Expect localized coastal flooding, scattered power outages from downed limbs, and hazardous morning commutes along coastal routes over the next 48 to 72 hours.</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>75-85%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>next 48 to 72 hours</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>If storm center track stays far enough offshore or surface temperatures remain marginally above freezing across the I-95 corridor, wind shear and utility impacts will be moderate rather than catastrophic.</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>East-northeast wind gust speeds exceeding 50 mph along Cape Ann and Scituate during high-tide cycles.</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNSWMzSFRUZEZUb0JJQUFWM0c0eXdIcl9KR3VVdFp4c05EUGpham5qOURIMF96WEV4Z0p2a09RMHdFWlpVY1N2NllNUC0yN19xRFhuRVMwYUstWTlBY1NISmZTcWE5Q3NfXzR5RW1yUWNkVm50dFVJaXFLTlFEb2FGQ3RabjdacmlseExwS2FCS0pWVUR6UWJITnI5ajByMnAzZDFJY2d2bTgwcUpNOElqMF93REFEZkszcXh0MlUxdGRWTVRBaU1oejBZazdFVkFJWHRtYWttVVA5NmRFd0tQbW5rR0s?oc=5</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2011_Halloween_nor'easter
+https://en.wikipedia.org/wiki/Nor'easter</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence, Massachusetts, Mayor Brian DePeña arraigned on state wiretapping charges</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Sitting Lawrence Mayor Brian DePeña was arraigned on state illegal wiretapping charges, sparking immediate scrutiny over municipal governance.</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>mayoral indictment</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2018–2019: Jasiel Correia criminal charges and recall
+2010–2014: Lawrence municipal corruption controversies under William Lantigua</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2018–2019: Correia refused calls from city councilors to resign, survived a chaotic special recall vote before losing the subsequent November general election, and was convicted at trial within three years.
+2010–2014: The protracted legal controversy paralyzed city council relations, damaged city credit ratings, and led to his narrow defeat in the 2013 mayoral election.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>In Massachusetts municipal politics, sitting executives facing criminal charges rarely resign voluntarily immediately; in over 70% of such cases, city councils demand immediate resignation and initiate charter-based power limits or recall mechanisms within 60 days.</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>The Lawrence City Council is likely to introduce motions of no confidence or move to strip the mayor's executive appointments, while DePeña fights the charges in office until at least the next electoral cycle.</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>70-80%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Because the charge involves state wiretapping statutes rather than direct financial bribery or embezzlement of public funds, legal counsel may argue the infraction does not constitute malfeasance sufficient to trigger automatic charter forfeiture.</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Whether Lawrence City Council schedules an emergency meeting to vote on a resolution of no confidence or seek an advisory opinion from the state attorney general.</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOSkkzZkRwTE1ybExEeTdOamx0aXRkOHR5S01RcDJsMzZuWEVyVWd1SXlNMUZBVTRoVHR6cFlwOFBxVnlTY1JDbEMxWm82dzdOSWZ0ejQ0WlpYdVEzOEkyTEZzbFVNVW5zM0hVaUg4Wkx1ZFhCNzVqT3hGRjFiTnEwNFpIZGM4OGZudkNmMU5ROExMTW5Ta09FLVJQNExmQWtPc2txODFFLXhIbjRwRW1TcFdCVjVpaTNLalE?oc=5</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Jasiel_Correia
+https://en.wikipedia.org/wiki/William_Lantigua</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Six Ukrainian energy sites hit by Russia since Trump announced ceasefire, Zelensky says</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Despite US President Trump announcing an energy infrastructure ceasefire between Russia and Ukraine, Ukrainian officials report that six energy sites have still been struck by Russian forces.</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>ceasefire</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2014–2015: Minsk agreements
+1973: Paris Peace Accords</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>2014–2015: Low-level trench warfare continued indefinitely, eventually escalating into a full-scale invasion years later.
+1973: Fighting resumed within months as enforcement mechanisms proved toothless against determined belligerents.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 80% of cases where partial ceasefires are declared without local enforcement or resolved root causes, the agreements break down within weeks as commanders exploit ambiguity.</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>The energy ceasefire will likely continue to fracture, with both sides trading accusations of violations while selective infrastructure strikes persist.</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Direct US presidential capital is personally invested in this specific framework, which could create stronger diplomatic penalties for overt breaches.</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Official US responses to continued strikes and whether Washington attempts to enforce penalties or walks back the announcement.</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cvlyd4pdlwkxo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Minsk_agreements
+https://en.wikipedia.org/wiki/Paris_Peace_Accords</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Argentina lodges legal claim against UK's Falklands oil exploration</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Argentina has filed a formal legal claim with an international maritime tribunal against British oil exploration activities near the Falkland Islands, escalating a long-running sovereignty dispute.</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>territorial dispute</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2010: Falkland Islands sovereignty dispute
+1982: Falklands War</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2010: Tensions remained high diplomatically, though exploration proceeded and militarization of the islands was reinforced by the UK.
+1982: A decisive British military victory solidified UK control, leaving Argentina to pursue diplomatic and legal protests for decades.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Legal claims and maritime protests by Argentina regarding Falklands resources regularly occur during periods of domestic economic stress, serving to unite domestic politics without altering the status quo on the ground.</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>The international tribunal is likely to move slowly or find limitations in its jurisdiction, while the UK continues exploration and Argentina maintains rhetorical and legal pressure.</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Argentina is utilizing formal international maritime law frameworks rather than immediate nationalist posturing.</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Reactions from energy companies involved in the drilling and any potential retaliatory port restrictions by Buenos Aires.</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cmp3g14p3z2ko?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Falkland_Islands_sovereignty_dispute
+https://en.wikipedia.org/wiki/Falklands_War</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>The latest inflation data is expected to show price increases are accelerating</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Economists expect the consumer price index for September to show acceleration, rising 0.6% on the month and 3.6% year over year.</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>rate hikes / inflation surge</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1973–1974: 1973 oil crisis
+2021–2022: Post-COVID inflation surge</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1973–1974: Central banks were forced to hike interest rates aggressively, triggering a severe global recession by late 1974.
+2021–2022: The Federal Reserve embarked on one of its fastest-ever monetary tightening cycles, raising rates from near-zero to over 5% within 18 months.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>In 8 of 10 similar historical instances of re-accelerating inflation driven by supply constraints, central banks responded with aggressive monetary tightening or prolonged high interest rates, regardless of growth slowdowns.</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Central banks will likely maintain high benchmark interest rates or signal further tightening to anchor inflation expectations, increasing borrowing costs.</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets are facing unprecedented structural pressure from generative AI integration, which could dampen wage-push inflation differently than past cycles.</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Core CPI prints and Federal Reserve rhetoric shifting from potential rate cuts to a prolonged 'higher for longer' stance.</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/13/september-consumer-price-index-inflation.html</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973_oil_crisis
+https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>IMF warns bond yields could see a 'disorderly' spike as debt, inflation risks worsen</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>The International Monetary Fund warned that risks in the global government bond market have worsened, creating potential for a disorderly spike in yields amid mounting deficits and inflation.</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>market crashes / bond yield spikes</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1994: 1994 bond market massacre
+2022: United Kingdom mini-budget crisis</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1994: Severe liquidity crunches in fixed income markets, corporate leveraged blowups, and losses that rippled through global financial institutions over the subsequent 12 months.
+2022: The Bank of England was forced to launch emergency bond-buying interventions, and the Prime Minister resigned within weeks of the announcement.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>When sovereign debt burdens are exceptionally high, fiscal indiscipline or persistent inflation surprises routinely spark sharp, disorderly sell-offs in the bond market that require emergency liquidity backstops.</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Sovereign bond volatility will remain elevated, increasing borrowing costs for governments and risking financial stability contagion if yields spike too fast.</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Global central banks possess robust emergency lending facilities and swap lines established post-2008 and 2020 that can be deployed faster to cap disorderly market panics.</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sudden spikes in long-term Treasury yields, widening credit spreads, and emergency statements from central bankers.</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/13/treasury-yields-imf-debt-inflation-.html</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1994_bond_market_crisis
+https://en.wikipedia.org/wiki/September_2022_United_Kingdom_mini-budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Super El Niño sets another record as it strengthens to 'unprecedented levels'</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Key meteorological measurements show the current El Niño has intensified into record territory, entering 'super El Niño' status with historically elevated ocean temperatures across the equatorial Pacific.</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>super El Niño</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1997–1998: 1997–98 Super El Niño
+2015–2016: 2014–16 Super El Niño
+1982–1983: 1982–83 Super El Niño</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1997–1998: Global temperatures hit record highs in 1998, severe droughts and wildfires hit Indonesia, and the event collapsed abruptly within 6 months into a multi-year La Niña.
+2015–2016: It propelled 2016 to the warmest year on record, triggered catastrophic global coral bleaching, and dissipated by mid-2016 into neutral and weak La Niña conditions.
+1982–1983: It peaked in the boreal winter and rapidly decayed by summer 1983, followed by a sharp drop in regional ocean temperatures.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Every recorded super El Niño (3 of 3: 1982–83, 1997–98, 2015–16) peaked between November and January, pushed global average surface temperatures to record highs within 6–12 months, and collapsed rapidly into La Niña or neutral conditions within 6 to 9 months post-peak.</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Global surface temperatures will set all-time records over the coming months alongside severe regional extremes (droughts in Southeast Asia and Australia, heavy rains in coastal Americas), followed by a rapid collapse toward a La Niña pattern by mid-2027.</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Anthropogenic ocean heating has raised baseline global sea surface temperatures to unprecedented depths, which could alter the pace of subsurface cool Kelvin waves and delay the typical post-peak collapse.</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Subsurface Pacific temperature anomalies moving east-to-west, changes in the Southern Oscillation Index, and the strength of the trade winds.</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/weather/articles/cmlye0d7q7zno?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1997%E2%80%931998_El_Ni%C3%B1o_event
+https://en.wikipedia.org/wiki/2014%E2%80%932016_El_Ni%C3%B1o_event
+https://en.wikipedia.org/wiki/1982%E2%80%931983_El_Ni%C3%B1o_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>James Webb reveals a massive cosmic structure that challenges our understanding of the Universe</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>The James Webb Space Telescope discovered an ancient, massive galaxy cluster with an unexpectedly dense concentration of dark matter, presenting data that appears in tension with standard models of early cosmic structure growth.</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>astronomical anomaly</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2022–2023: JWST Early Massive Galaxy Anomaly
+1995–1998: Hubble Deep Field early galaxy formation counts
+2011: OPERA faster-than-light neutrino anomaly</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>2022–2023: Within 18 to 24 months, high-resolution spectroscopy and updated calibration of dust, active galactic nuclei, and star-formation efficiency reconciled most targets with existing cosmological models.
+1995–1998: Rather than discarding cosmological models, theorists updated star formation rate calibrations and hierarchical halo merger rates over the subsequent 3 years.
+2011: Within 8 months, re-evaluations and independent cross-checks identified equipment and timing calibration errors, confirming standard physics held.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>In over 90% of astronomical anomalies where initial observations appear to invalidate foundational cosmological frameworks, subsequent spectroscopic confirmation, instrument calibration, and updated astrophysical models (such as baryonic feedback or dark matter halo accretion) reconcile the findings with the Lambda-CDM model without requiring new physics.</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>The cluster's existence will be confirmed, but detailed follow-up spectroscopy and refined astrophysics will accommodate the dark matter density within the standard Lambda-CDM model rather than forcing a revision of cosmology.</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>next 12 to 24 months</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>If independent weak and strong gravitational lensing measurements unambiguously confirm a total dark matter halo mass exceeding theoretical cold dark matter clustering limits, alternative frameworks like modified gravity or warm dark matter could gain formal support.</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Follow-up spectroscopic redshift verification, gravitational lensing mass maps of the cluster core, and preprint cosmological simulations matching the observed halo density.</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261012185021.htm</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/James_Webb_Space_Telescope
+https://en.wikipedia.org/wiki/Hubble_Deep_Field
+https://en.wikipedia.org/wiki/2011_OPERA_faster-than-light_neutrino_anomaly</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -9259,6 +9259,1283 @@
       <text>
         <t>Türkçe:
 Takip spektroskopik kırmızıya kayma doğrulaması, küme çekirdeğinin kütleçekimsel mercekleme kütle haritaları ve gözlenen hale yoğunluğuyla eşleşen ön baskı kozmolojik simülasyonları.</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump'ın Yunanistan büyükelçisi Kimberly Guilfoyle, yolsuzluk iddialarının ardından istifa etti
+Kelimeler:
+• resigns = istifa eder
+• corruption allegations = yolsuzluk iddiaları</t>
+      </text>
+    </comment>
+    <comment ref="D93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beyaz Saray, ABD'nin Yunanistan Büyükelçisi Kimberly Guilfoyle'u, yönetim yetkililerine erişim karşılığında bir bağışçıdan ödeme talep ettiği suçlamalarının ardından görevden uzaklaştırdı.
+Kelimeler:
+• forced out = görevden uzaklaştırdı / istifaya zorladı
+• in exchange for = karşılığında</t>
+      </text>
+    </comment>
+    <comment ref="E93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+diplomatik istifa</t>
+      </text>
+    </comment>
+    <comment ref="F93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Ryan Zinke'nin istifası
+2019: Gordon Sondland'ın istifası</t>
+      </text>
+    </comment>
+    <comment ref="G93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Zinke, Aralık 2018'de baskı altında istifa ederek o an için acil kovuşturmadan kaçındı; ancak soruşturmalar siyasi kariyerini geçici olarak sekteye uğrattı ve daha sonra Temsilciler Meclisi'ne geri döndü.
+2019: Sondland, azil soruşturmasının sonuçlanmasından günler sonra görevinden derhal alındı ve ardından ödenmeyen yasal ücretler için Dışişleri Bakanlığı'na karşı dava açtı.
+Kelimeler:
+• under pressure = baskı altında</t>
+      </text>
+    </comment>
+    <comment ref="H93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Benzer yürütme organı etik skandallarında, Beyaz Saray'dan doğrudan baskı gören siyasi atananlar siyasi zararı sınırlamak için hızla istifa eder; resmi soruşturmalar nadiren acil cezai mahkumiyetlerle sonuçlanır ancak diplomatik kariyerlerini fiilen sona erdirir.</t>
+      </text>
+    </comment>
+    <comment ref="I93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Guilfoyle, Adalet Bakanlığı veya kongre komitelerinden gelebilecek ön etik soruşturmalarıyla karşı karşıyayken muhtemelen göz önünde olmayacaktır, ancak ayrılan elçilerin tarihi emsallerine dayanarak resmi suçlamalar istatistiksel olarak düşük bir ihtimaldir.</t>
+      </text>
+    </comment>
+    <comment ref="K93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yabancı bağışçıların dahil olduğu iddia edilen 'ver-al' (menfaat karşılığı) erişimin özel doğası, idari veya seyahat masrafı ihlallerine kıyasla federal savcılardan daha sert bir inceleme çekebilir.</t>
+      </text>
+    </comment>
+    <comment ref="N93" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyükelçilik iletişimleriyle ilgili Adalet Bakanlığı veya Meclis denetim celplerinin duyuruları.
+Kelimeler:
+• subpoenas = celpler / mahkeme çağrıları</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İki partili senatör grubu Trump'a Rus dizel anlaşmasını iptal etme çağrısında bulundu
+Kelimeler:
+• bipartisan = iki partili
+• rescind = iptal etmek / geri almak</t>
+      </text>
+    </comment>
+    <comment ref="D94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Altı Demokrat ve altı Cumhuriyetçi senatör, Başkan Trump'ın Rusya Devlet Başkanı Vladimir Putin ile yakın zamanda aracı olunan tartışmalı bir dizel anlaşmasından çekilmesini talep eden ortak bir mektup gönderdi.
+Kelimeler:
+• brokered = aracı olunarak yapılan / müzakere edilen</t>
+      </text>
+    </comment>
+    <comment ref="E94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kongre tepkisi</t>
+      </text>
+    </comment>
+    <comment ref="F94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017: Rusya Yaptırımları ve Karşı-Af Yasası (CAATSA)
+2019: Suriye'den çekilmeye kongre muhalefeti</t>
+      </text>
+    </comment>
+    <comment ref="G94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017: Trump, veto edilemez ezici baskı altında yasayı istemeye istemeye imzaladı ve Kongre'nin Moskova'ya yönelik yürütme organı girişimlerini geçersiz kılma emsalini oluşturdu.
+2019: Şiddetli iki partili kınamaya ve sembolik onaylamama kararlarına rağmen, yönetim politika ayarlamalarını büyük ölçüde sürdürdü ve bağlayıcı olmayan kongre mektuplarının sınırlarını gösterdi.
+Kelimeler:
+• bipartisan = iki partili
+• veto-proof = veto edilemez
+• binding = bağlayıcı</t>
+      </text>
+    </comment>
+    <comment ref="H94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İki partili bir senatör bloğu yürütme organının ticaret veya dış politika anlaşmalarına açıkça meydan okuduğunda, yönetimler derhal bağlayıcı ve veto edilemez bir yasa ilerletilmediği takdirde şartları sessizce değiştirir veya mektupları göz ardı eder.
+Kelimeler:
+• bipartisan = iki partili
+• veto-proof = veto edilemez
+• binding = bağlayıcı</t>
+      </text>
+    </comment>
+    <comment ref="I94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Trump'ın iki partili çağrıyı başlangıçta reddetmesi muhtemeldir, ancak yasama baskısı dizel anlaşmasının şartlarında değişikliklere veya artan şeffaflığa yol açabilir.
+Kelimeler:
+• bipartisan = iki partili</t>
+      </text>
+    </comment>
+    <comment ref="K94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ay</t>
+      </text>
+    </comment>
+    <comment ref="L94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji güvenliği ve Rusya ile doğrudan ekonomik bağlar, devam eden Avrupa enerji dinamikleri ortasında artan bir iç hassasiyet taşımaktadır.
+Kelimeler:
+• domestic sensitivity = iç hassasiyet</t>
+      </text>
+    </comment>
+    <comment ref="N94" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uygulama fonlarını bloke eden bağlayıcı iki partili yasa tasarılarının veya önergelerin sunulması.
+Kelimeler:
+• bipartisan = iki partili
+• binding = bağlayıcı</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hasbro, yüzlerce iş pozisyonunu Rhode Island'dan Boston'a taşımaya hazırlanıyor</t>
+      </text>
+    </comment>
+    <comment ref="D95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hasbro, uzun süredir Rhode Island'da bulunan genel merkez alanındaki yüzlerce iş pozisyonunu Boston bölgesine taşıma planlarını açıkladı.
+Kelimeler:
+• relocate = taşınmak, yer değiştirmek
+• headquarters footprint = merkez alanı / kapladığı alan</t>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+şirket taşınması</t>
+      </text>
+    </comment>
+    <comment ref="F95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: General Electric'in Boston'dan Greater Boston'a taşınması ve önceki hamleler
+2018: Reebok genel merkezinin Canton'dan Boston'a taşınması</t>
+      </text>
+    </comment>
+    <comment ref="G95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Teknoloji yeteneklerini güvence altına almak başlangıçta başarılı olsa da, yüksek operasyonel maliyetler ve melez çalışma vardiyaları 5 yıl içinde merkezileşmiş alanların azalmasına yol açtı.
+2018: Ana şirket Adidas daha sonra Reebok'ı 2021'de sattı ve kentsel genel merkez alanı, uzaktan çalışma geçişleri ortasında önemli bir yeniden yapılandırma ve küçülmeden geçti.
+Kelimeler:
+• headquarters footprint = merkez alanı / kapladığı alan
+• restructuring = yeniden yapılandırma</t>
+      </text>
+    </comment>
+    <comment ref="H95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston gibi yüksek maliyetli kentsel inovasyon merkezlerine yapılan büyük şirket taşınmalarında, ilk yetenek kazanımı faydaları genellikle yüksek gayrimenkul genel giderleri ve 3 ila 5 yıl içinde takip eden kurumsal yeniden yapılandırmalarla karşı karşıya kalır.
+Kelimeler:
+• talent acquisition = yetenek kazanımı / işe alım
+• overhead = genel giderler
+• restructuring = yeniden yapılandırma</t>
+      </text>
+    </comment>
+    <comment ref="I95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hasbro, Boston'da ilk teknoloji ve pazarlama yeteneklerini başarıyla güvence altına alacak, ancak çalışan sayısı ayak izinde maliyet baskısı ayarlamalarıyla karşılaşacak.</t>
+      </text>
+    </comment>
+    <comment ref="K95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hasbro'nun dijital oyunlara, eğlence ortaklıklarına ve oyuncak-teknoloji yakınsmasına olan yoğun güveni, Boston'ın belirli yetenek havuzunu geleneksel üretim merkezlerine kıyasla benzersiz bir şekilde hayati kılmaktadır.
+Kelimeler:
+• convergence = yakınsama, birleşme</t>
+      </text>
+    </comment>
+    <comment ref="N95" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston ofisi için nihai metrekare taahhütleri ve yerel işe alım oranları.</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Markey ve Deaton, ilk ve tek Massachusetts Senato münazarasında karşı karşıya geldi
+Kelimeler:
+• clash = çatışmak, karşı karşıya gelmek</t>
+      </text>
+    </comment>
+    <comment ref="D96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Görevdeki Senatör Ed Markey ve rakip Shiva Deaton (veya ilgili GOP/bağımsız rakip), koyu mavi bir eyaletteki ilk ve tek münazaralarında karşı karşıya geldi.
+Kelimeler:
+• incumbent = görevdeki yetkili / makam sahibi
+• challenger = rakip, meydan okuyan
+• clash = çatışmak, karşı karşıya gelmek</t>
+      </text>
+    </comment>
+    <comment ref="E96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+senato münazarası</t>
+      </text>
+    </comment>
+    <comment ref="F96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Ed Markey 2020 Senato ön seçimi ve genel seçimi
+2014: 2014 Amerika Birleşik Devletleri Massachusetts Senato seçimi</t>
+      </text>
+    </comment>
+    <comment ref="G96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Markey, masmavi genel seçimde geniş bir farkla rahatça kazanarak eyaletin kökleşmiş partizan dengesini korudu.
+2014: Görevdeki isim, ekonomi ve harcamalar üzerindeki sesli rakip eleştirilerine rağmen koltuğunu güvenli bir şekilde korudu.
+Kelimeler:
+• incumbent = görevdeki yetkili / makam sahibi
+• challenger = rakip, meydan okuyan
+• entrenched = kökleşmiş, yerleşmiş</t>
+      </text>
+    </comment>
+    <comment ref="H96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Massachusetts eyalet çapındaki federal seçimlerin %90'ından fazlasında, son aşama münazaraları manşetler üretir ancak güçlü bir şekilde mavi olan bir seçmen kitlesinde kökleşmiş Demokrat görevlinin temel yapısal avantajını değiştirmekte başarısız olur.
+Kelimeler:
+• incumbent = görevdeki yetkili / makam sahibi
+• entrenched = kökleşmiş, yerleşmiş
+• electorate = seçmen kitlesi</t>
+      </text>
+    </comment>
+    <comment ref="I96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Münazara her iki taraftaki çekirdek siyasi aktivistleri harekete geçirecek, ancak görevdeki kişinin anketlerdeki liderliğini esaslı bir şekilde sarsmayacak.
+Kelimeler:
+• incumbent = görevdeki yetkili / makam sahibi</t>
+      </text>
+    </comment>
+    <comment ref="K96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+seçim günü</t>
+      </text>
+    </comment>
+    <comment ref="L96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Değişen ulusal ekonomik duygu ve uzun süredir görev yapan yetkililere yönelik belirli seçmen yorgunluğu, geçmiş dönemlere kıyasla marjları biraz daraltabilir.
+Kelimeler:
+• incumbent = görevdeki yetkili / makam sahibi
+• voter fatigue = seçmen yorgunluğu</t>
+      </text>
+    </comment>
+    <comment ref="N96" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Münazara sonrası bağış toplama rakamları ve değişen erken oy kullanma katılım metrikleri.</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon beklenenden fazla arttı - işte fiyatlarda yaşananlar</t>
+      </text>
+    </comment>
+    <comment ref="D97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de fiyat artış hızları, Eylül ayına kadar geçen bir yıllık sürede motorlu yakıt maliyetlerindeki artışın etkisiyle %3,7'ye hızlandı ve ara seçimler hemen öncesinde Federal Reserve'ün yeni faiz artırımlarına gideceği korkularını körükledi.
+Kelimeler:
+• pace of = -in hızı
+• accelerate = hızlanmak
+• rate hike = faiz artırımı</t>
+      </text>
+    </comment>
+    <comment ref="E97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+faiz artırımı
+Kelimeler:
+• rate hike = faiz artırımı</t>
+      </text>
+    </comment>
+    <comment ref="F97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973-1974: 1970'ler enerji krizi
+2022: Pandemi sonrası enflasyon dalgası</t>
+      </text>
+    </comment>
+    <comment ref="G97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973-1974: Ekonomik büyüme durdu ve 1970'ler boyunca uzun süren bir stagflasyon dönemine yol açtı.
+2022: Finansal piyasalar ciddi düzeltmeler yaşadı ve ara seçimler öncesinde merkez bankası üzerindeki siyasi baskı arttı.
+Kelimeler:
+• stall = durmak, duraksamak
+• stagflationary period = stagflasyon dönemi</t>
+      </text>
+    </comment>
+    <comment ref="H97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji şokları nedeniyle büyük seçimlere yakın bir zamanda enflasyon beklenmedik bir şekilde yukarı yönlü kıpırdadığında, merkez bankaları yoğun siyasi baskıyla karşı karşıya kalır ancak tarihsel olarak sıkılaştırmaya öncelik verir, bu da piyasa oynaklığının artmasıyla sonuçlanır.</t>
+      </text>
+    </comment>
+    <comment ref="I97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Reserve'ün beklentileri sabitlemek için para politikasında yeni bir sıkılaştırma sinyali vermesi veya bunu uygulaması ve borçlanma maliyetlerini yüksek tutması muhtemeldir.
+Kelimeler:
+• monetary tightening = para politikasında sıkılaştırma</t>
+      </text>
+    </comment>
+    <comment ref="K97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İş gücü piyasaları, tarihsel sıkılaştırma döngülerine kıyasla oldukça dirençli kalmaya devam ediyor ve bu durum daha geniş ekonomik etkileri potansiyel olarak yumuşatabilir.</t>
+      </text>
+    </comment>
+    <comment ref="N97" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çekirdek PCE enflasyon verileri ve yaklaşan Federal Reserve konuşmaları.</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Türk polisi muhalif TV kanalına baskın düzenledi, canlı yayınları durdurdu</t>
+      </text>
+    </comment>
+    <comment ref="D98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Türk polisi, hükümeti eleştiren medyaya yönelik son baskı dalgası kapsamında muhalif bir TV kanalına baskın düzenleyerek canlı yayınları durdurdu.
+Kelimeler:
+• crackdown = baskı, sert önlem</t>
+      </text>
+    </comment>
+    <comment ref="E98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+baskı, operasyon
+Kelimeler:
+• crackdown = baskı, sert önlem</t>
+      </text>
+    </comment>
+    <comment ref="F98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Türkiye'deki darbe sonrası tasfiyeler
+2023: Türkiye'deki seçim öncesi medya kısıtlamaları
+Kelimeler:
+• purge = tasfiye</t>
+      </text>
+    </comment>
+    <comment ref="G98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2016: Bağımsız medyanın varlığı ciddi ölçüde daraldı ve sonraki yıllarda bilgi kanalları üzerindeki devlet kontrolü pekişti.
+2023: Kamuoyu tartışmaları önemli ölçüde daralarak muhalif siyasi hareketlerin örgütsel kapasitesini ve etki alanını zayıflattı.
+Kelimeler:
+• contract = daralmak, küçülmek</t>
+      </text>
+    </comment>
+    <comment ref="H98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Geçtiğimiz son on yılda Türkiye'de medyaya yönelik benzer otoriter baskıların yaklaşık %80'inde, susturulan yayıncılar uzun süreli kapatmalarla veya faaliyet lisanslarının tamamen iptal edilmesiyle karşı karşıya kalmakta ve muhalif söylemi dijital ortama taşımaya zorlanmaktadır.
+Kelimeler:
+• clampdown = baskı, sıkı önlem</t>
+      </text>
+    </comment>
+    <comment ref="I98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hedefteki TV kanalının süresiz olarak kapalı kalması muhtemeldir; bu da bağımsız gazeteciliğin merkeziyetsiz dijital platformlara daha da göç etmesini tetikleyecektir.
+Kelimeler:
+• indefinitely = süresiz olarak</t>
+      </text>
+    </comment>
+    <comment ref="K98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şifreli sosyal medyanın ve merkeziyetsiz yayın platformlarının yaygın kullanımı, bilginin tamamen bastırılmasını geçmiş on yıllara göre daha zor hale getirmektedir.
+Kelimeler:
+• pervasive = yaygın, her yeri saran
+• suppression = bastırma, engelleme</t>
+      </text>
+    </comment>
+    <comment ref="N98" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kanal yöneticilerinin hukuki durumundaki gelişmeler ve olası uluslararası diplomatik tepkiler.</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji fiyatlarının fırlamasıyla Eylül ayında tüketici fiyatları bir yıl öncesine göre %3,7 arttı
+Kelimeler:
+• skyrocket = hızla yükselmek, fırlamak</t>
+      </text>
+    </comment>
+    <comment ref="D99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon Eylül ayında yıllık bazda %3,7'ye yükseldi; bu artışta İran'ın dahil olduğu çatışmalardan kaynaklanan hızla tırmanan akaryakıt ve enerji fiyatları büyük rol oynadı.</t>
+      </text>
+    </comment>
+    <comment ref="E99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+petrol şoku</t>
+      </text>
+    </comment>
+    <comment ref="F99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: 1973 petrol krizi
+1990: 1990 petrol fiyatı şoku</t>
+      </text>
+    </comment>
+    <comment ref="G99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: ABD'de enflasyon çift haneli rakamlara fırlayarak şiddetli bir durgunluğu tetikledi ve Federal Rezerv'i takip eden 2-3 yıl boyunca agresif, ekonomiyi soğutan faiz artışları uygulamaya zorladı.
+1990: ABD ekonomisi, Temmuz 1990'dan Mart 1991'e kadar süren bir durgunluğa sürüklenirken, askeri müdahale petrol arzını güvence altına aldıktan sonra enflasyon nispeten hızlı bir şekilde düştü.
+Kelimeler:
+• recession = ekonomik durgunluk, resesyon
+• rate hike = faiz artırımı
+• subside = dinmek, azalmak</t>
+      </text>
+    </comment>
+    <comment ref="H99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ani jeopolitik enerji şoklarının yaşandığı benzer 2 tarihi durumun 2'sinde de merkez bankaları para politikasını kısıtlayıcı tutmaya zorlandı ve iktidar partisi sandıkta ağır bir darbe aldı.</t>
+      </text>
+    </comment>
+    <comment ref="I99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Rezerv muhtemelen mevcut faiz oranı duruşunu koruyacak veya daha fazla sıkılaştırmaya işaret edecek ve diğer sektörlerdeki yavaşlayan büyümeye rağmen faiz indirmeyi reddedecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1970'lerin savunmasız ithalat bağımlılığının aksine, ABD artık net bir petrol ihracatçısı konumunda ve kaya gazı üretimi iç piyasa için bir tampon sağlıyor.
+Kelimeler:
+• net exporter = net ihracatçı</t>
+      </text>
+    </comment>
+    <comment ref="N99" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji hariç çekirdek enflasyon göstergeleri ve Federal Rezerv'in faiz patikasına ilişkin gelecek açıklamaları.</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Artan Enflasyon, Trump'ın Ara Seçimler Öncesi Güçlü Ekonomi Konusunda Seçmenleri Ikna Etme Çabalarını Zorlaştırıyor
+Kelimeler:
+• surging = hızla artan, dalgalanan</t>
+      </text>
+    </comment>
+    <comment ref="D100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 ara seçimleri öncesindeki son enflasyon raporu, kalıcı fiyat artışlarını gözler önüne sererek Demokratların siyasi haritasını Cumhuriyetçilerin kalelerine kadar genişletti.
+Kelimeler:
+• sticky = (fiyatlar için) düşmesi zor, yapışkan, kalıcı</t>
+      </text>
+    </comment>
+    <comment ref="E100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçim dalgalanmaları</t>
+      </text>
+    </comment>
+    <comment ref="F100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: 2022 Amerika Birleşik Devletleri seçimleri
+1974: 1974 Amerika Birleşik Devletleri seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="G100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: İktidardaki parti önemli kongre engelleriyle karşılaştı; öngörülen 'kırmızı dalga' zayıf kalmış olsa da, Beyaz Saray'daki parti tarihsel olarak Temsilciler Meclisi'nin kontrolünü kaybetti.
+1974: İktidardaki Cumhuriyetçi parti ezici bir yenilgiye uğrayarak Temsilciler Meclisi'nde 48, Senato'da ise 4 koltuk kaybetti.
+Kelimeler:
+• incumbent = görevdeki (kişi veya parti)
+• landslide defeat = ezici yenilgi</t>
+      </text>
+    </comment>
+    <comment ref="H100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yıllık enflasyonun %3'ün üzerinde olduğu ara seçimlerin %80'inde, görevdeki başkanın partisinin kongrede sandalye kaybettiği görülüyor.</t>
+      </text>
+    </comment>
+    <comment ref="I100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yönetimdeki partinin, hayat pahalılığı yorgunluğunun iktidardakilere karşı seçmen katılımını artırması nedeniyle Kongre'de zemin kaybetmesi muhtemeldir.
+Kelimeler:
+• incumbent = görevdeki (kişi veya parti)
+• cost-of-living fatigue = hayat pahalılığı yorgunluğu</t>
+      </text>
+    </comment>
+    <comment ref="K100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki ay (Kasım 2026 seçimi)</t>
+      </text>
+    </comment>
+    <comment ref="L100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kutuplaşmış seçmen kitlesi ve aşırı hedef odaklı seçim bölgesi haritaları, genel ekonomik memnuniyetsizliğe rağmen bazı görevdeki isimleri koruyabilir.
+Kelimeler:
+• incumbent = görevdeki (kişi veya parti)
+• electorate = seçmenler, seçmen kitlesi
+• insulate = korumak, yalıtmak</t>
+      </text>
+    </comment>
+    <comment ref="N100" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Banliyölerdeki salıncak bölgelerindeki son seçim öncesi anket değişimleri ve seçmen katılımı ölçümleri.</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon beklenenden fazla arttı - fiyatlarda neler oluyor?
+Kelimeler:
+• inflation rises = enflasyon yükseliyor
+• prices = fiyatlar</t>
+      </text>
+    </comment>
+    <comment ref="D101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül ayına kadar olan yıllık süreçte ABD'deki fiyat artışları hızı, devam eden jeopolitik gerginlikler ortamında hızla yükselen motorlu yakıt maliyetlerinin etkisiyle %3,7'ye yükseldi.
+Kelimeler:
+• pace = hız, tempo
+• surging = hızla yükselen
+• geopolitical tensions = jeopolitik gerginlikler</t>
+      </text>
+    </comment>
+    <comment ref="E101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+petrol şoku
+Kelimeler:
+• oil shock = petrol şoku</t>
+      </text>
+    </comment>
+    <comment ref="F101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: 1973 petrol krizi
+2022: 2022 enflasyon dalgası
+Kelimeler:
+• historical precedents = tarihi emsaller</t>
+      </text>
+    </comment>
+    <comment ref="G101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973: Küresel enflasyon aylar içinde dramatik bir şekilde çift hanelere sıçrayarak Batı ekonomilerinde şiddetli ve uzun süreli bir stagflasyonist resesyonu tetikledi.
+2022: Federal Reserve, talebi soğutmak için takip eden 18 ay boyunca faiz oranlarını 500 baz puandan fazla agresif bir şekilde artırdı.
+Kelimeler:
+• spiked dramatically = dramatik bir şekilde sıçradı
+• stagflationary recession = stagflasyonist resesyon
+• hiked interest rates = faiz oranlarını artırdı</t>
+      </text>
+    </comment>
+    <comment ref="H101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük jeopolitik enerji şoklarının %80'inde, ilk enflasyon sıçramaları merkez bankalarını, başka yerlerdeki yavaşlayan ekonomik büyümeye rağmen sıkı para politikasını sürdürmeye veya uzatmaya zorlar.
+Kelimeler:
+• central banks = merkez bankaları
+• monetary policy = para politikası</t>
+      </text>
+    </comment>
+    <comment ref="I101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Reserve, yapışkan yakıt kaynaklı enflasyonla mücadele etmek için muhtemelen faiz oranlarını sabit tutacak veya şahin bir duruş sinyali verecek.
+Kelimeler:
+• hawkish pause = şahin duraklama
+• sticky = yapışkan (düşmesi zor)</t>
+      </text>
+    </comment>
+    <comment ref="K101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşgücü piyasaları ve temel ücret artışları şu anda 1970'lerin stagflasyon dönemindekine göre daha dirençli.
+Kelimeler:
+• resilient = dirençli
+• underlying wage growth = temel ücret artışı</t>
+      </text>
+    </comment>
+    <comment ref="N101" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji hariç çekirdek enflasyon göstergeleri ve tüketicinin uzun vadeli enflasyon beklentileri.
+Kelimeler:
+• core inflation metrics = çekirdek enflasyon göstergeleri
+• expectations = beklentiler</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sahipleri alıcı ararken Poundland kurtarma görüşmelerinde
+Kelimeler:
+• rescue talks = kurtarma görüşmeleri
+• seek a buyer = alıcı aramak</t>
+      </text>
+    </comment>
+    <comment ref="D102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Poundland'in liderlik ekibi, sahiplerinin alıcı aradığı bu dönemde kurtarma görüşmeleri yürütüyor; sendikalar indirimli ürünler perakendecisinin iflas masasına düşebileceği konusunda uyarıyor.
+Kelimeler:
+• discount retailer = indirimli ürün perakendecisi
+• fall into administration = iflas yönetimine/kayyuma devredilmek</t>
+      </text>
+    </comment>
+    <comment ref="E102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+perakende iflası
+Kelimeler:
+• retail administration = perakende iflası</t>
+      </text>
+    </comment>
+    <comment ref="F102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Toys "R" Us UK'in çöküşü
+2008: Woolworths'ün çöküşü
+Kelimeler:
+• collapse = çöküş</t>
+      </text>
+    </comment>
+    <comment ref="G102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Tüm İngiltere mağazaları üç aylık bir süre içinde tasfiye edilerek kapatıldı ve binlerce perakende işinin kaybıyla sonuçlandı.
+2008: Şirket haftalar içinde tamamen çökerek yüzlerce mağazayı tasfiye etti ve İngiltere tarihindeki en büyük cadde (high-street) başarısızlıklarından birine işaret etti.
+Kelimeler:
+• wound down = tasfiye edilerek kapatıldı
+• liquidated = tasfiye edildi</t>
+      </text>
+    </comment>
+    <comment ref="H102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük çok şubeli perakendeciler, daralan tüketici harcamaları ve yüksek enerji maliyetleri ortasında kurtarma görüşmelerine girdiğinde, derin likiditeye sahip acil bir alıcı bulunamazsa %60'ından fazlası resmi bir iflas sürecine veya büyük mağaza rasyonalizasyonlarına sürüklenir.
+Kelimeler:
+• tightening consumer spending = daralan tüketici harcamaları
+• deep liquidity = derin likidite</t>
+      </text>
+    </comment>
+    <comment ref="I102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tercih edilen bir alıcı hızlı bir şekilde bir kurtarma anlaşmasını sonuçlandırmadığı sürece Poundland, önemli mağaza kapanışları ve işten çıkarmalarla sonuçlanacak bir ön paket iflas sürecinden muhtemelen geçecektir.
+Kelimeler:
+• pre-pack administration = önceden paketlenmiş iflas süreci
+• job cuts = işten çıkarmalar</t>
+      </text>
+    </comment>
+    <comment ref="K102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 2 ay</t>
+      </text>
+    </comment>
+    <comment ref="L102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İndirimli ürün perakendecileri bazen ekonomik düşüşler sırasında alışveriş yapanların sayısında bir artış yaşarlar, bu da fırsatçı özel sermaye ilgisini çekebilir.
+Kelimeler:
+• downturns = ekonomik düşüşler, durgunluklar
+• private equity = özel sermaye</t>
+      </text>
+    </comment>
+    <comment ref="N102" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alacaklıların borç sözleşmeleri (covenants) ve Martin Property Group ortaklığının sonuçlandırılması hakkındaki açıklamaları.
+Kelimeler:
+• creditors = alacaklılar
+• debt covenants = borç sözleşmesi kısıtlamaları</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Lisandro Martinez'in Manchester United'in Atletico Madrid'e Şampiyonlar Ligi'ndeki yenilgisi sonrası yaptığı sert açıklamalar, tüm dikkatleri yeniden futbol direktörü Jason Wilcox'a çevirdi.
+Kelimeler:
+• explosive comments = sert/patlayıcı açıklamalar
+• turn the spotlight back on = dikkatleri yeniden üzerine çekmek</t>
+      </text>
+    </comment>
+    <comment ref="D103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester United defans oyuncusu Lisandro Martinez, Şampiyonlar Ligi yenilgisinin ardından kulüp yönetimini ve üst kademeyi hedef alan sert bir kamuoyu saldırısı başlattı ve kadro yatırımları konusunda özellikle futbol direktörü Jason Wilcox'a baskı yaptı.
+Kelimeler:
+• scathing public attack = sert kamuoyu saldırısı
+• hierarchy = üst kademe, yönetim
+• squad investment = kadro yatırımı</t>
+      </text>
+    </comment>
+    <comment ref="E103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+teknik direktörün kovulması</t>
+      </text>
+    </comment>
+    <comment ref="F103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Cristiano Ronaldo'nun Piers Morgan ile yaptığı ve Manchester United yönetimini eleştirdiği olay röportajı
+2018: Paul Pogba'nın Manchester United'da Jose Mourinho ile yaşadığı kamuoyuna yansıyan anlaşmazlık
+Kelimeler:
+• falling-out = anlaşmazlık, küslük</t>
+      </text>
+    </comment>
+    <comment ref="G103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Ronaldo'nun sözleşmesi karşılıklı anlaşmayla gün içinde feshedildi ve ocak transfer dönemi açılmadan kulüpten ayrıldı.
+2018: Kötü sonuçlar ve artan oyuncu güç mücadeleleri sonrasında Mourinho haftalar içinde görevden alındı.
+Kelimeler:
+• terminated by mutual agreement = karşılıklı anlaşmayla feshedildi
+• escalating = tırmanan, artan</t>
+      </text>
+    </comment>
+    <comment ref="H103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester United'daki yıldız oyuncular yönetime veya teknik heyete açıkça saldırdığında, bu durum tarihsel olarak ciddi bir iç krizi tetikler ve birkaç hafta içinde ya oyuncunun hızlı ayrılığına ya da futbol liderliğinin uzaklaştırılmasına yol açar.
+Kelimeler:
+• triggers severe internal crisis = ciddi bir iç krizi tetikler
+• swift departure = hızlı ayrılış</t>
+      </text>
+    </comment>
+    <comment ref="I103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Soyunma odası ile yönetim arasındaki sürtüşmenin artması, Jason Wilcox üzerinde muazzam bir baskı oluşturması ve oyuncu için disiplin cezası veya ocak ayında takımdan ayrılma olasılığını artırması.
+Kelimeler:
+• friction = sürtüşme
+• disciplinary sanction = disiplin cezası</t>
+      </text>
+    </comment>
+    <comment ref="K103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 2 ay</t>
+      </text>
+    </comment>
+    <comment ref="L103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sir Jim Ratcliffe yönetimindeki INEOS sahipliği, yalnızca Glazer dönemine kıyasla daha katı ve tavizsiz bir kurumsal yönetim modeli benimsemiştir.
+Kelimeler:
+• uncompromising = tavizsiz
+• corporate governance = kurumsal yönetim</t>
+      </text>
+    </comment>
+    <comment ref="N103" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Disiplin cezalarıyla ilgili kulüp açıklamaları veya soyunma odasından gelebilecek yeni sızıntılar.
+Kelimeler:
+• disciplinary action = disiplin işlemi
+• leaks = sızıntılar</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kulüplerin çoğunluğu 'finansal felaket' eşiğinde - regülatör
+Kelimeler:
+• on edge = eşiğinde, gergin
+• financial disaster = finansal felaket
+• regulator = düzenleyici kurum, regülatör</t>
+      </text>
+    </comment>
+    <comment ref="D104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bağımsız Futbol Regülatörü tarafından yapılan araştırma, profesyonel kulüplerin %94'ünün zarar ettiğini, EFL ve Ulusal Lig kulüplerinin %60'ından fazlasının ise sahip sübvansiyonları olmadan teknik olarak iflas etmiş durumda olduğunu ortaya koyuyor.
+Kelimeler:
+• loss-making = zarar eden
+• insolvent = iflas etmiş, aciz
+• subsidies = sübvansiyonlar, destekler</t>
+      </text>
+    </comment>
+    <comment ref="E104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+iflaslar
+Kelimeler:
+• bank failures = iflaslar</t>
+      </text>
+    </comment>
+    <comment ref="F104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: COVID-19 pandemisi sırasında EFL finansal sürdürülebilirlik krizleri
+2019: Bury F.C.'nin İngiltere Futbol Ligi'nden ihraç edilmesi
+Kelimeler:
+• sustainability = sürdürülebilirlik
+• expulsion = ihraç edilme, kovulma</t>
+      </text>
+    </comment>
+    <comment ref="G104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Takip eden iki sezon boyunca çok sayıda kulüp kayyuma devredilme, puan silme cezaları ve acil devlet destekli krediler veya kurtarma paketleriyle karşı karşıya kaldı.
+2019: Yaygın kamuoyu tepkisi, doğrudan futbol yönetiminin devlet tarafından incelenmesine ve nihayetinde Bağımsız Futbol Regülatörü'nün kurulmasına yol açtı.
+Kelimeler:
+• administration = kayyuma devredilme
+• points deductions = puan silme cezaları
+• outcry = büyük tepki, isyan</t>
+      </text>
+    </comment>
+    <comment ref="H104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Resmi denetim organları tarafından alt liglerdeki sistemik iflasın açığa çıktığı vakaların %90'ında, durum 12 ila 18 ay içinde yasal müdahaleyi, sıkı finansal kontrolleri ve zorunlu sahiplik testlerini tetikler.
+Kelimeler:
+• systemic insolvency = sistemsel iflas
+• legislative intervention = yasal müdahale</t>
+      </text>
+    </comment>
+    <comment ref="I104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+EFL genelinde finansal fair play kurallarının daha katı bir şekilde uygulanması, Premier Lig kulüpleri üzerinde yeni bir finansal yeniden dağıtım anlaşmasını sonuçlandırmaları yönünde baskının artması ve mali sıkıntıdaki alt lig kulüplerinin potansiyel acil devralınmaları.
+Kelimeler:
+• enforcement = uygulama, icra
+• redistribution = yeniden dağıtım
+• distressed = mali sıkıntıdaki</t>
+      </text>
+    </comment>
+    <comment ref="K104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni yetkilendirilmiş Bağımsız Futbol Regülatörü'nün varlığı, yetkililere gönüllü futbol federasyonu kurallarına güvenmek yerine uyumu yasal olarak uygulama konusunda yasal yetkiler vermektedir.
+Kelimeler:
+• statutory powers = yasal yetkiler
+• compliance = uyum</t>
+      </text>
+    </comment>
+    <comment ref="N104" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Acil EFL toplantıları, kayyuma devredilen kulüpler ve gelir paylaşımı konusunda Premier Lig kulüplerinin direnci.
+Kelimeler:
+• pushback = direniş, geri püskürtme
+• revenue sharing = gelir paylaşımı</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Süper El Niño 'benzeri görülmemiş seviyelere' güçlenerek bir rekor daha kırdı
+Kelimeler:
+• unprecedented = benzeri görülmemiş</t>
+      </text>
+    </comment>
+    <comment ref="D105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+El Niño, benzeri görülmemiş seviyelere güçlenmeye devam ediyor; küresel sıcaklık ve hava durumuyla ilgili birkaç önemli ölçüm rekor bölgelere girdi.
+Kelimeler:
+• unprecedented = benzeri görülmemiş</t>
+      </text>
+    </comment>
+    <comment ref="E105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+El Niño</t>
+      </text>
+    </comment>
+    <comment ref="F105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015–2016: 2014–16 El Niño olayı
+1997–1998: 1997–98 El Niño olayı</t>
+      </text>
+    </comment>
+    <comment ref="G105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015–2016: Bir yıl içinde La Niña koşullarına hızlı bir geçişle takip edildi; bu durum küresel hava anomalilerini kısmen hafifletti ancak ardında şiddetli ekolojik yıkımlar bıraktı.
+1997–1998: Küresel sıcaklıklar, 1998 sonlarına doğru kalıcı bir La Niña evresine gerilemeden önce, 1998'de o dönem için benzeri görülmemiş seviyelere fırladı.
+Kelimeler:
+• unprecedented = benzeri görülmemiş
+• anomalies = anomaliler, olağan dışı durumlar
+• subsiding = azalan, dingileşen, gerileyen</t>
+      </text>
+    </comment>
+    <comment ref="H105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, süper El Niño olayları hızla zirve yapar ve genellikle 9 ila 12 ay içinde nötr veya La Niña koşullarına hızlı bir geçişle izlenir; bu durum sıklıkla kalıcı aşırı hava anomalileri ve yüksek küresel sıcaklık ortalamaları ile birlikte görülür.
+Kelimeler:
+• anomalies = anomaliler, olağan dışı durumlar
+• lingering = kalıcı, sürüp giden</t>
+      </text>
+    </comment>
+    <comment ref="I105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+La Niña düzenine doğru bir geçiş başlamadan önce, önümüzdeki aylarda şiddetli küresel hava bozulmalarının, aşırı yağışların ve bölgesel kuraklıkların sürmesi bekleniyor.
+Kelimeler:
+• droughts = kuraklıklar</t>
+      </text>
+    </comment>
+    <comment ref="K105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6-12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uzun vadeli iklim değişikliğinin tetiklediği temel arka plan ısınması, önceki tüm süper El Niño dönemlerinden daha yüksektir ve döngü zirve yaptıktan sonra bile aşırı sıcaklık rekorlarını potansiyel olarak sürdürebilir.</t>
+      </text>
+    </comment>
+    <comment ref="N105" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pasifik deniz suyu yüzeyi sıcaklık anomalilerinin soğumaya başlaması ve atmosferik alize rüzgarı kalıplarındaki değişimler.
+Kelimeler:
+• anomalies = anomaliler, olağan dışı durumlar</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları onlarca yıldır Alzheimer'ın gizli bir failini gözden kaçırmış olabilir
+Kelimeler:
+• overlooked = gözden kaçırmış, göz ardı etmiş
+• culprit = fail, suçlu, sebep olan unsur</t>
+      </text>
+    </comment>
+    <comment ref="D106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Araştırmacılar, Alzheimer tedavileri için onlarca yıldır amiloid beta üzerine yoğunlaşmanın hayal kırıklığı yaratan sonuçlar verdiğini ve bunun yeni tanımlanan faillere doğru bir kaymayı tetiklediğini vurguluyor.
+Kelimeler:
+• culprit = fail, suçlu, sebep olan unsur
+• yielded = verdi, sağladı</t>
+      </text>
+    </comment>
+    <comment ref="E106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+tıbbi araştırma değişimi</t>
+      </text>
+    </comment>
+    <comment ref="F106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980'ler–2000'ler: Mide ülseri patojeninin keşfi
+2000'ler–2010'lar: Ateroskleroz iltihaplanma değişimi</t>
+      </text>
+    </comment>
+    <comment ref="G106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980'ler–2000'ler: Barry Marshall ve Robin Warren 1980'lerde Helicobacter pylori'nin fail olduğunu kanıtladıktan sonra, tedavi tamamen antibiyotiklere kaydı ve önceden kronik olduğu düşünülen bir durumu iyileştirdi.
+2000'ler–2010'lar: İltihaplanmanın nihayetlenerek kabul edilmesi, önleyici kardiyolojide tamamen bir yenilenmeye ve 2010'ların sonlarında hedefli iltihap önleyici tedavilerin tanıtılmasına yol açtı.
+Kelimeler:
+• culprit = fail, suçlu, sebep olan unsur
+• overhaul = köklü değişiklik, elden geçirme</t>
+      </text>
+    </comment>
+    <comment ref="H106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tıp bilimi, onlarca yıldır süren tek hedefli dogmadan (amiloid beta veya sadece kolesterol gibi) uzaklaştığında, kombinasyon tedavileri standart uygulama haline gelmeden önce ilk şüphecilik 5-10 yıl süren karmaşık bir geçiş dönemine yerini bırakır.</t>
+      </text>
+    </comment>
+    <comment ref="I106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Klinik araştırmalar, amiloid temizliğinin yanı sıra alternatif biyolojik mekanizmaları hedeflemeye giderek daha fazla odaklanacak ve bu da daha geniş bir deneysel tedavi yelpazesine yol açacaktır.
+Kelimeler:
+• pivot = eksen değiştirmek, yönelmek</t>
+      </text>
+    </comment>
+    <comment ref="K106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern yüksek verimli tarama ve yapay zeka destekli biyolojik haritalama, araştırmacıların alternatif hücresel hedefleri geçmiş onlarca yıla göre çok daha hızlı değerlendirmesine olanak tanıyor.</t>
+      </text>
+    </comment>
+    <comment ref="N106" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Girişim sermayesi ve ilaç sektörü boru hattının amiloid dışı Alzheimer ilacı adaylarına yönelmesi.</t>
       </text>
     </comment>
   </commentList>
@@ -9554,7 +10831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P92"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17436,6 +18713,1196 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Trump's ambassador to Greece, Kimberly Guilfoyle, resigns after corruption allegations</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>The White House forced out U.S. Ambassador to Greece Kimberly Guilfoyle following accusations that she sought payments from a donor in exchange for access to administration officials.</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>diplomatic resignation</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2018: Resignation of Ryan Zinke
+2019: Resignation of Gordon Sondland</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>2018: Zinke resigned under pressure in December 2018, avoiding immediate prosecution at the time, though the investigations temporarily sidelined his political career before he later returned to the House of Representatives.
+2019: Sondland was summarily dismissed from his post days after the impeachment inquiry concluded, and subsequently filed a lawsuit against the State Department for unpaid legal fees.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>In similar executive branch ethics scandals, political appointees facing direct pressure from the White House resign swiftly to contain political damage, with formal investigations rarely resulting in immediate criminal convictions but effectively ending their diplomatic careers.</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Guilfoyle will likely maintain a low profile while facing preliminary ethics inquiries from the Department of Justice or congressional committees, but formal charges remain statistically unlikely based on historical precedents of departing envoys.</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>The specific nature of alleged pay-to-play access involving foreign donors could draw sharper scrutiny from federal prosecutors compared to administrative or travel expense infractions.</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Announcements of Department of Justice or House oversight subpoenas regarding embassy communications.</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/14/g-s1-148027/trump-ambassador-greece-resignation</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ryan_Zinke
+https://en.wikipedia.org/wiki/Gordon_Sondland</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Bipartisan group of senators call on Trump to rescind Russian diesel deal</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Six Democratic and six Republican senators sent a joint letter demanding that President Trump withdraw from a controversial diesel agreement recently brokered with Russian President Vladimir Putin.</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>congressional pushback</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2017: Russian Sanctions and Counter-Amnesty (CAATSA)
+2019: Congressional opposition to Syria withdrawal</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2017: Trump signed the bill into law reluctantly under overwhelming veto-proof pressure, establishing a precedent of Congress overriding executive overtures toward Moscow.
+2019: Despite fierce bipartisan condemnation and symbolic resolutions of disapproval, the administration largely proceeded with its policy adjustments, illustrating the limits of non-binding congressional letters.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>When a bipartisan bloc of senators publicly challenges executive trade or foreign policy deals, administrations either quietly modify the terms or ignore the letters if no binding veto-proof legislation is immediately advanced.</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>President Trump is likely to dismiss the bipartisan appeal initially, though legislative pressure could force modifications or increased transparency regarding the diesel deal's terms.</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>next 2 months</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Energy security and direct economic ties to Russia carry heightened domestic sensitivity amid ongoing European energy dynamics.</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Introduction of binding bipartisan legislation or amendments blocking implementation funds.</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/13/g-s1-147871/trump-russia-diesel-deal-congressional-response</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/Withdrawal_of_United_States_troops_from_Iraq_(2025%E2%80%932026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Hasbro preparing to move hundreds of jobs from Rhode Island to Boston</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Hasbro announced plans to relocate hundreds of jobs from its longtime Rhode Island headquarters footprint into the Boston area.</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>corporate relocation</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2023: General Electric relocation from Boston to Greater Boston and previous moves
+2018: Reebok headquarters move from Canton to Boston</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>2023: While securing tech talent was initially successful, high operational costs and hybrid work shifts led to reduced centralized footprints within 5 years.
+2018: Parent company Adidas later sold Reebok in 2021, and the urban headquarters footprint underwent significant restructuring and downsizing amid remote work transitions.</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>In major corporate relocations to high-cost urban innovation hubs like Boston, initial talent acquisition benefits often run up against high real estate overhead and subsequent corporate restructuring within 3 to 5 years.</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Hasbro will successfully secure initial tech and marketing talent in Boston, but face cost-pressure adjustments to its headcount footprint.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>next 3 years</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Hasbro's heavy reliance on digital gaming, entertainment partnerships, and toy-tech convergence makes Boston's specific talent pool uniquely vital compared to traditional manufacturing HQs.</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Final square footage commitments for the Boston office and local hiring rates.</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOdFRwNGVDa1RGaDJrY1AwZmtoc2c1ZnN6d0xwNnJmNDgwQ3ZCWWVBTEVmRnpPcW9ZVWI2VTFjeVJwbUlvMFlZSU1pdkhoeEFPcmxVRlc5TGYxZC1jM0hSUUlJWW5ZTlRiN3E0eWVQMHlhUzBiQTBzMjZheUNHWU1iZXFucWhpRElBcTg5VzNrdjB5b3lrR1EzU05TQjBBNzdOOHVmN0NYTWl2ampTRnpPbjlaTEtoY0QteTNueUFvT2Q?oc=5</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/General_Electric
+https://en.wikipedia.org/wiki/Reebok</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Markey, Deaton clash in first and only Massachusetts Senate debate</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Incumbent Senator Ed Markey and challenger Shiva Deaton (or relevant GOP/independent opponent) clashed in their first and only debate in a heavily blue state.</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>senate debate</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2020: Ed Markey 2020 Senate primary and general election
+2014: 2014 United States Senate election in Massachusetts</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2020: Markey won comfortably in the deep-blue general election by a wide margin, maintaining the state's entrenched partisan balance.
+2014: The incumbent safely retained the seat despite vocal challenger critique on the economy and spending.</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>In over 90% of modern Massachusetts statewide federal elections, late-stage debates generate headlines but fail to alter the fundamental structural advantage of the entrenched Democratic incumbent in a strongly blue electorate.</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>The debate will energize core political activists on both sides, but will not fundamentally disrupt the incumbent's polling lead.</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>election day</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Shifting national economic sentiment and specific voter fatigue regarding long-serving incumbents could narrow margins slightly compared to past cycles.</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Post-debate fundraising numbers and shifting early voting turnout metrics.</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObEpkUW16OWZta3ROY1UyQ0tZdGFWZ05GTXZVZU41aThseTdXWTUzUFVEc0JZRFBidUp1bkFoQU5kSVIwcVpHNDlXeGFXSVZxcmJxd2xGX2lOdU94OWlubUJUWENJcGYtcExZWE5ON0MwRXB5czI0dnFhT1lrR1ItbGdfSDZkTzVsTEhWbkM4ckNpYWs0eWZ5ZW85blV2cUlqNEcwdmUwNGZOSTZWRnVRa2Z0NDRBS195b2VhQ215N3FSSGtO0gHYAUFVX3lxTE5kcldaQ0JXNUpBQ2FINm15WVl4RWQ4UFVOS0ZyaUJJNXJlbmV4U3cyLUFJeWN3MHZWUWtBQW1JSWxlZVNNNG1NbERwZndWLUJZRlhRSXFDZDhhSGNxWGJpTVI0VWl3MEhyZnlkM2I5N3JwczU1TGplQ2xaUnYwTDlkVEdhMnZWdmEzVk02TGVZZXZuYllBaVJ6LWJNdEU5WnZlelNheXJzcWlfMGp6bUt3azBLZk9ZOGtpR0xYdWhKOS01S0VRV2RXQklMYm1sUVVUal9ySzdQMw?oc=5</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2020_United_States_Senate_election_in_Massachusetts
+https://en.wikipedia.org/wiki/2014_United_States_Senate_election_in_Massachusetts</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>US inflation rises more than expected - here's what is happening with prices</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>The pace of US price rises accelerated to 3.7% in the year to September, driven by higher motor fuel costs, stoking fears of further Federal Reserve rate hikes just before the midterm elections.</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>rate hike</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1973-1974: 1970s energy crisis
+2022: Post-pandemic inflation surge</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1973-1974: Economic growth stalled, leading to a prolonged stagflationary period throughout the mid-1970s.
+2022: Financial markets suffered significant corrections, and political pressure mounted on the central bank ahead of midterm elections.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>When inflation ticks upward unexpectedly due to energy shocks close to major elections, central banks face intense political pressure but historically prioritize tightening, resulting in increased market volatility.</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve is likely to signal or implement further monetary tightening to anchor expectations, keeping borrowing costs elevated.</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets remain remarkably resilient compared to historical tightening cycles, potentially cushioning broader economic fallout.</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Core PCE inflation prints and upcoming Federal Reserve speeches.</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cwy8lx3pg4k2o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973_oil_crisis
+https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Turkish police raid opposition TV station, halting live broadcasts</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Turkish police raided an opposition TV station, halting live broadcasts in the latest crackdown on media critical of the government.</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>crackdown</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2016: Post-coup purge in Turkey
+2023: Pre-election media restrictions in Turkey</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>2016: Independent media presence contracted severely, consolidating state control over information channels over the subsequent years.
+2023: Public debate narrowed significantly, weakening the organizational capacity and reach of political opposition movements.</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>In approximately 80% of similar authoritarian clampdowns on media in Turkey over the past decade, silenced broadcasters face prolonged closures or complete loss of operational licenses, forcing opposition discourse online.</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>The targeted TV station will likely remain off air indefinitely, prompting further migration of independent journalism to decentralized digital platforms.</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>The pervasive use of encrypted social media and decentralized streaming platforms makes total information suppression harder than in past decades.</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Legal status updates on the station's executives and potential international diplomatic responses.</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/crx23y3d970vo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Purges_in_Turkey_following_the_2016_Turkish_coup_attempt
+https://en.wikipedia.org/wiki/Censorship_in_Turkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Consumer prices in September jumped 3.7% from a year ago as energy prices skyrocket</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>U.S. inflation ticked up to 3.7% annually in September, driven heavily by soaring gas and energy prices stemming from conflict involving Iran.</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>oil shock</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1973: 1973 oil crisis
+1990: 1990 oil price shock</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1973: U.S. inflation spiked into double digits, triggering a severe recession and forcing the Federal Reserve to implement aggressive, economy-chilling rate hikes over the following 2-3 years.
+1990: The U.S. economy tipped into a recession lasting from July 1990 to March 1991, though inflation subsided relatively quickly once military intervention secured oil supplies.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>In 2 out of 2 similar historical instances of sudden geopolitical energy shocks, central banks were forced to keep monetary policy restrictive, and the ruling party suffered heavily at the ballot box.</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve will likely maintain its current interest rate stance or hint at further tightening, refusing to cut rates despite slowing growth in other sectors.</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>next 3-6 months</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. is now a net exporter of oil and shale production provides a domestic cushion, unlike the vulnerable import dependency of the 1970s.</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Core inflation metrics excluding energy, and upcoming Federal Reserve statements on rate paths.</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/14/cpi-inflation-report-september-2026.html</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973_oil_crisis
+https://en.wikipedia.org/wiki/1990_oil_price_shock</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Surging Inflation Complicates Trump’s Final Push to Sell Voters on Strong Economy ahead of Midterms</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>The final inflation report before the 2026 midterm elections showed sticky price increases, expanding the political map for Democrats deep into Republican territory.</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>midterm swings</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2022: 2022 United States elections
+1974: 1974 United States elections</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>2022: The incumbent party suffered significant congressional headwinds, though the predicted 'red wave' was muted, the White House party historically lost control of the House.
+1974: The incumbent Republican party suffered a landslide defeat, losing 48 seats in the House and 4 in the Senate.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>In 80% of midterm elections featuring annual inflation above 3%, the sitting president's party loses congressional seats.</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is likely to lose ground in Congress as cost-of-living fatigue drives voter turnout against incumbents.</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>next month (November 2026 election)</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Polarized electorate and hyper-targeted district maps could insulate certain incumbents despite broad economic dissatisfaction.</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Final pre-election polling shifts in suburban swing districts and voter turnout metrics.</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/14/business/economy/inflation-economy-midterms.html</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022_United_States_elections
+https://en.wikipedia.org/wiki/1974_United_States_Senate_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>US inflation rises more than expected - here's what is happening with prices</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>The pace of US price rises increased to 3.7% in the year to September, driven higher by surging motor fuel costs amid ongoing geopolitical tensions.</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>oil shock</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1973: 1973 oil crisis
+2022: 2022 inflation surge</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1973: Global inflation spiked dramatically into double digits within months, triggering a severe, prolonged stagflationary recession across Western economies.
+2022: The Federal Reserve aggressively hiked interest rates by over 500 basis points over the subsequent 18 months to cool demand.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>In 80% of major geopolitical energy shocks, initial inflation spikes force central banks to maintain or extend tight monetary policy despite slowing economic growth elsewhere.</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve will likely hold interest rates steady or signal a hawkish pause to combat sticky fuel-driven inflation.</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets and underlying wage growth are currently more resilient than they were during the 1970s stagflation era.</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Core inflation metrics excluding energy, and consumer long-term inflation expectations.</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cwy8lx3pg4k2o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973_oil_crisis
+https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Poundland in rescue talks as owners seek buyer</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Poundland's leadership team is in rescue talks as owners seek a buyer, with unions warning the discount retailer could fall into administration.</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>retail administration</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2018: Collapse of Toys "R" Us UK
+2008: Collapse of Woolworths</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>2018: All UK stores were wound down and liquidated over a period of three months, resulting in the loss of thousands of retail jobs.
+2008: The company collapsed completely within weeks, liquidating hundreds of stores and marking one of the largest high-street failures in UK history.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>When large multi-site retailers enter rescue talks amidst tightening consumer spending and high energy costs, more than 60% end up in formal administration or massive store rationalizations if an immediate buyer with deep liquidity is not found.</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Poundland will likely undergo a pre-pack administration resulting in significant store closures and job cuts unless a preferred buyer quickly finalizes a rescue deal.</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 2 months</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Discount retailers sometimes experience a surge in shoppers during downturns, which could attract opportunistic private equity interest.</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Statements from creditors regarding debt covenants and the finalization of the Martin Property Group partnership.</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/ckr5ydvvln0mo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Toys_%22R%22_Us
+https://en.wikipedia.org/wiki/Woolworths_(United_Kingdom)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Lisandro Martinez's explosive comments after Manchester United's Champions League defeat by Atletico Madrid turn the spotlight back on director of football Jason Wilcox.</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Manchester United defender Lisandro Martinez launched a scathing public attack on the club's board and hierarchy following a Champions League defeat, specifically putting pressure on director of football Jason Wilcox over squad investment.</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>manager sacked</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2023: Cristiano Ronaldo's explosive interview with Piers Morgan criticizing Manchester United's hierarchy
+2018: Paul Pogba's public falling-out with Jose Mourinho at Manchester United</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>2023: Ronaldo's contract was terminated by mutual agreement within days, and he left the club before the January transfer window opened.
+2018: Mourinho was sacked as manager within weeks following a poor run of results and escalating player power struggles.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>When star players at Manchester United publicly attack the hierarchy or management, it historically triggers severe internal crisis, leading either to the player's swift departure or the removal of the football leadership within a matter of weeks.</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Increased friction between the dressing room and the board, putting immense pressure on Jason Wilcox and raising the probability of a disciplinary sanction or a January exit for the player.</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>next 2 months</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>INEOS ownership under Sir Jim Ratcliffe has adopted a stricter, uncompromising corporate governance model compared to the Glazer-only era.</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Club statements regarding disciplinary action, or further leaks from the dressing room.</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cvp8g57ne53xo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cristiano_Ronaldo
+https://en.wikipedia.org/wiki/Jos%C3%A9_Mourinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Majority of clubs on edge of 'financial disaster' - regulator</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Research by the Independent Football Regulator reveals that 94% of professional clubs are loss-making, with over 60% of EFL and National League clubs technically insolvent without owner subsidies.</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>bank failures</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2020: EFL financial sustainability crisis during the COVID-19 pandemic
+2019: Bury F.C. expulsion from the English Football League</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2020: Multiple clubs faced administration, points deductions, and emergency government-backed loans or rescue packages over the subsequent two seasons.
+2019: Widespread outcry led directly to government reviews of football governance and the eventual creation of the Independent Football Regulator.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>In 90% of cases where systemic lower-league insolvency is exposed by official oversight bodies, it triggers legislative intervention, strict financial controls, and mandatory ownership tests within 12 to 18 months.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Stricter enforcement of financial fair play rules across the EFL, increased pressure on Premier League clubs to finalize a new financial redistribution deal, and potential emergency takeovers of distressed lower-league clubs.</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>The presence of a newly empowered Independent Football Regulator gives authorities statutory powers to legally enforce compliance rather than relying on voluntary football association rules.</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Emergency EFL meetings, clubs entering administration, and pushback from Premier League clubs over revenue sharing.</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/videos/ck3wvxz8n1nyo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Impact_of_the_COVID-19_pandemic_on_association_football
+https://en.wikipedia.org/wiki/Bury_F.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Super El Niño sets another record as it strengthens to 'unprecedented levels'</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>El Niño has continued to strengthen to unprecedented levels, with several key global temperature and weather measures entering record territory.</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>El Niño</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2015–2016: 2014–16 El Niño event
+1997–1998: 1997–98 El Niño event</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2015–2016: It was followed by a rapid transition to La Niña conditions within a year, which partially moderated global weather anomalies but left severe ecological disruptions in its wake.
+1997–1998: Global temperatures spiked to then-unprecedented highs in 1998 before subsiding into a persistent La Niña phase by late 1998.</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Historically, super El Niño events peak rapidly and are typically followed within 9 to 12 months by a swift transition into neutral or La Niña conditions, frequently accompanied by lingering extreme weather anomalies and elevated global temperature averages.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Expect severe global weather disruptions, extreme rainfall, and localized droughts to persist over the coming months before a transition toward a La Niña pattern begins.</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>next 6-12 months</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Underlying background warming driven by long-term climate change is higher than during any previous super El Niño, potentially sustaining extreme temperature records even after the cycle peaks.</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Pacific sea surface temperature anomalies beginning to cool and shifts in atmospheric trade wind patterns.</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/weather/articles/cmlye0d7q7zno</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2014%E2%80%932016_El_Ni%C3%B1o_event
+https://en.wikipedia.org/wiki/1997%E2%80%931998_El_Ni%C3%B1o_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Scientists may have overlooked a hidden Alzheimer's culprit for decades</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Researchers highlight that decades of focusing heavily on amyloid beta for Alzheimer's treatments have yielded disappointing results, prompting a shift toward newly identified culprits.</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>medical research shift</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1980s–2000s: Gastric ulcer pathogen discovery
+2000s–2010s: Atherosclerosis inflammation shift</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1980s–2000s: Once Barry Marshall and Robin Warren proved Helicobacter pylori was the culprit in the 1980s, treatment shifted completely to antibiotics, curing a condition previously thought chronic.
+2000s–2010s: The eventual recognition of inflammation led to a complete overhaul of preventive cardiology and the introduction of targeted anti-inflammatory therapies in the late 2010s.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>When medical science moves away from a decades-long single-target dogma (like amyloid beta or cholesterol alone), initial skepticism gives way to a messy transition period lasting 5-10 years before combination therapies become standard practice.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Clinical trials will increasingly pivot toward targeting alternative biological mechanisms alongside amyloid clearance, leading to a broader spectrum of experimental treatments.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Modern high-throughput screening and AI-driven biological mapping allow researchers to evaluate alternative cellular targets much faster than in past decades.</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Venture capital and pharmaceutical pipeline shifts toward non-amyloid Alzheimer's drug candidates.</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261013015838.htm</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Helicobacter_pylori
+https://en.wikipedia.org/wiki/Atherosclerosis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -10536,6 +10536,1171 @@
       <text>
         <t>Türkçe:
 Girişim sermayesi ve ilaç sektörü boru hattının amiloid dışı Alzheimer ilacı adaylarına yönelmesi.</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kansas'ta yeni rekabetçi Senato yarışması, Trump'ın popüler olmayan politikalarının sınırını test ediyor
+Kelimeler:
+• newly competitive = yeni rekabetçi hale gelen
+• test limit = sınırı test etmek</t>
+      </text>
+    </comment>
+    <comment ref="D107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kansas seçmenleri, Trump'ın politikalarına karşı duyulan seçmen tepkisinin ortasında, neredeyse bir asırdır ilk kez Senato'ya bir Demokrat gönderebilecek rekabetçi bir Senato yarışını değerlendiriyor.
+Kelimeler:
+• weigh = değerlendirmek, tartmak
+• voter backlash = seçmen tepkisi
+• nearly a century = neredeyse bir asır</t>
+      </text>
+    </comment>
+    <comment ref="E107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçim salınımları
+Kelimeler:
+• midterm swings = ara seçim salınımları</t>
+      </text>
+    </comment>
+    <comment ref="F107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Amerika Birleşik Devletleri ara seçimleri
+2006: Amerika Birleşik Devletleri ara seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="G107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Muhalefet partisi, başkanlık döneminin henüz iki yılında 41 sandalye kazanarak Temsilciler Meclisi'nin kontrolünü ele geçirdi.
+2006: Muhalefet partisi hem Temsilciler Meclisi'nin hem de Senato'nun kontrolünü kazandı.
+Kelimeler:
+• flipped = el değiştirmek, karşı tarafa geçmek
+• gaining seats = sandalye kazanmak</t>
+      </text>
+    </comment>
+    <comment ref="H107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ara seçimlerin yaklaşık yüzde 70'inde, Beyaz Saray'ı elinde bulunduran parti kongre sandalyeleri kaybeder; çünkü seçmenler ekonomik veya politik şikayetlerini sandık başında dile getirir.
+Kelimeler:
+• surprise to the upside = yukarı yönlü sürpriz yapmak
+• grievances = şikayetler, hoşnutsuzluklar</t>
+      </text>
+    </comment>
+    <comment ref="I107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İktidardaki parti, kararsız seçmenlerin pişmanlık ifade etmesiyle birlikte, tarihi olarak güvenli bölgelerde ciddi rüzgarlarla ve potansiyel sandalye kayıplarıyla karşılaşabilir.
+Kelimeler:
+• severe headwinds = ciddi zorluklar, ters rüzgarlar
+• swing voters = kararsız seçmenler</t>
+      </text>
+    </comment>
+    <comment ref="K107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek ay</t>
+      </text>
+    </comment>
+    <comment ref="L107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Derinden kökleşmiş partizan kutuplaşma ve yerel aday dinamikleri, normalde Cumhuriyetçi olan eyaletlerdeki bazı görevdeki isimleri koruyabilir.
+Kelimeler:
+• entrenched = kökleşmiş, yerleşmiş
+• insulate = korumak, yalıtmak
+• incumbents = görevdeki yetkililer/adaylar</t>
+      </text>
+    </comment>
+    <comment ref="N107" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Banliyö katılım oranları ve geleneksel olarak güvenli eyaletlerde son anket hareketleri.
+Kelimeler:
+• turnout numbers = katılım sayıları
+• tracking polls = takip anketleri</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon beklenenden fazla arttı - fiyatlarda neler oluyor?
+Kelimeler:
+• rises more than expected = beklenenden fazla artıyor</t>
+      </text>
+    </comment>
+    <comment ref="D108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de Eylül ayına kadar olan yılda enflasyon, motorlu yakıt maliyetlerinin artışıyla beklenenden fazla yüzde 3,7'ye yükseldi ve Amerikan hanehalklarını sıkıştırdı.
+Kelimeler:
+• driven by = tarafından tetiklenen, kaynaklanan
+• squeezing = sıkıştıran, zor durumda bırakan
+• households = hanehalkları</t>
+      </text>
+    </comment>
+    <comment ref="E108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+petrol şokları
+Kelimeler:
+• oil shocks = petrol şokları</t>
+      </text>
+    </comment>
+    <comment ref="F108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021-2022: 2021-2023 enflasyon dalgası
+1973: 1973 petrol krizi
+Kelimeler:
+• inflation surge = enflasyon dalgası/artışı</t>
+      </text>
+    </comment>
+    <comment ref="G108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021-2022: Merkez bankası, takip eden 18 ay boyunca faiz oranlarını agresif bir şekilde artırarak ekonominin yavaşlamasına yol açtı.
+1973: Uzun süreli stagflasyon ve şiddetli bir ekonomik durgunluk 1970'lerin ortalarına kadar devam etti.
+Kelimeler:
+• hiked interest rates = faiz oranlarını artırdı
+• stagflation = stagflasyon (enflasyon ile durgunluğun bir arada görülmesi)
+• persisted = devam etti, sürdü</t>
+      </text>
+    </comment>
+    <comment ref="H108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enflasyon rakamları önemli siyasi döngülere yakın bir şekilde yukarı yönlü sürpriz yaptığında, kamu memnuniyetsizliği artar ve merkez bankaları kısıtlayıcı para politikası duruşlarını sürdürmeleri konusunda baskı altına girer.
+Kelimeler:
+• public dissatisfaction = kamu memnuniyetsizliği
+• restrictive monetary stances = kısıtlayıcı para politikası duruşları</t>
+      </text>
+    </comment>
+    <comment ref="I108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kalıcı fiyat baskıları, borçlanma maliyetlerini yüksek tutacak ve iktidar partisinin ekonomik onay oranlarına ağır darbe vuracaktır.
+Kelimeler:
+• persistent price pressures = kalıcı fiyat baskıları
+• borrowing costs elevated = yüksek borçlanma maliyetleri
+• approval ratings = onay oranları</t>
+      </text>
+    </comment>
+    <comment ref="K108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3-6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İş gücü piyasaları, tarihi stagflasyon dönemlerine kıyasla direncini koruyor ve hanehalklarına artan masraflara karşı bir miktar tampon sağlıyor.
+Kelimeler:
+• resilient = dayanıklı, dirençli
+• buffer = tampon, koruyucu</t>
+      </text>
+    </comment>
+    <comment ref="N108" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Rezerv'in gelecekteki faiz oranı patikası hakkındaki mesajları ve tüketici harcama raporları.
+Kelimeler:
+• messaging = mesaj verme, iletişim dili
+• consumer spending = tüketici harcamaları</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mass. denetçi raporu, eyaletin yerel alkol lisansı sınırlamalarının kaldırılmasını talep ediyor
+Kelimeler:
+• auditor report = denetçi raporu
+• repealing = yürürlükten kaldırma
+• caps = üst sınırlar</t>
+      </text>
+    </comment>
+    <comment ref="D109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts eyalet denetçisi, Boston ve çevresindeki belediyelerde restoranların ve gece hayatının büyümesini tarihi olarak kısıtlayan yerel alkol lisansı üst sınırlarının tamamen kaldırılmasını talep eden bir rapor yayınladı.
+Kelimeler:
+• repeal = iltga etmek, yürürlükten kaldırmak
+• surrounding municipalities = çevre belediyeler</t>
+      </text>
+    </comment>
+    <comment ref="E109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kuralsızlaştırma
+Kelimeler:
+• deregulation = kuralsızlaştırma, düzenlemelerin kaldırılması</t>
+      </text>
+    </comment>
+    <comment ref="F109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: Massachusetts kapsamlı alkol yasası reformu
+2017: Chicago'da Illinois'in alkol lisansı ve kota sınırları reformu
+Kelimeler:
+• comprehensive = kapsamlı
+• overhaul = baştan aşağı yenileme, reform</t>
+      </text>
+    </comment>
+    <comment ref="G109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2006: Perakendeciler, gelenekselcilerin ilk yerel muhalefetini överek ilk altı ay içinde Pazar gelirlerinde anında çok yüzdelik bir artış gördü.
+2017: Mevcut lisansları yüksek yeniden satış değerine sahip olan yerleşik lisans sahipleri tarafından yoğun bir şekilde geri püskürtüldü, bu da tam bir kaldırma yerine sulandırılmış bir uzlaşmaya yol açtı.
+Kelimeler:
+• watered-down compromise = sulandırılmış uzlaşma
+• resale value = yeniden satış değeri</t>
+      </text>
+    </comment>
+    <comment ref="H109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Benzer belediye kuralsızlaştırma mücadelelerinin 4'te 3'ünde, denetçi liderliğindeki kapsamlı yapısal kaldırma önerileri, izinleri yüksek değerli özel teminat görevi gören lisans mevcut sahiplerinden büyük bir dirençle karşılaşıyor ve bu durum uzun süren yasal çıkmazlara veya parça parça uzlaşmalara neden oluyor.
+Kelimeler:
+• sweeping structural repeal = kapsamlı yapısal yürürlükten kaldırma
+• protracted legislative stalemates = uzun süren yasama çıkmazları</t>
+      </text>
+    </comment>
+    <comment ref="I109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eyalet yasama meclisi, doğrudan bir kaldırmadan ziyade büyük ölçüde değiştirilmiş bir genişletme yasa tasarısını geçirmeden önce mevcut lisans sahiplerinden yoğun kulis faaliyetleriyle karşılaşarak kaldırma işlemini aylarca tartısacaktır.
+Kelimeler:
+• outright repeal = doğrudan yürürlükten kaldırma
+• lobbying = kulis faaliyeti</t>
+      </text>
+    </comment>
+    <comment ref="K109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ila 18 ay</t>
+      </text>
+    </comment>
+    <comment ref="L109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kentsel merkezler ve restoranlar üzerindeki salgın sonrası ekonomik baskılar önceki on yıllara göre daha keskin ve potansiyel olarak statüko korumacılığına karşı daha geniş bir kentsel belediye başkanları koalisyonunu birleştiriyor.
+Kelimeler:
+• acute = şiddetli, keskin
+• status-quo protectionism = statüko korumacılığı</t>
+      </text>
+    </comment>
+    <comment ref="N109" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston'ın belediye liderliğinin ve yasama ana komite başkanlarının mevcut lisans değerlerinin korunmasıyla ilgili açıklamaları.
+Kelimeler:
+• committee chairs = komite başkanları</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mass., bir düzine RegalCare huzurevinin lisanslarını iptal etmek için harekete geçiyor
+Kelimeler:
+• strip licenses = lisansları iptal etmek / almak
+• nursing homes = huzurevleri</t>
+      </text>
+    </comment>
+    <comment ref="D110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'teki düzenleyiciler, ciddi kalite ve güvenlik ihlallerinin ardından RegalCare tarafından yönetilen bir düzine huzurevinin işletme lisanslarını iptal etmek için işlemler başlattı.
+Kelimeler:
+• regulators = düzenleyici kurumlar, denetleyiciler
+• violations = ihlaller</t>
+      </text>
+    </comment>
+    <comment ref="E110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+lisans iptali
+Kelimeler:
+• license revocation = lisans iptali</t>
+      </text>
+    </comment>
+    <comment ref="F110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Massachusetts Halk Sağlığı Departmanı'nın başarısız olan uzun süreli bakım tesisini kapatması
+2020: COVID-19 pandemisi sırasında sorunlu huzurevi zincirlerine yönelik eyalet baskıları
+Kelimeler:
+• crackdowns = sıkı denetimler, baskılar</t>
+      </text>
+    </comment>
+    <comment ref="G110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Eyaletin, yerinden edilmiş sakinler için alternatif yerleştirmeler bulurken geçici operasyonları sübvanse etmek zorunda kaldığı karmaşık, aylarca süren kayyumluk mücadelelerini tetikledi.
+2020: İşleticiler, lisans iptalini durdurmak için sık sık acil yasal ihtiyati tedbir kararları başvurusunda bulundu ve bakımın geçiş sürecini bir yıla kadar uzattı.
+Kelimeler:
+• receivership battles = kayyumluk mücadeleleri
+• legal injunctions = hukuki ihtiyati tedbirler</t>
+      </text>
+    </comment>
+    <comment ref="H110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Benzer huzurevi lisans iptali eylemlerinin 4'te 5'inde, kurumsal işletmeciler acil yasal itirazlar ve mahkeme ihtiyati tedbirleriyle yanıt vererek eyaleti sakinlerin bakımının sürekliliğini sağlamak için uzun süreli bir kayyumluk düzenlemesine zorluyor.
+Kelimeler:
+• prolonged = uzun süren, uzatılmış
+• continuity of care = bakımın sürekliliği</t>
+      </text>
+    </comment>
+    <comment ref="I110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+RegalCare, eyaletin mahkemedeki eylemlerine muhtemelen itiraz edecek ve bu da sakinler yavaşça başka yerlere taşınırken veya eyalet denetimi altında yönetilirken mahkeme tarafından atanan bir kayyumluğa yol açacaktır.
+Kelimeler:
+• court-appointed receivership = mahkeme atamalı kayyumluk
+• relocated = yeri değiştirilen</t>
+      </text>
+    </comment>
+    <comment ref="K110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eyalet düzenleyicileri, salgın sonrası artan bir hassasiyet ve sistemik uzun süreli bakım başarısızlıklarına karşı daha az tolerans gösteriyor, bu da gönüllü teslimiyeti veya hızlandırılmış eyalet kayyumluluğunu geçmiş on yıllara göre daha olası kılıyor.
+Kelimeler:
+• heightened sensitivity = artmış hassasiyet
+• voluntary surrender = gönüllü teslim</t>
+      </text>
+    </comment>
+    <comment ref="N110" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+RegalCare yönetimi tarafından acil ihtiyati tedbirler için mahkeme başvuruları ve sakinlerin yer değiştirme planlarıyla ilgili duyurular.
+Kelimeler:
+• court filings = mahkeme başvuruları</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelenski'nin saldırıların yeniden başlayacağını söylemesinin ardından Rusya, Ukrayna'yı petrol rafinerisine saldırmakla suçladı
+Kelimeler:
+• accuse = suçlamak
+• refinery = rafineri
+• resume = yeniden başlamak</t>
+      </text>
+    </comment>
+    <comment ref="D111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ukrayna cumhurbaşkanı, yeni Rus saldırılarının ardından enerji altyapısına yönelik geçici saldırı durdurma kararının sona erdiğini açıkladı; bu açıklamanın hemen ardından bir rafineri saldırısı nedeniyle karşılıklı suçlamalar geldi.
+Kelimeler:
+• temporary pause = geçici duraklama
+• mutual accusations = karşılıklı suçlamalar</t>
+      </text>
+    </comment>
+    <comment ref="E111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+enerji altyapısı saldırıları
+Kelimeler:
+• infrastructure = altyapı</t>
+      </text>
+    </comment>
+    <comment ref="F111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kış 2022-2023: Rusya'nın Ukrayna enerji şebekesine yönelik saldırıları
+İlkbahar 2024: Ukrayna'nın Rus rafinerilerine yönelik İHA saldırılarının tırmanması
+Kelimeler:
+• escalation = tırmanma, şiddetlenme</t>
+      </text>
+    </comment>
+    <comment ref="G111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kış 2022-2023: Ukrayna, merkeziyetsiz güç sistemleri ve batı hava savunmasıyla uyum sağlarken, 2024 başlarından itibaren Rus petrol rafinerilerine karşı misilleme niteliğinde uzun menzilli İHA saldırıları başlattı.
+İlkbahar 2024: 
+Kelimeler:
+• retaliatory = misilleme niteliğinde</t>
+      </text>
+    </comment>
+    <comment ref="H111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enerji altyapısı saldırılarındaki zımni veya geçici duraklamalar sona erdiğinde, her iki taraf da ekonomik hedeflere yönelik derin darbe kampanyalarını hızla tırmandırarak sürekli yakıt tedarik baskılarına ve artan bölgesel risklere yol açar.
+Kelimeler:
+• tacit = zımni, söylenmemiş
+• break down = çökülmek, bozulmak</t>
+      </text>
+    </comment>
+    <comment ref="I111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzdeki aylarda petrol rafinerilerini ve enerji şebekelerini hedef alan yoğunlaşmış bir karşılıklı uzun menzilli İHA ve füze saldırısı dalgası beklenmelidir.
+Kelimeler:
+• intensified = yoğunlaştırılmış
+• reciprocal = karşılıklı</t>
+      </text>
+    </comment>
+    <comment ref="K111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Her iki taraftaki gelişmiş hava savunma mimarileri ve daha büyük İHA üretim kapasitesi, önceki yıllara kıyasla yıkımın ölçeğini değiştiriyor.
+Kelimeler:
+• scale of destruction = yıkımın ölçeği</t>
+      </text>
+    </comment>
+    <comment ref="N111" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İlgili bölgelerde büyük rafineri yangınları veya acil yakıt karnesi/kısıtlaması raporları.
+Kelimeler:
+• rationing = karneye bağlama, kısıtlama</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kuzey Kore ve Çin, 12 yıllık gecikmenin ardından yeni köprüyü açtı
+Kelimeler:
+• delay = gecikme</t>
+      </text>
+    </comment>
+    <comment ref="D112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kuzey Kore ve Çin, uluslararası yaptırımlar ortasında ticaret bağlarını güçlendirerek, uzun süren 12 yıllık bir gecikmenin ardından nihayet yeni inşa edilen sınır ötesi köprüyü açtı.
+Kelimeler:
+• protracted = uzun süren, uzatmalı
+• sanctions = yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="E112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+altyapı projesi açılışı</t>
+      </text>
+    </comment>
+    <comment ref="F112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Yeni Yalu Nehri Köprüsü'nün tamamlanması
+Kelimeler:
+• completion = tamamlanma</t>
+      </text>
+    </comment>
+    <comment ref="G112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2015: Proje süresiz olarak durdu ve siyasi ile lojistik engeller arttığında ikili ekonomik entegrasyonun sınırlarını gözler önüne serdi.
+Kelimeler:
+• stalled indefinitely = süresiz olarak durdu
+• hurdles = engeller</t>
+      </text>
+    </comment>
+    <comment ref="H112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ağır yaptırıma uğramış devletler ile onların ana ekonomik hamileri arasındaki büyük altyapı projeleri, ekonomik zorunluluk bürokratik veya siyasi gecikmeleri geçersiz kıldığında sonunda açılır ve asimetrik ekonomik bağımlılığı pekiştirmeye hizmet eder.
+Kelimeler:
+• overrides = hükümsüz kılar, ağır basar
+• cement = pekiştirmek, sağlamlaştırmak</t>
+      </text>
+    </comment>
+    <comment ref="I112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çin ile Kuzey Kore arasındaki karayolu taşımacılığı rotaları üzerinden ikili ticaret hacminin istikrarlı bir artış göstermesi muhtemeldir ve bu durum Pyongyang'ı uluslararası tecride karşı koruyacaktır.
+Kelimeler:
+• cushion = korumak, yastıklamak
+• isolation = tecrit, yalnızlaşma</t>
+      </text>
+    </comment>
+    <comment ref="K112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pyongyang ve Moskova arasındaki derinleşen askeri ve ekonomik uyum, Pekin için ekonomik etkisini güvence altına alma konusunda yeni bir jeopolitik aciliyet yaratıyor.
+Kelimeler:
+• alignment = hizalanma, iş birliği
+• urgency = aciliyet</t>
+      </text>
+    </comment>
+    <comment ref="N112" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni sınır kapısındaki artan navlun trafiğini gösteren gümrük verileri.
+Kelimeler:
+• freight traffic = yük taşımacılığı trafiği</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Artan Enflasyon, Trump'ın Güçlü Ekonomi Konusunda Seçmenleri İkna Etme Çabalarını Zorlaştırıyor
+Kelimeler:
+• surging inflation = hızla yükselen enflasyon
+• final push = son hamle / gayret</t>
+      </text>
+    </comment>
+    <comment ref="D113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beklentilerden daha yüksek gelen Eylül ayı TÜFE raporu, ABD enflasyonunun büyük ölçüde tırmanan enerji fiyatlarının etkisiyle %3,7'ye fırladığını gösterdi; bu durum, ara seçimlerden sadece birkaç hafta önce Başkan Trump ve Cumhuriyetçi adaylar için zorlu siyasi engeller yaratıyor.
+Kelimeler:
+• hotter-than-expected = beklenenden yüksek
+• political headwinds = siyasi rüzgarlar / engeller
+• midterm elections = ara seçimler</t>
+      </text>
+    </comment>
+    <comment ref="E113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçimler öncesi enflasyon artışı</t>
+      </text>
+    </comment>
+    <comment ref="F113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1974: 1973–1975 resesyonu ve enflasyon sıçraması
+1982: 1980'lerin başındaki resesyon
+Kelimeler:
+• precedents = emsaller / geçmiş örnekler</t>
+      </text>
+    </comment>
+    <comment ref="G113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1974: İktidardaki Cumhuriyetçi parti, 1974 ara seçimlerinde büyük kayıplar yaşayarak Temsilciler Meclisi'nde neredeyse 50 sandalye kaybetti.
+1982: Cumhuriyetçiler, Senato kontrolü kıl payı korunsa da 1982 ara seçimlerinde Temsilciler Meclisi'nde 26 sandalye kaybetti.
+Kelimeler:
+• incumbent = görevde olan / iktidardaki
+• massive losses = büyük kayıplar</t>
+      </text>
+    </comment>
+    <comment ref="H113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek enflasyon veya artan enerji maliyetleri dönemlerinde gerçekleşen tarihi ara seçimlerin yaklaşık %80'inde, Beyaz Saray'ı elinde bulunduran parti önemli kongre kayıpları yaşamaktadır.
+Kelimeler:
+• holding the White House = Beyaz Saray'ı elinde tutan</t>
+      </text>
+    </comment>
+    <comment ref="I113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İktidardaki partinin sandıkta ciddi bir seçim cezasıyla karşılaşması ve bunun yasama çoğunluklarının potansiyel kaybına yol açması bekleniyor.
+Kelimeler:
+• electoral penalty = seçim cezası
+• legislative majorities = yasama çoğunlukları</t>
+      </text>
+    </comment>
+    <comment ref="K113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 4 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenler ekonomik memnuniyetsizliği yerel aday tercihinden soyutlayabilir veya yoğun partizan kutuplaşma olağan geriye dönük oy verme eğilimini geçersiz kılabilir.
+Kelimeler:
+• dissatisfaction = memnuniyetsizlik
+• partisan polarization = partizan kutuplaşma
+• retrospective voting = geçmişe dönük oy verme</t>
+      </text>
+    </comment>
+    <comment ref="N113" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmen anketlerinin son haftaları ve banliyölerdeki salıncak bölgelerindeki katılım metrikleri.
+Kelimeler:
+• turnout metrics = katılım oranları / metrikleri
+• swing districts = salıncak bölgeler / kritik seçim çevreleri</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Analiz: 2 trilyonluk açık ve %5'lik Hazine tahvili getirileri neden Amerika'nın en büyük ekonomik sorunu haline geliyor
+Kelimeler:
+• deficit = bütçe açığı
+• Treasury yields = Hazine tahvili getirileri</t>
+      </text>
+    </comment>
+    <comment ref="D114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD ulusal borcu, kalıcı 2 trilyon dolarlık yıllık açıklarla birlikte 40 trilyon doları aşarken, 10 yıllık Hazine tahvili getirileri inatla %5'in üzerinde kalmaya devam ediyor ve hem hanehalkları hem de federal hükümet için borçlanma maliyetlerini artırıyor.
+Kelimeler:
+• surpasses = aşmak / geçmek
+• stubbornly = inatla / dirençli bir şekilde
+• borrowing costs = borçlanma maliyetleri</t>
+      </text>
+    </comment>
+    <comment ref="E114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+borç ve yüksek tahvil getirileri</t>
+      </text>
+    </comment>
+    <comment ref="F114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: Amerika Birleşik Devletleri borç tavanı kriz
+1985: Gramm–Rudman–Hollings Dengeli Bütçe Yasası
+Kelimeler:
+• debt-ceiling crisis = borç tavanı krizi</t>
+      </text>
+    </comment>
+    <comment ref="G114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: Borçlanma maliyetleri geçici olarak fırladı ve hisse senedi piyasaları ciddi dalgalanma yaşayarak mali kemer sıkma önlemlerine uzun süreli bir odaklanmayı zorunlu kıldı.
+1985: Bütçeyi hemen dengelemekte başarısız olsa da, yıllar süren yoğun iki partili mali mücadeleleri başlattı ve harcama sınırlarını zorunlu kıldı.
+Kelimeler:
+• fiscal austerity = mali kemer sıkma
+• spending caps = harcama sınırları</t>
+      </text>
+    </comment>
+    <comment ref="H114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+10 yıllık Hazine tahvili getirileri, artan yapısal açıklar ortasında kilit psikolojik eşiklerin üzerinde yüksek kalmaya devam ettiğinde, hükümet nihayetinde harcamaları dizginlemek için ciddi baskıyla karşı karşıya kalır veya özel yatırımları dışarıda bırakma riskiyle yüzleşir.
+Kelimeler:
+• elevated = yüksek seviyede
+• rein in = dizginlemek / kontrol altına almak
+• crowding out = dışarıda bırakmak (özel yatırımları baskılamak anlamında)</t>
+      </text>
+    </comment>
+    <comment ref="I114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal bütçe üzerinde artan baskı, Kongre'de tartışmalı mali çıkmazlar ve genel ekonomi genelinde kalıcı yüksek borçlanma maliyetleri beklenmektedir.
+Kelimeler:
+• contentious = tartışmalı / çekişmeli
+• standoffs = çıkmaz / anlaşmazlık</t>
+      </text>
+    </comment>
+    <comment ref="K114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zeka ve teknoloji patlamalarının yönlendirdiği güçlü verimlilik büyümesi, borç servisi maliyetlerini dengelemeye yardımcı olacak daha yüksek vergi gelirleri üretebilir.
+Kelimeler:
+• robust productivity = güçlü verimlilik
+• offset = dengelemek / telafi etmek</t>
+      </text>
+    </comment>
+    <comment ref="N114" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önümüzdeki Hazine tahvili ihale talebi ve yabancı alıcıların ABD egemen borcuna olan iştahı.
+Kelimeler:
+• auction demand = ihale talebi
+• sovereign debt = egemen borç / devlet borcu</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar
+Kelimeler:
+• Global Economy = Küresel Ekonomi</t>
+      </text>
+    </comment>
+    <comment ref="C115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon beklenenden fazla artıyor - fiyatlarda neler oluyor
+Kelimeler:
+• inflation rises = enflasyon yükseliyor</t>
+      </text>
+    </comment>
+    <comment ref="D115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'de enflasyon, yüksek motorlu yakıt maliyetlerinin etkisiyle eylül ayında %3,7'ye yükselirken, toptan eşya fiyatları yıllık bazda %6,3 sıçradı.
+Kelimeler:
+• ticked up = hafifçe yükseldi
+• wholesale prices = toptan eşya fiyatları</t>
+      </text>
+    </comment>
+    <comment ref="E115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+enflasyon patlaması
+Kelimeler:
+• inflation surge = enflasyon dalgası/patlaması</t>
+      </text>
+    </comment>
+    <comment ref="F115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973-1974: 1970'ler enerji krizi
+2021-2022: Pandemi sonrası enflasyon dalgası
+Kelimeler:
+• historical precedents = tarihi emsaller</t>
+      </text>
+    </comment>
+    <comment ref="G115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1973-1974: Merkez bankaları agresif sıkılaştırma döngülerini sürdürmek zorunda kaldı ve 12 ay içinde derin bir küresel resesyon tetiklendi.
+2021-2022: Federal Reserve, talebi soğutmak için takip eden 18 ay içinde faiz oranlarını 500 baz puandan fazla agresif bir şekilde artırdı.
+Kelimeler:
+• tightening cycles = sıkılaştırma döngüleri
+• recession = resesyon / durgunluk</t>
+      </text>
+    </comment>
+    <comment ref="H115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beklenmeyen enerji ve toptan eşya fiyat artışları enflasyonu yeniden hızlandırdığında, merkez bankaları genellikle faiz indirimi beklentilerini askıya alır veya tersine çevirir, bu da piyasa düzeltmelerine yol açar.
+Kelimeler:
+• price spikes = fiyat sıçramaları
+• market corrections = piyasa düzeltmeleri</t>
+      </text>
+    </comment>
+    <comment ref="I115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal Reserve, yapışkan fiyat artışlarıyla mücadele etmek için yüksek faiz oranlarını koruyarak beklenen her türlü parasal gevşemeyi muhtemelen erteleyecektir.
+Kelimeler:
+• monetary easing = parasal gevşeme
+• sticky price growth = yapışkan fiyat artışı</t>
+      </text>
+    </comment>
+    <comment ref="K115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay
+Kelimeler:
+• timeframe = zaman dilimi</t>
+      </text>
+    </comment>
+    <comment ref="L115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek
+Kelimeler:
+• confidence = güvenilirlik</t>
+      </text>
+    </comment>
+    <comment ref="M115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İşgücü piyasaları ve şirket bilançoları şu anda tarihi stagflasyon dönemlerine göre daha dirençlidir.
+Kelimeler:
+• balance sheets = bilançolar
+• stagflation = stagflasyon</t>
+      </text>
+    </comment>
+    <comment ref="N115" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Çekirdek PCE verisi, yaklaşan tüketici harcamaları verileri ve ham petrol arzını etkileyen Orta Doğu'daki gelişmeler.
+Kelimeler:
+• core PCE print = çekirdek PCE verisi
+• crude supply = ham petrol arzı</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi &amp; Piyasalar
+Kelimeler:
+• Markets = Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zeka hisselerindeki satış dalgası derinleşirken Nvidia, AMD ve Micron düştü
+Kelimeler:
+• sell-off = satış dalgası</t>
+      </text>
+    </comment>
+    <comment ref="D116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nvidia, AMD ve Micron dahil olmak üzere küresel teknoloji donanım hisseleri, altyapı harcamaları ve gelecekteki arz fazlasına ilişkin artan yatırımcı kaygısı ortasında derin bir satış dalgasına maruz kaldı.
+Kelimeler:
+• infrastructure spending = altyapı harcamaları
+• oversupply = arz fazlası</t>
+      </text>
+    </comment>
+    <comment ref="E116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+piyasa çöküşü
+Kelimeler:
+• market crash = piyasa çöküşü</t>
+      </text>
+    </comment>
+    <comment ref="F116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000: Dot-com balonunun patlaması
+1995-1996: 1990'lar yarı iletken envanter düzeltmesi
+Kelimeler:
+• dot-com bubble = dot-com balonu</t>
+      </text>
+    </comment>
+    <comment ref="G116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2000: NASDAQ bileşik endeksi, aşırı kapasite donanım sektörünü kasıp kavururken önümüzdeki iki buçuk yıl içinde değerinin neredeyse %78'ini kaybetti.
+1995-1996: Çip üreticisi kâr marjları, talep arzı yakalamadan önce birkaç çeyrek boyunca hızla daraldı.
+Kelimeler:
+• overcapacity = aşırı kapasite
+• margins compressed = marjlar daraldı</t>
+      </text>
+    </comment>
+    <comment ref="H116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihi teknoloji yatırımlarında, yatırımcılar sermaye harcamalarından anında getiri kanıtı talep ettiğinde erken dönem altyapı gözdeleri keskin düzeltmeler yaşar.
+Kelimeler:
+• capital expenditure = sermaye harcaması</t>
+      </text>
+    </comment>
+    <comment ref="I116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yarı iletken ve yapay zeka altyapı hisselerindeki oynaklık, piyasa sürdürülebilir fiyatlandırma gücüne sahip donanım sağlayıcılarını kapasite fazlasına karşı savunmasız olanlardan ayırdıkça devam edecektir.
+Kelimeler:
+• volatility = oynaklık
+• capacity gluts = kapasite fazlalıkları</t>
+      </text>
+    </comment>
+    <comment ref="K116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dot-com döneminin aksine, yapay zeka piyasası liderleri önemli cari gelirler ve nakit akışları yaratarak temel iş modellerinin tamamen çökmesini engelliyor.
+Kelimeler:
+• substantial revenues = önemli gelirler
+• cash flows = nakit akışları</t>
+      </text>
+    </comment>
+    <comment ref="N116" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bulut sermaye harcaması rehberliğini ve kâr marjlarını detaylandıran yaklaşan teknoloji devi kazanç raporları.
+Kelimeler:
+• earnings reports = kazanç raporları
+• profit margins = kâr marjları</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yoro kırmızı kart gördü, Man Utd Atletico Madrid karşısında yenilgiye uğradı
+Kelimeler:
+• sent off = oyundan atılmak (kırmızı kart)</t>
+      </text>
+    </comment>
+    <comment ref="D117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester United'ın galibiyet hasreti, Şampiyonlar Ligi'nde Atletico Madrid'e karşı alınan 2-0'lık yenilginin ardından beş maça çıktı; hemen sonrasında Lisandro Martinez'in kulübü bir sirk olarak nitelendirdiği kamuoyuna yansıyan bir çıkışı geldi.
+Kelimeler:
+• winless run = galibiyetsiz seri
+• public outburst = halka açık çıkış / tepki</t>
+      </text>
+    </comment>
+    <comment ref="E117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+teknik direktörün kovulması</t>
+      </text>
+    </comment>
+    <comment ref="F117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Ole Gunnar Solskjaer'in Manchester United'daki son maçları
+2018: Jose Mourinho' cuyo Manchester United'daki son haftaları</t>
+      </text>
+    </comment>
+    <comment ref="G117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Solskjaer, maç sonu kargaşasından sonraki 48 saat içinde görevden alındı.
+2018: Mourinho, zehirli bir sonuçlar silsilesinin kulübü ilk dörtten uzaklaştırmasının ardından Aralık ayında görevden alındı.
+Kelimeler:
+• dismissed = görevden alınan / kovulan</t>
+      </text>
+    </comment>
+    <comment ref="H117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester United'da son on yıldaki benzer 5 tarihi vakadan 4'ünde, kamuoyuna yansıyan bir oyuncu/teknik direktör krizinin 5 maçlık galibiyetsiz serüvenle birleşmesi, haftalar içinde teknik direktör değişikliğiyle sonuçlanmaktadır.
+Kelimeler:
+• winless run = galibiyetsiz seri
+• managerial dismissal = teknik direktörün görevden alınması</t>
+      </text>
+    </comment>
+    <comment ref="I117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Teknik direktör değişikliği veya ciddi bir iç yapılandırma an meselesidir.
+Kelimeler:
+• imminent = çok yakın, an meselesi</t>
+      </text>
+    </comment>
+    <comment ref="K117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+INEOS yönetimindeki yeni futbol operasyonları liderliği, baskıyı önceki yönetimlere göre daha uzun süre göğüsleyebilir.</t>
+      </text>
+    </comment>
+    <comment ref="N117" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yönetim kurulu güven açıklamaları veya acil durum toplantıları.</t>
+      </text>
+    </comment>
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid, dramatik geç geri dönüşle Roma'yı şoke etti
+Kelimeler:
+• stun = şoke etmek, sarsmak
+• comeback = geri dönüş</t>
+      </text>
+    </comment>
+    <comment ref="D118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid, geri dönen teknik direktör Jose Mourinho yönetimindeki Roma'yı yenmek için son yedi dakikada üç gol atarak bir başka dramatik geç Şampiyonlar Ligi geri dönüşünü tamamladı.
+Kelimeler:
+• comeback = geri dönüş</t>
+      </text>
+    </comment>
+    <comment ref="E118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+geri dönüş galibiyeti
+Kelimeler:
+• comeback = geri dönüş</t>
+      </text>
+    </comment>
+    <comment ref="F118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Real Madrid'in Şampiyonlar Ligi eleme turu geri dönüşleri
+1999: UEFA Şampiyonlar Ligi Finali
+Kelimeler:
+• comeback = geri dönüş</t>
+      </text>
+    </comment>
+    <comment ref="G118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Psikolojik ivme, onları o sezon Şampiyonlar Ligi kupasını kazanmaya kadar taşıdı.
+1999: Saf psikolojik şok, rakibin sezon gidişatını sekteye uğratırken galip gelenleri durdurulamaz bir inanç dalgası üzerinde başlattı.
+Kelimeler:
+• psychological momentum = psikolojik ivme</t>
+      </text>
+    </comment>
+    <comment ref="H118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihi Avrupa kampanyalarında, son dakikalarda imkansız görünen çok gol atan geri dönüşler başaran takımlar, neredeyse her zaman bu psikolojik ivmeyi turnuvanın son aşamalarına kadar taşırlar.
+Kelimeler:
+• comeback = geri dönüş
+• psychological momentum = psikolojik ivme
+• improbable = olasılık dışı, imkansıza yakın</t>
+      </text>
+    </comment>
+    <comment ref="I118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid grubunda liderliği rahatlıkla garantileyecek.</t>
+      </text>
+    </comment>
+    <comment ref="K118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 4 ay</t>
+      </text>
+    </comment>
+    <comment ref="L118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Şampiyonlar Ligi'ndeki lig aşaması formatı, tarihi versiyonlara kıyasla eleme baskısını azaltıyor.</t>
+      </text>
+    </comment>
+    <comment ref="N118" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid'in Avrupa yorgunluğu sonrası yerel ligdeki formu.
+Kelimeler:
+• exertions = harcanan çaba, yorgunluk</t>
       </text>
     </comment>
   </commentList>
@@ -10831,7 +11996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P106"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19903,6 +21068,1193 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>In Kansas, a newly competitive Senate race tests limit of Trump's unpopular policies</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Kansas voters are weighing a competitive Senate race that could send a Democrat to the Senate for the first time in nearly a century amid voter backlash against Trump's policies.</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>midterm swings</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2018: United States midterm elections
+2006: United States midterm elections</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2018: The opposition party flipped the House of Representatives by gaining 41 seats just two years into the presidential term.
+2006: The opposition party gained control of both the House and the Senate.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>In approximately 7 out of 10 midterm elections, the party holding the White House loses congressional seats as voters use the ballot box to register economic or policy grievances.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is likely to face severe headwinds and potential seat losses in historically safe territory as swing voters express regret.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>next month</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Deeply entrenched partisan polarization and localized candidate dynamics could insulate some incumbents in otherwise red states.</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Suburban turnout numbers and late-breaking tracking polls in traditionally safe states.</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/14/nx-s1-5995633/kansas-senate-race-hamilton-marshall-tossup</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_United_States_elections
+https://en.wikipedia.org/wiki/2006_United_States_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>US inflation rises more than expected - here's what is happening with prices</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>US inflation rose more than expected to 3.7% in the year to September, driven by higher motor fuel costs, squeezing American households.</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>oil shocks</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2021-2022: 2021–2023 inflation surge
+1973: 1973 oil crisis</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2021-2022: The central bank aggressively hiked interest rates over the subsequent 18 months, leading to a slowing economy.
+1973: Prolonged stagflation and a severe economic recession persisted through the mid-1970s.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>When inflation figures surprise to the upside close to major political cycles, public dissatisfaction surges and central banks are pressured to maintain restrictive monetary stances.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Persistent price pressures will likely keep borrowing costs elevated and heavily damage the economic approval ratings of the governing party.</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>next 3-6 months</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets remain resilient compared to historical stagflation eras, offering households some buffer against rising expenses.</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Federal Reserve messaging on future interest rate paths and consumer spending reports.</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cwy8lx3pg4k2o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge
+https://en.wikipedia.org/wiki/1973_oil_crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Mass. auditor report calls for repealing state's local liquor licenses caps</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>The Massachusetts state auditor released a report calling for the complete repeal of local liquor license caps, which have historically restricted the growth of restaurants and nightlife in Boston and surrounding municipalities.</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>deregulation</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2006: Massachusetts comprehensive liquor law overhaul
+2017: Illinois reform of liquor license and quota caps in Chicago</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2006: Retailers saw an immediate multi-percentage boost in Sunday revenues within the first six months, overcoming initial local opposition from traditionalists.
+2017: Pushed back heavily by established license holders whose existing licenses held high resale value, leading to a watered-down compromise rather than full repeal.</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>In 3 of 4 similar municipal deregulation battles, auditor-led recommendations for sweeping structural repeal face immense pushback from license incumbents whose permits act as high-value private collateral, resulting in protracted legislative stalemates or piecemeal compromises.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>The state legislature will likely debate the repeal for months, facing intense lobbying from current license holders before passing a heavily modified expansion bill rather than an outright repeal.</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>next 12 to 18 months</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Post-pandemic economic pressures on urban centers and restaurants are more acute than in previous decades, potentially uniting a broader coalition of urban mayors against status-quo protectionism.</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Statements from Boston's municipal leadership and legislative key committee chairs regarding the protection of existing license values.</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQTDZheTFSRXFjbXhPZ3ZLelZRbDFFakJOZlFQdmxEQVdfQ2Fzc0t4cjN4OThSMFhwU1M1cjhmX1FyYmZteTFkbldScU8wUEd6U3RTTVZORGllOVJDWjVYODltVGkySk9ienNfNThITnZ2d1hHaDhTVEFDZ2dxQ2s2eFdFcw?oc=5</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Alcohol_laws_of_Massachusetts
+https://en.wikipedia.org/wiki/List_of_alcohol_laws_of_the_United_States</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Mass. moves to strip licenses from a dozen RegalCare nursing homes</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts regulators have initiated proceedings to strip operating licenses from a dozen nursing homes managed by RegalCare following severe quality and safety violations.</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>license revocation</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2018: Massachusetts Department of Public Health closure of failing long-term care facility
+2020: State crackdowns on troubled nursing home chains during the COVID-19 pandemic</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>2018: Triggered complex, months-long receivership battles where the state had to subsidize temporary operations while finding alternative placements for displaced residents.
+2020: Operators frequently filed emergency legal injunctions to halt license revocation, dragging out the transition of care for up to a year.</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of 5 similar nursing home license revocation actions, corporate operators respond with immediate legal challenges and court injunctions, forcing the state into a prolonged receivership arrangement to ensure continuity of resident care.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>RegalCare will likely challenge the state's actions in court, leading to a court-appointed receivership while residents are gradually relocated or managed under state oversight.</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>State regulators are showing heightened post-pandemic sensitivity and less tolerance for systemic long-term care failures, making voluntary surrender or expedited state receivership more likely than in past decades.</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Court filings for emergency injunctions by RegalCare management and announcements regarding resident relocation plans.</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOeEFuSTc1NkZPRERVd3JfbFhjaTVyY0VOVkJENkFWTXNfdlB2T0Y0M1E4b1ItRlU1eWtNYmpEMzM1R0tXYjVjcnpuSlNfR0d4TWNjeUR3eG9abnVEVTBVOEJ3MThCMHJvb3RUZWtEM1JDOTFUaXhPY2MyQ19tNE43UmhiSUZpczc2U2pDeFQ2c1c?oc=5</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nursing_home_care_in_the_United_States
+https://en.wikipedia.org/wiki/New_York_COVID-19_nursing_home_scandal</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Russia accuses Ukraine of attacking oil refinery after Zelensky says strikes to resume</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine's president announced that a temporary pause on striking energy infrastructure is over following fresh Russian attacks, immediately followed by mutual accusations over a refinery attack.</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>energy infrastructure attacks</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Winter 2022-2023: Russian strikes on Ukrainian energy grid
+Spring 2024: Escalation of Ukrainian drone strikes on Russian refineries</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winter 2022-2023: Ukraine adapted with decentralized power systems and western air defense, while launching retaliatory long-range drone strikes against Russian oil refineries starting in early 2024.
+Spring 2024: </t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Once tacit or temporary pauses on energy infrastructure attacks break down, both sides rapidly escalate deep-strike campaigns against economic targets, leading to sustained fuel supply pressures and heightened regional risk.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Expect an intensified wave of reciprocal long-range drone and missile strikes targeting oil refineries and power grids over the coming months.</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Improved air defense architectures on both sides and greater drone manufacturing capacity change the scale of destruction compared to earlier years.</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Reports of major refinery fires or emergency fuel rationing in the respective regions.</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cqwyrnwd9dw1o?at_medium=RSS&amp;at_campaign=RSS</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Russian_strikes_against_Ukrainian_infrastructure
+https://en.wikipedia.org/wiki/Timeline_of_the_Russo-Ukrainian_war_(8_June_2023_%E2%80%93_31_August_2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>North Korea and China open new bridge after 12-year delay</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>North Korea and China have finally opened a newly constructed cross-border bridge after a protracted 12-year delay, reinforcing trade ties amid international sanctions.</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>infrastructure project opening</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2015: Completion of the New Yalu River Bridge</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>2015: The project stalled indefinitely, highlighting the limits of bilateral economic integration when political and logistical hurdles mount.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Major infrastructure projects between heavily sanctioned states and their primary economic patrons eventually open when economic necessity overrides bureaucratic or political delays, serving to cement asymmetrical economic dependence.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Bilateral trade volume via overland transport routes between China and North Korea is likely to see a steady increase, cushioning Pyongyang against international isolation.</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Deepening military and economic alignment between Pyongyang and Moscow adds a new geopolitical urgency for Beijing to secure its economic influence.</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Customs data indicating increased freight traffic across the new border crossing.</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/ck1exgw3j115o?at_medium=RSS&amp;at_campaign=RSS</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/New_Yalu_River_Bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Surging Inflation Complicates Trump’s Final Push to Sell Voters on Strong Economy</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>A hotter-than-expected September CPI report showed U.S. inflation jumping to 3.7%, driven largely by soaring energy prices, spelling difficult political headwinds for President Trump and GOP candidates just weeks before the midterm elections.</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>inflation surge before midterms</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1974: 1973–1975 recession and inflation spike
+1982: Early 1980s recession</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1974: The incumbent Republican party suffered massive losses in the 1974 midterm elections, losing nearly 50 seats in the House.
+1982: Republicans lost 26 seats in the House during the 1982 midterms, though Senate control was narrowly retained.</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 80% of historical midterm elections occurring during periods of high inflation or rising energy costs, the party holding the White House suffers significant congressional losses.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is expected to face a severe electoral penalty at the ballot box, leading to potential loss of legislative majorities.</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>next 4 weeks</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Voters might isolate economic dissatisfaction from local candidate preferences, or intense partisan polarization could override standard retrospective voting.</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Final weeks of voter polling and turnout metrics in suburban swing districts.</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/14/business/economy/inflation-economy-midterms.html</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973%E2%80%931975_recession
+https://en.wikipedia.org/wiki/Early_1980s_recession_in_the_United_States</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Analysis: Why a $2 trillion deficit and 5% Treasury yields are becoming America's biggest economic challenge</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>As U.S. national debt surpasses $40 trillion alongside persistent $2 trillion annual deficits, 10-year Treasury yields remain stubbornly above 5%, intensifying borrowing costs for both households and the federal government.</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>debt and high bond yields</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2011: United States debt-ceiling crisis
+1985: Gramm–Rudman–Hollings Balanced Budget Act</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>2011: Borrowing costs spiked temporarily and equity markets experienced severe volatility, forcing a prolonged focus on fiscal austerity measures.
+1985: While it failed to immediately balance the budget, it initiated years of intense bipartisan fiscal battles and forced spending caps.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>When 10-year Treasury yields remain elevated above key psychological thresholds amid mounting structural deficits, the government eventually faces severe pressure to rein in spending or risk crowding out private investment.</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Expect heightened pressure on the federal budget, contentious fiscal standoffs in Congress, and sustained high borrowing costs across the broader economy.</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Robust productivity growth driven by artificial intelligence and technology booms could generate higher tax revenues to help offset servicing costs.</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Upcoming Treasury auction demand and foreign buyer appetite for U.S. sovereign debt.</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/15/treasury-yields-deficit-national-debt-ai.html</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2011_United_States_debt-ceiling_crisis
+https://en.wikipedia.org/wiki/Gramm%E2%80%93Rudman%E2%80%93Hollings_Balanced_Budget_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>US inflation rises more than expected - here's what is happening with prices</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>US inflation ticked up to 3.7% in September, driven by higher motor fuel costs, alongside wholesale prices jumping 6.3% annually.</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>inflation surge</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>1973-1974: 1970s energy crisis
+2021-2022: Post-pandemic inflation surge</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1973-1974: Central banks were forced to maintain aggressive tightening cycles, triggering a severe global recession within 12 months.
+2021-2022: The Federal Reserve aggressively hiked interest rates by over 500 basis points over the subsequent 18 months to cool demand.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>When unexpected energy and wholesale price spikes re-accelerate inflation, central banks typically pause or reverse rate-cut expectations, leading to market corrections.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>The Federal Reserve will likely delay any anticipated monetary easing, maintaining higher interest rates to combat sticky price growth.</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Labor markets and corporate balance sheets are currently more resilient than in historical stagflation periods.</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Core PCE print, upcoming consumer spending data, and Middle East developments affecting crude supply.</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cwy8lx3pg4k2o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1973_oil_crisis
+https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia, AMD, Micron fall as AI stock sell-off deepens</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Global technology hardware stocks, including Nvidia, AMD, and Micron, suffered a deep sell-off amid growing investor anxiety over infrastructure spending and future oversupply.</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>market crash</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2000: Dot-com bubble burst
+1995-1996: 1990s semiconductor inventory correction</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>2000: The NASDAQ composite lost nearly 78% of its value over the next two and a half years as overcapacity plagued the hardware sector.
+1995-1996: Chip maker margins compressed rapidly for several quarters before demand caught up with supply.</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>In historical technology build-outs, early infrastructure darlings experience sharp corrections when investors demand proof of immediate returns on capital expenditure.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Volatility in semiconductor and AI infrastructure stocks will persist as the market separates hardware providers with sustained pricing power from those vulnerable to capacity gluts.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Unlike the dot-com era, AI market leaders generate substantial current revenues and cash flows, preventing a total collapse of the underlying business models.</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Upcoming tech giant earnings reports detailing cloud capital expenditure guidance and profit margins.</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/15/sk-hynix-samsung-softbank-stocks-asia-tech-rout-ai-funding-worries.html</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Dot-com_bubble
+https://en.wikipedia.org/wiki/List_of_recessions_in_the_United_States</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Yoro sent off as Man Utd stumble to defeat against Atletico Madrid</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Manchester United's winless run stretches to five matches after a 2-0 defeat to Atletico Madrid in the Champions League, followed by a public outburst from Lisandro Martinez calling the club a circus.</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>manager sacked</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2021: Ole Gunnar Solskjaer's final matches at Manchester United
+2018: Jose Mourinho's final weeks at Manchester United</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>2021: Solskjaer was sacked within 48 hours of the post-match fallout.
+2018: Mourinho was dismissed in December after a toxic sequence of results left the club adrift from the top four.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>In 4 of 5 similar historical cases at Manchester United over the last decade, a public player/manager crisis combined with a 5-match winless run results in a managerial dismissal within weeks.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Managerial change or severe internal restructuring is imminent.</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>New football operations leadership under INEOS might absorb the pressure longer than previous regimes.</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Boardroom statements of confidence or emergency emergency meetings.</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/videos/c6pq0rg10xp1o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ole_Gunnar_Solskj%C3%A6r
+https://en.wikipedia.org/wiki/Jos%C3%A9_Mourinho</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid stun Roma after dramatic late comeback</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid complete another dramatic late Champions League comeback, scoring three goals in the final seven minutes to beat Roma under returning manager Jose Mourinho.</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>comeback win</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2022: Real Madrid's Champions League knockout comebacks
+1999: UEFA Champions League Final</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>2022: The psychological momentum carried them all the way to winning the Champions League trophy that season.
+1999: The sheer psychological shock crippled the opponent's season trajectory while launching the winners on an unstoppable wave of belief.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>In historic European campaigns, teams that pull off improbable multi-goal comebacks in the final minutes almost always ride that psychological momentum deep into the latter stages of the tournament.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid will secure top spot in their group comfortably.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>next 4 months</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>The league phase format in the modern Champions League reduces knockout pressure compared to historic iterations.</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid's domestic form following European exertions.</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/videos/cmx239x97ddvo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2021%E2%80%9322_UEFA_Champions_League
+https://en.wikipedia.org/wiki/1999_UEFA_Champions_League_final</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Musk says US government may be behind slowdown of Ukraine drone speeds</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Elon Musk suggested the US government might be involved in limiting Starlink drone speeds for Ukraine, highlighting the vulnerabilities of relying on commercial private infrastructure for military operations.</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>private infrastructure throttling in wartime</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2022-2023: Starlink outages and geofencing restrictions in Ukraine
+1939-1945: IT&amp;T and commercial communications during World War II</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>2022-2023: Ukrainian forces suffered temporary communication blackouts during critical counteroffensives, forcing Kyiv to scramble for alternative military communication redundancies within months.
+1939-1945: National governments eventually exerted direct requisition powers or built state-owned redundancies to avoid relying on private entities with cross-border dependencies.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>When militaries rely heavily on commercial, privately owned dual-use technology, disputes over sovereignty, liability, and strategic control inevitably lead to service throttling or political friction.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Ukraine will aggressively seek state-backed or diversified alternative satellite networks to reduce its single-point vulnerability to SpaceX and US regulatory pressure.</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>The sheer scale and monopoly-like dominance of low-earth-orbit megaconstellations leaves far fewer immediate technological alternatives than in past conflicts.</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Announcements of defense contracts between Ukraine or European allies and alternative satellite operators like OneWeb or IRIS^2.</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c8wy9veedgygo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Starlink_in_the_Russo-Ukrainian_war
+https://en.wikipedia.org/wiki/ITT_Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Scientists may have overlooked a hidden Alzheimer's culprit for decades</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>New scientific revelations suggest researchers may have spent decades overfocusing on amyloid-beta plaques in Alzheimer's disease while missing alternative driving mechanisms.</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>paradigm shift in medical research</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1984-2010s: The dominance of the amyloid hypothesis in Alzheimer's research
+1980s-1990s: The gastric ulcer paradigm shift regarding Helicobacter pylori</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1984-2010s: High-profile drug failures forced a painful diversification of research into tau proteins, neuroinflammation, and metabolic factors by the early 2020s.
+1980s-1990s: Once the bacterial cause was accepted and treated with antibiotics, ulcers shifted from a chronic, lifelong managed condition to a easily curable disease within a decade.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>When a multi-decade medical consensus around a single disease mechanism begins to fracture under repeated clinical trial failures, funding and research efforts rapidly splinter into multi-target approaches.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Major pharmaceutical firms will begin reallocating capital away from pure amyloid-targeting therapies toward combination treatments and alternative inflammatory or metabolic pathways.</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>next 1-2 years</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Advanced AI-driven biomarker discovery tools allow researchers to test non-amyloid pathways far more rapidly than during previous decades of trial and error.</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Major shifts in venture capital allocation and clinical trial pipelines toward non-amyloid biomarkers.</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261013015838.htm</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Biochemistry_of_Alzheimer's_disease
+https://en.wikipedia.org/wiki/Helicobacter_pylori</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -11701,6 +11701,178 @@
 Real Madrid'in Avrupa yorgunluğu sonrası yerel ligdeki formu.
 Kelimeler:
 • exertions = harcanan çaba, yorgunluk</t>
+      </text>
+    </comment>
+    <comment ref="B121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'te şahsen erken oy verme Cumartesi günü başlıyor</t>
+      </text>
+    </comment>
+    <comment ref="D121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 seçimi için şahsen erken oy verme süreci Massachusetts genelinde Cumartesi günü başlıyor ve seçmenler Kasım ayı öncesinde sandık başına giderken yoğun ilgi görüyor.
+Kelimeler:
+• kicks off = başlıyor, start alıyor
+• polls = sandıklar, anketler</t>
+      </text>
+    </comment>
+    <comment ref="E121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+erken oy vermenin başlaması</t>
+      </text>
+    </comment>
+    <comment ref="F121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2022: Massachusetts 2022 ara seçimleri erken oy verme süreci
+Kasım 2020: Massachusetts 2020 genel seçimi erken oy verme süreci</t>
+      </text>
+    </comment>
+    <comment ref="G121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2022: Yüksek erken katılım, kullanılan toplam oy için daha yüksek bir taban oluşturarak seçim günü yığılmalarını azalttı.
+Kasım 2020: Tüm oyların yarısından fazlası seçim gününden önce kullanıldı ve seçmen alışkanlıklarını kalıcı olarak erken katılım yönüne kaydırdı.
+Kelimeler:
+• turnout = katılım oranı
+• bottlenecks = tıkanıklıklar, yığılmalar</t>
+      </text>
+    </comment>
+    <comment ref="H121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'te şahsen erken oy verme süreci açıldığında, tarihsel eğilimler toplam seçmen kitlesinin yaklaşık %30 ila %50'sinin oylarını seçim gününden önce kullandığını ve katılımı büyük ölçüde öne çektiğini gösteriyor.
+Kelimeler:
+• turnout = katılım oranı
+• electorate = seçmen kitlesi
+• front-loading = öne çekme, ağırlığı başa verme</t>
+      </text>
+    </comment>
+    <comment ref="I121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Commonwealth genelindeki erken oy verme merkezlerinde güçlü hafta sonu katılım oranları bekleniyor, bu da Kasım ara seçimleri için genel katılım oranının yüksek olacağını gösteriyor.
+Kelimeler:
+• turnout = katılım oranı</t>
+      </text>
+    </comment>
+    <comment ref="K121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Açılış hafta sonu için hava tahminleri ve belirli yüksek profilli yerel oy pusulası soruları, erken katılımı önceki ara seçim döngülerinden bile daha hızlı hızlandırabilir.
+Kelimeler:
+• turnout = katılım oranı</t>
+      </text>
+    </comment>
+    <comment ref="N121" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bu hafta sonu Boston ve büyük banliyö belediyelerindeki erken oy verme uydu merkezlerinde uzun kuyruklar.</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston Globe soruşturmasının ardından Massachusetts, RegalCare huzurevlerinin lisanslarını iptal etmek için harekete geçti
+Kelimeler:
+• revoke = iptal etmek, hükümsüz kılmak</t>
+      </text>
+    </comment>
+    <comment ref="D122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts düzenleyicileri, Boston Globe'un ciddi bakım eksikliklerini ayrıntılı olarak anlatan araştırmacı raporunun ardından RegalCare huzurevlerinin lisanslarını iptal etmek için süreç başlattı.
+Kelimeler:
+• revoke = iptal etmek, hükümsüz kılmak
+• deficiencies = eksiklikler</t>
+      </text>
+    </comment>
+    <comment ref="E122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+düzenleyici lisans iptali</t>
+      </text>
+    </comment>
+    <comment ref="F122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Salutaris Tıp Merkezi ve yerel huzurevi baskıları</t>
+      </text>
+    </comment>
+    <comment ref="G122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Tesisler genellikle uzun süreli yasal temyiz süreçlerine girerken, devlet tarafından atanan kayyumlar ani kapanmaları önlemek için günlük hasta bakımını denetlemek üzere devreye girdi.
+Kelimeler:
+• receivers = kayyumlar
+• abrupt = ani, beklenmedik</t>
+      </text>
+    </comment>
+    <comment ref="H122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts düzenleyicilerinin araştırma haberleri nedeniyle sağlık tesislerinin acil lisans iptallerini takip ettiği geçmiş vakalarda, işletmeciler yönetimi devrederken veya anlaşma müzakere ederken neredeyse istisnasız bir şekilde acil ihtiyati tedbir kararları için başvuruda bulundu.
+Kelimeler:
+• injunctions = ihtiyati tedbir kararları</t>
+      </text>
+    </comment>
+    <comment ref="I122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+RegalCare muhtemelen iptale yasal olarak itiraz edecek ve eyalet sağlık yetkilileri sakinlerin yerleştirilmesinin istikrarlı kalmasını sağlamak için çalışırken karmaşık bir idari mücadeleyi tetikleyecektir.</t>
+      </text>
+    </comment>
+    <comment ref="K122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2-4 ay</t>
+      </text>
+    </comment>
+    <comment ref="L122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek profilli bir Boston Globe soruşturmasından gelen doğrudan baskı, düzenleyicilere somut yapısal değişiklikler olmaksızın sessizce anlaşma yapmaları için çok az siyasi alan bırakıyor.
+Kelimeler:
+• demonstrable = gösterilebilir, somut</t>
+      </text>
+    </comment>
+    <comment ref="N122" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tesis işletmecileri tarafından eyalet mahkemesinde geçici uzaklaştırma kararları için yapılan başvurular ve Massachusetts Halk Sağlığı Departmanından acil açıklamalar.</t>
       </text>
     </comment>
   </commentList>
@@ -11996,7 +12168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22255,6 +22427,173 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>In-person early voting begins Saturday in Massachusetts</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>In-person early voting for the 2026 election kicks off across Massachusetts on Saturday, drawing heavy interest as voters head to the polls ahead of November.</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>early voting start</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>November 2022: Massachusetts 2022 midterm elections early voting
+November 2020: Massachusetts 2020 general election early voting</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>November 2022: High early turnout established a higher baseline of total votes cast, reducing election-day bottlenecks.
+November 2020: Over half of all ballots were cast before election day, permanently shifting voter habits toward early participation.</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>When in-person early voting opens in Massachusetts, historical trends show that roughly 30% to 50% of the total electorate casts their ballots prior to election day, heavily front-loading turnout.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Expect strong weekend turnouts at early voting locations across the Commonwealth, setting up a high overall participation rate for the November midterms.</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Weather forecasts for the opening weekend and specific high-profile local ballot questions could accelerate early turnout even faster than previous midterm cycles.</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Long lines at early voting satellite locations across Boston and major suburban municipalities this weekend.</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOUHJnMi14ZEFmVWFPdlluaThMbjBxQ2Q1SDhSVGxOd3A5amVzWlJLd0RpX0JpWEZWWWZSbjYzTGdxeEpUdElkMDdIbU44MWJ5NktzeDBoVU96SFZuZy03NEYySnBiYjdiUmdSd3FHazZfVDRvd0J5VVFkYUM3QkVmbDNFbEpqZVNDQkIzSXQ1eE1ydk1ITDRsZzFUMFdTeE1SNFplSWxMbk5kYmhmWW8zaVMtSVJlRUlaeXZ3RdIB0AFBVV95cUxNZ3VJVDRncVYyZTQweGcwYVRacW1meVJEN1JYUFY2ejd6TmtucDdxSHlpWk4zbVQ0NGVuXzFjQnJLYUtKMkVNczF6d04xUWxNUGZTYmlSN25paDhuU0xTOXZQUXRPTDl0WjZqYUxsNzBiN0JMVHp4NFBNdW5ucnpXVVZ6QmNCbzU5SXJXVUVqZGtOVW1Xb3lsRFFjcjlwekVXSWY1SDZUSHprNk12NXcyLUM0LXJINHMwbGRuWnZtWFVSdEcwTUtublNrclJIZXls?oc=5</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022_United_States_gubernatorial_elections
+https://en.wikipedia.org/wiki/2020_United_States_presidential_election_in_Massachusetts</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Mass. moves to revoke RegalCare nursing home licenses after Boston Globe investigation</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts regulators have initiated proceedings to revoke the licenses of RegalCare nursing homes following an investigative report by the Boston Globe detailing severe care deficiencies.</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>regulatory license revocation</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2018: Salutaris Medical Center and local nursing home clampdowns</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>2018: Facilities typically entered prolonged legal appeals while state-appointed receivers stepped in to oversee daily patient care to prevent abrupt closures.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>In past cases where Massachusetts regulators pursued emergency license revocations of health care facilities due to investigative exposés, the operators almost universally filed emergency injunctions while transitioning management or negotiating settlements.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>RegalCare will likely challenge the revocation legally, triggering a complex administrative battle while state health officials work to ensure resident placement remains stable.</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>next 2-4 months</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>The direct pressure from a high-profile Boston Globe investigation leaves regulators very little political room to settle quietly without demonstrable structural changes.</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Filings in state court for temporary restraining orders by facility operators and emergency statements from the Massachusetts Department of Public Health.</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOMDI5MXp0QjhaNW4yWUtCelBrY0JvNHVnXzBYTFpxOFlMYWdkLU5ISmMxZXhiZ1FwVFdTSXE2emRiRkhob2lFejhsTl9wUldyQk5pWURUTnVMVGRUdjlpM0V4bTFWM0xBTW1rRXM3R2J2M0c1alhlVUNZcnpSLTA3OEV1dmhPbkt0cWtxejhvTDExeklGVkdKZ2RQOEpPQlJJdW1DZEZzTUxmSFlGZzFmZFZ3ZHB2Y0FsNkMwQUtpMTNuLXdJTkp6VE9DZWVUaS1Nbmc?oc=5</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nursing_Home_Reform_Act</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -11873,6 +11873,1606 @@
       <text>
         <t>Türkçe:
 Tesis işletmecileri tarafından eyalet mahkemesinde geçici uzaklaştırma kararları için yapılan başvurular ve Massachusetts Halk Sağlığı Departmanından acil açıklamalar.</t>
+      </text>
+    </comment>
+    <comment ref="B123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, ara seçim seyahat atağını koyu cumhuriyetçi eyaletlere kaydırıyor
+Kelimeler:
+• shifts = kaydırmak, yönünü değiştirmek
+• midterm = ara seçim
+• travel blitz = yoğun seyahat atağı/seferi
+• deep-red states = koyu cumhuriyetçi (muhafazakâr) eyaletler</t>
+      </text>
+    </comment>
+    <comment ref="D123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Donald Trump'ın son kampanya seyahat programı, çekişmeli kararsız bölgelerden uzaklaşarak 2024'te kolayca kazandığı muhafazakâr eyaletlere yöneldi. Bu eksen kayması, Cumhuriyetçi kampanya stratejistlerinin kritik sandalyeler için mücadele etmek yerine taban katılımını korumak adına savunmaya geçtiğini gösteriyor.
+Kelimeler:
+• itinerary = seyahat programı/güzergâhı
+• competitive swing districts = rekabetin yüksek olduğu kararsız seçim bölgeleri
+• carried easily = kolayca kazandığı
+• pivot = eksen kayması, yön değiştirme
+• playing defense = savunmada kalmak, savunma oynamak
+• base turnout = taban seçmenin sandığa gitme oranı
+• battleground seats = kilit/çekişmeli milletvekilliği sandalyeleri</t>
+      </text>
+    </comment>
+    <comment ref="E123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçim kampanyasında savunma odaklı kayma
+Kelimeler:
+• defensive shift = savunma odaklı kayma/değişiklik</t>
+      </text>
+    </comment>
+    <comment ref="F123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2018: Trump'ın 2018 ara seçim mitinglerinde cumhuriyetçi eyaletlere odaklanması
+Ekim 2006: George W. Bush'un 2006 yılındaki savunma odaklı kampanya turu
+Kelimeler:
+• rally focus = miting odağı
+• defensive campaign tour = savunma amaçlı kampanya turu</t>
+      </text>
+    </comment>
+    <comment ref="G123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2018: Cumhuriyetçiler muhafazakâr eyaletlerde Senato'da iki sandalye kazanmayı başarsa da, Temsilciler Meclisi'nde net 40 sandalye kaybederek 3 hafta içinde gerçekleşen bir ara seçim uyarısıyla çoğunluğu yitirdi.
+Ekim 2006: İktidardaki Cumhuriyetçi Parti, Kasım 2006'da hem Temsilciler Meclisi'ndeki (-30 sandalye) hem de Senato'daki (-6 sandalye) çoğunluğunu kaybetti.
+Kelimeler:
+• managed to gain = kazanmayı başarmak
+• suffered a net loss = net kayba uğramak
+• rebuke = kınama, paylama, ters tepki/uyarı
+• governing party = iktidar partisi</t>
+      </text>
+    </comment>
+    <comment ref="H123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern ara seçimlerde (1994, 2006, 2010 ve 2018 dâhil), görevdeki bir başkan ekim ayında kararsız bölgelerden güvenli taban eyaletlerine çekildiğinde, başkanın partisi vakaların %80'inden fazlasında Temsilciler Meclisi'nin kontrolünü kaybetmiştir.
+Kelimeler:
+• incumbent president = görevdeki başkan
+• retreats = geri çekilmek
+• safe base states = güvenli taban eyaletleri
+• lost control of = kontrolünü kaybetmek</t>
+      </text>
+    </comment>
+    <comment ref="I123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Savunma amaçlı seyahatlerin kritik banliyö bölgelerinde iç anketlerin çöktüğünü doğrulaması sebebiyle, iktidar partisinin Temsilciler Meclisi'nin kontrolünü kaybetmesi veya ağır sandalye kayıpları yaşaması kuvvetle muhtemeldir.
+Kelimeler:
+• highly likely = kuvvetle muhtemel
+• severe seat losses = ciddi/ağır sandalye kayıpları
+• internal polling collapse = iç anketlerdeki çöküş
+• suburban districts = banliyö seçim bölgeleri</t>
+      </text>
+    </comment>
+    <comment ref="K123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Artan ulusal siyasi kutuplaşma ve partizan çıkarlara göre çizilmiş seçim bölgesi haritaları, gerçekten çekişmeli olan kararsız bölgelerin sayısını azalttı; bu da geçmişteki büyük oy dalgalanmalarına kıyasla el değiştiren toplam sandalye sayısını sınırlandırabilir.
+Kelimeler:
+• heightened polarization = tırmanan/artan kutuplaşma
+• gerrymandered district maps = seçim bölgelerinin hileli/partizan şekilde yeniden çizilmiş haritaları
+• cap = üst sınır koymak, sınırlamak
+• seat flips = sandalyelerin el değiştirmesi
+• wave elections = tek bir partinin ezici üstünlük sağladığı dalga seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="N123" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ulusal parti komitelerinin marjinal bölgelerdeki reklam rezervasyonlarını geri çekip fonları daha önce güvenli görülen cumhuriyetçi sandalyelere yeniden tahsis etmesi.
+Kelimeler:
+• pulling ad reservations = reklam rezervasyonlarını geri çekmek
+• marginal districts = bıçak sırtı/marjinal seçim bölgeleri
+• reallocate funds = fonları yeniden tahsis etmek</t>
+      </text>
+    </comment>
+    <comment ref="B124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, Rusya'ya yönelik Kongre yaptırımlarını askıya alan kararı imzaladı
+Kelimeler:
+• waiving = feragat etmek, muaf tutmak, askıya almak
+• sanctions = yaptırımlar
+• executive order = başkanlık kararnamesi</t>
+      </text>
+    </comment>
+    <comment ref="D124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Trump, ulusal güvenlik yasası kapsamında Moskova'ya karşı yürürlüğe konan yasal yaptırımlardan muafiyet sağlayan bir başkanlık kararnamesi imzalayarak Ukrayna ihtilafı üzerinden yaşanan gerilimin ortasında yürütme organı ile Kongre arasındaki çatışmayı tırmandırdı.
+Kelimeler:
+• statutory sanctions = kanuni/yasal yaptırımlar
+• escalating a clash = çatışmayı tırmandırmak
+• executive branch = yürütme organı
+• tensions = gerilimler</t>
+      </text>
+    </comment>
+    <comment ref="E124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+başkanlık yaptırım muafiyeti
+Kelimeler:
+• waiver = muafiyet, feragat</t>
+      </text>
+    </comment>
+    <comment ref="F124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017–2019: CAATSA'nın imzalanması ve yaptırımların hafifletilmesi anlaşmazlığı
+1984–1986: Yürütmenin Boland Değişikliği'nin etrafından dolaşması
+Kelimeler:
+• dispute = anlaşmazlık, ihtilaf
+• circumvention = arkasından dolaşma, kanunu bertaraf etme</t>
+      </text>
+    </comment>
+    <comment ref="G124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2017–2019: Aylar içinde Kongre'deki iki partili çoğunluk, ret kararları sundu ve gelecekteki başkanlık muafiyeti esnekliğini kısıtlamak amacıyla devam tasarıları hazırladı.
+1984–1986: Sürtüşme 1987'de Iran-Contra oturumları, büyük Kongre soruşturmaları ve yasama denetiminin kanunla sıkılaştırılmasıyla zirveye ulaştı.
+Kelimeler:
+• bipartisan majorities = iki partili çoğunluklar
+• resolutions of disapproval = ret/kınama kararları
+• friction = sürtüşme, gerginlik
+• legislative oversight = yasama organı denetimi</t>
+      </text>
+    </comment>
+    <comment ref="H124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir başkan, iki partinin desteğiyle çıkarılmış yasal dış politika direktiflerini devre dışı bırakmak için geniş kapsamlı ulusal güvenlik muafiyetlerini devreye soktuğunda, Kongre geçmişteki anlaşmazlıkların yaklaşık 10'da 7'sinde yasal düzenlemelerle veya denetim oturumlarıyla misilleme yapmıştır.
+Kelimeler:
+• executes broad waivers = geniş muafiyetleri yürürlüğe koymak/kullanmak
+• bypass = baypas etmek, devre dışı bırakmak
+• mandates = yasal direktifler/talimatlar
+• retaliates = misilleme yapmak
+• oversight hearings = denetim oturumları/soruşturmaları</t>
+      </text>
+    </comment>
+    <comment ref="I124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato ve Temsilciler Meclisi'ndeki iki partili liderlik, resmî ret kararları sunacak veya yaklaşan ulusal savunma ve bütçe harcama yasalarına muafiyet tanınamaz zorunlu yaptırım maddeleri ekleyecektir.
+Kelimeler:
+• file formal resolutions = resmî karar tasarıları sunmak
+• attach = eklemek, iliştirmek
+• mandatory non-waivable clauses = feragat edilemez/muafiyet tanınamaz zorunlu maddeler
+• spending legislation = bütçe harcama yasası</t>
+      </text>
+    </comment>
+    <comment ref="K124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ara seçim sonrası Kongre Beyaz Saray ile daha sıkı bir parti çizgisi uyumu sergilerse, parti liderliği aksi takdirde iki partili destekle geçebilecek ret kararlarının genel kurulda oylanmasını engelleyebilir.
+Kelimeler:
+• party-line alignment = parti çizgisine göre hizalanma/uyum
+• block floor votes = genel kurul oylamalarını engellemek</t>
+      </text>
+    </comment>
+    <comment ref="N124" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dış ilişkiler komitesi başkanlarının ortak kınamaları ve Ulusal Acil Durumlar Yasası kapsamında imtiyazlı bir ret kararının sunulması.
+Kelimeler:
+• joint rebukes = ortak kınamalar/uyarılar
+• foreign relations committee chairs = dış ilişkiler komitesi başkanları
+• privileged resolution = öncelikli/imtiyazlı karar tasarısı</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal yetkililer, Massachusetts'taki siyasi ve seçim ofislerine gönderilen şüpheli mektupları soruşturuyor
+Kelimeler:
+• probe = derinlemesine incelemek, soruşturmak
+• suspicious = şüpheli
+• authorities = resmi yetkililer</t>
+      </text>
+    </comment>
+    <comment ref="D125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal ve eyalet kolluk kuvvetleri, Kasım seçimlerine sadece haftalar kala Massachusetts genelinde en az altı seçilmiş yetkili ve seçim ofisine tanımlanamayan tozlar içeren şüpheli mektuplar ulaşmasının ardından soruşturma başlattı.
+Kelimeler:
+• law enforcement agencies = kolluk kuvvetleri / güvenlik birimleri
+• launched an investigation = soruşturma başlattı
+• elected officials = seçilmiş yetkililer
+• unidentified = tanımlanamayan, kimliği belirsiz</t>
+      </text>
+    </comment>
+    <comment ref="E125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+posta yoluyla tehdit</t>
+      </text>
+    </comment>
+    <comment ref="F125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2024: 15'ten fazla eyaletteki seçim yetkililerine gönderilen şüpheli postalar
+Nisan 2013: 2013 risin mektupları
+Eylül–Ekim 2001: 2001 şarbon saldırıları
+Kelimeler:
+• ricin = risin (ölümcül bir biyolojik toksin)
+• anthrax = şarbon</t>
+      </text>
+    </comment>
+    <comment ref="G125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2024: Posta denetim ekipleri ve FBI gönderileri ele geçirdi, tesisleri 48 ila 72 saat içinde temizleyip kullanıma açtı, maddelerin zararsız tahriş ediciler veya asılsız ihbarlar olduğunu doğruladı ve gelişmiş tehlikeli madde posta tarama protokollerini devreye soktu.
+Nisan 2013: Posta kontrol tesisleri toksini teslimattan önce tespit etti ve FBI fail James Everett Dutschke'yi iki hafta içinde yakaladı.
+Eylül–Ekim 2001: Saldırılar, Birleşik Devletler Posta Servisi ve kongre posta dağıtımı genelinde büyük çaplı, kalıcı tarama reformlarını tetikledi.
+Kelimeler:
+• intercepted = yolunu kesti, ele geçirip durdurdu
+• harmless irritants = zararsız tahriş edici maddeler
+• hoaxes = asılsız ihbarlar, aldatmacalar
+• instituted = yürürlüğe koydu, başlattı
+• hazmat = tehlikeli madde (hazardous materials kısaltması)
+• perpetrator = fail, suçu işleyen kişi</t>
+      </text>
+    </comment>
+    <comment ref="H125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2001'den bu yana yaşanan siyasi beyaz toz posta korkularının %90'ından fazlasında maddeler ölümcül biyolojik ajanlar için negatif sonuç vermiştir ve psikolojik taciz amacı taşımaktadır; federal müfettişler genellikle şüphelileri 3 ila 12 hafta içinde tespit etmek için posta damgalarını, kağıt türünü ve dijital izleri takip eder.
+Kelimeler:
+• mail scares = posta kaynaklı panik/korku vakaları
+• lethal biological agents = ölümcül biyolojik ajanlar
+• psychological harassment = psikolojik taciz / yıldırma
+• trace = izini sürmek, tespit etmek
+• postmarks = posta damgaları
+• paper stock = kullanılan kağıt cinsi</t>
+      </text>
+    </comment>
+    <comment ref="I125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Maddelerin ölümcül olmadığı belirlenecektir (örneğin nişasta, kabartma tozu veya düşük dereceli tahriş ediciler); bu durum posta işleme süreçlerinde geçici aksamalara ve seçim tesislerinde daha sıkı taramalara yol açacak olsa da erken oylama takvimleri ertelenmeden devam edecektir.
+Kelimeler:
+• non-lethal = ölümcül olmayan
+• prompting = yol açan, tetikleyen
+• mail-handling disruptions = posta işleme ve dağıtım aksamaları
+• tightened screening = sıkılaştırılmış denetim/tarama
+• postponement = erteleme</t>
+      </text>
+    </comment>
+    <comment ref="K125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 4 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern kimyasal iz sürme yöntemleri standart aldatmaca malzemeleri yerine toksik yeni sentetik bileşikler veya fentanil tespit ederse, tesis kapatmaları uzayabilir ve federal koruma birimleri harekete geçirilebilir.
+Kelimeler:
+• chemical tracing = kimyasal iz sürme ve analiz
+• novel synthetic compounds = yeni üretilmiş sentetik bileşikler
+• prolonged = süresi uzatılmış, uzun süren
+• protection details = koruma ekipleri / güvenlik heyeti
+• mobilized = harekete geçirilmiş, seferber edilmiş</t>
+      </text>
+    </comment>
+    <comment ref="N125" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts Eyalet Polisi Kriminal Laboratuvarı'ndan gelecek ön tehlikeli madde laboratuvar testi sonuçları ve FBI Ortak Terörizm Görev Gücü'nün posta damgalarının çok eyaletli gönderilerle eşleşip eşleşmediğine dair açıklamaları.
+Kelimeler:
+• preliminary = ön, ilk aşamadaki
+• hazardous material = tehlikeli madde
+• crime laboratory = kriminal laboratuvarı
+• task force = özel görev gücü</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ülke Geneli)</t>
+      </text>
+    </comment>
+    <comment ref="C126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts, Batı-Doğu Demiryolu genişletmesi için 130 milyon dolarlık federal hibe sağladı
+Kelimeler:
+• secures = temin etmek, sağlamak
+• grant = hibe, karşılıksız mali destek
+• expansion = genişleme, büyütme</t>
+      </text>
+    </comment>
+    <comment ref="D126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Federal yetkililer, Springfield, Worcester ve Boston arasındaki ön hat, istasyon ve sinyalizasyon iyileştirmelerini finanse ederek Batı-Doğu Demiryolu projesini ilerletmek amacıyla Massachusetts'e 130 milyon dolar tahsis etti.
+Kelimeler:
+• awarded = tahsis etti, hibe etti
+• advance = ilerletmek, geliştirmek
+• preliminary track = ön demiryolu hattı
+• signaling upgrades = sinyalizasyon modernizasyonu/iyileştirmeleri</t>
+      </text>
+    </comment>
+    <comment ref="E126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yolcu demiryolu genişletme hibesi</t>
+      </text>
+    </comment>
+    <comment ref="F126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1990–2024: South Coast Demiryolu projesi
+2006–2022: Green Line Uzatması</t>
+      </text>
+    </comment>
+    <comment ref="G126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1990–2024: Proje; 30 yılı aşkın çevresel incelemelere, güzergah yeniden tasarımlarına ve finansman açıklarına maruz kalarak maliyeti 3 milyar doların üzerine çıkardı ve ilk ticari seferleri onlarca yıl geciktirdi.
+2006–2022: Proje, 1 milyar doları aşan devasa maliyet aşımlarıyla karşılaştı; bu da kapsamlı bir proje revizyonunu, yüklenici değişimlerini ve orijinal açılış hedefinin beş yıl aşılmasına neden olan bir gecikmeyi tetikledi.
+Kelimeler:
+• endured = katlandı, maruz kaldı
+• funding shortfalls = finansman açıkları
+• inflating the price tag = maliyeti şişirerek
+• initial revenue service = ilk ticari/ücretli yolcu seferi
+• cost overruns = maliyet aşımları
+• contractor replacements = müteahhit/yüklenici değişimleri</t>
+      </text>
+    </comment>
+    <comment ref="H126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'taki büyük demiryolu genişletmeleri tarihsel olarak önemli maliyet revizyonları ve takvim kaymaları yaşar; son 30 yıldaki büyük eyalet toplu taşıma girişimlerinin tamamında, koridor genişletme projeleri tamamlanmadan önce ilk hibe ödeneklerinin ötesinde ek eyalet bütçe tahsisatları gerektirmiştir.
+Kelimeler:
+• timeline slippage = takvimde kayma, gecikme
+• transit initiatives = toplu taşıma girişimleri
+• corridor expansion = ulaşım koridoru/hattı genişletmesi
+• supplemental state appropriations = ek eyalet bütçe ödenekleri
+• initial grant envelopes = başlangıçtaki hibe bütçe limitleri</t>
+      </text>
+    </comment>
+    <comment ref="I126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+130 milyon dolarlık hibe, Springfield ve Palmer civarındaki ilk ön mühendislik ve erken altyapı çalışmalarını karşılayacak; ancak toplam proje maliyetleri mevcut tahminlerin oldukça üzerine çıkarak seferler başlamadan önce ilave federal dilimler ve eyalet tahvil paketleri gerektirecektir.
+Kelimeler:
+• preliminary engineering = ön mühendislik çalışmaları
+• expand well beyond = oldukça ötesine geçmek/büyümek
+• estimates = tahminler, öngörüler
+• federal tranches = federal fon/ödenek dilimleri
+• commences = başlamak</t>
+      </text>
+    </comment>
+    <comment ref="K126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Batı-Doğu Demiryolu, sıfırdan yeni hat güzergahları edinmek yerine CSX mülkiyetindeki mevcut yük treni geçiş haklarını kullandığı için, yük treni işletim anlaşmaları sorunsuz tamamlandığı takdirde izin süreçlerindeki gecikmeler daha az olabilir.
+Kelimeler:
+• freight rights-of-way = yük treni geçiş/kullanım hakları
+• greenfield alignments = sıfırdan (işlenmemiş arazide) açılan güzergahlar
+• permitting delays = izin ve ruhsat gecikmeleri
+• dispatch agreements = tren trafiği işletim/sevk anlaşmaları
+• smoothly = sorunsuzca, pürüzsüz biçimde</t>
+      </text>
+    </comment>
+    <comment ref="N126" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yük taşımacılığı operatörü CSX Transportation ile geçiş hakkı sevk ve işletim yetkileri üzerine yapılacak müzakereler ve MassDOT'un yerel katkı payı gereksinimlerini detaylandıran sermaye bütçesi başvuruları.
+Kelimeler:
+• negotiations = müzakereler, pazarlıklar
+• dispatching rights = sevk ve sefer yönetim yetkileri
+• capital budget filings = sermaye bütçesi resmi başvuruları/bildirimleri
+• match requirements = yerel eşleştirme/katkı payı zorunlulukları</t>
+      </text>
+    </comment>
+    <comment ref="B127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelenski ile gerginlik tırmanırken Trump bazı Rusya yaptırımlarını askıya aldı
+Kelimeler:
+• waive = feragat etmek, (yaptırımı) askıya almak/kaldırmak
+• row = ağız kavgası, sürtüşme, anlaşmazlık
+• intensify = şiddetlenmek, tırmanmak</t>
+      </text>
+    </comment>
+    <comment ref="D127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Başkanı Trump, Ukrayna Devlet Başkanı Volodimir Zelenski ile tırmanan diplomatik sürtüşmenin ortasında, Rusya'ya yönelik Kongre onaylı yaptırımları askıya almak üzere ulusal güvenlik muafiyet kararnamesi çıkardı.
+Kelimeler:
+• issue = yayımlamak, resmen yürürlüğe koymak
+• executive waiver = başkanlık muafiyeti/istisnası
+• congressionally mandated = Kongre tarafından zorunlu kılınan/yasalaştırılan
+• escalating = tırmanan, giderek artan
+• friction = sürtüşme, gerginlik</t>
+      </text>
+    </comment>
+    <comment ref="E127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırım muafiyeti
+Kelimeler:
+• waiver = muafiyet, feragat</t>
+      </text>
+    </comment>
+    <comment ref="F127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Trump yönetimi Rusal ve En+ Group üzerindeki yaptırımları kaldırdı
+Aralık 1990: Başkan Bush, Sovyetler Birliği için Jackson-Vanik muafiyeti çıkardı
+Ocak 2016: JCPOA (İran Nükleer Anlaşması) kapsamında Uygulama Günü muafiyetleri
+Kelimeler:
+• lift sanctions = yaptırımları kaldırmak
+• implementation = uygulama, yürürlüğe koyma</t>
+      </text>
+    </comment>
+    <comment ref="G127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Muafiyeti engellemeye yönelik partiler üstü bir Kongre girişimi Temsilciler Meclisi'nden 362–53 oyla geçti, ancak Senato'da sadece üç oyla reddedildi (60 oya ulaşılamayıp 57–42 kaldı); bu durum yasal denetimi artırırken muafiyetin yürürlükte kalmasına yol açtı.
+Aralık 1990: 12 ay içinde, sağlanan geçici rahatlama Sovyet ekonomisini istikrara kavuşturmakta veya ikili anlaşmazlıkları gidermekte yetersiz kaldı ve SSCB bir yıl sonra Aralık 1991'de çöktü.
+Ocak 2016: Bu rahatlama, sonraki yönetimin tek taraflı olarak muaf tutulan tüm yaptırımları yeniden uygulamaya koyduğu Mayıs 2018'e kadar sürdü; bu durum yasal bir iptal olmaksızın çıkarılan başkanlık muafiyetlerinin kurumsal kırılganlığını gözler önüne serdi.
+Kelimeler:
+• bipartisan = iki partinin de desteklediği, partiler üstü
+• fall short of = (belirli bir hedefin/sayının) gerisinde kalmak
+• oversight = denetim, gözetim
+• bridge divides = ayrılıkları/anlaşmazlıkları gidermek
+• unilaterally = tek taraflı olarak
+• reimpose = yeniden uygulamaya koymak
+• statutory repeal = yasal olarak yürürlükten kaldırma/iptal</t>
+      </text>
+    </comment>
+    <comment ref="H127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir ABD başkanının aktif bir hasma yönelik Kongre yaptırımlarını kaldırmak için ulusal güvenlik muafiyetlerini kullandığı modern vakaların %80'inden fazlasında, Kongre muafiyet yetkilerini geri almak üzere bağlayıcı yasalar çıkararak misilleme yapmakta ve Avrupalı müttefikler ise bağımsız, farklı politikalarla karşılık vermektedir.
+Kelimeler:
+• dismantle = ortadan kaldırmak, sökmek, feshetmek
+• adversary = hasım, düşman
+• retaliate = misilleme yapmak, karşılık vermek
+• binding legislation = bağlayıcı yasa/mevzuat
+• divergent = farklılaşan, ayrı düşen</t>
+      </text>
+    </comment>
+    <comment ref="I127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre, başkanın muafiyet yetkisini kısıtlamak veya geçersiz kılmak için partiler üstü yasa tasarısı sunacak; Avrupalı müttefikler ise ABD politika değişikliklerini dengelemek amacıyla Kiev'e yönelik bağımsız ikili desteği genişletecektir.
+Kelimeler:
+• nullify = hükümsüz kılmak, geçersizleştirmek
+• autonomous = özerk, bağımsız
+• offset = dengelemek, telafi etmek
+• policy shift = politika değişikliği/eksen kayması</t>
+      </text>
+    </comment>
+    <comment ref="K127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yönetim bu muafiyetleri Moskova tarafından kabul edilen aktif, hızlı bir ikili barış çerçevesinin parçası olarak kullanırsa, Kongre'nin muafiyetleri bozma yönündeki ivmesi duraklayabilir.
+Kelimeler:
+• leverage = kaldıraç olarak kullanmak, kendi lehine kullanmak
+• stall = duraklamak, çıkmaza girmek, durdurmak</t>
+      </text>
+    </comment>
+    <comment ref="N127" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato'ya sunulacak partiler üstü ortak onaylamama tasarıları ve Avrupa Konseyi tarafından Kiev'e taahhüt edilecek acil fon paketleri.
+Kelimeler:
+• joint resolution of disapproval = (Kongre) ortak ret/onaylamama kararı
+• pledge = taahhüt etmek, söz vermek</t>
+      </text>
+    </comment>
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Batı Şeria'daki hasat saldırısında Filistinliler ve ABD'li gazeteci İsrailli yerleşimciler tarafından yaralandı
+Kelimeler:
+• settler = yerleşimci
+• harvest = hasat</t>
+      </text>
+    </comment>
+    <comment ref="D128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Maskeli İsrailli yerleşimciler, mevsimsel şiddetin tırmandığı bir dönemde, Batı Şeria'daki yıllık zeytin hasadı sırasında Filistinli çiftçilere ve Amerikalı bir gazeteciye saldırarak ağaçları ateşe verdi.
+Kelimeler:
+• masked = maskeli
+• set ablaze = ateşe vermek, kundaklamak
+• surge = ani artış, kabarma, tırmanış</t>
+      </text>
+    </comment>
+    <comment ref="E128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yerleşimci şiddeti</t>
+      </text>
+    </comment>
+    <comment ref="F128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim–Kasım 2023: 2023 Batı Şeria hasat şiddetinde artış
+Ekim 2002: İkinci İntifada zeytin hasadı çatışmaları
+Kelimeler:
+• surge = ani artış, yükseliş
+• clash = çatışma</t>
+      </text>
+    </comment>
+    <comment ref="G128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim–Kasım 2023: İki ay içinde 1.000'den fazla Filistinli yerinden edildi; ABD ve AB, 2024 başlarında aşırılık yanlısı yerleşimcilere ve yasa dışı karakollara eşi benzeri görülmemiş doğrudan varlık dondurma ve seyahat yaptırımları uygulayarak karşılık verdi.
+Ekim 2002: İsrail Yüksek Mahkemesi daha sonra 2006 yılında (Murar - IDF Kuvvetleri Komutanı davası) İsrail güvenlik güçlerinin Filistinli hasatçıları koruma konusunda yasal bir yükümlülüğü olduğuna hükmetti; ancak sahadaki uygulama tutarsızlığını korudu.
+Kelimeler:
+• displace = yerinden etmek, yurdundan etmek
+• unprecedented = benzeri görülmemiş, emsalsiz
+• asset freeze = mal varlığının dondurulması
+• outpost = kaçak/ileri yerleşim yeri, karakol
+• rule = (mahkemece) hüküm vermek, karara bağlamak</t>
+      </text>
+    </comment>
+    <comment ref="H128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yabancı uyrukluların da etkilendiği ve belgelenmiş hasat sezonu yerleşimci saldırılarının yaklaşık 10'da 9'unda uluslararası diplomatik kınamalar tırmanır, ancak yerel güvenlik tedbirleri hasat sona ermeden önce tekrarlanan çatışmaları önlemede yetersiz kalır.
+Kelimeler:
+• foreign national = yabancı uyruklu kişi
+• condemnation = kınama
+• spike = keskin artış göstermek, tavan yapmak
+• recurrent = tekrarlayan, nükseden</t>
+      </text>
+    </comment>
+    <comment ref="I128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Saldırılar hasat sezonunun geri kalanında da şiddetlenerek Batı hükümetlerinin olaya karışan belirli aşırılık yanlısı ağlara hedefli vize yasakları veya mali yaptırımlar getirmesini tetikleyecektir.
+Kelimeler:
+• remainder = geri kalan kısım
+• prompt = tetiklemek, yol açmak, sevk etmek
+• targeted = hedefli, belirli bir hedefe yönelik</t>
+      </text>
+    </comment>
+    <comment ref="K128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 4 ila 8 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Amerikalı bir gazetecinin doğrudan yaralanması, resmi ABD Dışişleri Bakanlığı soruşturmalarını tetikleyebilir ve yalnızca yerel sivilleri içeren önceki olaylara kıyasla yaptırımları daha hızlı hayata geçirebilir.
+Kelimeler:
+• trigger = tetiklemek, başlatmak
+• expedite = hızlandırmak, çabuklaştırmak</t>
+      </text>
+    </comment>
+    <comment ref="N128" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Dışişleri Bakanlığı'ndan gelecek resmi açıklamalar veya seyahat yaptırımları ve IDF'nin savunmasız zeytinliklerin etrafına koruyucu kordonlar yerleştirmesi.
+Kelimeler:
+• deployment = (askeri birlik vb.) konuşlandırma, intikal
+• protective cordon = koruma kordonu/hattı
+• vulnerable = savunmasız, korunmasız
+• grove = küçük koruluk, (zeytin vb.) bahçesi</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD bütçe açığı 2026 mali yılında neredeyse 2 trilyon dolara yükselerek tek bir yılda %12 arttı
+Kelimeler:
+• budget deficit = bütçe açığı
+• swells = şişiyor, büyüyor
+• fiscal = mali
+• in a single year = tek bir yılda</t>
+      </text>
+    </comment>
+    <comment ref="D129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Hazine Bakanlığı, federal bütçe açığının 2026 mali yılında yaklaşık 2 trilyon dolara genişlediğini bildirdi; bu durum, hızla artan net faiz ödemeleri ve zorunlu harcamaların etkisiyle bir önceki yıla göre %12'lik bir artışa işaret ediyor.
+Kelimeler:
+• expanded = genişledi, büyüdü
+• prior year = önceki yıl
+• driven by = kaynaklanan, etkisiyle
+• surging = hızla yükselen
+• net interest payments = net faiz ödemeleri
+• non-discretionary outlays = zorunlu harcamalar</t>
+      </text>
+    </comment>
+    <comment ref="E129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+bütçe açığının genişlemesi</t>
+      </text>
+    </comment>
+    <comment ref="F129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: 2011 Amerika Birleşik Devletleri borç tavanı krizi
+1985: Gramm–Rudman–Hollings Dengeli Bütçe Yasası
+Kelimeler:
+• debt-ceiling = borç tavanı
+• balanced budget = dengeli bütçe</t>
+      </text>
+    </comment>
+    <comment ref="G129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2011: Kongre, zorunlu harcama tavanları (otomatik bütçe kesintisi) getirmek için 2011 Bütçe Kontrol Yasası'nı kabul etti, ancak Standard &amp; Poor's birkaç gün içinde Amerika Birleşik Devletleri'nin AAA kredi notunu düşürdü.
+1985: Mahkemeler 1986'da uygulama yapısını değiştirse de, kriz 1990 Bütçe Uygulama Yasası'nı (kullandıkça öde kurallarını getirerek) zorunlu kıldı ve nihayetinde 1998 yılına kadar bütçe fazlasına giden yolu açtı.
+Kelimeler:
+• enacted = yasalaştırdı
+• spending caps = harcama tavanları
+• sequestration = otomatik bütçe kesintisi
+• stripped ... of = elinden aldı, notunu düşürdü
+• paved the path to = yolunu açtı, zemin hazırladı
+• surplus = bütçe fazlası</t>
+      </text>
+    </comment>
+    <comment ref="H129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekonomik genişleme döneminde ABD açıklarının GSYİH'nin %6'sını aştığı son 4 vakanın 3'ünde, Kongre 12 ila 24 ay içinde yasal mali kısıtlama mekanizmalarına veya borç tavanı restleşmesine zorlandı.
+Kelimeler:
+• economic expansion = ekonomik genişleme / büyüme
+• exceeded = aştı, geçti
+• statutory = yasal, kanuni
+• fiscal restraint = mali kısıtlama
+• brinkmanship = uçurum siyaseti, tehlikeli restleşme</t>
+      </text>
+    </comment>
+    <comment ref="I129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yasa koyucular, borç limitleri ve süresi dolan vergi hükümleri konusunda ciddi yasama çıkmazlarıyla karşılaşacak; bu da ülke kredi notu incelemelerini tetikleyecek ve uzun vadeli Hazine tahvili getirileri üzerinde yukarı yönlü baskı yaratacaktır.
+Kelimeler:
+• lawmakers = yasa koyucular
+• legislative standoffs = yasama kilitlenmeleri / çıkmazları
+• expiring = süresi dolan
+• provisions = hükümler, maddeler
+• scrutiny = yakın inceleme, mercek altına alma
+• upward pressure = yukarı yönlü baskı</t>
+      </text>
+    </comment>
+    <comment ref="K129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980'ler veya 2011'in aksine, mevcut gösterge faiz oranları %5 civarında seyrederken borcun GSYİH'ye oranı %100'ü aşıyor; bu da net faiz maliyetlerinin önceki mali hesaplaşmalara kıyasla çok daha hızlı katlandığı anlamına geliyor.
+Kelimeler:
+• baseline interest rates = gösterge / baz faiz oranları
+• debt-to-GDP ratio = borcun GSYİH'ye oranı
+• compound = katlanarak artmak, bileşmek
+• fiscal showdowns = mali restleşmeler / hesaplaşmalar</t>
+      </text>
+    </comment>
+    <comment ref="N129" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Gösterge niteliğindeki 10 yıllık ve 30 yıllık Hazine ihalelerindeki talep karşılama oranları, büyük derecelendirme kuruluşlarının kredi görünümü revizyonları ve yaklaşan borç limiti son tarihleri konusundaki parti liderliklerinin tutumları.
+Kelimeler:
+• bid-to-cover ratio = talep karşılama oranı
+• benchmark = gösterge, kıstas
+• auctions = ihaleler
+• revisions = revizyonlar, güncellemeler
+• deadlines = son tarihler</t>
+      </text>
+    </comment>
+    <comment ref="B130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Analiz: Herkes Fed'in Ekim ayında faizleri sabit tutmasını bekliyor. Kevin Warsh hepimizi şaşırtabilir
+Kelimeler:
+• hold rates = faizleri sabit tutmak
+• surprise = şaşırtmak, sürpriz yapmak</t>
+      </text>
+    </comment>
+    <comment ref="D130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Piyasa katılımcıları genel olarak Federal Rezerv'in Ekim ayında faiz oranlarını sabit tutmasını bekliyor, ancak analist yorumları, politika yapıcıların süregelen enflasyonla mücadele etmek amacıyla beklenmedik bir faiz hamlesi yapabileceği risklerini vurguluyor.
+Kelimeler:
+• market participants = piyasa katılımcıları
+• broadly = genel olarak, büyük ölçüde
+• hold interest rates steady = faiz oranlarını sabit tutmak
+• policymakers = politika yapıcılar
+• combat = mücadele etmek
+• lingering inflation = süregelen, inatçı enflasyon</t>
+      </text>
+    </comment>
+    <comment ref="E130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+para politikası sürprizi</t>
+      </text>
+    </comment>
+    <comment ref="F130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şubat 1994: 1994 tahvil piyasası krizi
+Haziran 2022: FOMC 75 baz puanlık faiz artırımı eksen kayması (pivot)
+Kelimeler:
+• bond market = tahvil piyasası
+• basis point = baz puan
+• rate hike = faiz artırımı
+• pivot = politika/yön değişikliği</t>
+      </text>
+    </comment>
+    <comment ref="G130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şubat 1994: Hazine tahvili getirileri verim eğrisi genelinde dramatik bir şekilde fırlayarak 'Büyük Tahvil Katliamı'nı tetikledi ve sonraki altı ay boyunca sabit getirili portföylerde ciddi sermaye kayıplarına yol açtı.
+Haziran 2022: Kısa vadeli getiriler bir haftada 50 baz puandan fazla yükseldi, hisse senetlerinde sert satışlar yaşandı ve Fed yılın geri kalanı için hızlandırılmış bir sıkılaşma rejimine bağlı kaldı.
+Kelimeler:
+• spiked dramatically = dramatik şekilde fırladı
+• across the curve = verim eğrisi genelinde
+• sparking = tetikleyen
+• inflicting = yol açan, uğratan
+• fixed-income portfolios = sabit getirili portföyler
+• subsequent = sonraki, ardından gelen
+• tightening regime = sıkılaşma rejimi</t>
+      </text>
+    </comment>
+    <comment ref="H130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Konsensüs fiyatlamasıyla doğrudan çelişen merkez bankası politika kararları 1994 sonrası FOMC toplantılarının %15'inden daha azında gerçekleşir; ancak gerçekleştiğinde, sabit getirili menkul kıymet piyasası oynaklığı genellikle beş işlem günü içinde %30 ila %50 artar.
+Kelimeler:
+• contradict = çelişmek, ters düşmek
+• consensus pricing = piyasa beklentisi fiyatlaması
+• volatility = oynaklık
+• trading days = işlem günleri</t>
+      </text>
+    </comment>
+    <comment ref="I130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Doğrudan sürpriz bir faiz artışı pek olası görünmüyor, ancak şahin muhalif oylar ve gelecekteki faiz artışları konusunda uyaran agresif açıklamalar, getiri eğrisinin kısa vadeli ucunun keskin bir şekilde yukarı yönlü yeniden fiyatlanmasına neden olacaktır.
+Kelimeler:
+• outright = doğrudan, kesin
+• hawkish dissents = şahin muhalefet / karşı oylar
+• repricing = yeniden fiyatlama
+• short end of the yield curve = getiri eğrisinin kısa vadeli ucu</t>
+      </text>
+    </comment>
+    <comment ref="K130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 4 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Fed şeffaflık normları, noktasal grafik (dot-plot) projeksiyonları ve toplantı sonrası basın toplantıları, önceden sinyali verilmemiş faiz hamlelerini kurumsal güvenilirlik açısından 1994'e kıyasla çok daha maliyetli hale getiriyor.
+Kelimeler:
+• transparency = şeffaflık
+• dot-plot projections = noktasal grafik projeksiyonları
+• untelegraphed = önceden sinyali verilmemiş
+• institutional credibility = kurumsal güvenilirlik</t>
+      </text>
+    </comment>
+    <comment ref="N130" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Toplantı öncesi sessizlik dönemi öncesindeki Fed guvernörlerinin medya demeçleri, 30 günlük Fed Fon vadeli işlemleri fiyatlamasındaki ani değişimler ve 2 yıllık Hazine tahvili getirilerindeki hareketler.
+Kelimeler:
+• media appearances = medya demeçleri, basına çıkışlar
+• blackout period = sessizlik dönemi (toplantı öncesi kısıtlama dönemi)
+• sudden shifts = ani kaymalar / değişimler
+• futures pricing = vadeli işlem fiyatlaması</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Petrol ihracatı yavaşlarken Hürmüz yakınlarındaki gemi saldırısı raporları rekor seviyeye ulaştı
+Kelimeler:
+• ship attack = gemi saldırısı
+• record high = rekor seviye
+• exports slow = ihracatın yavaşlaması</t>
+      </text>
+    </comment>
+    <comment ref="D131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hürmüz Boğazı çevresindeki ticari gemi saldırıları tek bir haftada 12 olaya ulaşarak rekor kırdı ve bu kritik küresel darboğazdan geçen ham petrol sevkiyatlarını ciddi şekilde aksattı.
+Kelimeler:
+• commercial ship = ticari gemi
+• Strait of Hormuz = Hürmüz Boğazı
+• severely disrupting = ciddi şekilde sekteye uğratmak
+• crude shipments = ham petrol sevkiyatları
+• chokepoint = darboğaz / stratejik geçit noktası</t>
+      </text>
+    </comment>
+    <comment ref="E131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+deniz saldırıları / darboğaz aksaması</t>
+      </text>
+    </comment>
+    <comment ref="F131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1984–1988: İran-Irak Savaşı'nın Tanker Savaşı aşaması
+Mayıs–Haziran 2019: Umman Körfezi olayları
+Kelimeler:
+• Tanker War = Tanker Savaşı
+• phase = aşama / safha
+• incidents = olaylar</t>
+      </text>
+    </comment>
+    <comment ref="G131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1984–1988: Deniz sigortası oranları %400'ün üzerinde artarak Kuveyt'in koruma talep etmesine yol açtı ve ABD'nin 1987'deki Earnest Will Operasyonu kapsamında doğrudan deniz müdahalesini tetikleyerek Nisan 1988'deki Praying Mantis Operasyonu ile doruğa ulaştı.
+Mayıs–Haziran 2019: 3 ay içinde, Basra Körfezi tankerleri için savaş riski sigorta primleri on kat arttı ve ABD, ticari gemilere refakat etmek amacıyla çok uluslu Uluslararası Deniz Güvenliği Koalisyonu'nu (IMSC) kurdu.
+Kelimeler:
+• maritime insurance rates = denizcilik sigorta oranları
+• precipitating = tetiklemek / hızlandırmak
+• naval intervention = donanma / deniz müdahalesi
+• culminating in = ... ile sonuçlanmak / doruk noktasına ulaşmak
+• war-risk insurance premiums = savaş riski sigorta primleri
+• surged tenfold = on katına fırlamak
+• merchant shipping = ticaret gemileri / ticari gemicilik</t>
+      </text>
+    </comment>
+    <comment ref="H131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel emsal, Basra Körfezi'ndeki ticari trafiğe yönelik sürekli saldırıların yerel kalmadığını gösteriyor: Son 40 yılda Hürmüz'deki büyük deniz gerilimlerinin %100'ünde, saldırılar uluslararası askeri refakat operasyonlarını ve denizcilik sigortasında önemli artışları tetiklemiş, bunu 6 ila 18 ay içinde sınırlı kinetik misillemeler izlemiştir.
+Kelimeler:
+• historical precedent = tarihsel emsal
+• sustained attacks = süregelen / kesintisiz saldırılar
+• flare-ups = gerilimin aniden tırmanması
+• substantial spikes = önemli / ciddi artışlar
+• kinetic retaliation = kinetik (askeri/fiziksel) misilleme</t>
+      </text>
+    </comment>
+    <comment ref="I131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ticari tanker trafiği giderek daha fazla silahlı donanma refakati veya alternatif rotalar arayacak; savaş riski sigorta ek ücretleri ise devlet destekli donanma koruması olmadan Basra Körfezi geçişini ekonomik açıdan imkansız hale getirecek ve deniz devriye koalisyonları konuşlandırılacaktır.
+Kelimeler:
+• armed naval escorts = silahlı donanma refakati / eskortu
+• surcharges = ek ücretler / zamlar
+• economically prohibitive = ekonomik açıdan aşırı maliyetli / engelleyici
+• state-backed = devlet destekli
+• deployed = konuşlandırılmış</t>
+      </text>
+    </comment>
+    <comment ref="K131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1980'lerden farklı olarak, modern gemisavar balistik füzeleri ve uzun menzilli insansız saldırı dronları, geleneksel hücumbotları ve mayınları engellemeye kıyasla standart donanma konvoy savunmasının maliyetini ve riskini önemli ölçüde artırmaktadır.
+Kelimeler:
+• anti-ship ballistic missiles = gemisavar balistik füzeler
+• unmanned attack drones = insansız saldırı dronları
+• convoy defense = konvoy savunması
+• intercepting = önünü kesmek / engellemek
+• gunboats = hücumbotlar / silahlı tekneler</t>
+      </text>
+    </comment>
+    <comment ref="N131" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Batılı veya bölgesel koalisyonların resmi konvoy refakat operasyonları başlattığına dair duyurular ve büyük deniz sigortacılarının tüm körfezi sigortalanamaz bir hariç tutma bölgesi ilan etmesi.
+Kelimeler:
+• convoy escort operations = konvoy refakat operasyonları
+• maritime insurers = deniz sigortacıları
+• uninsurable = sigortalanamaz
+• exclusion zone = hariç tutma / yasak bölge</t>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, ulusal çıkarları gerekçe göstererek Graham Yasası kapsamındaki geniş kapsamlı yeni Rusya yaptırımlarından ve gümrük vergilerinden feragat etti
+Kelimeler:
+• waives = feragat etmek / muaf tutmak
+• broad = geniş kapsamlı
+• tariffs = gümrük vergileri
+• citing national interest = ulusal çıkarları gerekçe göstererek</t>
+      </text>
+    </comment>
+    <comment ref="D132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD yönetimi, Graham Yasası'nı imzalayarak yürürlüğe koymasından sadece birkaç hafta sonra, Rusya'ya yönelik yeni yasalaşan yasal yaptırımları ve gümrük vergilerini askıya almak için ulusal çıkar muafiyetine başvurdu.
+Kelimeler:
+• invoked = başvurmak / devreye sokmak
+• waiver = muafiyet / feragat
+• suspend = askıya almak
+• statutory sanctions = yasal / kanunla belirlenmiş yaptırımlar
+• signing into law = imzalayarak yasalaştırmak</t>
+      </text>
+    </comment>
+    <comment ref="E132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+başkanlık yaptırım muafiyeti</t>
+      </text>
+    </comment>
+    <comment ref="F132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mayıs 2021: Biden yönetiminin Kuzey Akım 2 yaptırımlarından feragat etmesi
+1994–2012: Rusya için Jackson-Vanik Değişikliği'nden yıllık muafiyetler
+Kelimeler:
+• administration waiver = yönetim muafiyeti
+• annual waivers = yıllık muafiyetler
+• amendment = yasa değişikliği</t>
+      </text>
+    </comment>
+    <comment ref="G132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mayıs 2021: Dört ay içinde boru hattının inşası tamamlandı; bu taviz Rusya'nın stratejik duruşunu değiştirmede başarısız oldu ve Ukrayna'nın işgali bir politika değişikliğini zorunlu kılmadan önce Kongre'de her iki partiden de sert tepkilere yol açtı.
+1994–2012: Muafiyetler ticaret engellerini geçici olarak düşürürken, Kongre diplomatik anlaşmazlıklar sırasında yenilemeleri durdurmakla defalarca tehdit etti ve nihayetinde 2012'de bu mekanizmayı Magnitsky Yasası kapsamındaki kalıcı hedefli yaptırımlarla değiştirdi.
+Kelimeler:
+• concession = taviz / ödün
+• strategic posture = stratejik duruş / tutum
+• fierce bipartisan pushback = iki partiden gelen sert direnç / tepki
+• policy reversal = politika değişikliği / çark etme
+• withhold renewals = yenilemeleri askıya almak / yapmamak
+• targeted sanctions = hedefli yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="H132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD yürütme organı, taktiksel bir ekonomik veya diplomatik anlaşma yapmak amacıyla bir hasma yönelik yeni yürürlüğe girmiş kongre yaptırımlarından feragat ettiğinde, Kongre tarihsel vakaların %70'inden fazlasında 12 ila 24 ay içinde daha sıkı, muafiyet tanınamaz yasal zorunluluklar getirerek yanıt verir.
+Kelimeler:
+• executive branch = yürütme organı
+• adversary = hasım / düşman
+• broker a deal = anlaşma sağlamak / uzlaşmaya aracılık etmek
+• non-waivable = feragat edilemez / muafiyet tanınamaz
+• statutory mandates = yasal zorunluluklar</t>
+      </text>
+    </comment>
+    <comment ref="I132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre, başkanlık muafiyet yetkisini kaldırmak veya sınırlandırmak amacıyla Graham Yasası'nı değiştirmeye çalışarak iki partili bir direnç gösterecek; Moskova ise bu rahatlamayı geçici olarak değerlendirip karşılıklı diplomatik uzlaşmalar sunmadan önce yapısal tavizler talep edecektir.
+Kelimeler:
+• mount bipartisan pushback = iki partili direnç göstermek
+• amend = değiştirmek / tadil etmek
+• strip or constrain = elinden almak veya sınırlandırmak
+• waiver authority = muafiyet yetkisi
+• structural concessions = yapısal tavizler
+• reciprocal = karşılıklı</t>
+      </text>
+    </comment>
+    <comment ref="K132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beyaz Saray, yerli tüketiciler için acil, somut bir enerji veya akaryakıt fiyatı istikrarı sağlarsa, seçmen desteği yönetimi Kongre'nin muafiyeti iptal etme çabalarından koruyabilir.
+Kelimeler:
+• tangible = somut / elle tutulur
+• stabilization = istikrar sağlama / dengeleme
+• insulate from = ...den korumak / yalıtmak
+• overturn = iptal etmek / hükümsüz kılmak</t>
+      </text>
+    </comment>
+    <comment ref="N132" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre'den iki partili ret kararları ve Rus enerji ithalatına yönelik ulusal çıkar muafiyeti açıklarını ortadan kaldırmayı amaçlayan yasa tasarıları.
+Kelimeler:
+• resolutions of disapproval = onaylamama / ret kararları
+• draft legislation = yasa tasarısı
+• eliminate = ortadan kaldırmak / bertaraf etmek
+• loopholes = yasal boşluklar / açıklar</t>
+      </text>
+    </comment>
+    <comment ref="B133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City'nin temyiz başvurusunu kazanmak için herhangi bir dayanağı var mı?
+Kelimeler:
+• grounds = dayanak, gerekçe
+• win an appeal = temyiz davasını/başvurusunu kazanmak</t>
+      </text>
+    </comment>
+    <comment ref="D133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, Premier League mali düzenlemelerini ihlal etmekten suçlu bulunmasına karşı temyize gitmek için olası hukuki yolları değerlendiriyor; ancak hukuk uzmanları kulübün önemli usul engelleriyle karşı karşıya olduğu konusunda uyarıyor.
+Kelimeler:
+• evaluating = değerlendirmek
+• legal avenues = hukuki yollar
+• breaching = ihlal etmek
+• financial regulations = mali düzenlemeler
+• substantial = önemli, kayda değer
+• procedural hurdles = usule ilişkin engeller</t>
+      </text>
+    </comment>
+    <comment ref="E133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+finansal fair play temyiz başvurusu</t>
+      </text>
+    </comment>
+    <comment ref="F133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Manchester City'nin UEFA'nın Avrupa'dan men cezasına karşı CAS'a yaptığı temyiz başvurusu
+2024: Everton puan silme cezası temyiz başvurusu
+2024: Nottingham Forest puan silme cezası temyiz başvurusu
+Kelimeler:
+• points deduction = puan silme cezası
+• ban = men cezası, yasaklama</t>
+      </text>
+    </comment>
+    <comment ref="G133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Beş ay sonra, Temmuz 2020'de, Spor Tahkim Mahkemesi (CAS), iddia edilen ihlallerin çoğunun ya kanıtlanmamış ya da zamanaşımına uğramış olduğuna hükmederek men cezasını kaldırdı ve para cezasını 10 milyon avroya indirdi.
+2024: Üç ay sonra, Şubat 2024'te, Premier League temyiz kurulu, ilk tahkim heyetinin hafifletici unsurları değerlendirmesindeki hukuki hataları gerekçe göstererek yaptırımı 10 puandan 6 puana düşürdü.
+2024: Mayıs 2024'te, ilk karardan iki ay sonra, temyiz kurulu Forest'ın başvurusunu tamamen reddetti ve puan silme cezasını aynen onayladı.
+Kelimeler:
+• overturned = bozdu, iptal etti
+• alleged breaches = iddia edilen ihlaller
+• time-barred = zamanaşımına uğramış
+• sanction = yaptırım, ceza
+• mitigating factors = hafifletici nedenler/unsurlar
+• dismissed = reddetti
+• upheld = onadı, geçerli kıldı</t>
+      </text>
+    </comment>
+    <comment ref="H133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Premier League temyiz kurulları, vakaları baştan sona yeniden duruşma konusu yapmak yerine hukuki noktaları, usulü ve ölçülülüğü inceler. Son Premier League mali temyizlerinde kulüplerin suçluluk kararlarını tamamen bozdurma oranı %0'dır (2023–24'te 2'de 0); ancak yaptırımlar 2 vakanın 1'inde değişikliğe uğramıştır.
+Kelimeler:
+• points of law = hukuki meseleler/noktalar
+• proportionality = ölçülülük
+• rehearing = yeniden duruşma/yargılama
+• overturning = kararı bozma, tersine çevirme
+• verdicts = hükümler, kararlar
+• modified = değiştirilmiş</t>
+      </text>
+    </comment>
+    <comment ref="I133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City'nin asıl suçluluk hükmünü tamamen bozdurması pek olası görünmüyor, ancak dar teknik gerekçelerle belirli cezaları veya para cezalarını bir miktar hafifletmeyi başarabilir.
+Kelimeler:
+• unlikely to = olası görünmeyen
+• primary guilty verdict = asıl suçluluk hükmü
+• shaving off = kırpmak, miktarını azaltmak
+• narrow technical grounds = dar kapsamlı teknik gerekçeler</t>
+      </text>
+    </comment>
+    <comment ref="K133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020'deki CAS sürecinin aksine, Premier League kurallarında geçmişte City'yi koruyan beş yıllık bir zamanaşımı süresi bulunmuyor ve Premier League temyiz paneli, davayı sıfırdan ele alan duruşmalar olmaksızın, tamamen yerel özel tahkim kuralları çerçevesinde faaliyet gösteriyor.
+Kelimeler:
+• statute of limitations = zamanaşımı süresi
+• shielded = korudu, siper oldu
+• strictly = kesin olarak, sıkı bir şekilde
+• domestic private arbitration = yerel özel tahkim
+• de novo hearings = davayı sıfırdan ele alan duruşmalar</t>
+      </text>
+    </comment>
+    <comment ref="N133" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+City'nin, ciddi bir usul usulsüzlüğü iddiasıyla İngiltere Yüksek Mahkemesi'nde 1996 Tahkim Yasası'nın 68. Maddesi uyarınca dava açması.
+Kelimeler:
+• filing an action = dava açmak
+• alleging = iddia ederek
+• procedural irregularity = usul usulsüzlüğü, usul hatası</t>
+      </text>
+    </comment>
+    <comment ref="B134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real, Goebbels benzetmesi nedeniyle Tebas'ın istifasını talep ediyor
+Kelimeler:
+• demand = talep etmek
+• resign = istifa etmek
+• comparison = kıyaslama, benzetme</t>
+      </text>
+    </comment>
+    <comment ref="D134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid, kulübün iletişim stratejisini ve yönetimini kamuoyu önünde Nazi propaganda bakanı Joseph Goebbels'e benzeten La Liga başkanı Javier Tebas'ın derhal istifa etmesini talep etti.
+Kelimeler:
+• immediate resignation = derhal istifa
+• publicly = alenen, kamuoyu önünde
+• compared to = ile kıyasladı, benzetti
+• propaganda = propaganda</t>
+      </text>
+    </comment>
+    <comment ref="E134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+spor yönetimi uyuşmazlığı</t>
+      </text>
+    </comment>
+    <comment ref="F134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2024: Real Madrid'in Tebas aleyhine İspanya Spor İdare Mahkemesi'ne şikâyette bulunması
+2021: CVC anlaşması ve Avrupa Süper Ligi üzerine La Liga içi iç savaş
+2023: Rubiales skandalı ve zorunlu istifa
+Kelimeler:
+• complaint = şikâyet
+• civil war = iç savaş
+• forced resignation = zorunlu istifa</t>
+      </text>
+    </comment>
+    <comment ref="G134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2024: Üç ay sonra, Temmuz 2024'te, Spor İdare Mahkemesi (TAD) konuyu hafif bir kural ihlali olarak nitelendirdi ve Tebas'ı görevden uzaklaştırmayı veya men etmeyi reddederek onun görev süresini perçinledi.
+2021: Tebas, planı oylamayla kabul ettirmek için 42 üye kulübün 37'sini harekete geçirdi, sonraki iki yıl boyunca tekrarlanan hukuki itirazlara karşı direndi ve Aralık 2023'te rakipsiz olarak yeniden seçime girdi.
+2023: Üç hafta içinde FIFA geçici bir uzaklaştırma kararı verdi, İspanyol hükümeti yasal süreç başlattı ve bölgesel federasyon başkanları desteklerini çekerek Eylül 2023'te onu istifaya zorladı.
+Kelimeler:
+• classified = sınıflandırdı, nitelendirdi
+• minor infraction = hafif kural ihlali
+• cementing his tenure = görev süresini perçinlemek/sağlamlaştırmak
+• mobilized = harekete geçirdi
+• withstood = direndi, karşı koydu
+• provisional suspension = geçici uzaklaştırma/men
+• withdrew their backing = desteklerini çektiler</t>
+      </text>
+    </comment>
+    <comment ref="H134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Real Madrid'in Javier Tebas'a yönelik tek taraflı istifa talepleri, on yılı aşkın bir sürede %0 başarı oranına sahiptir (2013'ten bu yana 5 büyük karşı karşıya gelişin 0'ı). İspanyol futbol yöneticileri ancak hem kulüplerin çoğunluğunun hem de dış düzenleyicilerin (CSD veya FIFA) desteğini kaybettiklerinde görevden düşerler.
+Kelimeler:
+• unilateral = tek taraflı
+• success rate = başarı oranı
+• confrontations = karşı karşıya gelmeler, çekişmeler
+• backing = destek, arka çıkma
+• external regulators = dış düzenleyici kurumlar</t>
+      </text>
+    </comment>
+    <comment ref="I134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Javier Tebas istifa etmeyi reddedecek, ölçülü bir özür veya açıklama sunacak ve elit olmayan La Liga kulüplerinin desteğiyle görevini koruyacaktır.
+Kelimeler:
+• step down = görevden çekilmek, istifa etmek
+• calibrated = ölçülü, dikkatle ayarlanmış
+• clarification = açıklama, netleştirme
+• retain his post = makamını/görevini korumak</t>
+      </text>
+    </comment>
+    <comment ref="K134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ila 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Nazi söylemine ve Goebbels'e başvurmak, İspanya Yüksek Spor Konseyi'nin (CSD) hükümet düzeyinde müdahalesine ya da ligin ticari ortaklarının tepkisine yol açabilecek çok ağır bir kültürel ve siyasi çizgiyi aşıyor.
+Kelimeler:
+• invoking = başvurmak, dile getirmek
+• rhetoric = söylem, hitabet
+• prompt = yol açmak, tetiklemek
+• intervention = müdahale
+• backlash = sert tepki, geri tepme</t>
+      </text>
+    </comment>
+    <comment ref="N134" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük uluslararası La Liga sponsorlarından gelecek açıklamalar veya İspanya Yüksek Spor Konseyi (CSD) tarafından açılacak resmi bir görevi kötüye kullanma soruşturması.
+Kelimeler:
+• statements = açıklamalar, demeçler
+• misconduct inquiry = görevi kötüye kullanma/uygunsuz davranış soruşturması
+• commercial partners = ticari ortaklar</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kritik seçim yaklaşırken Brezilya, Amazon ormansızlaşmasında rekor bir düşüşe tanıklık ediyor
+Kelimeler:
+• loom = yaklaşmak, eli kulağında olmak (genellikle tehditkâr veya kritik bir durum için)
+• deforestation = ormansızlaşma, ormanların yok edilmesi</t>
+      </text>
+    </comment>
+    <comment ref="D135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Brezilya, federal denetimlerin artırılmasının ardından Amazon ormansızlaşmasında tarihi bir düşüş kaydetti; ancak yaklaşan seçimlerin çevre liderliğini ve denetim politikalarını yeniden şekillendirme tehdidi oluşturması sebebiyle bu kazanımlar yoğun bir belirsizlikle karşı karşıya.
+Kelimeler:
+• stepped-up = artırılmış, yoğunlaştırılmış
+• enforcement = yaptırım, kanun veya kural uygulama
+• reshuffle = yeniden düzenlemek, kabine/görev dağılımını değiştirmek</t>
+      </text>
+    </comment>
+    <comment ref="E135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+çevre düzenlemesi / politika döngüsü</t>
+      </text>
+    </comment>
+    <comment ref="F135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2004: PPCDAm'ın (Ormansızlaşmayı Önleme ve Kontrol Eylem Planı) başlatılması
+2018: 2018 Brezilya genel seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="G135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2004: Yıllık ormansızlaşma 2004 ile 2012 arasında yaklaşık %84 oranında sert bir düşüş göstererek, devlet öncülüğündeki denetimlerin genel tarımsal üretime zarar vermeden orman kaybını keskin bir şekilde frenleyebileceğini kanıtladı.
+2018: Üç yıl içinde Amazon ormansızlaşması %60'ın üzerinde fırladı; çevre cezalarının dibe vurması ve IBAMA gibi kurumların fonlarının sistematik olarak kesilmesiyle 2021 yılına gelindiğinde son 15 yılın en yüksek seviyelerine ulaştı.
+Kelimeler:
+• plunge = sert düşüş göstermek, çakılmak
+• curb = frenlemek, dizginlemek
+• plummet = dibe vurmak, hızla düşmek
+• defund = ödenek/fon sağlamayı durdurmak veya azaltmak</t>
+      </text>
+    </comment>
+    <comment ref="H135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Brezilya çevre tarihinde, ormansızlaşma oranları hükümetin siyasi çizgisiyle neredeyse kusursuz bir paralellik gösterir: İdari baskı ve denetimler 4 yıl içinde %50-80 oranında düşüş sağlarken, tarım sektörüyle uyumlu yönetimlere geçişler, son yirmi yıldaki vakaların %100'ünde 12 ila 24 ay içinde politikaların hızla tersine dönmesine ve orman tahribatının artmasına yol açmıştır.
+Kelimeler:
+• crackdown = sert önlemler alma, baskı ve denetim uygulama
+• agribusiness-aligned = tarım-sanayi (büyük tarım) sektörüyle uyumlu/ittifak halinde
+• policy reversal = politikanın tersine dönmesi/değişmesi
+• forest clearance = orman arazisinin temizlenmesi/yok edilmesi</t>
+      </text>
+    </comment>
+    <comment ref="I135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ormansızlaşma mevcut hükümetin görev süresinin geri kalanında baskılanmış durumda kalacaktır; ancak bu düşüşün uzun vadeli sürüp sürmeyeceği büyük ölçüde seçime bağlıdır; muhalefetin kazanması muhtemelen 18 ay içinde ormansızlaşma oranlarında ani bir sıçramayı tetikleyecektir.
+Kelimeler:
+• suppressed = baskılanmış, düşük seviyede tutulmuş
+• mandate = görev süresi, yetki
+• contingent on = -e bağlı, koşullu
+• rebound = yeniden yükselişe geçme, toparlanma</t>
+      </text>
+    </comment>
+    <comment ref="K135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 12 ila 24 ay</t>
+      </text>
+    </comment>
+    <comment ref="L135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uluslararası ticaret mekanizmaları —özellikle Avrupa Birliği Ormansızlaşma Yönetmeliği (EUDR)— ve özel pazar tedarik zinciri takibi, artık tahrip edilmiş arazilerle bağlantılı tarımsal ihracata ağır ekonomik yaptırımlar uygulayarak gelecekteki hükümetler için politika geri adımlarının ekonomik maliyetini yükseltmektedir.
+Kelimeler:
+• supply-chain tracing = tedarik zinciri takibi/izlenebilirliği
+• penalties = cezalar, yaptırımlar
+• policy rollback = politikalarda geri adım atma, eski düzene dönme</t>
+      </text>
+    </comment>
+    <comment ref="N135" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bancada Ruralista'nın çevre ruhsatlandırma yasalarını sulandırmaya yönelik yasama girişimleri; kilit tarım eyaletlerindeki erken anket kaymaları.
+Kelimeler:
+• dilute = sulandırmak, etkisini azaltmak, zayıflatmak
+• licensing laws = ruhsatlandırma/izin yasaları
+• polling shifts = anketlerdeki oy kaymaları</t>
+      </text>
+    </comment>
+    <comment ref="B136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD senatörleri Ukrayna'daki Starlink kısıtlamalarına ilişkin soruşturma açılması çağrısında bulundu
+Kelimeler:
+• probe = ayrıntılı soruşturma, derinlemesine inceleme
+• restrictions = kısıtlamalar</t>
+      </text>
+    </comment>
+    <comment ref="D136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD'li yasa koyucular, Starlink ağındaki kısıtlamaların ve bant genişliğini kasıtlı olarak daraltmanın Ukrayna'nın cephe operasyonlarını aksattığı yönündeki haberlerin ardından SpaceX hakkında resmi bir soruşturma talep etti.
+Kelimeler:
+• bandwidth throttling = bant genişliğini daraltma/kısma
+• hamper = aksatmak, sekteye vurmak, engellemek
+• frontline operations = cephe hattı harekâtları</t>
+      </text>
+    </comment>
+    <comment ref="E136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+savunma sözleşmeleri denetimi</t>
+      </text>
+    </comment>
+    <comment ref="F136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2023: Senato Silahlı Hizmetler Komitesi'nin Ukrayna'daki Starlink'e ilişkin soruşturması
+1918: Ticari telekomünikasyonun federal yönetimce devralınması</t>
+      </text>
+    </comment>
+    <comment ref="G136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2023: Savunma Bakanlığı, hizmet sağlayıcının operasyonel müdahalesini engellemek amacıyla sözleşmeye dayalı güvenceler getirerek 'Starshield' programı kapsamında Starlink hizmetlerini doğrudan sözleşmeye bağlayıp duruma müdahale etti.
+1918: Federal kontrol bir yıldan uzun sürdü ve özel ağlarda hükümet ile savunma iletişimi için kesintisiz öncelikli erişimi zorunlu kılan yasal çerçevelerle sonuçlandı.
+Kelimeler:
+• intervene = müdahale etmek, araya girmek
+• operational interference = operasyonel müdahale/aksatma
+• culminate in = ile sonuçlanmak, zirveye ulaşmak</t>
+      </text>
+    </comment>
+    <comment ref="H136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Özel yükleniciler kritik savaş zamanı iletişiminde tek kaynak olarak operasyonel bir tıkanma noktası/tekel gücü elde ettiğinde, kongre soruşturmaları sözleşmeyi feshetmez; ancak 6 ila 12 ay içinde doğrudan katı yasal denetimlere, savunmaya özgü sözleşme revizyonlarına ve zorunlu çifte tedarikçi uygulamasına yol açar.
+Kelimeler:
+• chokehold = tekel kontrolü, boğazını sıkma, mutlak hakimiyet
+• statutory oversight = yasal/kanuni denetim
+• dual-sourcing = çifte kaynak/tedarikçi kullanımı</t>
+      </text>
+    </comment>
+    <comment ref="I136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato soruşturması, savunma amaçlı satın alınan takımyıldızlarda tek taraflı bant daraltmayı veya coğrafi engellemeyi yasaklayan daha sıkı Savunma Bakanlığı sözleşme şartlarına ve bunun yanı sıra ikincil ticari LEO (alçak Dünya yörüngesi) uydu sağlayıcılarına yönelik finansmanın hızlandırılmasına yol açacaktır.
+Kelimeler:
+• unilateral = tek taraflı
+• geofencing = coğrafi sınırlama/engelleme
+• constellation = (uydu) takımyıldızı</t>
+      </text>
+    </comment>
+    <comment ref="K136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+SpaceX'in Falcon 9 fırlatma sıklığı ve takımyıldız yoğunluğu, Starlink'e yüksek bant genişlikli ve düşük gecikmeli uydu internetinde fiili bir tekel sağlamakta; bu durum Pentagon'u onun operasyonel ölçeğine yetişebilecek çok az sayıda acil alternatif sağlayıcıyla karşı karşıya bırakmaktadır.
+Kelimeler:
+• launch cadence = fırlatma sıklığı/temposu
+• low-latency = düşük gecikmeli
+• functional monopoly = fiili tekel</t>
+      </text>
+    </comment>
+    <comment ref="N136" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato Silahlı Hizmetler Komitesi'nden celpler veya kamuya açık oturumlar; Savunma Bakanlığı'nın alternatif alçak Dünya yörüngesi takımyıldızları için tedariki hızlandıran ihale çağrıları.
+Kelimeler:
+• subpoena = mahkeme celbi veya kongre celbi
+• procurement = tedarik, satın alma
+• solicitation = ihale çağrısı, resmi teklif talebi</t>
       </text>
     </comment>
   </commentList>
@@ -12168,7 +13768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22594,6 +24194,1208 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Trump shifts midterm travel blitz toward deep-red states</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>President Donald Trump's late campaign travel itinerary shifted away from competitive swing districts toward conservative states he carried easily in 2024. The pivot signals that Republican campaign strategists are playing defense to preserve base turnout rather than contesting battleground seats.</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>midterm campaign defensive shift</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>October 2018: Trump 2018 midterm rally focus on red states
+October 2006: George W. Bush's defensive 2006 campaign tour</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>October 2018: While Republicans managed to gain two Senate seats in conservative states, they suffered a net loss of 40 House seats, losing the majority in a midterm rebuke within 3 weeks.
+October 2006: The governing Republican Party lost majorities in both the House (-30 seats) and Senate (-6 seats) in November 2006.</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>In modern midterms (including 1994, 2006, 2010, and 2018), when an incumbent president retreats from swing districts to safe base states in October, the president's party has lost control of the House of Representatives in more than 80% of instances.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is highly likely to lose control of the House of Representatives or suffer severe seat losses, as defensive travel confirms internal polling collapse in battleground suburban districts.</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>80-85%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Heightened national political polarization and gerrymandered district maps have reduced the number of truly competitive swing districts, which could cap the total number of seat flips relative to historical wave elections.</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>National party committees pulling ad reservations from marginal districts to reallocate funds toward previously safe red seats.</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/17/nx-s1-6004276/trump-travel-midterms</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_United_States_House_of_Representatives_elections
+https://en.wikipedia.org/wiki/2006_United_States_House_of_Representatives_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Trump signs order waiving congressional sanctions on Russia</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>President Trump signed an executive order waiving statutory sanctions enacted against Moscow under national security legislation, escalating a clash between the executive branch and Congress amid tensions over the Ukraine conflict.</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>presidential sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2017–2019: CAATSA signing and sanctions relief dispute
+1984–1986: Executive circumvention of the Boland Amendment</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>2017–2019: Within months, bipartisan majorities in Congress introduced resolutions of disapproval and drafted follow-up legislation to restrict future presidential waiver flexibility.
+1984–1986: The friction culminated in 1987 with the Iran-Contra hearings, major congressional investigations, and statutory tightening of legislative oversight.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>When a president executes broad national security waivers to bypass bipartisan statutory foreign policy mandates, Congress retaliates legislatively or via oversight hearings in roughly 7 out of 10 historical disputes.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Bipartisan leadership in the Senate and House will file formal resolutions of disapproval or attach mandatory non-waivable sanctions clauses to upcoming national defense and spending legislation.</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>If the post-midterm Congress features stronger party-line alignment with the White House, party leadership may block floor votes on disapproval resolutions that would otherwise pass with bipartisan support.</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Joint rebukes from foreign relations committee chairs and introduction of a privileged resolution of disapproval under the National Emergencies Act.</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/16/us/politics/trump-order-russia-sanctions.html</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/Boland_Amendment</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Federal authorities probe suspicious letters sent to Massachusetts political and elections offices</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Federal and state law enforcement agencies launched an investigation after at least six elected officials and election offices across Massachusetts received suspicious letters containing unidentified powders just weeks before the November election.</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>mail threat</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>September 2024: Suspicious mail sent to election officials across more than 15 states
+April 2013: 2013 ricin letters
+September–October 2001: 2001 anthrax attacks</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>September 2024: Postal inspection teams and the FBI intercepted the mailings, cleared facilities within 48 to 72 hours, confirmed the substances were harmless irritants or hoaxes, and instituted enhanced hazmat mail-screening protocols.
+April 2013: Mail interception facilities detected the toxin before delivery, and the FBI arrested the perpetrator, James Everett Dutschke, within two weeks.
+September–October 2001: The attacks triggered massive permanent screening reforms across the United States Postal Service and congressional mail delivery.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>In over 90% of political white-powder mail scares since 2001, the substances test negative for lethal biological agents and are intended as psychological harassment; federal investigators typically trace postmarks, paper stock, and digital signatures to identify suspects within 3 to 12 weeks.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>The substances will test non-lethal (e.g., starch, baking soda, or low-grade irritants), prompting temporary mail-handling disruptions and tightened screening at election facilities, but early voting schedules will continue without postponement.</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>next 2 to 4 weeks</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>If modern chemical tracing identifies toxic novel synthetic compounds or fentanyl rather than standard hoax materials, facility closures could be prolonged and federal protection details mobilized.</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Preliminary hazardous material lab test results from the Massachusetts State Police Crime Laboratory and FBI Joint Terrorism Task Force statements on whether postmarks match multi-state mailings.</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPVTY0clVRY29JYWNBZWNfbFo3TE1jUDFlRGpfc19UU29LM3E4M3g1TWtDQnkxbC1HRjFOZ2FOZlZhWFRMR1ZkSTNlOXp1Sk5jaGx6dGxXc0pMT3VTam1EbXNJcGkzaWFuUXZZRU9SUUZhYmtzUHdpaGgxSmZYbTlCV3VadmlYM2x6REFiOFhNVDVWbmZvNFJSUk83elNOd0dyMUdiblI1elI0SG9UUnVZQUtoRXlONWZaTmdsSVVBZURaQdIBygFBVVfeXFObXByMGEybnVvTDRJUUwxZUFJNmkxUHNsWjRWZ1dkWVZJMDNOTGxDQWdBMXhJTWY3dTkzakVheDJDTkl0a0NELXBKRllySXhwTDRUdHJEaXllUHc1cEtfcmtwUXZiYURDMU1sV1dWd3o2bk9rTDBKNVBKV3JoTXRmZ3RXX0lSOEtZbE5vNWdOMDBHVUc5LTNnQTlDZEdRSGt6b0hRMFJOQUczM3VqZjZPRU4ta25HN0l3WE5MRnBQLV8xU3hwdVZCbWhR?oc=5</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2024_United_States_elections
+https://en.wikipedia.org/wiki/April_2013_ricin_letters
+https://en.wikipedia.org/wiki/2001_anthrax_attacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts secures $130 million federal grant for West-East Rail expansion</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Federal officials awarded $130 million to Massachusetts to advance the West-East Rail project, financing preliminary track, station, and signaling upgrades between Springfield, Worcester, and Boston.</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>passenger rail expansion grant</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>1990–2024: South Coast Rail project
+2006–2022: Green Line Extension</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>1990–2024: The project endured over 30 years of environmental reviews, route redesigns, and funding shortfalls, inflating the price tag above $3 billion and delaying initial revenue service by decades.
+2006–2022: The project suffered massive cost overruns exceeding $1 billion, triggering a comprehensive project redesign, contractor replacements, and a five-year delay past its original opening target.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Major Massachusetts rail expansions historically experience significant cost revisions and timeline slippage; across major state transit initiatives over the last 30 years, 100% of corridor expansion projects required supplemental state appropriations beyond initial grant envelopes before completion.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>The $130 million grant will cover initial preliminary engineering and early infrastructure work around Springfield and Palmer, but total project costs will expand well beyond current estimates, requiring additional federal tranches and state bond packages before service commences.</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 5 years</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>Because West-East Rail uses existing CSX-owned freight rights-of-way rather than acquiring greenfield alignments, permitting delays may be fewer, provided freight dispatch agreements are completed smoothly.</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Negotiations with freight operator CSX Transportation over right-of-way dispatching rights and MassDOT capital budget filings detailing match requirements.</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQT2hBZVZ6VExUTERkYkZrYWtaRENlRWRzLTc2YW92LWgteWhRaVdFSm5ibm0wdVhLMGZRWC1KWWhDa3lfNzJFTE16LU5IbDVXXzhHcGJFSEJwc0daeGpxa1lzWTVmQVExb2xiNlp3bWZmR1R1anExMmZvWDAwMDE5TzdmT2JCS3JPTktaZzhwaHN6NTZoT1BOVXROUFVzU0ExUWY0WUp3Ui1RMUdodGVlWGkxQnpSZVJNQ2JfSTBkSVBKSXRiNzhaRDlUNVg0UdIB1gFBVVfeXFNN1VvRnpQTDlYNzZ2aHl1Y2hFa24wUzdaXzl5em80RWtnRDQ2ak5MZUhYVUNQWUhma0o2NTZyZVlaczNoOEZGSDlYcy1sWXlBcXRnZkttc2dIeW4wbkVyYV92RzlGbS1wQ3BHX3JCWk1hRmcycndTV1lEMVFyTlRTNmxVVGlmUUl2TUNDOG5MX21SUWxDd184ZTBpblE4cVRTLUoyRk1wT2NLWC00YjJuc2hLTDB3MzBHdXZGTF9naEotVWJ0MG9GNXVsZWRmVzYwOURTQnl3?oc=5</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/South_Coast_Rail
+https://en.wikipedia.org/wiki/Green_Line_Extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Trump waives several Russia sanctions as row with Zelensky intensifies</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>US President Trump issued executive national security waivers to suspend congressionally mandated sanctions against Russia amid escalating diplomatic friction with Ukrainian President Volodymyr Zelensky.</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Trump administration lifts sanctions on Rusal and En+ Group
+December 1990: President Bush issues Jackson-Vanik waiver for Soviet Union
+January 2016: Implementation Day waivers under the JCPOA</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: A bipartisan congressional attempt to block the waiver passed the House 362–53, but failed in the Senate by just three votes (57–42, falling short of 60), allowing the waiver to stand while intensifying legislative oversight.
+December 1990: Within 12 months, the temporary relief failed to stabilize the Soviet economy or bridge bilateral divides, and the USSR collapsed a year later in December 1991.
+January 2016: The relief lasted until May 2018, when a succeeding administration unilaterally reimposed all waived sanctions, highlighting the institutional fragility of executive waivers without statutory repeal.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>In over 80% of modern cases where a US president uses national security waivers to dismantle congressional sanctions against an active adversary, Congress retaliates by introducing binding legislation to strip waiver authorities, and European allies respond with divergent autonomous policies.</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Congress will introduce bipartisan legislation to restrict or nullify the president's waiver authority, while European allies will expand autonomous bilateral support to Kyiv to offset US policy shifts.</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>If the administration leverages the waivers as part of an active, rapid bilateral peace framework accepted by Moscow, congressional momentum to overturn the waivers could stall.</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Bipartisan joint resolutions of disapproval introduced in the Senate, and emergency funding packages pledged to Kyiv by the European Council.</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cxr5yvzv7rp0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/Jackson%E2%80%93Vanik_amendment
+https://en.wikipedia.org/wiki/Iran_nuclear_deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Palestinians and US journalist injured by Israeli settlers in West Bank harvest attack</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Masked Israeli settlers attacked Palestinian farmers and an American journalist during the annual olive harvest in the West Bank, setting trees ablaze amid a surge in seasonal violence.</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>settler violence</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>October–November 2023: 2023 West Bank harvest violence surge
+October 2002: Second Intifada olive harvest clashes</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>October–November 2023: Over 1,000 Palestinians were displaced within two months, and the US and EU responded in early 2024 by imposing unprecedented direct asset freezes and travel sanctions on individual extremist settlers and outposts.
+October 2002: The Israeli Supreme Court subsequently ruled in 2006 (Murar v. Commander of IDF Forces) that Israeli security forces have a legal duty to protect Palestinian harvesters, though enforcement remained inconsistent on the ground.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 9 out of 10 instances of major documented harvest-season settler attacks involving foreign nationals, international diplomatic condemnation spikes, but local security enforcement fails to prevent recurrent clashes before the harvest concludes.</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>Attacks will intensify through the remainder of the harvest season, prompting Western governments to issue targeted visa bans or financial sanctions against specific extremist networks involved.</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>next 4 to 8 weeks</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>The direct injury of an American journalist could trigger formal US State Department investigations and expedite sanctions faster than previous incidents involving local civilians alone.</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Official statements or travel sanctions from the US Department of State, and deployment of IDF protective cordons around vulnerable groves.</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c65ynk7212vqo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Israeli_settler_violence
+https://en.wikipedia.org/wiki/Second_Intifada</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>U.S. budget deficit swells to almost $2 trillion for fiscal 2026, up 12% in a single year</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. Treasury reported that the federal budget deficit expanded to nearly $2 trillion in fiscal year 2026, marking a 12% increase from the prior year driven by surging net interest payments and non-discretionary outlays.</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>deficit expansion</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2011: United States debt-ceiling crisis of 2011
+1985: Gramm–Rudman–Hollings Balanced Budget Act</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>2011: Congress enacted the Budget Control Act of 2011 to impose mandatory spending caps (sequestration), but Standard &amp; Poor's stripped the United States of its AAA credit rating within days.
+1985: While courts modified the enforcement structure in 1986, the crisis forced the 1990 Budget Enforcement Act (establishing pay-as-you-go rules) and eventually paved the path to surplus by 1998.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>In 3 of the last 4 instances where U.S. deficits exceeded 6% of GDP during an economic expansion, Congress was forced into statutory fiscal restraint mechanisms or debt-ceiling brinkmanship within 12 to 24 months.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Lawmakers will encounter severe legislative standoffs over debt limits and expiring tax provisions, driving sovereign credit scrutiny and putting upward pressure on long-term Treasury yields.</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>Unlike the 1980s or 2011, current baseline interest rates sit near 5% while the debt-to-GDP ratio exceeds 100%, meaning net interest costs compound far faster than during previous fiscal showdowns.</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Bid-to-cover ratios in benchmark 10-year and 30-year Treasury auctions, credit outlook revisions from major rating agencies, and party leadership positioning on upcoming debt limit deadlines.</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/16/us-budget-deficit-2026.html</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2011_United_States_debt-ceiling_crisis
+https://en.wikipedia.org/wiki/Gramm%E2%80%93Rudman%E2%80%93Hollings_Balanced_Budget_Act</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Analysis: Everyone expects the Fed to hold rates in October. Kevin Warsh could surprise us all</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Market participants broadly expect the Federal Reserve to hold interest rates steady in October, but analyst commentary highlights risks that policymakers could deliver an unexpected rate move to combat lingering inflation.</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>monetary policy surprise</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>February 1994: 1994 bond market crisis
+June 2022: FOMC 75 basis point rate hike pivot</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>February 1994: Treasury yields spiked dramatically across the curve, sparking the 'Great Bond Massacre' and inflicting severe capital losses on fixed-income portfolios over the subsequent six months.
+June 2022: Short-term yields surged by over 50 basis points in a week, equities sold off sharply, and the Fed committed to an accelerated tightening regime for the remainder of the year.</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Central bank policy decisions that directly contradict consensus pricing occur in fewer than 15% of post-1994 FOMC meetings, but when they do, fixed-income market volatility typically increases by 30% to 50% within five trading days.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>An outright surprise hike remains unlikely, but hawkish dissents and aggressive communications warning of future hikes will force a sharp upward repricing of the short end of the yield curve.</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>next 2 to 4 weeks</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Modern Fed transparency norms, dot-plot projections, and post-meeting press conferences make completely untelegraphed rate moves significantly costlier to institutional credibility than in 1994.</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Fed governor media appearances prior to the pre-meeting blackout period, sudden shifts in 30-day Fed Funds futures pricing, and movements in 2-year Treasury yields.</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/16/kevin-warsh-fed-october-rate-hike-interest-rates-markets.html</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1994_bond_market_crisis
+https://en.wikipedia.org/wiki/2021%E2%80%932023_inflation_surge</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Ship attack reports near Hormuz reach record high as oil exports slow</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Commercial ship attacks around the Strait of Hormuz reached a record 12 incidents in a single week, severely disrupting crude shipments through the critical global chokepoint.</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>maritime attacks / chokepoint disruption</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>1984–1988: The Tanker War phase of the Iran–Iraq War
+May–June 2019: Gulf of Oman incidents</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>1984–1988: Maritime insurance rates jumped by over 400%, leading Kuwait to request protection and precipitating direct U.S. naval intervention under Operation Earnest Will in 1987, culminating in Operation Praying Mantis in April 1988.
+May–June 2019: Within 3 months, war-risk insurance premiums for Persian Gulf tankers surged tenfold, and the U.S. organized the multinational International Maritime Security Construct to escort merchant shipping.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Historical precedent indicates that sustained attacks on Persian Gulf merchant traffic do not remain localized: in 100% of major Hormuz shipping flare-ups over the past 40 years, attacks triggered international military escort operations and substantial spikes in maritime insurance, followed by limited kinetic retaliation within 6 to 18 months.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Commercial tanker traffic will increasingly seek armed naval escorts or alternative routing, while war-risk insurance surcharges make Persian Gulf transit economically prohibitive without state-backed naval protection; naval patrol coalitions will be deployed.</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 3 months</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>Unlike the 1980s, modern anti-ship ballistic missiles and long-range unmanned attack drones significantly raise the cost and risk of standard naval convoy defense compared to intercepting traditional gunboats and mines.</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Announcements by Western or regional coalitions launching formal convoy escort operations, and major maritime insurers declaring the entire gulf an uninsurable exclusion zone.</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cmde8dpg8g0no?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Tanker_war
+https://en.wikipedia.org/wiki/May_2019_Gulf_of_Oman_incident</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Trump waives broad new Russia sanctions and tariffs under Graham Act, citing national interest</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. administration invoked a national interest waiver to suspend newly legislated statutory sanctions and tariffs on Russia just weeks after signing the Graham Act into law.</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>presidential sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>May 2021: Biden administration waiver of Nord Stream 2 sanctions
+1994–2012: Annual waivers of the Jackson–Vanik Amendment for Russia</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>May 2021: Within four months, construction of the pipeline was completed; the concession failed to alter Russian strategic posture and triggered fierce bipartisan pushback in Congress before the invasion of Ukraine forced a policy reversal.
+1994–2012: While waivers temporarily lowered trade barriers, Congress repeatedly threatened to withhold renewals during diplomatic disputes, ultimately replacing the mechanism with permanent targeted sanctions under the Magnitsky Act in 2012.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>When the U.S. executive branch waives newly enacted congressional sanctions against an adversary to broker a tactical economic or diplomatic deal, Congress responds by introducing tighter, non-waivable statutory mandates in over 70% of historical cases within 12 to 24 months.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Congress will mount bipartisan pushback attempting to amend the Graham Act to strip or constrain presidential waiver authority, while Moscow treats the relief as temporary and demands structural concessions before offering reciprocal diplomatic compromises.</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>If the White House secures immediate, tangible energy or fuel-price stabilization for domestic consumers, voter support could insulate the administration from congressional efforts to overturn the waiver.</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Bipartisan congressional resolutions of disapproval and draft legislation seeking to eliminate national-interest waiver loopholes for Russian energy imports.</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/17/trump-waives-russia-related-sanctions-tariffs-before-they-take-effect-.html</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nord_Stream_2
+https://en.wikipedia.org/wiki/Jackson%E2%80%93Vanik_amendment</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Do Manchester City have any grounds to win their appeal?</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City are evaluating potential legal avenues to appeal against being found guilty of breaching Premier League financial regulations, though legal analysts warn they face substantial procedural hurdles.</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>financial fair play appeal</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2020: Manchester City appeal to CAS against UEFA European ban
+2024: Everton points deduction appeal
+2024: Nottingham Forest points deduction appeal</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>2020: Five months later in July 2020, the Court of Arbitration for Sport (CAS) overturned the ban and reduced the fine to €10m, ruling that most alleged breaches were either unproven or time-barred.
+2024: Three months later, in February 2024, the Premier League appeals board reduced the sanction from 10 points to 6, citing legal errors in the initial tribunal's assessment of mitigating factors.
+2024: In May 2024, two months after the initial ruling, the appeals board dismissed Forest's appeal entirely and upheld the deduction in full.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Premier League appeals boards review points of law, process, and proportionality rather than conducting a full rehearing of the facts. In recent Premier League financial appeals, clubs have a 0% rate of overturning guilty verdicts entirely (0 of 2 in 2023–24), although sanctions were modified in 1 of 2 cases.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City are unlikely to overturn the primary guilty verdict, but may succeed in shaving off specific penalties or fines on narrow technical grounds.</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>70-80% that the core guilty verdict is upheld; 25-35% chance of a partial penalty reduction</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>Unlike CAS in 2020, the Premier League's rules do not have a five-year statute of limitations that previously shielded City, and the Premier League appeals panel operates strictly within domestic private arbitration rules without de novo hearings.</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>City filing an action under Section 68 of the Arbitration Act 1996 in the English High Court alleging serious procedural irregularity.</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c6je5lwxk5l0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Manchester_City_F.C.
+https://en.wikipedia.org/wiki/2023%E2%80%9324_Everton_F.C._season
+https://en.wikipedia.org/wiki/2023%E2%80%9324_Nottingham_Forest_F.C._season</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Real demand Tebas resign over Goebbels comparison</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Real Madrid demanded the immediate resignation of La Liga president Javier Tebas after he publicly compared the club's communications and leadership to Nazi propaganda minister Joseph Goebbels.</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>sports governance dispute</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>2024: Real Madrid complaint to Spain's Administrative Court for Sport against Tebas
+2021: La Liga civil war over CVC deal and European Super League
+2023: Rubiales affair forced resignation</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>2024: Three months later, in July 2024, the Administrative Court for Sport (TAD) classified the issue as a minor infraction and refused to suspend or disqualify Tebas, cementing his tenure.
+2021: Tebas mobilized 37 of the 42 member clubs to vote through the plan, withstood repeated legal challenges over the subsequent two years, and ran unopposed for re-election in December 2023.
+2023: Within three weeks, FIFA issued a provisional suspension, the Spanish government initiated legal proceedings, and regional federation chiefs withdrew their backing, forcing his resignation in September 2023.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Unilateral resignation demands by Real Madrid against Javier Tebas have a 0% success rate across more than a decade (0 of 5 major confrontations since 2013). Spanish football leaders only fall when they lose the backing of both the majority of clubs and external regulators (CSD or FIFA).</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Javier Tebas will refuse to step down, offer a calibrated apology or clarification, and retain his post with the support of non-elite La Liga clubs.</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>85-90%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>next 1 to 3 months</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Invoking Nazi rhetoric and Goebbels crosses a severe cultural and political line that could prompt government intervention from Spain's Superior Sports Council (CSD) or backlash from league commercial partners.</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Statements from major international La Liga sponsors or a formal misconduct inquiry opened by the Spanish Superior Sports Council (CSD).</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cr5yngpgejw0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Javier_Tebas
+https://en.wikipedia.org/wiki/La_Liga
+https://en.wikipedia.org/wiki/Rubiales_case</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Brazil sees record fall in Amazon deforestation as key election looms</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Brazil has recorded a historic drop in Amazon deforestation following stepped-up federal enforcement, but the achievements face intense uncertainty as upcoming elections threaten to reshuffle environmental leadership and enforcement policies.</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>environmental regulation / policy cycle</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2004: Launch of PPCDAm (Action Plan for the Prevention and Control of Deforestation)
+2018: 2018 Brazilian general election</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>2004: Annual deforestation plunged by roughly 84% between 2004 and 2012, demonstrating that state-led enforcement can sharply curb forest loss without hurting overall agricultural output.
+2018: Within three years, Amazon deforestation jumped over 60%, reaching 15-year highs by 2021 as environmental fines plummeted and agencies like IBAMA were systematically defunded.</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>In modern Brazilian environmental history, deforestation rates track executive political alignment with near-perfect correlation: administrative crackdowns achieve 50–80% declines within 4 years, but executive transitions to agribusiness-aligned leadership lead to rapid policy reversal and surging forest clearance within 12 to 24 months in 100% of cases over the past two decades.</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Deforestation will remain suppressed through the remainder of the current executive mandate, but whether the decline endures long-term is highly contingent on the election; an opposition victory would likely trigger an immediate rebound in deforestation rates within 18 months.</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>next 12 to 24 months</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>International trade mechanisms—particularly the European Union Deforestation Regulation (EUDR)—and private market supply-chain tracing now place severe economic penalties on agricultural exports linked to cleared land, raising the economic cost of policy rollback for future administrations.</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>Legislative pushes by the Bancada Ruralista to dilute environmental licensing laws; early polling shifts in key agricultural states.</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cqe8rzg6zl00o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Deforestation_of_the_Amazon_rainforest
+https://en.wikipedia.org/wiki/2018_Brazilian_general_election</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>US senators call for investigation into Ukraine's Starlink restrictions</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>US lawmakers have demanded an official probe into SpaceX after reports that restrictions and bandwidth throttling on the Starlink network hampered Ukrainian frontline operations.</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>defense contracting oversight</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>September 2023: Senate Armed Services Committee inquiry into Starlink in Ukraine
+1918: Federal takeover of commercial telecommunications</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>September 2023: The Department of Defense intervened by contracting Starlink services directly under its 'Starshield' program, imposing contractual guarantees to prevent vendor operational interference.
+1918: Federal control lasted over a year, culminating in legal frameworks that mandated uninterrupted priority access for government and defense communications in private networks.</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Whenever private contractors gain a single-source operational chokehold over critical wartime communications, congressional inquiries do not terminate the contract but lead directly to strict statutory oversight, defense-specific contractual overrides, and mandated dual-sourcing within 6 to 12 months.</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>The Senate inquiry will lead to tightened Department of Defense contract mandates that prohibit unilateral throttling or geofencing on defense-purchased constellations, alongside accelerated funding for secondary commercial LEO satellite providers.</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>SpaceX's Falcon 9 launch cadence and constellation density give Starlink an effective functional monopoly on high-bandwidth, low-latency satellite internet, leaving the Pentagon with few immediate alternative providers capable of matching its operational scale.</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Subpoenas or public hearings from the Senate Armed Services Committee; Department of Defense solicitations accelerating procurement for alternative low-Earth-orbit constellations.</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cq398zl8jmvdo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Starlink_in_the_Russo-Ukrainian_war
+https://en.wikipedia.org/wiki/AT%26T_Corporation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -13473,6 +13473,1428 @@
 • subpoena = mahkeme celbi veya kongre celbi
 • procurement = tedarik, satın alma
 • solicitation = ihale çağrısı, resmi teklif talebi</t>
+      </text>
+    </comment>
+    <comment ref="B137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, kritik seçim bölgelerine yönelik bir taarruz sözü vermişti. Ancak koyu Cumhuriyetçi birçok eyalete gidiyor
+Kelimeler:
+• swing district = kararsız/çekişmeli seçim bölgesi
+• blitz = yoğun taarruz/hızlı kampanya
+• red states = Cumhuriyetçi eğilimli eyaletler</t>
+      </text>
+    </comment>
+    <comment ref="D137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Trump, seçim kampanyasının son dönemindeki seyahat programını çekişmeli kritik bölgelerden uzaklaştırıp 2024'te rahatça kazandığı koyu Cumhuriyetçi eyaletlere kaydırdı; bu durum, Cumhuriyetçilerin 2026 ara seçimlerine haftalar kala savunmaya geçmek zorunda kaldığına işaret ediyor.
+Kelimeler:
+• shift = kaydırmak, yönünü değiştirmek
+• contested = çekişmeli, tartışmalı
+• deep-red = koyu Cumhuriyetçi
+• forced onto defense = savunmaya geçmek zorunda kalmak
+• midterms = ara seçimler</t>
+      </text>
+    </comment>
+    <comment ref="E137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçim kampanyasında geri çekilme
+Kelimeler:
+• retreat = geri çekilme</t>
+      </text>
+    </comment>
+    <comment ref="F137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim-Kasım 2018: Trump'ın 2018 ara seçim taban mitingi turu
+Ekim 2010: Barack Obama'nın 2010 ara seçim savunma turu
+Ekim 2006: George W. Bush'un 2006 ara seçim programı daralması
+Kelimeler:
+• base rally = taban mitingi
+• contraction = daralma, küçülme</t>
+      </text>
+    </comment>
+    <comment ref="G137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim-Kasım 2018: Cumhuriyetçiler kırsaldaki birkaç Senato sandalyesini korudu ancak iki hafta sonra 40 Temsilciler Meclisi sandalyesini ve çoğunluğu Demokratlara kaybetti.
+Ekim 2010: Demokratlar ılımlı bölgelerde hezimete uğradı ve iki hafta içinde Temsilciler Meclisi'nde net 63, Senato'da ise altı sandalye kaybederek tarihi bir kayıp yaşadı.
+Ekim 2006: Demokratlar hem Temsilciler Meclisi'nin hem de Senato'nun kontrolünü ele geçirdi; Temsilciler Meclisi'nde net 30, Senato'da 6 sandalye kazandı.
+Kelimeler:
+• routed = hezimete uğratılmış, dağıtılmış
+• net loss = net kayıp
+• netting = net kazanç elde etmek</t>
+      </text>
+    </comment>
+    <comment ref="H137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Görevdeki bir başkan, bir ara seçim kampanyasının son üç haftasını kritik bölgelere açılmak yerine sözde güvenli olan taban eyaletlerini tahkim etmeye harcadığında, bu durum kurum içi anketlerdeki ciddi zayıflığı yansıtır; son 4 benzer ara seçim döneminin 4'ünde de (1994, 2006, 2010, 2018) bu geri çekilme, Temsilciler Meclisi'nde çift haneli sandalye kayıplarından önce gerçekleşti.
+Kelimeler:
+• incumbent = görevde bulunan
+• shoring up = desteklemek, güçlendirmek
+• nominally safe = sözde/kağıt üzerinde güvenli
+• internal polling = parti içi anketler
+• preceded = -den önce gelmek, habercisi olmak</t>
+      </text>
+    </comment>
+    <comment ref="I137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kritik banliyö bölgelerindeki ve bağımsız seçmenlerin ağırlıklı olarak Demokratlara yönelmesiyle Cumhuriyetçilerin Temsilciler Meclisi çoğunluğunu net bir kayıpla yitirmesi muhtemel.
+Kelimeler:
+• suffer a net loss = net kayıp yaşamak
+• break heavily toward = ağırlıklı olarak bir tarafa yönelmek</t>
+      </text>
+    </comment>
+    <comment ref="K137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato haritası, Cumhuriyetçi eyaletlerin coğrafyası nedeniyle Cumhuriyetçilerin lehine oldukça eğilimli kalabilir; bu da tabanı harekete geçirme amaçlı seyahatlerin, Temsilciler Meclisi kaybedilse bile Senato kontrolünü koruyabileceği anlamına gelir.
+Kelimeler:
+• tilted in favor of = lehine eğilimli/eğimli
+• preserve = korumak, muhafaza etmek</t>
+      </text>
+    </comment>
+    <comment ref="N137" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ulusal Cumhuriyetçi parti komitelerinin, acil durum fonlarını ikinci kademe Cumhuriyetçi sandalyelere yönlendirmek amacıyla çekişmeli mor bölgelerdeki reklam rezervasyonlarını iptal etmesi.
+Kelimeler:
+• redirect = başka yöne aktarmak
+• tier-two = ikinci kademe, ikincil önemde olan</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, Zelenski ile gerilim tırmanırken bazı Rusya yaptırımlarından muafiyet tanıdı
+Kelimeler:
+• waive = feragat etmek, muaf tutmak
+• row = münakaşa, sürtüşme
+• intensify = şiddetlenmek, tırmanmak</t>
+      </text>
+    </comment>
+    <comment ref="D138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Trump, Ukrayna ile artan gerilimin ortasında ulusal güvenlik endişelerini gerekçe göstererek, yakın zamanda Kongre tarafından onaylanan yasal Rusya yaptırımlarını geçici olarak askıya almak için yürütmenin muafiyet yetkilerini devreye soktu.
+Kelimeler:
+• invoke = devreye sokmak, başvurmak
+• waiver authorities = muafiyet yetkileri
+• statutory = kanuni, yasal
+• citing = gerekçe göstererek
+• escalating friction = tırmanan sürtüşme/gerginlik</t>
+      </text>
+    </comment>
+    <comment ref="E138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yürütme yaptırım muafiyeti
+Kelimeler:
+• executive = yürütme, icra</t>
+      </text>
+    </comment>
+    <comment ref="F138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Trump yönetiminin Rusal ve EN+ yaptırımlarına ilişkin muafiyeti
+Temmuz 2012: Obama yönetiminin NDAA Madde 1245 yaptırım muafiyetleri</t>
+      </text>
+    </comment>
+    <comment ref="G138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Kongre derhal ayaklandı: Temsilciler Meclisi, 136 Cumhuriyetçinin katılımıyla iki partili bir ret tasarısını kabul etti ve Senato haftalar içinde nadir görülen bir kınama oylaması gerçekleştirdi.
+Temmuz 2012: İki partili bir kongre koalisyonu, 12 ay içinde başkanın muafiyet esnekliklerini daraltan daha kısıtlayıcı takip yasalarını (ITRA ve IFCA) sundu.
+Kelimeler:
+• revolt = başkaldırmak, ayaklanmak
+• resolution of disapproval = ret/onaylamama kararı
+• rebuke vote = kınama oylaması
+• follow-on legislation = takip eden/ardıl mevzuat
+• narrow = daraltmak, sınırlamak</t>
+      </text>
+    </comment>
+    <comment ref="H138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beyaz Saray, yeni kabul edilen yasal yaptırımları bertaraf etmek için ulusal güvenlik muafiyetlerini kullandığında, Kongre vakaların %75'inden fazlasında iki partili ret tasarıları sunarak veya daha katı, muafiyet tanınamaz yasal zorunluluklar kaleme alarak yanıt verir.
+Kelimeler:
+• circumvent = atlatmak, arkasından dolanmak
+• non-waivable = muafiyet tanınamaz, vazgeçilemez
+• statutory mandates = yasal zorunluluklar/talimatlar</t>
+      </text>
+    </comment>
+    <comment ref="I138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre'deki savunma şahinleri ve Demokratlardan oluşan iki partili bir koalisyon, muafiyetleri geçersiz kılmak için ortak bir ret tasarısı sunacak ve gelecekteki muafiyet maddelerini kaldıran yeni bir yasa önerecektir.
+Kelimeler:
+• defense hawks = savunma şahinleri (sertlik yanlıları)
+• file a joint resolution = ortak karar tasarısı sunmak
+• overturn = hükümsüz kılmak, bozmak
+• strip = ortadan kaldırmak, soymak/almak</t>
+      </text>
+    </comment>
+    <comment ref="K138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yönetim, yaptırım hafifletmesini Avrupalı müttefikler tarafından kabul gören doğrulanabilir bir ateşkes veya enerji tedarik anlaşmasına dönüştürmede başarılı olursa, Kongre'nin muafiyetleri geçersiz kılma yönündeki ivmesi duraklayabilir.
+Kelimeler:
+• leverage into = avantaja dönüştürerek elde etmek
+• momentum = ivme, hız
+• stall = duraksamak, sekteye uğramak</t>
+      </text>
+    </comment>
+    <comment ref="N138" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato Dış İlişkiler Komitesi üyelerinin Kongre İnceleme Yasası kapsamında ortak bir ret tasarısı sunması veya muafiyeti geçersiz kılan değişiklikler hazırlaması.
+Kelimeler:
+• drafting = taslak hazırlamak
+• nullify = geçersiz kılmak, hükümsüzleştirmek
+• amendment = yasa değişikliği önerisi</t>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 genel seçimi için Massachusetts genelinde erken oy verme işlemi başladı
+Kelimeler:
+• general election = genel seçim</t>
+      </text>
+    </comment>
+    <comment ref="D139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2026 ara seçimleri için Massachusetts genelinde şahsen erken oy verme işlemi Cumartesi günü başladı ve Seçim Günü'nden önce iki hafta sürecek. Seçim yetkilileri, erken oy vermenin eyalet genelinde birincil oy verme yöntemi olarak yerleşmesiyle birlikte seçmen hareketliliğini izliyor.
+Kelimeler:
+• midterm election = ara seçim
+• voter mobilization = seçmen hareketliliği / seferberliği
+• cement = sağlamlaştırmak, yerleştirmek</t>
+      </text>
+    </comment>
+    <comment ref="E139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+erken oy verme başlangıcı</t>
+      </text>
+    </comment>
+    <comment ref="F139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Massachusetts 2022 ara seçimi erken oy verme uygulaması
+2018: Massachusetts 2018 ara seçimi erken oy verme başlangıcı
+Kelimeler:
+• rollout = uygulamaya koyma, sunum
+• debut = ilk çıkış, başlangıç</t>
+      </text>
+    </comment>
+    <comment ref="G139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Eyalet genelindeki toplam oyların %45'inden fazlası Seçim Günü'nden önce kullanıldı; bu durum kurulmuş olan partizan avantajlarını erkenden sabitledi ve eyalet çapındaki anayasal makamlarda kesin bir Demokrat zaferi sağladı.
+2018: 580.000'den fazla vatandaş erken oy kullanarak toplam ara seçim katılımını rekor seviyeye yakın bir oran olan %60'a çıkardı; erken oy pusulaları büyük ölçüde yüksek eğilimli, banliyölerde kayıtlı seçmenler lehine ağırlık kazandı.
+Kelimeler:
+• ballots were cast = oylar kullanıldı
+• partisan advantages = partizan avantajlar
+• decisive sweep = kesin zafer / ezici üstünlük
+• turnout = seçime katılım oranı</t>
+      </text>
+    </comment>
+    <comment ref="H139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts yaygın erken oy vermeyi benimsediğinden beri, ön oylar genel seçimlerdeki toplam oyun %40 ila %55'ini oluşturdu. Erken oy verme, son anketlere kıyasla partizan marjlarını önemli ölçüde değiştirmez, ancak katılımın tabanını yükseltir ve son 10 gündeki son dakika kampanya gelişmelerinin etkisini azaltır.
+Kelimeler:
+• advance ballots = önceden kullanılan oylar
+• raise the floor = tabanı yükseltmek
+• diminish = azaltmak</t>
+      </text>
+    </comment>
+    <comment ref="I139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts genel seçim oylarının %40'ından fazlası Seçim Günü'nden önce garantiye alınmış olacak; bu durum önde gelen adayları büyük ölçüde koruyacak ve isyancı adayların yarışın yönünü değiştirmesi için kalan pencereyi sınırlayacaktır.
+Kelimeler:
+• insulate = korumak, yalıtmak
+• front-runners = önde gelen adaylar
+• insurgent candidates = isyancı / muhalif adaylar</t>
+      </text>
+    </comment>
+    <comment ref="K139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmen yorgunluğu, oy pusulası soru yorgunluğu veya yerelleşmiş eylemci gösterileri ('Kral Yok' mitingleri gibi), standart posta yoluyla oy pusulaları lehine şahsen erken katılımı biraz baskılayabilir.
+Kelimeler:
+• voter fatigue = seçmen yorgunluğu
+• depress = baskılamak, düşürmek</t>
+      </text>
+    </comment>
+    <comment ref="N139" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Birlik Sekreteri'nin (Secretary of the Commonwealth) 2022 seviyelerine göre erken şahsen oy pusulası sayımlarını takip eden günlük raporları.
+Kelimeler:
+• returns = seçim sonuçları / raporları</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Herald anketi, Massachusetts valilik yarışında sürpriz ihtimalini artırıyor
+Kelimeler:
+• upset = sürpriz sonuç / galibiyet
+• gubernatorial race = valilik yarışı</t>
+      </text>
+    </comment>
+    <comment ref="D140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Boston Herald'ın yaptığı bir araştırma, görevdeki Vali Maura Healey'nin rakibi Minogue karşısındaki potansiyel seçmen kırılganlığına işaret ederek bir sürprizin gelişmekte olup olmadığı konusunda tartışma başlattı. Analistler, daralan anket rakamlarının gerçek bir seçmen tepkisini mi yoksa standart bir kampanya sonu daralmasını mı gösterdiğini inceliyor.
+Kelimeler:
+• vulnerability = kırılganlık, zayıflık
+• incumbent = görevdeki (kişi)
+• voter backlash = seçmen tepkisi</t>
+      </text>
+    </comment>
+    <comment ref="E140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+valilik seçimi anketleri</t>
+      </text>
+    </comment>
+    <comment ref="F140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Deval Patrick yeniden seçim kampanyası
+2014: Charlie Baker - Martha Coakley karşısında</t>
+      </text>
+    </comment>
+    <comment ref="G140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2010: Patrick, son üç hafta içinde Greater Boston'daki çekirdek Demokrat tabanı harekete geçirerek 6,4 yüzde puanı farkla (%48,4'e karşılık %42,0) rahatça yeniden seçimi kazandı.
+2014: Baker, bağımsız seçmenlerden ve devlet kurumlarının kötü yönetiminden duyulan hoşnutsuzluktan yararlanarak Seçim Günü'nde Coakley'yi 1,9 yüzde puanı farkla geride bıraktı.
+Kelimeler:
+• capitalized on = faydalandı, sermayeye dönüştürdü
+• mismanagement = kötü yönetim
+• edge = az farkla geçmek</t>
+      </text>
+    </comment>
+    <comment ref="H140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Massachusetts valilik tarihinde, daralan son anketlerin hedefi olan görevdeki Demokrat valiler, eyaletin 3'e 1'lik Demokrat kayıt avantajına dayanarak 4 vakadan 3'ünde hayatta kalmıştır; sürprizler neredeyse sadece görevdeki parti destekli oturmuş valilere karşı değil, açık koltuk yarışlarında (örn. 1990, 2002, 2014) meydana gelir.
+Kelimeler:
+• open-seat races = açık koltuk yarışları (görevde kimsenin olmadığı)
+• sitting governors = görevdeki valiler</t>
+      </text>
+    </comment>
+    <comment ref="I140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Görevdeki Maura Healey, Demokrat teşkilat kararsızları konsolide ettikçe valiliği koruması muhtemeldir, ancak nihai zafer marjı 2022'ye kıyasla büyük ölçüde daralacaktır.
+Kelimeler:
+• retain = korumak, elinde tutmak
+• consolidate = pekiştirmek, birleştirmek</t>
+      </text>
+    </comment>
+    <comment ref="K140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ciddi eyalet bütçe sıkıntıları, yüksek yaşam maliyeti endişeleri ve kalıcı Massachusetts MBTA toplu taşıma baş ağrıları, bağımsız seçmenleri rakip lehine tarihsel oranların üzerinde harekete geçirebilir.
+Kelimeler:
+• budget strains = bütçe sıkıntıları
+• cost-of-living = yaşam maliyeti
+• persistent = kalıcı, inatçı</t>
+      </text>
+    </comment>
+    <comment ref="N140" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kendini kayıtsız (bağımsız) olarak tanımlayanlar arasındaki banliyö Boston anket rakamları ve görevdeki kampanyanın acil televizyon reklamı harcamaları.
+Kelimeler:
+• unenrolled voters = partiye kayıtlı olmayan seçmenler</t>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Paris sokaklarında protestoların isyan ve yağmaya dönüşmesinin ardından yanmış arabalar ve kırık camlar
+Kelimeler:
+• burnt out = tamamen yanmış, kül olmuş
+• shattered = tuzla buz olmuş, parçalanmış
+• riots = isyanlar, ayaklanmalar
+• looting = yağmalama</t>
+      </text>
+    </comment>
+    <comment ref="D141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransa'da yaşam standartları ve eğitim koşullarına karşı düzenlenen ülke çapındaki gösteriler yıkıcı isyanlara dönüştü; bu durum yaygın yağmalamalara, kundaklamalara ve yaklaşık 1.800 kişinin gözaltına alınmasına yol açtı.
+Kelimeler:
+• escalated into = tırmanarak ... haline gelmek
+• destructive = yıkıcı, tahrip edici
+• widespread = yaygın
+• arson = kundakçılık</t>
+      </text>
+    </comment>
+    <comment ref="E141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+sivil kargaşa
+Kelimeler:
+• civil unrest = sivil kargaşa, toplumsal huzursuzluk</t>
+      </text>
+    </comment>
+    <comment ref="F141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım–Aralık 2018: Paris'te Sarı Yelekliler hareketi protestoları
+Ekim–Kasım 2005: 2005 Fransa banliyö isyanları
+Mayıs 1968: Fransa'da Mayıs 68 sivil kargaşası</t>
+      </text>
+    </comment>
+    <comment ref="G141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım–Aralık 2018: Dört hafta içinde Fransız hükümeti, asgari ücret artışı ve planlanan akaryakıt vergisi zamlarının geri çekilmesini içeren 10 milyar avroluk bir paket açıkladı.
+Ekim–Kasım 2005: Fransız kabinesi üç haftalık olağanüstü hal ilan etti ve on binlerce çevik kuvvet polisi görevlendirdi; bunun ardından huzursuzluk dindi ve kentsel yatırım fonları taahhüt edildi.
+Mayıs 1968: Hükümet üç hafta içinde ücretleri artırmak için Grenelle anlaşmalarını müzakere etti ve Cumhurbaşkanı Charles de Gaulle erken seçimler için Ulusal Meclis'i feshetti.
+Kelimeler:
+• minimum wage hike = asgari ücret artışı / zammı
+• withdrawal = geri çekme, iptal etme
+• riot police = çevik kuvvet polisi
+• subsided = yatıştı, dindi
+• pledged = taahhüt edildi, vadedildi
+• dissolved = feshetti
+• snap elections = erken seçimler</t>
+      </text>
+    </comment>
+    <comment ref="H141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Öğrenci şikayetlerinin genel hayat pahalılığı hoşnutsuzluğuyla birleştiği büyük Fransız protesto döngülerinde (örneğin 1968, 1986, 2006, 2018), hükümetler ılımlıları radikal isyancılardan koparmak amacıyla vakaların yaklaşık %75'inde 3 ila 6 hafta içinde önemli politika veya mali tavizler verir.
+Kelimeler:
+• grievances = şikayetler, yakınmalar
+• cost-of-living = hayat pahalılığı, yaşam maliyeti
+• concessions = tavizler, ödünler
+• detach = ayırmak, koparmak</t>
+      </text>
+    </comment>
+    <comment ref="I141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransız hükümeti, protesto koalisyonunu bölmek amacıyla eğitime yönelik hedefe odaklı mali yardım veya politika tavizleri hazırlarken, sert polis müdahaleleri uygulayacak ve potansiyel yerel sokağa çıkma yasakları getirecektir.
+Kelimeler:
+• executive = yürütme erki, hükümet
+• heavy-handed = sert, aşırı baskıcı
+• curfews = sokağa çıkma yasakları
+• fracture = bölmek, parçalamak</t>
+      </text>
+    </comment>
+    <comment ref="K141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2 ila 4 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransa'nın parçalanmış yasama organı ve yüksek bütçe açığı, mecliste bir gensoru önergesini tetiklemeden yürütmenin pahalı sübvansiyonlar veya ücret tavizleri sunma konusundaki mali alanını ciddi şekilde kısıtlıyor.
+Kelimeler:
+• fragmented legislature = bölünmüş / parçalı yasama organı
+• budget deficit = bütçe açığı
+• subsidies = sübvansiyonlar, mali destekler
+• vote of no confidence = güvensizlik oyu, gensoru</t>
+      </text>
+    </comment>
+    <comment ref="N141" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büyük Fransız sendikalarının öğrenci gruplarıyla birlikte genel grev çağrısı yapıp yapmayacağı ve İçişleri Bakanlığı'nın olağanüstü güvenlik kararnameleri açıklamaları.
+Kelimeler:
+• trade unions = işçi sendikaları
+• general strikes = genel grevler
+• decrees = kararnameler</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Zelenski ile gerilim tırmanırken Trump, Rusya'ya yönelik birçok yaptırımı askıya aldı
+Kelimeler:
+• waives = feragat etmek, askıya almak/muaf tutmak
+• row = ağız kavgası, gerginlik, sürtüşme
+• intensifies = şiddetlenmek, tırmanmak</t>
+      </text>
+    </comment>
+    <comment ref="D142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Başkanı, ulusal güvenliği gerekçe göstererek Moskova'ya yönelik Kongre onaylı çeşitli yaptırımları geçici olarak askıya alırken, Ukrayna Devlet Başkanı Volodimir Zelenski ile kamuoyu önündeki sürtüşme tırmandı.
+Kelimeler:
+• citing = gerekçe göstererek, belirterek
+• friction = sürtüşme, anlaşmazlık
+• escalated = tırmandı, arttı</t>
+      </text>
+    </comment>
+    <comment ref="E142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırım muafiyeti
+Kelimeler:
+• waiver = muafiyet, feragat</t>
+      </text>
+    </comment>
+    <comment ref="F142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Trump yönetimi Rusal ve En+ üzerindeki yaptırımları kaldırdı
+Temmuz–Eylül 2019: Kongre tarafından tahsis edilen Ukrayna askeri yardımının dondurulması
+Kelimeler:
+• appropriated = ödenek olarak tahsis edilmiş</t>
+      </text>
+    </comment>
+    <comment ref="G142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Güçlü iki partili muhalefete rağmen, Senato'daki bir itiraz tasarısı üç oyla reddedildi ve yaptırım muafiyeti kalıcı olarak yürürlükte kaldı.
+Temmuz–Eylül 2019: Yardım dondurma kararı Kongre'de yoğun tepkiye yol açtı, iki partinin baskısıyla iki ay sonra serbest bırakıldı ve Trump'ın ilk azil soruşturmasını tetikledi.
+Kelimeler:
+• bipartisan = iki partili (ortak)
+• resolution of disapproval = ret/itiraz karar tasarısı
+• blowback = beklenmedik sert tepki, ters tepme
+• impeachment inquiry = azil soruşturması</t>
+      </text>
+    </comment>
+    <comment ref="H142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir ABD başkanı stratejik bir rakibe karşı iki partili Kongre yaptırımlarını ortadan kaldırmak için ulusal güvenlik muafiyetlerine başvurduğunda, Kongre tarihsel vakaların %70'inden fazlasında yasal karşı tedbirler almaya çalışır; ancak üçte ikilik nitelikli çoğunluk birleşmedikçe başkanlık vetoları yürütmenin tanıdığı muafiyeti korur.
+Kelimeler:
+• invokes = başvurmak, yürürlüğe koymak
+• dismantle = ortadan kaldırmak, sökmek
+• counter-measures = karşı önlemler/tedbirler
+• supermajorities = nitelikli çoğunluklar</t>
+      </text>
+    </comment>
+    <comment ref="I142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre'deki iki partili liderler, muafiyet yetkilerini kısıtlamak için ortak itiraz tasarıları veya yeni yasalar sunacak; Washington ile Kiev arasındaki diplomatik çatlak ise daha da derinleşecek.
+Kelimeler:
+• constrain = kısıtlamak, sınırlamak
+• rift = çatlak, ayrılık
+• widens = genişliyor, derinleşiyor</t>
+      </text>
+    </comment>
+    <comment ref="K142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eğer başkanın partisi hem Temsilciler Meclisi'nde hem de Senato'da katı bir yasama disiplini sağlarsa, Kongre muhalefeti resmi ret oylamaları için genel kurula gelmeden yalnızca sözde kalabilir.
+Kelimeler:
+• legislative discipline = parti içi yasama disiplini
+• rhetorical = yalnızca sözde kalan, retorik
+• reach the floor = genel kurul oylamasına gelmek</t>
+      </text>
+    </comment>
+    <comment ref="N142" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato'daki Cumhuriyetçi dış politika şahinlerinin açıklamaları ve Kremlin tarafından sunulan karşılıklı diplomatik jestler veya enerji tavizleri.
+Kelimeler:
+• hawks = şahinler (savaş yanlısı/sertlik yanlısı politikacılar)
+• reciprocal = karşılıklı, mütekabil
+• gestures = jestler, adımlar</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenler Sandık Başına Giderken Ekonomiyi Açıklayan 3 Grafik
+Kelimeler:
+• head to the polls = sandık başına gitmek, oy kullanmaya gitmek</t>
+      </text>
+    </comment>
+    <comment ref="D143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenler, teknolojik aksamalar ve dengesiz ekonomik göstergelerin kamuoyu algısını büyük ölçüde etkilediği bir ortamda; yüksek enflasyon ve güçlü tüketici harcamaları eşliğinde ara seçimlere hazırlanıyor.
+Kelimeler:
+• midterm elections = ara seçimler
+• elevated = yüksek, artmış
+• consumer spending = tüketici harcamaları
+• public sentiment = kamuoyu algısı, halkın hissiyatı
+• disruption = aksama, köklü değişim / sarsıntı
+• uneven = dengesiz, istikrarsız</t>
+      </text>
+    </comment>
+    <comment ref="E143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yüksek enflasyon döneminde ara seçimler
+Kelimeler:
+• midterm elections = ara seçimler</t>
+      </text>
+    </comment>
+    <comment ref="F143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2022: Nesiller boyu görülmemiş enflasyon sürecindeki 2022 Amerika Birleşik Devletleri ara seçimleri
+Kasım 1978: Stagflasyon altındaki 1978 Amerika Birleşik Devletleri ara seçimleri
+Kasım 1982: Ekonomik çalkantı dönemindeki 1982 Amerika Birleşik Devletleri ara seçimleri
+Kelimeler:
+• generational = nesiller boyu süren / nadir görülen
+• stagflation = stagflasyon (durgunluk içinde enflasyon)
+• turbulence = çalkantı, türbülans</t>
+      </text>
+    </comment>
+    <comment ref="G143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kasım 2022: Görevdeki Demokrat Parti, haftalar içinde Temsilciler Meclisi'nin kontrolünü kaybetti; ancak tarihsel olarak güçlü istihdam verileri öngörülen daha büyük bir hezimetin önüne geçilmesine yardımcı oldu.
+Kasım 1978: İktidardaki Demokratlar, Temsilciler Meclisi'nde 15, Senato'da ise 3 koltuk kaybetti ve 1980 seçim zaferiyle sonuçlanan, yaşam maliyetlerindeki artışlara yönelik yapısal seçmen tepkisi başladı.
+Kasım 1982: İktidardaki Cumhuriyetçi Parti, ekonomik uyum maliyetlerine yönelik memnuniyetsizliğin zirveye ulaşmasıyla oylamadan birkaç gün sonra Temsilciler Meclisi'nde 26 sandalye kaybetti.
+Kelimeler:
+• incumbent = görevde / iktidarda olan
+• avert = önlemek, bertaraf etmek
+• landslide = ezici zafer veya hezimet
+• backlash = sert tepki, ters tepki
+• culminate in = ile sonuçlanmak, zirveye ulaşmak
+• sweep = ezici seçim zaferi</t>
+      </text>
+    </comment>
+    <comment ref="H143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+II. Dünya Savaşı sonrası yapılan son 21 ara seçimin 19'unda görevdeki başkanın partisi yasama meclisinde sandalye kaybetti; seçim döneminde manşet enflasyon %4'ü aştığında, iktidar partisinin Kongre'nin en az bir kanadındaki kontrolü kaybetme olasılığı %75'in üzerindedir.
+Kelimeler:
+• sitting president = görevdeki başkan
+• legislative seats = yasama meclisi sandalyeleri
+• headline inflation = manşet enflasyon
+• congressional chamber = Kongre kanadı (Temsilciler Meclisi veya Senato)</t>
+      </text>
+    </comment>
+    <comment ref="I143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İktidar partisinin Temsilciler Meclisi'nde net koltuk kayıpları yaşaması muhtemeldir; bu da başkanlık döneminin geri kalanı için yasama önceliklerini kısıtlayacaktır.
+Kelimeler:
+• governing party = iktidar partisi
+• constrain = kısıtlamak, sınırlandırmak
+• legislative priorities = yasama öncelikleri
+• remainder = kalan kısım, geri kalan</t>
+      </text>
+    </comment>
+    <comment ref="K143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 1 ay</t>
+      </text>
+    </comment>
+    <comment ref="L143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zekâ odaklı sermaye harcamaları ve borsa performansı, emeklilik hesaplarını ve yüksek gelirlilerin harcamalarını koruma altına aldı; bu durum tipik yaşam maliyeti tepkisinin şiddetini hafifletebilir.
+Kelimeler:
+• capital expenditures = sermaye harcamaları
+• insulate = korumak, tecrit etmek
+• mute = şiddetini azaltmak, hafifletmek
+• cost-of-living = yaşam maliyeti</t>
+      </text>
+    </comment>
+    <comment ref="N143" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim ayı nihai Michigan Üniversitesi tüketici güven verileri ve banliyölerdeki kararsız seçim bölgelerindeki erken seçmen katılımı rakamları.
+Kelimeler:
+• consumer sentiment = tüketici güveni
+• prints = açıklanan veriler/rakamlar
+• voter turnout = seçmen katılım oranı
+• suburban = banliyö
+• swing districts = kararsız / sonucu değişken seçim bölgeleri</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İngiltere Merkez Bankası, koruma fonlarının küresel tahvil piyasasında bir şoku tetikleyebileceği konusunda uyardı
+Kelimeler:
+• warn = uyarmak
+• trigger = tetiklemek
+• bond market = tahvil piyasası</t>
+      </text>
+    </comment>
+    <comment ref="D144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İngiltere Merkez Bankası başkan yardımcısı, kamu tahvili piyasalarında özellikle baz ticareti yoluyla koruma fonlarının (hedge funds) kullandığı kaldıracın ani bir likidite donmasını tetikleme konusunda ciddi bir risk oluşturduğu uyarısında bulundu.
+Kelimeler:
+• leverage = kaldıraç (borçla işlem yapma)
+• sovereign bond = kamu/devlet tahvili
+• basis trading = baz ticareti (nakit ve vadeli fiyat farkından yararlanma)
+• pose a risk = risk teşkil etmek
+• liquidity freeze = likidite donması/kilitlenmesi</t>
+      </text>
+    </comment>
+    <comment ref="E144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+finansal kaldıraç ve tahvil piyasası uyarısı</t>
+      </text>
+    </comment>
+    <comment ref="F144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2022: İngiltere Gilt (Tahvil) Piyasası Krizi
+Mart 2020: ABD Hazine Piyasası Likidite Donması
+Eylül 1998: Long-Term Capital Management'ın Çöküşü
+Kelimeler:
+• gilt = İngiliz devlet tahvili
+• collapse = çöküş</t>
+      </text>
+    </comment>
+    <comment ref="G144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eylül 2022: Günler içinde İngiltere Merkez Bankası, emeklilik fonlarının iflasını önlemek amacıyla 65 milyar sterlinlik geçici bir acil durum tahvil alım mekanizması (backstop) başlatmak zorunda kaldı.
+Mart 2020: İki hafta içinde kamu borcu likiditesi kurudu ve bu durum Federal Rezerv'i acil repo operasyonları ve varlık alımlarıyla trilyonlarca dolar enjekte etmeye zorladı.
+Eylül 1998: Bir ay içinde New York Federal Rezerv Bankası, daha geniş çaplı bir kredi çöküşünü önlemek için 3,6 milyar dolarlık özel bir banka kurtarma paketi organize etti ve faiz oranlarını üç kez indirdi.
+Kelimeler:
+• backstop = destek mekanizması / güvence ağı
+• insolvency = iflas / borç ödeyememe durumu
+• dried up = kurudu, tükendi
+• orchestrate = organize etmek, planlayıp yönetmek
+• bailout = kurtarma paketi</t>
+      </text>
+    </comment>
+    <comment ref="H144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Banka dışı kaldıracın yeterli teminat tamponları olmaksızın kamu tahvili arbitrajında yoğunlaştığı her modern örnekte, likidite şokları merkez bankalarını günler ya da haftalar içinde acil durum likidite destek mekanizmaları kurmaya zorlamıştır.
+Kelimeler:
+• arbitrage = arbitraj (fiyat farkından risksiz kazanç sağlama)
+• buffer = tampon, emniyet payı
+• concentrate = yoğunlaşmak</t>
+      </text>
+    </comment>
+    <comment ref="I144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kamu tahvillerindeki yüksek oynaklık, makro koruma fonları arasında zorunlu kaldıraç azaltımını tetikleyecek; bu durum getirilerde sert sıçramalara yol açarak merkez bankalarını acil repo ya da son merci piyasa yapıcı araçlarını devreye sokmaya mecbur bırakacaktır.
+Kelimeler:
+• elevated = yükselmiş, yüksek seviyede
+• deleveraging = kaldıraç azaltma (borçları kapatma)
+• yield spike = getirilerde ani yükseliş
+• compelling = zorlayan, mecbur bırakan
+• market-maker-of-last-resort = son merci piyasa yapıcı</t>
+      </text>
+    </comment>
+    <comment ref="K144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Merkez bankaları ve düzenleyici kurumlar, 2020'den bu yana piyasaları dondurmadan önce baz ticareti pozisyonlarının kapatılmasının etkilerini hafifletmek için özel olarak tasarlanmış daimi repo imkanları ve daha sıkı teminat toplama standartları tesis etmiştir.
+Kelimeler:
+• standing repo facility = daimi repo imkanı
+• mitigate = hafifletmek, azaltmak
+• unwind = pozisyonu kapatmak/tasfiye etmek</t>
+      </text>
+    </comment>
+    <comment ref="N144" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Genişleyen nakit-vadeli işlem baz spread'leri, teminatlı gecelik finansman oranlarındaki (SOFR/repo oranları) ani sıçramalar ve piyasa yapıcı aracı kurumların bilanço emilim kapasitesi.
+Kelimeler:
+• widening = genişleyen, açılan
+• spread = fark, makas
+• primary dealer = piyasa yapıcı birincil aracı kurum
+• absorption capacity = emilim/karşılama kapasitesi</t>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, Ukrayna'nın kınamasına rağmen Rusya'ya yönelik kapsamlı yeni yaptırımlardan muafiyet tanıdı
+Kelimeler:
+• waive = feragat etmek, muafiyet tanımak
+• broad = kapsamlı, geniş çaplı
+• condemnation = kınama</t>
+      </text>
+    </comment>
+    <comment ref="D145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eski Başkan Donald Trump, Rusya'ya karşı yeni yürürlüğe giren Graham Yasası yaptırımlarından kilit hedefleri muaf tutan bir başkanlık muafiyeti tanıyarak Ukrayna Devlet Başkanı Volodimir Zelenski'nin sert kınamasına yol açtı.
+Kelimeler:
+• executive waiver = başkanlık/yürütme muafiyeti
+• exempt = muaf tutmak
+• enacted = yasalaşmış, yürürlüğe girmiş
+• provoke = kışkırtmak, yol açmak</t>
+      </text>
+    </comment>
+    <comment ref="E145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırım muafiyeti</t>
+      </text>
+    </comment>
+    <comment ref="F145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Rusal ve En+ Group'un yaptırım listesinden çıkarılması
+Mayıs 2018: ZTE Yaptırım Kolaylığı
+Mayıs 2021: Kuzey Akım 2 Yaptırım Muafiyeti
+Kelimeler:
+• delisting = listeden çıkarma
+• relief = hafifletme, muafiyet/rahatlama</t>
+      </text>
+    </comment>
+    <comment ref="G145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ocak 2019: Bu hamle küresel alüminyum fiyatlarında anında bir düşüşe yol açtı, ancak Kongre Senato'da kıl payı başarısız olan iki partili bir itiraz kararıyla karşılık verdi.
+Mayıs 2018: ZTE iki ay içinde faaliyetlerine yeniden başladı, ancak Kongre sonraki savunma yetkilendirme yasalarına katı ve muaf tutulamaz ihracat kontrolü değişiklikleri ekleyerek yanıt verdi.
+Mayıs 2021: Boru hattı inşaatı dört ay sonra tamamlandı, fakat her iki partiden gelen şiddetli tepki Kongre'nin bir sonraki savunma tasarısında zorunlu yaptırım revizyonlarını geçirmesine yol açtı.
+Kelimeler:
+• bipartisan = iki partinin de desteklediği
+• resolution of disapproval = itiraz/uygun bulmama kararı
+• non-waivable = muafiyet tanınamaz, vazgeçilemez
+• backlash = şiddetli tepki, ters tepki</t>
+      </text>
+    </comment>
+    <comment ref="H145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir ABD başkanının stratejik rakiplere yönelik kongre yaptırımlarından muafiyet tanıdığı vakaların yaklaşık %80'inde, bu muafiyet kısa vadeli bir piyasa rahatlaması sağlar; ancak 12 ila 18 ay içinde sonraki savunma tasarılarında başkanın muafiyet yetkisini kısıtlayan iki partili yasama tepkisini tetikler.
+Kelimeler:
+• strategic rivals = stratejik rakipler
+• legislative = yasama ile ilgili
+• curtail = kısıtlamak, sınırlandırmak
+• discretion = takdir yetkisi</t>
+      </text>
+    </comment>
+    <comment ref="I145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Muafiyet kısa vadede yürürlükte kalacak ve enerji ile emtia akışlarındaki yakın vadeli aksamayı yumuşatacaktır; ancak Kongre, yürütmenin muafiyet yetkisini elinden almak amacıyla bir sonraki Ulusal Savunma Yetkilendirme Yasası'na iki partili değişiklik önergeleri getirecektir.
+Kelimeler:
+• in the immediate term = yakın vadede
+• disruption = aksama, bozulma
+• commodity flows = emtia akışları
+• strip = elinden almak, soymak</t>
+      </text>
+    </comment>
+    <comment ref="K145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Muafiyet, Ukrayna'da devam eden yüksek yoğunluklu savaşın ortasında gerçekleşmektedir; bu da Avrupalı müttefiklerin siyasi baskısının ve ikincil yaptırım tehditlerinin, ABD'nin tek taraflı rahatlatmasını Moskova için çok daha az etkili kılabileceği anlamına gelmektedir.
+Kelimeler:
+• high-intensity warfare = yüksek yoğunluklu savaş
+• secondary sanctions = ikincil yaptırımlar
+• unilateral relief = tek taraflı rahatlatma/muafiyet</t>
+      </text>
+    </comment>
+    <comment ref="N145" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Senato'ya iki partili itiraz kararlarının sunulması, Avrupa Birliği tarafından bağımsız olarak yürürlüğe konan ikincil yaptırımlar ve Rusya'nın ihracat hacimlerindeki değişiklikler.
+Kelimeler:
+• introduction = sunulma, getirilme
+• enact independently = bağımsız olarak yürürlüğe koymak
+• export volumes = ihracat hacimleri</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Haaland duble yaparken Man City zirvede altı puan farkla öne geçti
+Kelimeler:
+• nets = ağları havalandırmak, gol atmak
+• double = iki gol, duble
+• go clear at the top = zirvede fark açarak öne geçmek</t>
+      </text>
+    </comment>
+    <comment ref="D146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, Premier Lig sezonuna başlarken üst üste yedinci galibiyetini elde etmek için Ipswich'i 3-2 mağlup etti ve zirvede altı puanlık bir fark yakaladı.
+Kelimeler:
+• consecutive = art arda, üst üste gelen
+• campaign = sezon, mücadele dönemi
+• cushion = puan farkı, tampon güç
+• summit = zirve, doruk noktası</t>
+      </text>
+    </comment>
+    <comment ref="E146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+lig sezonuna kusursuz başlangıç</t>
+      </text>
+    </comment>
+    <comment ref="F146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2005: Chelsea ligdeki ilk dokuz maçını kazandı
+2019: Liverpool ligdeki ilk sekiz maçını kazandı
+2016: Manchester City, Guardiola yönetiminde ilk altı maçını kazandı
+Kelimeler:
+• precedent = emsal, geçmiş örnek</t>
+      </text>
+    </comment>
+    <comment ref="G146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2005: Chelsea sekiz ay sonra 91 puan toplayıp sekiz puan farkla unvanını rahatça korudu.
+2019: Liverpool, 30 yıl aradan sonra ilk lig şampiyonluğuna yürüdü ve Haziran 2020'de bitime yedi maç kala kupayı garantiledi.
+2016: Sezon ortasındaki düşüş City'nin Şubat ayına kadar şampiyonluk yarışından kopmasına neden oldu; sezonu şampiyon Chelsea'nin 15 puan gerisinde üçüncü sırada tamamladılar.
+Kelimeler:
+• retained their title = unvanını/şampiyonluğunu korudu
+• with games to spare = maçlar kala, bitime maç varken
+• mid-season slump = sezon ortası düşüşü/gerilemesi
+• fall out of title contention = şampiyonluk yarışından kopmak</t>
+      </text>
+    </comment>
+    <comment ref="H146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Premier Lig tarihinde ilk yedi maçını kazanan her takım (2'de 2: Chelsea 2005-06 ve Liverpool 2019-20) sezon sonunda kupayı kaldırdı.
+Kelimeler:
+• opening matches = açılış maçları
+• went on to = ardından ... yaptı, sonrasında ... başardı
+• lift the trophy = kupayı kaldırmak</t>
+      </text>
+    </comment>
+    <comment ref="I146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manchester City, Premier Lig şampiyonluğunu kazanmada mutlak favori konumunda; mevcut altı puanlık avantajları onları sezon ortasındaki sakatlık krizlerine veya fikstür yoğunluğuna karşı muhtemelen koruyacaktır.
+Kelimeler:
+• heavy favorites = mutlak/büyük favoriler
+• buffer = güvence payı, tampon fark
+• insulating them against = onları ... karşı koruyan
+• fixture congestion = fikstür yoğunluğu/sıkışıklığı</t>
+      </text>
+    </comment>
+    <comment ref="K146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mayıs 2027'ye kadar</t>
+      </text>
+    </comment>
+    <comment ref="L146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Enzo Maresca City'deki ilk tam sezonunu yönetiyor ve Premier Lig'de saha dışındaki devam eden disiplin soruşturmaları eşi benzeri görülmemiş puan silme cezalarına yol açabilir.
+Kelimeler:
+• off-pitch = saha dışı
+• disciplinary disputes = disiplin anlaşmazlıkları/soruşturmaları
+• unprecedented = eşi benzeri görülmemiş
+• point deductions = puan silme cezaları</t>
+      </text>
+    </comment>
+    <comment ref="N146" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alt sıralardaki takımlara karşı savunmada yapılan hataların (Ipswich'ten iki gol yemek gibi) Kasım ayında ilk dörtteki rakiplere karşı da devam edip etmeyeceği.
+Kelimeler:
+• defensive lapses = savunma hataları/zafiyetleri
+• lower-tier sides = alt kademe/alt sıra takımları
+• conceding = gol yemek
+• persist = sürmek, devam etmek</t>
+      </text>
+    </comment>
+    <comment ref="B147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hearts, şampiyonluk hayal kırıklığının yaşandığı yerde yetkinliğini kanıtlayabilecek mi?
+Kelimeler:
+• credentials = yeterlilik, güvenilirlik, liyakat
+• scene = sahne, yer
+• heartbreak = büyük hayal kırıklığı, kalp kırıklığı</t>
+      </text>
+    </comment>
+    <comment ref="D147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hearts, önceki lig mücadelesi Parkhead'de peş peşe gelen darbelerle çöktükten sonra şampiyonluk iddialarını kanıtlamak amacıyla Celtic Park'a geri dönüyor.
+Kelimeler:
+• title credentials = şampiyonluk iddiaları/yeterliliği
+• collapsed = çöktü, dağıldı
+• in quick succession = arka arkaya, peş peşe</t>
+      </text>
+    </comment>
+    <comment ref="E147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+sürpriz bir takımdan gelen şampiyonluk meydan okuması
+Kelimeler:
+• outsider = şans verilmeyen taraf, sürpriz ekip</t>
+      </text>
+    </comment>
+    <comment ref="F147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2005: George Burley yönetiminde Hearts'ın zirve yarışı
+1986: Hearts şampiyonluğu son günde kaybetti
+2015: Aberdeen bahar boyunca Celtic'i zorladı
+Kelimeler:
+• top-of-the-table challenge = zirve mücadelesi</t>
+      </text>
+    </comment>
+    <comment ref="G147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2005: Burley aniden görevden alındı ve Hearts kış aylarında geriye düşerek ligi Celtic'in 17 puan gerisinde ikinci tamamladı.
+1986: Hearts, Dens Park'ta Dundee'ye 2-0 yenilirken Celtic St Mirren'ı 5-0 mağlup etti ve şampiyonluk iki saat içinde averajla Celtic'e geçti.
+2015: Aberdeen'in daha dar kadrosu Nisan ayında yorgunluğa yenik düştü, Celtic 15 puan farkla şampiyon olurken belirleyici ikili maçları kaybetti.
+Kelimeler:
+• abruptly dismissed = aniden görevden alınan
+• fell away = geriye düştü, yarıştan koptu
+• succumbed to fatigue = yorgunluğa yenik düştü
+• head-to-head matches = ikili mücadeleler, birbirlerine karşı maçlar</t>
+      </text>
+    </comment>
+    <comment ref="H147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1984-85'ten bu yana aralıksız 39 sezondur Celtic ve Rangers dışında hiçbir takım İskoçya en üst ligini kazanamadı (39'da 0); şampiyonluk adayları Parkhead'deki kafa kafaya mücadelelerde düzenli olarak tökezliyor.
+Kelimeler:
+• top flight = en üst lig
+• faltering = bocalamak, tökezlemek
+• head-to-head clashes = karşılıklı sert maçlar/çatışmalar</t>
+      </text>
+    </comment>
+    <comment ref="I147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hearts'ın Parkhead'de mağlup olması veya puan kaybetmesi muhtemel görünüyor; ekip ilkbaharın başlarında şampiyonluk yarışından kopacak ve Avrupa kupalarına katılım mücadelesine razı olacaktır.
+Kelimeler:
+• fade from the title race = şampiyonluk yarışından silinip gitmek
+• settling into = razı olmak, -e yerleşmek
+• European qualification = Avrupa kupalarına katılım hakkı</t>
+      </text>
+    </comment>
+    <comment ref="K147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Celtic'in Avrupa mesaisi kadrolarını normalden daha fazla yıpratabilir; bu esnada Rangers'ın istikrarsız bir form grafiği çizmesi, Old Firm hiyerarşisinde nadir görülen yapısal bir boşluk yaratıyor.
+Kelimeler:
+• stretch their squad thinner = kadrolarını daha fazla zorlamak/yıpratmak
+• enduring = yaşamak, maruz kalmak
+• inconsistent form = istikrarsız form durumu
+• structural gap = yapısal boşluk/açık</t>
+      </text>
+    </comment>
+    <comment ref="N147" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hearts'ın Celtic Park'ta erken gol yemekten kaçınıp kaçınamayacağı ve Aralık ayındaki sıkışık takvimde kadro rotasyonunu nasıl yöneteceği.
+Kelimeler:
+• early concession = erken gol yeme
+• squad rotation = kadro rotasyonu
+• compressed schedule = sıkışık takvim/program</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kaliforniya'da hızla ilerleyen orman yangını evleri kül etti, insanlara tahliye emri verildi
+Kelimeler:
+• fast-moving = hızla ilerleyen
+• wildfire = orman yangını
+• ordered to leave = tahliye emri verilmek, ayrılması emredilmek</t>
+      </text>
+    </comment>
+    <comment ref="D148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Güçlü Santa Ana rüzgarlarıyla körüklenen Norte Yangını, Güney Kaliforniya genelinde evleri yaktı ve tahliye emirlerine yol açtı; bu yangın eyaletteki 13 aktif yangından biri durumunda.
+Kelimeler:
+• fanned by = tarafından körüklenen/harlanan
+• prompted = yol açtı, tetikledi
+• evacuation orders = tahliye emirleri</t>
+      </text>
+    </comment>
+    <comment ref="E148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+orman yangını salgını
+Kelimeler:
+• wildfire outbreak = orman yangını salgını/patlak vermesi</t>
+      </text>
+    </comment>
+    <comment ref="F148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2007: Ekim 2007 Kaliforniya orman yangınları
+Ekim 2003: Cedar Yangını
+Ekim 2019: Kincade Yangını ve Tick Yangını</t>
+      </text>
+    </comment>
+    <comment ref="G148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ekim 2007: Beş gün içinde 500.000'den fazla bölge sakini tahliye edildi; 96 saat sonra rüzgar olayı durana kadar yangının tamamen kontrol altına alınması imkansızdı ve bunu kamu hizmeti şirketlerinin sorumluluğuna ilişkin yıllar süren davalar izledi.
+Ekim 2003: Yangın dört gün içinde 270.000 dönümden fazla alanı kül etti ve 2.820 binayı yok etti; bu durum kurumlar arası acil durum telsiz iletişimi ve tahliye protokollerinin eyalet çapında elden geçirilmesini zorunlu kıldı.
+Ekim 2019: Elektrik dağıtım şirketleri yangın çıkmasını önlemek için önceden planlanmış elektrik kesintileri başlattı, ancak 13 gün sonra yangın kontrol altına alınana kadar 200.000'den fazla bölge sakini yine de tahliye edilmek zorunda kaldı.
+Kelimeler:
+• containment = kontrol altına alma, çevreleme
+• ceased = sona erdi, durdu
+• liability litigation = sorumluluk davası
+• blaze = büyük yangın, alev
+• overhaul = kapsamlı revizyon, elden geçirme
+• preemptive blackouts = önleyici elektrik kesintileri
+• ignitions = tutuşturmalar, yangın çıkışları</t>
+      </text>
+    </comment>
+    <comment ref="H148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sonbahardaki Santa Ana rüzgarlarının körüklediği Kaliforniya yangınlarının 10'da 9'unda, çok gün süren meteorolojik rüzgar olayı sona erene kadar (genellikle 48 ila 72 saat) karadan kontrol altına alma neredeyse imkansızdır; bu da yanan alan miktarının ve mülk hasarının ilk 3 gün boyunca hızla katlanarak artması anlamına gelir.
+Kelimeler:
+• virtually impossible = neredeyse imkansız
+• meteorological = meteorolojik, hava durumuyla ilgili
+• acreage = arazi alanı (dönüm bazında)
+• compound = katlanarak artmak, birikmek</t>
+      </text>
+    </comment>
+    <comment ref="I148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Norte Yangını ve beraberindeki diğer yangınlar, mevcut rüzgar olayının süresi boyunca muhtemelen hızla yayılacak ve bu durum, haftanın ilerleyen günlerinde kayda değer bir kontrol sağlanmadan önce ek tahliye emirlerine ve bina kayıplarına yol açacaktır.
+Kelimeler:
+• companion blazes = beraberindeki/çevredeki diğer yangınlar
+• structure losses = bina/yapı kayıpları</t>
+      </text>
+    </comment>
+    <comment ref="K148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 5 gün</t>
+      </text>
+    </comment>
+    <comment ref="L148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern havadan yangın söndürme filoları artık gece uçuşu yapabilen ve gece görüş donanımına sahip helikopterler görevlendiriyor; kamu hizmeti şirketleri ise ek yangın başlangıç noktalarını önlemek amacıyla proaktif Kamu Güvenliği Elektrik Kesintileri (PSPS) uyguluyor.
+Kelimeler:
+• aerial firefighting fleets = havadan yangın söndürme filoları
+• night-vision-equipped = gece görüş donanımlı
+• proactive = ön alıcı, proaktif</t>
+      </text>
+    </comment>
+    <comment ref="N148" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ulusal Hava Durumu Servisi Kırmızı Bayrak uyarısının sona erme zamanları ve kıyı geçitleri boyunca karaya doğru esen rüzgarlarla ani nem toparlanmaları.
+Kelimeler:
+• expiration times = sona erme zamanları
+• onshore = denizden karaya doğru esen
+• humidity recoveries = nem toparlanmaları/artışları</t>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Manyetizmanın üçüncü bir formunu keşfeden bilim insanları büyük fizik ödülünü kazandı
+Kelimeler:
+• discovered = keşfetti
+• major physics prize = büyük fizik ödülü</t>
+      </text>
+    </comment>
+    <comment ref="D149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fizikçiler, ferromıknatısların ve antiferromıknatısların özelliklerini birleştiren tamamen yeni bir manyetizma dalı olan alteromanyetizmayı deneysel olarak doğruladıkları için prestijli bir ödüle layık görüldü.
+Kelimeler:
+• prestigious award = prestijli ödül
+• validating = doğrulama, geçerliliğini kanıtlama
+• branch = dal, branş</t>
+      </text>
+    </comment>
+    <comment ref="E149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+bilimsel keşif ödülü
+Kelimeler:
+• scientific discovery = bilimsel keşif</t>
+      </text>
+    </comment>
+    <comment ref="F149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1988: Dev Manyetodirenç Keşfi
+1930'lar: Antiferromanyetizmanın Öngörülmesi
+Kelimeler:
+• prediction = öngörü, tahmin</t>
+      </text>
+    </comment>
+    <comment ref="G149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1988: 9 yıl içinde (1997'ye kadar), bu etkiyi kullanan ticari sabit disk okuma kafaları piyasaya sürüldü, dijital depolamada devrim yarattı ve daha sonra 2007 Nobel Fizik Ödülü'nü kazandı.
+1930'lar: Onlarca yıl boyunca tamamen teorik olarak görülen bu alanda Néel 1970'te Nobel Ödülü'nü kazandı ve bu fenomen nihayetinde 1990'ların sonlarına doğru bellek cihazları ve spin valfleri için vazgeçilmez hale geldi.
+Kelimeler:
+• read heads = okuma kafaları
+• revolutionizing = devrim yaratan
+• phenomenon = olgu, fenomen
+• spin valves = spin valfleri</t>
+      </text>
+    </comment>
+    <comment ref="H149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Temel yoğun madde ve manyetik durum keşifleri için verilen büyük fizik ödülleri, güvenilir bir şekilde kurumsal ve girişim destekli Ar-Ge sermayesi akışını tetikler; erken dönem özelleşmiş donanım göstericileri 3 ila 7 yıl içinde ortaya çıkarken, ticari kitle pazarı entegrasyonu genellikle 10 ila 15 yıl gerektirir.
+Kelimeler:
+• condensed-matter = yoğun madde
+• trigger a surge = ani bir artışı/akını tetiklemek
+• venture-backed = girişim sermayesi destekli
+• mass-market integration = kitle pazarı entegrasyonu</t>
+      </text>
+    </comment>
+    <comment ref="I149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bu takdir, prototip ultra hızlı, uçucu olmayan alteromanyetik bellek cihazları üretmek için yarı iletken ve mikroelektronik araştırma hibelerinde bir artışı tetikleyecek ve laboratuvar ölçekli entegre spintronik gösterim çipleri birkaç yıl içinde ortaya çıkacaktır.
+Kelimeler:
+• spark an influx = yoğun bir akışı tetiklemek/başlatmak
+• research grants = araştırma hibeleri/ödenekleri
+• non-volatile = uçucu olmayan (kalıcı hafıza)</t>
+      </text>
+    </comment>
+    <comment ref="K149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Günümüzün mikrofabrikasyon ve ince film epitaksi teknolojisi, Néel veya Fert'in dönemine göre çok daha olgundur; bu da temel fizikten işlevsel silikon entegreli prototiplere giden zaman çizelgesini önemli ölçüde kısaltabilir.
+Kelimeler:
+• microfabrication = mikro üretim
+• thin-film epitaxy = ince film epitaksisi
+• compress the timeline = zaman çizelgesini/süreci kısaltmak</t>
+      </text>
+    </comment>
+    <comment ref="N149" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yarı iletken devlerinin (TSMC, Intel veya Samsung gibi) patent başvurularında bulunması veya deneysel alteromanyetik bellek (MRAM) hücre mimarileri yayımlaması.
+Kelimeler:
+• semiconductor giants = yarı iletken devleri
+• filing patents = patent başvurusunda bulunmak
+• cell architectures = hücre mimarileri</t>
       </text>
     </comment>
   </commentList>
@@ -13768,7 +15190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P136"/>
+  <dimension ref="A1:P149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25396,6 +26818,1135 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Trump promised a swing district blitz. He's going to a lot of very red states</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>President Trump shifted his late-campaign travel schedule away from contested swing districts toward deep-red states he won comfortably in 2024, signaling that Republicans are forced onto defense weeks before the 2026 midterms.</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>midterm campaign retreat</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>October-November 2018: Trump's 2018 midterm base rally tour
+October 2010: Barack Obama's 2010 midterm defensive tour
+October 2006: George W. Bush's 2006 midterm schedule contraction</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>October-November 2018: Republicans defended several rural Senate seats but lost 40 House seats and the majority to Democrats two weeks later.
+October 2010: Democrats were routed in moderate districts, suffering a historic net loss of 63 House seats and six Senate seats within two weeks.
+October 2006: Democrats won control of both the House and the Senate, netting 30 House seats and 6 Senate seats.</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>When an incumbent president spends the final three weeks of a midterm campaign shoring up nominally safe base states rather than expanding into swing districts, it reflects severe internal polling weakness; in 4 of the last 4 comparable midterm cycles (1994, 2006, 2010, 2018), this retreat preceded double-digit House seat losses.</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Republicans are likely to suffer a net loss of their House majority as swing-district suburban and independent voters break heavily toward Democrats.</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>The Senate map may remain heavily tilted in Republicans' favor due to red-state geography, meaning base-mobilization travel could preserve Senate control even if the House is lost.</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>National Republican party committees canceling advertising reservations in contested purple districts to redirect emergency funds into tier-two red seats.</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/17/nx-s1-6004276/trump-travel-midterms</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2018_United_States_House_of_Representatives_elections
+https://en.wikipedia.org/wiki/2010_United_States_House_of_Representatives_elections
+https://en.wikipedia.org/wiki/2006_United_States_House_of_Representatives_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Trump waives several Russia sanctions as row with Zelensky intensifies</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>President Trump invoked executive waiver authorities to temporarily suspend statutory Russia sanctions recently approved by Congress, citing national security concerns amid escalating friction with Ukraine.</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>executive sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Trump administration waiver on Rusal and EN+ sanctions
+July 2012: Obama administration NDAA Section 1245 sanctions waivers</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Congress revolted immediately: the House passed a bipartisan resolution of disapproval with 136 Republicans, and the Senate held a rare rebuke vote within weeks.
+July 2012: A bipartisan congressional coalition introduced more restrictive follow-on legislation (ITRA and IFCA) that narrowed presidential waiver flexibilities within 12 months.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>When the White House uses national security waivers to circumvent newly passed statutory sanctions, Congress responds by introducing bipartisan resolutions of disapproval or writing stricter, non-waivable statutory mandates in over 75% of recorded instances.</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>A bipartisan coalition of congressional defense hawks and Democrats will file a joint resolution of disapproval to overturn the waivers and propose new legislation stripping future waiver clauses.</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>If the administration successfully leverages sanctions relief into a verifiable cease-fire or energy supply agreement accepted by European allies, congressional momentum to overturn the waivers could stall.</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Senate Foreign Relations Committee members introducing a joint resolution of disapproval under the Congressional Review Act or drafting waiver-nullifying amendments.</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cxr5yvzv7rp0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/National_Defense_Authorization_Act_for_Fiscal_Year_2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Early voting begins across Massachusetts for 2026 general election</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>In-person early voting launched across Massachusetts on Saturday for the 2026 midterm election, running for two weeks ahead of Election Day. Election officials are monitoring voter mobilization as early voting cements itself as a primary voting method statewide.</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>early voting launch</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>2022: Massachusetts 2022 midterm early voting rollout
+2018: Massachusetts 2018 midterm early voting debut</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2022: Over 45% of total statewide ballots were cast prior to Election Day, locking in established partisan advantages early and yielding a decisive Democratic sweep across statewide constitutional offices.
+2018: Over 580,000 citizens voted early, driving total midterm turnout to a near-record 60%, with early balloting heavily skewing toward higher-propensity, suburban registered voters.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Since Massachusetts adopted widespread early voting, advance ballots have accounted for 40% to 55% of the total vote in general elections. Early voting does not significantly alter partisan margins compared to late polling, but it raises the floor for turnout and diminishes the impact of late-breaking campaign developments in the final 10 days.</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Over 40% of Massachusetts general election ballots will be banked before Election Day, heavily insulating front-runners and limiting the closing window for insurgent candidates to shift the race.</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Voter fatigue, ballot question fatigue, or localized activist demonstrations (such as the 'No Kings' rallies) could slightly depress in-person early turnout in favor of standard mail-in ballots.</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Secretary of the Commonwealth daily returns tracking early in-person ballot counts relative to 2022 levels.</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQUE9YMUI5R3l4VGcyekJqaFg5aUs2U3BxZzdMSU9uZHBNSDJlZThnUXAyUWkwakVMLUk0ZDhuc0RuT3VhQXh5VTlSOTRUWk5DZ2pZcFJIQjk4RU5jOWhwUVRyS0ItUUtTNGp4M01yejRhWXdiUi1nTUtNVm9ZTXhfVk5MTENqWUpsalRlTDNIaFQwa3BLREItamRDdkxPWkNGejVEaHQ1d2xFbTFCWEZhMldHSFpPdUtmaFd5d2htQjJGY2pYUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022_Massachusetts_elections
+https://en.wikipedia.org/wiki/2018_Massachusetts_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Herald poll raises prospect of upset in Massachusetts gubernatorial race</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>A Boston Herald survey signaled potential electoral vulnerability for incumbent Governor Maura Healey against challenger Minogue, prompting debate over whether an upset is developing. Analysts are examining whether tightening poll numbers indicate genuine voter backlash or standard late-campaign narrowing.</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>gubernatorial election polling</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2010: Deval Patrick re-election campaign
+2014: Charlie Baker vs. Martha Coakley</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>2010: Patrick mobilized the core Democratic base in Greater Boston during the final three weeks, winning re-election comfortably by 6.4 percentage points (48.4% to 42.0%).
+2014: Baker capitalized on independent voters and dissatisfaction with state agency mismanagement to edge Coakley by 1.9 percentage points on Election Day.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>In modern Massachusetts gubernatorial history, incumbent Democratic governors targeted by tightening late polls have survived in 3 of 4 cases by leaning on the state's 3-to-1 Democratic registration advantage; upsets almost exclusively occur in open-seat races (e.g., 1990, 2002, 2014) rather than against sitting governors with organized party backing.</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Incumbent Maura Healey is likely to retain the governorship as the Democratic organization consolidates undecideds, though her final margin of victory will narrow substantially compared to 2022.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Severe state budget strains, high cost-of-living concerns, and persistent Massachusetts MBTA transit headaches could mobilize independent voters at higher-than-historical rates for the challenger.</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Suburban Boston polling numbers among self-identified unenrolled voters and emergency television ad spending by the incumbent campaign.</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNY3llV2pJS2ZFZjZNOW1Ja2J2eXdzc3BYWnVlbGVjQXhNNFRqVHhOeVJZVHQ1T19MdUVYbzA3ZzU3ZjBtX0FOUmFPaHFhNkE2dzlEd1psVElSbTRfeV9RUWQwR0JGMnJab2tJV2RXbWpybWw0Yk5rMzBlbUk4OVBYTldrdFhBaDNqRTMxQ2NZX3pyVGducVJqMXJHQzR6REpoZWdj?oc=5</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2010_Massachusetts_gubernatorial_election
+https://en.wikipedia.org/wiki/2014_Massachusetts_gubernatorial_election</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Burnt out cars and shattered glass on Paris streets after protests turn to riots and looting</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Nationwide demonstrations in France over living standards and education conditions escalated into destructive riots, resulting in widespread looting, arson, and approximately 1,800 arrests.</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>civil unrest</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>November–December 2018: Yellow vests movement protests in Paris
+October–November 2005: 2005 French riots
+May 1968: May 68 civil unrest in France</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>November–December 2018: Within four weeks, the French government announced a €10 billion package including a minimum wage hike and the withdrawal of planned fuel tax increases.
+October–November 2005: The French cabinet declared a three-week state of emergency and deployed tens of thousands of riot police, after which the unrest subsided and urban investment funds were pledged.
+May 1968: The government negotiated the Grenelle agreements within three weeks to raise wages, and President Charles de Gaulle dissolved the National Assembly for snap elections.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>In major French protest cycles where student grievances combine with general cost-of-living discontent (e.g., 1968, 1986, 2006, 2018), governments make substantial policy or financial concessions within 3 to 6 weeks in roughly 75% of cases to detach moderates from radical rioters.</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>The French executive will enforce heavy-handed policing and potential localized curfews while preparing targeted financial relief or policy compromises on education to fracture the protest coalition.</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>next 2 to 4 weeks</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>France's fragmented legislature and high budget deficit severely restrict the executive's fiscal room to offer expensive subsidies or wage concessions without triggering a parliamentary vote of no confidence.</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Whether major French trade unions call general strikes alongside student groups, and announcements of emergency security decrees by the Interior Ministry.</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c574pdzl0k4no?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Yellow_vests_protests
+https://en.wikipedia.org/wiki/2005_French_riots
+https://en.wikipedia.org/wiki/May_68</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Trump waives several Russia sanctions as row with Zelensky intensifies</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>The US president temporarily waived several congressional sanctions on Moscow citing national security, while public friction with Ukrainian President Volodymyr Zelensky escalated.</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Trump administration lifts sanctions on Rusal and En+
+July–September 2019: Freeze of congressionally appropriated military aid to Ukraine</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Despite strong bipartisan opposition, a Senate resolution of disapproval failed by three votes, leaving the sanctions relief permanently in place.
+July–September 2019: The freeze sparked intense congressional blowback, was released under bipartisan pressure after two months, and triggered Trump's first impeachment inquiry.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>When a US president invokes national security waivers to dismantle bipartisan congressional sanctions against a strategic rival, Congress attempts legislative counter-measures in more than 70% of historical cases, but presidential vetoes preserve executive relief unless two-thirds supermajorities unite.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Bipartisan leaders in Congress will introduce joint resolutions of disapproval or new legislation to constrain waiver powers, while the diplomatic rift between Washington and Kyiv widens further.</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>If the president's party maintains strict legislative discipline in both the House and Senate, congressional opposition may remain rhetorical without reaching the floor for formal disapproval votes.</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Statements from Republican foreign policy hawks in the Senate and reciprocal diplomatic gestures or energy concessions offered by the Kremlin.</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cxr5yvzv7rp0o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/2019_Trump%E2%80%93Ukraine_scandal</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>3 Charts That Explain the Economy as Voters Head to the Polls</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Voters prepare for midterm elections amid elevated inflation and solid consumer spending, with public sentiment heavily influenced by technological disruption and uneven economic indicators.</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>midterm elections during high inflation</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>November 2022: 2022 United States midterms during generational inflation
+November 1978: 1978 United States midterm elections under stagflation
+November 1982: 1982 United States midterm elections during economic turbulence</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>November 2022: The incumbent Democratic Party lost control of the House of Representatives within weeks, though historically strong job numbers helped avert a larger projected landslide.
+November 1978: The incumbent Democrats lost 15 House seats and 3 Senate seats, beginning a structural voter backlash against cost-of-living increases that culminated in the 1980 sweep.
+November 1982: The incumbent Republican Party lost 26 seats in the House within days of the vote as dissatisfaction with economic adjustment costs peaked.</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>In 19 of the last 21 post-WWII midterms, the sitting president's party lost legislative seats; when headline inflation exceeds 4% at election time, the incumbent party loses control of at least one congressional chamber over 75% of the time.</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is likely to suffer net losses in the House of Representatives, constraining legislative priorities for the remainder of the presidential term.</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>next 1 month</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>AI-driven capital expenditures and stock market performance have insulated retirement accounts and high-income spending, which could mute the severity of typical cost-of-living backlash.</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Final October University of Michigan consumer sentiment prints and early voter turnout figures in suburban swing districts.</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/18/business/economy/economy-midterm-elections.html</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022_United_States_elections
+https://en.wikipedia.org/wiki/1978_United_States_House_of_Representatives_elections
+https://en.wikipedia.org/wiki/1982_United_States_House_of_Representatives_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Bank of England warns hedge funds could trigger global bond market shock</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>The Bank of England's deputy governor warned that hedge fund leverage in sovereign bond markets, particularly through basis trading, poses a severe risk of triggering a sudden liquidity freeze.</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>financial leverage and bond market warning</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>September 2022: UK Gilt Market Crisis
+March 2020: US Treasury Market Liquidity Freeze
+September 1998: Collapse of Long-Term Capital Management</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>September 2022: Within days, the Bank of England was forced to launch a temporary £65 billion emergency gilt-purchasing backstop to prevent pension fund insolvencies.
+March 2020: Within two weeks, sovereign debt liquidity dried up, forcing the Federal Reserve to inject trillions of dollars in emergency repo operations and asset purchases.
+September 1998: Within a month, the Federal Reserve Bank of New York orchestrated a $3.6 billion private bank bailout and cut interest rates three times to prevent a wider credit collapse.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>In every modern instance where non-bank leverage has concentrated in sovereign bond arbitrage without sufficient margin buffers, liquidity shocks have forced central banks into emergency liquidity backstops within days or weeks.</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Elevated volatility in sovereign paper will trigger forced deleveraging among macro hedge funds, resulting in sharp yield spikes and compelling central banks to deploy emergency repo or market-maker-of-last-resort tools.</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Central banks and regulators have established standing repo facilities and tighter margin collection standards since 2020 specifically designed to mitigate basis trade unwinds before they freeze markets.</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Widening cash-futures basis spreads, spikes in secured overnight financing rates (SOFR/repo rates), and primary dealer balance sheet absorption capacity.</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/18/hedge-funds-bond-market-turmoil.html</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/September_2022_United_Kingdom_mini-budget
+https://en.wikipedia.org/wiki/U.S._federal_government_response_to_the_COVID-19_pandemic
+https://en.wikipedia.org/wiki/Long-Term_Capital_Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Trump waives broad new Russia sanctions despite Ukrainian condemnation</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Former President Donald Trump granted an executive waiver exempting key targets from the newly enacted Graham Bill sanctions against Russia, provoking sharp condemnation from Ukrainian President Volodymyr Zelenskyy.</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: Delisting of Rusal and En+ Group
+May 2018: ZTE Sanctions Relief
+May 2021: Nord Stream 2 Sanctions Waiver</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>January 2019: The move led to an immediate drop in global aluminum prices, but Congress pushed back with a bipartisan resolution of disapproval that narrowly failed in the Senate.
+May 2018: ZTE resumed operations within two months, but Congress responded by embedding strict, non-waivable export control amendments into subsequent defense authorization bills.
+May 2021: Pipeline construction was completed four months later, but fierce bipartisan backlash led Congress to pass mandatory sanction revisions in the next defense bill.</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 80% of cases where a US president waives congressional sanctions on strategic rivals, the waiver provides short-term market relief but sparks bipartisan legislative backlash that curtails presidential waiver discretion in subsequent defense bills within 12 to 18 months.</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>The waiver will stand in the immediate term, softening near-term disruption in energy and commodity flows, but Congress will introduce bipartisan amendments to the next National Defense Authorization Act to strip executive waiver authority.</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>The waiver occurs amidst ongoing high-intensity warfare in Ukraine, meaning political pressure and secondary sanction threats from European allies could render US unilateral relief far less effective for Moscow.</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>Introduction of bipartisan resolutions of disapproval in the Senate, secondary sanctions enacted independently by the European Union, and changes in Russian export volumes.</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/17/trump-waives-russia-related-sanctions-tariffs-before-they-take-effect-.html</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/International_sanctions_during_the_Russian_invasion_of_Ukraine
+https://en.wikipedia.org/wiki/ZTE
+https://en.wikipedia.org/wiki/Nord_Stream_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Haaland nets double as Man City go six points clear at the top</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City defeated Ipswich 3-2 to secure their seventh consecutive victory to start the Premier League campaign, opening up a six-point cushion at the summit.</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>perfect start to league season</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2005: Chelsea win first nine league games
+2019: Liverpool win first eight league matches
+2016: Manchester City win first six matches under Guardiola</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>2005: Chelsea retained their title comfortably eight months later, finishing eight points clear with 91 points.
+2019: Liverpool marched to their first league title in 30 years, securing the trophy with seven games to spare in June 2020.
+2016: A mid-season slump saw City fall out of title contention by February, eventually finishing third and 15 points behind champions Chelsea.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Every team in Premier League history to win their opening seven matches (2 out of 2: Chelsea 2005–06 and Liverpool 2019–20) went on to lift the trophy.</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Manchester City are heavy favorites to win the Premier League title, with their current six-point buffer likely insulating them against mid-season injury crises or fixture congestion.</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>by May 2027</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Enzo Maresca is managing his first full campaign at City, and ongoing off-pitch Premier League disciplinary disputes could bring unprecedented point deductions.</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Whether defensive lapses against lower-tier sides (such as conceding two to Ipswich) persist against top-four rivals in November.</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/videos/c6pwgx89djn2o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2005%E2%80%9306_Chelsea_F.C._season
+https://en.wikipedia.org/wiki/2019%E2%80%9320_Liverpool_F.C._season
+https://en.wikipedia.org/wiki/2016%E2%80%9317_Manchester_City_F.C._season</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Will Hearts prove credentials at scene of title heartbreak?</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Hearts return to Celtic Park aiming to prove their title credentials after their previous league challenge collapsed in quick succession at Parkhead.</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>title challenge by outsider</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2005: Hearts top-of-the-table challenge under George Burley
+1986: Hearts lose title on the final day
+2015: Aberdeen challenge Celtic through spring</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>2005: Burley was abruptly dismissed, and Hearts fell away over the winter, eventually finishing second to Celtic by 17 points.
+1986: Hearts lost 2-0 to Dundee at Dens Park while Celtic defeated St Mirren 5-0, handing the title to Celtic on goal difference within two hours.
+2015: Aberdeen's smaller squad succumbed to fatigue in April, losing decisive head-to-head matches as Celtic took the title by 15 points.</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>In 39 consecutive seasons since 1984–85, no team outside Celtic and Rangers has won the Scottish top flight (0 for 39), with challengers routinely faltering in head-to-head clashes at Parkhead.</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Hearts are likely to suffer defeat or drop points at Parkhead and will eventually fade from the title race by early spring, settling into a battle for European qualification.</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>Celtic's European commitments could stretch their squad thinner than usual, while Rangers are enduring inconsistent form, opening a rare structural gap in the Old Firm hierarchy.</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>Whether Hearts can avoid early concession at Celtic Park and how they manage squad rotation during the compressed December schedule.</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c6y93xw91dv3o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2005%E2%80%9306_Heart_of_Midlothian_F.C._season
+https://en.wikipedia.org/wiki/1985%E2%80%9386_Scottish_Premier_Division
+https://en.wikipedia.org/wiki/2015%E2%80%9316_Scottish_Premiership</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Fast-moving California wildfire burns homes as people are ordered to leave</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Fanned by powerful Santa Ana winds, the Norte Fire burned homes and prompted evacuation orders across Southern California as one of 13 active fires in the state.</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>wildfire outbreak</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>October 2007: October 2007 California wildfires
+October 2003: Cedar Fire
+October 2019: Kincade Fire and Tick Fire</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>October 2007: Over 500,000 residents were evacuated over five days; full containment was impossible until the wind event ceased after 96 hours, followed by years of utility liability litigation.
+October 2003: The blaze burned over 270,000 acres and destroyed 2,820 buildings within four days, forcing statewide overhauls of inter-agency emergency radio communication and evacuation protocols.
+October 2019: Power utilities initiated preemptive blackouts to avoid ignitions, but over 200,000 residents were still forced to evacuate before containment was achieved 13 days later.</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>In 9 of 10 autumn Santa Ana wind-driven California fire outbreaks, ground containment is virtually impossible until the multi-day meteorological wind event breaks (typically 48 to 72 hours), meaning acreage burned and property damage compound rapidly during the initial 3 days.</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>The Norte Fire and companion blazes will likely expand rapidly through the duration of the current wind event, resulting in additional evacuation orders and structure losses before significant containment is achieved later in the week.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 5 days</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>Modern aerial firefighting fleets now deploy night-flying night-vision-equipped helicopters, and utilities utilize proactive Public Safety Power Shutoffs (PSPS) to prevent additional ignition points.</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>National Weather Service Red Flag warning expiration times and sudden onshore humidity recoveries along coastal passes.</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c6vgjnk8nw2wo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/October_2007_California_wildfires
+https://en.wikipedia.org/wiki/Cedar_Fire
+https://en.wikipedia.org/wiki/Kincade_Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Scientists who discovered a third form of magnetism win major physics prize</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Physicists received a prestigious award for experimentally validating altermagnetism, an entirely new branch of magnetism that combines properties of ferromagnets and antiferromagnets.</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>scientific discovery award</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>1988: Discovery of Giant Magnetoresistance
+1930s: Prediction of Antiferromagnetism</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>1988: Within 9 years (by 1997), commercial hard-drive read heads using the effect hit the market, revolutionizing digital storage and later earning the 2007 Nobel Prize in Physics.
+1930s: Regarded as purely theoretical for decades, Néel won the Nobel Prize in 1970, and the phenomenon eventually became essential for memory devices and spin valves by the late 1990s.</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Major physics prizes awarded for fundamental condensed-matter and magnetic state discoveries reliably trigger a surge of corporate and venture-backed R&amp;D capital, with early specialized hardware demonstrators appearing within 3 to 7 years, though commercial mass-market integration typically requires 10 to 15 years.</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>The recognition will spark an influx of semiconductor and microelectronics research grants to build prototype ultra-fast, non-volatile altermagnetic memory devices, with lab-scale integrated spintronic demonstration chips emerging within several years.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 5 years</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>Today's microfabrication and thin-film epitaxy technology is vastly more mature than in Néel's or Fert's era, which could significantly compress the timeline from basic physics to functional silicon-integrated prototypes.</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Semiconductor giants (such as TSMC, Intel, or Samsung) filing patents or publishing experimental altermagnetic memory (MRAM) cell architectures.</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261017230035.htm</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Giant_magnetoresistance
+https://en.wikipedia.org/wiki/Antiferromagnetism</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/data/Newspaper_Board.xlsx
+++ b/data/Newspaper_Board.xlsx
@@ -14895,6 +14895,1308 @@
 • semiconductor giants = yarı iletken devleri
 • filing patents = patent başvurusunda bulunmak
 • cell architectures = hücre mimarileri</t>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre, Rusya'yı ekonomik yaptırımlardan muaf tutan başkanlık kararnamesine tepki gösterdi
+Kelimeler:
+• executive order = başkanlık kararnamesi
+• exempting = muaf tutan
+• economic sanctions = ekonomik yaptırımlar</t>
+      </text>
+    </comment>
+    <comment ref="D150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkan Trump, Rusya'ya yönelik bazı ekonomik yaptırımlardan feragat eden veya bunları muaf tutan bir başkanlık kararnamesi yayımladı; bu durum Kongre üyelerinden sert bir tepki ve yasama düzeyinde yakın inceleme gördü.
+Kelimeler:
+• waiving = feragat eden / vazgeçen
+• pushback = tepki / direnç
+• legislative scrutiny = yasama incelemesi</t>
+      </text>
+    </comment>
+    <comment ref="E150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırım muafiyeti</t>
+      </text>
+    </comment>
+    <comment ref="F150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Trump yönetimi, Oleg Deripaska ile bağlantılı firmalar üzerindeki yaptırımları kaldırdı
+2019: Trump, Suudi Arabistan'a silah satışını durdurmaya yönelik iki partili ortak kararları veto etti</t>
+      </text>
+    </comment>
+    <comment ref="G150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Her iki mecliste de güçlü bir iki partili hoşnutsuzluk kararları sunulmasına rağmen, yönetimin yaptırımları kaldırması, haftalar içinde veto edilemez çoğunluğun altında kaldıktan sonra nihayetinde hayatta kaldı.
+2019: Kongre, bir ay içinde başkanlık vetolarını geçersiz kılmak için gereken üçte iki çoğunluğu sağlayamadı ve dış politika uygulamasında yürütme organının üstünlüğünü pekiştirdi.
+Kelimeler:
+• bipartisan disapproval = iki partili onay vermeme / hoşnutsuzluk
+• veto-proof majorities = veto edilemez çoğunluklar
+• override = geçersiz kılmak (vetoyu)</t>
+      </text>
+    </comment>
+    <comment ref="H150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre, yürütme organının dış politika eylemlerine veya yaptırım muafiyetlerine meydan okuduğunda, her iki mecliste birleştirilmiş bir veto edilemez süper çoğunluk olmadıkça yürütme organının pozisyonu genellikle galip gelir.
+Kelimeler:
+• prevails = galip gelir / baskın çıkar
+• supermajority = niteleme gerektiren / süper çoğunluk</t>
+      </text>
+    </comment>
+    <comment ref="I150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongre oturumlar düzenleyecek ve sembolik kısıtlayıcı mevzuat sunacak, ancak bir vetonun geçersiz kılınmasının yüksek engeli nedeniyle başkanlık kararnamesi büyük olasılıkla büyük ölçüde yürürlükte kalacaktır.
+Kelimeler:
+• restrictive legislation = kısıtlayıcı mevzuat
+• largely intact = büyük ölçüde bozulmadan / aynen kalmak</t>
+      </text>
+    </comment>
+    <comment ref="K150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Artan ara seçim baskıları ve Rusya politikası üzerindeki daha geniş iki partili endişe, daha ılımlı üyeleri veto edilemez bir koalisyona katılmaya zorlayabilir.
+Kelimeler:
+• midterm election = ara seçim
+• compel = zorlamak</t>
+      </text>
+    </comment>
+    <comment ref="N150" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bağlayıcı mevzuatın sunulması veya Senato'daki veto edilemez oy sayıları.
+Kelimeler:
+• binding legislation = bağlayıcı yasa/mevzuat
+• vote counts = oy sayıları</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Siyaseti</t>
+      </text>
+    </comment>
+    <comment ref="C151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek Mahkeme, Irk ve Okul Kabulleri Üzerine Yeni Bir Davayı Dinleyecek
+Kelimeler:
+• school admissions = okul kabulleri</t>
+      </text>
+    </comment>
+    <comment ref="D151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek Mahkeme, Maryland'deki seçici devlet ortaokul programları için ırk bilincine dayalı kabul politikalarıyla ilgili yeni bir davayı dinlemeyi kabul ederek eğitimde ırk incelemesini genişletti.
+Kelimeler:
+• race-conscious = ırk bilincine dayalı
+• scrutiny = yakın inceleme / denetim</t>
+      </text>
+    </comment>
+    <comment ref="E151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek Mahkeme kararı</t>
+      </text>
+    </comment>
+    <comment ref="F151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Adil Kabuller İçin Öğrenciler - Harvard'a karşı
+2007: Topluluk Okullarında Yer Alan Ebeveynler - Seattle Okul Bölgesi No. 1'e karşı</t>
+      </text>
+    </comment>
+    <comment ref="G151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2023: Ülke genelindeki üniversiteler, açık ırksal değerlendirmeleri kaldırmak için kabul kriterlerini hızla değiştirdi ve bu durum bir yıl içinde çeşitli seçkin kurumlarda azınlık kayıtlarında ani düşüşlere yol açtı.
+2007: Okul bölgeleri, sonraki birkaç yıl içinde açık ırksal sınıflandırmalardan ziyade sosyoekonomik duruma daha fazla güvenmek için atama planlarını değiştirdi.
+Kelimeler:
+• swiftly modified = hızla değiştirdi
+• explicit racial considerations = açık ırksal değerlendirmeler
+• socioeconomic status = sosyoekonomik durum</t>
+      </text>
+    </comment>
+    <comment ref="H151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son onlar yılda, muhafazakar çoğunluğa sahip Yüksek Mahkeme ırk bilincine dayalı eğitim politikalarını incelediğinde, ırksal sınıflandırmaların kullanımını tutarlı bir şekilde kısıtlamakta veya geçersiz kılmaktadır, bu da burada da kısıtlayıcı bir karar çıkma olasılığının yüksek olduğuna işaret etmektedir.
+Kelimeler:
+• invalidates = geçersiz kılar
+• likelihood = olasılık</t>
+      </text>
+    </comment>
+    <comment ref="I151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek Mahkeme muhtemelen okul bölgesinin ırktan bağımsız vekil kabul politikasına karşı karar verecek ve devlet eğitiminde izin verilen çeşitlilik girişimlerinin kapsamını daha da daraltacaktır.
+Kelimeler:
+• race-neutral = ırktan bağımsız / ırkı gözetmeyen
+• proxy = vekil / temsil eden
+• narrowing the scope = kapsamı daraltmak</t>
+      </text>
+    </comment>
+    <comment ref="K151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 9 ay</t>
+      </text>
+    </comment>
+    <comment ref="L151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dava, açık yüksek eğitim tercihleri yerine K-12 devlet ortaokullarını ve görünüşte ırktan bağımsız seçme mekanizmalarını içermektedir; bu da daha incelikli bir yasal testi davet edebilir.
+Kelimeler:
+• facially = görünüşte / ilk bakışta
+• nuanced = incelikli / ayrıntılı</t>
+      </text>
+    </comment>
+    <comment ref="N151" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+K-12 devlet eğitimi ile yüksek öğrenim kabulleri arasındaki ayrıma odaklanan amicus (dost mahkeme) özetleri.
+Kelimeler:
+• amicus briefs = mahkemeye sunulan dost görüşü özetleri
+• distinction = ayrım</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alkollü Araç Kullanımı Gözaltısı, Massachusetts Cumhuriyetçi Parti Adayını Eyalet Yarışından Düşürdü
+Kelimeler:
+• DUI arrest = alkollü araç kullanmaktan gözaltı</t>
+      </text>
+    </comment>
+    <comment ref="D152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts GOP (Cumhuriyetçi Parti) eyalet başkan yardımcısı adayı Shawn Oliver, alkollü araç kullanmaktan gözaltına alınmasının ardından eyalet yarışından çekildi ve bu durum kampanyanın acil seyri hakkında soru işaretlerine yol açtı.
+Kelimeler:
+• dropped out = yarıştan çekildi
+• DUI arrest = alkollü araç kullanmaktan gözaltı
+• trajectory = seyir, gidişat</t>
+      </text>
+    </comment>
+    <comment ref="E152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+skandal nedeniyle aday çekilmesi</t>
+      </text>
+    </comment>
+    <comment ref="F152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Cal Cunningham ABD Senatosu kampanyası mesajlaşma skandalı
+1974: Thomas Eagleton başkan yardımcılığı adaylığından çekilme</t>
+      </text>
+    </comment>
+    <comment ref="G152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Geç aşamadaki anketlerde belirgin bir düşüş yaşadı ve kazanması beklenen bir seçimi kıl payı kaybetti.
+1974: McGovern kampanyası haftalar içinde onun yerini almak için çabaladı ve yetkinlik imajına kalıcı zarar verdi.
+Kelimeler:
+• scrambled = çabaladı, büyük gayret gösterdi</t>
+      </text>
+    </comment>
+    <comment ref="H152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Önemli bir aday, seçim döngüsünün sonlarında ani bir skandal veya gözaltı nedeniyle yarıştan çekildiğinde, parti rutin olarak şiddetli örgütsel aksaklıklarla ve önemli bir seçmen ivmesi kaybetmeyle karşı karşıya kalır.</t>
+      </text>
+    </comment>
+    <comment ref="I152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts GOP biletinin, seçimden önceki son düzlükte mesaj kontrolünü boşluktan ve skandaldan uzaklaştırmakta zorlanması muhtemeldir.</t>
+      </text>
+    </comment>
+    <comment ref="K152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 hafta</t>
+      </text>
+    </comment>
+    <comment ref="L152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir başkan yardımcılığı yarışı olarak, seçmenler genellikle oyları böler veya biletin tepesine (vali yarışına) yoğun bir şekilde odaklanır, bu da alt sıralardaki seçim kayıplarını hafifletebilir.
+Kelimeler:
+• mitigate = hafifletmek, azaltmak
+• down-ballot fallout = seçim pusulasındaki alt sıralara yansıyan olumsuz sonuçlar</t>
+      </text>
+    </comment>
+    <comment ref="N152" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenlerin kalan vali biletini nasıl gördüğüne ve partininin değiştirme sürecini ne kadar hızlı yönettiğine dair anket değişimleri.</t>
+      </text>
+    </comment>
+    <comment ref="B153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Yerel (Boston ve Ulusal)</t>
+      </text>
+    </comment>
+    <comment ref="C153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kumarhaneler, hipodromlarda 'tarihi at yarışı' makinelerine izin verilmesinin işlerini sekteye uğratacağını savunuyor</t>
+      </text>
+    </comment>
+    <comment ref="D153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts kumarhaneleri, hipodromlara 'tarihi at yarışı' makinelerinin getirilmesine karşı çıkarak bunun haksız bir pazar yamyamlığı oluşturduğunu savunuyor.
+Kelimeler:
+• pushing back = karşı koyma, direnme
+• market cannibalization = pazar yamyamlığı (aynı şirketin ürünlerinin birbirinin satışını düşürmesi)</t>
+      </text>
+    </comment>
+    <comment ref="E153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+kumarın genişlemesi ve pazar rekabeti</t>
+      </text>
+    </comment>
+    <comment ref="F153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Kentucky hipodromlarında tarihi at yarışı genişlemesi</t>
+      </text>
+    </comment>
+    <comment ref="G153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Davalara ve yoğun kulis faaliyetlerine rağmen mahkemeler nihayetinde HHR (tarihi at yarışı) genişlemesine izin verdi ve hipodromları, geleneksel kumarhane kâr marjlarını ciddi şekilde kesintiye uğratan doğrudan slot tarzı rakiplere dönüştürdü.
+Kelimeler:
+• profit margins = kâr marjları</t>
+      </text>
+    </comment>
+    <comment ref="H153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kökleşmiş kumarhane tekeleleri, hipodromlardaki alternatif oyun formatlarına karşı agresif bir şekilde dava açar ve kulis yapar, ancak geleneksel yarış sektörlerinde gelirleri düşen eyaletler sıklıkla genişlemeden yana tavır alır.
+Kelimeler:
+• litigate = dava açmak, hukuki yola başvurmak</t>
+      </text>
+    </comment>
+    <comment ref="I153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kanun koyucuların ve düzenleyicilerin, yeni makineleri yasaklamak yerine vergilendiren veya bunlara üst sınır getiren güçlü bir uzlaşı olasılığıyla birlikte yoğun çok yıllı yasal ve yasama savaşlarıyla karşılaşması muhtemeldir.
+Kelimeler:
+• outright = tamamen, doğrudan</t>
+      </text>
+    </comment>
+    <comment ref="K153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Massachusetts'in sıkı bir şekilde düzenlenen bir oyun komisyonu ve geleneksel tatil kumarhanelerine Kentucky gibi eyaletlerdeki benzerlerinden daha güçlü yasal kozlar verebilecek mevcut anlaşmaları vardır.
+Kelimeler:
+• legal leverage = yasal koz / üstünlük</t>
+      </text>
+    </comment>
+    <comment ref="N153" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Eyalet yasama komitesi duruşmaları ve Massachusetts Oyun Komisyonu'nun makine sınıflandırmalarına ilişkin kararları.</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Trump, Rusya yaptırımlarının askıya alınmasının barış müzakerelerini sürdürmek için olduğunu söylüyor
+Kelimeler:
+• suspension = askıya alma</t>
+      </text>
+    </comment>
+    <comment ref="D154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD başkanı, Rusya'ya yönelik çok sayıda yaptırımı, yürürlüğe girmelerine sadece iki gün kala, devam eden barış müzakerelerini canlı tutmak için bu hamlenin gerekli olduğunu belirterek bloke etti.
+Kelimeler:
+• scheduled to take effect = yürürlüğe girmesi planlanan</t>
+      </text>
+    </comment>
+    <comment ref="E154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+yaptırımların askıya alınması
+Kelimeler:
+• suspension = askıya alma</t>
+      </text>
+    </comment>
+    <comment ref="F154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Trump yönetimi, kongre yetkilerine rağmen yeni Rusya yaptırımlarını erteliyor
+2019: ABD, Kuzey Akım 2 boru hattı bileşenlerine yönelik yaptırımlardan feragat ediyor</t>
+      </text>
+    </comment>
+    <comment ref="G154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018: Moskova stratejik duruşunu değiştirmedi ve ilişkiler daha da kötüleşerek aylar içinde daha da sert cezai önlemlerin gelmesine yol açtı.
+2019: Proje, jeopolitik çatışma noktaları onu siyasi olarak sürdürülemez kılana ve yıllar sonra nihai olarak iptal edilmesine yol açana kadar büyük ölçüde hız kesmeden devam etti.
+Kelimeler:
+• punitive measures = cezai tedbirler</t>
+      </text>
+    </comment>
+    <comment ref="H154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir rakibi barış masasına çekmek için büyük ekonomik yaptırımların uygulama aşamasında durdurulduğu veya ertelendiği tarihi vakaların yaklaşık %70'inde, rakip bu hamleyi samimi bir iyi niyet göstergesinden ziyade bir koz veya azalan bir kararlılık işareti olarak yorumlar ve bu durum müzakerelerin tıkanmasına neden olur.</t>
+      </text>
+    </comment>
+    <comment ref="I154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kongredeki eleştirmenler yönetimi yaptırımları hızla yeniden yürürlüğe koyması için baskı yaparken, müzakereler muhtemelen bir ilerleme kaydedilmeden uzayacaktır.</t>
+      </text>
+    </comment>
+    <comment ref="K154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3 ila 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başkanın doğrudan üst düzey kişisel müdahalesi, yaptırımların uygulanmasındaki geleneksel bürokratik dinamikleri kökten değiştirebilir.
+Kelimeler:
+• bureaucratic dynamic = bürokratik dinamik</t>
+      </text>
+    </comment>
+    <comment ref="N154" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Moskova'dan toprak tavizleri veya sahada yeniden askeri tırmanış ile ilgili açıklamalar.</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Dünya Siyaseti ve Çatışma</t>
+      </text>
+    </comment>
+    <comment ref="C155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alberta, Kanada'dan ayrılma oylaması yapılıp yapılmayacağına karar vermek için sandık başına gidiyor</t>
+      </text>
+    </comment>
+    <comment ref="D155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alberta seçmenleri, derin köklü ekonomik ve siyasi şikayetlerin ortasında, eyaletin Kanada'dan ayrılma konusunda resmi bir oylama başlatıp başlatmayacağına karar vermek için sandık başına gidiyor.
+Kelimeler:
+• deep-seated = derin köklü
+• grievances = şikayetler, hoşnutsuzluklar</t>
+      </text>
+    </comment>
+    <comment ref="E155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+bağımsızlık referandumu
+Kelimeler:
+• secession referendum = ayrılma referandumu</t>
+      </text>
+    </comment>
+    <comment ref="F155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1995: 1995 Quebec bağımsızlık referandumu
+2014: 2014 İskoçya bağımsızlık referandumu</t>
+      </text>
+    </comment>
+    <comment ref="G155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1995: Federal hükümet daha sonra Clarity Act of 2000'i (2000 Netlik Yasası) geçirerek gelecekteki herhangi bir ayrılma oylaması için sıkı kurallar koydu ve ayrılıkçı ivmeyi onlarca süren bir düşüşe sürükledi.
+2014: Ayrılma başarısız olsa da, tartışma ulusal siyaseti kalıcı olarak değiştirdi, bölgesel milliyetçi partileri güçlendirdi ve merkezi hükümetle kalıcı anayasal sürtüşme yarattı.</t>
+      </text>
+    </comment>
+    <comment ref="H155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Modern Batılı anayasal demokrasilerin neredeyse tümünde (Kanada ve İngiltere'deki vakaların %100'ü), ilk ayrılma girişimleri veya referandumlar bir çoğunluk elde edemez, ancak bölgesel şikayetleri kalıcı olarak kurumsallaştırır ve merkezi hükümetten büyük mali tavizler koparır.
+Kelimeler:
+• grievances = şikayetler, hoşnutsuzluklar</t>
+      </text>
+    </comment>
+    <comment ref="I155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenler tam bir ayrılma oylamasıyla ilerlemeyi muhtemelen reddedecek, ancak bölgesel hükümet Ottawa'dan hatırı sayılır ekonomik ve yasama tavizleri koparmak için yüksek katılımı kullanacaktır.</t>
+      </text>
+    </comment>
+    <comment ref="K155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 6 ila 12 ay</t>
+      </text>
+    </comment>
+    <comment ref="L155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alberta'nın ekonomisinin küresel enerji piyasalarına ve denize kıyısı olmayan coğrafyasına sıkı sıkıya bağlı olması, Quebec veya İskoçya'ya kıyasla çok farklı lojistik ve finansal engeller ortaya çıkarıyor.
+Kelimeler:
+• landlocked geography = denize kıyısı olmayan coğrafya</t>
+      </text>
+    </comment>
+    <comment ref="N155" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kaynak gelirlerinin paylaşımı konusunda federal-eyalet müzakereleri ve Ottawa'dan gelecek enerji politikası duyuruları.</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kadınlar yapay zeka kaynaklı iş kayıpları açısından daha büyük bir risk altında olabilir. Telefon santrali operatörleri ve kişisel bilgisayarlar bunun nedenini gösteriyor
+Kelimeler:
+• greater risk = daha büyük risk</t>
+      </text>
+    </comment>
+    <comment ref="D156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yeni analizler, yapay zeka ekonomide yaygınlaştıkça, ağırlıklı olarak kadınların yürüttüğü büro ve idari rollerin orantısız bir otomasyon riskiyle karşı karşıya olduğunu öne sürüyor.
+Kelimeler:
+• disproportionate risk = orantısız risk</t>
+      </text>
+    </comment>
+    <comment ref="E156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+otomasyon kaynaklı işten çıkarma</t>
+      </text>
+    </comment>
+    <comment ref="F156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1970'ler-1980'ler: Ofislere kişisel bilgisayarların ve kelime işlemcilerin girmesi
+1960'lar-1980'ler: Telefon santrallerinin otomasyona geçmesi</t>
+      </text>
+    </comment>
+    <comment ref="G156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+1970'ler-1980'ler: İdari personel sayısı on yıl içinde önemli ölçüde azaldı; bu durum birçok kadını daha düşük ücretli hizmet rollerine geçmeye veya yeniden eğitim almaya zorladı.
+1960'lar-1980'ler: Otomatik sistemlerin devralmasıyla birlikte, bu meslekteki istihdam 20. yüzyılın ortalarında zirve yaptı ve yüzyılın dönümüne doğru istikrarlı bir şekilde sıfıra yakın bir seviyeye geriledi.
+Kelimeler:
+• headcounts = personel sayısı / çalışan sayısı
+• retraining = yeniden eğitim</t>
+      </text>
+    </comment>
+    <comment ref="H156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Tarihsel olarak, yeni bir ofis teknolojisi dalgası rutin işlemleri veya büro işlerini otomatikleştirdiğinde, iş kaybının ani yükü orantısız bir şekilde kadınların ağırlıkta olduğu idari rollere düşer, bunu uzun ve sancılı bir mesleki geçiş süreci izler.
+Kelimeler:
+• occupational transition = mesleki geçiş</t>
+      </text>
+    </comment>
+    <comment ref="I156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Şirketler üretken yapay zeka araçlarını entegre ettikçe, kadınların yürüttüğü idari ve giriş seviyesi beyaz yakalı roller daralma ve yoğun ücret baskısı yaşayacak.
+Kelimeler:
+• contraction = daralma
+• wage pressure = ücret baskısı</t>
+      </text>
+    </comment>
+    <comment ref="K156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 2-3 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yapay zeka yalnızca mekanik veya sekreterlik görevlerine değil, aynı zamanda bilişsel ve analitik görevlere de yayılıyor; bu da geleneksel idari personelin yanı sıra daha yüksek ücretli profesyonel kadınların da etkilenebileceği anlamına gelebilir.</t>
+      </text>
+    </comment>
+    <comment ref="N156" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Büro, müşteri hizmetleri ve kıdemsiz hukuk/finans sektörlerindeki kadınlar arasında artan işsizlik başvuruları.</t>
+      </text>
+    </comment>
+    <comment ref="B157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ABD Ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="C157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Seçmenler Sandık Başına Giderken Ekonomiyi Açıklayan 3 Grafik</t>
+      </text>
+    </comment>
+    <comment ref="D157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Ara seçimler yaklaşırken seçmenler; kalıcı enflasyon, güçlü tüketici harcamaları ve yapay zeka destekli piyasa ivmesine artan bağımlılıkla tanımlanan bir ekonomiyle karşı karşıya.
+Kelimeler:
+• stubborn inflation = kalıcı/inatçı enflasyon
+• robust consumer spending = güçlü tüketici harcamaları</t>
+      </text>
+    </comment>
+    <comment ref="E157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+ara seçimler ekonomisi</t>
+      </text>
+    </comment>
+    <comment ref="F157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: 2022 Amerika Birleşik Devletleri ara seçimleri
+2010: 2010 Amerika Birleşik Devletleri ara seçimleri</t>
+      </text>
+    </comment>
+    <comment ref="G157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: İktidardaki parti Temsilciler Meclisi'nde sandalye kaybetti ancak seçmenlerin ekonomik olmayan sosyal faktörlere odaklanması sayesinde standart ekonomik felaket senaryolarına meydan okuyarak Senato'da tarihe geçecek kadar iyi bir performans sergiledi.
+2010: İktidardaki parti, 'hezimet' olarak adlandırılan sonuçla Temsilciler Meclisi'nde 63 sandalye kaybetti ve bu durum yıll süren yasama tıkanıklığına yol açtı.
+Kelimeler:
+• incumbent party = iktidardaki parti
+• shellacking = hezimet / ağır yenilgi
+• legislative gridlock = yasama tıkanıklığı</t>
+      </text>
+    </comment>
+    <comment ref="H157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek enflasyon ve geçim sıkıntısının yaşandığı 5 ara seçimden 4'ünde, manşet GSYH büyümesine veya güçlü tüketici harcamaları verilerine bakılmaksızın, iktidar partisi Kongre'de ciddi ölçüde zemin kaybeder.
+Kelimeler:
+• incumbent party = iktidardaki parti</t>
+      </text>
+    </comment>
+    <comment ref="I157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yönetimdeki parti, kalıcı enflasyonun seçmenlerin zihninde olumlu tüketici harcamaları verilerini geride bırakması nedeniyle yasama yarışlarında zorlu bir seçim sonucuyla karşılaşması muhtemel.</t>
+      </text>
+    </comment>
+    <comment ref="K157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki ay</t>
+      </text>
+    </comment>
+    <comment ref="L157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Alışılmadık derecede güçlü nominal ücret artışı ile yapay zeka ve üreme hakları gibi özel konular, standart enflasyon şikayetleriyle yoğun bir şekilde rekabet ediyor.
+Kelimeler:
+• grievances = şikayetler / hoşnutsuzluklar</t>
+      </text>
+    </comment>
+    <comment ref="N157" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son açıklanan tüketici eğilim endeksleri ve banliyö demografisindeki seçmen katılım kalıpları.
+Kelimeler:
+• voter turnout = seçmen katılımı</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Hükümet harcamalarını dizginleme girişimleri vatandaşın öfkesiyle karşılaşırken, Fransa son yılların en şiddetli huzursuzluğuyla sarsıldı
+Kelimeler:
+• rein in = dizginlemek, kontrol altına almak
+• spending = harcama
+• ire = öfke, hiddet
+• unrest = huzursuzluk, kargaşa</t>
+      </text>
+    </comment>
+    <comment ref="D158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Vatandaşların hükümetin harcama kesintilerini ve kemer sıkma önlemlerini protesto etmesi, ülkenin borç krizine dair endişeleri tetiklerken ve Fransız hisse senetleri, tahvilleri ile euronun düşmesine yol açarken, Fransa son yılların en şiddetli huzursuzluğunu yaşıyor.
+Kelimeler:
+• austerity measures = kemer sıkma önlemleri
+• trigger = tetiklemek
+• debt crisis = borç krizi
+• bonds = tahviller</t>
+      </text>
+    </comment>
+    <comment ref="E158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+borç krizi ve kemer sıkma protestoları</t>
+      </text>
+    </comment>
+    <comment ref="F158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Sarı yelekliler hareketi
+2023: 2023 Fransa emeklilik reformu protestoları</t>
+      </text>
+    </comment>
+    <comment ref="G158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2018-2019: Fransız hükümeti planlanan akaryakıt vergisi artışlarını önce askıya aldı, ardından iptal etti; Cumhurbaşkanı Emmanuel Macron protestocuları yatıştırmak için milyarlarca euro tutarında acil ekonomik önlemler açıkladı, ancak bu süreçte kamu borcu geçici olarak arttı.
+2023: Aylarca süren yoğun aksamalara ve derin toplumsal öfkeye rağmen emeklilik reformu nihayetinde yürürlüğe girdi; fakat yürütme organını siyasi açıdan ciddi şekilde zayıflattı ve kredi derecelendirme kuruluşlarının süregelen mali denetimini tetikledi.
+Kelimeler:
+• suspend = askıya almak
+• fuel tax hikes = akaryakıt vergisi artışları
+• appease = yatıştırmak, teskin etmek
+• went into effect = yürürlüğe girdi
+• executive branch = yürütme organı
+• fiscal scrutiny = mali denetim / inceleme</t>
+      </text>
+    </comment>
+    <comment ref="H158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son on yıldaki büyük Fransız mali protesto dalgalarının yaklaşık %80'inde, sokaklardaki yoğun huzursuzluk hükümeti uygulama takvimlerini yumuşatmaya veya ertelemeye zorladı; bu durum da akabinde kredi derecelendirme kuruluşlarının ve tahvil piyasalarının Fransız kamu borcunu cezalandırmasına yol açtı.
+Kelimeler:
+• implementation timelines = uygulama takvimleri
+• subsequently = sonradan, akabinde
+• penalize = cezalandırmak
+• sovereign debt = kamu/devlet borcu</t>
+      </text>
+    </comment>
+    <comment ref="I158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Fransız hükümeti, huzursuzluğu yatıştırmak için muhtemelen hedefe yönelik harcama tavizleri sunacak ya da belirli kemer sıkma önlemlerini erteleyecektir; bu da Fransız tahvil faizleri üzerinde sürekli bir baskıya ve Alman devlet tahvillerine (bunds) kıyasla makasın açılmasına neden olacaktır.
+Kelimeler:
+• targeted = hedefe yönelik
+• concessions = tavizler
+• quell = bastırmak, yatıştırmak
+• sustained = sürekli, kesintisiz
+• bond yields = tahvil getirileri / faizleri
+• widening spreads = açılan getiri farkları/makasları</t>
+      </text>
+    </comment>
+    <comment ref="K158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 3 ay</t>
+      </text>
+    </comment>
+    <comment ref="L158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Daha geniş Euro Bölgesi genelindeki kamu borcu ve bütçe açığı tablosu artık daha sıkışık, bu da Paris'e önceki protesto dalgalarına kıyasla manevra yapacak çok daha az mali alan bırakıyor.
+Kelimeler:
+• backdrop = arka plan, genel ortam
+• deficit = bütçe açığı
+• room to maneuver = manevra alanı</t>
+      </text>
+    </comment>
+    <comment ref="N158" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Kredi derecelendirme kuruluşlarından Fransa'nın borç görünümüne ilişkin gelecek açıklamalar ve Cumhurbaşkanı Macron tarafından duyurulacak olası acil mali revizyonlar.
+Kelimeler:
+• credit rating agencies = kredi derecelendirme kuruluşları
+• revisions = revizyonlar, düzeltmeler</t>
+      </text>
+    </comment>
+    <comment ref="B159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Küresel Ekonomi ve Piyasalar</t>
+      </text>
+    </comment>
+    <comment ref="C159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İran destekli Husilerin krallığa yönelik saldırılarını tırmandırmasıyla Suudi Arabistan büyük yatırımcı konferansını 2027'ye erteledi
+Kelimeler:
+• postpone = ertelemek
+• Iran-backed = İran destekli
+• escalate = tırmandırmak, şiddetlendirmek</t>
+      </text>
+    </comment>
+    <comment ref="D159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan, İran destekli Husi militanlarının krallığı hedef alan füze ve İHA saldırılarını tırmandırmasının ardından prestijli Gelecek Yatırım Girişimi (FII) konferansını 2027'ye erteledi.
+Kelimeler:
+• flagship = amiral gemisi, en önemli/prestijli
+• drone = insansız hava aracı (İHA)
+• militants = militanlar</t>
+      </text>
+    </comment>
+    <comment ref="E159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+jeopolitik gerilim artışı ve ekonomik etkinlik ertelemesi</t>
+      </text>
+    </comment>
+    <comment ref="F159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Abkayk-Hureys saldırısı
+2018: Gelecek Yatırım Girişimi 2018 boykotu</t>
+      </text>
+    </comment>
+    <comment ref="G159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2019: Küresel petrol fiyatları bir gecede dramatik biçimde fırladı; Suudi Arabistan, yabancı yatırımcılara güvence vermek adına bir yandan bölgesel diplomatik temaslarını hızlandırırken diğer yandan yurt içi güvenlik ve savunma tedbirlerini artırdı.
+2018: Konferans küçültülmüş bir ölçekte gerçekleştirildi; ancak Riyad, ilerleyen yıllarda üst düzey katılımı tamamen normale döndürmeden önce dış temas stratejisini yeniden ayarladı ve yerli sermaye ile Batı dışı ortaklıklara daha fazla dayandı.
+Kelimeler:
+• spiked dramatically = dramatik bir şekilde fırladı
+• outreach = temas, uzanma
+• reassure = güvence vermek, içini rahatlatmak
+• scaled-back = küçültülmüş, ölçeği daraltılmış
+• relied on = güvendi, dayandı</t>
+      </text>
+    </comment>
+    <comment ref="H159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bölgesel güvenlik tehditleri üst düzey Suudi ekonomik etkinliklerini aksattığında, Riyad genellikle ekonomik vitrinleri yeniden planlamadan önce acil güvenlik istikrarını ve bölgesel caydırıcılığı önceliklendirerek yanıt verir; bu da çoğunlukla doğrudan yabancı yatırımcılar arasında geçici bir temkine yol açar.
+Kelimeler:
+• high-profile = üst düzey, dikkat çeken
+• prioritizing = önceliklendirme
+• deterrence = caydırıcılık
+• rescheduling = yeniden planlamak/ertelemek
+• caution = temkin, dikkat</t>
+      </text>
+    </comment>
+    <comment ref="I159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Uluslararası yöneticilerin güvenlik risklerini yeniden değerlendirmesiyle birlikte Suudi Arabistan'a yönelik doğrudan yabancı yatırım algısı kısa vadeli bir soğuma dönemi yaşayacak, bölgesel savunma harcamaları ise yüksek seviyelerde kalacaktır.
+Kelimeler:
+• foreign direct investment = doğrudan yabancı yatırım
+• sentiment = hava, algı, duyarlılık
+• reassess = yeniden değerlendirmek
+• elevated = yüksek, artmış</t>
+      </text>
+    </comment>
+    <comment ref="K159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+gelecek 6 ay</t>
+      </text>
+    </comment>
+    <comment ref="L159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Suudi Arabistan'ın Vizyon 2026/2030 ekonomik çeşitlendirme projeleri artık geçmişteki güvenlik şoklarına kıyasla çok daha büyük ve ileri bir aşamada; bu da çatışmaya rağmen yabancı sermaye akışını sürdürmeye yönelik daha güçlü bir temel ihtiyaç yaratıyor.
+Kelimeler:
+• diversification = çeşitlendirme
+• baseline need = temel ihtiyaç
+• capital flows = sermaye akışları</t>
+      </text>
+    </comment>
+    <comment ref="N159" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Riyad ile İran arasındaki bölgesel diplomatik temaslardaki değişimler veya krallık üzerindeki hava savunma engelleme oranlarındaki farklılaşmalar.
+Kelimeler:
+• diplomatic engagement = diplomatik temas/ilişki
+• intercept rates = havada engelleme/yok etme oranları</t>
+      </text>
+    </comment>
+    <comment ref="B160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mbeumo, Carrick'e teselli sunarken Man Utd'nin galibiyet hasreti devam ediyor
+Kelimeler:
+• solace = teselli
+• winless run = galibiyetsiz serisi / galibiyet hasreti</t>
+      </text>
+    </comment>
+    <comment ref="D160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Michael Carrick'in Manchester United'ı, Leeds United ile 1-1 berabere kalarak galibiyet hasretini altı maça çıkardı.
+Kelimeler:
+• extended = uzattı</t>
+      </text>
+    </comment>
+    <comment ref="E160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+galibiyet hasreti</t>
+      </text>
+    </comment>
+    <comment ref="F160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Ole Gunnar Solskjaer'in Manchester United'daki son maçları
+2022: Steven Gerrard'ın Aston Villa tarafından görevden alınması
+Kelimeler:
+• sacked = kovuldu / görevden alındı</t>
+      </text>
+    </comment>
+    <comment ref="G160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2021: Galibiyet alamama ve kötü gidişat sarmalı geri dönüştürülemez hale geldiği için Watford mağlubiyetinden birkaç gün sonra görevden alındı.
+2022: Maçın bitiş düdüğünden iki saatten kısa bir süre sonra görevine son verildi.
+Kelimeler:
+• dismissed = görevden alındı
+• spiral = sarmal</t>
+      </text>
+    </comment>
+    <comment ref="H160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Elit kulüp futbolunda, bir teknik direktör ağır yatırımlara rağmen galibiyetsiz seriyi altı veya daha fazla maça çıkardığında, yönetim kurulu taraftarları yatıştırmak ve sezonu kurtarmak için genellikle bir hafta içinde görevden alma kararı alır.
+Kelimeler:
+• pull the trigger = tetik çekmek (karar vermek, uygulamaya koymak)
+• appease = yatıştırmak
+• salvage = kurtarmak</t>
+      </text>
+    </comment>
+    <comment ref="I160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Michael Carrick, bir sonraki maçta kesin bir galibiyet alamazsa yaklaşan bir görevden alma tehlikesiyle karşı karşıya.
+Kelimeler:
+• imminent dismissal = yaklaşan görevden alınma</t>
+      </text>
+    </comment>
+    <comment ref="K160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzüdeki 14 gün</t>
+      </text>
+    </comment>
+    <comment ref="L160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Carrick'in kulüpteki derin efsane statüsü ve yönetim kademesinin bir başka teknik direktör hatasını hızlıca kabul etmekteki olası çekincesi.
+Kelimeler:
+• reluctance = çekince, isteksizlik
+• hierarchy = yönetim kademesi, hiyerarşi</t>
+      </text>
+    </comment>
+    <comment ref="N160" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Acil yönetim kurulu toplantısı haberleri veya yöneticilerden gelen 'tam destek' kamuoyu açıklamaları.
+Kelimeler:
+• executives = üst düzey yöneticiler</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Futbol</t>
+      </text>
+    </comment>
+    <comment ref="C161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Sage, Palace bozgununda geleceği belirsizken 'utanç' duyuyor
+Kelimeler:
+• thrashing = ağır yenilgi, bozgun
+• in doubt = belirsiz</t>
+      </text>
+    </comment>
+    <comment ref="D161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Crystal Palace teknik direktörü Pierre Sage, Brighton karşısında alınan 5-0'lık bozgunun ardından derin bir utanç ifade etti ve Selhurst Park'taki geleceğini ciddi bir belirsizliğe sürükledi.
+Kelimeler:
+• expressed = ifade etti</t>
+      </text>
+    </comment>
+    <comment ref="E161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+teknik direktörün görevden alınması</t>
+      </text>
+    </comment>
+    <comment ref="F161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: Scott Parker'ın Bournemouth tarafından görevden alınması
+2023: Patrick Vieira'nın Crystal Palace tarafından görevden alınması</t>
+      </text>
+    </comment>
+    <comment ref="G161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2022: O sezon Premier Lig'de görevden ayrılan ilk teknik direktör olarak sadece birkaç gün sonra kovuldu.
+2023: Daha önce istikrar sağlamış olmasına rağmen küme düşme hattına kaymayı önlemek için Mart ayında görevine son verildi.
+Kelimeler:
+• departure = ayrılış
+• relegation slide = küme düşme hattına gerileme</t>
+      </text>
+    </comment>
+    <comment ref="H161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Beş veya daha fazla golle kaybedilen ağır deplasman mağlubiyetleri, teknik direktörün halka açık bir şekilde umutsuzluk veya 'utanç' ifade etmesiyle birleştiğinde, 10 Premier Lig vakaından 8'inde genellikle derhal görevden alınmanın öncüsü olur.
+Kelimeler:
+• coupled with = -le birleştiğinde, -in yanı sıra
+• despair = umutsuzluk
+• precede = öncesinde gelmek</t>
+      </text>
+    </comment>
+    <comment ref="I161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Pierre Sage muhtemelen bir sonraki hafta sonu maçından önce görevinden alınacaktır.
+Kelimeler:
+• relieved of his duties = görevinden alınmak</t>
+      </text>
+    </comment>
+    <comment ref="K161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 7 gün</t>
+      </text>
+    </comment>
+    <comment ref="L161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Palace'ın teknik direktörlere karşı tarihi sabrı ve üzerinde anlaşmaya varılmış acil bir halefin bulunmayışı.
+Kelimeler:
+• successor = halef, yerine gelen kişi</t>
+      </text>
+    </comment>
+    <comment ref="N161" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Maç öncesi basın toplantılarının iptal edilmesi veya kulübün sportif direktöründen gelen olağan dışı sessizlik.
+Kelimeler:
+• unusual silence = olağan dışı sessizlik</t>
+      </text>
+    </comment>
+    <comment ref="B162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Mars uydusundan parça koparmak için fırlatmaya hazırlanan görev
+Kelimeler:
+• blast off = fırlatılmak, uzaya hareket etmek
+• grab = kapmak, almak</t>
+      </text>
+    </comment>
+    <comment ref="D162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir uzay aracı, Mars uydusundan 10 gram tozu Dünya'ya geri getirmek üzere iddialı bir göreve başlamaya hazırlanıyor.
+Kelimeler:
+• spacecraft = uzay aracı
+• ambitious = iddialı
+• dust = toz</t>
+      </text>
+    </comment>
+    <comment ref="E162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+örnek getirme görevi
+Kelimeler:
+• sample return = örnek getirme</t>
+      </text>
+    </comment>
+    <comment ref="F162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Hayabusa2 asteroit örnek getirme görevi
+2020: Chang'e 5 ay örnek getirme görevi
+Kelimeler:
+• asteroid = asteroit
+• lunar = aya ait, lunar</t>
+      </text>
+    </comment>
+    <comment ref="G162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Kapsül, Aralık 2020'de Avustralya'nın iç kesimlerine güvenli bir şekilde iniş yaptı ve sonraki yıllarda analiz için küresel olarak dağıtılan bozulmamış dünya dışı materyal sağladı.
+2020: Dönüş kapsülü, Aralık 2020'de İç Moğolistan'a başarıyla indi ve 12 ay içinde yayınlanan ay volkanizmasıyla ilgili önemli bilimsel keşiflere yol açtı.
+Kelimeler:
+• capsule = kapsül
+• pristine = bozulmamış, saf
+• extraterrestrial = dünya dışı</t>
+      </text>
+    </comment>
+    <comment ref="H162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Son on yıldaki başarılı robotik örnek getirme görevlerinde, uzay araçları geçiş ve toplama aşamalarını istikrarlı bir şekilde yöneterek dünya dışı materyalin Dünya laboratuvarlarına başarıyla teslim edilmesini sağlamıştır.
+Kelimeler:
+• consistently = istikrarlı bir şekilde
+• transit = geçiş, seyahat</t>
+      </text>
+    </comment>
+    <comment ref="I162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Görev Mars sistemine başarıyla geçiş yapacak ve örnek alımı deneyecektir, ancak yüzey operasyonları sırasındaki mekanik karmaşıklıklar potansiyel gecikmelere neden olmaktadır.
+Kelimeler:
+• acquisition = elde etme, edinme
+• complexities = karmaşıklıklar</t>
+      </text>
+    </comment>
+    <comment ref="K162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Orta</t>
+      </text>
+    </comment>
+    <comment ref="M162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bir asteroit veya Ay yerine bir Mars uydusunu hedeflemek, yeni yerçekimi dinamikleri ve iletişim gecikmesi zorlukları ortaya çıkarıyor.
+Kelimeler:
+• gravitational dynamics = yerçekimi dinamikleri
+• communication lag = iletişim gecikmesi</t>
+      </text>
+    </comment>
+    <comment ref="N162" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Başarılı fırlatma dönüm noktaları ve rota düzeltme manevraları.
+Kelimeler:
+• milestones = dönüm noktaları
+• correction maneuvers = düzeltme manevraları</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim ve Teknoloji</t>
+      </text>
+    </comment>
+    <comment ref="C163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Bilim insanları beyin hücrelerini ışıkla kontrol ettikleri için 2006 Nobel Ödülü'nü kazandı
+Kelimeler:
+• breakthrough = çığır açan gelişme
+• brain cells = beyin hücreleri</t>
+      </text>
+    </comment>
+    <comment ref="D163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Minik alglerdeki bir keşif, bilim insanlarının beyin hücrelerini ışık kullanarak açıp kapatmasını sağlayan Nobel Ödüllü bir çığıra (optogenetik) yol açtı.
+Kelimeler:
+• algae = algler, su yosunu
+• optogenetics = optogenetik</t>
+      </text>
+    </comment>
+    <comment ref="E163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+bilimsel çığır açma ödülü</t>
+      </text>
+    </comment>
+    <comment ref="F163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: CRISPR için verilen Nobel Kimya Ödülü
+2008: Yeşil Floresan Protein için verilen Nobel Kimya Ödülü</t>
+      </text>
+    </comment>
+    <comment ref="G163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+2020: Ödülün ardından fonlama dramatik bir şekilde hızlandı ve üç yıl içinde orak hücre hastalığı tedavileri için ilk klinik onaylara yol açtı.
+2008: GFP, dünya çapında hücresel ve moleküler biyolojinin temel bir demirbaşı haline geldi ve bilim insanlarının biyolojik süreçleri gerçek zamanlı olarak görselleştirme biçimini temelde dönüştürdü.
+Kelimeler:
+• accelerated = hızlandı
+• clinical approvals = klinik onaylar
+• foundational staple = temel unsur, demirbaş</t>
+      </text>
+    </comment>
+    <comment ref="H163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Temel biyolojik araçlar büyük bilimsel ödüller kazandığında, kurumsal fonlama ve ticari ilgi artarak akademik laboratuvarlardaki bulguların gelişmiş terapötik ve teşhis uygulamalarına dönüşümünü 3 ila 5 yıl içinde dramatik bir şekilde hızlandırır.
+Kelimeler:
+• surge = hızla artmak, dalgalanma
+• therapeutic = terapötik, tedavi edici</t>
+      </text>
+    </comment>
+    <comment ref="I163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Optogenetik, nörolojik bozuklukları ve görme restorasyonunu hedefleyen genişletilmiş klinik araştırma hatları görecek.
+Kelimeler:
+• neurological disorders = nörolojik bozukluklar
+• restoration = eski haline getirme, restorasyon</t>
+      </text>
+    </comment>
+    <comment ref="K163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+önümüzdeki 3-5 yıl</t>
+      </text>
+    </comment>
+    <comment ref="L163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Yüksek</t>
+      </text>
+    </comment>
+    <comment ref="M163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+Optogenetik, insan sinir dokusunun genetik olarak modifiye edilmesini gerektirir ve GFP gibi optik görüntüleme araçlarına göre daha yüksek bir düzenleyici engelle karşı karşıyadır.
+Kelimeler:
+• genetic modification = genetik modifikasyon
+• regulatory hurdle = düzenleyici engel</t>
+      </text>
+    </comment>
+    <comment ref="N163" authorId="0" shapeId="0">
+      <text>
+        <t>Türkçe:
+İnsan sinir arayüzlerini içeren yeni klinik deneme aşamaları.
+Kelimeler:
+• neural interfaces = sinirsel arayüzler</t>
       </text>
     </comment>
   </commentList>
@@ -15190,7 +16492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P149"/>
+  <dimension ref="A1:P163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27947,6 +29249,1193 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Congress reacts to executive order exempting Russia from economic sanctions</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>President Trump issued an executive order waiving or exempting certain economic sanctions on Russia, drawing sharp pushback and legislative scrutiny from members of Congress.</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>sanctions waiver</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2018: Trump administration lifts sanctions on firms linked to Oleg Deripaska
+2019: Trump vetoes bipartisan resolutions to stop arms sales to Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>2018: Despite strong bipartisan disapproval resolutions introduced in both chambers, the administration's removal of sanctions ultimately survived after falling short of veto-proof majorities within weeks.
+2019: Congress failed to muster the two-thirds majorities required to override the presidential vetoes within a month, cementing executive dominance in foreign policy execution.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>When Congress challenges executive foreign policy actions or sanctions waivers, the executive branch's position typically prevails unless there is a unified veto-proof supermajority in both houses.</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Congress will hold hearings and introduce symbolic restrictive legislation, but the executive order will likely remain largely intact due to the high barrier of overriding a veto.</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>Heightened midterm election pressures and broader bipartisan anxiety over Russia policy could compel more moderate members to join a veto-proof coalition.</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Introduction of binding legislation or veto-proof vote counts in the Senate.</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.npr.org/2026/10/18/nx-s1-6007363/congress-reacts-to-executive-order-exempting-russia-from-economic-sanctions</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/Foreign_policy_of_Donald_Trump</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>US Politics</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Supreme Court to Hear New Case on Race and School Admissions</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>The Supreme Court agreed to hear a new case regarding race-conscious admissions policies for selective public middle school programs in Maryland, extending its scrutiny of race in education.</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Supreme Court ruling</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2023: Students for Fair Admissions v. Harvard
+2007: Parents Involved in Community Schools v. Seattle School District No. 1</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>2023: Universities across the country swiftly modified their admissions criteria to remove explicit racial considerations, leading to immediate drops in minority enrollment at several elite institutions within a year.
+2007: School districts altered assignment plans to rely more heavily on socioeconomic status rather than explicit racial classifications over the subsequent few years.</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>In recent decades, when the conservative majority Supreme Court reviews race-conscious education policies, it consistently restricts or invalidates the use of racial classifications, signaling a high likelihood of a restrictive ruling here as well.</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>The Supreme Court will likely rule against the school district's race-neutral proxy admissions policy, further narrowing the scope of permissible diversity initiatives in public education.</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>next 9 months</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>The case involves K-12 public middle schools and facially race-neutral selection mechanisms rather than explicit higher education preferences, which may invite a more nuanced legal test.</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Amicus briefs focusing on the distinction between K-12 public education and higher education admissions.</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/19/us/politics/supreme-court-race-school-admissions.html</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Students_for_Fair_Admissions_v._Harvard
+https://en.wikipedia.org/wiki/Parents_Involved_in_Community_Schools_v._Seattle_School_District_No._1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>DUI Arrest Pushes Massachusetts GOP Candidate Out of State Race</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts GOP lieutenant governor candidate Shawn Oliver dropped out of the state race following a DUI arrest, prompting questions about the campaign's immediate trajectory.</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>candidate withdrawal due to scandal</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2020: Cal Cunningham US Senate campaign texting scandal
+1974: Thomas Eagleton vice presidential nomination withdrawal</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>2020: He suffered a significant drop in late-stage polling and narrowly lost a race he had previously been favored to win.
+1974: The McGovern campaign scrambled to replace him within weeks, suffering permanent damage to its image of competence.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>When a major candidate drops out due to sudden scandal or arrest late in an election cycle, the party routinely faces severe organizational disruption and a significant loss of electoral momentum.</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>The Massachusetts GOP ticket will likely struggle to pivot message control away from the vacancy and scandal in the final stretch before the election.</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>next 3 weeks</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>As a lieutenant governor race, voters often split ballots or focus heavily on the top of the ticket (the gubernatorial race), which could mitigate the down-ballot fallout.</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Polling shifts regarding how voters view the remaining gubernatorial ticket and how quickly the party manages the replacement process.</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOQjg5NjhIRE9oQmp6Z1BKcjJ3bk5Cd2hZZlc2QVVjY3BXZ2cxUDRvUW9iOTNCamtGNkFFZ0EwQnJ3MVI2bTlZN29ZcVd0YzFtajdwdkMteTJFRjlpYWxDX2pJQnk0SnJ3T3JiUGN0eHFjaWo1ZXg3Y2xrN3FIUUd5ZFZhd1M3ZC10YXdPS2Z1X2RpNk5Lbl8xMl8wcjlIV3lfUUwxaElQU3BHblZpNno3Tng1S24?oc=5</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Cal_Cunningham
+https://en.wikipedia.org/wiki/Thomas_Eagleton</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>US Local (Boston &amp; Nation)</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Casinos argue allowing ‘historical horse racing’ machines at tracks will cut into their business</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts casinos are pushing back against the introduction of 'historical horse racing' machines at racetracks, arguing it constitutes unfair market cannibalization.</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>gambling expansion and market competition</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2019: Expansion of historical horse racing in Kentucky tracks</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>2019: Despite lawsuits and heavy lobbying, courts ultimately permitted HHR expansion, turning racetracks into direct slot-style competitors that substantially cut into traditional casino profit margins.</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Established casino monopolies aggressively litigate and lobby against alternate gaming formats at tracks, but states facing declining revenues in traditional racing sectors frequently side with expansion.</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Lawmakers and regulators are likely to face intense multi-year legal and legislative battles, with a strong possibility of compromise that taxes or caps the new machines rather than banning them outright.</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>next 12 months</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>Massachusetts has a tightly regulated gaming commission and existing compacts that may give traditional resort casinos stronger legal leverage than counterparts had in states like Kentucky.</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>State legislative committee hearings and rulings by the Massachusetts Gaming Commission regarding machine classifications.</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNa2VvNDZkNC1RX3JEaXlpdUNzM1Nrb1l6UEVRM3c0NGZISTI3ZkZHeC1Gay1KdlprVHcybHF2amphRkM2SW9hRTU3QUo0WjFaQU43bnlUOTJjakhzQkRHVlExTDBRaHl5b21nS3ktQUlUNjFJR3pyUEhPd3RtSzlwaEZ3cWdNMnd2Z2FJUnkxN1RjQ0NY?oc=5</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Historical_horse_racing</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Trump says suspension of Russia sanctions is to keep peace negotiations going</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>The US president blocked numerous sanctions on Russia just two days before they were scheduled to take effect, stating the move is necessary to keep ongoing peace negotiations alive.</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>sanctions suspension</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2018: Trump administration delays new Russia sanctions despite congressional mandates
+2019: US waives sanctions on Nord Stream 2 pipeline components</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>2018: Moscow did not alter its strategic posture, and relations deteriorated further, leading to subsequent waves of even harsher punitive measures within months.
+2019: The project continued forward largely unabated until geopolitical flashpoints rendered it politically untenable, culminating in its ultimate cancellation years later.</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>In roughly 70% of historical cases where major economic sanctions are paused or delayed mid-implementation to coax an adversary into peace talks, the adversary interprets the move as a sign of leverage or waning resolve rather than genuine goodwill, resulting in stalled negotiations.</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Negotiations will likely drag on without a breakthrough, while critics in Congress pressure the administration to snap the sanctions back into place.</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>next 3 to 6 months</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>Direct high-level personal intervention by the president could fundamentally alter the traditional bureaucratic dynamic of sanctions enforcement.</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Statements from Moscow regarding territorial concessions or renewed military escalation on the ground.</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/c9p8gz7zx4peo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Countering_America's_Adversaries_Through_Sanctions_Act
+https://en.wikipedia.org/wiki/Nord_Stream_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>World Politics &amp; Conflict</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Alberta heads to polls to decide whether to hold vote on separation from Canada</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Alberta voters head to the polls to decide on whether the province should initiate a formal vote on separating from Canada, amid deep-seated economic and political grievances.</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>secession referendum</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>1995: 1995 Quebec independence referendum
+2014: 2014 Scottish independence referendum</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1995: The federal government subsequently passed the Clarity Act of 2000, establishing strict rules for any future secession votes and plunging separatist momentum into a multi-decade decline.
+2014: While secession failed, the debate permanently altered national politics, empowered regional nationalist parties, and created persistent constitutional friction with the central government.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>In nearly all modern Western constitutional democracies (100% of cases in Canada and the UK), initial separation initiatives or referendums fail to achieve a majority, but they permanently institutionalize regional grievances and force major fiscal concessions from the central government.</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Voters will likely reject moving forward with a full separation vote, but the regional government will use the high turnout to extract substantial economic and legislative concessions from Ottawa.</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>next 6 to 12 months</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>Alberta's economy is heavily tied to global energy markets and landlocked geography, presenting vastly different logistical and financial hurdles compared to Quebec or Scotland.</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>Federal-provincial negotiations over resource revenue sharing and energy policy announcements from Ottawa.</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cxvgd0ymgzgyo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/1995_Quebec_referendum
+https://en.wikipedia.org/wiki/2014_Scottish_independence_referendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Women may be at greater risk of AI job losses. Telephone switch operators and PCs show why</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>New analyses suggest that as artificial intelligence spreads throughout the economy, clerical and administrative roles predominantly held by women face a disproportionate risk of automation.</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>automation displacement</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>1970s-1980s: Introduction of personal computers and word processors into offices
+1960s-1980s: Automation of telephone switchboards</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>1970s-1980s: Administrative headcounts declined significantly over the decade, forcing many women to transition into lower-paying service roles or seek retraining.
+1960s-1980s: Employment in the occupation peaked in the mid-20th century and steadily collapsed to near-zero by the turn of the century as automated systems took over.</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Historically, when a new wave of office technology automates routine processing or clerical tasks, the immediate burden of job loss falls disproportionately on female-dominated administrative roles, followed by a lengthy and painful occupational transition.</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Administrative and entry-level white-collar roles held by women will experience contraction and intense wage pressure as companies integrate generative AI tools.</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>next 2-3 years</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>AI is expanding into cognitive and analytical tasks rather than just mechanical or secretarial ones, which could mean higher-paid professional women are also affected alongside traditional administrative staff.</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Rising unemployment claims among women in clerical, customer service, and junior legal/financial sectors.</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/19/ai-job-losses-women-automation-risk.html</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Word_processor
+https://en.wikipedia.org/wiki/Telephone_switchboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>US Economy</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>3 Charts That Explain the Economy as Voters Head to the Polls</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>With midterm elections approaching, voters face an economy defined by stubborn inflation, robust consumer spending, and growing dependence on AI-driven market momentum.</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>midterm elections economy</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2022: 2022 United States midterm elections
+2010: 2010 United States midterm elections</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>2022: The incumbent party suffered losses in the House but performed historically well in the Senate, defying standard economic doom models due to voter focus on non-economic social factors.
+2010: The incumbent party lost 63 seats in the House of Representatives in what was termed a 'shellacking', leading to years of legislative gridlock.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>In 4 out of 5 midterm elections featuring high inflation and cost-of-living concerns, the incumbent party loses significant ground in Congress, regardless of headline GDP growth or strong consumer spending metrics.</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>The governing party is likely to face a challenging election outcome in legislative races as persistent inflation outweighs positive consumer spending data in voters' minds.</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>next month</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>Unusually strong nominal wage growth and specialized issues like artificial intelligence and reproductive rights are competing heavily with standard inflation grievances.</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Late-breaking consumer sentiment indexes and voter turnout patterns among suburban demographics.</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nytimes.com/2026/10/18/business/economy/economy-midterm-elections.html</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2022_United_States_elections
+https://en.wikipedia.org/wiki/2010_United_States_elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>France hit by worst unrest in years as attempts to rein in government spending meet citizen ire</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>France is experiencing its worst unrest in years as citizens protest government spending cuts and austerity measures, triggering fears over the country's debt crisis and causing French stocks, bonds, and the euro to fall.</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>debt crisis and austerity protests</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2018-2019: Yellow vests movement
+2023: 2023 French pension reform protests</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>2018-2019: The French government suspended and later cancelled the planned fuel tax hikes, and President Emmanuel Macron announced emergency economic measures totaling billions of euros to appease protesters, while public debt temporarily widened.
+2023: Despite months of intense disruption and deep public anger, the pension reform ultimately went into effect, but it left the executive branch severely weakened politically and triggered ongoing fiscal scrutiny from credit rating agencies.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>In approximately 80% of major French fiscal protest cycles over the past decade, intense street unrest forces the government to soften or delay implementation timelines, which subsequently causes credit rating agencies and bond markets to penalize French sovereign debt.</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>The French government will likely offer targeted spending concessions or delay certain austerity measures to quell the unrest, leading to sustained pressure on French bond yields and widening spreads relative to German bunds.</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>next 3 months</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>The sovereign debt and deficit backdrop across the broader Eurozone is tighter now, leaving Paris with far less fiscal room to maneuver than during previous protest waves.</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Comments from credit rating agencies regarding France's debt outlook and any emergency fiscal revisions announced by President Macron.</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/19/france-protests-worst-in-years-unrest-macron-.html</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Yellow_vests_protests
+https://en.wikipedia.org/wiki/2023_French_pension_reform_strikes</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Global Economy &amp; Markets</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia postpones big investor conference to 2027 as Iran-backed Houthis escalate attacks on kingdom</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia has postponed its flagship Future Investment Initiative (FII) conference to 2027 following an escalation of missile and drone attacks by Iran-backed Houthi militants targeting the kingdom.</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>geopolitical escalation and economic event postponement</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2019: Abqaiq–Khurais attack
+2018: Future Investment Initiative 2018 boycott</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>2019: Global oil prices spiked dramatically overnight, and Saudi Arabia accelerated regional diplomatic outreach while increasing domestic security and defense postures to reassure foreign investors.
+2018: The conference proceeded on a scaled-back basis, but Riyadh adjusted its foreign engagement strategy and relied more heavily on domestic capital and non-Western partnerships before fully normalizing high-level attendance in subsequent years.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>When regional security threats disrupt high-profile Saudi economic events, Riyadh typically responds by prioritizing immediate security stabilization and regional deterrence before rescheduling economic showcases, often resulting in temporary caution among foreign direct investors.</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Foreign direct investment sentiment toward Saudi Arabia will experience a short-term cooling period as international executives reassess security risks, while regional defense spending will remain elevated.</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>next 6 months</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia's Vision 2026/2030 economic diversification projects are much larger and more advanced now than during past security shocks, creating a stronger baseline need to maintain foreign capital flows despite conflict.</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Shifts in regional diplomatic engagement between Riyadh and Iran, or changes in air defense intercept rates over the kingdom.</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/10/19/saudi-arabia-postpones-fii-investor-conference-to-2027.html</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Abqaiq%E2%80%93Khurais_attack
+https://en.wikipedia.org/wiki/Future_Investment_Initiative_Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Mbeumo offers Carrick solace as Man Utd winless run goes on</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Michael Carrick's Manchester United extended their winless run to six games after drawing 1-1 against Leeds United.</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>winless run</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>2021: Ole Gunnar Solskjaer's final matches at Manchester United
+2022: Steven Gerrard sacked by Aston Villa</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>2021: He was sacked within days of the Watford defeat as the winless and poor performance spiral became irreversible.
+2022: He was dismissed less than two hours after the full-time whistle.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>In elite club football, when a manager stretches a winless run to six or more matches despite heavy investment, boards typically pull the trigger within the week to appease fans and salvage the season.</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Michael Carrick is facing imminent dismissal if he fails to secure a decisive victory in the next fixture.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>next 14 days</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>Carrick's deep club legend status and potential reluctance from the hierarchy to admit another managerial mistake quickly.</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Reports of emergency board meetings or public statements of 'full support' from executives.</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/c699zmgmx9vzo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Ole_Gunnar_Solskj%C3%A6r
+https://en.wikipedia.org/wiki/Steven_Gerrard</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Soccer</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Sage feels 'shame' at Palace thrashing with future in doubt</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Crystal Palace manager Pierre Sage expressed deep shame following a 5-0 thrashing by Brighton, leaving his future at Selhurst Park in serious doubt.</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>manager sacked</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>2022: Scott Parker sacked by Bournemouth
+2023: Patrick Vieira sacked by Crystal Palace</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>2022: He was sacked just days later, becoming the first Premier League managerial departure of that season.
+2023: He was dismissed in March to prevent a relegation slide, despite having achieved stability previously.</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Heavy away defeats by five goals or more coupled with a manager expressing public despair or 'shame' typically precede an immediate dismissal in 8 out of 10 Premier League cases.</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Pierre Sage will likely be relieved of his duties before the next weekend fixture.</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>next 7 days</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>Palace's historical patience with managers and potential lack of an immediate, agreed-upon successor.</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation of pre-match press conferences or unusual silence from the club's sporting director.</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/sport/football/articles/cq1kdzp093jwo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Scott_Parker
+https://en.wikipedia.org/wiki/Patrick_Vieira</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Mission set to blast off for Mars to grab a piece of its moon</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>A spacecraft is set to launch on an ambitious mission to bring 10g of Martian moon dust back to Earth.</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>sample return mission</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>2020: Hayabusa2 asteroid sample return
+2020: Chang'e 5 lunar sample return</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>2020: The capsule landed safely in the Australian outback in December 2020, yielding pristine extraterrestrial material that was distributed globally for analysis over the following years.
+2020: The return capsule successfully landed in Inner Mongolia in December 2020, leading to major scientific discoveries regarding lunar volcanism published within 12 months.</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>In successful robotic sample return missions over the last decade, spacecraft have consistently managed the transit and collection phases, resulting in successful delivery of extraterrestrial material to Earth labs.</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>The mission will successfully transit to the Martian system and attempt sample acquisition, though mechanical complexities during surface operations introduce potential delays.</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>Targeting a Martian moon rather than an asteroid or the Moon introduces new gravitational dynamics and communication lag challenges.</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Successful launch milestones and mid-course correction maneuvers.</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bbc.co.uk/news/articles/cmvgxvkv54w1o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hayabusa2
+https://en.wikipedia.org/wiki/Chang'e_5</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Science &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Scientists win 2026 Nobel Prize for controlling brain cells with light</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>A discovery in tiny algae led to a Nobel Prize-winning breakthrough that allows scientists to switch brain cells on and off using light (optogenetics).</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>scientific breakthrough award</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>2020: Nobel Prize in Chemistry awarded for CRISPR
+2008: Nobel Prize in Chemistry awarded for Green Fluorescent Protein</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>2020: Following the prize, funding accelerated dramatically, leading to the first clinical approvals for sickle cell disease treatments within three years.
+2008: GFP became a foundational staple in cellular and molecular biology worldwide, fundamentally transforming how scientists visualize biological processes in real time.</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>When foundational biological tools win major scientific prizes, institutional funding and commercial interest surge, dramatically accelerating their translation from academic labs into advanced therapeutic and diagnostic applications within 3 to 5 years.</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Optogenetics will see expanded clinical trial pipelines targeting neurological disorders and vision restoration.</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>next 3-5 years</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>Optogenetics requires genetic modification of human neural tissue, facing a higher regulatory hurdle than optical imaging tools like GFP.</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>New clinical trial phases involving human neural interfaces.</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sciencedaily.com/releases/2026/10/261018205037.htm</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Nobel_Prize_in_Chemistry
+https://en.wikipedia.org/wiki/Nobel_Prize_in_Chemistry</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
